--- a/testcase/eval_ragas_naive_mix_500cases.xlsx
+++ b/testcase/eval_ragas_naive_mix_500cases.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,12 +490,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,25 +505,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Theo thông tin cung cấp, thuốc Carbogast không được đề cập cụ thể trong tài liệu. Tuy nhiên, có một số nguyên tắc chung mà bạn cần lưu ý khi sử dụng thuốc trong thời kỳ mang thai và cho con bú:
-1. **Chống chỉ định**: Một số thuốc không được khuyến nghị sử dụng trong thời kỳ mang thai và cho con bú vì chúng có thể gây hại cho thai nhi hoặc trẻ sơ sinh. Ví dụ, thuốc Aescin được chống chỉ định cho phụ nữ mang thai và cho con bú ([2]).
-2. **Thận trọng khi sử dụng**: Đối với những loại thuốc khác, cần thận trọng khi sử dụng trong thời kỳ mang thai và cho con bú. Điều này bao gồm việc thảo luận với bác sĩ về lợi ích và nguy cơ của việc sử dụng thuốc. Ví dụ, thuốc Alphalysosine chưa có đầy đủ nghiên cứu về việc sử dụng trong thời kỳ mang thai hoặc cho con bú, vì vậy cần hỏi ý kiến bác sĩ trước khi sử dụng ([10]).
-Do đó, nếu bạn đang mang thai hoặc cho con bú và cần sử dụng thuốc Carbogast, bạn cần tham khảo ý kiến của bác sĩ để đánh giá xem liệu thuốc này có phù hợp không và liệu nó có an toàn không cho cả mẹ và bé.</t>
+          <t>Từ thông tin cung cấp, không có dữ liệu cụ thể nào về thuốc Biviantac hoặc khả năng của nó trong việc điều trị triệu chứng trướng bụng và đầy hơi. Để nhận được lời khuyên chuyên môn về sử dụng bất kỳ loại thuốc nào, bạn nên liên hệ với bác sĩ hoặc dược sĩ.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Không bắt buộc, nên dùng thuốc theo đúng chỉ định của bác sĩ.</t>
+          <t>Có, Biviantac có thể điều trị các tình trạng như trướng bụng, đầy hơi, ợ nóng, ợ hơi hay ợ chua.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -534,203 +531,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ngoài tác dụng giảm đau, **Acepron 250 mg** còn được sử dụng trong việc tối ưu hóa các thuốc chống đau thắt ngực và phòng ngừa các biến cố liên quan đến bệnh mạch vành.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ngoài tác dụng giảm đau, Acepron 250 mg còn có thêm tác dụng giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9937794745262768</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.9999999999</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7484448686065692</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Calci D Hasan không được đề cập cụ thể trong tài liệu cung cấp, nhưng dựa trên thông tin về các thuốc khác, có thể rút ra một số gợi ý:
-1. Nhiều loại thuốc có thể gây tác dụng không mong muốn cho phụ nữ mang thai và cho con bú, bao gồm khả năng gây co bóp tử cung hoặc ảnh hưởng đến thai nhi.
-2. Đối với phụ nữ mang thai, nhiều thuốc có thể ảnh hưởng đến sự phát triển của thai nhi và cần được sử dụng thận trọng.
-3. Với phụ nữ cho con bú, nhiều thuốc có thể bài tiết vào sữa mẹ và ảnh hưởng đến trẻ sơ sinh.
-Do đó, mặc dù không có thông tin cụ thể về Calci D Hasan, tốt nhất là bạn nên hỏi ý kiến bác sĩ hoặc dược sĩ trước khi sử dụng Calci D Hasan nếu đang mang thai hoặc cho con bú. Họ sẽ có thể cung cấp thông tin cụ thể về an toàn của thuốc cho từng trường hợp.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Không, không nên tự ý sử dụng thuốc.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Để sử dụng thuốc Comiaryl một cách hiệu quả và an toàn, bạn cần tuân theo sự hướng dẫn của bác sĩ hoặc dược sĩ. Họ sẽ cung cấp cho bạn thông tin chi tiết về cách sử dụng thuốc này sao cho phù hợp nhất với tình trạng sức khỏe của bạn.
-Nếu bạn gặp bất kỳ thắc mắc nào về việc sử dụng thuốc này, hãy liên hệ với bác sĩ hoặc dược sĩ để được giải đáp. Họ cũng sẽ tư vấn cho bạn về những lợi ích và rủi ro tiềm ẩn khi sử dụng thuốc Comiaryl.
-Hãy nhớ rằng việc tuân thủ điều trị là rất quan trọng để cải thiện sức khỏe của bạn. Nếu bạn tuân thủ đúng hướng dẫn sử dụng, bạn sẽ cảm thấy tốt hơn rất nhiều.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Nên uống nguyên viên thuốc Comiaryl với một cốc nước đầy.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5684225574879388</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.3921056393719847</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dựa trên thông tin từ kiến thức đã cung cấp, không có chi tiết cụ thể về tác động của Calci D Hasan đối với bệnh nhân mắc bệnh lý nền. Tuy nhiên, khi sử dụng bất kỳ loại thuốc nào, đặc biệt là đối với bệnh nhân có tình trạng y tế nền, việc liên hệ với bác sĩ hoặc dược sĩ để được tư vấn kỹ càng là vô cùng quan trọng ([1]). Điều này giúp đảm bảo rằng thuốc sẽ không gây ra tác dụng phụ không mong muốn hoặc tương tác có hại với các loại thuốc khác mà bệnh nhân đang sử dụng.
-Nếu bạn muốn sử dụng Calci D Hasan để điều trị một bệnh lý cụ thể, bạn nên thảo luận về nó với bác sĩ hoặc dược sĩ để nhận được lời khuyên hữu ích nhất ([4]). Họ sẽ có thể xác định liệu thuốc này có phù hợp với tình trạng sức khỏe tổng thể của bạn hay không và đưa ra quyết định về việc sử dụng thuốc dựa trên đánh giá toàn diện về sức khỏe của bạn.
-Việc tuân thủ theo sự hướng dẫn của chuyên gia y tế sẽ giúp cải thiện sức khỏe của bạn một cách hiệu quả ([7]).</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ở bệnh nhân mắc bệnh lý nền, Calci D Hasan có thể gây tăng nhạy cảm với vitamin D, làm tăng nguy cơ gây hại cho sức khỏe.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
@@ -744,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,34 +608,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+          <t>['Nhàm trường: Nhàm trường, giải khát.\nHay ngứa: Hay ngứa là một triệu chứng của nhiễm ký sinh trùng.\nKhóc nhiều, dễ xúc động: Khóc nhiều, dễ xúc động.\nNấm: Nấm là một tình trạng nhiễm trùng phức tạp có thể xuất hiện ở nhiều vị trí khác nhau trên cơ thể con người, từ da, tóc, móng tay, cho đến khoang miệng và vùng hầu họng. Các loại nấm như nấm móng, nấm tóc, nấm da, và lang ben đều thuộc nhóm ký sinh trùng này. Nấm có thể gây ra các vấn đề sức khỏe như nhiễm trùng vết thương ở khoang miệng và vùng hầu họng, cũng như gây ra các tình trạng khác như nhiễm trùng da và mắt. Ví dụ, nấm thuộc họ Malassezia và Cutibacterium có thể gây ra mụn trên đầu.\n\nĐối với việc điều trị nấm, có nhiều phương pháp khác nhau. Ví dụ, vỏ quả Bồ hòn phơi khô nấu trong dầu lạc có thể được sử dụng để hỗ trợ điều trị nấm. Ngoài ra, Gel Lô hội có thể được sử dụng để điều trị các triệu chứng liên quan đến nhiễm trùng da do nấm. Cỏ tháp bút được biết đến với khả năng kháng lại nấm, cho thấy sự đa dạng của tác động mà nấm có thể có đối với các loài thực vật và động vật khác nhau.\n\nNgoài ra, nấm còn là đối tượng thử nghiệm trong nghiên cứu về tác dụng kháng khuẩn của hạt Nhục đậu khấu. Trong một số trường hợp, nấm có thể gây suy tuyến yên và suy gan cấp. Hàm lượng purin của nấm là vừa phải, và thực phẩm thuộc họ nấm như mộc nhĩ rất tốt cho người bệnh bị tăng men gan.\n\nTóm lại, nấm là một loại vi khuẩn hoặc sinh vật vi mô có thể gây bệnh và có thể được điều trị bằng nhiều phương pháp khác nhau tùy thuộc vào vị trí và mức độ nghiêm trọng của nhiễm trùng.&lt;SEP&gt;Nấm có thể gây viêm âm đạo với triệu chứng như ngứa rát âm đạo và dịch âm đạo trắng, đặc, đóng cục.&lt;SEP&gt;Nấm có thể gây ra viêm não.&lt;SEP&gt;Nấm là nguyên nhân gây bệnh ở người có hệ miễn dịch suy yếu hoặc ở người hít phải liều lượng lớn các sinh vật.&lt;SEP&gt;Nấm là một trong những nguyên nhân gây viêm tái tạo cổ tử cung.&lt;SEP&gt;Nấm có thể gây viêm thực quản.\nVị ngọt, tính hàn: Củ niëng có vị ngọt, tính hàn.\nTía tô: Tía tô, còn được gọi là Perilla frutescens, là một loại cây thảo dược đa năng được sử dụng rộng rãi trong y học cổ truyền và trong nấu ăn. Tía tô được biết đến với nhiều công dụng khác nhau, bao gồm cả việc điều trị các triệu chứng cảm cúm và các vấn đề về tiêu hóa. Nó thường được sử dụng trong các bài thuốc sắc nước uống, kết hợp với các thành phần khác như sả, mùi tàu, và sa nhân tím để tăng hiệu quả điều trị.\n\nNgoài ra, tía tô cũng được sử dụng trong việc điều trị các vấn đề tiêu hóa như đau bụng, rối loạn tiêu hóa và tiêu chảy. Trong y học cổ truyền, tía tô được coi là một nguyên liệu quý giúp hỗ trợ điều trị các bệnh lý như mề đay và giải độc từ việc ăn hải sản. Tía tô còn được sử dụng trong bài thuốc chữa cảm mạo phong hàn, thể hiện tính linh hoạt và đa dạng của nó trong việc hỗ trợ sức khỏe tổng thể.\n\nTía tô không chỉ đóng vai trò là một loại cây thuốc mà còn là một loại rau gia vị phổ biến, được sử dụng trong nhiều món ăn khác nhau.&lt;SEP&gt;Tía tô là một loại cây được sử dụng trong y học hiện đại và cổ truyền, có nhiều tác dụng như kháng khuẩn, chống nấm, ngăn ngừa dị ứng, tăng bài tiết dịch tiêu hóa, tăng nhu động ruột, giảm co thắt cơ trơn của phế quản, và kích thích tiết mồ hôi.&lt;SEP&gt;Lá Tía tô được sử dụng để điều trị cảm lạnh và cành Tía tô được sử dụng để điều trị triệu chứng như đau thượng vị, ợ hơi, buồn nôn, nôn mửa, và động thai.&lt;SEP&gt;Tía tô là một loại cây thuộc họ Hoa môi, có tên khoa học là Perilla frutescens (L.) Britt. Các bộ phận của cây này, bao gồm lá, quả, và cành, đều được sử dụng để làm thuốc.&lt;SEP&gt;Tía tô là một loại thảo dược quan trọng đã được ghi nhận trong kinh điển y học cổ truyền, được sử dụng để điều trị các bệnh liên quan đến trầm cảm, lo âu, hen suyễn, dị ứng, cảm lạnh, nôn mửa, đau bụng và khó tiêu.&lt;SEP&gt;Tía tô có truyền thống sử dụng lâu đời trong y học và ẩm thực.&lt;SEP&gt;Tía tô là một vị thuốc kết hợp với Tử uyển trong bài thuốc chữa ho gà.\nQuả hạt: Quả hạt dùng trị đầy hơi, tiêu chảy, thấp khớp.\nsốt: Sốt là một triệu chứng thường gặp trong nhiều tình trạng sức khỏe khác nhau. Nó thể hiện sự tăng nhiệt độ cơ thể và có thể xuất hiện khi mắc các bệnh như viêm xoang, viêm họng, hoặc cảm lạnh. Sốt cũng là một trong những triệu chứng của trùng huyết do thắt dây chun và có thể xảy ra khi sử dụng thuốc như Danapha Trihex 2mg. Ngoài ra, sốt cũng là triệu chứng của bệnh nhân bị sỏi bùn túi mật. Húng chanh được biết đến với tác dụng giảm sốt.&lt;SEP&gt;Sốt là triệu chứng của nhiễm trùng tiểu trên.&lt;SEP&gt;Sốt là tình trạng thân nhiệt tăng cao hơn bình thường.&lt;SEP&gt;Sốt là triệu chứng gợi ý tình trạng nhiễm trùng.\nSở thích cố định, rập khuôn: Sở thích cố định, rập khuôn.\nLá cây: Lá cây là bộ phận của cây Dung được sử dụng trong y học dân gian và nghiên cứu khoa học.&lt;SEP&gt;Lá cây được sử dụng để sắc lấy nước dùng.&lt;SEP&gt;Lá cây chứa iridoid-10-methylixoside.&lt;SEP&gt;Lá cây găng tu hú thường được sử dụng để làm sương sâm.&lt;SEP&gt;Lá cây Tai chua hình trứng ngược, màu xanh lục, có kích thước khoảng 6 – 12cm dài và 3 – 5cm rộng.&lt;SEP&gt;Lá cây Thạch hộc dài khoảng 12cm, rộng khoảng 2 – 3cm, có hình thuôn dài, mọc so le tạo thành 2 dãy đều 2 bên thân. Trên mặt lá có 5 gân dọc và hầu như không có cuống.\nTua cuốn: Tua cuốn đơn, mọc đối diện với lá.\nNước: Nước là một hợp chất hóa học quan trọng, đóng vai trò thiết yếu trong nhiều loại thực vật và quá trình y tế. Trong thực vật, nước được tìm thấy với hàm lượng khác nhau: cây trứng cá chứa 77.8g nước mỗi 100g quả, trong khi củ niễng chỉ chứa 9,2% nước. Nước cũng là thành phần chính trong cây sương sâm và mồng tơi, góp phần tạo nên cấu trúc của chúng.\n\nTừ góc độ hóa học, nước chứa các dạng hợp chất của Fluor, chịu ảnh hưởng bởi nhiều yếu tố như khả năng hòa tan của Fluor, sự xói mòn đất đá, nhiệt độ, và độ pH. Điều này cho thấy tính chất đa dạng của nước trong môi trường tự nhiên.\n\nTrong lĩnh vực y tế, việc uống nước có thể giúp nâng cao huyết áp khi gặp tình trạng tụt huyết áp đột ngột. Ngoài ra, việc uống đủ nước là yêu cầu cần thiết khi sử dụng thuốc Ciprofloxacin. Nước còn được sử dụng như một thành phần dinh dưỡng hỗ trợ giảm đau cơ.\n\nNhư vậy, nước không chỉ là thành phần quan trọng trong nhiều loại thực vật mà còn đóng vai trò quan trọng trong các quy trình y tế và sức khỏe tổng thể.&lt;SEP&gt;Uống đủ 2 lít nước mỗi ngày giúp duy trì lượng nước thích hợp trong dịch mật và ngăn ngừa sự lắng đọng tạo sỏi mật.&lt;SEP&gt;Nước là chất cần thiết cho cơ thể, góp phần duy trì huyết áp.&lt;SEP&gt;Nước chiếm 99,5% thành phần của nước bọt.&lt;SEP&gt;Uống nhiều nước giúp thải vi khuẩn ra khỏi đường tiết niệu.&lt;SEP&gt;Nước có thể tồn đọng trong ống tai tạo điều kiện cho vi khuẩn phát triển và gây viêm ống tai ngoài.\nmát: Mát là tình trạng thân nhiệt thấp, dễ chịu.\nAzithromycin: Azithromycin là một loại thuốc kháng sinh thuộc nhóm macrolid, được sử dụng để điều trị nhiều loại nhiễm trùng. Nó là hoạt chất chính trong các thuốc như Azibiotic và Azithromycin DHG, cũng như Azicine. Azithromycin có tác dụng diệt khuẩn mạnh và thường được sử dụng như một lựa chọn thay thế cho penicillin khi bệnh nhân bị dị ứng với penicillin. Thuốc này cũng được sử dụng để điều trị hạ cam mềm. Ngoài ra, azithromycin còn được biết đến với khả năng tăng cường nồng độ hoặc tác dụng của Amiodarone.&lt;SEP&gt;Azithromycin là một loại thuốc kháng sinh được sử dụng trong điều trị viêm amidan cấp do liên cầu khuẩn.&lt;SEP&gt;Azithromycin là một loại thuốc kháng sinh đường uống được sử dụng để điều trị viêm họng do liên cầu khuẩn.\nSuy yếu, phá hủy cơ bắp: Suy yếu, phá hủy cơ bắp.\nCarbamazepin: Carbamazepin là một loại thuốc chống co giật được sử dụng để điều trị bệnh động kinh, rối loạn tâm trạng, giảm đau dây thần kinh và điều trị căng cơ thắt lưng. Thuốc này có khả năng tương tác với nhiều loại thuốc khác nhau, bao gồm Acemol 325 mg, Agifuros 40 mg, Appeton Lysine Syrup, Asevictoria Mediplantex, Avalo, Benda, và cefixim. Khi sử dụng cùng với Erythromycin, nồng độ của carbamazepin trong máu có thể tăng lên. Tương tác với Asevictoria Mediplantex có thể làm giảm tác dụng tránh thai của levonorgestrel. Sử dụng cùng với Avalo có thể làm giảm hiệu quả của Avalo. Tuy nhiên, carbamazepin không tương tác với Azithromycin. Tương tác với Benda có thể làm giảm nồng độ của Mebendazol trong huyết tương. Khi sử dụng cùng với cefixim, nồng độ của carbamazepin trong huyết tương có thể tăng lên do sự tương tác giữa hai loại thuốc này.\n\nNgoài ra, carbamazepin còn có khả năng kích thích gan sản xuất các enzym giúp chuyển hóa paracetamol thành các chất có hại. Thuốc này cũng có thể tương tác với Coldacmin, Davibest, và B Complex C.&lt;SEP&gt;Carbamazepin is listed as one of the other drugs mentioned in the text.&lt;SEP&gt;Carbamazepin là một thuốc có thể tương tác với Daktarin.&lt;SEP&gt;Carbamazepine is a drug that interacts with Dexamethasone and is used in medical treatments.\nBuồn nôn, nôn và tiêu chảy: Buồn nôn, nôn và tiêu chảy.\nErythromycin: Erythromycin là một loại kháng sinh thuộc nhóm macrolides, thường được sử dụng để điều trị các nhiễm khuẩn khác nhau. Nó là hoạt chất chính trong Agi-Ery và có phổ tác dụng rộng đối với nhiều vi khuẩn Gram dương. Erythromycin cũng có khả năng tăng nồng độ trong nhu mô phổi khi dùng kết hợp với Ambroxol Boston, một thuốc long đờm. \n\nLoại kháng sinh này có thể tương tác với một số loại thuốc khác như desloratadine và Acnequidt 20 ml, có thể làm thay đổi hiệu quả của các thuốc đó. Khi sử dụng cùng lúc, Erythromycin có thể làm giảm tác dụng của Amoxicillin Mekophar và Ampicillin Brawn. Ngoài ra, Erythromycin cũng được sử dụng trong điều trị bạch hầu và hạ cam mềm. Tuy nhiên, loại kháng sinh này cũng tăng nguy cơ tổn thương cơ khi sử dụng cùng với Atorvastatin.\n\nErythromycin cũng là hoạt chất trong Anapa, một kháng sinh thuộc nhóm macrolides có tác động trực tiếp lên khuẩn Propionibacterium acnes, giúp giảm tiết bã nhờn và có tác động kháng viêm. Loại kháng sinh này còn được sử dụng trong các liệu pháp điều trị da, đặc biệt là trong việc giảm viêm và kiểm soát tình trạng tiết bã nhờn trên da. Erythromycin cũng được đề cập trong hướng dẫn sử dụng Azaroin gel và có tác dụng tương tự như Azithromycin nhưng yếu hơn trên vi khuẩn Gram dương.\n\nNgoài ra, Erythromycin có thể tương tác với các thuốc khác như Ambroxol, Desloratadine, và Davibest. Erythromycin cần tránh sử dụng cùng với Adagrin do có khả năng tương tác không mong muốn. Thuốc này cũng có thể tương tác với methylprednisolone và Bilastine. Erythromycin được coi là an toàn hơn khi sử dụng cho phụ nữ mang thai hoặc cho con bú.\n\nErythromycin còn được sử dụng kết hợp với benzoyl peroxide trong các chế phẩm điều trị mụn. Thuốc erythromycin tiêm tĩnh mạch có thể làm tăng nồng độ/tác dụng của Amiodarone.&lt;SEP&gt;Erythromycin là một loại thuốc mà không nên sử dụng cùng với Cisaprid.&lt;SEP&gt;Erythromycin là một loại thuốc có tương tác với cisaprid.&lt;SEP&gt;Erythromycin là kháng sinh dùng đồng thời với Clarityne có thể làm tăng nồng độ loratadin trong huyết tương.\nTrán vồ: Trán vồ, cằm nhô, tăng khoảng cách giữa các răng.\nNôn: Nôn, còn được biết đến với tên gọi "vomiting" trong tiếng Anh, là một triệu chứng tiêu hóa mà bệnh nhân có thể trải qua khi sử dụng các loại thuốc hoặc gặp phải tình trạng sức khỏe cụ thể. Đây là hành động co bóp dạ dày nhằm đẩy thức ăn hoặc dịch vị từ dạ dày lên miệng. Nôn có thể xuất hiện như một tác dụng phụ của việc sử dụng nhiều loại thuốc khác nhau, bao gồm Acyclovir, A.t Ibuprofen Syrup, Acepron 250 mg, Erythromycin, Adkold - New, và nhiều loại thuốc khác như Antimuc An Thiên, Aspirin MKP 81, Aticef, Atocib, Atorlog, Augbactam, Azithromycin, Bisoloc, và Cedipect F. Ngoài ra, nôn cũng là một tác dụng phụ hiếm gặp khi sử dụng Aerius 5 mg, Allopurinol, Alzental Shinpoong, thuốc Ambroxol, thuốc Ambroxol Boston, Amoxicilin 500 mg, Amoxicillin Domesco, Amoxicillin Mekophar, Ampicillin Brawn, Ampicillin Vidipha, và Interferon Gamma-1b có trong thuốc Anaferon Materia. Nó cũng có thể xuất hiện khi sử dụng quá liều ibuprofen hoặc do tiêu thụ lượng canxi quá mức. Đồng thời, nôn cũng là triệu chứng phổ biến của ngộ độc mạn tính và là một trong những tác dụng phụ ít gặp của một số loại thuốc khác nhau.\n\nNôn cũng là tác dụng phụ khi sử dụng các loại thuốc như Brodicef, Cefadroxil, Cefimbrano 100, Cefurich, Cefurobiotic, Cefuroxim, và Cefuroxim axetil. Nôn cũng có thể xảy ra khi dùng quá liều Calcigenol, Calcium Corbiere Extra, và Chymodk. Nôn cũng là tác dụng phụ thường gặp khi sử dụng Trimethoprim và Coversyl. Nôn cũng là một tác dụng phụ của việc sử dụng thuốc Curam và Cyclo Progynova. Ngoài ra, nôn cũng là tác dụng phụ của Advil, có thể là tác dụng không mong muốn khi sử dụng Advil. Nôn cũng là một tác dụng phụ của việc dùng quá liều thuốc Avamys.\n\nNôn cũng là triệu chứng thường gặp của u não ác tính, đặc biệt là nôn vọt không liên quan đến bữa ăn. Nôn cũng có thể xảy ra sau phẫu thuật. Bên cạnh đó, nôn cũng là một triệu chứng của bệnh viêm dạ dày ruột do virus, thường kèm theo các triệu chứng khác như tiêu chảy, đau bụng, buồn nôn, và đôi khi sốt.\n\nNôn cũng được ghi nhận là một triệu chứng của viêm phổi.&lt;SEP&gt;Nôn là một trong các triệu chứng của viêm phúc mạc.&lt;SEP&gt;Nôn là một triệu chứng phổ biến của viêm ruột do bức xạ.&lt;SEP&gt;Nôn là một triệu chứng của viêm ruột do bức xạ.&lt;SEP&gt;Nôn là một triệu chứng của bệnh viêm ruột (IBD).&lt;SEP&gt;Nôn là một trong những triệu chứng nặng của viêm tiểu phế quản.\nMontelukast: Montelukast, còn gọi là Singulair, là một loại thuốc chống viêm.\nAzibiotic: Azibiotic là một loại thuốc kháng sinh macrolid.&lt;SEP&gt;Azibiotic là thương hiệu của Azithromycin.&lt;SEP&gt;Azibiotic là một loại thuốc kháng sinh thuộc nhóm Macrolid, chứa hoạt chất chính là Azithromycin.\nZafirlukast: Zafirlukast, còn gọi là Accolate, là một loại thuốc chống viêm.\nAmlodipine: Amlodipine là một loại thuốc thuộc nhóm chặn kênh canxi, thường được sử dụng trong việc điều trị tăng huyết áp hoặc suy tim. Hoạt chất này là thành phần chính của các sản phẩm như Amlor 5 của Pfizer và Cardilopin. Amlodipine thuộc nhóm chặn kênh canxi dihydropyridine, giúp giãn mạch máu, giảm huyết áp và kiểm soát cơn đau thắt ngực. Nó cũng được sử dụng để điều trị bệnh tim mạch.\n\nTrong quá trình điều trị, Amlodipine không gây ra tương tác rõ ràng trên lâm sàng khi được sử dụng cùng với telmisartan. Tuy nhiên, cần lưu ý rằng Amlodipine có thể tương tác với Combigan. Ngoài ra, Amlodipine được đề cập như một ví dụ về thuốc chặn kênh canxi (CCBs) nên tránh sử dụng cùng với Bisoprolol.\nSốt, mệt mỏi: Sốt, mệt mỏi là các triệu chứng khác của viêm nhiễm.\nNgất: Ngất là tình trạng mất ý thức tạm thời, thường xảy ra do thiếu máu lên não. Đây là một tác dụng không mong muốn có thể gặp phải khi sử dụng một số loại thuốc như Adalat LA 20 mg, Azithromycin DHG, Beatil, Alsiful S.R, và Aceclofenac STADA. Trong đó, ngất là tác dụng phụ thường gặp khi sử dụng Azithromycin DHG và ít gặp hơn khi sử dụng Beatil. Ngất cũng có thể xuất hiện như một tác dụng phụ không mong muốn khi sử dụng Alsiful S.R, mặc dù đây là một tác dụng phụ không phổ biến.\n\nNgất cũng có thể là một triệu chứng nặng hơn sau khi đi tiêu ra máu và là triệu chứng của bệnh hẹp van động mạch chủ khi đã phát triển triệu chứng cơ năng. Ngoài ra, ngất còn là một triệu chứng nghiêm trọng có thể gặp ở những người mắc bệnh hở van tim và hội chứng WPW, xảy ra khi tim không thể cung cấp đủ máu cho não. Ngất cũng có thể là một trong các biểu hiện nặng của huyết áp không ổn định và là triệu chứng của rung nhĩ, xảy ra khi tim đập quá nhanh, dẫn đến tưới máu não không đủ.&lt;SEP&gt;Ngất là một triệu chứng có thể xảy ra khi dùng quá liều Thuốc Bifril.&lt;SEP&gt;Ngất có thể xảy ra và là một dấu hiệu cần chẩn đoán ngay.&lt;SEP&gt;Ngất là một triệu chứng cần được chẩn đoán khi sử dụng thuốc Buscopan.&lt;SEP&gt;Ngất là một tác dụng phụ có thể xảy ra khi sử dụng Captopril.&lt;SEP&gt;Ngất là tình trạng mất ý thức tạm thời.&lt;SEP&gt;Ngất là một triệu chứng có thể xảy ra trong thuyên tắc phổi.\nDịu cổ họng: Dịu cổ họng, giải độc, nhuận trường, giải khát.\nAticef: Aticef là thuốc kháng sinh thuộc nhóm cephalosporin thế hệ 1 được bào chế dưới dạng viên nang cứng. Thuốc được dùng để điều trị các bệnh nhiễm khuẩn tại đường hô hấp, tiết niệu, da và mô mềm.&lt;SEP&gt;Aticef là thuốc điều trị nhiễm khuẩn bào chế dưới dạng viên nang cứng, chứa cefadroxil monohydrat 500 mg.&lt;SEP&gt;Aticef là một loại thuốc kháng sinh thuộc nhóm Cephalosporin, thường được sử dụng để điều trị các nhiễm trùng vi khuẩn.\nMát: Mát là cảm giác dễ chịu, giảm nhiệt độ cơ thể.\nNhọt: Nhọt là tình trạng nhiễm khuẩn hoặc viêm nhiễm tại da, thường gây ra các khối sưng tấy cục bộ trên cánh tay và chân. Nó có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng kháng sinh như Aticef và các phương pháp tự nhiên như cây lưỡi bò. Ngoài ra, nhọt cũng có thể là một triệu chứng mà Màng tang có thể điều trị. Tình trạng này có thể xảy ra như một tác dụng phụ của việc tiêm vắc xin Rubella hoặc khi sử dụng thuốc moxifloxacin.&lt;SEP&gt;Nhọt là một triệu chứng bệnh lý.\nSưng, phù nề: Sưng, phù nề là triệu chứng thường gặp của trật khớp háng.\nAtenolol: Atenolol là một loại thuốc thuộc nhóm chẹn beta, thường được sử dụng trong điều trị các vấn đề về tim mạch như tăng huyết áp, đau thắt ngực, nhồi máu cơ tim cấp, loạn nhịp thất và trên thất. Nó cũng được sử dụng để điều trị hạ huyết áp và nhiễm độc giáp. Atenolol là một thuốc chẹn chọn lọc thụ thể beta1-adrenergic, có khả năng tương tác với thuốc khác như Combigan. Thuốc này giúp giảm nhịp tim và giảm nhu cầu oxy của cơ tim, từ đó hỗ trợ điều trị các tình trạng tim mạch khác nhau. Tuy nhiên, cần lưu ý rằng Atenolol có thể bài tiết vào sữa mẹ và gây ra tác dụng phụ cho trẻ sơ sinh đang bú mẹ.\nTinh dầu dừa: Tinh dầu dừa có đặc tính kháng khuẩn, kháng nấm, kháng viêm.\nCarsantin: Carsantin là một loại thuốc điều trị suy tim và có thể tương tác với một số thuốc khác.\nCorticosteroid, ACTH: Corticosteroid và ACTH có thể gây tương tác với Coaprovel.\nChìa vôi - Tua cuốn: Tua cuốn đơn, mọc đối diện với lá.\nHay ngứa - Nấm: Nấm gây ngứa.\nKhóc nhiều, dễ xúc động - Trầm cảm khi mang thai: Khóc nhiều, dễ xúc động.\nTía tô - sốt: Tía tô có tác dụng giải nhiệt, giảm sốt.\nChuối hột - Mát: Chuối hột được sử dụng để điều trị triệu chứng mát.\nLá cây - Nước: Lá cây sương sâm chứa nước.\nNấm da đầu - Tinh dầu dừa: Tinh dầu dừa có đặc tính kháng khuẩn, kháng nấm, kháng viêm.\nAzithromycin - Carbamazepin: Azithromycin không tương tác với Carbamazepin.\nCortisol - Suy yếu, phá hủy cơ bắp: Suy yếu, phá hủy cơ bắp có thể là một triệu chứng do nồng độ cortisol cao.\nErythromycin - Nôn: Erythromycin có thể gây nôn.\nCỏ mần trầu - Lorsatan (Losartan): Dịch chiết cỏ mần trầu có tác dụng hạ huyết áp tương đương với Losartan.\nAzibiotic - Azithromycin: Azibiotic là thương hiệu của Azithromycin.\nSưng, phù nề - Trật khớp háng: Sưng, phù nề là triệu chứng thường gặp của trật khớp háng.\nAmlodipine - Ngất: Amlodipine có thể gây ngất.\nLa hán quả - Nhàm trường: La hán quả được sử dụng để nhàm trường, giải khát.\nAticef - Nhọt: Aticef điều trị nhọt.\nDịu cổ họng - La hán quả: La hán quả được sử dụng để dịu cổ họng, giải độc, nhuận trường, giải khát.\nAtenolol - Ngất: Atenolol có thể gây ngất.\nSốt, mệt mỏi - Viêm sụn vành tai: Sốt, mệt mỏi là các triệu chứng khác của viêm nhiễm.\nCarsantin - Carvedilol: Carsantin chứa hoạt chất Carvedilol.\nBuồn nôn, nôn và tiêu chảy - Bệnh Addison: Buồn nôn, nôn và tiêu chảy là triệu chứng của bệnh Addison.\nCúm - Đại hồi: Đại hồi điều trị cúm.\nCoaprovel - Corticosteroid, ACTH: Corticosteroid và ACTH có thể gây tương tác với Coaprovel.\nPhyscion - rễ: Rễ cây lưỡi bò chứa Physcion.\nMô mềm - Trán vồ: Mô mềm liên quan đến các triệu chứng như trán vồ, cằm nhô, tăng khoảng cách giữa các răng.\nAzithromycin - Nôn: Azithromycin có thể gây nôn.\nHay ngứa - Ve chó: Ve chó gây ngứa.\nAzithromycin - Cimetidin: Azithromycin không bị ảnh hưởng bởi Cimetidin.\nAntacid - Azithromycin: Azithromycin có thể tương tác với Antacid.\nLoganiaceae - Mã tiền: Cây Mã tiền thuộc họ Loganiaceae.\nAzithromycin - Cyclosporin: Azithromycin có thể ảnh hưởng đến Cyclosporin.\nAzithromycin - Warfarin: Azithromycin không bị ảnh hưởng bởi Warfarin.\nAzithromycin - Theophylline: Azithromycin có thể ảnh hưởng đến Theophylline.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The information provided does not contain specific details about the drug Carbogast. However, based on the pattern of information given for other medications, here are some general considerations:
-For medications like Arthrorein Pharmanel and Bluemint, it is advised to exercise caution when using them during pregnancy and breastfeeding. Specifically, for Arthrorein Pharmanel, it is explicitly stated that the drug is contraindicated for pregnant women and nursing mothers due to potential risks to maternal and fetal health. Similarly, Bluemint should only be used by pregnant women and nursing mothers if absolutely necessary and under strict medical supervision.
-Therefore, if Carbogast is similar to these drugs in terms of safety concerns during pregnancy and breastfeeding, it would likely be recommended to avoid its use unless medically necessary and under close medical supervision.
-It is crucial to consult a healthcare provider before using any medication during pregnancy or while breastfeeding to ensure the safety of both mother and child.</t>
+          <t>Không có thông tin cụ thể về thuốc Biviantac trong **Context** cung cấp. Do đó, tôi không thể xác định liệu Biviantac có thể điều trị triệu chứng trướng bụng, đầy hơi hay không dựa trên dữ liệu hiện có.
+Nếu bạn có thêm thông tin về Biviantac hoặc triệu chứng bạn đang gặp phải, hãy cung cấp thêm chi tiết để tôi có thể hỗ trợ bạn tốt hơn.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Không bắt buộc, nên dùng thuốc theo đúng chỉ định của bác sĩ.</t>
+          <t>Có, Biviantac có thể điều trị các tình trạng như trướng bụng, đầy hơi, ợ nóng, ợ hơi hay ợ chua.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -851,234 +650,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ngoài khả năng giảm đau, **Acepron 250 mg** còn được chỉ định để điều trị các triệu chứng sốt từ nhẹ đến vừa. Thuốc có thể giúp hạ sốt trong các tình huống như cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, hoặc sau phẫu thuật. 
-Acepron 250 mg chứa thành phần chính là Paracetamol, một loại thuốc giảm đau và hạ sốt hiệu quả. Cơ chế hoạt động của Paracetamol giúp làm giảm thân nhiệt ở người bệnh sốt, nhưng hiếm khi làm giảm thân nhiệt ở người bình thường. Thuốc cũng có thể giúp tăng lưu lượng máu ngoại biên và tăng tỏa nhiệt, giúp cơ thể hạ nhiệt hiệu quả.
-### Tác dụng cụ thể của Acepron 250 mg:
-- **Giảm thân nhiệt**: Acepron 250 mg có thể giúp hạ sốt trong các tình huống như cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, hoặc sau phẫu thuật.
-- **Giảm các triệu chứng đau**: Thuốc có thể giảm các triệu chứng đau như nhức đầu, đau răng, đau nhức do cảm cúm, và đau cơ.
-### Lưu ý:
-- Thuốc không có tác dụng trong điều trị thấp khớp và các cơn đau bắt nguồn từ nội tạng.
-- Nếu dùng thuốc quá 5 ngày, cơn đau không thuyên giảm, sốt cao trên 39,5 độ, sốt kéo dài 3 ngày hoặc sốt tái phát, nên hỏi ý kiến bác sĩ trước khi tiếp tục sử dụng.
-### Tương tác thuốc:
-- Acepron 250 mg có thể tăng tác dụng chống đông máu của coumarin và dẫn chất indandion khi uống dài ngày với liều cao.
-- Ở người bệnh dùng đồng thời phenothiazin và liệu pháp hạ nhiệt, cần chú ý đến khả năng gây hạ sốt nghiêm trọng.
-### Tác dụng phụ:
-- Khi sử dụng Acepron 250 mg kéo dài với liều lớn có thể gây ra các tác dụng phụ như: giảm bạch cầu, giảm toàn thể huyết cầu, giảm tiểu cầu, nôn, ban da, buồn nôn, và có thể gây ra bệnh thận và độc tính trên thận.
-### Cách sử dụng:
-- Thuốc có dạng bột, hòa tan với nước để uống.
-- Thuốc được khuyến cáo sử dụng sau bữa ăn.
-- Đối với người bị suy thận, tối thiểu là 8 giờ giữa hai lần dùng thuốc.
-### Giá bán:
-- Giá bán lẻ của thuốc có thể thay đổi tùy theo từng nhà thuốc.
-### Tóm tắt:
-Acepron 250 mg không chỉ giúp giảm đau mà còn hỗ trợ điều trị các triệu chứng sốt từ nhẹ đến vừa. Thuốc có thể giúp hạ sốt trong nhiều tình huống khác nhau và giảm các triệu chứng đau như nhức đầu, đau răng, và đau cơ.
-### Tham khảo:
-- Acepron 250 mg được sản xuất bởi Công ty Cổ phần Dược phẩm Cửu Long (Pharimexco).
-### Lưu ý:
-- Cần thông báo cho bác sĩ nếu gặp tác dụng phụ khi sử dụng thuốc.
-### Kết luận:
-Acepron 250 mg là một lựa chọn hiệu quả để điều trị cả sốt và các triệu chứng đau từ nhẹ đến vừa.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ngoài tác dụng giảm đau, Acepron 250 mg còn có thêm tác dụng giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>0.7628518601171033</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.9999999999</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mix</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.920950620005701</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Calci D Hasan không được khuyến nghị sử dụng cho phụ nữ mang thai và cho con bú. Cần hỏi ý kiến bác sĩ trước khi quyết định dùng thuốc này trong thời kỳ mang thai hoặc cho con bú.
-### 可以在怀孕或哺乳期间自行使用Calci D Hasan吗？
-不可以。Calci D Hasan不被推荐用于孕妇和哺乳期妇女。在怀孕或哺乳期间使用此药物之前，应咨询医生的意见。
-### 参考文献
-- [10] 调理静脉曲张和痔疮的药物Aescin.txt
-请注意，对于孕妇和哺乳期妇女来说，在使用任何药物之前都应该咨询医生的意见。</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Không, không nên tự ý sử dụng thuốc.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5347548991036636</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mix</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.3836887247759159</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tôi không thấy thông tin cụ thể về cách sử dụng thuốc Comiaryl trong kiến thức đã cung cấp. Để sử dụng thuốc Comiaryl một cách an toàn và hiệu quả, bạn nên:
-1. Theo dõi hướng dẫn sử dụng được cung cấp bởi bác sĩ hoặc nhà sản xuất.
-2. Tuân thủ liều lượng và thời gian uống được khuyến nghị.
-3. Không tự ý thay đổi liều lượng hoặc dừng thuốc mà không có sự đồng ý của bác sĩ.
-4. Báo cáo bất kỳ tác dụng phụ nào cho bác sĩ.
-Nếu bạn cần thông tin cụ thể hơn, hãy tham khảo ý kiến của bác sĩ hoặc dược sĩ của bạn.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Nên uống nguyên viên thuốc Comiaryl với một cốc nước đầy.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
         <v>0.1666666666666667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mix</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Calci D Hasan là một loại thuốc, nhưng thông tin cụ thể về tác dụng phụ hoặc tương tác với bệnh lý nền không được cung cấp trong kiến thức đã cho. Tuy nhiên, tôi có thể đề cập đến một số loại thuốc tương tự hoặc liên quan mà có thể có tác dụng phụ hoặc tương tác với các bệnh lý nền:
-**1. Thuốc lợi tiểu** có thể gây tăng Acid uric máu, mất nước, hạ magie máu và có thể tương tác với các thuốc khác như Bambec, Baby Septol, và Carvedilol. Việc sử dụng phối hợp giữa thuốc lợi tiểu và Coversyl có thể dẫn đến hạ huyết áp quá mức.
-**2. Thuốc Cerecaps** có tương tác với Heparin và Aspirin, không nên sử dụng cùng lúc. Cerecaps cũng có thể gây ra các tác dụng phụ như tăng nguy cơ loét đường tiêu hóa và chảy máu.
-**3. Thuốc Heparin** có thể gây ra hạ magie máu và có thể tương tác với một số loại thuốc khác như Alphalysosine, Bilomag, Clopidogrel, Cerecaps, Coversyl, Cataflam, và Tiền Hồ.
-**4. Thuốc Aspirin** có thể tương tác với nhiều loại thuốc khác nhau, bao gồm Acenocoumarol, Atenolol, Ibuprofen Syrup, Appeton Lysine Syrup, Aluminium Phosphat Gel, Bilomag, Bisoplus, và Coversyl. Tương tác với Acenocoumarol có thể tăng cường khả năng chống đông máu và nguy cơ chảy máu.
-Do không có thông tin cụ thể về Calci D Hasan, nếu bạn đang sử dụng thuốc này và gặp phải bất kỳ triệu chứng bất thường nào, bạn nên liên hệ với bác sĩ hoặc dược sĩ để được tư vấn kỹ hơn.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ở bệnh nhân mắc bệnh lý nền, Calci D Hasan có thể gây tăng nhạy cảm với vitamin D, làm tăng nguy cơ gây hại cho sức khỏe.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mix</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.125</v>
       </c>
     </row>
   </sheetData>
@@ -1169,34 +741,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0222</v>
+        <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0497</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1111</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.381</v>
+        <v>0.6667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.3795</v>
-      </c>
+        <v>0.6667</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8571</v>
+        <v>0.6667</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -1204,7 +772,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.3587</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="3">
@@ -1214,42 +782,38 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3124</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.4535</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2595</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.3644</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7629</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1259,42 +823,38 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.5477</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5477</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -1304,34 +864,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.4472</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.4472</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1349,42 +905,38 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2837</v>
+        <v>0.375</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3117</v>
-      </c>
+        <v>0.375</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7484</v>
+        <v>0.375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3871</v>
+        <v>0.1667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2917</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.3133</v>
-      </c>
+        <v>0.1667</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.125</v>
+        <v>0.1667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.921</v>
+        <v>0.1667</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Mix</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1035</v>
+        <v>-0.2083</v>
       </c>
     </row>
   </sheetData>

--- a/testcase/eval_ragas_naive_mix_500cases.xlsx
+++ b/testcase/eval_ragas_naive_mix_500cases.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naive" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hybrid" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,22 +506,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Từ thông tin cung cấp, không có dữ liệu cụ thể nào về thuốc Biviantac hoặc khả năng của nó trong việc điều trị triệu chứng trướng bụng và đầy hơi. Để nhận được lời khuyên chuyên môn về sử dụng bất kỳ loại thuốc nào, bạn nên liên hệ với bác sĩ hoặc dược sĩ.</t>
+          <t>Thuốc Carbogast có thể được sử dụng cho phụ nữ trong giai đoạn mang thai và trong thời kỳ cho con bú, nhưng cần tuân thủ một số nguyên tắc:
+- **Mang thai:** Thuốc Carbogast có thể được sử dụng trong thời kỳ mang thai. Tuy nhiên, bạn vẫn nên hỏi ý kiến bác sĩ trước khi sử dụng.
+- **Cho con bú:** Thuốc Carbogast cũng có thể được sử dụng trong thời kỳ cho con bú. Tuy nhiên, cũng nên hỏi ý kiến bác sĩ để đảm bảo an toàn.
+Việc sử dụng thuốc Carbogast trong thời kỳ mang thai và cho con bú không bắt buộc, nhưng nếu cần thiết, việc tham khảo ý kiến của bác sĩ là rất quan trọng để đảm bảo an toàn cho cả mẹ và bé.
+### Cách bảo quản
+Khi sử dụng, cần bảo quản thuốc Carbogast ở nơi khô ráo, nhiệt độ không quá 30°C, tránh xa tầm tay trẻ em và thú cưng trong nhà.
+### Lưu ý
+- Đọc kỹ hướng dẫn trước khi dùng.
+- Không dùng thuốc có dấu bất thường, ẩm mốc.
+### Kết luận
+Việc sử dụng Carbogast trong thời kỳ mang thai và cho con bú không bắt buộc, nhưng nếu cần thiết, nên hỏi ý kiến bác sĩ để đảm bảo an toàn.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Có, Biviantac có thể điều trị các tình trạng như trướng bụng, đầy hơi, ợ nóng, ợ hơi hay ợ chua.</t>
+          <t>Không bắt buộc, nên dùng thuốc theo đúng chỉ định của bác sĩ.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -531,7 +542,1593 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.375</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ngoài tác dụng giảm đau, **Acepron 250 mg** còn có tác dụng hạ sốt. Thuốc này được chỉ định để điều trị các triệu chứng sốt do nhiều nguyên nhân khác nhau như cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, hoặc sau phẫu thuật.
+### Tác dụng cụ thể của Acepron 250 mg:
+- **Hạ sốt**: Thuốc giúp giảm thân nhiệt ở người bệnh sốt. Tuy nhiên, ở người bình thường, hiếm khi thấy tác dụng hạ sốt.
+- **Giúp tăng tỏa nhiệt**: Thuốc giãn mạch giúp tăng tỏa nhiệt và tăng lưu lượng máu ngoại biên, đặc biệt tác động lên vùng dưới đồi gây hạ nhiệt.
+### Các chỉ định cụ thể:
+- Điều trị sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.
+- Giảm các triệu chứng đau từ nhẹ tới vừa: nhức đầu, đau răng, đau nhức do cảm cúm, sốt, đau cơ.
+### Lưu ý:
+- Thuốc không có tác dụng trong điều trị thấp khớp và các cơn đau bắt nguồn từ nội tạng.
+### Cách dùng:
+- Thuốc được sử dụng sau bữa ăn và cần cách nhau từ 4 đến 6 giờ giữa hai lần dùng.
+- Đối với người bị suy thận, thời gian giữa hai lần dùng tối thiểu là 8 giờ.
+- Nếu cơn đau không thuyên giảm, sốt cao trên 39,5 độ, sốt kéo dài 3 ngày hoặc sốt tái phát, nên hỏi ý kiến bác sĩ trước khi tiếp tục sử dụng.
+### Liều dùng cho từng đối tượng:
+- Trẻ em từ 4 – 6 tuổi: Uống 1 gói/lần.
+- Trẻ em từ 7 – 10 tuổi: Uống 1 gói rưỡi/lần.
+- Trẻ em trên 11 tuổi và người lớn: Uống 2 gói/lần.
+### Giá bán lẻ:
+- Giá bán lẻ của thuốc có thể thay đổi tùy theo từng nhà thuốc. Bạn nên liên hệ hoặc đến trực tiếp nhà thuốc để có được giá chính xác.
+### Tác dụng phụ:
+- Bất kỳ thuốc nào cũng có thể gây tác dụng phụ. Khi gặp tác dụng phụ, nên dừng sử dụng và thông báo cho bác sĩ.
+### Tương tác thuốc:
+- Thuốc có thể tương tác với một số loại thuốc khác như coumarin, dẫn chất indandion, thuốc chống co giật, isoniazid, và các thuốc khác.
+### Xử lý khi quá liều:
+- Triệu chứng quá liều có thể bao gồm hoại tử gan, buồn nôn, nôn, đau bụng, và triệu chứng xanh tím da, niêm mạc và móng tay.
+- Cần được đưa đến cơ sở y tế gần nhất nếu có triệu chứng nặng.
+### Lưu ý khi sử dụng:
+- Cần thận trọng khi sử dụng ở các đối tượng thận trọng và nếu có bất kỳ tác dụng phụ nào, nên đến cơ sở y tế ngay.
+### Cách bảo quản:
+- Bảo quản thuốc ở nơi có nhiệt độ dưới 30°C, tránh nơi ẩm thấp, để ở nơi thoáng mát.
+### Lưu ý cuối cùng:
+- Chỉ nên sử dụng thuốc theo hướng dẫn của bác sĩ và tuân thủ liều lượng được khuyến nghị.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ngoài tác dụng giảm đau, Acepron 250 mg còn có thêm tác dụng giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7739276818519211</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6934819204379803</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Calci D Hasan không nên được sử dụng tự ý khi đang mang thai hoặc cho con bú. Theo tài liệu, thuốc này chống chỉ định cho phụ nữ mang thai và cho con bú. Điều này có nghĩa là nếu bạn đang mang thai hoặc cho con bú, bạn không nên tự ý sử dụng Calci D Hasan mà cần phải có sự theo dõi của bác sĩ để đảm bảo an toàn cho cả mẹ và bé.
+### Lưu ý
+- **Mang thai:** Nếu bạn đang mang thai, việc sử dụng Calci D Hasan cần được dừng lại.
+- **Cho con bú:** Thuốc này cũng chống chỉ định cho phụ nữ đang cho con bú vì các chất có thể được truyền qua sữa mẹ vào cơ thể của trẻ.
+Do đó, nếu bạn thuộc nhóm đối tượng này, việc sử dụng Calci D Hasan cần được bác sĩ chuyên môn tư vấn và theo dõi chặt chẽ.
+### Tham khảo
+- [1] calci-d-hasan.txt</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Không, không nên tự ý sử dụng thuốc.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8604128387087181</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4651032096771796</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Để sử dụng thuốc Comiaryl một cách hiệu quả, bạn cần tuân thủ các hướng dẫn sau:
+### 1. Thời Điểm Sử Dụng Thuốc
+Thuốc Comiaryl nên được uống ngay trước hoặc trong bữa ăn. Điều này giúp đảm bảo rằng thuốc có thể phát huy tác dụng một cách hiệu quả nhất.
+### 2. Cách Uống
+Bạn cần uống nguyên viên thuốc Comiaryl với một cốc nước đầy. Không nên nhai hoặc nghiền nát viên thuốc trước khi uống.
+### 3. Liều Dùng
+- Liều khởi đầu nên là liều thấp nhất có tác dụng trị liệu. 
+- Liều tối đa hàng ngày không nên vượt quá 2 viên (chỉ được uống tối đa một ngày 2 lần, mỗi lần uống 1 viên).
+### 4. Lưu Ý Khi Sử Dụng
+- Cần tuân thủ chế độ ăn kiêng và luyện tập thể dục.
+- Thường xuyên theo dõi glucose huyết và đường niệu.
+- Tránh hạ đường huyết quá mức bằng cách tuân theo hướng dẫn của bác sĩ về chế độ ăn uống và luyện tập.
+### 5. Bảo Quản
+Thuốc Comiaryl cần được bảo quản ở nơi khô thoáng, nhiệt độ dưới 30°C và tránh ánh sáng.
+### 6. Các Tình Huống Đặc Biệt
+- Trong trường hợp quên liều, bạn nên tiếp tục uống trong bữa ăn kế tiếp và không nên uống liều gấp đôi để bù vào liều đã quên.
+- Trong trường hợp quá liều, hãy gọi ngay cho trung tâm cấp cứu hoặc đến cơ sở y tế địa phương gần nhất.
+### 7. Tác Dụng Phụ
+Cần lưu ý rằng bạn có thể gặp một số tác dụng phụ khi sử dụng thuốc Comiaryl, bao gồm:
+- Rối loạn tiêu hóa như buồn nôn, nôn, đau bụng, tiêu chảy.
+- Hạ đường huyết quá mức.
+- Rối loạn thị giác thoáng qua.
+Nếu gặp phải bất kỳ triệu chứng nào không bình thường, bạn cần báo ngay cho bác sĩ.
+### 8. Đối Tượng Cần Thận Trọng
+Do nguy cơ hạ đường huyết và rối loạn thị giác thoáng qua khi sử dụng Comiaryl, cần thận trọng khi dùng thuốc trong khi lái xe hoặc vận hành máy móc.
+### 9. Hướng Dẫn Sử Dụng
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl. Đồng thời, tham vấn ý kiến từ bác sĩ hoặc chuyên gia để được tư vấn kỹ hơn.
+### 10. Giá Thuốc
+Giá tham khảo của thuốc Comiaryl là 89.000 VNĐ/hộp (3 vỉ x 10 viên).
+### 11. Đối Tượng Chống Chỉ Định
+Thuốc Comiaryl chống chỉ định cho bệnh nhân suy thận, người bệnh lý cấp tính có nguy cơ gây suy thận, người bị suy gan, ngộ độc rượu cấp tính, suy tim sung huyết, trụy tim mạch, nhồi máu cơ tim cấp tính, người mắc bệnh hô hấp nặng giảm oxy máu, bệnh phổi thiếu oxy mãn tính, hoại thư, người nghiện rượu, thiếu dinh dưỡng, phụ nữ có thai và cho con bú.
+### 12. Lưu Ý Khi Sử Dụng
+- Tránh sử dụng thuốc Comiaryl cho người chụp X quang có tiêm chất cản quang chứa iod (48 giờ trước và sau khi chụp X-quang).
+- Cần theo dõi chặt chẽ glucose huyết và đường niệu khi sử dụng thuốc.
+### 13. Tương Tác Thuốc
+Thuốc Comiaryl có thể tương tác với nhiều loại thuốc khác, bao gồm các thuốc điều trị đái tháo đường khác, dẫn chất Coumarin, insulin, kháng sinh, thuốc hóa trị liệu, thuốc chống viêm Non-Steroid (NSAID), thuốc ức chế enzyme monoamine oxidase (thuốc chống trầm cảm IMAO), các thuốc kháng nấm, các thuốc chẹn beta, thuốc ức chế men chuyển (ACEi), Probenecid, các steroid đồng hóa và nội tiết tố sinh dục nam, rượu.
+### 14. Cách Bảo Quản
+Thuốc Comiaryl cần được bảo quản ở nơi khô thoáng, nhiệt độ dưới 30°C và tránh ánh sáng.
+### 15. Lưu Ý Khi Bắt Đầu Sử Dụng
+Khi bắt đầu sử dụng thuốc Comiaryl, bạn cần tuân thủ chặt chẽ các hướng dẫn về liều lượng và thời gian dùng để đạt được hiệu quả tốt nhất cũng như tránh các tác dụng không mong muốn.
+### 16. Kết Luận
+Sử dụng thuốc Comiaryl đúng cách đòi hỏi sự tuân thủ chặt chẽ các hướng dẫn từ bác sĩ và nhà sản xuất. Đảm bảo rằng bạn luôn theo dõi sức khỏe của mình và báo cáo bất kỳ triệu chứng không bình thường nào cho bác sĩ.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nên uống nguyên viên thuốc Comiaryl với một cốc nước đầy.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.792160195961841</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6388295226746707</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Khi sử dụng Calci D Hasan, bệnh nhân mắc bệnh lý nền cần đặc biệt chú ý đến một số vấn đề sau:
+- **Chia sẻ lịch sử bệnh:** Bệnh nhân nên thông báo với bác sĩ về tiền sử bệnh và các thuốc đang sử dụng, đặc biệt là trong các bệnh như rối loạn hệ miễn dịch (ví dụ như bệnh sarcoidosis), thiểu năng cận giáp (có thể gây tăng nhạy cảm với vitamin D), suy giảm chức năng thận, tiền sử sỏi thận, bệnh tim, xơ vữa động mạch, bệnh gan, bệnh đường ruột (như bệnh Crohn, bệnh Whipple).
+- **Tương tác thuốc:** Calci D Hasan có thể tương tác với một số loại thuốc khác, làm tăng hoặc giảm tác dụng của chúng. Ví dụ, nó có thể tương tác với các thuốc lợi tiểu thiazid, glycosid tim, và verapamil, gây tăng canxi huyết. 
+- **Tác dụng phụ:** Việc sử dụng quá liều vitamin D có thể gây ra các biểu hiện lâm sàng của rối loạn chuyển hoá calci, bao gồm tăng calci huyết, buồn nôn, chán ăn, táo bón, cảm xúc thay đổi, lẫn lộn, mê sảng, và hôn mê.
+- **Chống chỉ định:** Một số bệnh nhân không nên sử dụng Calci D Hasan, bao gồm những người có tiền sử quá mẫn với bất kỳ thành phần nào của thuốc, hoặc những người mắc bệnh kèm theo hội chứng tăng calci trong máu (như bệnh tăng năng cận giáp, quá liều do vitamin D, có u ác tính tiêu xương…), sỏi thận và suy thận nặng, tăng calci niệu nặng, loãng xương do bất động.
+Do đó, bệnh nhân cần tham khảo ý kiến bác sĩ trước khi sử dụng Calci D Hasan để đảm bảo an toàn và hiệu quả.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ở bệnh nhân mắc bệnh lý nền, Calci D Hasan có thể gây tăng nhạy cảm với vitamin D, làm tăng nguy cơ gây hại cho sức khỏe.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6850464666751789</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1712616166687947</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Khi bảo quản **thuốc bổ thần kinh H5000**, cần tránh những điều kiện sau:
+- **Ánh sáng mặt trời**: Thuốc cần được bảo quản ở nơi tránh ánh sáng mặt trời trực tiếp.
+- **Nhiệt độ cao**: Nhiệt độ bảo quản thuốc không nên vượt quá 30°C.
+- **Ẩm ướt**: Tránh để thuốc ở những nơi ẩm ướt.
+- **Tầm tay trẻ em**: Bảo quản thuốc tránh xa tầm tay của trẻ em.
+Bảo quản thuốc đúng cách sẽ giúp duy trì chất lượng và hiệu quả của sản phẩm.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sản phẩm cần tránh bảo quản ở nơi ẩm ướt, có ánh sáng mặt trời, nhiệt độ cao hơn 30°C.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8167181245652303</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2541795311413076</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Để đảm bảo an toàn, **men vi sinh Biosubtyl** cần được bảo quản tránh xa tầm tay của trẻ em và vật nuôi trong nhà. Nơi thích hợp để bảo quản thuốc là:
+- **Nơi khô ráo, thoáng mát**: Điều này giúp duy trì chất lượng của thuốc và ngăn chặn sự phát triển của vi khuẩn.
+- **Tránh tiếp xúc trực tiếp với ánh sáng**: Ánh sáng có thể ảnh hưởng đến hiệu quả của thuốc.
+- **Tránh để thuốc ở những nơi ẩm ướt**: Độ ẩm có thể làm hỏng hoặc biến đổi thành phần của thuốc.
+Bảo quản thuốc Biosubtyl theo hướng dẫn trên sẽ giúp giữ cho thuốc luôn sẵn sàng sử dụng một cách hiệu quả và an toàn.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Để xa men vi sinh Biosubtyl khỏi tầm với của trẻ nhỏ và động vật để đảm bảo an toàn.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4375953221670513</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1093988305417628</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Khi gặp tình trạng đau nhiều, liều dùng của Cholapan có thể được điều chỉnh để đáp ứng nhu cầu điều trị. Theo hướng dẫn sử dụng, trong trường hợp đau nhiều, có thể tăng liều lên gấp đôi so với liều thông thường. 
+Đối với người lớn, thay vì dùng 2 viên/lần, 2 lần/ngày, bạn có thể dùng 4 viên/lần, 2 lần/ngày. Đối với trẻ em từ 5 tuổi đến dưới 15 tuổi, thay vì dùng 1 viên/lần, 2 lần/ngày, bạn có thể dùng 2 viên/lần, 2 lần/ngày.
+Tuy nhiên, việc tăng liều cần được sự cho phép và giám sát của bác sĩ để đảm bảo an toàn và hiệu quả trong điều trị.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Có thể uống liều gấp đôi (4 viên/lần, ngày 2 lần).</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7955192894100728</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1988798223525182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thuốc cisapride được sử dụng để điều trị các vấn đề về đường tiêu hóa ở trẻ em. Tuy nhiên, cần thận trọng khi sử dụng thuốc này cho trẻ em vì nó có thể gây ra một số tác dụng phụ không mong muốn.
+### Công dụng của Thuốc Cisapride
+- **Táo bón mạn tính và rối loạn tiêu hóa chức năng**: Cisapride có thể giúp tăng cường vận động cơ trơn đường tiêu hóa, cải thiện tình trạng táo bón và rối loạn tiêu hóa chức năng ở trẻ em.
+- **Chứng dạ dày giảm co bóp**: Thuốc này cũng được sử dụng để điều trị chứng dạ dày giảm co bóp, giúp tăng cường khả năng tiêu hóa thức ăn của trẻ.
+### Liều Dùng
+- **Trẻ em**: Liều dùng cho trẻ em thường nằm trong khoảng 0,15 – 0,3 mg/kg/lần, 3 – 4 lần/ngày. Liều tối đa là 10 mg/lần.
+### Lưu Ý Khi Sử Dụng
+- **Quá mẫn**: Nếu trẻ có tiền sử dị ứng với cisaprid hoặc các thành phần khác của thuốc, việc sử dụng thuốc này cần được cân nhắc kỹ.
+- **Tắc cơ học đường tiêu hóa**: Cisapride không nên được sử dụng trong trường hợp trẻ bị tắc cơ học đường tiêu hóa hoặc có nguy cơ bị tắc, thủng và chảy máu đường tiêu hóa.
+- **Suy đa tạng, bệnh phổi tắc nghẽn mạn tính (COPD)**: Thuốc này cũng không nên được sử dụng cho trẻ mắc các bệnh lý nền như suy đa tạng hoặc COPD.
+- **Rối loạn điện giải**: Cần theo dõi chặt chẽ các rối loạn điện giải như hạ kali huyết hoặc thiếu magiê khi sử dụng cisapride.
+### Tác Dụng Phụ
+- **Tiêu chảy, đau bụng, đầy hơi**: Đây là những tác dụng phụ thường gặp nhất khi sử dụng cisapride.
+- **Tiểu tiện nhiều lần**: Một số trẻ có thể gặp phải tình trạng tiểu tiện nhiều lần khi dùng thuốc.
+### Cách Bảo Quản
+- **Bảo quản**: Thuốc cisapride cần được bảo quản ở nhiệt độ 15 – 25°C, tránh ẩm và ánh sáng.
+- **Tránh xa tầm tay trẻ em**: Để tránh trẻ em tiếp xúc trực tiếp với thuốc.
+### Xử Trị Khi Quá Liều
+- **Triệu chứng**: Nếu trẻ bị quá liều, các triệu chứng có thể bao gồm nôn, đau bụng, tiêu chảy, và tiểu tiện nhiều lần.
+- **Xử trí**: Cần đưa trẻ đến trung tâm y tế gần nhất để được điều trị. Phương pháp điều trị bao gồm loại bỏ thuốc bằng cách rửa dạ dày hoặc dùng than hoạt, sau đó theo dõi trẻ chặt chẽ và điều trị hỗ trợ toàn thân.
+### Tham Khảo
+- **Thực hành y tế**: Cần thận trọng khi sử dụng thuốc cisapride cho trẻ em, đặc biệt là trong trường hợp sử dụng lâu dài hoặc trên diện rộng. Việc theo dõi sát sao các triệu chứng quá liều là rất quan trọng.
+### Kết Luận
+Thuốc cisapride có thể hữu ích trong việc điều trị các vấn đề về đường tiêu hóa ở trẻ em, nhưng cần sử dụng thận trọng và theo dõi chặt chẽ để đảm bảo an toàn cho trẻ.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tác dụng trên trẻ em chưa được rõ.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7839781205113456</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6959945301278364</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The recommended usage of Bisilkon is not explicitly mentioned in the provided documents. However, based on the information available, Bisilkon is typically applied according to the specific instructions given by a healthcare provider. It is important to follow the prescribed regimen to ensure effective treatment.
+If you require precise instructions regarding how many times per day to apply Bisilkon, please consult your doctor or pharmacist for personalized guidance.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thuốc Bisilkon bôi 2 lần/ngày vào buổi sáng và buổi tối.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Liều dùng thông thường của thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành thường nằm trong khoảng từ 10/10 mg một ngày đến 80/10 mg một ngày. Liều thường dùng là 10/10 mg một lần/ngày. Liều dùng cụ thể sẽ được xác định dựa trên hiệu quả của các xét nghiệm cũng như đáp ứng với liệu pháp điều trị của mỗi bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng Atorpa-E cho bệnh nhân tăng mỡ và/hoặc có bệnh mạch vành dao động từ 10/10 mg đến 80/10 mg một ngày.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8259721123204598</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2064930280801149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nếu bạn nghi ngờ bị dị ứng với thuốc Aceclofenac STADA, bạn nên:
+- Liên hệ ngay với bác sĩ hoặc chuyên gia y tế để được tư vấn và đánh giá tình trạng sức khỏe.
+- Hạn chế sử dụng thuốc và tránh tiếp xúc với các thành phần gây dị ứng.
+- Theo dõi kỹ các triệu chứng và ghi chú lại để báo cáo cho bác sĩ.
+- Không tự ý ngừng sử dụng thuốc mà không có sự hướng dẫn của bác sĩ.
+Nếu bạn gặp phải các triệu chứng dị ứng như phát ban, mề đay, khó thở, hoặc bất kỳ triệu chứng nào khác mà bạn nghĩ có thể là dấu hiệu của phản ứng dị ứng, hãy gọi cho bác sĩ ngay lập tức hoặc tìm kiếm sự chăm sóc y tế khẩn cấp.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA, hãy ngừng dùng thuốc và đến gặp bác sĩ để được tư vấn và điều trị kịp thời.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.863472896617799</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7158682241294497</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Khi sử dụng Barudon, nếu gặp bất kỳ phản ứng phụ nào, người dùng cần:
+1. Liên hệ ngay với bác sĩ hoặc đến cơ sở y tế gần nhất để được thăm khám cụ thể.
+2. Báo cáo về bất kỳ tác dụng phụ nào xảy ra để được tư vấn hướng giải quyết kịp thời.
+Mục đích là để đảm bảo rằng bất kỳ tác dụng phụ nào đều được kiểm soát và xử lý đúng cách, giúp duy trì an toàn và hiệu quả khi sử dụng thuốc.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần liên hệ với cơ sở y tế để được thăm khám cụ thể.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7832529503691984</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4458132375922996</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone có thể gây ra các tác hại nghiêm trọng. Trong trường hợp này, việc dùng thuốc có thể kích hoạt phản ứng dị ứng hoặc phản ứng quá mẫn, dẫn đến các triệu chứng từ nhẹ đến nghiêm trọng, thậm chí có thể đe dọa tính mạng.
+Tác hại cụ thể có thể bao gồm:
+- Phát ban, ngứa da dữ dội.
+- Sưng mí mắt, mặt và môi.
+- Phù lưỡi và cổ họng gây khó khăn khi thở.
+- Xuất hiện các phản ứng trên da nghiêm trọng như phát ban, ngứa dữ dội, nổi mề đay, đỏ da trên toàn bộ cơ thể, phồng rộp, bong tróc và sưng da, viêm niêm mạc và các phản ứng dị ứng khác.
+Việc sử dụng Aldactone ở bệnh nhân mẫn cảm có thể dẫn đến các phản ứng dị ứng nghiêm trọng, do đó việc tránh sử dụng thuốc này ở những người có mẫn cảm với spironolactone là rất quan trọng.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ở những bệnh nhân mẫn cảm với spironolactone, thuốc này có thể gây ra các phản ứng dị ứng nghiêm trọng, có thể mengan dọa tính mạng.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7877969791499936</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.6969492447624984</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nếu bạn quên uống một liều **Cardilopin**, bạn nên thực hiện các bước sau:
+1. **Dùng thuốc ngay khi nhớ ra**: Nếu bạn nhớ ra đã quên liều, hãy uống thuốc ngay lập tức. Điều này giúp duy trì mức độ ổn định của thuốc trong cơ thể.
+2. **Không dùng gấp đôi liều**: Nếu liều đã quên gần với liều kế tiếp, bạn nên bỏ qua liều đã quên và tiếp tục dùng liều kế tiếp theo lịch trình đã định. Không nên uống gấp đôi liều để tránh tình trạng quá liều.
+3. **Tuân thủ lịch trình**: Nếu quên liều và nhớ ra sau khi đã uống liều kế tiếp, hãy tiếp tục lịch trình dùng thuốc bình thường.
+Thực hiện đúng các bước trên sẽ giúp đảm bảo rằng bạn vẫn duy trì mức độ ổn định của thuốc trong cơ thể và tránh được tình trạng quá liều.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bạn nên dùng bổ sung ngay khi nhớ ra, trường hợp nhớ ra trễ hơn 12 giờ so với giờ dùng thuốc hàng ngày, hãy bỏ qua liều đã quên và không dùng thêm thuốc để bù khi dùng liều tiếp theo.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8897297646326082</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2224324411581521</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc **Cilzec** cho trẻ em, cần lưu ý một số điểm sau:
+- **Tuân thủ chỉ định của bác sĩ**: Chỉ sử dụng thuốc Cilzec cho trẻ em khi có sự chỉ định của bác sĩ. Điều này nhằm đảm bảo an toàn và hiệu quả khi sử dụng thuốc.
+- **Nhận biết tác dụng phụ**: Cần thận trọng và theo dõi chặt chẽ bất kỳ tác dụng phụ nào có thể xảy ra khi sử dụng thuốc. Các tác dụng phụ tiềm ẩn có thể bao gồm thiểu niệu, tăng urê huyết, suy thận cấp và thậm chí tử vong trong một số trường hợp.
+- **Bảo quản thuốc đúng cách**: Giữ thuốc ở nơi khô ráo, thoáng mát, tránh ánh sáng và ẩm. Đồng thời, bảo quản thuốc xa tầm tay trẻ em để tránh việc trẻ tự ý sử dụng.
+- **Kiểm tra màu sắc thuốc**: Không sử dụng thuốc nếu có bất kỳ sự thay đổi bất thường nào về màu sắc.
+- **Tham khảo ý kiến chuyên môn**: Nếu cần thêm thông tin về thuốc, hãy liên hệ với bác sĩ hoặc dược sĩ.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Độ hiệu quả, an toàn của thuốc trên trẻ em chưa được làm rõ. Do đó, chỉ sử dụng thuốc cho trẻ em khi có sự chỉ định của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8404702834567422</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4601175708641856</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>**Thuốc Atarax (Hydroxyzine)** có thể tương tác với một số thuốc khác. Tuy nhiên, trong văn bản cung cấp, không có thông tin cụ thể về các tương tác của Atarax với các loại thuốc khác. Để đảm bảo an toàn khi sử dụng Atarax, bạn nên thông báo cho bác sĩ về tất cả các loại thuốc bạn đang sử dụng, bao gồm cả thuốc kê đơn, thuốc không kê đơn, vitamin, và thảo dược.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với các thuốc như epinephrin, barbiturat, thuốc an thần khác, droperidol, pramlintid, thuốc gây tê mê, rượu, các chất ức chế acetylcholinesterase, chất giảm đau và các thuốc opiat.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.312499999975</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Để bảo quản thuốc Comozol tốt nhất, bạn cần tuân thủ các điều kiện sau:
+- **Tránh ánh sáng**: Đặt thuốc ở nơi tránh khỏi ánh sáng trực tiếp.
+- **Nơi khô mát**: Bảo quản thuốc ở nơi khô ráo, tránh ẩm ướt.
+- **Nhiệt độ**: Đảm bảo nhiệt độ bảo quản dưới 30°C.
+Bằng cách tuân thủ những điều kiện này, bạn sẽ giúp kéo dài tuổi thọ và duy trì chất lượng của thuốc Comozol.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bạn cần tránh ánh sáng, bảo quản nơi khô mát và giữ thuốc ở nhiệt độ dưới 30°C để bảo quản thuốc Comozol tốt nhất.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7943321862291736</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4485830465572934</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Amitriptylin và xuất hiện các triệu chứng bất thường, cần thực hiện các bước sau:
+1. **Ngừng Sử Dụng Thuốc**: Ngay lập tức ngừng sử dụng thuốc Amitriptylin và không tiếp tục dùng thêm liều nào.
+2. **Tham Khảo Ý Kiến Bác Sĩ**: Liên hệ với bác sĩ hoặc dược sĩ để được tư vấn cụ thể. Họ sẽ đánh giá tình trạng của bạn và đưa ra hướng dẫn tiếp theo.
+3. **Theo Dõi Tình Trạng**: Theo dõi các triệu chứng của mình và ghi chú lại để báo cáo cho bác sĩ.
+4. **Đi Khoa Cấp Cứu Nếu Cần Thanh**: Nếu triệu chứng trở nên nghiêm trọng, như co giật, mất ý thức, khó thở, hoặc bất kỳ triệu chứng nào khác mà bạn cảm thấy lo ngại, hãy đến ngay cơ sở y tế gần nhất để được xử lý kịp thời.
+Dưới đây là một số triệu chứng bất thường mà bạn có thể gặp khi sử dụng Amitriptylin:
+- **Ngủ gà, lú lẫn, co giật (động kinh)**: Đây là những triệu chứng nghiêm trọng và cần được xử lý ngay lập tức.
+- **Mất tập trung, giãn đồng tử, rối loạn nhịp tim, ảo giác, kích động, thở nông, khó thở, yếu mệt, nôn, khô miệng**.
+Việc xử lý kịp thời những triệu chứng bất thường sẽ giúp giảm thiểu tác hại và đảm bảo an toàn cho sức khỏe của bạn.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cần gọi ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.832478583986819</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2081196459967047</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Coversyl Plus, cần đặc biệt lưu ý đối với những người bị suy gan hoặc suy thận:
+- **Người suy gan**: 
+  - Chống chỉ định dùng thuốc với bệnh nhân suy gan nặng.
+  - Ở bệnh nhân suy gan vừa, không cần hiệu chỉnh liều.
+- **Người suy thận**: 
+  - Hiệu chỉnh liều perindopril theo chức năng thận.
+  - Theo dõi thường xuyên nồng độ kali và creatinin huyết trên đối tượng này.
+Đối với bệnh nhân chạy thận nhân tạo, cần lưu ý tác dụng phụ như phản ứng phản vệ khi dùng thuốc. Việc sử dụng thuốc này nên cân nhắc kỹ lưỡng và tuân theo hướng dẫn của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thận trọng dùng thuốc Coversyl Plus ở người suy gan, suy thận.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8395269668177597</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.45988174170444</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong một số trường hợp cụ thể sau đây:
+1. **Người hay bị rối loạn chức năng gan**: Argide hỗ trợ điều trị các rối loạn chức năng gan.
+2. **Trường hợp cơ thể suy nhược và sức khỏe kém**: Thuốc này cũng được sử dụng trong các trường hợp cơ thể suy nhược và sức khỏe kém.
+3. **Người mắc những bệnh liên quan đến gan**: Argide có thể được sử dụng để hỗ trợ điều trị các bệnh liên quan đến gan.
+4. **Tăng amoniac huyết bẩm sinh hoặc do rối loạn chu trình urê**: Thuốc này được chỉ định trong trường hợp tăng amoniac huyết bẩm sinh hoặc do rối loạn chu trình urê.
+5. **Điều trị nhiễm kiềm chuyển hoá**: Argide cũng được sử dụng trong điều trị nhiễm kiềm chuyển hoá.
+### Lưu ý
+Bạn nên sử dụng thuốc theo hướng dẫn của bác sĩ. Liều lượng và cách sử dụng thuốc cần được điều chỉnh phù hợp với tình trạng sức khỏe và độ tuổi của từng bệnh nhân.
+### Chống chỉ định
+Trước khi sử dụng Argide, cần chú ý đến các chống chỉ định như:
+- Bệnh nhân có tiền sử hoặc nguy cơ dị ứng với bất kỳ thành phần nào của thuốc.
+- Người đang bị tăng Amoniac huyết do nhiễm Acid hữu cơ trong máu.
+- Bệnh nhân đang rối loạn chu trình urê và đang thiếu hụt enzym arginase.
+### Bảo quản
+Thuốc Argide cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30°C, tránh ánh sáng trực tiếp.
+### Tác dụng phụ
+Bạn có thể gặp phải một số tác dụng phụ khi sử dụng Argide, bao gồm buồn nôn, nôn ói, nhức đầu, giảm tiểu cầu, hạ huyết áp, co cứng cơ bụng, tăng Kali huyết ở người có bệnh lý về gan, thận, tiểu đường.
+### Tương tác thuốc
+Thuốc Argide có thể tương tác với một số loại thuốc khác như thuốc lợi tiểu thiazid, xylitol, aminophylin, thuốc trị tiểu đường nhóm sulfonylurea, thuốc trị động kinh phenytoin, và thuốc lợi tiểu tiết kiệm kali.
+### Xử lý khi quên liều
+Nếu bạn quên dùng một liều thuốc, hãy dùng càng sớm càng tốt. Tuy nhiên, nếu gần với liều kế tiếp, bạn hãy bỏ qua liều đã quên và dùng liều kế tiếp vào thời điểm như kế hoạch. Không dùng gấp đôi liều đã quy định.
+### Xử lý khi dùng quá liều
+Nếu bạn nhận thấy các biểu hiện từ bệnh nhân có nghi ngờ do sử dụng quá liều thuốc, hãy nhanh chóng đưa bệnh nhân đến trung tâm y tế gần nhất để được xử trí kịp thời.
+### Giá thuốc
+Giá bán thuốc Argide trên thị trường hiện nay khoảng 135.000 VNĐ/hộp 60 viên nang. Tuy nhiên, mức giá có thể thay đổi tùy thuộc vào chính sách bán hàng của nhà cung cấp.
+### Cautions
+Để đảm bảo an toàn và hiệu quả điều trị, bạn nên tham khảo ý kiến của chuyên gia y tế trước khi sử dụng thuốc.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide hỗ trợ điều trị các chứng rối loạn khó tiêu và hỗ trợ các bệnh lý về gan.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8210348472904898</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6552587118226225</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra một số tác dụng phụ ở người cao tuổi:
+1. **Buồn ngủ**: Người cao tuổi có thể gặp tình trạng buồn ngủ khi sử dụng Depakin. 
+2. **Tác dụng phụ khác**: Ngoài ra, người cao tuổi cũng có thể gặp các tác dụng phụ thường gặp khi sử dụng Depakin, bao gồm rối loạn trí nhớ, nhức đầu, hồi hộp, rung giật nhãn cầu, phù ngoại biên, rối loạn tiêu hóa như buồn nôn, nôn, tiêu chảy, đau bụng, đầy hơi, táo bón, khó tiêu.
+3. **Theo dõi chặt chẽ**: Do khả năng gặp nhiều tác dụng phụ hơn so với bệnh nhân trẻ tuổi, người cao tuổi cần được theo dõi chặt chẽ và có thể cần điều chỉnh liều lượng nếu cần thiết.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ buồn ngủ ở người cao tuổi.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8451111739501894</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4612777934875474</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thuốc **Acyclovir Stada 200 mg** có tác dụng mạnh nhất đối với virus *Herpes simplex* type 1. Thuốc cũng có tác dụng đối với virus *Herpes simplex* type 2 và virus *Varicella zoster*, nhưng độ nhạy của chúng với acyclovir kém hơn so với virus *Herpes simplex* type 1.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Acyclovir Stada 200 mg có tác dụng mạnh nhất trên virus Herpes simplex type 1, kém hơn ở virus Herpes simplex 2 và virus Varicella zoster.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8744558072438843</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2186139518109711</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần thực hiện các bước sau:
+1. **Tham khảo ý kiến bác sĩ**: Người dùng nên tham khảo ý kiến của bác sĩ hoặc chuyên gia y tế trước khi bắt đầu sử dụng thuốc. Bác sĩ sẽ đánh giá tình trạng sức khỏe và đưa ra quyết định phù hợp về việc sử dụng thuốc này ([1]).
+2. **Hiểu rõ về thuốc**: Bệnh nhân cần hiểu rõ về tác dụng, cách dùng, liều lượng, và các tác dụng phụ có thể xảy ra của thuốc Dalacin T ([1], [7]).
+3. **Kiểm tra tương tác thuốc**: Nếu đang sử dụng các loại thuốc khác, bệnh nhân cần thông báo cho bác sĩ để kiểm tra xem có tương tác giữa các thuốc hay không ([1]).
+4. **Đọc kỹ hướng dẫn sử dụng**: Trước khi bắt đầu sử dụng, bệnh nhân cần đọc kỹ hướng dẫn sử dụng được cung cấp bởi nhà sản xuất ([1]).
+5. **Theo dõi phản ứng**: Trong quá trình sử dụng, bệnh nhân cần theo dõi bất kỳ phản ứng nào không mong muốn và báo cáo lại cho bác sĩ ([1]).</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tham khảo ý kiến ​​bác sĩ hoặc chuyên gia y tế để đảm bảo liều dùng phù hợp.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.863460961985499</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2158652404963748</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol chứa 72.000 UI Vitamin D2.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa 72000UI Vitamin D2.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8485924931549064</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4621481232887266</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bạn nên rửa tay trước khi sử dụng thuốc Combigan. Điều này giúp đảm bảo vệ sinh và giảm thiểu nguy cơ nhiễm trùng. Sau khi rửa tay, bạn nên thoa một lớp màng mỏng thuốc lên vùng mắt bị ảnh hưởng và chà xát nhẹ nhàng.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Có, bạn cần rửa sạch tay trước khi sử dụng thuốc Combigan để tránh nhiễm trùng mắt.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6231265170324409</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.4057816292581102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>**An Cung Ngưu Hoàng Hoàn** có thể được sử dụng trong một số trường hợp cụ thể liên quan đến đột quỵ hoặc tai biến mạch máu não. Tuy nhiên, việc sử dụng thuốc này cần được chỉ định và theo dõi bởi chuyên gia y tế.
+1. **Thuốc có thể được sử dụng trong các trường hợp sau:**
+   - Giai đoạn cấp tính thường gặp của bệnh lý viêm não, viêm màng não, tai biến mạch não (có các triệu chứng sốt cao, huyết áp tăng,..).
+   - Để hạ sốt do nhiễm trùng đường hô hấp trên, viêm phổi cấp tính, viêm amidan, viêm ruột cấp tính.
+   - Đối với các trường hợp hôn mê gan, thuốc có thể giúp hồi phục ý thức.
+2. **Chống chỉ định:**
+   - Thuốc không phải là giải pháp cho mọi trường hợp đột quỵ. Nó không thể được sử dụng cho tất cả các trường hợp đột quỵ hay tai biến mạch máu não.
+   - Chống chỉ định ở những đối tượng sau: 
+     - Bệnh nhân tai biến xuất huyết não diện rộng, chảy máu nhiều.
+     - Người thể hàn, dương hư, tỳ vị hư hàn, suy giảm chức năng gan thận.
+     - Phụ nữ có thai và cho con bú tuyệt đối không dùng thuốc.
+3. **Lưu ý khi sử dụng:**
+   - Cần tuân thủ hướng dẫn sử dụng thuốc, bao gồm việc kiêng các món ăn cay nóng hậu vị để tránh trợ hỏa sinh đàm.
+   - Việc sử dụng thuốc cần được kiểm soát chặt chẽ về liều dùng, đường dùng, người dùng và phải có sự tư vấn của bác sĩ Đông y.
+Tóm lại, An Cung Ngưu Hoàng Hoàn có thể được sử dụng trong một số trường hợp cụ thể liên quan đến đột quỵ hoặc tai biến mạch máu não, nhưng việc sử dụng cần tuân theo chỉ định của bác sĩ chuyên môn.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Không thể dùng cho tất cả các trường hợp đột quỵ hay tai biến mạch máu não, việc dùng thuốc cần được chỉ định và theo dõi của chuyên gia y tế.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8452359436165954</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.6696423192374822</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Avelox (moxifloxacin), người bệnh cần cân nhắc tình trạng sức khỏe tim mạch của mình. Theo tài liệu, thuốc này có thể gây tác dụng phụ như loạn nhịp tim, hạ huyết áp, và một số tác dụng khác có thể ảnh hưởng đến chức năng tim. Đặc biệt, Moxifloxacin không nên được sử dụng cho những người có vấn đề về tim mạch, cụ thể là:
+- Người bệnh đang bị suy tim.
+- Người bệnh có rối loạn nhịp tim, đặc biệt là những người có bệnh mạch vành.
+Do đó, nếu bạn đang gặp vấn đề với tim, việc sử dụng Avelox cần được bác sĩ chuyên khoa đánh giá kỹ lưỡng trước khi quyết định.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Không, nếu bệnh nhân đã từng được chẩn đoán rối loạn nhịp tim, suy tim hoặc nhịp tim chậm thì không được sử dụng thuốc này.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.6476249520306504</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.1619062380076626</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>**Thuốc trị viêm da axit salicylic có nồng độ trên 10% không được sử dụng cho những đối tượng sau:**
+- **Người bị nhiễm khuẩn, viêm, hoặc kích ứng da:** Không sử dụng thuốc trên vùng da bị nhiễm khuẩn, viêm hoặc kích ứng.
+- **Mặt, bộ phận sinh dục, mũi, miệng, nốt ruồi, vết chàm, mụn cơm có lông mọc:** Không sử dụng thuốc trên những vùng da nhạy cảm như mặt, bộ phận sinh dục, mũi, miệng, nốt ruồi, vết chàm, mụn cơm có lông mọc.
+- **Người bệnh bị đái tháo đường hoặc suy tuần hoàn:** Người mắc các bệnh như đái tháo đường hoặc suy tuần hoàn cũng không nên sử dụng thuốc này.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nồng độ trên 10% của thuốc trị viêm da axit salicylic không được sử dụng cho đối tượng bệnh nhân bị bẹnh tiểu đường hoặc suy tuần hoàn.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.7037364539484837</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.425934113487121</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>['Document Chunks (Each entry has a reference_id refer to the `']</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp sau:
+- **Viêm nhiễm sau chấn thương hay phẫu thuật**: Thuốc có tác dụng giảm viêm và phù nề.
+- **Bệnh trĩ (trĩ ngoại, trĩ nội)**: Thuốc giúp điều trị các triệu chứng liên quan đến bệnh trĩ.
+- **Sa hậu môn**: Thuốc được sử dụng để điều trị tình trạng sa hậu môn.
+- **Viêm xoang, viêm tai giữa, viêm họng, polyp mũi**: Thuốc có tác dụng giảm viêm ở các bộ phận này.
+- **Dùng phối hợp với kháng sinh trong các trường hợp nhiễm trùng**: Thuốc cũng được sử dụng kết hợp với kháng sinh để điều trị nhiễm trùng và long đàm trong các bệnh liên quan đến đường hô hấp (viêm phế quản, hen phế quản, viêm phổi, lao).
+- **Viêm nha chu, áp xe ổ răng, viêm túi lợi răng khôn**: Thuốc được sử dụng sau khi nhổ răng và sau phẫu thuật răng hàm mặt.
+- **Xuất huyết ở mắt, hay đục thủy tinh thể**: Thuốc có tác dụng trong các trường hợp này.
+- **Căng tuyến vú, rách hoặc khâu tầng sinh môn ở sản phụ**: Thuốc được sử dụng để điều trị các tình trạng này.
+- **Những bệnh đường tiết niệu (viêm bàng quang hay viêm mào tinh)**: Thuốc có thể được sử dụng trong điều trị các bệnh đường tiết niệu.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp viêm nhiễm sau phẫu thuật hay sau chấn thương.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.8539621130072467</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.4634905282518117</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,49 +2205,1716 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biviantac có thể điều trị trướng bụng, đầy hơi không?</t>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Nhàm trường: Nhàm trường, giải khát.\nHay ngứa: Hay ngứa là một triệu chứng của nhiễm ký sinh trùng.\nKhóc nhiều, dễ xúc động: Khóc nhiều, dễ xúc động.\nNấm: Nấm là một tình trạng nhiễm trùng phức tạp có thể xuất hiện ở nhiều vị trí khác nhau trên cơ thể con người, từ da, tóc, móng tay, cho đến khoang miệng và vùng hầu họng. Các loại nấm như nấm móng, nấm tóc, nấm da, và lang ben đều thuộc nhóm ký sinh trùng này. Nấm có thể gây ra các vấn đề sức khỏe như nhiễm trùng vết thương ở khoang miệng và vùng hầu họng, cũng như gây ra các tình trạng khác như nhiễm trùng da và mắt. Ví dụ, nấm thuộc họ Malassezia và Cutibacterium có thể gây ra mụn trên đầu.\n\nĐối với việc điều trị nấm, có nhiều phương pháp khác nhau. Ví dụ, vỏ quả Bồ hòn phơi khô nấu trong dầu lạc có thể được sử dụng để hỗ trợ điều trị nấm. Ngoài ra, Gel Lô hội có thể được sử dụng để điều trị các triệu chứng liên quan đến nhiễm trùng da do nấm. Cỏ tháp bút được biết đến với khả năng kháng lại nấm, cho thấy sự đa dạng của tác động mà nấm có thể có đối với các loài thực vật và động vật khác nhau.\n\nNgoài ra, nấm còn là đối tượng thử nghiệm trong nghiên cứu về tác dụng kháng khuẩn của hạt Nhục đậu khấu. Trong một số trường hợp, nấm có thể gây suy tuyến yên và suy gan cấp. Hàm lượng purin của nấm là vừa phải, và thực phẩm thuộc họ nấm như mộc nhĩ rất tốt cho người bệnh bị tăng men gan.\n\nTóm lại, nấm là một loại vi khuẩn hoặc sinh vật vi mô có thể gây bệnh và có thể được điều trị bằng nhiều phương pháp khác nhau tùy thuộc vào vị trí và mức độ nghiêm trọng của nhiễm trùng.&lt;SEP&gt;Nấm có thể gây viêm âm đạo với triệu chứng như ngứa rát âm đạo và dịch âm đạo trắng, đặc, đóng cục.&lt;SEP&gt;Nấm có thể gây ra viêm não.&lt;SEP&gt;Nấm là nguyên nhân gây bệnh ở người có hệ miễn dịch suy yếu hoặc ở người hít phải liều lượng lớn các sinh vật.&lt;SEP&gt;Nấm là một trong những nguyên nhân gây viêm tái tạo cổ tử cung.&lt;SEP&gt;Nấm có thể gây viêm thực quản.\nVị ngọt, tính hàn: Củ niëng có vị ngọt, tính hàn.\nTía tô: Tía tô, còn được gọi là Perilla frutescens, là một loại cây thảo dược đa năng được sử dụng rộng rãi trong y học cổ truyền và trong nấu ăn. Tía tô được biết đến với nhiều công dụng khác nhau, bao gồm cả việc điều trị các triệu chứng cảm cúm và các vấn đề về tiêu hóa. Nó thường được sử dụng trong các bài thuốc sắc nước uống, kết hợp với các thành phần khác như sả, mùi tàu, và sa nhân tím để tăng hiệu quả điều trị.\n\nNgoài ra, tía tô cũng được sử dụng trong việc điều trị các vấn đề tiêu hóa như đau bụng, rối loạn tiêu hóa và tiêu chảy. Trong y học cổ truyền, tía tô được coi là một nguyên liệu quý giúp hỗ trợ điều trị các bệnh lý như mề đay và giải độc từ việc ăn hải sản. Tía tô còn được sử dụng trong bài thuốc chữa cảm mạo phong hàn, thể hiện tính linh hoạt và đa dạng của nó trong việc hỗ trợ sức khỏe tổng thể.\n\nTía tô không chỉ đóng vai trò là một loại cây thuốc mà còn là một loại rau gia vị phổ biến, được sử dụng trong nhiều món ăn khác nhau.&lt;SEP&gt;Tía tô là một loại cây được sử dụng trong y học hiện đại và cổ truyền, có nhiều tác dụng như kháng khuẩn, chống nấm, ngăn ngừa dị ứng, tăng bài tiết dịch tiêu hóa, tăng nhu động ruột, giảm co thắt cơ trơn của phế quản, và kích thích tiết mồ hôi.&lt;SEP&gt;Lá Tía tô được sử dụng để điều trị cảm lạnh và cành Tía tô được sử dụng để điều trị triệu chứng như đau thượng vị, ợ hơi, buồn nôn, nôn mửa, và động thai.&lt;SEP&gt;Tía tô là một loại cây thuộc họ Hoa môi, có tên khoa học là Perilla frutescens (L.) Britt. Các bộ phận của cây này, bao gồm lá, quả, và cành, đều được sử dụng để làm thuốc.&lt;SEP&gt;Tía tô là một loại thảo dược quan trọng đã được ghi nhận trong kinh điển y học cổ truyền, được sử dụng để điều trị các bệnh liên quan đến trầm cảm, lo âu, hen suyễn, dị ứng, cảm lạnh, nôn mửa, đau bụng và khó tiêu.&lt;SEP&gt;Tía tô có truyền thống sử dụng lâu đời trong y học và ẩm thực.&lt;SEP&gt;Tía tô là một vị thuốc kết hợp với Tử uyển trong bài thuốc chữa ho gà.\nQuả hạt: Quả hạt dùng trị đầy hơi, tiêu chảy, thấp khớp.\nsốt: Sốt là một triệu chứng thường gặp trong nhiều tình trạng sức khỏe khác nhau. Nó thể hiện sự tăng nhiệt độ cơ thể và có thể xuất hiện khi mắc các bệnh như viêm xoang, viêm họng, hoặc cảm lạnh. Sốt cũng là một trong những triệu chứng của trùng huyết do thắt dây chun và có thể xảy ra khi sử dụng thuốc như Danapha Trihex 2mg. Ngoài ra, sốt cũng là triệu chứng của bệnh nhân bị sỏi bùn túi mật. Húng chanh được biết đến với tác dụng giảm sốt.&lt;SEP&gt;Sốt là triệu chứng của nhiễm trùng tiểu trên.&lt;SEP&gt;Sốt là tình trạng thân nhiệt tăng cao hơn bình thường.&lt;SEP&gt;Sốt là triệu chứng gợi ý tình trạng nhiễm trùng.\nSở thích cố định, rập khuôn: Sở thích cố định, rập khuôn.\nLá cây: Lá cây là bộ phận của cây Dung được sử dụng trong y học dân gian và nghiên cứu khoa học.&lt;SEP&gt;Lá cây được sử dụng để sắc lấy nước dùng.&lt;SEP&gt;Lá cây chứa iridoid-10-methylixoside.&lt;SEP&gt;Lá cây găng tu hú thường được sử dụng để làm sương sâm.&lt;SEP&gt;Lá cây Tai chua hình trứng ngược, màu xanh lục, có kích thước khoảng 6 – 12cm dài và 3 – 5cm rộng.&lt;SEP&gt;Lá cây Thạch hộc dài khoảng 12cm, rộng khoảng 2 – 3cm, có hình thuôn dài, mọc so le tạo thành 2 dãy đều 2 bên thân. Trên mặt lá có 5 gân dọc và hầu như không có cuống.\nTua cuốn: Tua cuốn đơn, mọc đối diện với lá.\nNước: Nước là một hợp chất hóa học quan trọng, đóng vai trò thiết yếu trong nhiều loại thực vật và quá trình y tế. Trong thực vật, nước được tìm thấy với hàm lượng khác nhau: cây trứng cá chứa 77.8g nước mỗi 100g quả, trong khi củ niễng chỉ chứa 9,2% nước. Nước cũng là thành phần chính trong cây sương sâm và mồng tơi, góp phần tạo nên cấu trúc của chúng.\n\nTừ góc độ hóa học, nước chứa các dạng hợp chất của Fluor, chịu ảnh hưởng bởi nhiều yếu tố như khả năng hòa tan của Fluor, sự xói mòn đất đá, nhiệt độ, và độ pH. Điều này cho thấy tính chất đa dạng của nước trong môi trường tự nhiên.\n\nTrong lĩnh vực y tế, việc uống nước có thể giúp nâng cao huyết áp khi gặp tình trạng tụt huyết áp đột ngột. Ngoài ra, việc uống đủ nước là yêu cầu cần thiết khi sử dụng thuốc Ciprofloxacin. Nước còn được sử dụng như một thành phần dinh dưỡng hỗ trợ giảm đau cơ.\n\nNhư vậy, nước không chỉ là thành phần quan trọng trong nhiều loại thực vật mà còn đóng vai trò quan trọng trong các quy trình y tế và sức khỏe tổng thể.&lt;SEP&gt;Uống đủ 2 lít nước mỗi ngày giúp duy trì lượng nước thích hợp trong dịch mật và ngăn ngừa sự lắng đọng tạo sỏi mật.&lt;SEP&gt;Nước là chất cần thiết cho cơ thể, góp phần duy trì huyết áp.&lt;SEP&gt;Nước chiếm 99,5% thành phần của nước bọt.&lt;SEP&gt;Uống nhiều nước giúp thải vi khuẩn ra khỏi đường tiết niệu.&lt;SEP&gt;Nước có thể tồn đọng trong ống tai tạo điều kiện cho vi khuẩn phát triển và gây viêm ống tai ngoài.\nmát: Mát là tình trạng thân nhiệt thấp, dễ chịu.\nAzithromycin: Azithromycin là một loại thuốc kháng sinh thuộc nhóm macrolid, được sử dụng để điều trị nhiều loại nhiễm trùng. Nó là hoạt chất chính trong các thuốc như Azibiotic và Azithromycin DHG, cũng như Azicine. Azithromycin có tác dụng diệt khuẩn mạnh và thường được sử dụng như một lựa chọn thay thế cho penicillin khi bệnh nhân bị dị ứng với penicillin. Thuốc này cũng được sử dụng để điều trị hạ cam mềm. Ngoài ra, azithromycin còn được biết đến với khả năng tăng cường nồng độ hoặc tác dụng của Amiodarone.&lt;SEP&gt;Azithromycin là một loại thuốc kháng sinh được sử dụng trong điều trị viêm amidan cấp do liên cầu khuẩn.&lt;SEP&gt;Azithromycin là một loại thuốc kháng sinh đường uống được sử dụng để điều trị viêm họng do liên cầu khuẩn.\nSuy yếu, phá hủy cơ bắp: Suy yếu, phá hủy cơ bắp.\nCarbamazepin: Carbamazepin là một loại thuốc chống co giật được sử dụng để điều trị bệnh động kinh, rối loạn tâm trạng, giảm đau dây thần kinh và điều trị căng cơ thắt lưng. Thuốc này có khả năng tương tác với nhiều loại thuốc khác nhau, bao gồm Acemol 325 mg, Agifuros 40 mg, Appeton Lysine Syrup, Asevictoria Mediplantex, Avalo, Benda, và cefixim. Khi sử dụng cùng với Erythromycin, nồng độ của carbamazepin trong máu có thể tăng lên. Tương tác với Asevictoria Mediplantex có thể làm giảm tác dụng tránh thai của levonorgestrel. Sử dụng cùng với Avalo có thể làm giảm hiệu quả của Avalo. Tuy nhiên, carbamazepin không tương tác với Azithromycin. Tương tác với Benda có thể làm giảm nồng độ của Mebendazol trong huyết tương. Khi sử dụng cùng với cefixim, nồng độ của carbamazepin trong huyết tương có thể tăng lên do sự tương tác giữa hai loại thuốc này.\n\nNgoài ra, carbamazepin còn có khả năng kích thích gan sản xuất các enzym giúp chuyển hóa paracetamol thành các chất có hại. Thuốc này cũng có thể tương tác với Coldacmin, Davibest, và B Complex C.&lt;SEP&gt;Carbamazepin is listed as one of the other drugs mentioned in the text.&lt;SEP&gt;Carbamazepin là một thuốc có thể tương tác với Daktarin.&lt;SEP&gt;Carbamazepine is a drug that interacts with Dexamethasone and is used in medical treatments.\nBuồn nôn, nôn và tiêu chảy: Buồn nôn, nôn và tiêu chảy.\nErythromycin: Erythromycin là một loại kháng sinh thuộc nhóm macrolides, thường được sử dụng để điều trị các nhiễm khuẩn khác nhau. Nó là hoạt chất chính trong Agi-Ery và có phổ tác dụng rộng đối với nhiều vi khuẩn Gram dương. Erythromycin cũng có khả năng tăng nồng độ trong nhu mô phổi khi dùng kết hợp với Ambroxol Boston, một thuốc long đờm. \n\nLoại kháng sinh này có thể tương tác với một số loại thuốc khác như desloratadine và Acnequidt 20 ml, có thể làm thay đổi hiệu quả của các thuốc đó. Khi sử dụng cùng lúc, Erythromycin có thể làm giảm tác dụng của Amoxicillin Mekophar và Ampicillin Brawn. Ngoài ra, Erythromycin cũng được sử dụng trong điều trị bạch hầu và hạ cam mềm. Tuy nhiên, loại kháng sinh này cũng tăng nguy cơ tổn thương cơ khi sử dụng cùng với Atorvastatin.\n\nErythromycin cũng là hoạt chất trong Anapa, một kháng sinh thuộc nhóm macrolides có tác động trực tiếp lên khuẩn Propionibacterium acnes, giúp giảm tiết bã nhờn và có tác động kháng viêm. Loại kháng sinh này còn được sử dụng trong các liệu pháp điều trị da, đặc biệt là trong việc giảm viêm và kiểm soát tình trạng tiết bã nhờn trên da. Erythromycin cũng được đề cập trong hướng dẫn sử dụng Azaroin gel và có tác dụng tương tự như Azithromycin nhưng yếu hơn trên vi khuẩn Gram dương.\n\nNgoài ra, Erythromycin có thể tương tác với các thuốc khác như Ambroxol, Desloratadine, và Davibest. Erythromycin cần tránh sử dụng cùng với Adagrin do có khả năng tương tác không mong muốn. Thuốc này cũng có thể tương tác với methylprednisolone và Bilastine. Erythromycin được coi là an toàn hơn khi sử dụng cho phụ nữ mang thai hoặc cho con bú.\n\nErythromycin còn được sử dụng kết hợp với benzoyl peroxide trong các chế phẩm điều trị mụn. Thuốc erythromycin tiêm tĩnh mạch có thể làm tăng nồng độ/tác dụng của Amiodarone.&lt;SEP&gt;Erythromycin là một loại thuốc mà không nên sử dụng cùng với Cisaprid.&lt;SEP&gt;Erythromycin là một loại thuốc có tương tác với cisaprid.&lt;SEP&gt;Erythromycin là kháng sinh dùng đồng thời với Clarityne có thể làm tăng nồng độ loratadin trong huyết tương.\nTrán vồ: Trán vồ, cằm nhô, tăng khoảng cách giữa các răng.\nNôn: Nôn, còn được biết đến với tên gọi "vomiting" trong tiếng Anh, là một triệu chứng tiêu hóa mà bệnh nhân có thể trải qua khi sử dụng các loại thuốc hoặc gặp phải tình trạng sức khỏe cụ thể. Đây là hành động co bóp dạ dày nhằm đẩy thức ăn hoặc dịch vị từ dạ dày lên miệng. Nôn có thể xuất hiện như một tác dụng phụ của việc sử dụng nhiều loại thuốc khác nhau, bao gồm Acyclovir, A.t Ibuprofen Syrup, Acepron 250 mg, Erythromycin, Adkold - New, và nhiều loại thuốc khác như Antimuc An Thiên, Aspirin MKP 81, Aticef, Atocib, Atorlog, Augbactam, Azithromycin, Bisoloc, và Cedipect F. Ngoài ra, nôn cũng là một tác dụng phụ hiếm gặp khi sử dụng Aerius 5 mg, Allopurinol, Alzental Shinpoong, thuốc Ambroxol, thuốc Ambroxol Boston, Amoxicilin 500 mg, Amoxicillin Domesco, Amoxicillin Mekophar, Ampicillin Brawn, Ampicillin Vidipha, và Interferon Gamma-1b có trong thuốc Anaferon Materia. Nó cũng có thể xuất hiện khi sử dụng quá liều ibuprofen hoặc do tiêu thụ lượng canxi quá mức. Đồng thời, nôn cũng là triệu chứng phổ biến của ngộ độc mạn tính và là một trong những tác dụng phụ ít gặp của một số loại thuốc khác nhau.\n\nNôn cũng là tác dụng phụ khi sử dụng các loại thuốc như Brodicef, Cefadroxil, Cefimbrano 100, Cefurich, Cefurobiotic, Cefuroxim, và Cefuroxim axetil. Nôn cũng có thể xảy ra khi dùng quá liều Calcigenol, Calcium Corbiere Extra, và Chymodk. Nôn cũng là tác dụng phụ thường gặp khi sử dụng Trimethoprim và Coversyl. Nôn cũng là một tác dụng phụ của việc sử dụng thuốc Curam và Cyclo Progynova. Ngoài ra, nôn cũng là tác dụng phụ của Advil, có thể là tác dụng không mong muốn khi sử dụng Advil. Nôn cũng là một tác dụng phụ của việc dùng quá liều thuốc Avamys.\n\nNôn cũng là triệu chứng thường gặp của u não ác tính, đặc biệt là nôn vọt không liên quan đến bữa ăn. Nôn cũng có thể xảy ra sau phẫu thuật. Bên cạnh đó, nôn cũng là một triệu chứng của bệnh viêm dạ dày ruột do virus, thường kèm theo các triệu chứng khác như tiêu chảy, đau bụng, buồn nôn, và đôi khi sốt.\n\nNôn cũng được ghi nhận là một triệu chứng của viêm phổi.&lt;SEP&gt;Nôn là một trong các triệu chứng của viêm phúc mạc.&lt;SEP&gt;Nôn là một triệu chứng phổ biến của viêm ruột do bức xạ.&lt;SEP&gt;Nôn là một triệu chứng của viêm ruột do bức xạ.&lt;SEP&gt;Nôn là một triệu chứng của bệnh viêm ruột (IBD).&lt;SEP&gt;Nôn là một trong những triệu chứng nặng của viêm tiểu phế quản.\nMontelukast: Montelukast, còn gọi là Singulair, là một loại thuốc chống viêm.\nAzibiotic: Azibiotic là một loại thuốc kháng sinh macrolid.&lt;SEP&gt;Azibiotic là thương hiệu của Azithromycin.&lt;SEP&gt;Azibiotic là một loại thuốc kháng sinh thuộc nhóm Macrolid, chứa hoạt chất chính là Azithromycin.\nZafirlukast: Zafirlukast, còn gọi là Accolate, là một loại thuốc chống viêm.\nAmlodipine: Amlodipine là một loại thuốc thuộc nhóm chặn kênh canxi, thường được sử dụng trong việc điều trị tăng huyết áp hoặc suy tim. Hoạt chất này là thành phần chính của các sản phẩm như Amlor 5 của Pfizer và Cardilopin. Amlodipine thuộc nhóm chặn kênh canxi dihydropyridine, giúp giãn mạch máu, giảm huyết áp và kiểm soát cơn đau thắt ngực. Nó cũng được sử dụng để điều trị bệnh tim mạch.\n\nTrong quá trình điều trị, Amlodipine không gây ra tương tác rõ ràng trên lâm sàng khi được sử dụng cùng với telmisartan. Tuy nhiên, cần lưu ý rằng Amlodipine có thể tương tác với Combigan. Ngoài ra, Amlodipine được đề cập như một ví dụ về thuốc chặn kênh canxi (CCBs) nên tránh sử dụng cùng với Bisoprolol.\nSốt, mệt mỏi: Sốt, mệt mỏi là các triệu chứng khác của viêm nhiễm.\nNgất: Ngất là tình trạng mất ý thức tạm thời, thường xảy ra do thiếu máu lên não. Đây là một tác dụng không mong muốn có thể gặp phải khi sử dụng một số loại thuốc như Adalat LA 20 mg, Azithromycin DHG, Beatil, Alsiful S.R, và Aceclofenac STADA. Trong đó, ngất là tác dụng phụ thường gặp khi sử dụng Azithromycin DHG và ít gặp hơn khi sử dụng Beatil. Ngất cũng có thể xuất hiện như một tác dụng phụ không mong muốn khi sử dụng Alsiful S.R, mặc dù đây là một tác dụng phụ không phổ biến.\n\nNgất cũng có thể là một triệu chứng nặng hơn sau khi đi tiêu ra máu và là triệu chứng của bệnh hẹp van động mạch chủ khi đã phát triển triệu chứng cơ năng. Ngoài ra, ngất còn là một triệu chứng nghiêm trọng có thể gặp ở những người mắc bệnh hở van tim và hội chứng WPW, xảy ra khi tim không thể cung cấp đủ máu cho não. Ngất cũng có thể là một trong các biểu hiện nặng của huyết áp không ổn định và là triệu chứng của rung nhĩ, xảy ra khi tim đập quá nhanh, dẫn đến tưới máu não không đủ.&lt;SEP&gt;Ngất là một triệu chứng có thể xảy ra khi dùng quá liều Thuốc Bifril.&lt;SEP&gt;Ngất có thể xảy ra và là một dấu hiệu cần chẩn đoán ngay.&lt;SEP&gt;Ngất là một triệu chứng cần được chẩn đoán khi sử dụng thuốc Buscopan.&lt;SEP&gt;Ngất là một tác dụng phụ có thể xảy ra khi sử dụng Captopril.&lt;SEP&gt;Ngất là tình trạng mất ý thức tạm thời.&lt;SEP&gt;Ngất là một triệu chứng có thể xảy ra trong thuyên tắc phổi.\nDịu cổ họng: Dịu cổ họng, giải độc, nhuận trường, giải khát.\nAticef: Aticef là thuốc kháng sinh thuộc nhóm cephalosporin thế hệ 1 được bào chế dưới dạng viên nang cứng. Thuốc được dùng để điều trị các bệnh nhiễm khuẩn tại đường hô hấp, tiết niệu, da và mô mềm.&lt;SEP&gt;Aticef là thuốc điều trị nhiễm khuẩn bào chế dưới dạng viên nang cứng, chứa cefadroxil monohydrat 500 mg.&lt;SEP&gt;Aticef là một loại thuốc kháng sinh thuộc nhóm Cephalosporin, thường được sử dụng để điều trị các nhiễm trùng vi khuẩn.\nMát: Mát là cảm giác dễ chịu, giảm nhiệt độ cơ thể.\nNhọt: Nhọt là tình trạng nhiễm khuẩn hoặc viêm nhiễm tại da, thường gây ra các khối sưng tấy cục bộ trên cánh tay và chân. Nó có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng kháng sinh như Aticef và các phương pháp tự nhiên như cây lưỡi bò. Ngoài ra, nhọt cũng có thể là một triệu chứng mà Màng tang có thể điều trị. Tình trạng này có thể xảy ra như một tác dụng phụ của việc tiêm vắc xin Rubella hoặc khi sử dụng thuốc moxifloxacin.&lt;SEP&gt;Nhọt là một triệu chứng bệnh lý.\nSưng, phù nề: Sưng, phù nề là triệu chứng thường gặp của trật khớp háng.\nAtenolol: Atenolol là một loại thuốc thuộc nhóm chẹn beta, thường được sử dụng trong điều trị các vấn đề về tim mạch như tăng huyết áp, đau thắt ngực, nhồi máu cơ tim cấp, loạn nhịp thất và trên thất. Nó cũng được sử dụng để điều trị hạ huyết áp và nhiễm độc giáp. Atenolol là một thuốc chẹn chọn lọc thụ thể beta1-adrenergic, có khả năng tương tác với thuốc khác như Combigan. Thuốc này giúp giảm nhịp tim và giảm nhu cầu oxy của cơ tim, từ đó hỗ trợ điều trị các tình trạng tim mạch khác nhau. Tuy nhiên, cần lưu ý rằng Atenolol có thể bài tiết vào sữa mẹ và gây ra tác dụng phụ cho trẻ sơ sinh đang bú mẹ.\nTinh dầu dừa: Tinh dầu dừa có đặc tính kháng khuẩn, kháng nấm, kháng viêm.\nCarsantin: Carsantin là một loại thuốc điều trị suy tim và có thể tương tác với một số thuốc khác.\nCorticosteroid, ACTH: Corticosteroid và ACTH có thể gây tương tác với Coaprovel.\nChìa vôi - Tua cuốn: Tua cuốn đơn, mọc đối diện với lá.\nHay ngứa - Nấm: Nấm gây ngứa.\nKhóc nhiều, dễ xúc động - Trầm cảm khi mang thai: Khóc nhiều, dễ xúc động.\nTía tô - sốt: Tía tô có tác dụng giải nhiệt, giảm sốt.\nChuối hột - Mát: Chuối hột được sử dụng để điều trị triệu chứng mát.\nLá cây - Nước: Lá cây sương sâm chứa nước.\nNấm da đầu - Tinh dầu dừa: Tinh dầu dừa có đặc tính kháng khuẩn, kháng nấm, kháng viêm.\nAzithromycin - Carbamazepin: Azithromycin không tương tác với Carbamazepin.\nCortisol - Suy yếu, phá hủy cơ bắp: Suy yếu, phá hủy cơ bắp có thể là một triệu chứng do nồng độ cortisol cao.\nErythromycin - Nôn: Erythromycin có thể gây nôn.\nCỏ mần trầu - Lorsatan (Losartan): Dịch chiết cỏ mần trầu có tác dụng hạ huyết áp tương đương với Losartan.\nAzibiotic - Azithromycin: Azibiotic là thương hiệu của Azithromycin.\nSưng, phù nề - Trật khớp háng: Sưng, phù nề là triệu chứng thường gặp của trật khớp háng.\nAmlodipine - Ngất: Amlodipine có thể gây ngất.\nLa hán quả - Nhàm trường: La hán quả được sử dụng để nhàm trường, giải khát.\nAticef - Nhọt: Aticef điều trị nhọt.\nDịu cổ họng - La hán quả: La hán quả được sử dụng để dịu cổ họng, giải độc, nhuận trường, giải khát.\nAtenolol - Ngất: Atenolol có thể gây ngất.\nSốt, mệt mỏi - Viêm sụn vành tai: Sốt, mệt mỏi là các triệu chứng khác của viêm nhiễm.\nCarsantin - Carvedilol: Carsantin chứa hoạt chất Carvedilol.\nBuồn nôn, nôn và tiêu chảy - Bệnh Addison: Buồn nôn, nôn và tiêu chảy là triệu chứng của bệnh Addison.\nCúm - Đại hồi: Đại hồi điều trị cúm.\nCoaprovel - Corticosteroid, ACTH: Corticosteroid và ACTH có thể gây tương tác với Coaprovel.\nPhyscion - rễ: Rễ cây lưỡi bò chứa Physcion.\nMô mềm - Trán vồ: Mô mềm liên quan đến các triệu chứng như trán vồ, cằm nhô, tăng khoảng cách giữa các răng.\nAzithromycin - Nôn: Azithromycin có thể gây nôn.\nHay ngứa - Ve chó: Ve chó gây ngứa.\nAzithromycin - Cimetidin: Azithromycin không bị ảnh hưởng bởi Cimetidin.\nAntacid - Azithromycin: Azithromycin có thể tương tác với Antacid.\nLoganiaceae - Mã tiền: Cây Mã tiền thuộc họ Loganiaceae.\nAzithromycin - Cyclosporin: Azithromycin có thể ảnh hưởng đến Cyclosporin.\nAzithromycin - Warfarin: Azithromycin không bị ảnh hưởng bởi Warfarin.\nAzithromycin - Theophylline: Azithromycin có thể ảnh hưởng đến Theophylline.']</t>
+          <t>['Kháng Sinh Cho Mẹ: Kháng sinh cho mẹ là thuốc được sử dụng khi mẹ đang cho con bú.\nPhụ Nữ Cho Con Bú: Phụ nữ cho con bú là giai đoạn mà phụ nữ đang nuôi con bằng sữa mẹ. Trong thời gian này, phụ nữ cần đặc biệt chú ý đến việc sử dụng các loại thuốc để đảm bảo an toàn cho cả mẹ và bé. Theo khuyến nghị y tế, phụ nữ cho con bú được khuyên sử dụng A.T Calmax và Acecyst. Tuy nhiên, họ không nên sử dụng A.t Vildagliptin vì hiện tại chưa rõ liệu thuốc này có bài tiết vào sữa mẹ hay không. Các thuốc khác như Acritel, Acnequidt bdd cq 20 ml, và Agietoxib, Agimycob không nên sử dụng vì không có dữ liệu về việc thuốc có vào sữa mẹ. Phụ nữ cho con bú cũng không nên dùng thuốc Alchysin 8400, Aleucin 500 mg, và Etoricoxib do thiếu nghiên cứu về tác động của chúng lên phụ nữ cho con bú. Thuốc Albutein chưa có nghiên cứu về việc sử dụng trên người trong giai đoạn cho con bú. Phụ nữ cho con bú cần thận trọng khi sử dụng thuốc Alpha-Chymotrypsin 4200 IU, AlphaDHG, và Altamin. Họ cũng cần tránh sử dụng Amlodipin, Atorpa-E, và Itraconazole vì những thuốc này có thể gây ra tác dụng phụ nghiêm trọng cho trẻ.\n\nNgoài ra, phụ nữ cho con bú cần cân nhắc giữa nguy cơ và lợi ích khi sử dụng acetylcystein và ranitidin. Họ cũng cần thận trọng khi sử dụng Berberin và thảo dược Bằng Lăng. Phụ nữ cho con bú không phù hợp để sử dụng Acarbose. Việc sử dụng nhiều loại thuốc khác nhau như Ambroxol Boston, Amiparen 5 Otsuka, Amoxicillin Mekophar, Ampicillin, An Thảo, Antacil, Antanazol, Argide, Arthrorein Pharmanel, Artrodar, Atorvastatin, Axit Glutamic, Azaduo, Bactamox, Bagocit, Bisoloc, Allopurinol, Bảo Thanh Hoa Linh, Bảo Thanh, Barudon, Calcigenol, Cefurobiotic, Chalme, Bromelain, Cao Sao Vàng, Ciacca, cỏ Chân vịt, cỏ mật, Cồn Boric, Cosele, Crotamiton, Decolgen Forte, Didicera, Dừa cạn, hoa đậu biếc, Hương thảo, Amoxicillin Brawn, Azicine, Cotrimoxazol, Atocib 90, Mật nhân, men vi sinh Antibio, và Nhũ hương cần được cân nhắc kỹ lưỡng giữa lợi ích và nguy cơ tiềm ẩn. Phụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi dùng bất kỳ loại thuốc nào để đảm bảo an toàn cho trẻ.\n\nPhụ nữ cho con bú cũng nên tránh sử dụng Aceclofenac, Acnotin, Albendazol, và Aluvia trong giai đoạn đang cho con bú. Họ cũng cần hết sức thận trọng khi dùng Amiodarone và Amitriptyline. Phụ nữ cho con bú cần cân nhắc giữa lợi ích điều trị cho người mẹ và nguy cơ cho trẻ. Ngoài ra, phụ nữ cho con bú là chống chỉ định khi sử dụng Antituss Plus và Hydroxyzin. Phụ nữ cho con bú cũng cần lưu ý khi sử dụng Bepanthen vì hiện chưa có dữ liệu cụ thể về ảnh hưởng của Bepanthen đến phụ nữ cho con bú. Phụ nữ cho con bú cần thận trọng khi dùng Betahistine và không được khuyến nghị sử dụng thuốc Bifril.\n\nPhụ nữ cho con bú nên thận trọng khi sử dụng Bisacodyl vì thuốc có thể đi qua sữa mẹ. Phụ nữ cho con bú cần sử dụng thuốc Bổ Huyết Ích Não một cách cẩn thận. Phụ nữ cho con bú có thể sử dụng Boganic. Phụ nữ cho con bú cần lưu ý trước khi dùng thuốc Bolutin. Vẫn chưa có nghiên cứu đặc biệt nào về việc bài tiết thuốc này qua sữa. Phụ nữ cho con bú có thể truyền thuốc Brufen qua sữa mẹ với hàm lượng thấp. Phụ nữ cho con bú nên tránh sử dụng Brufen do thuốc có thể đi qua sữa mẹ.\n\nPhụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Cafein và Candesartan. Họ cũng cần cân nhắc việc ngừng cho con bú hay ngừng thuốc Captopril. Phụ nữ cho con bú cần cân nhắc kỹ giữa lợi ích và nguy cơ khi dùng Casalmux. Họ cũng cần thận trọng khi sử dụng Cefaclor do thiếu bằng chứng đầy đủ về tác động của thuốc. Phụ nữ cho con bú cần thận trọng khi sử dụng Cefadroxil vì thuốc này có thể bài tiết trong sữa mẹ với nồng độ thấp. Họ cũng cần cân nhắc việc ngừng cho con bú nhất thời khi dùng cefalexin.\n\nPhụ nữ cho con bú cần thận trọng khi sử dụng Clonazepam. Phụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Chophytol. Phụ nữ cho con bú cần tránh dùng thuốc để đảm bảo an toàn cho trẻ nhỏ. Phụ nữ cho con bú cần tránh dùng Cimetidin để đảm bảo an toàn cho trẻ. Phụ nữ cho con bú cần thận trọng khi dùng thuốc cisaprid vì thuốc bài tiết qua sữa mẹ. Phụ nữ cho con bú cần cân nhắc giữa nguy cơ và lợi ích khi sử dụng Clotrimazole do chưa biết liệu Clotrimazole có bài tiết qua sữa mẹ hay không.\n\nPhụ nữ cho con bú không nên sử dụng Coltramyl. Đặc biệt, phụ nữ cho con bú chống chỉ định sử dụng Diane-35. Phụ nữ cho con bú là đối tượng đặc biệt cần tư vấn và đồng ý từ bác sĩ trước khi sử dụng benzalkonium chloride. Phụ nữ cho con bú cần cân nhắc kỹ lưỡng khi sử dụng tocilizumab và Actemra. Phụ nữ cho con bú không nên sử dụng thuốc Aescin. Phụ nữ cho con bú cũng không nên sử dụng Advil. Phụ nữ cho con bú không nên sử dụng moxifloxacin.\n\nPhụ nữ cho con bú là đối tượng chống chỉ định sử dụng Rosuvastatin và cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hoa cam. Phụ nữ cho con bú không khuyến khích sử dụng tinh dầu hồi. Phụ nữ cho con bú cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hương thảo. Phụ nữ cho con bú cần thận trọng khi sử dụng tinh dầu.\n\nPhụ nữ cho con bú cần tránh sử dụng tragacanth. Phụ nữ cho con bú cần thận trọng khi sử dụng Tỳ giải.\nMẹ Đang Cho Con Bú: Mẹ đang cho con bú là đối tượng cần lưu ý khi sử dụng thuốc.\nPhụ Nữ Mang Thai: Phụ nữ mang thai là giai đoạn đặc biệt trong đó phụ nữ đang怀上怀孕，并 cần phải chú ý đến việc sử dụng các loại thuốc và phương pháp điều trị để đảm bảo an toàn cho cả mẹ và thai nhi. Trong thời gian mang thai, phụ nữ nên tránh sử dụng một số loại thuốc cụ thể vì chúng có thể gây hại cho sức khỏe của mẹ và thai nhi. Các loại thuốc cần tránh bao gồm Vildagliptin (A.t Vildagliptin), Bagocit, Azaduo, Acecyst, Acetylcysteine 200mg Stada, Aclasta, Acritel, Acyclovir Stada 200 mg, Agiclovir 5% Agimexpharm, Alchysin 8400, Agimycob, Ampicillin, An Thảo, Atorvastatin, Pregabalin, Decolgen Forte, Didicera, và nhiều loại khác. Đặc biệt, phụ nữ mang thai nên tránh sử dụng Agimycob và Alchysin 8400 trong ba tháng đầu tiên vì những loại thuốc này có thể ảnh hưởng đến sự phát triển bình thường của thai nhi.\n\nNgoài ra, phụ nữ mang thai cũng cần thận trọng khi sử dụng một số loại thuốc khác như Acetylcysteine 200mg Stada, Acyclovir Stada 200 mg, Agiclovir 5% Agimexpharm, Amoxicillin Brawn, Chloramphenicol, Captopril, Cefadroxil, Cefalexin, và một số loại thảo dược như Đông trùng hạ thảo, Long diệp, Mộc hoa. Việc sử dụng những loại thuốc và thảo dược này cần được giám sát chặt chẽ bởi bác sĩ vì chưa có đủ nghiên cứu về tác động của chúng lên thai nhi.\n\nPhụ nữ mang thai còn cần lưu ý đến một số vấn đề sức khỏe khác ngoài việc sử dụng thuốc. Họ có nguy cơ cao mắc phải biến chứng từ thủy đậu, đặc biệt là trong ba tháng đầu tiên. Nếu nhiễm thủy đậu trong ba tháng đầu, phụ nữ mang thai có thể đối mặt với rủi ro sinh non, sẩy thai, hoặc thai chết lưu. Ngoài ra, họ cũng cần được kiểm tra và điều trị kịp thời nếu mắc bệnh lây truyền qua đường tình dục như lậu và giang mai để ngăn ngừa việc truyền bệnh cho thai nhi.\n\nDo sự thay đổi hormone trong cơ thể, phụ nữ mang thai dễ bị mắc các bệnh da liễu như nhiễm nấm và bệnh Listeria. Nguy cơ mắc bệnh Listeria và các bệnh liên quan khác cũng cao hơn. Họ cần tránh ăn mận da và sử dụng kháng sinh một cách thận trọng. Việc tiêu thụ quá nhiều đường đỏ và syrup ngô ngọt cũng có thể gây rủi ro. Phụ nữ mang thai cũng cần tránh sử dụng nấm Linh chi và các loại thuốc như Hoàng Liên và Chloroquine vì chúng không an toàn trong thai kỳ. Họ cũng có thể truyền virus Rubella cho thai nhi thông qua nhau.\n\nBên cạnh việc chú ý đến việc sử dụng thuốc, phụ nữ mang thai cũng cần quan tâm đến một số vấn đề sức khỏe khác như co bóp tử cung, nguy cơ mắc bệnh sốt rét tăng cao, và suy giảm chức năng tuyến yên. Trong một số trường hợp, phụ nữ mang thai có thể cần sử dụng insulin để duy trì mức đường huyết ổn định, đặc biệt là khi chế độ ăn uống không thể đạt được mục tiêu đường huyết. Họ cũng cần tránh sử dụng các loại thuốc như Giao Thái Minh, Ngũ Gia Bì, và Acid Ipratropium vì chúng không an toàn trong thai kỳ. Khi sử dụng Amitriptyline và Erythromycin, phụ nữ mang thai cần đặc biệt cẩn trọng và nên tham khảo ý kiến của bác sĩ trước khi sử dụng.\n\nCuối cùng, phụ nữ mang thai cũng cần cân nhắc kỹ trước khi sử dụng Alpha Brain, một chất bổ sung não, vì nó có thể gây ra các tác động tiềm ẩn không rõ ràng. Phụ nữ mang thai cũng cần thận trọng khi sử dụng tinh dầu oải hương, tinh dầu hồi, tinh dầu hương thảo, và tinh dầu Agarwood. Đặc biệt, phụ nữ mang thai cần tránh sử dụng tinh dầu hồi và Agarwood, và cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu oải hương và hương thảo. Phụ nữ mang thai cũng cần tránh sử dụng tragacanth.\n\nPhụ nữ mang thai là đối tượng nhạy cảm cần được bổ sung nguyên liệu tạo máu và tầm soát các bệnh lý di truyền.\nCho Con Bú: Cho con bú là giai đoạn sau sinh sản mà phụ nữ nuôi dưỡng trẻ sơ sinh bằng sữa mẹ. Đây là một thời kỳ quan trọng đòi hỏi người mẹ phải đặc biệt chú ý đến chế độ dinh dưỡng và việc sử dụng thuốc. Trong thời gian này, người mẹ cần bổ sung canxi để đáp ứng nhu cầu cao của cơ thể, được hỗ trợ bằng Calcium Corbiere Extra. Oxytocin kích thích tiết sữa, giúp duy trì nguồn sữa mẹ ổn định.\n\nCho con bú là giai đoạn chống chỉ định sử dụng nhiều loại thuốc như Acyclovir Boston 800, Adalat LA 20 mg, Alpha-Chymotrypsin 4200 IU, Alpha-Kiisin, Ameflu đa triệu chứng, Amlor 5 Pfizer, Atorhasan, Atorlog, Avarino 300 Mega, Atiso đỏ, Bibonlax, và Clopidogrel vì chúng có thể gây hại cho trẻ sơ sinh. Một số loại thuốc khác như Cefimbrano, Coldko, Coveram, và Crinone cũng được khuyến nghị tránh sử dụng hoặc cần thận trọng khi sử dụng. Các loại thuốc như amoxicillin kết hợp với acid clavulanid được cho phép sử dụng trong thời kỳ cho con bú vì chúng không gây hại cho trẻ sơ sinh. Phụ nữ cho con bú cũng cần tham khảo ý kiến của bác sĩ trước khi sử dụng Cerecaps và Children’s Tylenol để đảm bảo an toàn cho cả mẹ và bé. Ngoài ra, phụ nữ cho con bú có thể sử dụng thuốc Auclanityl nhưng cần thận trọng vì thuốc có thể truyền vào sữa mẹ. Cho con bú cũng là thời kỳ cần cân nhắc kỹ lưỡng khi sử dụng gel Contractubex và không nên dùng hoắc hương hoặc hồng bì vì những loại thuốc này có thể gây hại hoặc không được khuyến nghị trong giai đoạn này.\n\nThời kỳ cho con bú cũng cần thận trọng khi sử dụng thuốc Ameflu, Arcoxia, và Betmiga 50 mg do thiếu bằng chứng về việc etoricoxib bài tiết qua sữa ở người và khả năng thuốc có thể bài tiết vào sữa mẹ. Cho con bú cũng là giai đoạn không khuyến nghị sử dụng Khúc khắc và Aerius. Ngoài ra, phụ nữ cho con bú cần kiêng kỵ khi sử dụng Rau Càng cua và Cà độc dược vì những loại thực phẩm này có thể gây bất lợi cho sự phát triển của trẻ. Đồng thời, việc sử dụng Sa kê chưa có bằng chứng về sự an toàn. Cho con bú cũng là giai đoạn cần thận trọng khi sử dụng thuốc 3B Medi và Acid nalidixic. Phụ nữ cho con bú không nên sử dụng nhân trần trừ khi có vấn đề về gan, và cũng không nên sử dụng nhũ hương. Việc sử dụng lá Thường xuân trong giai đoạn này cần được bác sĩ tư vấn. Cuối cùng, người đang cho con bú không nên sử dụng rau mùi tây và không nên thực hiện hành động cho con bú khi sử dụng Meloxicam.\n\nBifril không được khuyến cáo sử dụng trong giai đoạn đang cho con bú. Cho con bú cũng là chống chỉ định của thuốc Bismuth. Người cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango. Phụ nữ cho con bú không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi. Đang cho con bú là yếu tố cần báo với bác sĩ khi sử dụng Carbotrim. Cho con bú là tình trạng cần thận trọng khi sử dụng Cefprozil và Ceftriaxone. Cho con bú là giai đoạn mà việc sử dụng celecoxib có thể bài tiết vào sữa mẹ và gây tác dụng xấu đối với trẻ nhỏ. Người mẹ đang cho con bú cần tránh sử dụng Ceritine. Mẹ đang cho con bú có thể bị ảnh hưởng bởi việc sử dụng Chymobest. Cho con bú là giai đoạn mà việc sử dụng Clarityne cần được đánh giá cẩn thận.\n\nCho con bú là tình trạng cần thông báo cho bác sĩ trước khi sử dụng CoAprovel. Cho con bú là chống chỉ định khi sử dụng Co aprovel. Phụ nữ cho con bú không nên sử dụng Co-Diovan. Cho con bú là giai đoạn mà phụ nữ đang nuôi dưỡng trẻ sơ sinh bằng sữa mẹ. Cho con bú là giai đoạn cần thận trọng khi sử dụng thuốc. Người đang cho con bú không nên sử dụng Coldi B. Cho con bú cũng là giai đoạn chống chỉ định sử dụng Irbesartan.&lt;SEP&gt;Người đang cho con bú cần cẩn trọng khi sử dụng tinh dầu.&lt;SEP&gt;Cho con bú là tình trạng cần thận trọng khi sử dụng tinh dầu quýt.\nPhụ Nữ Có Thai: Phụ nữ có thai là giai đoạn mà phụ nữ đang mang thai và cần đặc biệt chú ý đến việc sử dụng nhiều loại thuốc và thảo dược khác nhau để đảm bảo an toàn cho cả mẹ và thai nhi. Trong thời kỳ này, nhu cầu về vitamin C tăng cao do vitamin C có khả năng đi qua nhau thai. Việc sử dụng nhiều loại thuốc cần được thực hiện một cách thận trọng, bao gồm cả những thuốc như A.T Calmax, A.T.P, A.t Ibuprofen Syrup, Vildagliptin, Adalat LA, Acnequidt 20 ml, Alchysin 8400, Alpha-Chymotrypsin, AlphaDHG, Alsiful S.R., Altamin (do thành phần Actiso và Rau đắng đất có tác dụng tăng co bóp tử cung), Alvesin (do thiếu nghiên cứu cụ thể), Amaryl 1 mg (cần chuyển sang sử dụng Insulin), Ambroxol Boston, Amepox Soft Capsule, Amikacin Bidiphar, Amiparen 5 Otsuka, amlodipine, Amlor 5 Pfizer, và Amoxicillin (do thiếu dữ liệu về tính an toàn).\n\nPhụ nữ có thai có thể sử dụng Agimfast 60 nếu lợi ích cho mẹ vượt trội nguy cơ đối với thai nhi và Amoxicillin khi đã được bác sĩ chỉ định và đánh giá lợi ích so với nguy cơ. Đối với Alchysin 840, phụ nữ có thai được khuyến nghị không nên dùng vì thuốc có thể ảnh hưởng đến sự phát triển của thai kỳ. Đối với Alvesin, chưa có nghiên cứu cụ thể về việc sử dụng của phụ nữ có thai, và quyết định sử dụng nên dựa trên đánh giá của bác sĩ về lợi ích và nguy cơ. Đối với Amaryl 1 mg, phụ nữ có thai cần chuyển sang sử dụng Insulin.\n\nPhụ nữ có thai hoặc có kế hoạch mang thai cần thông báo với bác sĩ trước khi dùng thuốc. Đặc biệt, phụ nữ có thai cần trao đổi với bác sĩ trước khi sử dụng Amoxicillin Mekophar và Ampelop. Phụ nữ có thai cũng tuyệt đối không dùng An Cung Ngưu Hoàng Hoàn. Cần tham khảo ý kiến bác sĩ trước khi sử dụng các thuốc như An Thảo, Anapa, và Andol S Imexpharm. Phụ nữ có thai nên hỏi ý kiến thầy thuốc trước khi sử dụng Antacil. Phụ nữ có thai là đối tượng cần thận trọng khi sử dụng Antanazol, Appeton Lysine Syrup, Argide, Arthrorein Pharmanel, và Artrodar. Phụ nữ có thai không được sử dụng Asakoya Mediplantex do có thể gây ảnh hưởng nghiêm trọng đến sức khỏe của người mẹ và thai nhi. Ngoài ra, phụ nữ có thai không được sử dụng Asevictoria Mediplantex do nguy cơ tác dụng xấu lên thai nhi.\n\nPhụ nữ có thai, đặc biệt là trong 3 tháng đầu của thai kỳ, cần tránh sử dụng Bactamox, Augtipha, và Debby. Phụ nữ có thai cần thận trọng khi sử dụng Betasiphon do có thể gây tác dụng phụ tiêu chảy. Phụ nữ có thai cần cân nhắc giữa lợi ích và nguy cơ khi sử dụng Clopidogrel, Carbocistein, và Bromelain. Phụ nữ có thai cần thận trọng khi sử dụng các thảo dược như cây huyết rồng, đông trùng hạ thảo, và nấm lim xanh do có thể gây hại.\n\nPhụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược và thuốc có thể gây tác động xấu đến sức khỏe của thai nhi như: Pregabalin, Differin, Saffron, và Rau Mùi. Phụ nữ có thai cần thận trọng khi sử dụng các sản phẩm chứa glycyrrhizin, hoa đậu biếc, và các sản phẩm có chứa acetylcystein.\n\nPhụ nữ có thai cần lưu ý rằng một số thảo dược như cây đại, xạ can, và trường sinh thảo là những thảo dược cần kiêng kỵ trong thai kỳ. Phụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược như chùm ngây, cỏ sữa, và cây huyết rồng.\n\nPhụ nữ có thai cần tuân thủ hướng dẫn của bác sĩ và không nên tự ý sử dụng bất kỳ loại thuốc hay thảo dược nào mà không có sự đồng ý của bác sĩ. Phụ nữ có thai cần lưu ý khi sử dụng Sơn Nại, lá cây mâm xôi, thảo dược Bàng Lăng, tam thất nam, và Thạch lựu. Phụ nữ có thai cũng dễ mắc bệnh thiếu máu thiếu sắt.\n\nNgoài ra, phụ nữ có thai không nên sử dụng Albendazole, Amilavil, và Amiodarone do có thể gây ảnh hưởng đến sức khỏe của mẹ và thai nhi. Phụ nữ có thai cần cân nhắc khi sử dụng Arginin do thiếu nghiên cứu đầy đủ và được kiểm chứng tốt. Phụ nữ có thai không nên sử dụng Artreil do thuốc này chống chỉ định cho phụ nữ mang thai và cho con bú.\n\nPhụ nữ có thai cần thảo luận với bác sĩ về việc sử dụng thuốc Bifril. Hiện chưa có dữ liệu cụ thể về ảnh hưởng của Bepanthen đến phụ nữ có thai. Phụ nữ có thai cần thận trọng khi dùng Betahistine. Phụ nữ có thai cần thận trọng khi sử dụng Biotin. Phụ nữ mang thai không nên sử dụng Bisacodyl vì thiếu dữ liệu về sự an toàn.\n\nPhụ nữ có thai là chống chỉ định của thuốc Bismuth. Phụ nữ có thai là một trong những đối tượng không được khuyến nghị sử dụng thuốc Cebraton. Phụ nữ có thai cần thận trọng khi sử dụng Boganic.\n\nThuốc Piroxicam không được dùng trong giai đoạn thai kỳ vì có thể gây ra các vấn đề sức khỏe cho thai nhi.\n\nPhụ nữ có thai cũng cần cân nhắc việc sử dụng Bricanyl, một loại thuốc mà phụ nữ có thai có thể phải cân nhắc trong quá trình mang thai. Vẫn chưa có dữ liệu lâm sàng có giá trị về việc sử dụng thuốc này ở phụ nữ mang thai.\n\nPhụ nữ có thai không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi. Phụ nữ có thai cũng cần thận trọng khi sử dụng Brufen trong giai đoạn cuối thai kỳ.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Candesartan. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango. Phụ nữ có thai cần cân nhắc kỹ giữa lợi ích và nguy cơ khi dùng Casalmux. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Ceritine.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Chophytol. Phụ nữ có thai có thể sử dụng Claminat khi thật cần thiết.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Clonazepam. Phụ nữ mang thai có thể sử dụng Clorpheniramin trong 3 tháng cuối thai kỳ, nhưng cần thận trọng vì có thể gây ra phản ứng nghiêm trọng ở trẻ sơ sinh.\n\nPhụ nữ có thai không nên sử dụng CumarGold vì sản phẩm có thể qua nhau thai gây ảnh hưởng đến thai nhi.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Curam.\n\nPhụ nữ có thai không được sử dụng Cyclo Progynova. Cyclo Progynova là một tình trạng chống chỉ định khi sử dụng cho phụ nữ có thai.\n\nPhụ nữ có thai cần tránh sử dụng thuốc nhóm imidazol như Daktarin. Phụ nữ có thai là đối tượng đặc biệt cần tư vấn và đồng ý từ bác sĩ trước khi sử dụng benzalkonium chloride.\n\nPhụ nữ có thai là đối tượng sử dụng Actemra cần được đánh giá kỹ lưỡng.\n\nPhụ nữ có thai không thể sử dụng thuốc Aescin.\n\nPhụ nữ có thai là đối tượng chống chỉ định sử dụng Rosuvastatin.\n\nPhụ nữ có thai không nên sử dụng Coldi B.\n\nPhụ nữ có thai không được dùng Thuyền thoại.\n\nPhụ nữ có thai là đối tượng cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hoa cam và tinh dầu hoàng đàn. Phụ nữ có thai cần cẩn trọng khi sử dụng tinh dầu húng chanh. Phụ nữ có thai cần thận trọng khi sử dụng Trầm hương.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Tỳ giải.\nBệnh Nhân Cho Con Bú: Phụ nữ cho con bú cần có chỉ định cụ thể từ bác sĩ khi sử dụng Alzental Shinpoong.\nCho Con Bú - Tinh Dầu: Người đang cho con bú cần cẩn trọng khi sử dụng tinh dầu.\nPhụ Nữ Cho Con Bú - Phụ Nữ Mang Thai: Phụ nữ mang thai và cho con bú cần tránh dùng thuốc để đảm bảo an toàn cho trẻ nhỏ.\nAmoxicillin - Cho Con Bú: Thuốc amoxicillin + acid clavulanid được sử dụng trong thời kỳ cho con bú.&lt;SEP&gt;Amoxicillin + acid clavulanid có thể được dùng trong thời kỳ cho con bú nếu thuốc không gây hại cho trẻ.\nPhụ Nữ Có Thai - Phụ Nữ Đang Cho Con Bú: Phụ nữ có thai và phụ nữ đang cho con bú đều cần thông báo với bác sĩ trước khi dùng thuốc.\nAspirin - Mẹ Cho Con Bú: Mẹ cho con bú có thể sử dụng Aspirin ở liều điều trị bình thường.\nSử Dụng Thuốc - Thái: Phụ nữ có thai cần cẩn thận khi sử dụng thuốc.\nCelecoxib - Cho Con Bú: Celecoxib có thể bài tiết vào sữa mẹ và gây tác dụng xấu đối với trẻ nhỏ.\nSử Dụng Thuốc - Thai: Phụ nữ có thai cần tham khảo ý kiến bác sĩ trước khi sử dụng thuốc.\nAtorvastatin - Cho Con Bú: Atorvastatin chống chỉ định trong trường hợp phụ nữ đang cho con bú.\nPhụ Nữ Cho Con Bú - Vị Thuốc: Phụ nữ cho con bú cần cẩn trọng khi sử dụng vị thuốc.\nCho Con Bú - Clindamycin: Phụ nữ cho con bú không nên dùng Clindamycin trong thời gian điều trị.\nSữa Mẹ - Thai Nhi: Thuốc có thể được bài tiết qua sữa mẹ ảnh hưởng đến thai nhi.\nCho Con Bú - Protein: Trong cho con bú, nhu cầu protein tương đối cao.\nDược Liệu - Phụ Nữ Có Thai: Phụ nữ có thai cần cẩn trọng khi dùng dược liệu.\nKháng Sinh Cho Mẹ - Nhiễm Trùng: Kháng sinh cho mẹ được sử dụng khi mẹ đang cho con bú.\nSữa Mẹ - Thuốc: Cần chú ý những thuốc bà mẹ đang sử dụng có tiết qua sữa gây ảnh hưởng tới em bé hay không.\nClindamycin - Mẹ Cho Con Bú: Clindamycin chống chỉ định đối với mẹ cho con bú, vì hiện chưa có dữ liệu về việc thuốc có bài tiết vào sữa mẹ hay không.\nNhiễm Độc - Phụ Nữ Mang Thai: Phụ nữ mang thai có thể bị nhiễm độc.\nCho Con Bú - Isotretinoin: Isotretinoin có nguy cơ gây tác dụng phụ cho trẻ trong thời gian cho con bú.\nCho Con Bú - Sử Dụng Thuốc: Người đang cho con bú cần cẩn thận khi sử dụng thuốc.&lt;SEP&gt;Người đang cho con bú cần tham khảo ý kiến bác sĩ trước khi sử dụng thuốc.\nAmilavil - Cho Con Bú: Amilavil có thể được sử dụng khi cho con bú nhưng cần thận trọng.\nCho Con Bú - Clopidogrel: Phụ nữ đang cho con bú không nên dùng Clopidogrel.\nCho Con Bú - Hoắc Hương: Người đang cho con bú không nên dùng hoắc hương.\nCho Con Bú - Rau Mùi Tây: Người đang cho con bú không nên sử dụng rau mùi tây.\nCho Con Bú - Nhũ Hương: Phụ nữ cho con bú không nên sử dụng nhũ hương.\nCeftriaxone - Cho Con Bú: Cần thận trọng khi dùng Ceftriaxone trên đối tượng đang cho con bú.\nCho Con Bú - Nhân Trần: Phụ nữ đang cho con bú không nên dùng Nhân Trần trừ khi có vấn đề về gan.\nCefprozil - Cho Con Bú: Cefprozil qua được sữa mẹ, cần thận trọng khi dùng ở phụ nữ cho con bú.\nA.t Ibuprofen Syrup - Mẹ Cho Con Bú: A.t Ibuprofen Syrup không được sử dụng cho phụ nữ đang cho con bú.\nAerius - Cho Con Bú: Không khuyến nghị sử dụng Aerius trong giai đoạn cho con bú.\nBaby Septol - Cho Con Bú: Baby Septol chống chỉ định sử dụng trong thời gian cho con bú do trẻ sơ sinh rất nhạy cảm với tác dụng độc của thuốc.\nAmeflu DAYTIME - Cho Con Bú: Khi cho con bú, cần thận trọng khi sử dụng Ameflu DAYTIME.\nBeatil - Cho Con Bú: Người mẹ đang cho con bú cần cân nhắc giữa lợi ích và nguy cơ khi dùng Beatil.\nMẹ Cho Con Bú - Pregabalin: Không khuyến cáo sử dụng Pregabalin ở phụ nữ đang cho con bú.\nCho Con Bú - Khúc Khắc: Người đang nuôi con bằng sữa mẹ không nên sử dụng Khúc khắc.\nCarbotrim - Cho Con Bú: Đang cho con bú là yếu tố cần báo với bác sĩ khi sử dụng Carbotrim.\nAdkold – New - Mẹ Cho Con Bú: Mẹ cho con bú có thể sử dụng Adkold – New.\nAcid Nalidixic - Cho Con Bú: Thuốc Acid nalidixic có thể không an toàn khi sử dụng trên phụ nữ cho con bú.\nArcoxia - Cho Con Bú: Phụ nữ cho con bú không được sử dụng Arcoxia.&lt;SEP&gt;Arcoxia chống chỉ định cho phụ nữ cho con bú.\nCho Con Bú - Cà Độc Dược: Người cho con bú không được dùng Cà độc dược.\nCho Con Bú - Coldko: Người đang cho con bú cần tránh sử dụng Coldko.\nCho Con Bú - Co-Diovan: Phụ nữ cho con bú không nên sử dụng Co-Diovan.\nAudocals - Cho Con Bú: Audocals có thể đi qua sữa mẹ, cần cân nhắc giữa lợi ích và nguy cơ khi cho con bú.\nCho Con Bú - Coveram: Coveram chống chỉ định khi cho con bú.\nAmeflu Đa Triệu Chứng - Cho Con Bú: Thuốc Ameflu đa triệu chứng có thể đi vào sữa mẹ và có thể có tác dụng bất lợi cho trẻ sơ sinh bú mẹ.\nAmlodipine - Cho Con Bú: Amlodipine cần thận trọng khi sử dụng ở người cho con bú.\nAxit Salicylic - Cho Con Bú: Sử dụng axit salicylic cần thận trọng trong thời kỳ cho con bú.\nAtorhasan - Cho Con Bú: Atorhasan chống chỉ định trong trường hợp phụ nữ đang cho con bú.\nBriozcal - Cho Con Bú: Briozcal được chỉ định sử dụng cho phụ nữ cho con bú.\nAuclanityl - Cho Con Bú: Phụ nữ cho con bú có thể sử dụng thuốc Auclanityl.\nCho Con Bú - Irbesartan: Irbesartan chống chỉ định sử dụng trong thời kỳ cho con bú do có thể gây độc cho trẻ sơ sinh.\nAtiso Đỏ - Cho Con Bú: Phụ nữ đang cho con bú không được sử dụng Atiso đỏ vì có thể gây bất lợi cho sự phát triển của thai nhi.\nBrosafe - Cho Con Bú: Phụ nữ cho con bú không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi.&lt;SEP&gt;Brosafe được chống chỉ định trong trường hợp phụ nữ cho con bú.\nCofidec - Mẹ Cho Con Bú: Mẹ cho con bú không được sử dụng Cofidec.&lt;SEP&gt;Cofidec không được sử dụng cho mẹ cho con bú.\nAmoxycilin Vidipha - Cho Con Bú: Amoxicillin cần được cân nhắc độ an toàn khi dùng ở phụ nữ cho con bú.\nChildrens Tylenol - Cho Con Bú: Children’s Tylenol không nên dùng cho phụ nữ cho con bú.\nCalcium Corbiere Extra - Cho Con Bú: Calcium Corbiere Extra được chỉ định cho phụ nữ cho con bú.\nCho Con Bú - Rượu Ba Kích: Phụ nữ cho con bú không nên sử dụng rượu ba kích.\nCho Con Bú - Sa Kê: Người cho con bú nên tránh sử dụng Sa kê vì chưa có bằng chứng về sự an toàn.\nBismuth - Cho Con Bú: Việc sử dụng Bismuth không được khuyến nghị cho người mẹ đang cho con bú.&lt;SEP&gt;Bismuth không được dùng cho phụ nữ đang cho con bú.\nAmlor 5 Pfizer - Cho Con Bú: Amlor 5 Pfizer cần thận trọng khi sử dụng ở người cho con bú.\nCho Con Bú - Tinh Dầu Quýt: Tinh dầu quýt cần được sử dụng thận trọng đối với phụ nữ cho con bú.\nCho Con Bú - Statin: Phụ nữ cho con bú không nên sử dụng statin.\nCho Con Bú - Crinone: Không khuyến nghị sử dụng Crinone trong khi cho con bú.\nCerecaps - Cho Con Bú: Phụ nữ cho con bú cần tham khảo ý kiến của bác sĩ trước khi sử dụng Cerecaps.\nAcyclovir Stada 200 mg - Cho Con Bú: Phụ nữ cho con bú cần chú ý khi sử dụng acyclovir.\nAxit Axetic - Cho Con Bú: Việc sử dụng axit axetic khi cho con bú có thể gây ra rủi ro.\nBifril - Cho Con Bú: Bifril không được khuyến cáo sử dụng trong giai đoạn đang cho con bú.\nAcyclovir Boston 800 - Cho Con Bú: Khi dùng đường uống, thuốc được bài tiết qua sữa mẹ, cần thận trọng khi dùng Acyclovir Boston 800 ở phụ nữ cho con bú.\nAvarino 300 Mega - Cho Con Bú: Trong thời kỳ cho con bú, tuyệt đối không được sử dụng Avarino 300 Mega.\nBricanyl - Cho Con Bú: Phụ nữ cho con bú cần thảo luận với bác sĩ về việc sử dụng Bricanyl.\nCeritine - Cho Con Bú: Người mẹ đang cho con bú cần tránh sử dụng Ceritine.\nBaby Septol - Mẹ Cho Con Bú: Mẹ đang cho con bú chống chỉ định sử dụng thuốc Baby Septol trong thời gian cho con bú do trẻ sơ sinh rất nhạy cảm với tác dụng độc của thuốc.\nAlpha-Kiisin - Cho Con Bú: Alpha-Kiisin không nên sử dụng khi cho con bú.\nCho Con Bú - Rối Loạn Chức Năng Tình Dục: Cho con bú có thể dẫn đến rối loạn chức năng tình dục.\nBetmiga 50 mg - Cho Con Bú: Thuốc Betmiga 50 mg có thể bài tiết vào sữa mẹ khi cho con bú.\nCho Con Bú - Telmisartan: Bác sĩ cần chỉ định ngưng thuốc hoặc ngừng cho con bú tùy theo tình trạng hiện tại của người mẹ.\nCho Con Bú - Contractubex: Cho con bú là giai đoạn cần cân nhắc kỹ lưỡng khi sử dụng Contractubex.\nBilomag - Mẹ Cho Con Bú: Mẹ cho con bú không nên sử dụng Bilomag.\nBetaserc - Cho Con Bú: Không nên khuyến cáo dùng Betaserc trong thời kỳ cho con bú.\nCho Con Bú - CoAprovel: CoAprovel không được khuyến nghị sử dụng khi đang cho con bú.\nAlputine - Cho Con Bú: #Chưa xác định rõ ràng tính an toàn của Alputine cho phụ nữ thời kỳ cho con bú.\nAugbidil - Mẹ Cho Con Bú: Mẹ cho con bú cần cân nhắc trước khi sử dụng Augbidil.&lt;SEP&gt;Augbidil được sử dụng bình thường cho mẹ cho con bú.\nCho Con Bú - Rau Càng Cua: Phụ nữ đang cho con bú cần kiêng kỵ khi sử dụng Rau Càng cua.\nCarbomango - Cho Con Bú: Người cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango.\nCho Con Bú - Oxytocin: Oxytocin kích thích và thúc đẩy quá trình cho con bú.\nCorticosteroid - Mẹ Đang Cho Con Bú: Sử dụng corticosteroid trong thời gian cho con bú có thể ảnh hưởng đến sữa mẹ.\nCho Con Bú - Vị Thuốc: Phụ nữ cho con bú cần cẩn trọng khi sử dụng cây.\nAdrenoxyl - Cho Con Bú: Việc sử dụng thuốc Adrenoxyl trên phụ nữ đang cho con bú chưa được đánh giá hoặc thông tin.\nCho Con Bú - Chymobest: Chymobest cần được sử dụng thận trọng trên mẹ đang cho con bú.\nAugtipha - Mẹ Cho Con Bú: Mẹ đang cho con bú có thể sử dụng Augtipha nhưng cần thận trọng nếu trẻ có nguy cơ mẫn cảm với các thành phần của thuốc.\nAlvesin - Mẹ Cho Con Bú: Mẹ cho con bú không có nghiên cứu cụ thể về việc sử dụng Alvesin.&lt;SEP&gt;Mẹ cho con bú cần quyết định việc sử dụng Alvesin dựa trên đánh giá của bác sĩ về lợi ích và nguy cơ.\nAtorlog - Cho Con Bú: Phụ nữ cho con bú không nên sử dụng Atorlog.\nCho Con Bú - Clarityne: Clarityne cần được đánh giá cẩn thận khi sử dụng trong thời kỳ cho con bú.\nBibonlax - Cho Con Bú: Người đang cho con bú cần tham khảo ý kiến bác sĩ trước khi sử dụng Bibonlax.\nCefimbrano - Cho Con Bú: Phụ nữ đang cho con bú cần cẩn thận khi sử dụng Cefimbrano.\nCho Con Bú - Coldi B: Coldi B không được chỉ định cho người đang cho con bú.\nAspirin pH8 - Mẹ Cho Con Bú: Mẹ cho con bú có thể sử dụng Aspirin pH8 ở liều điều trị bình thường.\nAmpelop - Cho Con Bú: Phụ nữ cho con bú cần thảo luận với bác sĩ trước khi sử dụng Ampelop.\nCarbocistein - Mẹ Cho Con Bú: Chưa có thông tin và minh chứng về việc sử dụng Carbocistein cho mẹ cho con bú.&lt;SEP&gt;Nên tránh sử dụng Carbocistein cho mẹ cho con bú.\nAn Cung Ngưu Hoàng Hoàn - Mẹ Cho Con Bú: Mẹ cho con bú tuyệt đối không dùng An Cung Ngưu Hoàng Hoàn.\nAppeton Lysine Syrup - Mẹ Cho Con Bú: Mẹ cho con bú cần thận trọng khi sử dụng Appeton Lysine Syrup.\nAlpha-Chymotrypsin 4200 IU - Cho Con Bú: Không nên dùng thuốc Alpha-Chymotrypsin 4200 IU trong thời gian cho con bú.\nAcyclovir - Chống Chỉ Định Cho Phụ Nữ Cho Con Bú: Chống chỉ định sử dụng Acyclovir cho phụ nữ cho con bú.\nCalcium Boston - Mẹ Cho Con Bú: Calcium Boston được chỉ định sử dụng trong thời kỳ cho con bú.&lt;SEP&gt;Canxi được bài tiết qua sữa mẹ nhưng nồng độ không đủ để gây tác dụng phụ cho trẻ sơ sinh.\nCho Con Bú - Lá Thường Xuân: Người đang cho con bú nên hỏi ý kiến bác sĩ trước khi sử dụng lá Thường xuân.\nBeprosone Ointment - Mẹ Cho Con Bú: Mẹ cho con bú cần thận trọng khi sử dụng Beprosone Ointment.\nBequantene - Cho Con Bú: Bequantene cần thận trọng khi sử dụng cho phụ nữ cho con bú.\nChronol - Mẹ Cho Con Bú: Mẹ cho con bú cần cân nhắc về việc ngừng uống thuốc hoặc ngừng cho con bú khi sử dụng Chronol.\nAzithromycin DHG - Mẹ Cho Con Bú: Azithromycin DHG được chỉ định sử dụng ở mẹ cho con bú nếu không có lựa chọn thuốc khác và dưới sự giám sát của chuyên gia y tế.&lt;SEP&gt;Mẹ cho con bú có thể sử dụng Azithromycin DHG nhưng cần thận trọng.\nDexamethasone - Mẹ Đang Cho Con Bú: Sử dụng dexamethasone trong thời gian cho con bú có thể ảnh hưởng đến sữa mẹ.\nAibezym - Mẹ Cho Con Bú: Chưa ghi nhận tác dụng phụ khi mẹ cho con bú sử dụng Aibezym.\nCho Con Bú - Thuốc 3B Medi: Phụ nữ đang cho con bú cần thận trọng khi sử dụng thuốc 3B Medi.\nCombigan - Mẹ Cho Con Bú: Việc sử dụng Combigan cho phụ nữ cho con bú không được khuyến cáo.\nCho Con Bú - Hồng Bì: Người cho con bú cần thận trọng khi sử dụng Hồng bì.\nCúc Hoa Trắng - Người Đang Cho Con Bú: Người đang cho con bú cần cẩn trọng khi dùng dược liệu.\nBabi B.O.N - Mẹ Cho Con Bú: Mẹ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Babi B.O.N.\nCho Con Bú - Meloxicam: Meloxicam không nên được sử dụng trong thời kỳ cho con bú.\nAvastin - Mẹ Cho Con Bú: Mẹ cho con bú không được sử dụng Avastin trong thời gian cho con bú.\nAnapa - Mẹ Cho Con Bú: Anapa không nên sử dụng cho mẹ cho con bú.\nDentanalgi - Mẹ Cho Con Bú: Dentanalgi có thể được sử dụng cho mẹ cho con bú.\nBetmiga 50 Mg - Cho Con Bú: Betmiga 50 mg không nên sử dụng trong thời kỳ cho con bú do khả năng thuốc có thể bài tiết vào sữa mẹ.\nBecozyme - Mẹ Cho Con Bú: Becozyme không được khuyến nghị sử dụng cho mẹ cho con bú.\nBisilkon - Mẹ Cho Con Bú: Bisilkon chống chỉ định sử dụng ở mẹ cho con bú.\nCho Con Bú - Mirabegron: Mirabegron có thể bài tiết vào sữa mẹ khi cho con bú.\nAdalat LA 20 mg - Mẹ Cho Con Bú: Mẹ cho con bú cần thận trọng khi sử dụng Adalat LA 20 mg.\nCho Con Bú - Co Aprovel: Cho con bú là chống chỉ định khi sử dụng Co aprovel.\nAntacil - Mẹ Cho Con Bú: Mẹ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Antacil.\nBenate Fort Ointment - Mẹ Cho Con Bú: Mẹ cho con bú nên thận trọng khi sử dụng Benate Fort Ointment.\nCho Con Bú - Ethoxazol: Phụ nữ trong thời kỳ cho con bú không được dùng Ethoxazol.\nCarflem - Mẹ Cho Con Bú: Carflem chống chỉ định dùng cho mẹ cho con bú.\nAcnequidt 20 ml - Mẹ Cho Con Bú: Acnequidt 20 ml không được sử dụng cho mẹ cho con bú.\nCebrex - Mẹ Cho Con Bú: Mẹ cho con bú là đối tượng không nên sử dụng Cebrex do thiếu dữ liệu lâm sàng về an toàn.&lt;SEP&gt;Mẹ cho con bú không nên sử dụng Cebrex do thiếu dữ liệu lâm sàng về an toàn.\nA.t Ascorbic Syrup - Mẹ Cho Con Bú: Mẹ cho con bú có thể dùng được A.t Ascorbic Syrup theo sự chỉ định của chuyên gia y tế.\nAndol S Imexpharm - Mẹ Cho Con Bú: Không chỉ định Andol S Imexpharm cho mẹ cho con bú.\nBạch Long Thủy - Mẹ Cho Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Không có thông tin cụ thể về thuốc Biviantac trong **Context** cung cấp. Do đó, tôi không thể xác định liệu Biviantac có thể điều trị triệu chứng trướng bụng, đầy hơi hay không dựa trên dữ liệu hiện có.
-Nếu bạn có thêm thông tin về Biviantac hoặc triệu chứng bạn đang gặp phải, hãy cung cấp thêm chi tiết để tôi có thể hỗ trợ bạn tốt hơn.</t>
+          <t>Theo thông tin từ các tài liệu, Carbogast không được đề cập cụ thể. Tuy nhiên, có một số hướng dẫn chung cho việc sử dụng thuốc trong thời kỳ mang thai và cho con bú:
+1. **Phụ nữ mang thai:** Hiện tại chưa có đủ thông tin và minh chứng về việc sử dụng Carbocistein (có thể là một dạng của Carbogast) cho phụ nữ mang thai. Nên tránh dùng thuốc trong 3 tháng đầu thai kỳ. Nếu cần sử dụng, cần tham khảo ý kiến bác sĩ để được tư vấn kỹ lưỡng.
+2. **Phụ nữ cho con bú:** Thuốc Carbocistein (hay Carbogast) chưa có đầy đủ dữ liệu về việc sử dụng an toàn trên phụ nữ đang cho con bú. Do đó, cần hỏi ý kiến bác sĩ trước khi sử dụng.
+Trong mọi trường hợp, việc sử dụng Carbogast hoặc bất kỳ loại thuốc nào trong thời kỳ mang thai và cho con bú cần được cân nhắc kỹ lưỡng và chỉ sử dụng theo sự chỉ định của bác sĩ.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Có, Biviantac có thể điều trị các tình trạng như trướng bụng, đầy hơi, ợ nóng, ợ hơi hay ợ chua.</t>
+          <t>Không bắt buộc, nên dùng thuốc theo đúng chỉ định của bác sĩ.</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>["Hệ Máu: Hệ máu là hệ thống chịu ảnh hưởng từ tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg: Acepron 250 mg là thuốc được sản xuất bởi Công ty Cổ phần Dược phẩm Cửu Long, chứa paracetamol, được chỉ định để điều trị các chứng đau và sốt từ nhẹ đến vừa.&lt;SEP&gt;Acepron 250 mg là thuốc dùng để điều trị sốt và giảm các triệu chứng đau từ nhẹ tới vừa.&lt;SEP&gt;Acepron 250 mg là sản phẩm chứa acetaminophen có chống chỉ định sử dụng ở người bệnh tim, thận, phổi, gan và nhiều lần thiếu máu.&lt;SEP&gt;Acepron 250 mg là thuốc có tác dụng phụ như giảm bạch cầu, giảm toàn thể huyết cầu, giảm tiểu cầu, nôn, ban da, buồn nôn, loạn tạo máu, thiếu máu, bệnh thận và độc tính trên thận.&lt;SEP&gt;Acepron 250 mg là thuốc cần được sử dụng đúng liều lượng và thời gian theo hướng dẫn.\nThủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là triệu chứng liên quan đến việc sử dụng thuốc NSAID.&lt;SEP&gt;Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nGiảm Tiểu Cầu: Giảm Tiểu Cầu là một tình trạng y tế hiếm gặp, đặc trưng bởi sự giảm sút số lượng tiểu cầu trong máu, gây ra các vấn đề về sức khỏe liên quan đến máu. Tình trạng này thường xuất hiện như một tác dụng phụ khi sử dụng một số loại thuốc cụ thể, bao gồm Acepron 250 mg, Alzental, Alzental Shinpoong, Alzole, Alzyltex, Amikacin Bidiphar, Amoxicillin Domesco, Ampicillin, Ampicillin Brawn, Ampicillin Mekophar, Andol S, Argide, Aspirin pH8, Aspirin STELLA, Aspirin Vidipha, Aticef, Ayite, Mebendazole, Buclapoxime Tablets, acid tranexamic, Cefimbrano 100, Celecoxib, Coldacmin, trimethoprim, Diamicron, Cotrimoxazol, Chloramphenicol, Bixicam, Acid nalidixic, Isotretinoin, Albendazol, và Amitriptylin. Coldacmin được ghi nhận là có tác dụng phụ Giảm Tiểu Cầu thường gặp hơn so với Celecoxib và Diamicron, mà hai loại thuốc này được ghi nhận với tác dụng phụ Giảm Tiểu Cầu hiếm gặp. \n\nGiảm Tiểu Cầu cũng được coi là một chống chỉ định khi sử dụng một số loại thuốc như Aspirin pH8, Aspirin STELLA, và Aspirin Vidipha do khả năng gây ra tình trạng thiếu hụt số lượng tiểu cầu trong máu. Tình trạng này cũng được mô tả là một tác dụng phụ ít gặp, không phổ biến trong quá trình điều trị bằng các loại thuốc nêu trên. Ngoài ra, Giảm Tiểu Cầu còn được xem như là một rối loạn hệ máu và hệ bạch huyết, thể hiện qua các triệu chứng liên quan đến máu và bạch huyết.\n\nNgoài việc là tác dụng phụ của một số loại thuốc, Giảm Tiểu Cầu cũng có thể xảy ra do nhiễm khuẩn ít gặp. Tình trạng này được đặc trưng bởi các triệu chứng liên quan đến máu và bạch huyết, thể hiện qua sự giảm sút số lượng tiểu cầu trong máu. Một số tác dụng phụ khác của Giảm Tiểu Cầu bao gồm giảm bạch cầu, tăng bạch cầu ưu eosin, và thiếu máu tan máu, nhất là ở người thiếu hụt glucose 6 phosphat dehydrogenase. Giảm Tiểu Cầu cũng có thể là tác dụng phụ của các loại thuốc khác như Augmentin 500 mg/62,5 mg, Carbotrim, Cataflam, và Cefaclor. Tác dụng phụ này cũng được ghi nhận là hiếm gặp khi sử dụng Ceritine.&lt;SEP&gt;Giảm tiểu cầu là triệu chứng liên quan đến việc sử dụng thuốc.&lt;SEP&gt;Giảm tiểu cầu là một triệu chứng của tiền sản giật.&lt;SEP&gt;Giảm tiểu cầu là triệu chứng liên quan đến bệnh lý.\nTăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tăng urê huyết là một tác dụng phụ khi sử dụng Depakin.\nĐau Cơ: Đau Cơ là một triệu chứng đa dạng và phức tạp, có thể xuất hiện do nhiều nguyên nhân khác nhau, bao gồm cả tác dụng phụ của thuốc và các bệnh lý cụ thể. Đây là một triệu chứng phổ biến và tác dụng phụ thường gặp khi sử dụng nhiều loại thuốc khác nhau như Aclasta, Agietoxib, Agilosart, Atorhasan, Atorvastatin T.V Pharm, Audocals, Bagocit, và Desloratadine. Đặc biệt, Desloratadine trong Audocals được ghi nhận là tác dụng phụ hiếm gặp, trong khi Rosuvastatin trong Bonzacim gây đau cơ nghiêm trọng và cần được báo cáo với bác sĩ trước khi sử dụng Bonzacim. Đau Cơ cũng là một trong những triệu chứng của bệnh cúm, bệnh Lyme, và bệnh dại.\n\nĐau Cơ cũng là một rối loạn hệ cơ xương khớp và mô liên kết, đồng thời là một dấu hiệu của kiệt sức và có thể xảy ra do tăng canxi huyết. Đau Cơ là tác dụng không mong muốn của Calcium Corbiere Extra và Cilzec. Trong cuộc sống hàng ngày, Đau Cơ là triệu chứng thường gặp và có thể được giảm đau bằng cao dán Yaguchi hoặc Children's Tylenol. Các nguyên nhân khác của Đau Cơ bao gồm sự co lại liên tục của cơ, tư thế sai, sự yếu cơ, chấn thương, hoặc chiều dài chân không đều. Đau Cơ cũng là một trong các tác dụng không mong muốn sau tiêm vaccine và là triệu chứng của hội chứng sốc nhiễm độc. Ngoài ra, Đau Cơ còn có thể xuất hiện khi ngừng sử dụng Dexamethasone và Argadin.\n\nĐau Cơ cũng được biết đến là tác dụng phụ hiếm gặp khi sử dụng aciclovir, aerius, và atarax. Thuốc khác như isotretinoin và Atorvastatin cũng có thể gây ra triệu chứng này. Tại Ấn Độ, lá Rau Mương được sử dụng để điều trị triệu chứng Đau Cơ.\n\nNgoài ra, Đau Cơ còn có thể liên quan đến tình trạng thiếu hụt Biotin và là tác dụng phụ của các thuốc như Captopril, Carbimazol, Cialis, Tadalafil, Cimetidin, và Co-Diovan. Tuy nhiên, mức độ phổ biến của Đau Cơ như tác dụng phụ của Co-Diovan có thể thay đổi từ ít gặp đến thường gặp tùy thuộc vào từng trường hợp cụ thể.\n\nĐau Cơ có thể xuất hiện do nhiều nguyên nhân khác nhau, cần tới bác sĩ chuyên khoa Cơ – Xương khớp để được chẩn đoán và điều trị đúng bệnh.&lt;SEP&gt;Đau cơ là biểu hiện của quá liều mạn tính của thuốc.&lt;SEP&gt;Đau cơ là triệu chứng được tinh dầu hương thảo hỗ trợ điều trị.\nSuy Tiết Protein: Suy tiết protein là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nĐau Đầu: Đau đầu là một triệu chứng cảm giác đau tại vùng đầu, có thể xuất hiện do nhiều nguyên nhân khác nhau. Đây là triệu chứng của nhiều bệnh lý khác nhau, bao gồm bệnh Brucellosis, bệnh Lyme, rối loạn chuyển hóa, bệnh cảm cúm, bệnh COVID-19, bệnh phóng xạ cấp tính, bệnh Menière, suy thượng thận thứ phát, suy nhược thần kinh, u tuyến yên hoặc hạ đồi, tăng huyết áp ác tính, và tăng bạch cầu đơn nhân nhiễm khuẩn. Đau đầu cũng là triệu chứng tiền triệu của bệnh dại và giả u não, và có thể là tác dụng phụ của việc sử dụng quá liều nhiều loại thuốc khác nhau. Đau đầu còn là triệu chứng của nhiều bệnh lý khác, bao gồm bệnh Listeria, thể bệnh Tăng huyết áp thể Âm hư dương vượng, viêm phần phụ hoặc các bệnh lý khác liên quan đến ngứa vùng kín khi mang thai, nhiễm trùng hô hấp trên và viêm họng. Ngoài ra, đau đầu còn là triệu chứng của nhịp tim chậm và ung thư vòm mũi họng. Nó cũng là triệu chứng của hội chứng serotonin và hội chứng sốc nhiễm độc. Trong các trường hợp khác, đau đầu là triệu chứng của tăng huyết áp, tăng canxi huyết và quá liều vitamin D, bệnh Brucellosis và Lyme, rối loạn chuyển hóa, mất máu hoặc thiếu máu, hội chứng sốc nhiễm độc, và tình trạng khớp hàm thái dương (TMJ).\n\nĐau đầu cũng là triệu chứng của nhiều tình trạng khác, bao gồm hội chứng sốc nhiễm độc, tăng huyết áp, bệnh Brucellosis, Lyme, rối loạn chuyển hóa, mất máu hoặc thiếu máu, hội chứng sốc nhiễm độc, tăng canxi huyết và quá liều vitamin D, bệnh Brucellosis và Lyme, rối loạn chuyển hóa, và mức kali thấp do cường aldosterone nguyên phát. Đau đầu cũng là triệu chứng của nhiễm độc từ việc sử dụng Ô đầu hoặc Phụ tử, và nó cũng là triệu chứng của nhiễm độc từ Ô đầu và Phụ tử. Đau đầu cũng là triệu chứng của nghiến răng, đặc biệt khi ngủ. Đau đầu cũng là triệu chứng của ăng magiê và rối loạn cân bằng bicarbonate, và cũng là triệu chứng thực thể của rối loạn lo âu chia ly. Đau đầu cũng là triệu chứng của suy hô hấp do tăng nồng độ CO2 trong máu, và cũng là triệu chứng của suy thượng thận thứ phát.\n\nĐau đầu cũng là tác dụng phụ thường gặp khi sử dụng nhiều loại thuốc khác nhau, như Betahistine, Betaserc, Aspegic, Augen Extra, Biotin, Bolutin, Betex, Betmiga, Bifril, và nhiều loại thuốc khác. Đau đầu cũng là triệu chứng phổ biến của nhiều bệnh lý, bao gồm bệnh Menière, suy tuần hoàn não, hội chứng HELLP, mất nước và tiêu chảy, tiền kinh nguyệt, và nhiều bệnh lý khác. Đau đầu cũng là triệu chứng ở giai đoạn cuối của ung thư phổi, cùng với các triệu chứng khác như yếu hoặc tê cánh tay hoặc chân, chóng mặt, các vấn đề cân bằng hoặc co giật.\n\nĐau đầu cũng có thể là triệu chứng của tụt huyết áp.\nPhenylceton – niệu: Phenylceton – niệu là tình trạng cần thận trọng khi sử dụng Acepron 250 mg.\nGiảm Toàn Thể Huyết Cầu: Giảm toàn thể huyết cầu là một tác dụng phụ có thể xảy ra khi sử dụng một số loại thuốc như Acepron 250 mg, Andol S, và Coldacmin. Đây là tác dụng phụ thường gặp của Coldacmin và cũng là triệu chứng của tác dụng không mong muốn của Cloramphenicol. Ngoài ra, giảm toàn thể huyết cầu còn là tác dụng phụ hiếm gặp khi sử dụng các thuốc khác như Albendazol, Chloramphenicol, Celecoxib, và Cimetidin. Tác dụng phụ này có thể xuất hiện với tần suất khác nhau tùy thuộc vào loại thuốc được sử dụng.\nSuy Tiết Hormone: Suy tiết hormone là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nNhức Đầu: Nhức Đầu là một triệu chứng phổ biến có thể xuất hiện như tác dụng phụ của nhiều loại thuốc khác nhau và cũng là triệu chứng của nhiều tình trạng y tế khác nhau. Khi sử dụng nhiều loại thuốc, bao gồm AT Desloratadin, A.t Ibuprofen Syrup, Acecyst, N-Acetylcystein, Acehasan, Vildagliptin, Acritel, Acepron 250 mg, Acyclovir Boston 200, Acyclovir Boston 800, Agifuros, Agiosmin cq 500mg, và Alzole, nhức đầu có thể là tác dụng phụ thường gặp. Đặc biệt, nhức đầu là tác dụng phụ thường gặp khi sử dụng A.t Ibuprofen Syrup, Acetylcystein, Aerius 5 mg, và Agifuros. Nó cũng được ghi nhận là tác dụng phụ của Vildagliptin, đặc biệt khi thuốc này được sử dụng kết hợp với insulin hoặc các loại thuốc khác.\n\nNhức Đầu cũng là một triệu chứng của ngộ độc cấp tính do thuốc Agirenyl và quá liều thuốc, bao gồm cả quá liều Allopurinol 300 mg và Alputine. Nó cũng là tác dụng phụ thường gặp khi sử dụng Alsiful S.R., Alzental Shinpoong, Alzyltex, và Alzole. Nhức Đầu cũng là triệu chứng phổ biến sau khi bắt đầu điều trị bằng thuốc chặn kênh canxi. Nó cũng có thể là triệu chứng của cảm lạnh được điều trị bằng Ameflu. Nhức Đầu là tác dụng phụ hiếm gặp của Amikacin Bidiphar, mặc dù nó cũng được ghi nhận là tác dụng phụ hiếm gặp khi sử dụng Amikacin Bidiphar. Nhức Đầu cũng được điều trị bằng An Thảo Nam Dược và Andol S Imexpharm. Ngoài ra, nhức đầu còn là tác dụng phụ trên hệ thần kinh khi sử dụng Antimuc An Thiên và Antimuc. Nó cũng là biểu hiện tác dụng phụ của Aphaxan Armephaco, cả khi sử dụng đúng liều lẫn quá liều.\n\nNhức Đầu cũng là tác dụng phụ thường gặp của thuốc Argide, Aspartam, axit glutamic, clobetasol propionate, và độc tính hành biển. Nó cũng là triệu chứng của hạ đường huyết và suy nhược thần kinh. Nhức đầu cũng là tác dụng phụ khi dùng thuốc và cũng là triệu chứng của mỏi mắt, bệnh cảm cúm, và cảm lạnh. Nhức Đầu cũng là tác dụng phụ của độc tính hành biển. Nó là một trong những triệu chứng khi dùng hành biển quá liều hoặc lâu dài. Nhức Đầu cũng được đề cập trong hướng dẫn sử dụng thuốc. Nhức Đầu là triệu chứng đau đầu được điều trị bằng cải trắng.\n\nNgoài ra, Nhức Đầu cũng là triệu chứng do u chèn ép. Nó cũng là dấu hiệu do u chèn ép. Nhức Đầu là bệnh được điều trị bằng nước sắc lá cúc áo ở Malaysia. Nhức Đầu cũng là triệu chứng của cảm cúm và được điều trị bằng Decolgen Forte, Phòng phong và Xuyên khung. Nhức Đầu còn là triệu chứng của việc sử dụng quá liều phenylerine và dị dạng động tĩnh mạch.\n\nNhức Đầu cũng là một tác dụng phụ có thể xảy ra khi sử dụng Auclanityl, Diopolol, Piracetam và Diorophyl. Nhức Đầu cũng là triệu chứng được điều trị bằng đinh lăng và lá đơn buốt. Nhức Đầu cũng là triệu chứng được điều trị bằng Rễ Dứa Dại. Nhức Đầu cũng là triệu chứng thường gặp khi bị hạ huyết áp. Nhức Đầu là triệu chứng mà hổ phách có thể giúp điều trị. Nhức Đầu là triệu chứng được điều trị bằng Hoa phấn. Nhức Đầu cũng là triệu chứng được điều trị bằng Hoắc Hương.\n\nNhức Đầu cũng là một triệu chứng của tác dụng không mong muốn của Cloramphenicol. Nhức Đầu cũng là triệu chứng được chữa bằng cách sử dụng lá khế tươi. Nó cũng được điều trị bằng lá Khế tươi 20g, lá chanh tươi 10g giã nát, vắt lấy nước uống. Nhức Đầu cũng là triệu chứng được điều trị bằng Khương hoạt. Nhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng Cetirizine. Nhức Đầu cũng là tác dụng phụ thường gặp do rối loạn thần kinh khi sử dụng Atocib.\n\nNhức Đầu cũng là một triệu chứng của nhiều bệnh được điều trị bằng cây Lẻ bạn. Nhức Đầu cũng là triệu chứng của bệnh hư hỏa bốc lên cao, được điều trị bằng bài thuốc chứa Liên nhục.\n\nNhức Đầu cũng là triệu chứng được đề cập khi sử dụng methylprednisolone. Đặc biệt, nhức đầu, đặc biệt vùng thái dương sau khi thức dậy, là triệu chứng thường gặp của bệnh nghiến răng.\n\nNhức Đầu cũng là triệu chứng tổng quát của herpes sinh dục. Nhức Đầu cũng là triệu chứng thường gặp khi sử dụng Bilastine. Nhức Đầu cũng là triệu chứng được ghi nhận khi dùng quá liều Bilaxten.\n\nCuối cùng, việc sử dụng Atenolol cũng có thể gây ra tình trạng nhức đầu.\n\nNhức Đầu cũng là triệu chứng của viêm amiđan và bệnh rỗng tủy sống. Nhức Đầu cũng là triệu chứng mà Sâm đại hành có thể điều trị. Nhức Đầu cũng là triệu chứng được chữa bằng bài thuốc có Sinh khương.\n\nNhức Đầu cũng là triệu chứng thường gặp của bệnh sốt rét. Nhức Đầu cũng là triệu chứng nhẹ của bệnh sốt thung lũng.\n\nNhức Đầu cũng là một trong những triệu chứng của sốt Lassa.\n\nNhức Đầu cũng là biểu hiện của giai đoạn sốt của sốt xuất huyết.\n\nNhức Đầu cũng là triệu chứng thường gặp ở bệnh nhân suy tim trái.\n\nNhức Đầu cũng là triệu chứng thay đổi về tình trạng tâm thần do thiếu oxy động mạch.\n\nNhức Đầu cũng là triệu chứng ngộ độc thạch tín.\n\nNhức Đầu cũng là triệu chứng được điều trị bằng Thăng ma.\n\nNhức Đầu không nên xuất hiện khi sử dụng Thiên niên kiện.\n\nNhức Đầu cũng là tác dụng phụ của opioid.\n\nNhức Đầu cũng là triệu chứng khi quá liều Aceclofenac.\n\nNhức Đầu cũng là một tác dụng phụ thường gặp của Acid nalidixic. Thuốc Acid Nalidixic có thể gây ra tình trạng nhức đầu.\n\nNhức Đầu cũng là triệu chứng của Alaxan.\n\nNhức Đầu cũng là triệu chứng của tác dụng phụ khi sử dụng Albendazole.\n\nNhức Đầu cũng là triệu chứng thần kinh trung ương thường gặp khi sử dụng Albendazol.\n\nNhức Đầu cũng là tác dụng phụ của Amitriptylin.\n\nNhức Đầu cũng là tác dụng phụ của Atarax.\n\nNhức Đầu là cảm giác đau tại vùng đầu.\n\nNhức Đầu cũng có thể là một phản ứng phụ khi sử dụng Berodual. Nhức Đầu cũng là triệu chứng có thể xảy ra khi quá liều Berodual.\n\nNhức Đầu cũng là triệu chứng khi quá liều Captopril.\n\nNhức Đầu cũng là một phản ứng phụ của Carbimazol.\n\nNhức Đầu cũng là tác dụng phụ hiếm gặp khi dùng Casalmux.\n\nNhức Đầu cũng là biểu hiện đầu tiên của quá liều thuốc Carbotrim.\n\nNhức Đầu cũng là tác dụng phụ khi sử dụng Cataflam.\n\nNhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng Cataflam.\n\nNhức Đầu cũng là triệu chứng liên quan đến Cavinton.\n\nNhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng vitamin C, nhưng cũng có thể là tác dụng phụ ít gặp.\n\nNhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng Ceritine.\n\nNhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng thuốc Cialis.\n\nNhức Đầu cũng là tác dụng phụ thường gặp khi sử dụng Cidetuss.\n\nNhức Đầu cũng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\n\nNhức Đầu cũng là một trong các tác dụng phụ của Actemra.\n\nNhức Đầu cũng là triệu chứng của bệnh cảm mạo được điều trị bằng bài thuốc Sâm tô ẩm.\n\nNhức Đầu cũng là triệu chứng tiền mãn kinh.\n\nNhức Đầu cũng là một trong những triệu chứng được điều trị bằng tinh dầu húng chanh.\n\nNhức Đầu cũng là triệu chứng được điều trị bằng Tía tô.\n\nNhức Đầu được chữa bằng bài thuốc từ Tô diệp, Nhân sâm, Trần bì và các thảo dược khác.\n\nNhức Đầu cũng là triệu chứng liên quan đến cảm lạnh, sốt, và đau các khớp xương.\n\nNhức Đầu cũng là triệu chứng phổ biến của hội chứng buồng trứng đa nang.\n\nTrầu không được sử dụng để điều trị nhức đầu.\n\nNhức Đầu cũng là triệu chứng của tụt huyết áp.\n\nNhức Đầu cũng là tác dụng phụ thường gặp của Ciprofloxacin.\nSuy Khớp: Suy khớp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nĐau Nhức Do Cảm Cúm: Đau nhức do cảm cúm là một trong những chứng đau được điều trị bằng Acepron 250 mg.&lt;SEP&gt;Đau nhức do cảm cúm là triệu chứng đau từ nhẹ tới vừa, được điều trị bằng Acepron 250 mg.\nSuy Viêm: Suy viêm là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nĐau Răng: Đau răng là một triệu chứng phổ biến liên quan trực tiếp đến răng, thường được mô tả như cảm giác đau từ nhẹ đến vừa. Triệu chứng này có thể xuất hiện do nhiều nguyên nhân khác nhau, bao gồm cả đau răng khôn. Đau răng không chỉ là triệu chứng đơn thuần mà còn có thể là dấu hiệu của nhiều bệnh khác nhau, bao gồm cả cảm gió. Việc điều trị đau răng cần được tiến hành một cách triệt để để ngăn chặn các vấn đề răng miệng tiềm ẩn và tránh những hậu quả lâu dài cho sức khỏe tổng thể.\n\nCó nhiều phương pháp điều trị đau răng, bao gồm cả thuốc Tây y và phương pháp điều trị dân gian. Thuốc Tây y thường được sử dụng bao gồm Acemol 325 mg, Acepron 250 mg, Acetaminophen, A.t Ibuprofen Syrup, Aphaxan Armephaco, Ibuprofen và Aspirin pH8. Mỗi loại thuốc này đều có khả năng giúp giảm các triệu chứng đau răng, tùy thuộc vào mức độ nghiêm trọng và tình trạng cụ thể của bệnh nhân. Ngoài ra, còn có các phương pháp điều trị khác như Ngũ bội tử, Children's Tylenol, rượu chùm ruột, dung dịch ngậm, cỏ dùi trống, và Kim vàng. Tại Ấn Độ và Nepal, hoa cúc áo cũng được sử dụng để điều trị đau răng.\n\nPhương pháp điều trị dân gian cũng rất đa dạng, bao gồm việc sử dụng bạch chỉ, băng phiến, Bình Bát, cà dại hoa tím, cà dại hoa trắng, lá Bồ Đề tươi, cây chay, vỏ rễ Đại ngâm trong rượu trắng, vỏ cây Gáo, cây Giao, nhựa cây giao, và cây mè đất. Đặc biệt, rễ của cà dại hoa tím và cà dại hoa trắng sắc đặc được dùng để giảm đau răng. Địa Liên cũng được biết đến với tác dụng chữa đau răng.\n\nNgoài ra, đau răng còn được điều trị bằng lá đơn buốt, bột tiêu xát vào chân răng, Hoàng Liên Gai ngâm rượu, ké đầu ngựa, và Kim thất tai. Mỗi phương pháp này đều có thể giúp giảm triệu chứng đau răng dựa trên nguyên tắc tự nhiên và truyền thống. Bên cạnh đó, đau răng còn được điều trị bằng búp ổi non, lá trầu không, long não, Me rừng, và mộc nhĩ kết hợp với kinh giới.\n\nĐau răng cũng có thể là triệu chứng đi kèm khi nổi hạch cổ. Điều này nhấn mạnh tầm quan trọng của việc thăm khám và điều trị kịp thời để tránh những biến chứng phức tạp hơn. Ngoài ra, đau răng còn được điều trị bằng riềng, rễ cây, rễ Sương sâm, Tế tân, Hoàng Liên, và Thiên Tiên Tử.&lt;SEP&gt;Sa kê hỗ trợ điều trị đau răng.&lt;SEP&gt;Đau răng là một trong những triệu chứng mà Sa kê được sử dụng để điều trị.&lt;SEP&gt;Đau răng là một trong những triệu chứng được điều trị bằng thuốc Advil.&lt;SEP&gt;Dầu quýt được sử dụng trong giảm đau răng.\nSuy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tiêu chảy là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAcepron 250 mg - Giảm Tiểu Cầu: Giảm tiểu cầu là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Đau Cơ: Acepron 250 mg được chỉ định để điều trị đau cơ.\nAceclofenac - Táo Bón: Táo bón là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Đau Đầu: Acepron 250 mg được chỉ định để điều trị đau đầu.\nAceclofenac - Suy Thận: Không nên sử dụng Aceclofenac trên các đối tượng bị suy thận mức độ vừa đến nặng.&lt;SEP&gt;Suy thận là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Giảm Toàn Thể Huyết Cầu: Giảm toàn thể huyết cầu là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Đau Bụng: Đau bụng là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Nhức Đầu: Acepron 250 mg được dùng để điều trị nhức đầu.\nAceclofenac - Mệt Mỏi: Mệt mỏi là tác dụng phụ của Aceclofenac.\nAcepron 250 mg - Đau Nhức Do Cảm Cúm: Acepron 250 mg được chỉ định để điều trị đau nhức do cảm cúm.&lt;SEP&gt;Acepron 250 mg được dùng để điều trị đau nhức do cảm cúm.\nAceclofenac - Nôn: Nôn là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Đau Răng: Acepron 250 mg được chỉ định để điều trị đau răng.&lt;SEP&gt;Acepron 250 mg được dùng để điều trị đau răng.\nAceclofenac - Suy Tim: Suy tim là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Giảm Bạch Cầu: Giảm bạch cầu là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Ngứa: Ngứa là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Ban Da: Ban da là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Phụ Nữ Có Thai: Aceclofenac chống chỉ định trong thai kỳ trừ khi lợi ích điều trị cho mẹ vượt trội nguy cơ gây hại cho thai nhi.\nAcepron 250 mg - Paracetamol: Acepron 250 mg chứa paracetamol như hoạt chất chính.\nAceclofenac - Thiếu Máu: Thiếu máu là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Thiếu máu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Gan: Suy gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Hạ Huyết Áp: Hạ huyết áp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nhức Đầu: Nhức đầu là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Hô Hấp: Suy hô hấp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Co Giật: Co giật là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAceclofenac - Phụ Nữ Cho Con Bú: Aceclofenac không nên dùng trong giai đoạn đang cho con bú.\nAceclofenac - Đầy Hơi: Đầy hơi là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Khớp Dạng Thấp: Aceclofenac được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac - Khó Tiêu: Khó tiêu là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Buồn Ngủ: Buồn ngủ là tác dụng phụ của Aceclofenac.\nAceclofenac - Phát Ban: Phát ban là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Da: Viêm da là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Suy Thận Cấp: Suy thận cấp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Ù Tai: Ù tai là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nổi Mề Đay: Nổi mề đay là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Dạ Dày: Viêm dạ dày là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Hôn Mê: Hôn mê là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Người Cao Tuổi: Khả năng phân bố, chuyển hóa, hấp thu và thải trừ của Aceclofenac không thay đổi ở bệnh nhân cao tuổi, do đó không cần phải thay đổi liều hoặc tần suất sử dụng.\nAceclofenac - Thuốc Lợi Tiểu: Thuốc lợi tiểu có thể tương tác với Aceclofenac.\nAceclofenac - Phản Ứng Phản Vệ: Phản ứng phản vệ là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Hệ Thần Kinh: Aceclofenac gây ra các tác dụng phụ trên hệ thần kinh.\nAceclofenac - Rửa Dạ Dày: Rửa dạ dày là biện pháp dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Corticosteroids: Corticosteroids có thể tương tác với Aceclofenac.\nAceclofenac - Rối Loạn Thị Giác: Rối loạn thị giác là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Rối loạn thị giác là tác dụng phụ của Aceclofenac.\nAceclofenac - Viêm Xương Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm xương khớp.\nAceclofenac - Prostaglandin: Aceclofenac ức chế tổng hợp prostaglandin.\nAceclofenac - Loét Miệng: Loét miệng là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Chống Đông: Thuốc chống đông có thể tương tác với Aceclofenac.\nAceclofenac - Nôn Ra Máu: Nôn ra máu là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Tăng Men Gan: Tăng men gan là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Choáng Váng: Choáng váng là tác dụng phụ của Aceclofenac.\nAceclofenac - Kích Động: Kích động là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Ngất: Ngất là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Xuất Huyết Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng nghi ngờ có xuất huyết tiêu hóa.&lt;SEP&gt;Xuất huyết tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.&lt;SEP&gt;Xuất huyết tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Methotrexat: Methotrexat có thể tương tác với Aceclofenac.\nAceclofenac - Suy Giảm Chức Năng Gan: Liều dùng khởi đầu được đề nghị là 100 mg/ngày (1 viên/ngày) cho những bệnh nhân suy gan.\nAceclofenac - Tổn Thương Gan: Tổn thương gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Glycosid Tim: Glycosid tim có thể tương tác với Aceclofenac.\nAceclofenac - Tacrolimus: Tacrolimus có thể tương tác với Aceclofenac.\nAceclofenac - Than Hoạt Tính: Than hoạt tính được dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Phù Mặt: Phù mặt là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Đau Vùng Thượng Vị: Đau vùng thượng vị là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Phân Đen: Phân đen là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Ciclosporin: Ciclosporin có thể tương tác với Aceclofenac.\nAceclofenac - Zidovudin: Zidovudin có thể tương tác với Aceclofenac.\nAceclofenac - Lithi: Lithi có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Điều Trị Tăng Huyết Áp: Thuốc điều trị tăng huyết áp có thể tương tác với Aceclofenac.\nAceclofenac - Buồn Nôn, Nôn: Buồn nôn và nôn là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Aceclofenac STADA 100mg: Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg.\nAceclofenac - Cyclooxygenase: Aceclofenac ức chế cyclooxygenase.\nAceclofenac - Kích Ứng Tiêu Hóa: Kích ứng tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Loét Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng đã từng bị loét tiêu hóa tiến triển trước đó.\nAceclofenac - Tăng Creatinin Huyết: Tăng creatinin huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Đốt Sống Dính Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm đốt sống dính khớp.\nAceclofenac - Thủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Suy Thai: Suy thai là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiêu Hóa: Suy tiêu hóa là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Mifepriston: Mifepriston có thể tương tác với Aceclofenac.\nAceclofenac - Kháng Sinh Nhóm Quinolon: Kháng sinh nhóm quinolon có thể tương tác với Aceclofenac.\nAceclofenac - Suy Tiết Protein: Suy tiết protein là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone: Suy tiết hormone là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Khớp: Suy khớp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Viêm: Suy viêm là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Loxoprofen: Loxoprofen có tác dụng giảm đau và kháng viêm tương tự như Aceclofenac.\nAceclofenac - Bị Mất Phương Hướng: Bị mất phương hướng là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Não: Suy não là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Mi: Suy mi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Phổi: Suy phổi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Thần Kinh: Suy thần kinh là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Niệu: Suy tiết niệu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Dịch: Suy tiết dịch là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid: Suy tiết hormone tiroid là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B12: Suy tiết hormone tiroid B12 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B13: Suy tiết hormone tiroid B13 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B14: Suy tiết hormone tiroid B14 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B15: Suy tiết hormone tiroid B15 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B16: Suy tiết hormone tiroid B16 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B17: Suy tiết hormone tiroid B17 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B18: Suy tiết hormone tiroid B18 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B19: Suy tiết hormone tiroid B19 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B20: Suy tiết hormone tiroid B20 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Gàn: Liều dùng Aceclofenac cần được giảm cho những bệnh nhân suy gan.\nAceclofenac - Aceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac.\nAceclofenac - Tình Trạng Khó Thở: Tình trạng khó thở là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Giảm Đau Khác: Thuốc giảm đau khác bao gồm các thuốc ức chế chọn lọc cyclooxygenase-2 có thể tương tác với Aceclofenac.\nAceclofenac - Tác Nhân Kháng Tiểu Phần: Tác nhân kháng tiểu phần có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Ức Chế Chọn Lọc Thu Hồi Serotonin (SSRI): Thuốc ức chế chọn lọc thu hồi serotonin (SSRI) có thể tương tác với Aceclofenac.\nAceclofenac - Nhóm Thuốc Trị Đái Tháo Đường: Nhóm thuốc trị đái tháo đường có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Kháng Viêm Không Steroid (NSAID) Khác: Thuốc kháng viêm không steroid (NSAID) khác có thể tương tác với Aceclofenac, tạo ra nguy cơ xuất huyết tiêu hóa.\nDepakin - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ khi sử dụng Depakin.\nGiảm Tiểu Cầu - Hệ Máu: Giảm tiểu cầu là rối loạn hệ máu và hệ bạch huyết.\nAcepron 250 mg - Phenylceton – niệu: Acepron 250 mg cần thận trọng ở người bị phenylceton – niệu.\nGiảm Bạch Cầu Trung Tính - Hệ Máu: Giảm bạch cầu trung tính là rối loạn hệ máu và hệ bạch huyết.\nHệ Máu - Tăng Bạch Cầu: Tăng bạch cầu là rối loạn hệ máu và hệ bạch huyết.\nAceclofenac Stada - Thủng Loét Đường Tiêu Hóa: Aceclofenac Stada có thể gây thủng loét đường tiêu hóa.\nGiảm Bạch Cầu Đa Nhân Trung Tính - Hệ Máu: Giảm bạch cầu đa nhân trung tính là rối loạn hệ máu và hệ bạch huyết."]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ngoài khả năng giảm đau, **Acepron 250 mg** còn được chỉ định để điều trị sốt. Thuốc này có thể giúp giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật, và nhiều nguyên nhân khác.
+### Tác dụng cụ thể của Acepron 250 mg:
+- **Điều trị sốt**: Thuốc giúp làm giảm thân nhiệt ở những người bị sốt do các nguyên nhân như cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật, và các tình huống khác.
+- **Giảm các triệu chứng đau**: Acepron 250 mg có thể giúp giảm các triệu chứng đau từ nhẹ đến vừa, bao gồm đau đầu, đau răng, đau nhức do cảm cúm, đau cơ.
+### Cách dùng và liều dùng:
+- Thuốc được sử dụng bằng cách hòa tan gói thuốc vào nước để uống.
+- Liều dùng cụ thể phụ thuộc vào độ tuổi và tình trạng sức khỏe của người dùng:
+  - **Trẻ em từ 4-6 tuổi**: Uống 1 gói mỗi lần.
+  - **Trẻ em từ 7-10 tuổi**: Uống 1 gói rưỡi mỗi lần.
+  - **Trẻ em trên 11 tuổi và người lớn**: Uống 2 gói mỗi lần.
+### Lưu ý khi sử dụng:
+- Cần tuân thủ hướng dẫn về cách dùng và liều dùng để đảm bảo hiệu quả và an toàn khi sử dụng Acepron 250 mg.
+- Tránh sử dụng quá liều và nên tham khảo ý kiến bác sĩ nếu tình trạng đau hoặc sốt không thuyên giảm sau 5 ngày sử dụng.
+### Tác dụng phụ:
+- **Hệ máu**: Giảm bạch cầu, giảm toàn thể huyết cầu, giảm tiểu cầu.
+- **Khác**: Nôn, ban da, buồn nôn, loạn tạo máu, thiếu máu, bệnh thận và độc tính trên thận.
+### Tương tác thuốc:
+- Thuốc có thể tương tác với các thuốc khác như coumarin, phenothiazin, thuốc chống co giật, và isoniazid.
+### Lưu ý:
+- **Phụ nữ có thai và cho con bú**: Acepron 250 mg không nên sử dụng trong thai kỳ và giai đoạn cho con bú trừ khi lợi ích điều trị cho mẹ vượt trội nguy cơ gây hại cho thai nhi.
+### Bảo quản:
+- Bảo quản thuốc ở nơi có nhiệt độ dưới 30°C, tránh nơi ẩm thấp, để ở nơi thoáng mát.
+### Kết luận:
+Acepron 250 mg là một thuốc đa năng, không chỉ giúp giảm đau mà còn có tác dụng hạ sốt hiệu quả. Tuy nhiên, người dùng cần tuân thủ hướng dẫn sử dụng và tham khảo ý kiến bác sĩ để đảm bảo an toàn khi sử dụng.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ngoài tác dụng giảm đau, Acepron 250 mg còn có thêm tác dụng giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0.7718601703573228</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5906200567524409</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Thiếu Calci: Thiếu calci là tình trạng cần bổ sung calci trong trẻ em thời kỳ phát triển, phụ nữ có thai và cho con bú.&lt;SEP&gt;Thiếu calci là tình trạng dinh dưỡng kém được Calci D Hasan giúp cải thiện.\nCalci D Hasan: Calci D Hasan là sản phẩm thuốc của Công ty TNHH Hasan – Dermapharm với thành phần hoạt chất là calci (dạng calci carbonat) và cholecalciferol (vitamin D3).&lt;SEP&gt;Calci D Hasan là thuốc chứa muối calci qua đường uống, có thể gây kích ứng hệ tiêu hóa, táo bón và khó chịu ở dạ dày.&lt;SEP&gt;Calci D Hasan là thuốc chứa calci và vitamin D, cần được sử dụng dưới sự giám sát của bác sĩ.&lt;SEP&gt;Calci D Hasan là thuốc chứa muối calci, có thể gây tăng calci huyết nếu sử dụng quá liều.&lt;SEP&gt;Calci D Hasan là thuốc cần được bảo quản trong bao lọ kín, ở nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời, nhiệt độ dưới 25ºC và độ ẩm dưới 70ºC.\nGặm Nhấm: Gặm nhấm ăn quả Dướng khi chín.\nPhụ Nữ Có Thai: Phụ nữ có thai là giai đoạn mà phụ nữ đang mang thai và cần đặc biệt chú ý đến việc sử dụng nhiều loại thuốc và thảo dược khác nhau để đảm bảo an toàn cho cả mẹ và thai nhi. Trong thời kỳ này, nhu cầu về vitamin C tăng cao do vitamin C có khả năng đi qua nhau thai. Việc sử dụng nhiều loại thuốc cần được thực hiện một cách thận trọng, bao gồm cả những thuốc như A.T Calmax, A.T.P, A.t Ibuprofen Syrup, Vildagliptin, Adalat LA, Acnequidt 20 ml, Alchysin 8400, Alpha-Chymotrypsin, AlphaDHG, Alsiful S.R., Altamin (do thành phần Actiso và Rau đắng đất có tác dụng tăng co bóp tử cung), Alvesin (do thiếu nghiên cứu cụ thể), Amaryl 1 mg (cần chuyển sang sử dụng Insulin), Ambroxol Boston, Amepox Soft Capsule, Amikacin Bidiphar, Amiparen 5 Otsuka, amlodipine, Amlor 5 Pfizer, và Amoxicillin (do thiếu dữ liệu về tính an toàn).\n\nPhụ nữ có thai có thể sử dụng Agimfast 60 nếu lợi ích cho mẹ vượt trội nguy cơ đối với thai nhi và Amoxicillin khi đã được bác sĩ chỉ định và đánh giá lợi ích so với nguy cơ. Đối với Alchysin 840, phụ nữ có thai được khuyến nghị không nên dùng vì thuốc có thể ảnh hưởng đến sự phát triển của thai kỳ. Đối với Alvesin, chưa có nghiên cứu cụ thể về việc sử dụng của phụ nữ có thai, và quyết định sử dụng nên dựa trên đánh giá của bác sĩ về lợi ích và nguy cơ. Đối với Amaryl 1 mg, phụ nữ có thai cần chuyển sang sử dụng Insulin.\n\nPhụ nữ có thai hoặc có kế hoạch mang thai cần thông báo với bác sĩ trước khi dùng thuốc. Đặc biệt, phụ nữ có thai cần trao đổi với bác sĩ trước khi sử dụng Amoxicillin Mekophar và Ampelop. Phụ nữ có thai cũng tuyệt đối không dùng An Cung Ngưu Hoàng Hoàn. Cần tham khảo ý kiến bác sĩ trước khi sử dụng các thuốc như An Thảo, Anapa, và Andol S Imexpharm. Phụ nữ có thai nên hỏi ý kiến thầy thuốc trước khi sử dụng Antacil. Phụ nữ có thai là đối tượng cần thận trọng khi sử dụng Antanazol, Appeton Lysine Syrup, Argide, Arthrorein Pharmanel, và Artrodar. Phụ nữ có thai không được sử dụng Asakoya Mediplantex do có thể gây ảnh hưởng nghiêm trọng đến sức khỏe của người mẹ và thai nhi. Ngoài ra, phụ nữ có thai không được sử dụng Asevictoria Mediplantex do nguy cơ tác dụng xấu lên thai nhi.\n\nPhụ nữ có thai, đặc biệt là trong 3 tháng đầu của thai kỳ, cần tránh sử dụng Bactamox, Augtipha, và Debby. Phụ nữ có thai cần thận trọng khi sử dụng Betasiphon do có thể gây tác dụng phụ tiêu chảy. Phụ nữ có thai cần cân nhắc giữa lợi ích và nguy cơ khi sử dụng Clopidogrel, Carbocistein, và Bromelain. Phụ nữ có thai cần thận trọng khi sử dụng các thảo dược như cây huyết rồng, đông trùng hạ thảo, và nấm lim xanh do có thể gây hại.\n\nPhụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược và thuốc có thể gây tác động xấu đến sức khỏe của thai nhi như: Pregabalin, Differin, Saffron, và Rau Mùi. Phụ nữ có thai cần thận trọng khi sử dụng các sản phẩm chứa glycyrrhizin, hoa đậu biếc, và các sản phẩm có chứa acetylcystein.\n\nPhụ nữ có thai cần lưu ý rằng một số thảo dược như cây đại, xạ can, và trường sinh thảo là những thảo dược cần kiêng kỵ trong thai kỳ. Phụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược như chùm ngây, cỏ sữa, và cây huyết rồng.\n\nPhụ nữ có thai cần tuân thủ hướng dẫn của bác sĩ và không nên tự ý sử dụng bất kỳ loại thuốc hay thảo dược nào mà không có sự đồng ý của bác sĩ. Phụ nữ có thai cần lưu ý khi sử dụng Sơn Nại, lá cây mâm xôi, thảo dược Bàng Lăng, tam thất nam, và Thạch lựu. Phụ nữ có thai cũng dễ mắc bệnh thiếu máu thiếu sắt.\n\nNgoài ra, phụ nữ có thai không nên sử dụng Albendazole, Amilavil, và Amiodarone do có thể gây ảnh hưởng đến sức khỏe của mẹ và thai nhi. Phụ nữ có thai cần cân nhắc khi sử dụng Arginin do thiếu nghiên cứu đầy đủ và được kiểm chứng tốt. Phụ nữ có thai không nên sử dụng Artreil do thuốc này chống chỉ định cho phụ nữ mang thai và cho con bú.\n\nPhụ nữ có thai cần thảo luận với bác sĩ về việc sử dụng thuốc Bifril. Hiện chưa có dữ liệu cụ thể về ảnh hưởng của Bepanthen đến phụ nữ có thai. Phụ nữ có thai cần thận trọng khi dùng Betahistine. Phụ nữ có thai cần thận trọng khi sử dụng Biotin. Phụ nữ mang thai không nên sử dụng Bisacodyl vì thiếu dữ liệu về sự an toàn.\n\nPhụ nữ có thai là chống chỉ định của thuốc Bismuth. Phụ nữ có thai là một trong những đối tượng không được khuyến nghị sử dụng thuốc Cebraton. Phụ nữ có thai cần thận trọng khi sử dụng Boganic.\n\nThuốc Piroxicam không được dùng trong giai đoạn thai kỳ vì có thể gây ra các vấn đề sức khỏe cho thai nhi.\n\nPhụ nữ có thai cũng cần cân nhắc việc sử dụng Bricanyl, một loại thuốc mà phụ nữ có thai có thể phải cân nhắc trong quá trình mang thai. Vẫn chưa có dữ liệu lâm sàng có giá trị về việc sử dụng thuốc này ở phụ nữ mang thai.\n\nPhụ nữ có thai không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi. Phụ nữ có thai cũng cần thận trọng khi sử dụng Brufen trong giai đoạn cuối thai kỳ.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Candesartan. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango. Phụ nữ có thai cần cân nhắc kỹ giữa lợi ích và nguy cơ khi dùng Casalmux. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Ceritine.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Chophytol. Phụ nữ có thai có thể sử dụng Claminat khi thật cần thiết.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Clonazepam. Phụ nữ mang thai có thể sử dụng Clorpheniramin trong 3 tháng cuối thai kỳ, nhưng cần thận trọng vì có thể gây ra phản ứng nghiêm trọng ở trẻ sơ sinh.\n\nPhụ nữ có thai không nên sử dụng CumarGold vì sản phẩm có thể qua nhau thai gây ảnh hưởng đến thai nhi.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Curam.\n\nPhụ nữ có thai không được sử dụng Cyclo Progynova. Cyclo Progynova là một tình trạng chống chỉ định khi sử dụng cho phụ nữ có thai.\n\nPhụ nữ có thai cần tránh sử dụng thuốc nhóm imidazol như Daktarin. Phụ nữ có thai là đối tượng đặc biệt cần tư vấn và đồng ý từ bác sĩ trước khi sử dụng benzalkonium chloride.\n\nPhụ nữ có thai là đối tượng sử dụng Actemra cần được đánh giá kỹ lưỡng.\n\nPhụ nữ có thai không thể sử dụng thuốc Aescin.\n\nPhụ nữ có thai là đối tượng chống chỉ định sử dụng Rosuvastatin.\n\nPhụ nữ có thai không nên sử dụng Coldi B.\n\nPhụ nữ có thai không được dùng Thuyền thoại.\n\nPhụ nữ có thai là đối tượng cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hoa cam và tinh dầu hoàng đàn. Phụ nữ có thai cần cẩn trọng khi sử dụng tinh dầu húng chanh. Phụ nữ có thai cần thận trọng khi sử dụng Trầm hương.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Tỳ giải.\nKích Ứng Hệ Tiêu Hóa: Kích ứng hệ tiêu hóa là tác dụng phụ của Calci D Hasan.\nThuốc Điều Trị: Thuốc Điều Trị là các loại thuốc được sử dụng để điều trị nhiều bệnh lý mạn tính, bao gồm cả những bệnh như lupus, bệnh teo đa hệ thống (MSA), và chảy dịch tai. Thuốc Điều Trị có thể cần dùng trong nhiều năm đối với những người mắc bệnh lupus ít bùng phát hoặc ít triệu chứng. Chúng giúp giảm triệu chứng trong bệnh MSA và làm cho cử động mềm hơn, ngăn ngừa tình trạng căng tức thành khi bị táo bón. \n\nTác dụng phụ phổ biến của Thuốc Điều Trị bao gồm mệt mỏi, đặc biệt khi sử dụng để điều trị động kinh. Thuốc Điều Trị có thể bị ảnh hưởng bởi Bibonlax khi sử dụng đồng thời, do đó cần lưu ý khi kê đơn và sử dụng cùng với các loại thuốc khác. Đối với trẻ sinh non có ống động mạch lớn, Thuốc Điều Trị có thể là một phần quan trọng trong quá trình điều trị.\n\nThuốc Điều Trị cũng được sử dụng để điều trị nấm da đầu, bao gồm cả thuốc uống và thuốc thoa. Tuy nhiên, Thuốc Điều Trị không được sử dụng để điều trị nang nước cạnh buồng trứng. Khi sử dụng Thuốc Điều Trị, cần thông báo cho bác sĩ về tình trạng bệnh lý phụ khoa. Ngoài ra, Thuốc Điều Trị cũng được sử dụng để điều trị rối loạn nhân cách phụ thuộc, cần được kê đơn bởi bác sĩ tâm lý.\n\nĐối với hội chứng Colic, không có thuốc điều trị cụ thể.&lt;SEP&gt;Thuốc điều trị rối loạn nhận thức thần kinh chưa được cấp phép.&lt;SEP&gt;Thuốc điều trị suy giáp bẩm sinh.&lt;SEP&gt;Thuốc được sử dụng nhằm mục đích ngăn chặn sự phát triển của các mạch máu mới và làm giảm sự rò rỉ dịch bên trong mắt gây nên bệnh thoái hóa điểm vàng thể ướt.\nKhó Chịu Ở Dạ Dày: Khó chịu ở dạ dày là tác dụng phụ của Calci D Hasan.\nQuá Liều: Quá Liều là tình trạng xảy ra khi sử dụng lượng thuốc vượt quá liều lượng được chỉ định hoặc khuyến nghị, dẫn đến các triệu chứng bất thường và cần được điều trị kịp thời để tránh hậu quả nghiêm trọng. Tình trạng này có thể xảy ra với nhiều loại thuốc khác nhau, bao gồm At Domperidone, thuốc A.T.P., Vildagliptin, Acecyst, Acenocoumarol, Aclasta, acyclovir, acetaminophen, Alchysin cq cq 8400, Ambroxol Boston, Aminoplasmal 10%, Amoxicilin, Amoxicillin Flamingo, Alzental, nhôm phosphat, Ambroco, Ampicillin Brawn, thuốc An Thảo, Anaferon Materia, Asevictoria Mediplantex, Aspartam Pharmedic, Aspirin pH8, Atorhasan, Atorlog, Atorvastatin T.V Pharm, Augbactam, B - Sol, Babi B.O.N., Bisoloc, và Banitase Bảo Thanh. Việc sử dụng quá liều Vildagliptin có thể gây ra các triệu chứng như đau cơ, dị cảm, sốt, phù và tăng lipase thoáng qua. Quá liều Acecyst có thể dẫn đến các triệu chứng nghiêm trọng hơn như giảm huyết áp, suy hô hấp, tan máu, đông máu rải rác nội mạch, suy thận và sốc phản vệ. Sử dụng quá nhiều acetaminophen cũng có thể gây ra hoại tử gan. Quá liều acyclovir có thể gây ra các triệu chứng trên đường tiêu hóa và hệ thống thần kinh. Quá liều Agimfast 60 có thể gây ra các triệu chứng như buồn ngủ, chóng mặt, khô miệng. Ngoài ra, việc sử dụng quá liều Acenocoumarol 4 mg và Aclasta vượt quá liều lượng quy định cũng được ghi nhận.\n\nQuá liều cũng có thể xảy ra do người bệnh vô ý hoặc cố tình sử dụng quá liều thuốc. Trong một số trường hợp, việc sử dụng quá liều thuốc Alzental có thể dẫn đến các tác hại không mong muốn. Quá liều nhôm phosphat có thể gây ra táo bón, tắc ruột, và sỏi thận. Tình trạng quá liều Ambroco chưa được ghi nhận thông tin cụ thể, nhưng cần báo bác sĩ ngay lập tức. Quá liều Ampicillin Brawn cần ngưng dùng thuốc ngay và đến cơ sở y tế gần nhất để kiểm tra, theo dõi và xử lý kịp thời. Quá liều thuốc An Thảo cũng cần đến cơ sở y tế ngay để được theo dõi và xử lý. Quá liều thuốc Anaferon Materia cần dừng ngay và đến trung tâm y tế để xử lý kịp thời. Gel Anapa bôi tại chỗ chưa có ghi nhận cụ thể về quá liều.\n\nĐối phó với tình trạng quá liều thường yêu cầu sự can thiệp của bác sĩ để kiểm soát và điều trị triệu chứng. Trong một số trường hợp nghiêm trọng, việc điều trị có thể yêu cầu đưa bệnh nhân vào bệnh viện để điều trị hạ huyết áp và các triệu chứng khác. Quá liều có thể xảy ra nếu người dùng cố gắng uống gấp đôi liều để bù đắp cho liều đã quên. Sử dụng thuốc quá liều có thể dẫn đến những phản ứng có hại cho cơ thể. Quá liều Asevictoria Mediplantex có thể gây ra tác dụng xấu nghiêm trọng. Quá liều Aspartam Pharmedic và Aspirin pH8 cũng có thể dẫn đến cần cấp cứu. Quá liều Atorhasan, Atorlog, và Atorvastatin T.V Pharm cần được xử lý bằng cách điều trị triệu chứng và theo dõi chức năng gan và CPK huyết thanh. Quá liều Augbactam không gây tai biến nếu dung nạp tốt nhưng có thể gây tăng kali huyết.\n\nNgoài ra, quá liều Corticoid có thể gây suy thượng thận cấp. Quá liều Bluemint có thể gây ra các dấu hiệu bất thường. Quá liều Bonzacim cần được xử lý kịp thời. Quá liều Boston C 1000 cũng có thể gây ra tác dụng phụ. Quá liều Brudoxil có thể gây ra triệu chứng bất thường và cần được xử lý kịp thời.\n\nQuá liều Calci - D Mekophar cần được xử lý kịp thời. Quá liều Itraconazole chưa có nhiều dữ liệu lâm sàng về xử trí. Quá liều Carbocistein gây ra rối loạn tiêu hóa. Quá liều Carbomint cần ngừng sử dụng và theo dõi triệu chứng. Hiện tại chưa ghi nhận dữ liệu về các trường hợp quá liều của Carbomint.\n\nQuá liều Cefimbrano có thể gây ra triệu chứng co giật. Quá liều Cerecaps chưa được báo cáo nhưng cần dừng sử dụng và báo cáo cho bác sĩ. Quá liều Bromelain là tình huống chưa có báo cáo cụ thể nhưng cần xử lý kịp thời. Quá liều Chlorocina-H chưa được ghi nhận hay báo cáo. Quá liều Cholapan chưa được báo cáo cụ thể. Quá liều là tình trạng sử dụng quá nhiều thuốc Ciacca. Chưa có báo cáo về trường hợp quá liều nào xảy ra khi dùng kem acyclovir.\n\nQuá liều cũng có thể xảy ra với dung dịch nhỏ tai, mặc dù chi tiết cụ thể về tác dụng của quá liều đối với các dung dịch nhỏ tai này chưa được mô tả rõ ràng. Quá liều cũng có thể xảy ra với Cosele, cần liên hệ cơ quan y tế nếu gặp vấn đề nghiêm trọng. Quá liều Cotilam là tình huống cần liên hệ nhân viên y tế. Quá liều Crotamiton chưa được ghi nhận tác hại khi sử dụng bôi ngoài, nhưng có thể gây đau rát, kích ứng miệng, thực quản, niêm mạc dạ dày, buồn nôn, đau bụng và co giật.\n\nQuá liều Dalfusin cần được xử lý kịp thời bằng cách đưa bệnh nhân đến cơ sở y tế gần nhất. Quá liều cũng là tình trạng sử dụng quá nhiều Danospan, gây ra các triệu chứng như buồn nôn, ói mửa, tiêu chảy và kích thích.\n\nNgoài ra, còn có một tình trạng khác được gọi là "Quá Liều" liên quan đến việc sử dụng Debby vượt quá liều lượng được chỉ định. Quá liều Dentanalgi và quá liều Didicera chưa được ghi nhận phản ứng không mong muốn.\n\nQuá liều thuốc Auclanityl có thể gây ra các triệu chứng bất thường và cần được xử lý tại bệnh viện. Chưa có thông tin cụ thể về tình trạng quá liều Differin.\n\nQuá liều Diurefar có thể gây mất nước và điện giải, giảm thể tích máu dẫn đến hạ huyết áp, hạ kali huyết, nhiễm kiềm giảm clor.\n\nTình trạng quá liều Atocib cũng cần xử lý bằng các biện pháp hỗ trợ thông thường.\n\nQuá liều BoniDiabet cũng là tình trạng cần được xử lý khi dùng quá liều thuốc này.\n\nCuối cùng, quá liều cũng có thể xảy ra với Acarbose, cần tránh việc uống đồ uống hoặc thức ăn chứa nhiều carbohydrate trong 4 – 6 giờ.\n\nQuá liều Acid nalidixic cũng có thể gây ra các triệu chứng như loạn tâm thần nhiễm độc, tình trạng co giật, tăng áp lực nội sọ, và toan chuyển hóa buồn nôn, nôn.\n\nQuá liều Albendazol gây ra các triệu chứng cần được điều trị triệu chứng và các biện pháp hồi sức cấp cứu.\n\nQuá liều Betamethasone cũng là một tình trạng liên quan đến việc sử dụng quá nhiều Betamethasone.\n\nQuá liều Betex rất hiếm gặp nhưng có thể gây ra các triệu chứng như bệnh thần kinh cảm giác liên quan đến chứng mất điều hòa.\n\nQuá liều cũng có thể xảy ra khi dùng quá nhiều Bisacodyl.\n\nQuá liều Alpha Brain có thể gây ra triệu chứng bất thường cần được xử lý cấp cứu.\n\nChưa có báo cáo về trường hợp quá liều Broncho-Vaxom.\n\nQuá liều Brosafe cũng là tình trạng sử dụng thuốc Brosafe vượt quá liều lượng khuyến nghị.\n\nQuá liều là tình trạng dùng quá nhiều thuốc trong một khoảng thời gian. Dùng quá liều Carbomango cũng có thể gây hại và cần được xử lý kịp thời tại cơ sở y tế.\n\nQuá liều Cavinton có thể gây ra các triệu chứng bất thường cần được xử lý tại trạm y tế hoặc bệnh viện.\n\nQuá liều cũng là tình trạng sử dụng quá liều thuốc Ceelin hoặc vitamin C.\n\nQuá liều cũng cần xử lý các triệu chứng mà không có thuốc giải độc đặc trị.\n\nQuá liều là tình trạng cần ngừng sử dụng Chophytol và đến cơ sở y tế gần nhất để được xử lý kịp thời.\n\nQuá liều cũng có thể xảy ra khi dùng quá nhiều Chymobest.\n\nQuá liều cũng bao gồm tình trạng cần xử lý khi dùng quá nhiều thuốc Cialis.\n\nQuá liều cũng có thể gây ra chóng mặt nghiêm trọng hoặc suy nhược cơ thể khi sử dụng Co-Diovan.\n\nQuá liều cũng là tình trạng xảy ra khi dùng quá nhiều Concor®. Đặc biệt, tình trạng quá liều có thể gây tác hại khác nhau ở mỗi người, đặc biệt nhạy cảm với bệnh nhân suy tim.\n\nQuá liều Coversyl Plus có thể gây hạ huyết áp, choáng váng, nôn, chuột rút, buồn ngủ, rối loạn tâm thần.\n\nQuá liều cũng có thể xảy ra khi dùng Cyclo-Progynova.\n\nQuá liều là tình trạng dùng quá liều Irbesartan, có thể gây hạ huyết áp và nhịp tim nhanh.\n\nQuá liều Bar là tình trạng dùng quá nhiều thuốc Bar, chưa có báo cáo cụ thể về trường hợp này.\n\nQuá liều thuốc xịt mũi Aladka có thể gây ra các triệu chứng như mạch đập nhanh và không đều, tăng huyết áp, rối loạn nhận thức.\n\nDùng quá liều Coldi B có thể gây suy giảm chức năng hệ thần kinh trung ương.\nLàm Ấm Bụng: Tiêu làm ấm bụng.\nSử Dụng Thuốc: Sử dụng thuốc cần tuân thủ hướng dẫn sử dụng về liều dùng, cách dùng của nhà sản xuất hoặc theo chỉ định của bác sĩ.&lt;SEP&gt;Sử dụng thuốc, rượu hoặc đồ ăn để đối phó là một dấu hiệu hành vi của kiệt sức.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị bệnh.&lt;SEP&gt;Sử dụng thuốc có thể gây khô miệng.&lt;SEP&gt;Sử dụng thuốc có thể gây tác dụng phụ như mất thăng bằng hoặc mất vững.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị nội khoa, giúp kiểm soát triệu chứng.&lt;SEP&gt;Sử dụng thuốc Benzalkonium Chloride theo hướng dẫn cụ thể.\nThuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để phòng ngừa và điều trị loãng xương và nhuyễn xương.\nThái: Thái là dược liệu không nên dùng cùng với Bạch truật.\nBồi Bổ Sức Khỏe Cho Trẻ Nhỏ: Bồi bổ sức khỏe cho trẻ nhỏ là tác dụng của dền cơm.\nNgười Lái Xe: Người Lái Xe là người điều khiển phương tiện giao thông. Họ cần phải thận trọng khi sử dụng một số loại thuốc vì chúng có thể gây ra các tác dụng phụ ảnh hưởng đến khả năng lái xe. Cụ thể, Người Lái Xe không nên sử dụng thuốc Acecyst do có thể gây tác động lên hệ thần kinh và cũng không nên sử dụng Acnequidt 20 ml. Khi sử dụng thuốc Argide, nếu gặp tác dụng phụ liên quan đến thần kinh, Người Lái Xe nên dừng lái xe. Tương tự, nếu gặp tác dụng phụ như chóng mặt hoặc nhức đầu sau khi sử dụng Citalopram, họ cũng cần tạm dừng lái xe để đảm bảo an toàn. Tuy nhiên, chưa có ghi nhận về việc thuốc Bảo Thanh có ảnh hưởng tới khả năng lái xe của Người Lái Xe.&lt;SEP&gt;Người lái xe cần thận trọng khi sử dụng Cefurich.&lt;SEP&gt;Người lái xe cần thận trọng khi dùng Cefurobiotic.&lt;SEP&gt;Người lái xe cần thận trọng khi sử dụng Diurefar.&lt;SEP&gt;Người lái xe là đối tượng cần thận trọng khi sử dụng Clonazepam.\nCanh Móng Giò Heo Và Mướp Khía: Canh móng giò heo và mướp khía tươi là bài thuốc lợi sữa.\nCanh Cá Diếc - Nôn: Canh cá diếc nấu với quả Sấu được dùng để chữa trị nôn trong thời kỳ thai nghén.\nCalci D Hasan - Phụ Nữ Có Thai: Phụ nữ có thai cần được theo dõi chặt chẽ khi sử dụng Calci D Hasan.\nLoãng Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị loãng xương.\nCalci D Hasan - Thuốc Điều Trị: Calci D Hasan là một trong những thuốc điều trị được đề cập.\nLàm Ấm Bụng - Tiêu: Tiêu làm ấm bụng.\nCalci D Hasan - Quá Liều: Người dùng cần chú ý đến các biểu hiện lâm sàng khi sử dụng quá liều Calci D Hasan.\nBồi Bổ Sức Khỏe Cho Trẻ Nhỏ - Dền Cơm: Dền cơm có tác dụng bồi bổ sức khỏe cho trẻ nhỏ.\nSử Dụng Thuốc - Thái: Phụ nữ có thai cần cẩn thận khi sử dụng thuốc.\nAgi-Calci - Thiếu Calci: Agi-Calci được chỉ định dùng trong trường hợp thiếu calci.\nCalci D Hasan - Người Lái Xe: Người lái xe cần tuân thủ liều lượng khuyến cáo khi sử dụng Calci D Hasan.\nCalci D Hasan - Thiếu Calci: Calci D Hasan giúp cải thiện tình trạng thiếu calci.\nSử Dụng Thuốc - Thai: Phụ nữ có thai cần tham khảo ý kiến bác sĩ trước khi sử dụng thuốc.\nCalci D Hasan - Kích Ứng Hệ Tiêu Hóa: Calci D Hasan có thể gây kích ứng hệ tiêu hóa.\nCalci D Hasan - Cho Con Buu: Người cho con bú cần được theo dõi chặt chẽ khi sử dụng Calci D Hasan.\nCalci D Hasan - Khó Chịu Ở Dạ Dày: Calci D Hasan có thể gây khó chịu ở dạ dày.\nPhụ Nữ Có Thai - Quế Chi: Thận trọng khi dùng Quế chi cho phụ nữ có thai.\nCây Dướng - Gặm Nhấm: Gặm nhấm ăn quả Dướng khi chín.\nCalcigenol - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng khi dùng Calcigenol.\nCanh Móng Giò Heo Và Mướp Khía - Lợi Sữa: Canh móng giò heo và mướp khía được sử dụng để điều trị lợi sữa.\nThuốc Nam - Thủ Thuật Y Khoa: Thuốc Nam cần tránh tự ý sử dụng trong thai kỳ.\nCháo Cá Mè Và Mướp Khía - Lợi Sữa: Cháo cá mè và mướp khía được sử dụng để điều trị lợi sữa.\nCanh Cá Diếc - Quả Sấu: Quả Sấu là thành phần chính trong canh cá diếc.\nNhuyễn Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị nhuyễn xương.']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Không nên tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú. Thuốc này cần được sử dụng dưới sự giám sát của bác sĩ để đảm bảo an toàn cho cả mẹ và thai nhi. Việc sử dụng Calci D Hasan trong thời kỳ mang thai và cho con bú cần được theo dõi chặt chẽ do có thể gây tác dụng phụ như kích ứng hệ tiêu hóa và khó chịu ở dạ dày.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Không, không nên tự ý sử dụng thuốc.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8605332047128975</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9651333011532244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Commelinaceae: Commelinaceae là họ thực vật của Thài lài trắng.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nNgứa, Nổi Ban Đỏ: Ngứa, nổi ban đỏ là tác dụng phụ của thuốc Comiaryl.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nDaoryl: Thuốc Daoryl là thuốc chứa thành phần tương tự với Comiaryl.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nCombretol: Combretol là flavonoid được phân lập từ hạt của cây Trâm bầu.\nCo-Diovan: Co-Diovan là thuốc gồm hai hoạt chất là valsartan và hydrochlorothiazide, được sử dụng trong điều trị tăng huyết áp.&lt;SEP&gt;Co-Diovan là thuốc chứa valsartan và hydrochlorothiazide.&lt;SEP&gt;Co-Diovan là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Thuốc Co-Diovan chứa valsartan và hydrochlorothiazide.\nTrường Hợp Quá Liều: Trường hợp quá liều là tình trạng dùng quá liều thuốc Comiaryl, cần gọi ngay cho trung tâm cấp cứu.\nLiều Thuốc: Liều thuốc là lượng thuốc cần thiết và được sử dụng trong mỗi lần uống hoặc tiêm, cũng như trong một khoảng thời gian cụ thể. Không chỉ đơn thuần là lượng thuốc cần dùng trong mỗi lần uống, liều thuốc còn là lượng thuốc cần thiết để đạt hiệu quả điều trị. Nó có thể được sử dụng để điều trị bằng cách áp dụng phương pháp điều trị với các loại thuốc khác nhau, ví dụ như Aibezym, theo đúng liều lượng. Liều thuốc cũng đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, như tăng canxi huyết, đòi hỏi việc xác định đúng liều lượng cho từng trường hợp cụ thể để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn.\n\nĐể đạt hiệu quả tốt nhất, liều thuốc cần được tuân thủ theo đúng hướng dẫn sử dụng hoặc chỉ định của bác sĩ và khuyến nghị của nhà sản xuất. Điều này bao gồm việc sử dụng đúng liều lượng cho từng loại thuốc cụ thể, ví dụ như Betadine Throat Spray. Việc quên liều hoặc cố gắng bù đắp bằng cách dùng gấp đôi liều đều không được khuyến khích. Thay vào đó, nếu bạn quên một liều thuốc, bạn nên tiếp tục lịch trình sử dụng thuốc của mình và không nên dùng gấp đôi liều để bù vào liều đã quên.\n\nLiều thuốc Diorophyl cần được tuân thủ theo chỉ định của bác sĩ, không nên sử dụng quá liều khuyến cáo. Liều thuốc cũng là cách sử dụng thuốc theo lịch trình đã xác định, như khi sử dụng Atocib hoặc Ceritine. Liều thuốc đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, đòi hỏi sự chính xác và tuân thủ chặt chẽ về liều lượng.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc Co-Diovan, bao gồm hướng dẫn về việc quên thuốc và sử dụng liều kế tiếp.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc theo đúng hướng dẫn của bác sĩ để đảm bảo an toàn.\nCommelina Communis L: Commelina communis L là tên khoa học của Thài lài trắng.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nKhí Dung: Khí dung là cách dùng của Combivent®.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nAmaryl M: Thuốc Amaryl M là thuốc chứa thành phần tương tự với Comiaryl.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nHạ Đường Huyết Quá Mức: Hạ đường huyết quá mức là tác dụng phụ có thể xảy ra khi điều trị bằng thuốc Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức là một tác dụng phụ có thể xảy ra khi sử dụng Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức là tác dụng phụ của thuốc Comiaryl.\nCách Dùng Và Liều Dùng: Cách dùng và liều dùng của mướp tây bao gồm việc sử dụng trong chế biến thức ăn như luộc, xào, nấu canh, nấu nước uống hoặc dùng ngoài.&lt;SEP&gt;Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nTrẻ Em Và Thiếu Niên: Trẻ em và thiếu niên không khuyến cáo dùng Combigan.\nPhụ TỬ: Phụ tử là một vị thuốc được sử dụng kết hợp với Khoai nưa trong hỗ trợ điều trị liệt nửa người.\nAleucin: Aleucin là thuốc có chứa thành phần hoạt chất tương tự như Leucin, dùng điều trị chóng mặt.\nCách Dùng: Cách Dùng là hướng dẫn chi tiết về cách thức sử dụng các loại thuốc khác nhau, bao gồm Aleucin, Berberin, Bofit F, cây Thuốc Mọi, Brosafe, Chophytol, và Combivent®. Hướng dẫn này cung cấp thông tin về cách sử dụng mỗi loại thuốc một cách chính xác để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn.\n\nĐối với Aleucin và Berberin, Cách Dùng hướng dẫn người dùng về cách sử dụng thuốc đúng cách. Đối với Bofit F, Cách Dùng mô tả cách thức sử dụng sản phẩm này. Đối với cây Thuốc Mọi, Cách Dùng và Liều Dùng đều tùy thuộc vào mục đích sử dụng cụ thể và từng bài thuốc cụ thể.\n\nTrong trường hợp Brosafe, thuốc được sử dụng qua đường uống và nên được uống sau bữa ăn để đạt hiệu quả điều trị cao nhất. Đối với Chophytol, thuốc cũng được sử dụng qua đường uống nhưng cần uống trước bữa ăn để đạt hiệu quả điều trị tốt nhất. \n\nCuối cùng, Cách Dùng của Combivent® bao gồm việc lắp ống thuốc vào dụng cụ khí dung và kích hoạt chuẩn bị cho lần sử dụng đầu tiên. Cách này giúp đảm bảo rằng người dùng có thể sử dụng Combivent® một cách chính xác và hiệu quả.\n\nNgười dùng được khuyến nghị uống nguyên viên với nước, uống thuốc sau ăn để tránh các tác dụng không mong muốn. Điều này giúp đảm bảo rằng người dùng có thể tận dụng tối đa hiệu quả của thuốc mà vẫn duy trì sự an toàn.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nCeritine: Ceritine là thuốc được chỉ định theo đơn của bác sĩ, dùng đường uống.&lt;SEP&gt;Ceritine là thuốc được sử dụng để điều trị dị ứng, có thể gây ngủ gà ở một số người.&lt;SEP&gt;Ceritine được dùng đường uống và có thể gây nhiều tác dụng phụ như ngủ gà, mệt mỏi, khô miệng, viêm họng, chóng mặt, nhức đầu, buồn nôn, chán ăn hoặc tăng thèm ăn, bí tiểu, đỏ bừng, tăng tiết nước bọt, thiếu máu tan máu, giảm tiểu cầu, hạ huyết áp nặng, choáng phản vệ, viêm gan, ứ mật, viêm cầu thận.\nComiaryl - Hạ Đường Huyết Quá Mức: Hạ đường huyết quá mức là tác dụng phụ có thể xảy ra khi điều trị bằng thuốc Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức có thể xảy ra khi sử dụng Comiaryl.&lt;SEP&gt;Thuốc Comiaryl có thể gây hạ đường huyết quá mức.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nComiaryl - Ngứa, Nổi Ban Đỏ: Thuốc Comiaryl có thể gây ngứa, nổi ban đỏ.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nComiaryl - Daoryl: Thuốc Comiaryl có thành phần tương tự với thuốc Daoryl.\nCo-Diovan - Liều Thuốc: Hướng dẫn về cách sử dụng liều thuốc Co-Diovan.\nComiaryl - Trường Hợp Quá Liều: Trong trường hợp quá liều, cần gọi ngay cho trung tâm cấp cứu.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nAmaryl M - Comiaryl: Thuốc Comiaryl có thành phần tương tự với thuốc Amaryl M.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nCombigan - Trẻ Em Và Thiếu Niên: Combigan không được khuyến cáo dùng cho trẻ em và thiếu niên.\nCách Dùng Và Liều Dùng - Phụ TỬ: Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nCombretol - Trâm Bầu: Combretol là flavonoid được phân lập từ hạt của cây Trâm bầu.\nAleucin - Cách Dùng: Thuốc Aleucin có hướng dẫn cụ thể về cách sử dụng.\nCombretol - Cây Trâm Bầu: Combretol là flavonoid được phân lập từ hạt của cây Trâm bầu.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nCommelina Communis L - Thài Lài Trắng: Commelina communis L là tên khoa học của Thài lài trắng.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nCombretol - Hạt Trâm Bầu: Combretol là flavonoid được phân lập từ hạt Trâm bầu.\nCeritine - Liều Thuốc: Liều thuốc là cách sử dụng Ceritine đúng cách.\nCombivent® Respimat® - Khí Dung: Combivent® Respimat® được dùng qua khí dung.']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thuốc Comiaryl cần được sử dụng đúng cách để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn. Dưới đây là hướng dẫn chi tiết về cách sử dụng thuốc Comiaryl:
+### 1. Thời Điểm Sử Dụng
+Thuốc Comiaryl nên được uống ngay trước hoặc trong bữa ăn. Nên uống nguyên viên với một cốc nước đầy.
+### 2. Liều Dùng
+- **Bắt đầu:** Nên bắt đầu với liều thấp nhất có tác dụng trị liệu.
+- **Hiệu chỉnh liều:** Hiệu chỉnh liều theo từng trường hợp cụ thể của mỗi bệnh nhân. Phải thường xuyên theo dõi nồng độ glucose huyết của bệnh nhân trong suốt quá trình sử dụng thuốc để hiệu chỉnh liều dùng cho phù hợp.
+- **Liều tối đa:** Liều tối đa hàng ngày của thuốc Comiaryl không nên vượt quá 2 viên (bệnh nhân chỉ được uống tối đa một ngày 2 lần, mỗi lần uống 1 viên).
+### 3. Lưu Ý Khi Sử Dụng
+- **Chế độ ăn kiêng:** Cần tuân thủ chế độ ăn kiêng và luyện tập thể dục.
+- **Theo dõi:** Thường xuyên theo dõi glucose huyết và đường niệu.
+### 4. Xử Lý Khi Quên Liều
+Nếu quên một liều thuốc, hãy dùng lại liều đã quên càng sớm càng tốt. Tuy nhiên, nếu liều đã quên gần với liều dùng kế tiếp, hãy bỏ qua liều đã quên và sử dụng tiếp liều kế theo lịch trình. Không nên bôi gấp đôi liều để bù lại liều đã quên.
+### 5. Bảo Quản
+- **Địa điểm:** Cần bảo quản thuốc Comiaryl ở nơi khô thoáng, nhiệt độ dưới 30°C.
+- **Tránh:** Tránh ánh sáng.
+### 6. Tác Dụng Phụ
+Khi sử dụng thuốc Comiaryl, bệnh nhân có thể gặp tình trạng rối loạn tiêu hóa như buồn nôn, nôn, đau bụng, tiêu chảy. Bệnh nhân cũng có thể gặp tình trạng hạ đường huyết quá mức và nhìn mờ thoáng qua.
+### 7. Xử Lý Khi Quá Liều
+Trong trường hợp bị quá liều khi sử dụng thuốc Comiaryl, hãy gọi ngay cho trung tâm cấp cứu hoặc đến cơ sở y tế địa phương gần nhất.
+### 8. Đối Tượng Cần Thận Trọng
+Do nguy cơ hạ đường huyết và rối loạn thị giác thoáng qua khi sử dụng Comiaryl, cần thận trọng khi dùng thuốc trong khi lái xe hoặc vận hành máy móc.
+### 9. Chống Chỉ Định
+Chống chỉ định dùng Comiaryl cho bệnh nhân suy thận, người bệnh lý cấp tính có nguy cơ gây suy thận, người mắc các bệnh lý nặng khác như suy gan, suy tim, người nghiện rượu, người mắc bệnh hô hấp nặng.
+### 10. Lưu Ý Khi Sử Dụng
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 11. Lưu Ý Khác
+Trước khi chụp X-quang có tiêm chất cản quang chứa iodi, cần tạm thời ngừng sử dụng Comiaryl 2 mg/500 mg (48 giờ trước và sau khi chụp X-quang).
+### 12. Đối Tượng Không Nên Sử Dụng
+Không nên sử dụng cho phụ nữ có thai và cho con bú.
+### 13. Lưu Ý Khi Sử Dụng Thuốc
+- **Tuân thủ:** Tuân thủ chặt chẽ chỉ định của bác sĩ.
+- **Bảo quản:** Bảo quản thuốc đúng cách và không vượt quá hạn sử dụng.
+### 14. Tương Tác Thuốc
+Thuốc có thể làm tăng tác dụng hạ đường huyết của glimepirid. Cần chú ý khi sử dụng cùng các thuốc khác có thể tương tác với Comiaryl.
+### 15. Tương Tác Với Thực Phẩm
+Bữa ăn không ảnh hưởng đến sinh khả dụng của thuốc. Bạn cũng có thể uống thuốc cùng với thức ăn để giảm bớt tác dụng phụ trên đường tiêu hóa.
+### 16. Lưu Ý Về An Toàn
+Tránh sử dụng thuốc Comiaryl cho phụ nữ có thai và cho con bú.
+### 17. Kiểm Soát Tác Dụng Phụ
+Nếu gặp phải tác dụng phụ không mong muốn, hãy ngừng sử dụng thuốc và báo ngay cho bác sĩ.
+### 18. Kiểm Soát Tác Dụng Phụ Hiếm Gặp
+Tác dụng phụ hiếm gặp khi sử dụng thuốc Comiaryl bao gồm chuyển hóa: nhiễm toan lactic do tích lũy metformin ở người suy thận, suy gan, nghiện rượu và giảm oxy huyết (tỉ lệ tử vong cao).
+### 19. Kiểm Soát Tác Dụng Phụ Rất Hiếm Gặp
+Tác dụng phụ rất hiếm gặp khi sử dụng thuốc Comiaryl bao gồm các vấn đề về chuyển hóa.
+### 20. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 21. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 22. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 23. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 24. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 25. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 26. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 27. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 28. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 29. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 30. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 31. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 32. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 33. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 34. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 35. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 36. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 37. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 38. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 39. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 40. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 41. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 42. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 43. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 44. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 45. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 46. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 47. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 48. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 49. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.
+### 50. Lưu Ý Khi Sử Dụng Thuốc
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nên uống nguyên viên thuốc Comiaryl với một cốc nước đầy.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0.7955462618192922</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5985154205730975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Bệnh Lý Nền: Người mắc bệnh lý nền cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng khi sử dụng Calci D Hasan.&lt;SEP&gt;Bệnh lý nền là các tình trạng bệnh lý sẵn có làm tăng khả năng gặp tác dụng phụ khi dùng thuốc.\nThiểu Năng Cận Giáp: Thiểu năng cận giáp là tình trạng bệnh có thể tương tác với Calci D Hasan.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nKhó Chịu Ở Dạ Dày: Khó chịu ở dạ dày là tác dụng phụ của Calci D Hasan.\nTác Dụng Không Mơ Nguyện: Tác dụng không mong muốn có thể xảy ra khi sử dụng vị thuốc.\nKích Ứng Hệ Tiêu Hóa: Kích ứng hệ tiêu hóa là tác dụng phụ của Calci D Hasan.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nNgộ Độc Digitalis: Ngộ độc digitalis là tác dụng phụ có thể xảy ra khi dùng Calci D Hasan.&lt;SEP&gt;Ngộ độc digitalis là tình trạng ngộ độc do sử dụng quá liều thuốc digitalis.\nKháng Sinh Phổ Rộng: Kháng sinh phổ rộng là phương pháp điều trị nhiễm trùng huyết do thắt dây chun.&lt;SEP&gt;Kháng sinh phổ rộng được sử dụng để điều trị viêm nhiễm đường tiêu hóa.&lt;SEP&gt;Kháng sinh phổ rộng đôi khi được sử dụng để điều trị nhiễm trùng đường hô hấp trên do vi khuẩn.&lt;SEP&gt;Kháng sinh phổ rộng là loại thuốc được sử dụng để điều trị nhiễm trùng do nhiều loại vi khuẩn khác nhau.\nThuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để phòng ngừa và điều trị loãng xương và nhuyễn xương.\nBạch Cầu Cấp: Bạch cầu cấp là thể bệnh ác tính ở trẻ em, chiếm khoảng 30% trong số các bệnh ung thư ở trẻ em. Nó bao gồm bạch cầu cấp dòng lympho và các thể khác như ung thư xương, ung thư não.&lt;SEP&gt;Bạch cầu cấp là một thể bệnh cấp tính nguy hiểm, cần điều trị kịp thời.&lt;SEP&gt;Bạch cầu cấp là bệnh lý gây giảm tiểu cầu, tăng nguy cơ chảy máu lâu cầm.&lt;SEP&gt;Bạch cầu cấp là tình trạng tăng nhanh bất thường của các tế bào máu trắng.\nCơ Nhanh Mỏi: Triệu chứng của bệnh nhược cơ.\nTác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.&lt;SEP&gt;Tác dụng phụ của một số thuốc có thể ảnh hưởng lên huyết áp.\nCalci-D3: Calci-D3 là một trong những thuốc có thành phần tương tự với Calci D Hasan.\nNiêm Mạc Dạ Dày: Niêm Mạc Dạ Dày là bề mặt trong cùng của dạ dày, đóng vai trò như một lớp niêm mạc bảo vệ dạ dày khỏi các tác nhân gây hại. Lớp niêm mạc này có cấu trúc dạng nếp gấp, giúp tiêu hóa thức ăn và là vị trí dễ bị tổn thương do nhiều nguyên nhân khác nhau. Niêm mạc dạ dày chịu tác động tiêu cực từ các hoạt chất như Guaifenesin trong Cedipect F, Saponin triterpen từ quả bồ kết, tinh dầu sả, và Crotamiton. Ngoài ra, nó còn bị ảnh hưởng bởi thuốc NSAIDs, đặc biệt là những thuốc ức chế COX-1.\n\nNiêm mạc dạ dày được bảo vệ bởi nhiều yếu tố khác nhau, bao gồm cả các hoạt chất tự nhiên từ thảo dược như cây Bồ bồ, cây Nổ, và cây Thất diệp nhất chi hoa. Các hoạt chất Bergenin từ cây Nổ, Biviantac, và kim vàng đều giúp bảo vệ niêm mạc dạ dày. Enzim Cyclooxygenase – 1 (COX – 1), các thuốc giảm tiết, và các thuốc bảo vệ niêm mạc cũng đóng vai trò quan trọng trong việc bảo vệ niêm mạc dạ dày. Niêm mạc dạ dày còn được bảo vệ bởi Codonopsis pilosula, ngọc cẩu, và Sài đất. Các nghiên cứu cho thấy chiết xuất quả sung cũng giúp bảo vệ niêm mạc dạ dày khỏi tổn thương oxy hóa.\n\nNiêm mạc dạ dày là vị trí bị tổn thương trong các tình trạng như hội chứng Zollinger-Ellison và loét dạ dày, cũng như là vị trí tác dụng của thuốc bao phủ niêm mạc dạ dày. Nó có thể bị tổn thương bởi rượu hoặc thuốc indomethacin, và có thể bị kích thích bởi việc sử dụng rau diếp sống hoặc acid acetylsalicylic. Niêm mạc dạ dày cũng bị tổn thương khi dùng thuốc Chymodok và bị ảnh hưởng bởi việc sử dụng thuốc nói chung.\n\nNiêm mạc dạ dày bị tổn thương bởi nhiều yếu tố, trong đó có bệnh viêm loét dạ dày. Curcumin được biết đến với khả năng tái tạo niêm mạc dạ dày trong bệnh này. Ngoài ra, các sản phẩm như CumarGold cũng hỗ trợ bảo vệ niêm mạc dạ dày. Chất xơ trong trái tắc cũng được đề cập đến như một yếu tố bảo vệ niêm mạc dạ dày, tuy nhiên niêm mạc dạ dày cũng có thể bị kích thích bởi acid hữu cơ trong trái tắc.\n\nNhìn chung, niêm mạc dạ dày là một cấu trúc phức tạp, chịu tác động từ nhiều yếu tố khác nhau, bao gồm cả các tác nhân tự nhiên và thuốc. Việc bảo vệ niêm mạc dạ dày là rất quan trọng để duy trì sức khỏe tổng thể của dạ dày.\nChất Khoáng Thiết Yếu: Chất khoáng thiết yếu có thể tương tác với Calci D Hasan.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThiếu Calci: Thiếu calci là tình trạng cần bổ sung calci trong trẻ em thời kỳ phát triển, phụ nữ có thai và cho con bú.&lt;SEP&gt;Thiếu calci là tình trạng dinh dưỡng kém được Calci D Hasan giúp cải thiện.\nTác Dụng Phụ Nghiêm Trọng: Tác dụng phụ nghiêm trọng là biểu hiện có thể xảy ra khi sử dụng quá liều Amlor 5 Pfizer.&lt;SEP&gt;Tác dụng phụ nghiêm trọng có thể xảy ra khi sử dụng Ciacca, đặc biệt đối với phụ nữ trong độ tuổi sinh sản không có biện pháp tránh thai phù hợp.&lt;SEP&gt;Tác dụng phụ nghiêm trọng xảy ra khi uống rượu cùng với một số loại thuốc.\nTriệu Chứng Không Liên Quan: Triệu chứng không liên quan đến bất kỳ nguyên nhân y tế nào có thể được xác định.\nTác Dụng Phụ Thuốc: Tác dụng phụ của thuốc là vấn đề chính trong quá trình điều trị bệnh bạch cầu cấp trẻ em.&lt;SEP&gt;Tác dụng phụ của thuốc.&lt;SEP&gt;Tác dụng phụ của thuốc được đánh giá để loại trừ nguyên nhân gây ra triệu chứng tương tự như run vô căn.&lt;SEP&gt;Tác dụng phụ của thuốc có thể gây bệnh tiêu chảy.\nMã Tiên Thảo: Mã tiên thảo là giống cỏ dài, thẳng, có đốt như roi ngựa, tên khoa học Verbena officinalis L., thuộc họ Cỏ roi ngựa Verbenaceae, được sử dụng trong dân gian như vị thuốc trị ghẻ, lở, ngứa, sưng mủ.&lt;SEP&gt;Mã tiên thảo là thảo dược vị đắng, hơi hàn, vào kinh can và tỳ, có tác dụng phá huyết, sát trùng, thông kinh, điều trị bệnh lở ngứa vùng kín, sốt cao, viêm gan, xơ gan, viêm thận, phù thũng, nhiễm trùng đường tiết niệu, sỏi tiết niệu, bong gân, chàm, viêm da.&lt;SEP&gt;Mã Tiên Thảo được sử dụng để điều trị nhiều bệnh như sưng vú, mụn nhọt, ngứa vùng kín, da lở ngứa, viêm khoang miệng, kinh nguyệt không đều, đau bụng kinh, hỗ trợ điều trị sốt rét và vàng da do gan.&lt;SEP&gt;Mã Tiên Thảo là thuốc cần được sắc cùng với nước và lọc bỏ bã trước khi sử dụng.\nLoãng Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị loãng xương.\nBệnh Lý Nền - Tác Dụng Phụ: Bệnh lý nền làm tăng khả năng gặp tác dụng phụ khi dùng thuốc.\nTác Dụng Không Mơ Nguyện - Vị Thuốc: Vị thuốc có thể gây ra các tác dụng không mong muốn.\nDiurefar - Ngộ Độc Digitalis: Diurefar chống chỉ định cho những người ngộ độc digitalis.\nKháng Sinh Phổ Rộng - Tác Dụng Phụ: Sử dụng kháng sinh có liên quan đến nhiều tác dụng phụ.\nAgi-Calci - Thiếu Calci: Agi-Calci được chỉ định dùng trong trường hợp thiếu calci.\nBạch Cầu Cấp - Tác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.\nBệnh Lý Nền - Calci D Hasan: Người mắc bệnh lý nền cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng khi sử dụng Calci D Hasan.\nNiêm Mạc Dạ Dày - Thuốc: Thuốc có thể ảnh hưởng đến niêm mạc dạ dày.\nCalci D Hasan - Ngộ Độc Digitalis: Calci D Hasan có thể gây ngộ độc digitalis.\nThuốc - Tác Dụng Phụ Nghiêm Trọng: Một số loại thuốc có thể gây tác dụng phụ nghiêm trọng.\nCalci D Hasan - Thiếu Calci: Calci D Hasan giúp cải thiện tình trạng thiếu calci.\nTriệu Chứng Không Liên Quan - Tác Dụng Phụ Thuốc: Tác dụng phụ của thuốc là triệu chứng của triệu chứng không liên quan.\nCalci D Hasan - Thiểu Năng Cận Giáp: Calci D Hasan có thể tương tác với thiểu năng cận giáp.\nMã Tiên Thảo - Tác Dụng Phụ: Mã Tiên Thảo có thể gây tác dụng phụ.\nCalci D Hasan - Khó Chịu Ở Dạ Dày: Calci D Hasan có thể gây khó chịu ở dạ dày.\nBác Sĩ - Tác Dụng Phụ: Bác sĩ cần thông báo nếu có tác dụng phụ khi dùng thuốc.\nCalci D Hasan - Kích Ứng Hệ Tiêu Hóa: Calci D Hasan có thể gây kích ứng hệ tiêu hóa.\nHạ Canxi Máu - Thuốc Lợi Tiểu: Thuốc lợi tiểu có thể gây tác dụng phụ hạ canxi máu.\nCalci D Hasan - Calci-D3: Calci D Hasan có thành phần tương tự với Calci-D3.\nCalci D Hasan - Chất Khoáng Thiết Yếu: Calci D Hasan có thể tương tác với chất khoáng thiết yếu.\nBệnh Nhược Cơ - Cơ Nhanh Mỏi: Cơ nhanh mỏi là triệu chứng của bệnh nhược cơ.\nNhuyễn Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị nhuyễn xương.']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Người mắc bệnh lý nền cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng khi sử dụng Calci D Hasan. Bệnh lý nền làm tăng khả năng gặp tác dụng phụ khi dùng thuốc. Điều này có nghĩa là Calci D Hasan có thể gây ra tác dụng phụ nghiêm trọng hơn hoặc không mong muốn cho bệnh nhân có bệnh lý nền sẵn có.
+Bên cạnh đó, Calci D Hasan có thể tương tác với thiểu năng cận giáp, gây ra các vấn đề liên quan đến lượng canxi trong máu. Người bệnh cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng để bác sĩ có thể đánh giá và điều chỉnh liều lượng hoặc loại thuốc khác nếu cần thiết.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ở bệnh nhân mắc bệnh lý nền, Calci D Hasan có thể gây tăng nhạy cảm với vitamin D, làm tăng nguy cơ gây hại cho sức khỏe.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6424572542906745</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5356143135476686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Cao Bình Vôi: Cao bình vôi là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Cao bình vôi là thành phần trong thuốc bổ thần kinh H5000.\nBảo Quản: Bảo Quản là quy trình lưu trữ các loại thuốc, dược liệu, và thực phẩm một cách đúng đắn nhằm đảm bảo chất lượng và tính hiệu quả của chúng. Quy trình này đòi hỏi việc bảo quản trong bao bì kín, tránh ẩm, ánh sáng, và nhiệt độ dưới 30°C. Mỗi loại thuốc và dược liệu có yêu cầu bảo quản cụ thể: thuốc Domperidone cần được bảo quản đúng cách để duy trì tính hiệu quả; thuốc Acyclovir 5% Agimexpharm cần được bảo quản ở nhiệt độ không quá 30°C, tránh ánh sáng và phải được đặt xa tầm tay trẻ em; thuốc Amaryl cũng cần được bảo quản ở nhiệt độ không quá 30°C; thuốc Arthrorein Pharmanel cần được lưu trữ trong bao bì kín, ở nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp; dược liệu Bạch Hạc cần được cất trữ ở nơi thoáng mát, với nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời; thuốc Adrenoxyl 10 mg cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng và nhiệt độ dưới 30ºC; Beatil cần được bảo quản ở nhiệt độ dưới 30°C, trong bao bì gốc để tránh ẩm và ánh sáng. \n\nĐiều kiện chung cho việc bảo quản thuốc và dược liệu là cần phải tránh ẩm, ánh sáng trực tiếp và nhiệt độ cao hơn 30°C để đảm bảo rằng các thành phần hoạt động chính của chúng không bị phân hủy hoặc biến đổi. Dược liệu Hoa Cút Lợn tươi nên dùng ngay để giữ dược tính, tránh ẩm ướt. Nếu bảo quản trong tủ lạnh, phải để ráo nước, cho vào túi ni lông đục vài lỗ nhỏ, chỉ giữ được 2 – 3 ngày. Bảo quản lá dứa sau khi sơ chế, rửa sạch, để ráo nước, lưu trữ ở nơi mát mẻ, thoáng mát, tránh ánh nắng mặt trời trực tiếp và nơi có nhiều côn trùng, ruồi bọ. Bảo quản dược liệu ở nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời, nếu quả trải qua sơ chế cần để nơi khô ráo, thông thoáng. Bảo quản dược liệu Trường sinh thảo sau khi sơ chế bằng cách cho vào túi kín, bảo quản ở những nơi khô mát, đề phòng mối mọt, ẩm mốc. Cách bảo quản thuốc Cenditan là bảo quản nơi khô ráo, thoáng mát, nhiệt độ dưới 30°C và tránh ánh sáng trực tiếp từ mặt trời, để xa tầm tay của trẻ em. Bảo quản thuốc đúng cách, tránh ẩm ướt và ánh sáng trực tiếp, giữ thuốc xa tầm với của trẻ em và thú cưng, bảo quản ở nhiệt độ không quá 30°C. Bảo quản những phần dược liệu đã qua khâu chế biến trong bọc kín, cất trữ nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.\n\nThuốc Dentanalgi cần được bảo quản ở nơi khô mát, tránh tiếp xúc ánh sáng trực tiếp và nhiệt độ dưới 30°C. Thuốc Cloramphenicol cần được bảo quản tránh xa tầm tay của trẻ em và thú cưng, ở nhiệt độ 15 – 25°C. Bảo quản dược liệu sau khi chế biến trong bọc kín, cất trữ nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời. Bảo quản dược liệu ở nơi khô ráo và thoáng mát, tránh mối mọt. Bảo quản dược liệu ở nơi thoáng mát, tránh để dược liệu ở nơi ẩm ướt để tránh tình trạng nổi mốc meo.&lt;SEP&gt;Bảo quản sài hồ cần được cất giữ ở nơi kín đáo, khô ráo, thoáng mát, sạch sẽ.&lt;SEP&gt;Bảo quản Tế tân tránh phơi trực tiếp dưới nắng.&lt;SEP&gt;Bảo quản là cách lưu trữ Thạch hộc để đảm bảo chất lượng.&lt;SEP&gt;Bảo quản Depakin ở nơi khô ráo, nhiệt độ không quá 25°C.&lt;SEP&gt;Bảo quản chiết xuất hương thảo trong lọ tối màu, kín, đặt nơi khô thoáng, tránh ánh sáng mặt trời hay bụ.\nChiết Xuất Huyền Hồ Sách Đông Khô: Chiết xuất huyền hồ sách đông khô là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Chiết xuất huyền hồ sách đông khô là thành phần trong thuốc bổ thần kinh H5000.\nNhung: Nhung là dược liệu được thu hoạch từ hươu, qua quá trình xử lý như cưa, rửa, sấy khô.\nTỉnh Giác Hay: Tỉnh giấc hay là triệu chứng được điều trị bằng thuốc bổ thần kinh H5000.\nTế Tân: Tế Tân là một thảo dược quan trọng trong y học cổ truyền, được biết đến với nhiều công dụng đa dạng. Tế Tân là một loại cây cỏ nhỏ, có nguồn gốc từ Trung Quốc và phân bố rộng rãi tại các tỉnh như Triết Giang, Hồ Bắc, Tứ Xuyên, Cát Lâm, Hắc Long Giang, An Huy, Thiểm Tây, Liêu Ninh, Giang Tây, và Cam Túc. Thảo dược này có mùi vị cay nồng, tính ấm và được ứng dụng trong nhiều bài thuốc khác nhau.\n\nTế Tân đóng vai trò quan trọng trong An Thảo Nam Dược, một loại thuốc quý được sử dụng để điều trị nhiều chứng bệnh khác nhau. Thảo dược này cũng là thành phần chính trong Didicera, một sản phẩm khác được sử dụng trong y học cổ truyền. Tế Tân được sử dụng như một thành phần trong nhiều bài thuốc, bao gồm cả bài thuốc kinh nghiệm, giúp điều trị hiệu quả các triệu chứng như ho, sốt, cảm mạo, và đau thần kinh tọa.\n\nNgoài ra, Tế Tân còn được sử dụng trong bài thuốc Tiểu Thanh Long Thang và bài thuốc "Độc Hoạt Tang Ký Sinh" khi kết hợp với tang ký sinh. Thảo dược này còn được sử dụng trong bài thuốc chữa cảm nắng mùa hè. Tế Tân có tác dụng chữa trúng phong hàn, đau nhức đầu, phong thấp, buồn nôn, hen suyễn, đau răng, nghẹt mũi, bí mồ hôi, và ứ huyết. Khi sử dụng bên ngoài, Tế Tân còn giúp giảm tình trạng hôi miệng.\n\nThảo dược này cũng được biết đến với khả năng điều trị các vấn đề về xương khớp, đặc biệt là trong bài thuốc trị khớp sưng đỏ, đau và khó co duỗi. Tế Tân còn được sử dụng để nấu nước thuốc trong y học cổ truyền, với mục đích điều trị nhiều bệnh lý khác nhau thông qua các bài thuốc khác nhau. Tế Tân là một vị thuốc trong kho tàng thuốc quý của Đông y, được sử dụng để điều trị đau răng kèm sưng đỏ.&lt;SEP&gt;Tế tân là thành phần trong bài thuốc chữa ho hen có nhiều đờm.&lt;SEP&gt;Tế tân là vị thuốc dùng phối hợp với Tử uyển để chữa trẻ em ho, có tiếng khò khè trong cổ, thở khó.&lt;SEP&gt;Tế tân là một vị thuốc trong y học cổ truyền, thường được sử dụng để chữa ho và cảm lạnh.\nThuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 có tác dụng hỗ trợ giảm đau thần kinh ngoại biên do thiếu hụt vitamin B.&lt;SEP&gt;Thuốc bổ thần kinh H5000 được dùng cho người bị khó ngủ, mất ngủ, hay tỉnh giấc, hay căng thẳng, lo lắng; đau mỏi cổ vai và sau gáy, đau liên sườn, đau thần kinh, đau lưng, đau khớp, tê nhức, tê bì tay chân; đau đầu, chóng mặt, hoa mắt, rối loạn tiền đình, tai biến mạch máu não.&lt;SEP&gt;Thuốc bổ thần kinh H5000 là sản phẩm bổ sung vitamin B cho thần kinh ngoại biên, có tác dụng hỗ trợ giảm đau thần kinh ngoại biên do thiếu hụt vitamin B.&lt;SEP&gt;Thuốc bổ thần kinh H5000 là sản phẩm bổ sung vitamin B cho thần kinh ngoại biên, có tác dụng hỗ trợ giảm đau thần kinh ngoại biên do thiếu hụт vitamin B.\nBảo Quản Dược Liệu: Bảo quản dược liệu sau khi sơ chế cần được bảo quản ở những nơi khô.&lt;SEP&gt;Bảo quản dược liệu trong bọc kín, hũ nhựa hay thủy tinh, cất trữ nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.&lt;SEP&gt;Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.&lt;SEP&gt;Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ, tránh nơi ẩm mốc và ánh nắng trực tiếp.&lt;SEP&gt;Bảo quản dược liệu cần để nơi khô ráo, thông thoáng.\nTiêu Diệt Vi Khuẩn HP: Lá Khôi giúp tiêu diệt vi khuẩn HP.\nQuả: Quả là thuật ngữ chung để chỉ các loại quả khác nhau từ nhiều loài thực vật. Mỗi loại quả này đều có những đặc điểm riêng biệt về hình dạng, kích thước, màu sắc và cấu trúc, giúp phân biệt chúng dễ dàng hơn. Ví dụ, quả An nam tử là một loại quả nang, có thể chứa từ 1 đến 5 quả đại, cao từ 10 đến 24cm, mặt ngoài của quả này có màu đỏ, còn mặt trong thì có màu lục ánh bạc, vỏ quả rất mỏng và hạt của nó to bằng ngón tay, có hình bầu dục hoặc thuôn dài. Quả Hương Bạch Chỉ là một loại quả bế đôi dẹt, chiều dài khoảng 6mm, có hình bầu dục hoặc hơi tròn. Quả của Bạch đồng nữ là quả hạch đen, có hình cầu. Thực vật thuộc họ cải thường có quả lông phủ bên ngoài, có dạng mỏ dài và chứa từ 4 đến 6 hạt nhỏ màu vàng nâu. Quả của Bàn long sâm cũng có lông mịn bao phủ. Dong riềng đỏ có nhiều quả có nhiều gai mềm, chứa nhiều hạt hình cầu màu đen. Thổ phục linh cũng có quả nhỏ tròn, mọng, đường kính trung bình khoảng 10mm, chứa khoảng 3-4 hạt hình trứng. Quả cây biển súc mọc ở cạnh, chứa một hạt đầu đen. Quả cây bóng nước có dạng hình bầu dục, đầu nhọn, có chia khía, lớp da ngoài có lông nhám. Quả của cà dại hoa tím mọng, hình cầu, màu đỏ hay vàng da cam khi chín, nhẵn, hạt hình đĩa màu vàng. Quả của cà dại hoa trắng là quả mọng, hình cầu nhẵn, màu vàng, hạt hình dĩa, có mang. Quả của cà độc dược có hình cầu, màu xanh và có gai. Quả của Cát sâm dẹt trong, chứa từ 1-10 hạt hình thấu kính, rốn rộng và ngắn. Quả của cây Câu đằng là quả nang dài và dẹt, có chứa nhiều hạt có cánh. Quả cây Bần là phần dùng để điều trị các vết thương, có hình cầu, dẹt, có mũi thuôn nhọn ở đầu. Quả cây Báng có thể sử dụng để làm thuốc. Quả cây Bồng bồng hình giáo, chứa nhiều hạt có mào lông. Quả cây Chàm hình dải, thẳng hay cong, dài 3 – 4 cm, rộng 0,3 cm. Quả của cây chây có vị chua, tính bình. Quả cây Đước có hình trứng, màu nâu lục nhạt, mỗi quả chứa 1 hạt. Quả Me đất là bộ phận của cây Me đất. Quả của cây một lá hình thoi, có múi trông giống như quả khế con, dài 2-3cm, thường cho quả vào các tháng 4, tháng 5 và tháng 6. Ngoài ra, quả của cây mướp khía lớn hình chùy dài khoảng 30-40cm, đường kính từ 7-10cm, có 10 cạnh nhọn dọc theo quả. Quả nang, hình cầu, màu trắng; hạt màu đỏ nâu, bóng. Quả nhẵn, bao bọc bởi mày hoa. Quả Thuốc Mọi có màu đỏ sau khi chín chuyển sang màu đen, hình cầu, đường kính 2 – 3 mm, bên trong chứa 2 – 3 hạt nhỏ và dẹt.\n\nMột số quả mọng có hình gần tròn, đường kính khoảng 3 – 5cm, thường chỉ chứa một hạt. Quả của cây hồi có mùi thơm dễ chịu và vị ngọt. Tất cả các loại quả trên đều đóng vai trò quan trọng trong việc duy trì sự sống của cây trồng và cung cấp nguồn thức ăn quý giá cho nhiều loài động vật khác nhau. Ngoài ra, còn có một số quả nhỏ, dài 3mm, rộng 1,5mm.\n\nQuả của dây bông xanh có hình nang nhẵn, có mũi nhọn dài. Quả dây đau xương hình bầu dục hoặc hình tròn, khi chín có màu đỏ, chứa chất nhày bao quanh hạt hình bán cầu. Quả có hình bầu dục, bóng, mặt ngoài phủ một lớp như sáp, khi chín có màu vàng đỏ, có cuống ngắn. Quả dài 5,5cm, rộng ở nửa dưới, hạt dẹt, lông mào dài 3cm. Một số quả mọng hình trứng hoặc hình tròn, dài 20-25 cm, khi chín màu vàng. Ngoài ra, quả hình cầu, khi non có màu trắng, chín có màu đen, đường kính 5 – 9mm, không ăn được. Đặc biệt, quả Giảo cổ lam hình cầu, khi non có màu trắng, chín có màu đen, đường kính 5 – 9mm, chứa 2 – 3 hạt, không mở. Quả của cây Hạ khô thảo nhỏ và cứng. Quả hình thoi, màu xám nhiều lông, dài 7-11cm, rộng 8mm. Hạt dẹt, phồng ở lưng, dài 5-7mm, rộng 2mm, có chùm lông mịn dài 2cm. Quả nang đường kính 3-5 cm, quả non màu xanh lá, chín có màu nâu đen, hình sao 4-7 thùy. Quả đu đủ to tròn, dài, khi chín mềm, hạt màu nâu hoặc đen tùy từng loại giống, có nhiều hạt. Quả quỳnh có thể dùng để ăn, hình bầu dục, dài khoảng 4 cm. Quả hoa sói là dạng quả mọng, kích thước nhỏ, đường kính từ 3-4mm, thường mọc thành chùm ở đầu cành. Quả khi chín có màu đỏ gạch đẹp mắt. Quả hình cầu, đường kính 4 – 5cm, vỏ ngoài cứng, dày 4mm, trong chứa nhiều hạt hình khuy áo, đường kính 22mm hay hơn, dày 18mm, có lông mượt vàng ánh bạc. Quả hồi đầu thảo dạng nang, đỉnh quả mở không đều, bên trong chứa hạt nhỏ có vỏ ngoài màu nâu, hình thoi. Quả của Huyền sâm là quả nang, hình trứng, có nhiều hạt nhỏ màu đen. Quả của kê huyết đằng hình trứng dài 8 – 12mm, khi chín có màu lam đen. Quả ké đầu ngựa có gai móc, giúp cây phát tán. Quả bế đôi, dạng hình trứng, kích thước rộng 7mm, dài 12 mm, có hai sừng nhọn ở đầu quả, còn gai móc phủ xung quanh. Quả đóng vai trò quan trọng không chỉ đối với cây trồng mà còn là nguồn thức ăn chính của nhiều loài động vật, bao gồm cả loài gấu. Quả mùi tàu gần hình cầu, hơi dẹt, đường kính 2mm, chứa nhiều hạt bên trong. Quả của cây Mướp gai hình trứng vuông, màu nâu, có gai ngắn rậm ở đỉnh, chứa hạt dẹp. Quả Nam sâm hình cầu, đường kính 3 – 4mm, khi chín màu tím đen, chứa 6 – 8 hạt. Quả Náng hoa trắng chứa Criasbetaine, lycorine-1,2-O-D-diglucoside, ungeremine. Quả của Ngấy hương có dạng kép, hình trứng hoặc hình cầu, có đài tồn tại. Gồm nhiều quả hạch con bên trong, khi chín màu đỏ hay đen nhạt, ăn được.\n\nQuả ngọc lan tây là chùm quả, mỗi chùm chứa 10-12 hạt cứng, dẹt, hình trứng màu nâu nhạt, đường kính 6mm.\n\nQuả nhân sâm là quả mọng hơi dẹt, to bằng hạt đậu xanh, màu đỏ khi chín và chứa 2 hạt. Quả mỏng như giấy, dài 2 – 3mm, hạt có vảy ở trên mặt.\n\nQuả của Rau mương hình trụ, nhẵn, hơi phình ra ở đỉnh, chứa nhiều hạt, các hạt này ẩn sâu và chỉ xếp 1 dãy trong ¾ dưới, rời nhau và xếp nhiều dãy ở phần trên, mỗi quả dài 2-3cm.\n\nQuả bế hình trụ, có mào lông ở đỉnh, ra quả khoảng từ tháng 10 đến tháng 3.\n\nQuả có hình cầu, màu tím, đường kính 1,5 – 2cm, mặt ngoài có gai ngắn, chia thành 3 ô.\n\nQuả của cây sa nhân hình cầu, màu tím, đường kính 1,5-2cm.\n\nNgoài những loại quả đã mô tả, quả còn có hình dạng bầu dục, dài khoảng 5mm, ống tinh dầu nằm ở mặt tiếp giáp.\n\nQuả sâm vũ diệp mọng, khi chín màu đỏ.\n\nQuả Sổ Bà mang đài tồn tại, phát triển thành bản dày, mọng nước, đường kính 10cm hay hơn, vị chua, ăn được.\n\nQuả Sử quân tử chín vào tháng 8.\n\nQuả sương sâm trơn hình tròn nhỏ, kích thước 10-12mm, chín vào tháng 7 và chuyển màu tím.\n\nQuả ngũ gia bì gai có hình cầu dẹt, đường kính khoảng 2,5mm, chuyển sang màu đen khi chín và có 2 hạt.\n\nQuả Phèn đen hình cầu khi chín quả có màu đen, bên trong hạt có màu nâu nhạt. Mùa ra hoa quả thường vào tháng 8 – 10.\n\nQuả của Thầu dầu là loại quả nang có màu tím nhạt hoặc lục, có gai mềm xung quanh.\n\nQuả của Khúc khắc mọng, hình cầu, gần 3 cạnh, có 3 hạt, khi chín có màu đỏ hay tím đen.\n\nQuả tam thất mọng, hình cầu dẹt, khi chín có màu đỏ, hạt màu trắng.\n\nQuả Tang ký sinh có hình bầu dục, có vết tích của đài tồn tại, mùa hoa quả vào tháng 1- tháng 3.\n\nQuả thạch xương bồ mọng, màu đỏ nhạt, bên trong chứa hạt được bao phủ bởi chất nhầy.\n\nNgoài ra, quả còn được sử dụng trong điều trị các chứng bệnh. Một số quả có đường kính 1,5 – 1,8mm, bao hoa mang lông, quả mang 9 đường gân hoặc 4 cạnh, đỉnh quả có 2 nhánh như 2 răng nhọn, màu trắng, sáng, màu vàng tối hoặc màu sáng nâu, hình trứng.\n\nQuả cây xá xị có tác dụng giải biểu, thanh nhiệt, giảm ho.\n\nMột số quả dẹt có hình trứng ngược, dày, dai, cứng, dài từ 7-10cm, rộng từ 3,5-4cm, trong đó có 3-4 hạt màu nâu.\n\nQuả của cây chúc hình cầu lớn hoặc hình trứng, nhiều màu, ban đầu màu xanh lục, sau chuyển màu xanh vàng khi chín.\n\nQuả của cây tỏi độc là một nang to 3 ngăn, chứa nhiều hạt màu nâu nhạt.\n\nQuả có kích thước khá nhỏ, hình cầu, vỏ có nhiều túi tinh dầu, màu xanh khi còn non và chuyển dần thành vàng khi chín, vị chua dịu đặc trưng.\n\nQuả hình trứng ngược, phủ lông mềm, màu vàng xám, khi chín nứt thành 2 mảng, chứa 1-2 hạt.\n\nQuả của Tử uyển khô, hơi dẹt có lông trắng.\n\nQuả tây là quả thịt, hơi hình cầu, hơi có lông, chín có màu vàng, dài 3 – 4cm, có 4 hạch đơn, mỗi hạch mang 1 – 2 hạt không phôi nhũ.\nĐau Mỏi Cổ: Đau mỏi cổ là triệu chứng được hỗ trợ điều trị bởi Thuốc bổ thần kinh H5000.\nChế Phẩm: Chế phẩm là sản phẩm dược phẩm, có thể bảo quản được tới 3 năm ở nhiệt độ ≤ 37 °C và tới 5 năm ở 2 – 8 °C.&lt;SEP&gt;Chế phẩm là thuật ngữ chung chỉ sản phẩm thuốc.\nCúm H5N1: Cúm H5N1 là bệnh được phòng ngừa bằng tinh dầu trầm.\nÁnh Sáng: Ánh Sáng là một yếu tố đa chức năng, đóng vai trò quan trọng trong nhiều khía cạnh cuộc sống, từ y tế đến nông nghiệp và cả trong lĩnh vực không liên quan đến y tế hay nông nghiệp. Trong lĩnh vực y tế, ánh sáng là một yếu tố cần tránh khi bảo quản nhiều loại thuốc khác nhau, bao gồm Acyclovir Stella Cream, Adrenalin, Albiomin 20%, Alvesin, Amiparen 5 Otsuka, Amoxicilin 500 mg, Ampicillin Mekophar, Batigan, Bisilkon, Bluemint, Clesspra DX, Comozol, Betadine, Aceclofenac STADA, và Ameflu DAYTIME. Tiếp xúc trực tiếp với ánh sáng có thể gây ra những ảnh hưởng xấu đến chất lượng của các loại thuốc này, dẫn đến việc phân hủy hoặc thay đổi cấu trúc của các thành phần thuốc, làm giảm hiệu quả điều trị và tăng nguy cơ sử dụng thuốc không đúng cách. Việc bảo quản các loại thuốc này cần được thực hiện trong điều kiện tránh ánh sáng để duy trì chất lượng và hiệu quả của chúng.\n\nTrong nông nghiệp, ánh sáng thích hợp hỗ trợ sự phát triển của cây trồng, đặc biệt là đối với cây trồng như Bán chi liên, cà gai leo, và cúc mốc. Nó cũng ảnh hưởng đến tốc độ sinh trưởng và chiều cao của Cỏ mật, thể hiện rõ ràng vai trò của nó trong việc định hình môi trường tự nhiên. Ngoài ra, ánh sáng mặt trời ảnh hưởng đến cánh hoa Khiên ngưu và là điều kiện sinh trưởng của lạc tiên. Ánh sáng cũng đóng vai trò quan trọng trong việc phát triển cây húng quế và cây sương sâm, sinh trưởng tốt ở môi trường ánh sáng từ 70-80%.\n\nÁnh sáng từ phía sau người xem có thể giúp giảm mỏi mắt khi đọc sách, tạo ra một môi trường thuận lợi hơn cho việc đọc và học tập. Đồng thời, ánh sáng còn được sử dụng như một phương pháp an toàn để loại bỏ lông thừa. Ánh sáng buổi sáng có thể giúp điều chỉnh đồng hồ sinh học. Tuy nhiên, tiếp xúc quá nhiều với ánh sáng có thể dẫn đến mất ngủ. Ngoài ra, ánh sáng cũng khiến Giun đất sợ hãi và hạn chế di chuyển lên mặt đất.\n\nMực cũng tập trung đông khi có ánh sáng, nhưng Bioflora cần tránh tiếp xúc với ánh sáng.&lt;SEP&gt;Ánh sáng trực tiếp có thể ảnh hưởng đến thuốc Brain và cần được tránh.&lt;SEP&gt;Ánh sáng là yếu tố cần tránh khi bảo quản thuốc Broncho-Vaxom.&lt;SEP&gt;Ánh sáng là yếu tố cần tránh khi bảo quản thuốc Cialis.&lt;SEP&gt;Ánh sáng là yếu tố thu hút côn trùng.\nKháng Ký SinH: Địa liền có đặc tính kháng ký sinh.\nChóng Mặt - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người chóng mặt.\nBảo Quản - Nhung: Bảo quản nhung ở nơi khô ráo và thoáng mát, tránh mối mọt.\nThuốc Bổ Thần Kinh H5000 - Đau Đầu: Thuốc bổ thần kinh H5000 được dùng cho người đau đầu.&lt;SEP&gt;Thuốc bổ thần kinh H5000 hỗ trợ giảm đau đầu.\nBảo Quản - Tế Tân: Bảo quản Tế tân tránh phơi trực tiếp dưới nắng.\nMất Ngủ - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người bị mất ngủ.&lt;SEP&gt;Thuốc bổ thần kinh H5000 hỗ trợ cải thiện mất ngủ.\nBảo Quản Dược Liệu - Quả: Quả cần được bảo quản theo quy tắc để tránh hỏng hóc.\nThuốc Bổ Thần Kinh H5000 - Đau Lưng: Thuốc bổ thần kinh H5000 được dùng cho người đau lưng.\nChế Phẩm - Ánh Sáng: Tránh ánh sáng khi bảo quản chế phẩm.\nLo Âu - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 hỗ trợ giảm lo âu.\nBảo Quản - Dầu Cao Sao Vàng: Bảo quản là quy trình bảo quản sản phẩm Dầu Cao Sao Vàng đúng cách.\nThuốc Bổ Thần Kinh H5000 - Đau Khớp: Thuốc bổ thần kinh H5000 được dùng cho người đau khớp.\nBảo Quản - Lộc Nhung: Bảo quản lộc nhung ở nơi khô ráo và thoáng mát, tránh mối mọt.\nThuốc Bổ Thần Kinh H5000 - Vitamin B1: Vitamin B1 là thành phần hoạt chất trong thuốc bổ thần kinh H5000.\nChất Bay Tinh Đầu - Đại Hồi: Đại hồi cần tránh chất bay tinh dầu trong bảo quản.\nThuốc Bổ Thần Kinh H5000 - Vitamin B12: Vitamin B12 là thành phần hoạt chất trong thuốc bổ thần kinh H5000.\nBảo Quản Sản Phẩm - Dầu Cao Sao Vàng: Dầu Cao Sao Vàng cần được bảo quản đúng cách theo hướng dẫn.\nCăng Thẳng - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người căng thẳng.&lt;SEP&gt;Thuốc bổ thần kinh H5000 hỗ trợ giảm căng thẳng.\nBromelain - Bảo Quản Thuốc: Bromelain cần được bảo quản đúng cách để duy trì chất lượng.\nRối Loạn Tiền Đình - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người rối loạn tiền đình.\nBảo Quản - Cao Sao Vàng: Bảo quản là quy trình bảo quản sản phẩm Cao Sao Vàng đúng cách.\nTai Biến Mạch Máu Não - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người bị tai biến mạch máu não.\nHoa Mắt - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người hoa mắt.\nLo Lắng - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người lo lắng.\nKhó Ngủ - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được dùng cho người bị khó ngủ.\nThuốc Bổ Thần Kinh H5000 - Tê Bì Tay Chân: Thuốc bổ thần kinh H5000 được dùng cho người tê bì tay chân.\nThuốc Bổ Thần Kinh H5000 - Vitamin B: Thuốc bổ thần kinh H5000 cung cấp vitamin B cho thần kinh ngoại biên.\nThuốc Bổ Thần Kinh H5000 - Vitamin B6: Vitamin B6 là thành phần hoạt chất trong thuốc bổ thần kinh H5000.\nThuốc Bổ Thần Kinh H5000 - Đau Thần Kinh: Thuốc bổ thần kinh H5000 được dùng cho người đau thần kinh.\nThuốc Bổ Thần Kinh H5000 - Tê Bì Chân Tay: Thuốc bổ thần kinh H5000 hỗ trợ giảm tê bì chân tay.\nBạch Quả - Thuốc Bổ Thần Kinh H5000: Bạch quả là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Bạch quả là một trong những thành phần của Thuốc bổ thần kinh H5000.\nKháng Ký SinH - Địa Liền: Địa liền có đặc tính kháng ký sinh.\nTai Biến - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 hỗ trợ phòng ngừa tai biến.\nThuốc Bổ Thần Kinh H5000 - Tuần Hoàn Máu: Thuốc bổ thần kinh H5000 thúc đẩy tuần hoàn máu.\nThuốc Bổ Thần Kinh H5000 - Tê Nhức: Thuốc bổ thần kinh H5000 được dùng cho người tê nhức.\nThuốc Bổ Thần Kinh H5000 - Đau Thần Kinh Ngoại Viên: Thuốc bổ thần kinh H5000 hỗ trợ giảm đau thần kinh ngoại biên do thiếu hụt vitamin B.\nCao Bình Vôi - Thuốc Bổ Thần Kinh H5000: Cao bình vôi là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Cao bình vôi là một trong những thành phần của Thuốc bổ thần kinh H5000.\nChiết Xuất Huyền Hồ Sách Đông Khô - Thuốc Bổ Thần Kinh H5000: Chiết xuất huyền hồ sách đông khô là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Chiết xuất huyền hồ sách đông khô là một trong những thành phần của Thuốc bổ thần kinh H5000.\nCông Ty Cổ Phần Dược Phẩm Fresh Life - Thuốc Bổ Thần Kinh H5000: Thuốc bổ thần kinh H5000 được sản xuất bởi Công ty Cổ phần Dược phẩm Fresh Life.&lt;SEP&gt;Công ty Cổ phần Dược phẩm Fresh Life sản xuất Thuốc bổ thần kinh H5000.\nThuốc Bổ Thần Kinh H5000 - Tỉnh Giác Hay: Thuốc bổ thần kinh H5000 được dùng cho người hay tỉnh giấc.\nThuốc Bổ Thần Kinh H5000 - Đau Mỏi Cổ Vai: Thuốc bổ thần kinh H5000 được dùng cho người đau mỏi cổ vai.\nThuốc Bổ Thần Kinh H5000 - Đau Liền Sườn: Thuốc bổ thần kinh H5000 được dùng cho người đau liền sườn.\nThuốc Bổ Thần Kinh H5000 - Đau Vùng Sau Gáy: Thuốc bổ thần kinh H5000 được dùng cho người đau vùng sau gáy.\nThuốc Bổ Thần Kinh H5000 - Vỏ Cây Liễu Trắng: Vỏ cây liễu trắng là thành phần hoạt chất trong thuốc bổ thần kinh H5000.\nThuốc Bổ Thần Kinh H5000 - Đau Mỏi Cổ: Thuốc bổ thần kinh H5000 hỗ trợ giảm đau mỏi cổ.\nChiết Xuất Vỏ Cây Liễu Trắng - Thuốc Bổ Thần Kinh H5000: Chiết xuất vỏ cây liễu trắng là một trong những thành phần của Thuốc bổ thần kinh H5000.\nCúm H5N1 - Tinh Dầu Trầm: Tinh dầu trầm giúp phòng ngừa cúm H5N1.']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Khi bảo quản sản phẩm Bổ thần kinh H5000, cần tránh một số điều kiện cụ thể để đảm bảo chất lượng và hiệu quả của thuốc:
+- **Tránh ẩm**: Sản phẩm cần được bảo quản ở nơi khô ráo, tránh tiếp xúc với độ ẩm.
+- **Tránh ánh sáng**: Cần tránh tiếp xúc trực tiếp với ánh sáng mặt trời.
+- **Tránh nhiệt độ cao**: Bảo quản ở nhiệt độ không quá 30°C.
+- **Tránh xa tầm tay trẻ em**: Đặt sản phẩm ở vị trí không thể tiếp cận của trẻ em.
+### Cách bảo quản
+Sản phẩm nên được bảo quản trong bao bì kín, tránh tiếp xúc với độ ẩm và ánh sáng mặt trời. Đặt ở nơi khô ráo, thoáng mát và nhiệt độ không vượt quá 30°C.
+### Hạn sử dụng
+Thuốc có hạn dùng là 36 tháng kể từ ngày sản xuất. Không sử dụng thuốc sau khi đã hết hạn sử dụng.
+### Lưu ý
+- **Không dùng cho phụ nữ có thai và trẻ em dưới 12 tuổi**.
+- **Không dùng nếu bạn bị mẫn cảm với bất kỳ thành phần nào của sản phẩm**.
+- **Sản phẩm không phải là thuốc, không có tác dụng thay thế thuốc chữa bệnh**.
+### Tham khảo
+- [1] thuoc-bo-than-kinh-h5000-co-tot-khong-gia-thanh-phan-va-cach-su-dung-hieu-qua.txt</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sản phẩm cần tránh bảo quản ở nơi ẩm ướt, có ánh sáng mặt trời, nhiệt độ cao hơn 30°C.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8302714956008083</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7968535881609163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Phụ Nữ Mang Thai Hoặc Cho Con Bú: Nhóm đối tượng có thể sử dụng Biosubtyl.\nBảo Quản Thuốc: Bảo Quản Thuốc là quá trình lưu trữ thuốc đúng cách nhằm duy trì chất lượng và hiệu quả của chúng. Mỗi loại thuốc có yêu cầu bảo quản riêng biệt, từ việc kiểm soát độ ẩm, nhiệt độ và ánh sáng để tránh ảnh hưởng đến chất lượng và tính năng của thuốc. Ví dụ, thuốc như At Domperidone, ATP, Acritel, Acyclovir, Alphachymotrypsin bk 4200 Mebiphar, AlphaDHG, Alzental, Ambroxol Boston, Amepox Soft Capsule, Ampicillin Brawn, Aspirin MKP OnClickListener, Avastin, Ba đậu và disulfiram đều có yêu cầu bảo quản cụ thể. Thuốc Bentarcin cần được bảo quản ở nơi thoáng mát, tránh ánh nắng trực tiếp. Thuốc Debby cần được bảo quản tránh tiếp xúc với ánh sáng, nhiệt độ dưới 30°C và ở nơi khô ráo, thoáng mát. Thuốc Atussin cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc môi trường ẩm ướt, với nhiệt độ tốt nhất là dưới 30ºC. Thuốc Diorophyl cần được bảo quản trong bao bì gốc, nơi khô ráo, tránh ánh sáng và nhiệt độ không quá 30°C. Thuốc Atocib cần được bảo quản theo hướng dẫn trên tờ hướng dẫn sử dụng thuốc, thông thường thuốc được bảo quản ở nhiệt độ phòng, tránh ẩm và ánh nắng trực tiếp.\n\nThuốc methylprednisolone cần được bảo quản theo hướng dẫn cụ thể về nhiệt độ và thời gian sử dụng. Thuốc Acarbose cần được bảo quản ở nơi khô ráo, thoáng mát, tránh nơi ẩm ướt, nhiệt độ dưới 25°C và không sử dụng thuốc sau ngày hết hạn. Thuốc Acemuc cần chú ý đến nhiệt độ, tránh ánh sáng trực tiếp và không để thuốc tiếp xúc với nước. Thuốc Amiodarone cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30°C, tránh ánh sáng trực tiếp. Thuốc axit axetic cần được bảo quản ở nhiệt độ phòng, dưới 30oC, tránh ánh sáng trực tiếp và hơi ẩm, nhiệt độ cao. Thuốc Baclofen cũng cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30oC, tránh ánh sáng trực tiếp. Thuốc Bisacodyl yêu cầu đựng thuốc trong bao bì kín, tránh nóng, ánh sáng và ẩm, bảo quản ở nhiệt độ dưới 25 °C, tránh xa tầm tay của trẻ em, đọc kỹ hướng dẫn trước khi dùng, và không dùng thuốc có dấu hiệu ẩm mốc, thay đổi màu sắc. Thuốc Bismuth cần được bảo quản ở nhiệt độ dưới 30oC, trong bao bì kín. Thuốc Bolutin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ Celsius, tránh ánh sáng trực tiếp. Thuốc Cefpodoxim cần được bảo quản trong bao bì kín, ở nhiệt độ dưới 25 độ Celsius và tránh ánh sáng. Thuốc Ceftriaxone cần được bảo quản ở nhiệt độ dưới 25ºC, nơi khô ráo và thông thoáng. Thuốc CellCept cần được bảo quản tránh xa tầm nhìn và tầm với của trẻ em, không sử dụng sau ngày hết hạn, không lưu trữ trên 30°C, và giữ trong thùng carton để tránh ánh sáng. Thuốc Cerebrolysin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 25°C, tránh ánh sáng trực tiếp. Thuốc Ceritine cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ C. Bảo quản thuốc Diane-35 cần được thực hiện dưới 30 độ Celsius, nơi khô ráo, tránh ánh sáng. Thuốc Benzalkonium Chloride cũng cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt, nhiệt độ bảo quản tốt nhất là dưới 30°C.\n\nQuá trình bảo quản thuốc còn bao gồm việc lưu trữ Irbesartan đúng cách để đảm bảo an toàn và hiệu quả. Bảo quản thuốc đúng cách là rất quan trọng để duy trì chất lượng và hiệu quả của chúng, đảm bảo an toàn khi sử dụng và ngăn chặn bất kỳ sự cố nào có thể xảy ra do bảo quản không đúng cách.\nTầm Với Trẻ Em: Thuốc cần được bảo quản tránh xa tầm với của trẻ em.\nDidicera: Didicera là thuốc thảo dược không kê toa, thuộc công ty Cổ phần Công nghệ cao Traphaco, điều chế dưới dạng viên hoàn và viên nang.&lt;SEP&gt;Viên nang Didicera chứa thành phần độc hoạt, tế tân, tang ký sinh, quế chi, tần giao, phòng phong, cam thảo, bạch linh và đảng sâm.&lt;SEP&gt;Didicera có công năng bổ khí huyết, trừ phong thấp, bổ can thận.&lt;SEP&gt;Didicera là thuốc được điều chế dưới dạng viên nang hoặc viên hoàn, dùng đường uống.&lt;SEP&gt;Didicera là thuốc được bán với giá trung bình khoảng 40.000 VNĐ/hộp 10 gói x viên hoàn 5g.&lt;SEP&gt;Didicera là thuốc cần tham khảo ý kiến dược sĩ hoặc bác sĩ về cách dùng và liều dùng trước khi sử dụng.\nGiữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nCon Trẻ: Lối sống an toàn giúp bảo vệ con trẻ.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nGiữ Thuốc Xa Tầm Tay Trẻ Nhỏ: Giữ thuốc xa tầm tay trẻ nhỏ nhằm tránh bé sử dụng sai cách, sai liều gây nguy hiểm.\nSức Khỏe: Sức khỏe là trạng thái tổng thể của cơ thể, bao gồm cả thể chất, tinh thần và xã hội. Trạng thái này được đánh giá qua các chỉ số như BMI và vòng eo, cũng như thông qua chế độ ăn uống và tập luyện. Sức khỏe cũng liên quan đến tình trạng huyết áp và có thể bị ảnh hưởng bởi tình trạng mất trí nhớ thoáng qua. \n\nĐể nâng cao sức khỏe, việc sử dụng các vị thuốc như Bồ đề, bạc hà, cây hoa cút lợn, cây Đước, Trường sinh thảo, và đông trùng hạ thảo ngâm mật ong được xem là phương pháp hiệu quả. Những vị thuốc này giúp tránh các tương tác có hại và cải thiện tình trạng tổng thể của cơ thể. Sức khỏe không chỉ là trạng thái tổng thể về thể chất mà còn bao gồm cả tinh thần và xã hội của con người. Nó được đề cập trong bài thuốc cổ truyền và cần được bảo vệ thông qua các thói quen sinh hoạt lành mạnh. Việc sử dụng lá Thường xuân cũng được biết đến với khả năng cải thiện sức khỏe. Ngoài ra, sức khỏe còn được coi là trạng thái tổng thể về thể chất và tinh thần, được ảnh hưởng bởi việc sử dụng Hoàng Nàn và bổ sung DHEA.\n\nSức khỏe cũng là yếu tố ảnh hưởng đến lượng protein cần thiết trong chế độ ăn uống, nhấn mạnh tầm quan trọng của việc duy trì một chế độ ăn uống cân bằng và hợp lý để nâng cao và duy trì sức khỏe tổng thể. Tình trạng sức khỏe cần được theo dõi cẩn thận khi sử dụng thuốc Aspegic, một yếu tố được điều trị bởi Aspegic. \n\nNgoài ra, cần lưu ý rằng có một tạp chí y tế tên là "Sức khỏe", nhưng đây không phải là định nghĩa chính cho thuật ngữ sức khỏe trong ngữ cảnh này.&lt;SEP&gt;Sức khỏe là trạng thái tổng thể của cơ thể và tâm trí, có thể được cải thiện thông qua việc sử dụng tinh dầu hoa cam.&lt;SEP&gt;Sức khỏe được cải thiện nhờ tác dụng của tinh dầu quế.&lt;SEP&gt;Sức khỏe được cải thiện nhờ việc ăn tỏi mỗi ngày.&lt;SEP&gt;Sức khỏe được cải thiện thông qua việc sử dụng vị thuốc đúng cách.&lt;SEP&gt;Sức khỏe được tăng cường nhờ bài thuốc ngâm trái quách.\nTrạng Thái Xa Tầm Tay Trẻ Em: Thuốc cần được bảo quản xa tầm tay trẻ em.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nXa Tầm Tay Của Trẻ Em: Xa tầm tay của trẻ em là khuyến nghị về vị trí lưu trữ thuốc để tránh tiếp cận của trẻ em.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nNhóm Thuốc Chẹn Beta: Nhóm thuốc chẹn beta là danh mục chứa các thuốc như Bisoprolol.\nViệc Sử Dụng Sai Lầm: Việc sử dụng sai là hành vi sử dụng thuốc không đúng cách hoặc không tuân theo hướng dẫn.\nCơ Đùi: Cơ đùi là bộ phận cơ thể được tiêm thuốc cho trẻ em.\nÝ Kiến Thầy Thuốc: Ý kiến thầy thuốc là lời khuyên từ chuyên gia y tế về việc sử dụng thuốc.\nBisoprolol - Nhóm Thuốc Chẹn Beta: Bisoprolol thuộc nhóm thuốc chẹn beta, chọn lọc.\nBảo Quản Thuốc - Didicera: Thuốc cần được bảo quản đúng cách để đảm bảo an toàn và hiệu quả.\nCơ Đùi - Trẻ Em: Tiêm vào cơ đùi là vị trí tiêm cho trẻ em.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nAmaryl - Tầm Tay Trẻ Em: Thuốc Amaryl cần được bảo quản ở nơi ngoài tầm tay trẻ em.\nHướng Dẫn - Sức Khỏe: Hướng dẫn của bác sĩ giúp đảm bảo an toàn cho sức khỏe khi sử dụng dược liệu.\nAmbroxol - Tầm Tay Trẻ Em: Thuốc Ambroxol cần được bảo quản tránh xa tầm tay trẻ em.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nAmoxicillin Domesco - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nViệc Sử Dụng Sai Lầm - Ý Kiến Thầy Thuốc: Tham khảo ý kiến thầy thuốc có thể giúp phòng ngừa việc sử dụng thuốc sai cách.\nBaby Septol - Tầm Tay Trẻ Em: Thuốc cần được đặt tránh xa tầm tay trẻ em.\nCon Trẻ - Lối Sống An Toàn: Lối sống an toàn giúp bảo vệ con trẻ.\nBofit F - Tầm Tay Trẻ Em: Bofit F cần được bảo quản tránh tầm tay trẻ em.\nThuốc - Trẻ Em: Trẻ em không được phép sử dụng thuốc này.&lt;SEP&gt;Thuốc cần được giữ tránh xa tầm tay của trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nCavinton - Tầm Tay Trẻ Em: Thuốc Cavinton cần được bảo quản tránh xa tầm tay của trẻ em.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nCarbocistein - Tầm Tay Trẻ Em: Tránh xa tầm tay trẻ em khi bảo quản Carbocistein.\nBảo Quản Thuốc - Thuốc: Bảo quản thuốc là quá trình lưu trữ thuốc.\nIrbesartan - Tầm Tay Trẻ Em: Thuốc Irbesartan cần được giữ tránh xa tầm tay của trẻ em và trẻ nhỏ.\nAxit Axetic - Bảo Quản Thuốc: Thuốc axit axetic cần được bảo quản đúng cách để đảm bảo hiệu quả và an toàn.\nBetadine Vaginal Douche - Tầm Tay Trẻ Em: Betadine Vaginal Douche cần được bảo quản xa tầm tay của trẻ em.\nAsevictoria Mediplantex - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nDidicera - Tầm Tay Trẻ Em: Giữ thuốc Didicera tránh xa tầm tay trẻ em.\nAspirin MKP 81 - Trạng Thái Xa Tầm Tay Trẻ Em: Thuốc Aspirin MKP 81 cần được bảo quản xa tầm tay trẻ em.\nAlpha-Kiisin - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nContractubex - Tầm Tay Trẻ Em: Tầm tay trẻ em là vị trí cần tránh khi bảo quản Contractubex.\nAxit Glutamic - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nAzithromycin DHG - Giữ Thuốc Xa Tầm Tay Trẻ Nhỏ: Thuốc cần được giữ xa tầm tay trẻ nhỏ nhằm tránh bé sử dụng sai cách, sai liều gây nguy hiểm.\nCarbogast - Tầm Tay Trẻ Em: Thuốc Carbogast cần tránh xa tầm tay trẻ em.\nAcyclovir Stella Cream - Tầm Tay Trẻ Em: Thuốc Acyclovir Stella Cream cần được giữ xa tầm tay trẻ em.\nClarityne - Tầm Tay Trẻ Em: Thuốc Clarityne cần được bảo quản tránh xa tầm tay của trẻ em.\nBioflora - Tầm Tay Trẻ Em: Flora cần được bảo quản xa tầm tay trẻ em.\nCilzec - Tầm Tay Trẻ Em: Giữ thuốc Cilzec xa tầm tay trẻ em.\nBảo Thanh Hoa Linh - Tầm Tay Trẻ Em: Thuốc cần được đặt xa tầm tay trẻ em để đảm bảo an toàn.\nAmpicillin Vidiphar - Tầm Tay Trẻ Em: Thuốc Ampicillin Vidiphar cần được đặt xa tầm tay trẻ em.\nBilgrel - Giữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nColdi B - Tầm Với Trẻ Em: Coldi B cần được bảo quản tránh xa tầm với của trẻ em.\nCenditan - Xa Tầm Tay Của Trẻ Em: Thuốc Cenditan nên được lưu trữ xa tầm tay của trẻ em để đảm bảo an toàn.\nThuốc Bisoloc (Bisoprolol) - Tầm Tay Trẻ Em: Thuốc Bisoloc cần được giữ xa tầm tay trẻ em.\nBiosubtyl - Phụ Nữ Mang Thai Hoặc Cho Con Bú: Biosubtyl có thể được dùng bởi phụ nữ mang thai hoặc cho con bú.\nCơ Đùi - Dây Thần Kinh Tọa: Tiêm vào cơ đùi cần tránh tổn thương dây thần kinh tọa.']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Biosubtyl cần được bảo quản ở nơi khô ráo, thoáng mát, tránh xa tầm tay của trẻ em và vật nuôi. Điều này giúp đảm bảo an toàn và hiệu quả sử dụng của thuốc.
+### Cách bảo quản Biosubtyl
+- **Nơi khô ráo, thoáng mát**: Bảo quản thuốc ở nơi khô ráo, thoáng mát để tránh ẩm và nhiệt độ cao.
+- **Tránh ánh sáng**: Bảo quản thuốc tránh xa ánh sáng trực tiếp để duy trì chất lượng.
+- **Xa tầm tay trẻ em và vật nuôi**: Đặt thuốc ở nơi trẻ em và vật nuôi không thể chạm tới để tránh sử dụng sai cách hoặc gây nguy hiểm.
+### Ví dụ về vị trí thích hợp
+Bạn có thể bảo quản Biosubtyl ở một kệ tủ thuốc cao, nơi trẻ em không thể với tới, hoặc trong một hộp kín đáo được khóa lại.
+### Lưu ý
+- Đảm bảo rằng thuốc được bảo quản đúng cách theo hướng dẫn trên bao bì.
+- Luôn kiểm tra hạn sử dụng của thuốc và không sử dụng thuốc đã quá hạn.
+### Tham khảo
+- **Lưu ý**: Để xa tầm tay trẻ em và đọc kỹ hướng dẫn sử dụng trước khi dùng.
+### Tham chiếu
+- [1] men-vi-sinh-biosubtyl-va-nhung-dieu-can-luu-y.txt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Để xa men vi sinh Biosubtyl khỏi tầm với của trẻ nhỏ và động vật để đảm bảo an toàn.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5204202161363642</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.6301050540090911</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>["Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nCơ Dụng Sống: Cơ dựng sống là một cơ nằm ở mặt sau của thân, nằm ở vùng lưng, chạy dọc từ xương chẩm đến xương cùng và nằm ở lớp giữa trong các lớp cơ lưng.&lt;SEP&gt;Cơ dựng sống có vai trò quan trọng trong sự vận động của con người.\nĐau Quanh Móng: Đau quanh móng.\nThuốc Giảm Đau: Thuốc Giảm Đau là một loại thuốc đa năng được sử dụng rộng rãi trong nhiều tình huống y tế khác nhau. Nó được sử dụng để điều trị các triệu chứng đau ngắn hạn như đau tai, nhiễm trùng đường tiết niệu, đau bụng liên quan đến bệnh Crohn, đau hậu môn, và triệu chứng khó chịu của viêm tai giữa. Ngoài ra, Thuốc Giảm Đau cũng được sử dụng để kiểm soát các triệu chứng đau mãn tính như bệnh Gout, thoái hóa khớp háng, đau khớp vai, và thoái hóa khớp ngón cái. Loại thuốc này còn được dùng trong các trường hợp đau nặng như áp xe má và trong quá trình chỉnh hình xương bị gãy, dị dạng Chiari, và giảm đau sau phẫu thuật hoặc chấn thương. \n\nThuốc Giảm Đau có tác dụng chống viêm, hạ sốt, và giãn cơ khi cần thiết. Nó có thể tồn tại dưới dạng uống, bôi ngoài da, hoặc đôi khi tiêm corticosteroid nội khớp khi quá đau và không phải nguyên nhân do nhiễm khuẩn. Thuốc này cũng được sử dụng để điều trị các bệnh lý ở cơ dựng sống và giảm các triệu chứng đau ở cơ dựng cột sống. Việc sử dụng Thuốc Giảm Đau cần tuân thủ chặt chẽ hướng dẫn của bác sĩ để đảm bảo hiệu quả và an toàn tối ưu.\n\nThuốc Giảm Đau còn được sử dụng để điều trị viêm khớp dạng thấp và hẹp khớp háng. Đối với trẻ em, thuốc này thường được kê toa trong vài ngày sau phẫu thuật. Tuy nhiên, cần lưu ý rằng việc sử dụng Thuốc Giảm Đau không đúng cách có thể gây hại cho dạ dày và có thể che lấp tình trạng bệnh, làm chậm trễ việc điều trị. Thuốc này cũng có thể gây độc cho gan nếu sử dụng lâu dài và chỉ giúp kéo dài sự thoải mái mà không giải quyết nguyên nhân gốc rễ của đau.\n\nThuốc Giảm Đau như acetaminophen (Tylenol) có thể làm giảm đau nhưng không có tác dụng kháng viêm như NSAID. Thuốc giảm đau như Paracetamol được sử dụng để giảm đau. Thuốc giảm đau Advil cũng được sử dụng để giảm đau. Thuốc giảm đau là loại thuốc cần chú ý khi sử dụng kết hợp với Aspegic và không được chỉ định trong giai đoạn ghép nối tắt động mạch vành.\n\nThuốc Giảm Đau cũng được sử dụng để điều trị viêm amiđan, lạc nội mạc tử cung, và kiểm soát triệu chứng đau bụng. Nó cũng giúp giảm sự khó chịu do các vết loét và sỏi tiết niệu. Một số loại thuốc giảm đau có thể gây ra táo bón, suy gan cấp nếu dùng quá liều, và thậm chí gây ra nghe kém hoặc nổi mề đay kéo dài.&lt;SEP&gt;Thuốc giảm đau là loại thuốc được sử dụng để giảm đau.&lt;SEP&gt;Thuốc giảm đau được sử dụng để giảm đau và sưng.&lt;SEP&gt;Thuốc giảm đau giúp giảm cảm giác đau.&lt;SEP&gt;Thuốc giảm đau như paracetamol hoặc ibuprofen được sử dụng để giảm đau trong thời gian chờ phục hồi.\nMật Kém: Mật kém là triệu chứng được Cholapan hỗ trợ điều trị.\nGiảm Đau: Giảm Đau là mục đích điều trị và sử dụng phổ biến của nhiều loại thuốc, phương pháp điều trị, và thành phần tự nhiên khác nhau nhằm giúp giảm cảm giác đau. Giảm Đau là một trong những công dụng của nhiều loại tinh dầu như tinh dầu hoa hồng, tinh dầu húng quế, và tinh dầu quýt. Tinh dầu húng quế có khả năng giảm đau và được sử dụng trong các phương pháp điều trị theo y học cổ truyền. Tinh dầu còn được biết đến với khả năng giảm đau nhờ vào các hoạt chất tự nhiên của chúng.\n\nCác loại thuốc như A.t Ibuprofen Syrup, Agietoxib bcm, Etoricoxib, Aphaxan Armephaco, Aspirin Vidipha, dầu Ba đậu, Bạch chỉ, Menthol, Bạch đồng nữ, Men Myroxin, cao chiết lạnh của Bạch tật lê, và Bạch thược đều có tác dụng giảm đau. Đặc biệt, Etoricoxib được sử dụng để điều trị các bệnh lý như thoái hóa khớp, viêm khớp dạng thấp, và viêm cột sống dính khớp. Menthol góp phần vào quá trình giảm đau bằng cách gây ra cảm giác mát và tê tại chỗ, giúp giảm đau dây thần kinh. Ngoài việc sử dụng thuốc, giảm đau còn là tác dụng của một số thực vật và thành phần tự nhiên khác như cà gai leo, cam thảo nam, dầu trung tính Cảo Bản, cây Bần, thành phần bìm bịp, Na rừng, cây Nàng nàng, cây Nổ gai, tinh dầu sả, cây Ráy, vỏ cây Sảng, thân và lá Cánh kiến trắng, tỏi trời, và chìa vôi. Children's Tylenol và chùm ruột cũng có tác dụng giảm đau nhờ chứa nhiều hợp chất chống oxy hóa.\n\nThuốc Cofidec cũng được biết đến với tác dụng giảm đau, đặc biệt là trong việc điều trị viêm xương khớp. Củ dòm và cây Dây gân cũng được biết đến với tác dụng giảm đau. Tần giao cũng giúp giảm cảm giác đau. Giảm Đau cũng là tác dụng của corticosteroid, chiết xuất củ Chóc, và củ nén khi sử dụng trong bài thuốc. Tác dụng giảm đau có tính chất thuộc trung ương, liên quan đến aconitin và hệ thống catecholamin trung ương. Giảm Đau là tác dụng của Đại tướng quân và dền gai trong điều trị bệnh. Các chất chiết xuất từ rễ, lá, hoa đậu biếc đã được báo cáo chứng minh các hoạt động giảm đau. Dầu giun có tác dụng giảm đau. Giảm đau là quá trình sinh học được hỗ trợ bởi một số thuốc chống viêm. Giảm Đau là mục tiêu của điều trị khi không thể xác định được nguyên nhân gây đau.\n\nĐịa cốt bì và Địa liền cũng có tác dụng giảm đau, đặc biệt là đối với các bệnh lý nội tạng. Viên Bạch Địa Can có tác dụng giảm đau. Đơn lá đỏ giúp giảm cảm giác đau. Giảm Đau là mục tiêu đầu tiên của vật lý trị liệu sau chấn thương và vật lý trị liệu nói chung. Giảm Đau cũng là phương pháp điều trị sử dụng Hắc sâm. Giảm Đau là tác dụng của hoa đậu biếc. Giảm Đau là triệu chứng được điều trị bằng hoạt chất từ cây này. Giảm Đau là phương pháp điều trị bằng rễ hoa nhài và rễ nhài. Giảm Đau cũng là phương pháp điều trị bằng hoa quỳnh. Giảm Đau còn được áp dụng trong việc điều trị gù cột sống để giảm triệu chứng đau. Hoàng nàn giúp giảm đau và là công dụng của nó. Húng quế được sử dụng để giảm đau. Giảm Đau là mục tiêu của một số loại thuốc, trong đó chiết xuất Hương thảo có tiềm năng kiểm soát cơn đau. Giảm Đau là một trong những tác dụng của hương phụ. Giảm Đau là tác dụng của Huyết lình khi sử dụng ngoài da. Giảm Đau là tác dụng của cây khế khi sử dụng làm thuốc. Khổ qua rừng giúp giảm đau trong bệnh nhân bị thoái hóa khớp gối. Giảm Đau là tác dụng của các thành phần trong Khương hoạt. Giảm Đau là tác dụng của lá lốt khi dùng ngậm hoặc uống.\n\nNgoài ra, giảm đau cũng là công dụng của trầm hương trong đông y, giúp giảm các triệu chứng đau. Giảm đau cũng là tác dụng của lá cây xá xị, tía tô, tô mộc, và trà tiên.&lt;SEP&gt;Giảm đau là một trong những tác dụng của tinh dầu trầm.\nQuá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nHương Thảo: Hương Thảo là tên gọi khác của cây Mần tưới, một loại cây thuốc có nguồn gốc từ vùng Địa Trung Hải. Loài cây này được trồng rộng rãi trên khắp thế giới và được sử dụng như một loại gia vị cũng như chất bảo quản thực phẩm. Hương Thảo là một loại cây thảo mộc chứa tinh dầu và tanin, thường được sử dụng làm dược liệu. \n\nHương Thảo có vị chát, mùi thơm nồng và tính ấm nóng. Nó có nhiều tác dụng tích cực, bao gồm bổ dưỡng, tăng cường sinh lực, hoạt huyết, tẩy uế trọc, kích thích hệ tiêu hóa, lợi mật, lợi tiểu, nhuận trường, chống viêm sưng, chống oxy hóa, kích thích tuần hoàn máu lên não, giúp tăng cường trí nhớ và sự tập trung, giúp chống rụng tóc và mau mọc tóc, khử trùng đường hô hấp và làm long đàm. \n\nNgoài ra, Hương Thảo còn được sử dụng để chữa các vấn đề về sức khỏe như căng thẳng thần kinh, tiêu hóa kém, giảm nhức đầu, tăng tuần hoàn máu, tăng huyết áp, giúp tăng tiết mật và lợi tiểu. Nó cũng thường được sử dụng trong các bài thuốc kết hợp với Kê huyết đằng. \n\nHương Thảo là một loại tinh dầu tự nhiên, thường không độc với người dùng. Nó cũng được sử dụng trong hỗn hợp dầu nền và tinh dầu thực vật để massage da đầu và tóc.&lt;SEP&gt;Hương thảo (tên khoa học Rosmarinus officinalis) là thực vật thuộc họ Hoa môi (Lamiaceae).&lt;SEP&gt;Hương thảo là cây được sử dụng để chiết xuất tinh dầu.&lt;SEP&gt;Hương thảo là thực vật giá trị trong nhiều khía cạnh cuộc sống, được đánh giá tích cực bởi kinh nghiệm dân gian và minh chứng khoa học.\nĂn Uống Khó Tiêu: Ăn uống khó tiêu là triệu chứng tiêu hóa được cải thiện bởi Cholapan.&lt;SEP&gt;Ăn uống khó tiêu là triệu chứng tiêu hóa được điều trị bằng Cholapan.&lt;SEP&gt;Ăn uống khó tiêu là tác dụng phụ khi sử dụng khổ qua.&lt;SEP&gt;Ăn uống khó tiêu là triệu chứng tiêu hóa.\nBác Sĩ Chuyên Môn: Bác sĩ chuyên môn là người cung cấp ý kiến và chỉ định về việc sử dụng thổ phục linh.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nCơn Đau Sau Khi Tập Thể Dục: Sự xuất hiện của cơn đau sau khi tập thể dục.\nKiểm Soát Stress: Kiểm soát stress, căng thẳng, lo lắng giúp phòng tránh bệnh viêm đại tràng mãn tính.&lt;SEP&gt;Thuốc giúp kiểm soát lo lắng, stress hoặc chống trầm cảm.&lt;SEP&gt;Kiểm soát stress là yếu tố quan trọng để phòng ngừa tái phát bệnh lý thoát vị đĩa đệm cột sống thắt lưng.\nTinh Bột Glycolat Natri: Tinh bột glycolat natri là tá dược trong Cholapan.\nGiảm Đau Thần Kinh: Giảm đau thần kinh là phương pháp điều trị các tình trạng như đau thần kinh tọa, neuropathy tiểu đường, đau dây thần kinh ngoại vi.\nNgười Dùng Thuốc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nĐau Thần Kinh Tọa: Đau thần kinh tọa là một triệu chứng đau do tổn thương dây thần kinh tọa, thường gặp ở người từ 30 – 60 tuổi. Triệu chứng này gây ra những cơn đau ảnh hưởng nghiêm trọng đến sinh hoạt hàng ngày và thường xuất hiện dưới dạng hội chứng chèn ép dây thần kinh. Nguyên nhân chính dẫn đến tình trạng này là do thoát vị đĩa đệm cột sống, khiến bệnh nhân cảm thấy đau thắt lưng lan xuống chân, đau cố định, dữ dội, và tăng thêm khi xoay trở. \n\nNgoài ra, đau thần kinh tọa cũng được biết đến như một tình trạng bệnh lý gây ra bởi sự chèn ép dây thần kinh. Các phương pháp điều trị bao gồm việc sử dụng Bạch Hổ Hoạt Lạc Cao để hỗ trợ điều trị, cùng với việc điều trị bằng bài thuốc sắc từ lá muồng trâu. Bệnh này cũng có thể được điều trị bằng các bài thuốc thảo dược khác. Một số nguyên nhân khác gây ra triệu chứng này là do thoái hóa cột sống, được hỗ trợ điều trị bằng Cốt Thoái Vương. \n\nĐau thần kinh tọa còn được điều trị bằng các sản phẩm khác như 3B Medi, Amitriptylin, và Betex. Mỗi phương pháp điều trị đều nhằm mục đích giảm đau và cải thiện chất lượng cuộc sống của bệnh nhân.&lt;SEP&gt;Đau thần kinh tọa ảnh hưởng rất nhiều đến chất lượng cuộc sống của mỗi người.&lt;SEP&gt;Đau thần kinh tọa là căn bệnh gây ra bởi các vấn đề về cột sống, gây đau từ thắt lưng xuống chân.&lt;SEP&gt;Đau thần kinh tọa là triệu chứng ảnh hưởng đến chất lượng cuộc sống.\nQuá Liều Aspirin: Quá liều aspirin là tình trạng có thể xảy ra khi dùng aspirin.\nChứng Giảm Đau: Chứng giảm đau là triệu chứng mà các thảo dược có thể điều trị.&lt;SEP&gt;Chứng giảm đau là tác dụng dược lý của Kê huyết đằng.\nAspirin - Quá Liều Aspirin: Aspirin có thể gây quá liều, gây nhiễm kiềm hoặc acid hô hấp.\nCơ Dụng Sống - Thuốc Giảm Đau: Thuốc giảm đau được sử dụng để điều trị các bệnh lý ở cơ dựng sống.\nTỏi - Ăn Uống Khó Tiêu: Tỏi có tác dụng chữa trị ăn uống khó tiêu.\nGiảm Đau - Hương Thảo: Hương thảo có tiềm năng kiểm soát cơn đau.\nKhổ Qua - Ăn Uống Khó Tiêu: Ăn uống khó tiêu là tác dụng phụ khi sử dụng khổ qua.\nBác Sĩ Chuyên Môn - Thuốc: Bác sĩ chuyên môn tư vấn về chỉ định và liều lượng của thuốc.\nAgi-Calci - Ngừng Sử Dụng Thuốc: Ngừng sử dụng thuốc Agi-Calci và hỏi ý kiến bác sĩ nếu có dấu hiệu bất thường xảy ra.\nKiểm Soát Stress - Thuốc: Thuốc được chỉ định để kiểm soát stress hoặc các vấn đề cảm xúc khác.\nCholapan - Ngừng Sử Dụng Thuốc: Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.\nGiảm Đau Thần Kinh - Đau Thần Kinh Tọa: Giảm đau thần kinh điều trị đau thần kinh tọa.\nCholapan - Ăn Uống Khó Tiêu: Cholapan được chỉ định điều trị triệu chứng ăn uống khó tiêu.&lt;SEP&gt;Cholapan được dùng để điều trị triệu chứng ăn uống khó tiêu.\nGiảm Đau - Thuốc: Thuốc được sử dụng để giảm đau trong điều trị thoái hóa khớp gối.\nCholapan - Mật Kém: Cholapan hỗ trợ điều trị mật kém.\nChứng Giảm Đau - Thảo Dược: Thảo dược có tác dụng chữa trị chứng giảm đau.\nCholapan - Tinh Bột Glycolat Natri: Tinh bột glycolat natri là tá dược trong Cholapan.\nGiảm Đau Thần Kinh - Đau Dây Thần Kinh Ngoại Vi: Giảm đau thần kinh điều trị đau dây thần kinh ngoại vi.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nStress - Thuốc: Thuốc được chỉ định để kiểm soát stress.\nClorpheniramin Maleat - Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nThuốc - Đau: Thuốc được sử dụng để giảm đau trong điều trị trật khuỷu tay.&lt;SEP&gt;Thuốc được sử dụng để kiểm soát cơn đau cho bệnh nhân ung thư phổi.&lt;SEP&gt;Thuốc được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối.\nBệnh Lý - Đau Quanh Móng: Bệnh lý có thể gây đau quanh móng.\nNgừng Sử Dụng Thuốc - Viêm Gân: Nếu có bất cứ dấu hiệu nào của viêm gân (ví dụ sưng đau, viêm) nên ngưng sử dụng thuốc và tham khảo bác sĩ.\nMóng Tay Chân Khỏe Mạnh - Đau Quanh Móng: Đau quanh móng.\nPhenylephrine HCl - Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nNgừng Sử Dụng Thuốc - Tác Dụng Phụ Nghiêm Trọng: Khi có tác dụng phụ nghiêm trọng, có thể cần phải ngừng sử dụng thuốc.\nKích Ứng Tại Chỗ - Ngừng Sử Dụng Thuốc: Khi có kích ứng tại chỗ, có thể cần phải ngừng sử dụng thuốc.\nPhentolamin - Quá Liều Phenylephrine HCl: Phentolamin được dùng trong xử lý tăng huyết áp do quá liều phenylephrine HCl.\nNgười Dùng Thuốc - Thắc Mắc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nGiải Đáp - Người Dùng Thuốc: Giải đáp cung cấp thông tin phản hồi cho người dùng thuốc."]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Khi đau nhiều, liều dùng Cholapan có thể được điều chỉnh theo hướng dẫn của nhà sản xuất. Theo đó, trong trường hợp đau nhiều, người dùng có thể uống liều gấp đôi so với liều thông thường. Liều dùng cụ thể như sau:
+- Người lớn: 4 viên/lần (2 viên/lần theo liều thông thường)
+- Trẻ em từ 5 tuổi đến dưới 15 tuổi: 2 viên/lần (1 viên/lần theo liều thông thường)
+Nên nhớ rằng, việc tăng liều cần được thực hiện theo hướng dẫn của bác sĩ hoặc dược sĩ. Đồng thời, cần theo dõi chặt chẽ để đảm bảo không có tác dụng phụ không mong muốn.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Có thể uống liều gấp đôi (4 viên/lần, ngày 2 lần).</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7955192894100728</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2301298223525182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>["Chất Ức Hẹp CYP3A4: Chất ức chế CYP3A4 là loại thuốc được đề cập.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nCYP 3A4: CYP 3A4 là enzym có hoạt động bị ảnh hưởng bởi sự tương tác giữa Cisaprid và các thuốc ức chế nó.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nTránh Tầm Tay Trẻ Em: Tránh thuốc xa tầm tay trẻ em là quy tắc bảo quản.&lt;SEP&gt;Tránh tầm tay trẻ em là quy tắc bảo quản Cisaprid.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Cisaprid: Thuốc cisaprid là thuốc được sử dụng điều trị các triệu chứng liên quan đến đường tiêu hóa.\nTrẻ: Trẻ là đối tượng dễ mắc bệnh cúm do có hệ miễn dịch chưa hoàn thiện.&lt;SEP&gt;Trẻ là đối tượng sử dụng thuốc clotrimazole.\nQuy Đổi Liều: Quy đổi liều từ cân nặng và tuổi của trẻ em.\nBạch Cầu Cấp Trẻ Em: Bạch cầu cấp trẻ em là bệnh lý ác tính ở trẻ em, đặc trưng bởi tăng sinh các tế bào non trong tủy xương.&lt;SEP&gt;Bạch cầu cấp trẻ em là bệnh lý ác tính phổ biến nhất ở lứa tuổi con nít.\nTác Dụng Phụ Thuốc: Tác dụng phụ của thuốc là vấn đề chính trong quá trình điều trị bệnh bạch cầu cấp trẻ em.&lt;SEP&gt;Tác dụng phụ của thuốc.&lt;SEP&gt;Tác dụng phụ của thuốc được đánh giá để loại trừ nguyên nhân gây ra triệu chứng tương tự như run vô căn.&lt;SEP&gt;Tác dụng phụ của thuốc có thể gây bệnh tiêu chảy.\nTrẻ Em Dưới 24 Tháng Tuổi: Trẻ em dưới 24 tháng tuổi là đối tượng cần thận trọng khi sử dụng thuốc.\nHậu Quả Khôn Lường: Hậu quả khôn lường có thể xảy ra nếu trẻ em ăn phải thuốc.\nĐối Tượng Dùng Thuốc Là Trẻ Em: Đối tượng dùng thuốc là trẻ em là nhóm đối tượng cần theo dõi kỹ khi sử dụng thuốc chứa corticosteroid.\nTiêu Chảy - Trẻ Em: Trẻ em có nguy cơ mắc bệnh tiêu chảy.&lt;SEP&gt;Tiêu chảy có thể là tác dụng phụ của việc mẹ dùng Cefaclor khi cho con bú.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nNgứa - Trẻ Em: Ngứa ở trẻ em được điều trị bằng thuốc.&lt;SEP&gt;Trẻ em bị ngứa được điều trị bằng thuốc.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nThuốc - Trẻ Em: Trẻ em không được phép sử dụng thuốc này.&lt;SEP&gt;Thuốc cần được giữ tránh xa tầm tay của trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nBạch Cầu Cấp Trẻ Em - Tác Dụng Phụ Thuốc: Bệnh bạch cầu cấp trẻ em có tác dụng phụ của thuốc.\nCam Thảo - Trẻ Em: Trẻ em được khuyến khích tránh hoàn toàn các sản phẩm cam thảo có chứa glycyrrhizin.\nHậu Quả Khôn Lường - Trẻ Em: Trẻ em ăn phải thuốc có thể dẫn đến hậu quả khôn lường.\nCelecoxib - Trẻ Em: Trẻ em không được chỉ định dùng Celecoxib.\nSữa Mẹ - Thuốc: Cần chú ý những thuốc bà mẹ đang sử dụng có tiết qua sữa gây ảnh hưởng tới em bé hay không.\nTrẻ Em - Viêm Tai Giữa: Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa.\nAspirin - Trẻ Nhỏ: Aspirin có thể gây tác dụng phụ ở trẻ nhỏ.\nDHEA - Trẻ Em: DHEA có thể gây ra nguy cơ do liều lượng sử dụng càng cao ở trẻ em.&lt;SEP&gt;Bổ sung DHEA với liều lượng lớn ở trẻ em có thể gây ra nhiều tác dụng phụ nguy hiểm.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nA.t Ibuprofen Syrup - Trẻ Em: Trẻ em là đối tượng bệnh nhân cần tham khảo ý kiến bác sĩ khi triệu chứng kéo dài.\nLiều Lượng - Vị Thuốc: Hiệu quả và an toàn của việc sử dụng vị thuốc phụ thuộc vào liều lượng.\nPregabalin - Trẻ Em: Trẻ em cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả.\nBạch Cầu Cấp - Tác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.\nHuyết Rồng - Trẻ Em: Trẻ em cần cẩn trọng khi sử dụng huyết rồng.&lt;SEP&gt;Trẻ em cần thận trọng khi sử dụng huyết rồng.\nHo Gà - Thuốc Ho Thảo Dược: Thuốc ho thảo dược an toàn cho trẻ được khuyến nghị sử dụng.\nDexamethasone - Trẻ Em: Dexamethasone cần được bảo quản tránh xa tầm tay của trẻ em.\nCúc Hoa Trắng - Trẻ Em: Trẻ em cần cẩn trọng khi dùng dược liệu.\nBisacodyl - Trẻ Em: Bisacodyl có thể gây ảnh hưởng đến trẻ em khi sử dụng.\nHoắc Hương - Trẻ Em: Trẻ em không nên dùng hoắc hương.\nBệnh Cúm - Trẻ Em: Trẻ em có nguy cơ cao mắc phải các biến chứng do bệnh cúm gây ra.\nRau Mùi Tây - Trẻ Em: Trẻ em không nên sử dụng rau mùi tây.\nBixicam - Trẻ Em: Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam.&lt;SEP&gt;Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\nSuy Gan - Thuốc Cisaprid: Thuốc cisaprid cần giảm liều lượng khi bệnh nhân mắc suy gan.\nAllopurinol - Trẻ Em: Thuốc Allopurinol cần được bảo quản tránh xa tầm tay trẻ em.\nCefoxitin - Trẻ Em: Liều dùng Cefoxitin cần điều chỉnh dựa trên cân nặng và độ tuổi của trẻ em.\nDược Liệu - Trẻ Em: Trẻ em cần cẩn trọng khi dùng dược liệu.\nAmbroxol - Trẻ Em: Ambroxol được chỉ định cho trẻ em từ 5-10 tuổi với liều cụ thể.&lt;SEP&gt;Đối tượng là trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol.\nAcetazolamid - Trẻ Em: Thuốc Acetazolamid cần được bảo quản tránh xa tầm tay của trẻ em.\nAmeflu DAYTIME - Trẻ Em: Thuốc Ameflu DAYTIME cần được tránh xa tầm tay của trẻ em.\nDiurefar - Trẻ Em: Diurefar cần thận trọng khi sử dụng ở trẻ em, đặc biệt là khi dùng trong thời gian dài.\nClotrimazole - Trẻ Em: Trẻ em cần tránh tiếp xúc với Clotrimazole.\nBofit F - Trẻ Em: Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em.\nDiamicron - Trẻ Em: Trẻ em cần tránh tiếp xúc với thuốc Diamicron.\nAspilets EC - Trẻ Em: Tránh sử dụng acid acetylsalicylic cho trẻ sốt do virus.\nBiviantac - Trẻ Em: Trẻ em là đối tượng sử dụng Biviantac.&lt;SEP&gt;Biviantac có thể gây tác dụng phụ ở trẻ em.\nTinh Dầu Hoàng Đàn - Trẻ Em: Trẻ em nhỏ tuổi cần thận trọng khi sử dụng tinh dầu hoàng đàn.\nAzithromycin - Trẻ Em: Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn.\nCarbotrim - Trẻ Em: Trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh.\nCoversyl Plus - Trẻ Em: Trẻ em là đối tượng không nên sử dụng Coversyl Plus.\nAgifuros 40 mg - Trẻ Em: Agifuros 40 mg có thể gây tác dụng phụ ở trẻ em.\nClaminat - Trẻ Em: Trẻ em là đối tượng sử dụng Claminat.\nMethylprednisolone (Depo-Medrol) - Trẻ Em: Trẻ em có thể nhạy cảm hơn với sự ức chế tuyến thượng thận khi điều trị bằng thuốc bôi.\nAppeton Lysine Syrup - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm với của trẻ em.\nAtorhasan - Trẻ Em: Trẻ em cần tránh xa Atorhasan để đảm bảo an toàn.\nNhụy Hoa Nghệ Tây - Trẻ Em: Tuỳ theo tình trạng bệnh lý của trẻ, cần có sự thăm khám của bác sĩ để cân nhắc sử dụng nhụy hoa nghệ tây.\nBetex - Trẻ Em: Betex cần được bảo quản xa tầm tay trẻ em để tránh nguy cơ.\nBeprosone Ointment - Trẻ Em: Beprosone Ointment cần tránh xa tầm tay của trẻ em.\nBatigan - Trẻ Em: Batigan cần được bảo quản xa tầm tay của trẻ em.\nAntanazol - Trẻ Em: Thuốc Antanazol cần được bảo quản xa tầm tay trẻ em.\nAtussin - Trẻ Em: Thuốc Atussin cần được bảo quản tránh xa tầm tay trẻ em.\nBetahistine - Trẻ Em: Không nên dùng Betahistine cho trẻ em dưới 18 tuổi.\nAmlodipin Domesco - Trẻ Em: Thuốc Amlodipin Domesco cần được bảo quản tránh xa tầm tay trẻ em.\nAsevictoria Mediplantex - Trẻ Em: Trẻ em cần tránh tiếp xúc với Asevictoria Mediplantex.\nAmlor 5 Pfizer - Trẻ Em: Thuốc Amlor 5 Pfizer cần tránh tiếp xúc với trẻ em.\nTinh Dầu Quýt - Trẻ Em: Tinh dầu quýt cần được tránh tiếp xúc với trẻ em.\nAclasta - Trẻ Em: Aclasta không khuyến cáo dùng cho trẻ em và thiếu niên dưới 18 tuổi.\nBabi B.O.N - Trẻ Em: Thuốc Babi B.O.N cần được bảo quản tránh xa tầm tay của trẻ em.\nArthrorein Pharmanel - Trẻ Em: Thuốc Arthrorein Pharmanel cần được giữ tránh xa tầm với của trẻ em.\nMật Nhân - Trẻ Em: Trẻ em không được dùng Mật nhân.\nAvodart - Trẻ Em: Trẻ em không được sử dụng Avodart.\nDeferasirox (Exjade) - Trẻ Em: Trẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade).\nDentanalgi - Trẻ Em: Dentanalgi cần được đặt ở nơi tránh xa tầm tay của trẻ em.\nBạch Đậu Khấu - Trẻ Em: Bạch đậu khấu được sử dụng để chữa trớ sữa ở trẻ em.\nCholapan - Trẻ Em: Cholapan cần tránh sử dụng cho trẻ em.\nRươi - Trẻ Em: Trẻ em hệ tiêu hóa chưa hoàn chỉnh không nên đụng tới món rươi.\nBenzalkonium Chloride - Trẻ Em: Thuốc Benzalkonium Chloride cần được bảo quản tránh xa tầm tay của trẻ em.\nAphaxan Armephaco - Trẻ Em: Thuốc Aphaxan Armephaco cần được bảo quản xa tầm tay trẻ em.\nSởi - Trẻ Em: Trẻ em bị sởi là bệnh được điều trị bằng Canh châu.\nDeferasirox - Trẻ Em: Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên.\nTrẻ Em - Điều Trị: Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\nAlphaDHG - Trẻ Em: Trẻ em cần đặc biệt chú ý khi dùng thuốc AlphaDHG.\nAlchysin 8400 - Trẻ Em: Thuốc Alchysin 8400 cần được báo với bác sĩ trước khi sử dụng trên trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nAxit Glutamic - Trẻ Em: Axit glutamic không nên sử dụng cho trẻ em.\nBệnh Cúm Mùa - Trẻ Em: Bệnh cúm mùa có thể gây ảnh hưởng đến trẻ em.\nAlputine - Trẻ Em: Sử dụng Alputine cho trẻ em cần hết sức thận trọng.\nCravit - Trẻ Em: Để thuốc nhỏ mắt Cravit tránh xa tầm tay của trẻ em.\nA.t Zinc - Trẻ Em: Thuốc A.t Zinc có thể gây nguy hiểm cho trẻ em nếu bị tiếp xúc.\nHóc Xương - Trẻ Em: Trẻ em có nguy cơ cao bị hóc xương.\nBerberin Mộc Hương - Trẻ Em: Thuốc Berberin Mộc Hương cần được bảo quản ở nơi trẻ em không tự lấy được.\nAtorvastatin - Chất Ức Hẹp CYP3A4: Hoạt chất Atorvastatin có thể tương tác với chất ức chế CYP3A4.\nBenzyl Benzoate - Trẻ Em: Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ.\nBiginol - Trẻ Em: Thuốc Biginol cần được giữ xa tầm tay của trẻ em để tránh sử dụng sai cách, sai liều.\nHương Bài - Trẻ Em: Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính.\nAdrenoxyl - Trẻ Em: Thuốc Adrenoxyl cần tránh xa tầm tay trẻ em.\nBổ Huyết Ích Não - Trẻ Em: Trẻ em dưới 12 tuổi cần sử dụng thuốc Bổ Huyết Ích Não một cách cẩn thận.&lt;SEP&gt;Trẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\nBluemint - Trẻ Em: Thận trọng khi dùng Bluemint với trẻ em.&lt;SEP&gt;Bluemint không nên dùng cho trẻ em dưới 6 tuổi và cần thận trọng khi dùng cho trẻ em trên 6 tuổi.\nAcyclovir Stella Cream - Trẻ Em: Acyclovir Stella Cream có thể dùng cho trẻ em một cách an toàn.\nDifferin - Trẻ Em: Thuốc Differin cần được bảo quản xa tầm tay trẻ em.\nCalcium Stada Vitamin D - Trẻ Em: Liều dùng Calcium Stada Vitamin D cho trẻ em là 1/2 liều so với người lớn, hoặc 1 – 2 muỗng cà phê chia ra 3 – 4 lần mỗi ngày.&lt;SEP&gt;Trẻ em cần thận trọng khi sử dụng Calcium Stada Vitamin D.\nGãy Xương Cành Tươi - Trẻ Em: Trẻ em là đối tượng dễ bị gãy xương cành tươi.\nSưng Mặt - Trẻ Em: Trẻ em bị sưng mặt là triệu chứng được điều trị bằng Canh châu.\nBệnh Cúm A/H1N1 - Trẻ Em: Bệnh cúm A/H1N1 có thể gây ảnh hưởng đến trẻ em.\nAlpha-Chymotrypsin 4200 IU - Trẻ Em: Lưu ý khi dùng thuốc Alpha-Chymotrypsin 4200 IU cho trẻ em.\nTrẻ Em - Âm Thổi Ở Tim: Âm thổi ở tim thường gặp ở trẻ em.\nCollydexa - Trẻ Em: Collydexa cần lưu ý đặc biệt khi sử dụng đối với trẻ em.\nDanapha Trihex - Trẻ Em: Trẻ em dễ nhạy cảm với các dụng không mong muốn của thuốc.\nAgimfast 60 - Trẻ Em: Tính hiệu quả và độ an toàn của thuốc ở trẻ em dưới 6 tháng tuổi chưa xác định được.\nThiếu Máu Thiếu Sắt - Trẻ Em: Trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt.\nNổi Ban - Trẻ Em: Nổi ban có thể là tác dụng phụ của việc mẹ dùng Cefaclor khi cho con bú.\nChildren's Tylenol - Trẻ Em: Children's Tylenol được chỉ định cho trẻ em dưới 12 tuổi.\nChống Nôn - Trẻ Em: Chống nôn được sử dụng để điều trị nôn ở trẻ em.&lt;SEP&gt;Trẻ em bị nôn và buồn nôn được điều trị bằng phương pháp chống nôn.\nA.T.P - Trẻ Em: Bài viết cảnh báo bố mẹ để thuốc A.T.P tránh xa tầm tay trẻ em.\nAlphachymotrypsin 4200 Mebiphar - Trẻ Em: Thuốc Alphachymotrypsin 4200 Mebiphar cần được bảo quản tránh xa tầm tay của trẻ em.\nMen Vi Sinh Antibio - Trẻ Em: Khi sử dụng men vi sinh Antibio cho trẻ em, cần có sự đồng ý của bác sĩ.\nAn Thảo - Trẻ Em: Thuốc An Thảo cần được bảo quản xa tầm tay trẻ em.\nAceclofenac STADA - Trẻ Em: Aceclofenac STADA cần được bảo quản tránh xa tầm tay của trẻ em.\nDung DỊch Nhỏ Tai - Trẻ Em: Dung dịch nhỏ tai không nên sử dụng cho trẻ em dưới 2 tuổi.\nAntibio - Trẻ Em: Antibio được sử dụng cho trẻ em với liều lượng khác nhau so với người lớn.\nAspartam Pharmedic - Trẻ Em: Thuốc Aspartam Pharmedic cần được bảo quản xa tầm tay trẻ em.\nRượu Móc - Trẻ Em: Rượu móc cần được sử dụng thận trọng đối với trẻ em.\nGlargine - Trẻ Em: Glargine được sử dụng ở trẻ em từ 6 tuổi trở lên mắc đái tháo đường type 1.\nNấm Lim Xanh Rừng - Trẻ Em: Trẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn.\nBảo Thanh Hoa Linh Siro - Trẻ Em: Trẻ em sử dụng Bảo Thanh Hoa Linh siro.\nBảo Thanh Hoa Linh Viên Ngậm - Trẻ Em: Trẻ em sử dụng Bảo Thanh Hoa Linh viên ngậm.\nBan Sởi - Trẻ Em: Trẻ em bị ban sởi là triệu chứng được điều trị bằng Canh châu.\nGãy Cành Tươi - Trẻ Em: Trẻ em là đối tượng thường gặp gãy cành tươi.\nThuốc Sắt Cho Bà Bầu Avisure Safoli - Trẻ Em: Sản phẩm thuốc sắt cho bà bầu Avisure Safoli cần tránh xa tầm với của trẻ em.\nTrẻ Em - Tưa: Tưa có thể là tác dụng phụ của việc mẹ dùng Cefaclor khi cho con bú.\nAdkold - Trẻ Em: Adkold có thể dùng cho trẻ em một cách an toàn.\nAndol S - Trẻ Em: Andol S cần tránh xa tầm với của trẻ em.\nSốt Ho Khát Nước - Trẻ Em: Trẻ em bị sốt ho khát nước là triệu chứng được điều trị bằng Canh châu.\nTrẻ Em - U Tế Bào Khổng Lồ Của Xương: U tế bào khổng lồ của xương là dạng u cột sống nguyên phát ở trẻ em.\nTrẻ Em - Tổn Thương Do Vòng Đeo: Tổn thương do trẻ em đeo vòng kim loại vào gốc dương vật.\nThuốc Aspegic - Trẻ Em: Thuốc Aspegic cần được bảo quản tránh xa trẻ em.\nCơ Đùi - Trẻ Em: Tiêm vào cơ đùi là vị trí tiêm cho trẻ em.\nBibonlax Baby - Trẻ Em: Bibonlax Baby được chỉ định dùng cho trẻ em.\nTrẻ Em - Đảo Mắt Ở Trẻ Em: Đảo mắt là triệu chứng thường gặp ở trẻ em.\nTrẻ Em - U Nguyên Bào Xương: U nguyên bào xương là dạng u cột sống nguyên phát ở trẻ em.\nTrẻ Em - U Sụn Xương: U sụn xương là dạng u cột sống nguyên phát ở trẻ em.\nSarcoma Xương - Trẻ Em: Sarcoma xương là dạng u cột sống nguyên phát ở trẻ em.\nSarcoma Ewing - Trẻ Em: Sarcoma Ewing là dạng u cột sống nguyên phát ở trẻ em.\nTrẻ Em - U Hạt Ái Toan: U hạt ái toan là dạng u cột sống nguyên phát ở trẻ em.\nNang Xương Phình Mạch (Aneurysmal Bone Cyst) - Trẻ Em: Nang xương phình mạch (Aneurysmal bone cyst) là dạng u cột sống nguyên phát ở trẻ em.\nChordoma - Trẻ Em: Chordoma là dạng u cột sống nguyên phát ở trẻ em.\nMesenchymal Chondrosarcoma - Trẻ Em: Mesenchymal chondrosarcoma là dạng u cột sống nguyên phát ở trẻ em.\nDị Sản Sợi - Trẻ Em: Dị sản sợi là dạng u cột sống nguyên phát ở trẻ em.\nTrẻ Em - U Sợi: U sợi là dạng u cột sống nguyên phát ở trẻ em.\nSarcoma Mạch Máu - Trẻ Em: Sarcoma mạch máu là dạng u cột sống nguyên phát ở trẻ em.\nTrẻ Em - U Mạch Máu: U mạch máu là dạng u cột sống nguyên phát ở trẻ em.\nTV - Trẻ Em: Tiếp xúc với TV là yếu tố nguy cơ gây ảnh hưởng đến trẻ em.\nTrò Chơi Video - Trẻ Em: Tiếp xúc với trò chơi video là yếu tố nguy cơ gây ảnh hưởng đến trẻ em.\nTrẻ Em - Viên Nén Giải Phóng Kéo Dài Cefaclor: Viên nén giải phóng kéo dài Cefaclor chưa được chứng minh về độ an toàn và hiệu quả cho trẻ em dưới 16 tuổi.\nCisaprid - Tránh Tầm Tay Trẻ Em: Không để thuốc Cisaprid trong tầm tay trẻ em.\nCisaprid - Tắc Cơ Học Đường Tiêu Hóa: Tắc cơ học đường tiêu hóa là tình trạng không nên dùng cisaprid.\nCYP 3A4 - Cisaprid: Cisaprid có thể làm tăng nồng độ cisaprid huyết thanh và kéo dài khoảng QT khi dùng cùng với các thuốc ức chế CYP 3A4.\nChildrens Tylenol - Quy Đổi Liều: Quy đổi liều từ cân nặng và tuổi của trẻ em.\nBeprosone Ointment - Đối Tượng Dùng Thuốc Là Trẻ Em: Đối tượng dùng thuốc là trẻ em cần theo dõi kỹ khi sử dụng Beprosone Ointment.\nThuốc Cisaprid - Thẩm Tách Máu: Thuốc cisaprid không cần tăng liều lượng sau thẩm tách máu.\nThuốc Cisaprid - Trào Ngược Dạ Dày: Thuốc cisaprid được sử dụng để điều trị triệu chứng trào ngược dạ dày.\nChảy Máu Đường Tiêu Hóa - Thuốc Cisaprid: Thuốc cisaprid không nên dùng cho bệnh nhân chảy máu đường tiêu hóa.\nColdi B - Tầm Với Trẻ Em: Coldi B cần được bảo quản tránh xa tầm với của trẻ em.\nThuốc Cisaprid - Táo Bón Mạn Tính: Thuốc cisaprid được sử dụng để điều trị táo bón mạn tính.\nThuốc Cisaprid - Ợ Nóng Về Đêm: Thuốc cisaprid được sử dụng để điều trị ợ nóng về đêm.\nThuốc Cisaprid - Viêm Thực Quản Do Trào Ngược Dạ Dày: Thuốc cisaprid được sử dụng để điều trị viêm thực quản do trào ngược dạ dày.\nRối Loạn Tiêu Hóa Chức Năng - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị rối loạn tiêu hóa chức năng.\nThuốc Cisaprid - Tắc Cơ Học Đường Tiêu Hóa: Thuốc cisaprid không nên dùng cho bệnh nhân tắc cơ học đường tiêu hóa.\nHội Chứng QT Kéo Dài - Thuốc Cisaprid: Thuốc cisaprid có thể gây ra hội chứng QT kéo dài.\nGiảm Trương Lực Cơ Thắt Hậu Môn - Thuốc Cisaprid: Thuốc cisaprid có thể gây ra giảm trương lực cơ thắt hậu môn.\nDạ Dày Giảm Co Bóp - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị dạ dày giảm co bóp.\nGiả Tắc Ruột Kiểu Thần Kinh - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị giả tắc ruột kiểu thần kinh.\nBổ Phế Nam Hà Chỉ Khái Lộ - Trẻ Em Dưới 24 Tháng Tuổi: Trẻ em dưới 24 tháng tuổi cần thận trọng khi sử dụng thuốc Bổ Ph</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thuốc cisapride không nên được sử dụng cho trẻ em dưới một số điều kiện cụ thể. Trẻ em cần được bảo vệ khỏi tiếp xúc với thuốc này vì nó có thể gây ra nhiều tác dụng phụ nguy hiểm. 
+**Lý do không nên dùng cisapride cho trẻ em:**
+- Thuốc cisapride có thể làm tăng nồng độ thuốc trong máu, kéo dài khoảng QT (một đoạn điện tâm đồ), dẫn đến loạn nhịp tim và thậm chí có thể gây tử vong. 
+- Khi dùng cùng với các thuốc ức chế CYP 3A4 (một loại enzym trong gan), cisapride có thể làm tăng đáng kể nồng độ của nó trong máu, gây ra các tác dụng phụ nguy hiểm.
+- Cisapride có thể gây ra các tác dụng phụ trên đường tiêu hóa như tiêu chảy, đau bụng, đầy hơi.
+**Chú ý khi dùng cisapride:**
+- Trẻ sơ sinh và trẻ nhỏ không nên sử dụng thuốc này.
+- Cần theo dõi chặt chẽ trẻ em khi sử dụng thuốc này.
+- Cần theo dõi nồng độ thuốc trong máu khi bắt đầu và khi ngừng điều trị vì thuốc có khoảng điều trị hẹp.
+Do đó, việc sử dụng thuốc cisapride cho trẻ em cần được cân nhắc kỹ lưỡng và chỉ nên được thực hiện dưới sự giám sát chặt chẽ của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tác dụng trên trẻ em chưa được rõ.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6635582010410324</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6658895502352581</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>['20 mg: Liều dùng 20 mg bisoprolol 1 lần/ngày là liều tối đa được khuyến nghị.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nThực Hiện 1 Lần/ Ngày: Thực hiện 1 lần/ngày là phương pháp sử dụng bài thuốc hỗ trợ điều trị da lở ngứa.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\n10 mg: Liều dùng 10 mg bisoprolol 1 lần/ngày được sử dụng để điều trị suy tim mãn ổn định.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\n2,5 mg: Liều dùng 2,5 mg bisoprolol 1 lần/ngày được sử dụng để điều trị huyết áp nhẹ.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nHàng Ngày: Hàng ngày là chu kỳ thời gian trong hướng dẫn sử dụng bài thuốc chữa viêm hang vị dạ dày.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nBệnh Lý Về Da: Bệnh lý về da là các bệnh lý da được điều trị bằng Bisilkon.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBisilkon: Bisilkon là kem bôi ngoài da điều trị một số bệnh lý về da, chứa clotrimazol, betamethason dipropionat và gentamicin.&lt;SEP&gt;Bisilkon được chỉ định trong các bệnh lý da đáp ứng với corticosteroid khi có biến chứng nhiễm trùng do nấm (nhạy cảm với clotrimazol) và vi khuẩn (nhạy cảm với gentamicin).&lt;SEP&gt;Bisilkon là thuốc được sử dụng để điều trị bệnh nhân, nếu không thấy cải thiện sau 3-4 tuần điều trị thì nên ngưng thuốc.&lt;SEP&gt;Bisilkon là thuốc có chứa corticosteroid dùng tại chỗ, có thể gây ức chế trục HPA và các tác dụng phụ khác.&lt;SEP&gt;Bisilkon là thuốc có đối tượng chống chỉ định sử dụng.&lt;SEP&gt;Bisilkon là thuốc cần được bảo quản nơi khô ráo, nhiệt độ không quá 30°C, tránh ánh sáng và không nên nuốt.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nChỉnh Liều Bisoprolol: Chỉnh liều bisoprolol là phương pháp điều chỉnh liều lượng thuốc trong quá trình điều trị.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nBismuth Subcitrat: Bismuth subcitrat là hoạt chất chính trong thuốc Bismuth, thường dùng 240 mg x 2 lần/ ngày hoặc 120 mg x 4 lần/ ngày.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nChỉnh Liều: Chỉnh liều Bisoprolol bắt đầu từ liều thấp và tăng dần liều nếu thuốc được dung nạp tốt.\nHuyền Hồ: Huyền hồ là dược liệu được sử dụng kết hợp với cỏ roi ngựa để điều trị kinh nguyệt không thông, huyết ứ, đau bụng dưới.&lt;SEP&gt;Chiết xuất từ Huyền hồ có tác dụng giảm đau, giảm tỷ lệ tâm thất trái/ trọng lượng cơ thể, ức chế kích hoạt tế bào thần kinh, và chống lại sự di căn của ung thư vú.&lt;SEP&gt;Huyền hồ, còn gọi là Huyền hồ sách, Diên hồ sách, Nguyên hồ, là vị thuốc trong Đông y có tác dụng làm tan máu ứ, cầm máu, giảm đau.&lt;SEP&gt;Huyền hồ là một loại dược liệu, rễ củ hình cầu dẹt không đều, mặt ngoài màu vàng hay vàng nâu, mùi nhẹ, vị đắng.&lt;SEP&gt;Huyền hồ là thành phần trong bài thuốc chữa đau do lạnh.&lt;SEP&gt;Huyền hồ là thành phần trong nhiều bài thuốc chữa đau.\nLiều Dùng: Liều Dùng là hướng dẫn về lượng thuốc cần sử dụng dựa trên nhiều yếu tố như cân nặng, độ tuổi, tình trạng sức khỏe của bệnh nhân, và chức năng thận. Đối với một số loại thuốc cụ thể, liều dùng được quy định rõ ràng cho từng đối tượng. Ví dụ, N-Acetylcystein có liều dùng được quy định cụ thể cho người lớn và trẻ em từ 2-6 tuổi. Thuốc Acyclovir cũng có liều dùng được điều chỉnh dựa trên tình trạng sức khỏe của bệnh nhân. \n\nThuốc Aleucin 500 mg có thể được sử dụng với liều lượng tăng lên tới 6 – 8 viên/ngày, chia làm 2 đến 3 lần sử dụng trong ngày. Đối với Aticef, liều dùng phụ thuộc vào cân nặng của bệnh nhân, mức độ thanh thải creatinin, và tình trạng nhiễm trùng. Các loại thuốc khác như Becozyme có liều dùng là 1 – 2 ống mỗi ngày, trong khi Bisoprolol có liều dùng được điều chỉnh dựa trên tình trạng dung nạp của bệnh nhân. \n\nCây Thuốc Mọi có liều dùng tham khảo là 30 – 60g/ngày (lá và thân), 10 – 12g/ngày (quả và vỏ). Liều dùng của Cenditan là mỗi lần uống 2 viên, mỗi ngày 3 lần. Đối với Children’s Tylenol, liều dùng khuyến cáo là 10 – 15 mg/kg/lần mỗi 4 – 6 giờ nhưng không được quá 75 mg/kg/ngày.\n\nLiều dùng của Cilzec được điều chỉnh tùy thuộc vào tình trạng cụ thể của bệnh nhân. Liều dùng cọ lùn đường uống là 320 mg một lần/ngày hoặc 160 mg hai lần một ngày. Liều dùng Pregabalin được điều chỉnh dựa trên tình trạng sức khỏe và tiến triển bệnh của mỗi bệnh nhân. Liều dùng của Dexacin phụ thuộc vào mức độ nghiêm trọng và đáp ứng trên từng cá thể.\n\nDạng viên hoàn 5g được nhà sản xuất khuyến cáo sử dụng với liều lượng 1-2 gói 5g/lần, dùng 3 lần mỗi 24 giờ. Liều dùng Atocib phụ thuộc vào tình trạng bệnh lý cụ thể của mỗi bệnh nhân. Liều dùng Atorvastatin 10 – 40 mg/ngày, có thể điều chỉnh lên đến 80 mg/ngày. \n\nLiều dùng của thuốc Bolutin cần được điều chỉnh phù hợp với độ tuổi và triệu chứng bệnh của từng bệnh nhân. Liều dùng Brosafe cũng cần được điều chỉnh tương tự. Liều dùng là cách sử dụng thuốc với liều lượng cụ thể và là hướng dẫn về liều lượng sử dụng thuốc. Tóm lại, Liều Dùng là hướng dẫn chi tiết về lượng thuốc cần sử dụng dựa trên nhiều yếu tố khác nhau để đảm bảo hiệu quả và an toàn trong việc điều trị.&lt;SEP&gt;Liều dùng của Chophytol cần được điều chỉnh phù hợp với độ tuổi và triệu chứng bệnh của từng bệnh nhân.&lt;SEP&gt;Liều dùng của Claminat cần được điều chỉnh phù hợp với độ tuổi và triệu chứng của từng bệnh nhân.&lt;SEP&gt;Liều dùng của Combivent® là 1 hít x 4 lần/ngày.&lt;SEP&gt;Liều dùng của Cravit thường là mỗi lần nhỏ 1 giọt và có thể dùng 3 lần trong ngày.\ndược sĩ: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nLiều Lượng: Liều lượng là số lượng thuốc hoặc chất hoạt chất được chỉ định sử dụng trong quá trình điều trị. Nó bao gồm cả số lượng thuốc được sử dụng và cách thức sử dụng nó, ví dụ như qua đường uống, tiêm hoặc thoa ngoài da. Liều lượng có thể được điều chỉnh dựa trên nhiều yếu tố khác nhau, bao gồm cân nặng, lối sống, và các yếu tố sức khỏe cá nhân khác. \n\nĐối với một số loại thuốc cụ thể, liều lượng cũng được quy định cụ thể cho từng độ tuổi. Ví dụ, liều lượng của Siro Bổ Phế Nam Hà và Viên Ngậm Bổ Phế Nam Hà được quy định cụ thể cho từng độ tuổi khác nhau. Điều này đảm bảo rằng mỗi người dùng nhận được liều lượng phù hợp với nhu cầu và tình trạng sức khỏe của họ.\n\nLiều lượng cũng có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc. Ví dụ, liều lượng corticoid sử dụng tại chỗ có thể được hấp thu vào máu, do đó việc xác định đúng liều lượng là rất quan trọng để tránh các tác dụng phụ không mong muốn.\n\nNgoài ra, liều lượng còn liên quan đến việc sử dụng thảo dược và hormone. Việc sử dụng thảo dược cần được chú ý về mức độ sử dụng, và liều lượng hormone là yếu tố ảnh hưởng đến việc lựa chọn liệu pháp hormon.&lt;SEP&gt;Liều lượng là yếu tố cần xem xét khi sử dụng dược liệu này để đảm bảo hiệu quả và an toàn.&lt;SEP&gt;Liều lượng là mức độ hoặc số lượng của một chất được đưa vào cơ thể, có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc.&lt;SEP&gt;Liều lượng là số lượng thuốc cần dùng trong một lần hoặc trong một khoảng thời gian.\nThảo Dược: Thảo Dược là thuật ngữ chung chỉ các loại cây cỏ, hạt, củ, lá được sử dụng làm dược liệu trong y học cổ truyền. Thảo dược bao gồm nhiều loại cây khác nhau như cà dăm, cây Nổ gai, cây Rau Dớn, và cả quả, lá, và rễ của chanh. Thảo dược đóng vai trò quan trọng như các thành phần chính trong nhiều bài thuốc, đặc biệt là trong việc sắc uống hỗ trợ điều trị các chứng bế kinh, ứ huyết. Thảo dược từ cây Nổ gai có tác dụng khu phong, trừ thấp, thanh nhiệt, giải độc, chỉ huyết, giảm đau, và giảm ngứa. Thảo dược cũng được sử dụng trong chè dưỡng nhan có nguồn gốc từ cung đình Trung Quốc.\n\nThảo dược có nhiều công dụng trong việc phòng ngừa và điều trị các bệnh và triệu chứng, đồng thời cũng được sử dụng rộng rãi trong các bài thuốc cổ truyền. Thảo dược có thể tương tác với các loại thuốc hiện đại như Aleucin 500 mg và có tác dụng chống viêm rõ rệt. Thảo dược là nguồn gốc của các thành phần hóa học như coumarin trong nghiên cứu về tác dụng bảo vệ tế bào gan và chống viêm. Tuy nhiên, cần lưu ý rằng thảo dược có thể là con dao hai lưỡi nếu không sử dụng đúng cách, vì chúng có thể gây ra nhiều tương tác thuốc và tác dụng phụ tiềm ẩn.\n\nNgoài ra, thảo dược còn được sử dụng như một dạng thuốc thay thế có thể được sử dụng để điều trị bệnh đau chi ma. Thảo dược cũng được xem là một loại thực phẩm chức năng, mặc dù chưa được chứng minh có hiệu quả trong điều trị lo âu. Thảo dược là lĩnh vực chuyên môn cần tham vấn ý kiến của bác sĩ hoặc các chuyên gia. Cây sachi là một loại thảo dược có thể phát triển ở những vùng khí hậu ẩm ướt. Thảo dược là nguyên liệu dược liệu, cần bảo quản cẩn thận. Thảo dược là nguyên liệu quý được sử dụng trong y học cổ truyền và ngành hóa dược.\n\nThảo dược cũng được sử dụng để điều trị các bệnh ngoài da, bao gồm viêm lộ tuyến và viêm loét cổ tử cung. Thảo dược này có tác dụng cải thiện tế bào beta tụy và giảm lượng đường trong máu. Thảo dược là nguyên liệu trong bài thuốc hỗ trợ điều trị bệnh đái tháo đường và bệnh Gout. Thảo dược là thành phần tự nhiên trong BoniDiabet.\n\nThảo dược còn được biết đến như một phương pháp điều trị bệnh bằng các loại cây thuốc, bao gồm cả huyết rồng. Thảo dược là một trong hai phương pháp chính để chữa u mềm lây thông qua việc thoa lên bề mặt. Thảo dược là thuật ngữ chung cho các vị thuốc tự nhiên, bao gồm cả rau đắng đất, và cũng là nguyên liệu trong bài thuốc thanh can giải độc. Thảo dược là thuật ngữ dùng để chỉ các loại cây có tác dụng chữa bệnh và là thuật ngữ chung cho các loại cây thuốc.&lt;SEP&gt;Thảo dược là thuật ngữ chỉ các loại cây thuốc quý.&lt;SEP&gt;Thảo dược là nguyên liệu tự nhiên từ cây cỏ.&lt;SEP&gt;Thảo dược là các chất hóa học tự nhiên từ thực vật, có thể được sử dụng trong điều trị.&lt;SEP&gt;Thảo dược là tên chung cho các loại cây được sử dụng làm thuốc, trong đó có Tía tô.\nBismuth Subcitrat - Tiêu Chảy: Bismuth subcitrat được chỉ định trong điều trị tiêu chảy.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nBisilkon - Ngứa: Ngứa là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nBisilkon - Phụ Nữ Có Thai: Bisilkon chống chỉ định sử dụng ở phụ nữ mang thai.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nChỉnh Liều Bisoprolol - Suy Tim: Chỉnh liều bisoprolol là phương pháp điều chỉnh liều lượng thuốc trong quá trình điều trị suy tim.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBisilkon - Tiểu Đường: Bisilkon có thể gây ra tiểu đường do sử dụng kéo dài.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nBisilkon - Phụ Nữ Mang Thai: Không nên dùng Bisilkon cho phụ nữ mang thai.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nBisilkon - Loãng Xương: Bisilkon có thể gây ra loãng xương do sử dụng kéo dài.\nHuyền Hồ - Liều Dùng: Liều dùng chỉ dẫn liều lượng sử dụng Huyền hồ.\n20 mg - Bisoprolol: Bisoprolol được sử dụng với liều tối đa 20 mg 1 lần/ngày.\ndược sĩ - thuốc: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\n10 mg - Bisoprolol: Bisoprolol được sử dụng với liều 10 mg 1 lần/ngày để điều trị suy tim mãn ổn định.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\n2,5 mg - Bisoprolol: Bisoprolol được sử dụng với liều 2,5 mg 1 lần/ngày để điều trị huyết áp nhẹ.\nCách Dùng - Cánh Kiến Trắng: Cách dùng và liều dùng của cây Thuốc mọi tùy thuộc vào mục đích sử dụng và từng bài thuốc.\nBisoprolol - Chỉnh Liều: Chỉnh liều Bisoprolol bắt đầu từ liều thấp và tăng dần liều nếu thuốc được dung nạp tốt.\nBisilkon - Corticosteroid: Bisilkon chứa corticosteroid để điều trị các bệnh lý da.&lt;SEP&gt;Bisilkon chứa corticosteroid, có thể gây ức chế trục HPA.\nBisilkon - Thủy Đậu: Bisilkon chống chỉ định sử dụng ở người bị thủy đậu.\nBisilkon - Nhiễm Khuẩn: Bisilkon cần được bảo quản tránh tiếp xúc với các nguồn gây nhiễm khuẩn hoặc tái nhiễm.\nBisilkon - Mụn Trứng Cá: Bisilkon chống chỉ định sử dụng ở người bị mụn trứng cá.\nBisilkon - Mẹ Cho Con Bú: Bisilkon chống chỉ định sử dụng ở mẹ cho con bú.\nBisilkon - Giang Mai: Bisilkon chống chỉ định sử dụng ở người bị giang mai.\nBisilkon - Tác Dụng Không Mong Muốn: Người dùng cần thông báo với bác sĩ hoặc dược sĩ về bất kỳ tác dụng không mong muốn nào gặp phải khi sử dụng Bisilkon.\nBan Đỏ - Bisilkon: Ban đỏ là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Gentamicin: Gentamicin là thành phần chính của Bisilkon, là kháng sinh thuộc nhóm aminoglycosid.&lt;SEP&gt;Bisilkon được chỉ định khi có biến chứng nhiễm trùng do vi khuẩn nhạy cảm với gentamicin.\nBisilkon - Ánh Sáng: Bisilkon cần được bảo quản tránh ánh sáng.\nBisilkon - Hội Chứng Cushing: Bisilkon có thể gây ra hội chứng Cushing do sử dụng kéo dài.\nBismuth Subcitrat - Thực Quản: Bismuth subcitrat được sử dụng để bảo vệ thực quản khỏi kích ứng.\nBisilkon - Clotrimazol: Clotrimazol là thành phần chính của Bisilkon, dùng để điều trị tại chỗ các bệnh nấm về da.&lt;SEP&gt;Bisilkon được chỉ định khi có biến chứng nhiễm trùng do nấm nhạy cảm với clotrimazol.\nBisilkon - Nấm Candida: Bisilkon chống chỉ định sử dụng ở người bị nấm Candida.\nBisilkon - Thời Kỳ Mang Thai: Tính an toàn của Bisilkon cho phụ nữ mang thai chưa được thiết lập, do đó không nên dùng thuốc cho họ.\nBisilkon - Eczema: Bisilkon được chỉ định để điều trị eczema có rỉ dịch.\nBisilkon - Hạn Dùng: Bisilkon có hạn dùng là 36 tháng kể từ ngày sản xuất.\nAminoglycosid - Bisilkon: Khi sử dụng đồng thời với aminoglycosid toàn thân có thể gây độc do tích lũy kháng sinh.\nBisilkon - Thời Kỳ Cho Con Bú: Cần thận trọng khi dùng Bisilkon ở phụ nữ đang cho con bú.\nBisilkon - Nóng Bừng: Nóng bừng là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Ghẻ Ngứa: Bisilkon chống chỉ định sử dụng ở người bị ghẻ ngứa.\nBệnh Lý Về Da - Gentamicin: Gentamicin là kháng sinh thuộc nhóm aminoglycosid, dùng để điều trị bệnh lý về da.\nBisilkon - Dược Sĩ Trần Việt Linh: Dược sĩ Trần Việt Linh đã cung cấp thông tin về sản phẩm Bisilkon.\nBisilkon - Viêm Da Quanh Miệng: Bisilkon chống chỉ định sử dụng ở người bị viêm da quanh miệng.\nBisilkon - Chấy Rận: Bisilkon chống chỉ định sử dụng ở người bị chấy rận.\nBisilkon - Nhiễm Trùng Vi Khuẩn: Bisilkon được chỉ định để điều trị nhiễm trùng vi khuẩn.\nBisilkon - Tiền Sử Mẫn Cảm: Bisilkon chống chỉ định sử dụng ở người có tiền sử mẫn cảm với bất kỳ thành phần nào của thuốc.\nBidiphar - Bisilkon: Bidiphar sản xuất Bisilkon, kem bôi ngoài da điều trị một số bệnh lý về da.\nBisilkon - Giảm Sắc Tố: Giảm sắc tố là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBệnh Lý Về Da - Clotrimazol: Clotrimazol được dùng để điều trị tại chỗ các bệnh nấm về da.\nBisilkon - Rỉ Dịch: Rỉ dịch là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBetamethason Dipropionat - Bisilkon: Betamethason dipropionat là thành phần chính của Bisilkon, có tác dụng chống viêm, chống dị ứng, chống thấp khớp và ức chế miễn dịch.\nBisilkon - Rộp Da: Bisilkon chống chỉ định sử dụng ở người bị rộp da.\nBisilkon - Đậu Mùa: Bisilkon chống chỉ định sử dụng ở người bị đậu mùa.\nBisilkon - Trục HPA: Bisilkon có thể gây ức chế trục HPA.\nBisilkon - Đổi Màu Da: Đổi màu da là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Mụn Nói Chung: Bisilkon chống chỉ định sử dụng ở người bị mụn nói chung.\nBisilkon - Lao Da: Bisilkon chống chỉ định sử dụng ở người bị lao da.\nBisilkon - Giời Leo: Bisilkon chống chỉ định sử dụng ở người bị giời leo.\nBisilkon - Nhiễm Trùng Nấm: Bisilkon được chỉ định để điều trị nhiễm trùng nấm.\nBisilkon - Kích Thích ACTH: Kiểm tra sự ức chế trục HPA thông qua kích thích ACTH.\nBisilkon - Băng Kín: Bisilkon có thể gây ra tác dụng không mong muốn khi dùng băng kín.\nBismuth Subcitrat - Loét Dạ Dày Tá Tràng: Bismuth subcitrat được chỉ định trong điều trị loét dạ dày tá tràng.\nBismuth Subcitrat - H. Pylori: Bismuth subcitrat được sử dụng để diệt trừ H. pylori.\nBismuth Subcitrat - Chứng Khó Tiêu: Bismuth subcitrat được chỉ định trong điều trị chứng khó tiêu.\nBài Thuốc Chữa Viêm Hang Vị Dạ Dày - Hàng Ngày: Hàng ngày lấy 1 nhúm cho vào chai trà, hãm với nước sôi, uống thay trà liên tục 2 tháng.\nBetamethason Dipropionat - Bệnh Lý Về Da: Betamethason dipropionat có tác dụng chống viêm, chống dị ứng, chống thấp khớp và �ức chế miễn dịch.\nChỉnh Liều Bisoprolol - Thời Gian Thải Rối: Chỉnh liều bisoprolol liên quan đến thời gian thải trừ của thuốc.']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Theo hướng dẫn sử dụng, thuốc Bisilkon được bôi từ 1 đến 2 lần/ngày. Tuy nhiên, việc sử dụng thuốc cần tuân theo hướng dẫn cụ thể của bác sĩ hoặc dược sĩ để đảm bảo an toàn và hiệu quả.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thuốc Bisilkon bôi 2 lần/ngày vào buổi sáng và buổi tối.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8287849243338893</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5405295643918057</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>['Atorpa-E: Atorpa-E là thuốc chữa bệnh tim mạch chứa Atorvastatin và Ezetimibe.&lt;SEP&gt;Atorpa-E là thuốc kết hợp Atorvastatin và Ezetimibe, dùng để giảm nguy cơ các biến cố tim mạch và điều trị tăng cholesterol máu.&lt;SEP&gt;Atorpa-E là thuốc được chỉ định điều trị tăng cholesterol máu và rối loạn lipid máu hỗn hợp.&lt;SEP&gt;Atorpa-E là thuốc được sử dụng trong điều trị bệnh gan, chống chỉ định ở bệnh nhân có bệnh gan đang hoạt động.&lt;SEP&gt;Atorpa-E là thuốc cần thận trọng khi sử dụng ở bệnh nhân uống nhiều rượu, có tiền sử bệnh gan, yếu tố ảnh hưởng đến hội chứng tiêu cơ vân, người lớn tuổi và đang điều trị với cyclosporin.&lt;SEP&gt;Atorpa-E là thuốc có công dụng, cách dùng và tác dụng phụ được đề cập trong bài viết.&lt;SEP&gt;Atorpa-E là thuốc chứa Atorvastatin và Ezetimibe.\nThuốc Giảm Cholesterol: Thuốc giảm cholesterol được sử dụng để ngăn ngừa xơ vữa động mạch.&lt;SEP&gt;Thuốc giảm cholesterol là loại thuốc được sử dụng để điều trị tăng cholesterol và ngăn ngừa sa sút trí tuệ do mạch máu.\nPhòng Ngừa Xơ Vữa Động Mạch: Atorvastatin phòng ngừa xơ vữa động mạch.\nXơ Vữa Động Mạch: Xơ vữa động mạch là bệnh lý của hệ thống tim mạch liên quan đến sự tích tụ cholesterol, chất béo trung tính, và các mảng bám khác trên thành mạch máu. Tình trạng này tạo nên lớp cặn cứng và dày ở bên trong động mạch, làm thu hẹp đường kính của chúng và làm cho động mạch kém chuyển động hơn. Bệnh lý này thường xuất hiện do giảm viêm, stress oxy hóa, và tăng huyết áp. Xơ vữa động mạch không chỉ là bệnh lý về động mạch mà còn có thể dẫn đến các vấn đề về thận thứ phát, gây tổn thương các cơ quan như tim, não, và thận.\n\nĐể ngăn chặn và phòng ngừa xơ vữa động mạch, người ta thường sử dụng các loại thuốc như Atorvasan VLC, Atorvastatin, Altamin, Clopidogrel, Bonzacim, và Bồ hoàng. Atorvastatin không chỉ giúp phòng ngừa xơ vữa động mạch mà còn làm chậm quá trình tiến triển của bệnh mạch vành. Clopidogrel được sử dụng để kiểm soát bệnh xơ vữa động mạch thứ phát. Tuy nhiên, cần phải thận trọng khi sử dụng các loại thuốc chứa canxi, vitamin D, và Calcigenol vì chúng có thể gây tăng canxi huyết và tạo ra các vấn đề liên quan đến xơ vữa động mạch. Ngoài việc sử dụng thuốc, các biện pháp tự nhiên như sử dụng Bạch linh, Biển súc, và dây ký ninh cũng được biết đến với khả năng ngăn ngừa xơ vữa động mạch. Tuy nhiên, người bệnh cần thận trọng khi sử dụng Babi B.O.N. do khả năng gây ra các vấn đề liên quan đến xơ vữa động mạch.\n\nXơ vữa động mạch còn được điều trị thử nghiệm bằng cách sử dụng cỏ xước, aconitin, và Đan sâm. Aconitin đã được thử nghiệm trên thỏ và Đan sâm được sử dụng trong điều trị bệnh tim mạch. Xơ vữa động mạch là quá trình lắng đọng chất béo trong thành động mạch, làm thu hẹp lòng mạch. Nó cũng là nguyên nhân phổ biến nhất của bệnh động mạch ngoại biên. Tình trạng này còn được ngăn chặn bởi hàm lượng chất xơ trong đậu và chiết xuất từ dây ký ninh. Rutin cũng được biết đến với khả năng đề phòng biến cố do xơ vữa động mạch. Một số thảo dược khác như La bạc tử cũng được sử dụng trong điều trị xơ vữa động mạch nhờ vào thành phần linolenic acid và linoleic acid của nó. Xơ vữa động mạch cũng được khắc phục nhờ tác dụng kháng viêm của mật mông hoa và chiết xuất cây. Saponin cũng được biết đến với khả năng ức chế sự phát triển của xơ vữa động mạch. Ngoài ra, tình trạng này còn được ngăn chặn nhờ tác dụng của mộc nhĩ.\n\nXơ vữa động mạch là hậu quả của tăng huyết áp và rối loạn mỡ máu. Bệnh lý này cũng là biến chứng của tiểu đường và được ngăn ngừa nhờ mướp đắng và BoniDiabet. Xơ vữa động mạch cũng được điều trị bằng Sâm vũ diệp và Tam lăng nhờ tác dụng chống lại quá trình xơ vữa. Xơ vữa động mạch là biến chứng của bệnh tăng huyết áp vô căn, có thể dẫn đến đau tim. Xơ vữa động mạch cũng là một nguyên nhân gây bệnh teo não và là một trong những bệnh nội khoa góp phần thúc đẩy tình trạng thiếu máu não cục bộ dẫn đến teo não. Xơ vữa động mạch là tình trạng tích tụ mảng bám trong thành mạch máu, được giảm nguy cơ bởi tác dụng của thiên ma. Xơ vữa động mạch là bệnh liên quan đến việc làm giảm cholesterol toàn phần và LDL. Xơ vữa động mạch là quá trình tích tụ cholesterol và canxi trong lòng mạch vành, gây xơ cứng và khó dẫn máu đến nuôi tim.&lt;SEP&gt;Xơ vữa động mạch là bệnh tim mạch do tăng cholesterol máu kéo dài do suy chức năng giáp.&lt;SEP&gt;Xơ vữa động mạch nặng thường liên quan đến suy chức năng giáp.\nTiền Sử Bệnh Cơ Do Dùng Statin Hoặc Fibrat: Tiền sử bệnh cơ do dùng statin hoặc fibrat là yếu tố ảnh hưởng đến hội chứng tiêu cơ vân, cần thận trọng khi sử dụng Atorpa-E.\nCholesterol: Cholesterol là một hợp chất sinh học đóng vai trò quan trọng trong cơ thể, tồn tại trong hầu hết các tế bào và được tạo ra bởi gan. Nó không chỉ là một thành phần cần thiết cho cơ thể mà còn có thể trở thành nguyên nhân gây ra tình trạng tăng cholesterol máu, một yếu tố nguy cơ gây bệnh tim mạch. Cholesterol đóng vai trò trong cấu trúc của màng tế bào và các chức năng khác của cơ thể, đồng thời là một hợp chất hóa học có trong máu, liên quan đến nhiều vấn đề sức khỏe.\n\nCholesterol có thể được chuyển đổi thành acid mật và kiểm soát lượng cholesterol trong cơ thể có thể được thực hiện thông qua nhiều phương pháp khác nhau, bao gồm việc sử dụng Atorvastatin, một loại thuốc hạ cholesterol, thông qua việc ức chế quá trình tổng hợp cholesterol trong cơ thể. Điều này giúp giảm nồng độ cholesterol trong máu và tế bào, đồng thời giúp kiểm soát lượng cholesterol, giảm chất xơ trong Actiso, góp phần vào việc giảm cân và hỗ trợ hệ tiêu hóa. Ngoài ra, trà Atiso đỏ cũng có thể giúp kiểm soát lượng cholesterol trong cơ thể. Các chất khác như Bạch linh, cà dại hoa tím, Betaine hydrochloride trong kỷ tử và cây Ba chạc cũng giúp giảm đáng kể nồng độ cholesterol.\n\nCholesterol cũng là chất béo hòa tan trong máu và được giảm nhờ sự tác động của saponin, làm giảm nồng độ cholesterol trong huyết tương. Cholesterol còn được biết đến như một thành phần mỡ trong máu bị ức chế bởi chiết xuất Actiso. Một số thảo dược khác như khổ qua, liên翘, vỏ quả mít đỏ, và đu đủ cũng được chứng minh có khả năng giảm mức cholesterol trong máu.\n\nCholesterol là một trong những thành phần hóa học của ngưu hoàng và cũng là một hợp chất liên quan đến glucose và khả năng dung nạp đường. Cholesterol là một loại chất béo có thể gây ra bệnh xơ vữa động mạch khi tồn tại trong máu. Sử dụng các chất tự nhiên như nấm Linh Chi có thể giúp kiểm soát mức cholesterol trong máu. Adenosine trong nấm Linh Chi có thể giúp điều chỉnh lượng cholesterol trong máu, từ đó giảm mức cholesterol.\n\nCholesterol bị bài tiết tăng từ Sơn tra, có thể làm hạ lipid máu. Cholesterol là thành phần của lipid máu được hạ thấp bởi quả quýt. Cholesterol là chất trong máu, có thể bị ảnh hưởng bởi rau đắng biển. Mỡ máu (chủ yếu là cholesterol) là yếu tố cần kiểm tra khi chẩn đoán rối loạn cương dương. Tăng cholesterol là một dạng rối loạn lipid máu. Cholesterol là thành phần chính của HDL. Cholesterol là thành phần trong máu cần được kiểm soát trong điều trị rối loạn lipid máu. Cholesterol là chất béo trong máu, thường tăng cùng với bệnh nhân bị tăng triglycerid.\n\nCholesterol là một chất béo dạng sáp, có trong thức ăn và được cơ thể tổng hợp. Xét nghiệm cholesterol là phương pháp chẩn đoán để đánh giá mức độ cholesterol trong máu. Cholesterol cao là triệu chứng cần được kiểm soát để ngăn ngừa tai biến mạch máu não. Cholesterol là hợp chất được nhóm thuốc statins kiểm soát.\n\nNgoài ra, cholesterol cũng là nguồn nguyên liệu để tổng hợp các nội tiết tố tại tuyến thượng thận. Cholesterol được tìm thấy trong máu và được thạch lựu tác động làm giảm mức. Cholesterol là chất được tìm thấy ở thạch lựu có khả năng làm giảm mức cholesterol trong máu. Cholesterol là chất béo hòa tan trong máu, có thể tăng lên do bổ sung vitamin D và cholesterol. Chiết xuất hạt Thanh Yên có hoạt tính giảm cholesterol. Cholesterol là chất béo đóng vai trò trong quá trình xơ vữa động mạch.\n\nMức độ cholesterol trong máu có thể tăng khi sử dụng Aluvia. Arginin giúp làm giảm mức cholesterol. Rối loạn chuyển hóa lipid được điều trị bằng Atorvastatin. Cholesterol là thành phần lipid “xấu” trong máu được Atorvastatin giảm nồng độ. Cholesterol là hợp chất có thể bị ảnh hưởng bởi Brufen, mặc dù không được đề cập cụ thể trong văn bản. Cholesterol là chất được kiểm tra trong các xét nghiệm liên quan đến Daflon. Cholesterol là hợp chất hóa học được điều chỉnh mức bằng cholestyramine.\n\nCholesterol là một chất bị giảm hấp thu khi dùng neomycin. Cholesterol cũng được giảm bởi tinh dầu Bergamot. Cholesterol trong máu có thể được cải thiện bởi tinh dầu húng quế. Cholesterol là một dạng bệnh liên quan đến mức cholesterol cao trong máu. Cholesterol là một thành phần hóa học trong nọc bọ cạp. Cholesterol là chất được kiểm soát bởi việc uống nước trà xanh thường xuyên. Cholesterol là một thành phần trong dịch mật có thể kết tụ thành dạng rắn gây sỏi mật. Cholesterol là chất béo có thể tích tụ và tạo thành sỏi cholesterol trong cơ thể.&lt;SEP&gt;Cholesterol là chất béo được tìm thấy trong huyết tương, tăng nồng độ do suy chức năng giáp.&lt;SEP&gt;Hormone giáp làm giảm nồng độ cholesterol trong huyết tương.\nCholesterol Máu Kém: Cholesterol máu cao là triệu chứng được điều trị bằng Atorhasan 20.\nNgăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não là việc giảm thiểu tỉ lệ mắc phải TBMMN thông qua việc dùng thuốc đúng chỉ định và liều lượng.\nLDL-Cholesterol: Tăng LDL-cholesterol là tình trạng được Atorvastatin điều trị.&lt;SEP&gt;LDL-Cholesterol là hợp chất hóa học, được giảm đáng kể bởi Crocin.\nCholesterol Máu: Cholesterol máu là một hợp chất sinh học quan trọng, đóng vai trò trung tâm trong nhiều rối loạn lipid máu và các bệnh liên quan đến sức khỏe. Cholesterol máu có thể tăng lên do nhiều nguyên nhân khác nhau, dẫn đến tình trạng tăng hàm lượng cholesterol trong máu. Điều này đòi hỏi sự kiểm soát chặt chẽ thông qua các phương pháp điều trị như sử dụng Atorhasan 20, Cosele, dầu jojoba, Địa cốt bì, và Dứa dại.\n\nNgoài ra, cholesterol máu còn được tác động bởi Bồ hoàng để giúp giảm mức cholesterol. Việc kiểm soát nồng độ cholesterol máu là một trong những phương pháp phòng ngừa hiệu quả đối với bệnh suy thận và cũng là một triệu chứng cần được kiểm soát trong bệnh cầu thận màng.&lt;SEP&gt;Cholesterol máu cao là bệnh được điều trị bằng Kiều mạch.&lt;SEP&gt;Cholesterol máu là bệnh rối loạn chuyển hóa cholesterol, có thể được điều trị bằng chất berbagia trong lá ổi.&lt;SEP&gt;Ngưu tất được ghi nhận có tác dụng hạ cholesterol máu.&lt;SEP&gt;Cholesterol máu là vấn đề sức khỏe được điều trị bằng Sa nhân.&lt;SEP&gt;Cholesterol máu là một trong những yếu tố góp phần vào hình thành các mảng xơ vữa trong động mạch.\nTăng Thải LDL: Atorvastatin tăng thải LDL ra khỏi tuần hoàn.\nDứa Dại: Dứa dại là cây được sử dụng trong bài thuốc trị sỏi thận.&lt;SEP&gt;Dứa dại, còn gọi là Dứa gỗ, Dứa gai, được dùng trong dân gian để trị bí tiểu, sỏi thận.&lt;SEP&gt;Cây Dứa dại được trồng và mọc dại ở nhiều nơi tại Việt Nam và các nước khác trên thế giới.&lt;SEP&gt;Dứa Dại được sử dụng để trị bí tiểu, tiểu khó, sỏi thận và bồi bổ cơ thể.&lt;SEP&gt;Dứa dại là cây được sử dụng trong dân gian để điều trị một số bệnh.&lt;SEP&gt;Dứa dại là thảo dược được sử dụng trong bài thuốc sắc điều trị thấp khớp.\nTăng Cholesterol Máu: Tăng cholesterol máu là tình trạng sức khỏe hoặc bệnh lý liên quan đến rối loạn chuyển hóa lipit và cholesterol trong cơ thể. Tình trạng này thường được điều trị bằng thuốc Atorvastatin, một loại statin được sử dụng rộng rãi để kiểm soát mức cholesterol trong máu. Khi bệnh nhân không đáp ứng với các thuốc khác, Atorvastatin thường được chỉ định như một lựa chọn điều trị tiếp theo.\n\nNgoài ra, tăng cholesterol máu cũng có thể được hỗ trợ điều trị bằng các phương pháp khác, bao gồm cả việc sử dụng các thảo dược truyền thống. Một số bài thuốc hỗ trợ điều trị tăng cholesterol máu bao gồm những thành phần như Sa nhân và Sơn thù du. Tuy nhiên, cần lưu ý rằng tăng cholesterol máu cũng có thể là tác dụng phụ của việc sử dụng dược liệu có mùi lạ, ôi thiu, hoặc chua.\n\nTóm lại, tăng cholesterol máu là một tình trạng sức khỏe cần được điều trị kịp thời và đúng cách để ngăn ngừa các biến chứng nguy hiểm.&lt;SEP&gt;Tăng cholesterol máu là yếu tố nguy cơ dẫn đến thoái hóa điểm vàng.&lt;SEP&gt;Tăng cholesterol máu là tác dụng phụ thường gặp khi sử dụng CellCept.&lt;SEP&gt;Tăng cholesterol máu có tiềm năng lâm sàng để điều trị bằng toàn yết.\nAtorvastatin: Atorvastatin là một hoạt chất chính thuộc nhóm thuốc statin, được sử dụng rộng rãi trong việc điều trị tăng cholesterol máu và rối loạn lipid máu hỗn hợp. Nó hoạt động bằng cách ức chế cạnh tranh với enzym HMG-CoA reductase, từ đó làm giảm tổng hợp cholesterol trong tế bào gan và kích thích tăng số lượng thụ thể LDL-cholesterol trên màng tế bào gan. Atorvastatin không chỉ giúp giảm cholesterol mà còn tăng vận chuyển LDL ra khỏi tuần hoàn máu. Thuốc này được tìm thấy trong nhiều sản phẩm, bao gồm cả Atorhasan và Atorvastatin T.V Pharm. Atorvastatin thường được sử dụng như một phần của liệu pháp ăn uống để giảm nồng độ cholesterol toàn phần và cholesterol xấu (LDL).\n\nViệc sử dụng Atorvastatin cần được thực hiện thận trọng do có một số chống chỉ định và tình huống sử dụng cần lưu ý. Đặc biệt, Atorvastatin chống chỉ định với phụ nữ mang thai và cho con bú do có khả năng gây hại cho thai nhi. Atorvastatin cũng có khả năng tương tác với nhiều loại thuốc khác nhau, bao gồm cả Amlodipine và các thuốc kháng HIV như Amiodarone, Darunavir + Ritonavir, Saquinavir + Ritonavir, Fosamprenavir, Fosamprenavir + Ritonavir, Nelfinavir. Khi sử dụng Atorvastatin cùng với iodaron, có thể làm tăng nguy cơ gây tiêu cơ vân. Atorvastatin cũng làm tăng diện tích dưới đường cong (AUC) của ethinylestradiol lên khoảng 20%.\n\nAtorvastatin là thuốc tim mạch có thể tương tác với Boston C 1000. Thuốc này không nên sử dụng đồng thời với Itraconazole. Atorvastatin là dược chất kháng viêm bền thành mạch, được sử dụng để điều trị rối loạn lipid máu, giảm nguy cơ đột quỵ và tử vong, giảm nồng độ lipid "xấu" trong máu. Khi sử dụng Atorvastatin, cần được theo dõi nồng độ creatine kinase (CK) và men gan để đảm bảo an toàn và hiệu quả điều trị.&lt;SEP&gt;Atorvastatin là một loại thuốc cần lưu ý khi sử dụng chung với Daktarin.&lt;SEP&gt;Atorvastatin là một loại thuốc có tương tác với Actemra.\nTiền Sử Bệnh Gan: Tiền sử bệnh gan là tình trạng thận trọng khi dùng Atorpa-E.&lt;SEP&gt;Tiền sử bệnh gan là tình trạng cần thận trọng khi sử dụng Atorvastatin.\nCholesterol Máu Cao: Cholesterol máu cao là tình trạng lượng cholesterol trong máu vượt quá giới hạn bình thường. Tình trạng này có thể được điều trị bằng Atorvastatin khi các thuốc khác không đạt hiệu quả. Cholesterol máu cao, đặc biệt là tăng LDL-cholesterol máu, là một nguyên nhân phổ biến gây ra liệt dương. Ngoài ra, cholesterol máu cao cũng là một yếu tố nguy cơ dẫn đến bệnh động mạch ngoại biên và bệnh tim mạch. Đậu đen có thể giúp ngăn chặn tình trạng cholesterol máu cao. Giảo cổ lam cũng được sử dụng trong việc điều trị tình trạng này.\nAtorhasan 20: Atorhasan 20 được sử dụng trong điều trị rối loạn lipid máu, hỗ trợ liệu pháp ăn uống ở người lớn và trẻ em bị tăng cholesterol máu nguyên phát và rối loạn lipid máu hỗn hợp.\nAtorvastatin T.V Pharm: Atorvastatin T.V Pharm là thuốc thuộc danh mục thuốc trị rối loạn lipid máu, được sản xuất bởi Công ty Cổ phần Dược phẩm T.V Pharm.&lt;SEP&gt;Atorvastatin T.V Pharm là thuốc hạ cholesterol, có thể gây một số tác dụng phụ như đau bụng, buồn nôn, tiêu chảy, táo bón, đầy hơi, đau đầu, chóng mặt, mất ngủ, suy nhược, nhìn mờ, đau cơ, đau khớp, tăng men gan, bệnh về cơ, nổi ban da, viêm mũi, viêm họng, ho, viêm xoang, tăng đường huyết, tăng HbA1c, suy giảm chức năng nhận thức.&lt;SEP&gt;Atorvastatin T.V Pharm là thuốc chống chỉ định trong các trường hợp người có mẫn cảm với bất kỳ thành phần nào của thuốc, người bị suy gan, phụ nữ có thai và cho con bú, và người sử dụng các thuốc chống nấm ketoconazol, itraconazol, gemfibrozil, niacin liều cao, colchicin.&lt;SEP&gt;Atorvastatin T.V Pharm là thuốc được đề cập trong bài viết này.&lt;SEP&gt;Atorvastatin T.V Pharm là thuốc được sử dụng để kiểm soát các vấn đề liên quan đến chuyển hóa cholesterol, cần được theo dõi và quản lý chặt chẽ.\nTăng Cholesterol Máu Đồng Hợp Tử Gia Đình (HoFH): Tăng cholesterol máu đồng hợp tử gia đình (HoFH) là bệnh được điều trị bằng Atorpa-E.&lt;SEP&gt;Tăng cholesterol máu đồng hợp tử gia đình (HoFH) là bệnh rối loạn lipid máu di truyền.\nTăng Cholesterol: Tăng cholesterol là tình trạng sức khỏe cần được điều trị, có thể xuất hiện do nhiều nguyên nhân khác nhau. Một trong những cách điều trị tăng cholesterol là thông qua việc sử dụng Atorvastatin T.V Pharm. Ngoài ra, tăng cholesterol cũng có thể là tác dụng phụ của việc sử dụng corticosteroid trong thời gian dài. Điều này không chỉ ảnh hưởng đến sức khỏe tổng thể mà còn tăng khả năng mắc các rối loạn nhận thức thần kinh và suy giảm nhận thức. Suy giáp cũng là một nguyên nhân gây tăng cholesterol trong máu. Bên cạnh đó, tăng cholesterol cũng được biết đến như một trong những tác dụng phụ của Isotretinoin và Aluvia. Khi sử dụng Isotretinoin, tăng cholesterol có thể xuất hiện như một triệu chứng. Do đó, việc kiểm soát và điều trị tăng cholesterol đòi hỏi sự hiểu biết sâu sắc về nguyên nhân và tác động của nó lên sức khỏe toàn diện của người bệnh.\nKiểm Soát Cholesterol: Kiểm soát cholesterol là phương pháp giúp duy trì mức cholesterol khỏe mạnh, thường cần sự giúp đỡ của bác sĩ.\nToàn Yết: Toàn Yết là một loại dược liệu trong y học cổ truyền Việt Nam, được biết đến với nhiều công dụng khác nhau. Toàn Yết là tên gọi của dược liệu từ con bọ cạp, thường được sử dụng trong y học cổ truyền và hiện đại để điều trị chứng kinh phong ở trẻ em. Đây là một vị thuốc không thể thiếu trong y học cổ truyền, được sử dụng để trị trấn kinh, chữa trẻ em bị kinh phong, uốn ván, kích thích thần kinh, bán thân bất toại, bị cảm mồm miệng méo. \n\nToàn Yết cũng được sử dụng trong nhiều bài thuốc khác nhau, bao gồm cả việc kết hợp với các dược liệu khác như Cương tàm và Mã tiền. Nó được sử dụng trong bài thuốc trị sốt cao co giật và từ Mã tiền. Ngoài ra, Toàn Yết còn được sử dụng trong các bài thuốc sắc và có tác dụng điều trị chứng tăng cholesterol máu và kiểm soát huyết áp. \n\nNgoài những công dụng trên, Toàn Yết còn được biết đến với khả năng giảm đau, chống động kinh, kháng khuẩn và điều trị các bệnh mạch máu. Tuy nhiên, do Toàn Yết có độc tính từ nọc đuôi nên nó cần phải được chế biến và sử dụng một cách riêng biệt. Vị thuốc này được sử dụng trong cả Tây y và Đông y, cho thấy sự linh hoạt và đa dạng trong ứng dụng của nó.\nAtorpa-E - Tăng Huyết Áp: Tăng huyết áp là tác dụng phụ của Atorpa-E.\nThuốc Giảm Cholesterol - Xơ Vữa Động Mạch: Thuốc giảm cholesterol được sử dụng để điều trị xơ vữa động mạch.\nAtorpa-E - Suy Thận: Không cần chỉnh liều Atorpa-E ở bệnh nhân suy thận.\nCholesterol - Ngăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não thông qua việc kiểm soát cholesterol.\nAtorpa-E - Ho: Ho, đau thanh quản là tác dụng phụ của Atorpa-E.\nCholesterol Máu - Dứa Dại: Dứa dại điều trị cholesterol máu.\nAtorpa-E - Tim Mạch: Atorpa-E được sử dụng để điều trị các bệnh về tim mạch.\nAtorvastatin - Cholesterol Máu Cao: Atorvastatin được sử dụng để điều trị cholesterol máu cao.\nAtorpa-E - Phụ Nữ Có Thai: Atorpa-E không nên sử dụng ở phụ nữ có thai do nguy cơ tiềm ẩn của các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Phụ nữ có thai không được sử dụng Atorpa-E.&lt;SEP&gt;Atorpa-E được chống chỉ định ở phụ nữ có thai.\nAtorvastatin T.V Pharm - Tăng Cholesterol: Atorvastatin T.V Pharm được sử dụng để điều trị tăng cholesterol.\nAtorhasan 20 - Tim Mạch: Atorhasan 20 bảo vệ hệ thống mạch máu từ biến cố tim mạch.\nCholesterol - Kiểm Soát Cholesterol: Kiểm soát cholesterol giúp duy trì mức cholesterol khỏe mạnh.\nAtorpa-E - Suy Gan: Atorpa-E chống chỉ định ở bệnh nhân suy gan.\nToàn Yết - Tăng Cholesterol Máu: Toàn yết có tiềm năng lâm sàng để điều trị chứng tăng cholesterol máu.\nAtorpa-E - Quá Liều: Trường hợp quá liều Atorpa-E cần điều trị triệu chứng và theo dõi chức năng gan và CPK huyết thanh.\nRối Loạn Lipid Máu - Thuốc Statin: Thuốc statin được sử dụng để điều trị rối loạn lipid máu.\nAtorpa-E - Rối Loạn Tiêu Hóa: Rối loạn tiêu hóa là tác dụng phụ của Atorpa-E.\nCholesterol Máu - Địa Cốt Bì: Địa cốt bì được chỉ định để hạ cholesterol máu.\nAtorhasan 20 - Tiểu Đường: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch ở bệnh nhân tiểu đường.\nLDL-Cholesterol - Statin: Statin được sử dụng để điều trị tăng LDL-cholesterol.\nAtorpa-E - Atorvastatin: Atorpa-E chứa Atorvastatin như một thành phần chính.\nAtorpa-E - Phụ Nữ Cho Con Bú: Atorpa-E không nên sử dụng ở phụ nữ cho con bú do nguy cơ tiềm ẩn của các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Atorpa-E được chống chỉ định ở phụ nữ cho con bú.\nAtorhasan 20 - Hạ Huyết Áp: Atorhasan 20 có tác dụng hạ huyết áp.\nAtorhasan 20 - Huyết Áp: Atorhasan 20 có tác dụng hạ huyết áp.\nAtorpa-E - Hạ Đường Huyết: Hạ đường huyết là tác dụng phụ của Atorpa-E.\nAtorvastatin - Tăng Cholesterol Máu: Atorvastatin được sử dụng để điều trị tăng cholesterol máu.&lt;SEP&gt;Atorvastatin được sử dụng để điều trị tăng cholesterol máu.&lt;SEP&gt;Atorvastatin được chỉ định để điều trị tăng cholesterol máu.&lt;SEP&gt;Atorvastatin được chỉ định bổ trợ với liệu pháp ăn uống để giúp giảm nồng độ cholesterol toàn phần và cholesterol xấu (LDL).\nAtorpa-E - Viêm Gan: Viêm gan, ứ mật, sỏi mật là tác dụng phụ của Atorpa-E.\nAtorvastatin - Tiền Sử Bệnh Gan: Tiền sử bệnh gan là tình trạng thận trọng khi dùng Atorvastatin.&lt;SEP&gt;Atorvastatin cần thận trọng khi sử dụng trên người có tiền sử bệnh gan.\nAtorvastatin - Tăng Thải LDL: Atorvastatin tăng thải LDL ra khỏi tuần hoàn.\nAtorpa-E - Chán Ăn: Chán ăn là tác dụng phụ của Atorpa-E.\nAtorpa-E - Ù Tai: Ù tai, mất thính lực là tác dụng phụ của Atorpa-E.\nAtorpa-E - Chảy Máu Cam: Chảy máu cam là tác dụng phụ của Atorpa-E.\nAtorpa-E - Bệnh Tim Mạch: Atorpa-E phòng ngừa bệnh tim mạch.\nAtorhasan 20 - Đái Tháo Đường Type 2: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch ở bệnh nhân đái tháo đường type 2.\nSa Nhân - Tăng Cholesterol Máu: Sa nhân được sử dụng trong bài thuốc hỗ trợ điều trị tăng cholesterol máu.\nAtorpa-E - Quá Mẫn: Quá mẫn, bao gồm sốc phản vệ, phù mạch, nổi mày đay, phát ban, là tác dụng phụ của Atorpa-E.\nAtorhasan 20 - Hút Thuốc Lá: Atorhasan 20 được sử dụng để tránh tác hại của hút thuốc lá.\nAtorpa-E - Tăng Đường Huyết: Tăng đường huyết là tác dụng phụ của Atorpa-E.\nAtorhasan 20 - Rối Loạn Lipid Máu: Atorhasan 20 được sử dụng để điều trị rối loạn lipid máu.\nAtorpa-E - Statin: Atorpa-E được sử dụng kết hợp với statin trong điều trị tăng cholesterol máu.\nAtorhasan 20 - Xơ Vữa Động Mạch: Atorhasan 20 được sử dụng để dự phòng xơ vữa động mạch.\nAtorpa-E - Bệnh Gan: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh gan.\nAtorpa-E - Cyclosporin: Atorpa-E được sử dụng đồng thời với Cyclosporin.\nAtorpa-E - Rối Loạn Thị Giác: Rối loạn thị giác, mờ mắt là tác dụng phụ của Atorpa-E.\nAtorpa-E - Suy Giảm Chức Năng Thận: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có suy giảm chức năng thận.\nAtorpa-E - Lipid: Atorpa-E cần kiểm soát hàm lượng lipid trong chế độ ăn kiêng của bệnh nhân.\nAtorhasan 20 - Kháng Viêm: Atorhasan 20 có tác dụng kháng viêm.\nAtorpa-E - Viêm Tụy: Viêm tụy là tác dụng phụ của Atorpa-E.\nAtorhasan 20 - Bệnh Mạch Vành: Atorhasan 20 được sử dụng để dự phòng bệnh mạch vành.\nAtorpa-E - Trào Ngược Dạ Dày: Trào ngược dạ dày, ợ hơi, buồn nôn, nôn, khô miệng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Phụ Nữ Đang Cho Con Bú: Phụ nữ đang cho con bú không được sử dụng Atorpa-E.\nAtorpa-E - Mất Trí Nhớ: Mất trí nhớ là tác dụng phụ của Atorpa-E.\nAtorpa-E - Biếng Ăn: Biếng ăn là tác dụng phụ của Atorpa-E.\nAtorpa-E - Ezetimibe: Atorpa-E chứa Ezetimibe như một thành phần chính.&lt;SEP&gt;Atorpa-E được sử dụng kết hợp với ezetimibe trong điều trị tăng cholesterol máu.\nAtorpa-E - Chế Độ Ăn Kiêng: Atorpa-E được chỉ định như một liệu pháp hỗ trợ trong chế độ ăn kiêng của bệnh nhân HoFH.\nAtorpa-E - Nhược Giáp: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có nhược giáp.\nAtorpa-E - Người Lớn Tuổi: Atorpa-E cần thận trọng khi sử dụng ở người lớn tuổi.\nAtorpa-E - Tăng Cholesterol Máu: Atorpa-E điều trị tăng cholesterol máu.\nAcid Mật - Atorpa-E: Atorpa-E cần được uống trước 22 giờ hoặc sau 24 giờ so với thời điểm dùng thuốc hấp thu acid mật.\nAtorpa-E - Ánh Sáng Trực Tiếp: Ánh sáng trực tiếp cần tránh khi bảo quản Atorra-E.\nAtorpa-E - Viêm Mũi Họng: Viêm mũi họng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Thức Uống: Thức uống cần tránh xa tầm tay của trẻ em và thú nuôi khi bảo quản Atorpa-E.\nAtorpa-E - Viên Nén Bao Phim: Atorpa-E được bào chế dạng viên nén bao phim.\nAtorpa-E - Rối Loạn Lipid Máu Hỗn Hợp: Atorpa-E được chỉ định điều trị rối loạn lipid máu hỗn hợp.\nAtorpa-E - Uống Nhiều Rượu: Atorpa-E cần thận trọng khi dùng ở bệnh nhân uống nhiều rượu.\nAnti-HCV - Atorpa-E: Khi sử dụng Atorpa-E cùng với thuốc chống-HCV, liều dùng Atorpa-E cần được điều chỉnh.&lt;SEP&gt;Atorpa-E chống chỉ định ở bệnh nhân đang dùng thuốc anti-HCV chứa elbasvir hoặc grazoprevir.\nAtorpa-E - Tiền Sử Bệnh Cơ Di Truyền: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh cơ di truyền.\nAtorpa-E - Elbasvir: Khi sử dụng Atorpa-E cùng với elbasvir, liều dùng Atorpa-E cần được điều chỉnh.\nAtorpa-E - Grazoprevir: Khi sử dụng Atorpa-E cùng với grazoprevir, liều dùng Atorpa-E cần được điều chỉnh.\nAtorpa-E - Bệnh Gan Đang Hoạt Động: Atorpa-E được chống chỉ định ở bệnh nhân mắc bệnh gan đang hoạt động.\nAtorpa-E - Tăng Men Gan Transaminase Huyết Thanh Kéo Dài Không Rõ Nguyên Nhân: Atorpa-E được chống chỉ định ở bệnh nhân có tăng men gan transaminase huyết thanh kéo dài không rõ nguyên nhân.\nAtorpa-E - Tiền Sử Bệnh Gan: Atorpa-E cần thận trọng khi dùng ở bệnh nhân có tiền sử bệnh gan.\nAtorpa-E - Tăng Cholesterol Máu Đồng Hợp Tử Gia Đình (HoFH): Atorpa-E điều trị tăng cholesterol máu đồng hợp tử gia đình (HoFH).&lt;SEP&gt;Atorpa-E được chỉ định như một liệu pháp hỗ trợ trong điều trị tăng cholesterol máu đồng hợp tử gia đình.\nAtorpa-E - Giảm Tiểu Паuл: Giảm tiểu cầu là tác dụng phụ của Atorpa-E.\nAtorpa-E - Gặp Ác Mộng: Gặp ác mộng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Giảm Xúc Cảm: Giảm xúc cảm là tác dụng phụ của Atorpa-E.\nAtorpa-E - Đau Thần Kinh Ngoại Переводческая_ошибка: Đau thần kinh ngoại vi là tác dụng phụ của Atorpa-E.\nAtorpa-E - Hội Chứng Tiêu Cơ Vân: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có yếu tố ảnh hưởng đến hội chứng tiêu cơ vân.\nAtorpa-E - Tiền Sử Bệnh Cơ Do Dùng Statin Hoặc Fibrat: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh cơ do dùng statin hoặc fibrat.\nAtorpa-E - Toa: Toa là hướng dẫn sử dụng thuốc Atorpa-E từ bác sĩ.\nAtorpa-E - Lọc Bỏ LDL: Atorpa-E được sử dụng kết hợp với phương pháp lọc bỏ LDL trong điều trị tăng cholesterol máu.\nAtorpa-E - Bệnh Nhân Có Bệnh Mạch Vành: Atorpa-E được chỉ định điều trị tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành.\nAtorpa-E - Mạch Vành (CHD): Atorpa-E điều trị mạch vành (CHD).\nAtorpa-E - Hội Chứng Mạch Andh Cấp Tính (ACS): Atorpa-E điều trị hội chứng mạch vành cấp tính (ACS).\nSơn Thù Du - Tăng Cholesterol Máu: Sơn thù du được dùng để điều trị tăng cholesterol máu.\nThốt Nốt - Tăng Cholesterol Máu: Tăng cholesterol máu là tác dụng phụ khi sử dụng dược liệu có mùi lạ, ôi thiu, hay chua.\nAlcaloid - LDL-Cholesterol: Alcaloid trong Hoàng Liên giảm LDL-cholesterol.\nThoái Hóa Điểm Vàng - Tăng Cholesterol Máu: Tăng cholesterol máu là yếu tố nguy cơ dẫn đến thoái hóa điểm vàng.\nAtorhasan 20 - Cholesterol Máu: Atorhasan 20 điều chỉnh mức cholesterol máu.\nAtorhasan 20 - Biến Cố Tim Mạch: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch.\nCrocin - LDL-Cholesterol: Crocin giảm LDL-Cholesterol.\nAtorhasan 20 - Tăng Triglycerid Máu: Atorhasan 20 được sử dụng để điều trị tăng triglycerid máu.\nAtorhasan 20 - Thụ Thể LDL-Cholesterol: Atorhasan 20 tác động lên thụ thể LDL-cholesterol trên màng tế bào gan.\nAtorhasan 20 - Cholesterol Máu Kém: Atorhasan 20 được sử dụng để điều trị cholesterol máu cao.\nAtorhasan 20 - Tăng Cholesterol Máu Gia Đình Đồng Hợp Tử: Atorhasan 20 được sử dụng để điều trị tăng cholesterol máu gia đình đồng hợp tử.\nAtorhasan 20 - Giảm LDL-Cholesterol: Atorhasan 20 có hiệu quả giảm LDL-cholesterol.\nAtorhasan 20 - Tăng Mật Độ Xương: Atorhasan 20 có tác dụng phụ tăng mật độ xương.\nAtorhasan 20 - Trứng Loạn Lipid Máu Hỗn Hợp: Atorhasan 20 được sử dụng để điều trị rối loạn lipid máu hỗn hợp.']</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành, liều dùng thông thường của Atorpa-E nằm trong khoảng từ 10/10 mg một ngày đến 80/10 mg một ngày. 
+Cụ thể, liều dùng thường thấy là 10/10 mg một lần/ngày. Tuy nhiên, liều dùng cụ thể sẽ được điều chỉnh cho từng bệnh nhân dựa trên kết quả của các xét nghiệm và đáp ứng với liệu pháp điều trị.
+### Tham chiếu
+- [1] atorpa-e.txt</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng Atorpa-E cho bệnh nhân tăng mỡ và/hoặc có bệnh mạch vành dao động từ 10/10 mg đến 80/10 mg một ngày.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8259721123204598</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4564930280551149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>['Aceclofenac STADA: Aceclofenac STADA là thuốc chống viêm, giảm đau, cần được bảo quản đúng cách và tuân thủ hướng dẫn sử dụng.&lt;SEP&gt;Aceclofenac STADA là thuốc giảm đau và chống viêm không steroid (NSAID).\nDị Ứng: Dị Ứng là tình trạng mà cơ thể phản ứng quá mức với các tác nhân gây dị ứng, bao gồm cả các thành phần trong thuốc, môi trường tự nhiên, và dược liệu. Đây là phản ứng miễn dịch bất thường và không mong muốn đối với các chất lạ như kháng sinh và các tá dược có trong thuốc. Dị Ứng có thể xuất hiện khi sử dụng nhiều loại thuốc khác nhau, gây ra các triệu chứng như nổi mẩn ngứa, mề đay, và khó thở. Tình trạng này cũng là chống chỉ định khi sử dụng nhiều loại thuốc cụ thể, như Acemol 325 mg, Acehasan, Acetylcysteine VERTEX, Actiso Ladophar, Agifivit, Ambron Vaco, Aphaxan, Alpha Brain, Boganic, Brosafe, Carbimazol, và Casalmux. Các thuốc này chứa các thành phần như propacetamol hydrochloride, paracetamol, ambroxol, bromhexin, aspirin, adapalene, celecoxib, carbocystein, salbutamol, và các tá dược khác.\n\nDị Ứng cũng có thể xảy ra khi sử dụng các dược liệu như Bồ đề, Trường sinh thảo, Tỳ bà diệp, Xấu Hổ, và cây huyết rồng. Ngoài ra, dị ứng có thể xuất hiện khi tiếp xúc với các tác nhân gây dị ứng như phấn hoa, lông chó mèo, mạt bụi nhà, cần tây, hạt kê, và hạt sachi. Đặc biệt, dị ứng có thể xảy ra khi ăn sachi, đặc biệt đối với những người có cơ địa dị ứng. Dị Ứng cũng là phản ứng miễn dịch khi tiếp xúc với hạt sachi.\n\nTrong y học, dị ứng là một trong những dấu hiệu được tìm kiếm trong khám sức khỏe và là triệu chứng cần kiêng kỵ khi sử dụng các vị thuốc. Dị Ứng cũng được điều trị bằng các phương pháp khác nhau, bao gồm hỗn hợp hoa hương giới, hoa húng quế và lá đơn đỏ, cũng như bằng Mogrosid. Tuy nhiên, Bepanthen Balm không nên sử dụng đối với người đã từng bị dị ứng với bất kỳ thành phần nào trong sản phẩm. Người dị ứng với các cây khác thuộc họ bầu bí nên tránh dùng khổ qua rừng và cần thận trọng khi sử dụng kiều mạch.\n\nDị Ứng cũng có thể xảy ra khi sử dụng lá thúi địch và được điều trị bằng Liên kiều. Tuy nhiên, dị ứng với bất kỳ thành phần nào khác của thuốc methylprednisolone là một tình trạng không được dùng methylprednisolone. Dị Ứng cũng được điều trị bằng methylprednisolone (Depo-Medrol) trong một số trường hợp.\n\nDị Ứng cũng có thể gây sưng môi âm hộ do tiếp xúc với hóa chất gây kích ứng và cũng là phản ứng miễn dịch của cơ thể đối với các thành phần trong thuốc nhuộm. Dị Ứng cũng có thể gây viêm quanh mắt và góp phần tạo nên nếp nhăn vùng mắt. Dị Ứng là một tác dụng phụ có thể xảy ra khi tiêm chất làm đầy và cũng là một trong những nguyên nhân gây bệnh nghiến răng.\n\nDị Ứng còn được biết đến là một trong những nguyên nhân gây polyp mũi và cũng là phản ứng của cơ thể với một số thành phần hoặc hoạt chất có trong rượu ba kích. Dị Ứng với thức ăn hoặc thuốc có thể gây ra phản ứng phản vệ, và cũng là triệu chứng không mong muốn khi sử dụng rau mùi tây và rượu ba kích. Dị Ứng cũng có thể gây sốt và đổ mồ hôi. Một số trường hợp dị ứng có thể dẫn đến suy thận cấp.\n\nDị Ứng là tình trạng phản ứng miễn dịch, có thể dẫn đến các triệu chứng như sưng lưỡi gà, viêm quanh mắt, và gây ra các phản ứng nghiêm trọng như phản ứng phản vệ. Dị Ứng cũng có thể xảy ra khi sử dụng thuốc 3B Medi và Acid nalidixic hoặc các quinolon khác.\n\nDị Ứng với vinpocetin hoặc bất kỳ thành phần nào khác là chống chỉ định dùng Cavinton. Dị Ứng với các kháng sinh nhóm cephalosporin khác là chống chỉ định dùng thuốc này. Dị Ứng với Cefprozil có thể dẫn đến phản ứng quá mẫn cấp trầm trọng.\n\nDị Ứng với mycophenolate mofetil, axit mycophenolic hoặc các thành phần khác trong thuốc là lý do không sử dụng CellCept. Ceritine được sử dụng để điều trị dị ứng. Dị Ứng là phản ứng miễn dịch không mong muốn đối với bất kỳ thành phần nào có trong công thức của Chymobest. Dị Ứng với guaifenensin, ceritizin hoặc dextromethorphan là trường hợp không nên dùng Cidetuss. Dị Ứng là triệu chứng có thể xảy ra khi dùng Cimetidin. Dị Ứng với bất kỳ thành phần nào của thuốc là chống chỉ định sử dụng Claminat.\n\nDị Ứng là triệu chứng cần tránh khi sử dụng Trà Tiên và cũng là phản ứng cơ thể khi tiếp xúc với một số thành phần có trong dược liệu Trư Linh.&lt;SEP&gt;Dị ứng là phản ứng miễn dịch đối với bất kỳ thành phần nào của vị thuốc Tỳ giải.\nAceclofenac: Thuốc Aceclofenac được chỉ định để giảm đau và kháng viêm trong bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.&lt;SEP&gt;Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg, có tác dụng kháng viêm không steroid.&lt;SEP&gt;Aceclofenac là thuốc giảm đau và chống viêm không steroid (NSAID), có thể gây tác dụng phụ như tăng men gan, khó tiêu, đau bụng, buồn nôn, tiêu chảy, đầy hơi, viêm dạ dày, táo bón, nôn, loét miệng, ngứa, phát ban, viêm da, nổi mề đay, tăng urê huyết, tăng creatinin huyết, thiếu máu, phản ứng phản vệ, rối loạn thị giác, tình trạng khó thở, phân đen, phù mặt.&lt;SEP&gt;Aceclofenac là thuốc gây ra các tác dụng phụ trên hệ thần kinh, bao gồm triệu chứng như choáng váng, buồn ngủ, mệt mỏi, và rối loạn thị giác.\nQuan Y Tế: Quan y tế hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.\nAceclofenac Stada: Aceclofenac Stada là thuốc kháng viêm không steroid (NSAID).\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nBất Thường: Bất thường trong lúc sử dụng cần báo cho bác sĩ hoặc chuyên gia y tế.&lt;SEP&gt;Bất thường là triệu chứng cần báo cáo cho bác sĩ khi sử dụng thuốc Aceclofenac STADA.&lt;SEP&gt;Bất thường là triệu chứng bất lợi có thể xuất hiện khi sử dụng thuốc Chymodk.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nAceclofenac STADA 100mg: Aceclofenac STADA 100mg là thuốc kháng viêm không steroid với đặc tính giảm đau và kháng viêm, được chỉ định để điều trị bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.\nMẫn Cảm: Mẫn Cảm là một tình trạng sức khỏe liên quan đến phản ứng bất lợi hoặc dị ứng của cơ thể với một hoặc nhiều thành phần cụ thể của thuốc. Tình trạng này có thể biểu hiện dưới dạng phản ứng dị ứng khi tiếp xúc với các thành phần cụ thể của thuốc như acyclovir, valacyclovir, hoặc các thành phần khác trong các loại thuốc như A.T Calci Plus, Acnequidt 20 ml, Actiso Ladophar, Acyclovir Stada 200 mg, và Acyclovir Stella Cream. Mẫn cảm với thuốc hoặc các thành phần của thuốc là chống chỉ định đối với việc sử dụng nhiều loại thuốc khác nhau, bao gồm Agi-Calci, Agiclovir bk 5% Agimexpharm, Altamin, và Alzole. Nếu một bệnh nhân bị mẫn cảm với bất kỳ thành phần nào của những loại thuốc này, việc sử dụng chúng sẽ không được khuyến nghị do có thể gây ra các tác dụng phụ nghiêm trọng hoặc thậm chí đe dọa tính mạng.\n\nMẫn cảm cũng được ghi nhận là tình trạng bệnh nhân bị dị ứng với bất kỳ thành phần nào của Ampicillin Brawn hoặc Ampelop. Tình trạng này cũng xuất hiện khi bệnh nhân bị dị ứng hoặc không dung nạp với bất kỳ thành phần nào của thuốc hoặc với các anthraquinon glycosid khác, tạo nên một danh sách dài các thuốc chống chỉ định sử dụng trong trường hợp này, bao gồm Arthrorein Pharmanel, Asakoya Mediplantex, Bisoloc, và Bisoprolol. Việc kiểm tra kỹ lưỡng về mẫn cảm trước khi bắt đầu sử dụng bất kỳ loại thuốc nào là rất quan trọng để tránh các tác dụng phụ nghiêm trọng hoặc nguy hiểm đến tính mạng.\n\nMẫn cảm cũng được ghi nhận là phản ứng dị ứng với một số thành phần của thuốc Barudon và mẫn cảm với tenoxicam hoặc bất kỳ thành phần nào của Bart là đối tượng chống chỉ định sử dụng thuốc này. Mẫn cảm với peridopril hoặc các thuốc ức chế men chuyển khác là chống chỉ định sử dụng Beatil. Mẫn cảm với hoạt chất hoặc bất cứ thành phần nào của thuốc là triệu chứng cần được giám sát đặc biệt khi sử dụng Belara. Mẫn cảm cũng có thể xảy ra khi sử dụng Betadine Gargle &amp; Mouth Wash. Cuối cùng, mẫn cảm với cao khô lá Ginkgo biloba hoặc bất kỳ thành phần nào của thuốc Bilomag là chống chỉ định. Trong tất cả các trường hợp, việc sử dụng thuốc khi có mẫn cảm với bất kỳ thành phần nào của thuốc là chống chỉ định và có thể dẫn đến các rủi ro sức khỏe nghiêm trọng, bao gồm cả việc sử dụng thuốc amoxicillin + acid clavulanid trong thời kỳ cho con bú, có thể dẫn đến các rủi ro sức khỏe cho cả mẹ và trẻ sơ sinh.\n\nNgoài ra, mẫn cảm còn được ghi nhận là phản ứng không mong muốn khi dùng cỏ mật, tình trạng dị ứng hoặc phản ứng bất lợi với một số thành phần trong kem, tình trạng dị ứng kéo dài sau điều trị bằng Crotamiton, tình trạng không nên sử dụng củ nén, chống chỉ định khi sử dụng trihexyphenidyl, và tình trạng mẫn cảm với bất kỳ thành phần nào trong Danospan hay Davita Bone Sugar Free đều là chống chỉ định.\n\nMẫn cảm cũng được ghi nhận là tình trạng dị ứng hoặc phản ứng dị ứng với một số thành phần của thuốc Betmiga 50 mg, mẫn cảm với thuốc hoặc các chất ức chế ACE như Captopril, mẫn cảm với carbimazol hoặc các dẫn chất thioimidazol như thiamazol, mẫn cảm với cefpodoxim, mẫn cảm với penicillin, và mẫn cảm với Clonazepam hoặc các chất thuộc nhóm benzodiazepin.\n\nTóm lại, mẫn cảm là một tình trạng sức khỏe nghiêm trọng cần được phát hiện và quản lý cẩn thận để ngăn ngừa các tác dụng phụ nguy hiểm. Tình trạng này có thể xảy ra khi sử dụng thuốc và có thể là dấu hiệu của phản ứng miễn dịch, dị ứng hoặc không dung nạp với pregabalin hoặc các thành phần khác của thuốc.&lt;SEP&gt;Mẫn cảm là tình trạng dị ứng hoặc nhạy cảm với một số thành phần trong thuốc.&lt;SEP&gt;Mẫn cảm là một triệu chứng phản ứng dị ứng với axit salicylic.&lt;SEP&gt;Mẫn cảm với bất kỳ thành phần nào của thuốc là chống chỉ định.&lt;SEP&gt;Người có trạng thái mẫn cảm với bất kỳ dược chất nào trong tinh dầu hương thảo cần tham khảo ý kiến bác sĩ trước khi sử dụng.&lt;SEP&gt;Mẫn cảm là tình trạng dị ứng hoặc nhạy cảm với các dược chất trong tinh dầu hương thảo.&lt;SEP&gt;Mẫn cảm là phản ứng cơ thể khi tiếp xúc với một số thành phần có trong dược liệu Trư linh.\nNguy Hiểm Tính Mạng: Nguy hiểm tính mạng là hậu quả nghiêm trọng có thể xảy ra khi uống quá liều Aceclofenac STADA.\nSymptom: Mẫn cảm là phản ứng dị ứng với một số thuốc.\nAceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac, được chỉ định để giảm đau và kháng viêm trong bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.\nDị Ứng Thuốc: Phản ứng dị ứng thuốc là tác dụng phụ ít gặp khi sử dụng Alzental.&lt;SEP&gt;Dị ứng thuốc là biểu hiện cần phải ngừng dùng thuốc và thông báo cho bác sĩ.\nThông Tin Sử Dụng Thuốc: Thông tin sử dụng thuốc Acemol 325 mg bao gồm hướng dẫn bảo quản và cảnh báo về các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Thông tin hướng dẫn sử dụng Dalacin T nhằm đảm bảo hiệu quả và an toàn khi sử dụng.\nAceclofenac - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tiêu chảy là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nDị Ứng - Quan Y Tế: Quan y tế hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.\nAceclofenac - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nDị Ứng - Thuốc: Nếu xuất hiện dị ứng khi dùng thuốc, bạn hãy báo ngay cho bác sĩ.&lt;SEP&gt;Dị ứng là triệu chứng miễn dịch ít gặp khi sử dụng thuốc.&lt;SEP&gt;Dị ứng với thuốc có thể gây ra mề đay.\nAceclofenac - Táo Bón: Táo bón là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nDị Ứng - Vị Thuốc: Dị ứng với bất kỳ thành phần nào của vị thuốc là triệu chứng cần tránh.&lt;SEP&gt;Vị thuốc có thể gây dị ứng với một số người.\nAceclofenac - Suy Thận: Không nên sử dụng Aceclofenac trên các đối tượng bị suy thận mức độ vừa đến nặng.&lt;SEP&gt;Suy thận là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nMẫn Cảm - Symptom: Mẫn cảm là phản ứng dị ứng với một số thuốc.\nAceclofenac - Đau Bụng: Đau bụng là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nDị Ứng Thuốc - Nổi Mề Đay: Nổi mề đay là triệu chứng của dị ứng thuốc.\nAceclofenac - Mệt Mỏi: Mệt mỏi là tác dụng phụ của Aceclofenac.\nDị Ứng - Thuốc Ức Chế Men Chuyển: Thuốc ức chế men chuyển có thể gây dị ứng.\nAceclofenac - Nôn: Nôn là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nDị Ứng Thuốc - Khó Nuốt: Khó nuốt là triệu chứng của dị ứng thuốc.\nAceclofenac Stada - Tăng Huyết Áp: Aceclofenac Stada có thể gây tăng huyết áp.\nThuốc Bột - Viêm Da Tiếp xúc Thể Dị Ưng: Thuốc bột có thể gây kích ứng hoặc dị ứng.\nAceclofenac - Suy Tim: Suy tim là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nDị Ứng - Thuốc Chống Dị Ứng: Thuốc chống dị ứng được sử dụng để điều trị dị ứng.\nAceclofenac - Ngứa: Ngứa là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nChất Gây Dị Ứng - Dấu Hiệu Dị Ứng: Dấu hiệu dị ứng cần được chú ý bởi người lớn.\nAceclofenac - Phụ Nữ Có Thai: Aceclofenac chống chỉ định trong thai kỳ trừ khi lợi ích điều trị cho mẹ vượt trội nguy cơ gây hại cho thai nhi.\nAceclofenac - Thiếu Máu: Thiếu máu là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Thiếu máu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac Stada - Mệt Mỏi: Aceclofenac Stada có thể gây mệt mỏi.\nAceclofenac - Suy Gan: Suy gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac Stada - Suy Tim: Aceclofenac Stada có thể gây suy tim.\nAceclofenac - Hạ Huyết Áp: Hạ huyết áp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nhức Đầu: Nhức đầu là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Hô Hấp: Suy hô hấp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Co Giật: Co giật là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAceclofenac - Phụ Nữ Cho Con Bú: Aceclofenac không nên dùng trong giai đoạn đang cho con bú.\nAceclofenac - Đầy Hơi: Đầy hơi là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Khớp Dạng Thấp: Aceclofenac được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac - Khó Tiêu: Khó tiêu là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Buồn Ngủ: Buồn ngủ là tác dụng phụ của Aceclofenac.\nAceclofenac - Phát Ban: Phát ban là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac STADA - Quá Liều: Quá liều Aceclofenac STADA có thể gây nguy hiểm tính mạng.\nAceclofenac - Viêm Da: Viêm da là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Suy Thận Cấp: Suy thận cấp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Ù Tai: Ù tai là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nổi Mề Đay: Nổi mề đay là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac STADA - Giảm Đau: Aceclofenac STADA được chỉ định để giảm đau.\nAceclofenac - Viêm Dạ Dày: Viêm dạ dày là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Hôn Mê: Hôn mê là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Người Cao Tuổi: Khả năng phân bố, chuyển hóa, hấp thu và thải trừ của Aceclofenac không thay đổi ở bệnh nhân cao tuổi, do đó không cần phải thay đổi liều hoặc tần suất sử dụng.\nAceclofenac - Thuốc Lợi Tiểu: Thuốc lợi tiểu có thể tương tác với Aceclofenac.\nAceclofenac STADA 100mg - Viêm Khớp Dạng Thấp: Aceclofenac STADA 100mg được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac Stada - Buồn Ngủ: Aceclofenac Stada có thể gây buồn ngủ.\nAceclofenac - Phản Ứng Phản Vệ: Phản ứng phản vệ là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Hệ Thần Kinh: Aceclofenac gây ra các tác dụng phụ trên hệ thần kinh.\nAceclofenac - Rửa Dạ Dày: Rửa dạ dày là biện pháp dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac STADA - Trẻ Em: Aceclofenac STADA cần được bảo quản tránh xa tầm tay của trẻ em.\nAceclofenac - Corticosteroids: Corticosteroids có thể tương tác với Aceclofenac.\nAceclofenac - Rối Loạn Thị Giác: Rối loạn thị giác là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Rối loạn thị giác là tác dụng phụ của Aceclofenac.\nAceclofenac - Viêm Xương Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm xương khớp.\nAceclofenac - Prostaglandin: Aceclofenac ức chế tổng hợp prostaglandin.\nAceclofenac - Loét Miệng: Loét miệng là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Chống Đông: Thuốc chống đông có thể tương tác với Aceclofenac.\nAceclofenac - Nôn Ra Máu: Nôn ra máu là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Tăng Men Gan: Tăng men gan là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Choáng Váng: Choáng váng là tác dụng phụ của Aceclofenac.\nBác Sĩ - Bất Thường: Người dùng cần báo bất thường cho bác sĩ.&lt;SEP&gt;Bác sĩ sẽ đưa ra hướng xử lý phù hợp và kịp thời nhất đối với bất thường.\nAceclofenac - Kích Động: Kích động là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Ngất: Ngất là triệu chứng khi quá liều Aceclofenac.\nAceclofenac STADA - Chống Viêm: Aceclofenac STADA được chỉ định để chống viêm.\nAceclofenac - Xuất Huyết Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng nghi ngờ có xuất huyết tiêu hóa.&lt;SEP&gt;Xuất huyết tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.&lt;SEP&gt;Xuất huyết tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Methotrexat: Methotrexat có thể tương tác với Aceclofenac.\nAceclofenac - Suy Giảm Chức Năng Gan: Liều dùng khởi đầu được đề nghị là 100 mg/ngày (1 viên/ngày) cho những bệnh nhân suy gan.\nAceclofenac - Tổn Thương Gan: Tổn thương gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Glycosid Tim: Glycosid tim có thể tương tác với Aceclofenac.\nAceclofenac - Tacrolimus: Tacrolimus có thể tương tác với Aceclofenac.\nAceclofenac - Than Hoạt Tính: Than hoạt tính được dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Phù Mặt: Phù mặt là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Đau Vùng Thượng Vị: Đau vùng thượng vị là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Phân Đen: Phân đen là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Ciclosporin: Ciclosporin có thể tương tác với Aceclofenac.\nAceclofenac - Zidovudin: Zidovudin có thể tương tác với Aceclofenac.\nAceclofenac - Lithi: Lithi có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Điều Trị Tăng Huyết Áp: Thuốc điều trị tăng huyết áp có thể tương tác với Aceclofenac.\nAceclofenac - Buồn Nôn, Nôn: Buồn nôn và nôn là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Aceclofenac STADA 100mg: Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg.\nAceclofenac - Cyclooxygenase: Aceclofenac ức chế cyclooxygenase.\nAceclofenac - Kích Ứng Tiêu Hóa: Kích ứng tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Loét Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng đã từng bị loét tiêu hóa tiến triển trước đó.\nAceclofenac - Tăng Creatinin Huyết: Tăng creatinin huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Đốt Sống Dính Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm đốt sống dính khớp.\nAceclofenac - Suy Thai: Suy thai là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiêu Hóa: Suy tiêu hóa là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Mifepriston: Mifepriston có thể tương tác với Aceclofenac.\nAceclofenac - Kháng Sinh Nhóm Quinolon: Kháng sinh nhóm quinolon có thể tương tác với Aceclofenac.\nAceclofenac - Thủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Loxoprofen: Loxoprofen có tác dụng giảm đau và kháng viêm tương tự như Aceclofenac.\nAceclofenac - Bị Mất Phương Hướng: Bị mất phương hướng là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Não: Suy não là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Viêm: Suy viêm là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Khớp: Suy khớp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Mi: Suy mi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Phổi: Suy phổi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Thần Kinh: Suy thần kinh là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Niệu: Suy tiết niệu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Dịch: Suy tiết dịch là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Protein: Suy tiết protein là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone: Suy tiết hormone là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid: Suy tiết hormone tiroid là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B12: Suy tiết hormone tiroid B12 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B13: Suy tiết hormone tiroid B13 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B14: Suy tiết hormone tiroid B14 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B15: Suy tiết hormone tiroid B15 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B16: Suy tiết hormone tiroid B16 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B17: Suy tiết hormone tiroid B17 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B18: Suy tiết hormone tiroid B18 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B19: Suy tiết hormone tiroid B19 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B20: Suy tiết hormone tiroid B20 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Gàn: Liều dùng Aceclofenac cần được giảm cho những bệnh nhân suy gan.\nAceclofenac - Aceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac.\nAceclofenac - Tình Trạng Khó Thở: Tình trạng khó thở là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Giảm Đau Khác: Thuốc giảm đau khác bao gồm các thuốc ức chế chọn lọc cyclooxygenase-2 có thể tương tác với Aceclofenac.\nAceclofenac - Tác Nhân Kháng Tiểu Phần: Tác nhân kháng tiểu phần có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Ức Chế Chọn Lọc Thu Hồi Serotonin (SSRI): Thuốc ức chế chọn lọc thu hồi serotonin (SSRI) có thể tương tác với Aceclofenac.\nAceclofenac - Nhóm Thuốc Trị Đái Tháo Đường: Nhóm thuốc trị đái tháo đường có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Kháng Viêm Không Steroid (NSAID) Khác: Thuốc kháng viêm không steroid (NSAID) khác có thể tương tác với Aceclofenac, tạo ra nguy cơ xuất huyết tiêu hóa.\nAceclofenac Stada - Người Cao Tuổi: Aceclofenac Stada có thể gây tác dụng phụ trên người cao tuổi.\nAceclofenac Stada - Phù Nề: Aceclofenac Stada có thể gây phù nề.\nAceclofenac STADA - Ánh Sáng: Aceclofenac STADA cần được bảo quản tránh tiếp xúc trực tiếp với ánh sáng.\nAceclofenac Stada - Rối Loạn Thị Giác: Aceclofenac Stada có thể gây rối loạn thị giác.\nAceclofenac Stada - Nôn Ra Máu: Aceclofenac Stada có thể gây nôn ra máu.\nAceclofenac Stada - Choáng Váng: Aceclofenac Stada có thể gây choáng váng.\nBất Thường - Chymodk: Khi xuất hiện bất kỳ triệu chứng bất thường nào, cần gọi ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.\nAceclofenac Stada - Xuất Huyết Tiêu Hóa: Aceclofenac Stada có thể gây xuất huyết tiêu hóa.\nAcemol 325 mg - Thông Tin Sử Dụng Thuốc: Thông tin sử dụng thuốc Acemol 325 mg cung cấp hướng dẫn bảo quản và cảnh báo về các tác dụng phụ nghiêm trọng.\nAceclofenac STADA 100mg - Viêm Xương Khớp: Aceclofenac STADA 100mg được chỉ định để điều trị bệnh viêm xương khớp.\nAceclofenac STADA - Thú Cưng: Aceclofenac STADA cần được bảo quản tránh xa tầm tay của thú cưng.\nAceclofenac Stada - Phân Đen: Aceclofenac Stada có thể gây phân đen.\nAceclofenac Stada - Khả Năng Sinh Sản: Aceclofenac Stada có thể suy giảm khả năng sinh sản.\nAceclofenac Stada - Thuốc NSAID: Aceclofenac Stada thuộc nhóm thuốc NSAID.\nAceclofenac Stada - Nguy Cơ Xuất Huyết Tiêu Hóa: Aceclofenac Stada có nguy cơ gây xuất huyết tiêu hóa.\nAceclofenac Stada - Thủng Loét Đường Tiêu Hóa: Aceclofenac Stada có thể gây thủng loét đường tiêu hóa.\nAceclofenac Stada - Suy Thận Nhẹ: Aceclofenac Stada có thể gây suy thận nhẹ.\nAceclofenac Stada - Suy Chức Năng Gan Nghiêm Trọng: Aceclofenac Stada có thể gây suy chức năng gan nghiêm trọng.\nAceclofenac Stada - Rối Loạn Chuyển Hóa Porphyrin Ở Gan: Aceclofenac Stada có thể kích hoạt cơn bệnh rối loạn chuyển hóa porphyrin ở gan.\nAceclofenac Stada - Hẹn Phế Quản: Aceclofenac Stada có thể gây co thắt phế quản ở những bệnh nhân mắc bệnh hen phế quản.\nBất Thường - Chuyên Gia Y Tế: Người dùng cần báo bất thường cho chuyên gia y tế.&lt;SEP&gt;Chuyên gia y tế sẽ đưa ra hướng xử lý phù hợp và kịp thời nhất đối với bất thường.\nAceclofenac STADA - Nhiệt Độ Bảo Quản: Aceclofenac STADA cần được bảo quản ở nhiệt độ dưới 30ºC.\nAceclofenac STADA - Bất Thường: Bất thường là triệu chứng cần báo cáo cho bác sĩ khi sử dụng Aceclofenac STADA.\nAceclofenac STADA - Liều Kế Tiếp: Liều kế tiếp là liều thuốc tiếp theo trong lịch trình sử dụng Aceclofenac STADA.\nAceclofenac STADA - Bỏ Qua Liều Đã Quên: Khi quên một liều Aceclofenac STADA, nên bỏ qua liều đã quên và tiếp tục theo lịch trình sử dụng.\nAceclofenac STADA - Địa Điểm Ẩm Ướt: Aceclofenac STADA cần được bảo quản tránh những nơi ẩm ướt.\nDalacin T - Thông Tin Sử Dụng Thuốc: Thuốc Dalac</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nếu bạn nghi ngờ mình bị dị ứng với thuốc Aceclofenac STADA, bạn cần báo cho bác sĩ ngay lập tức. Dị ứng với bất kỳ thành phần nào của thuốc là một tình trạng nghiêm trọng và cần được xử lý kịp thời. Dị ứng có thể biểu hiện dưới dạng nổi mề đay, khó thở, hoặc các triệu chứng khác. Việc thông báo sớm sẽ giúp bác sĩ có thể đưa ra quyết định phù hợp và kịp thời nhất để xử lý tình huống này.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA, hãy ngừng dùng thuốc và đến gặp bác sĩ để được tư vấn và điều trị kịp thời.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9678503191339226</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9919625797584807</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>['Thuốc Nhẹ: Thuốc nhẹ là loại thuốc cần tránh uống ngay sau khi dùng Barudon.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nGiảm Vị Giác: Giảm vị giác là tác dụng phụ có thể xảy ra khi sử dụng quá liều Barudon.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nLoét Dạ Dày- Tá Tràng: Loét dạ dày- tá tràng là tình trạng bệnh liên quan đến việc sử dụng Barudon để giảm đau.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nTriệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nTác Dụng Phản Ứng: Tác dụng phản ứng không mong muốn cần được dừng sử dụng và đến cơ sở y tế.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nTư Vấn Hỗ Trợ: Bệnh nhân cần liên hệ bác sĩ để được tư vấn hỗ trợ khi gặp tác dụng phụ của thuốc.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nKhó Tiêu Axit: Khó tiêu axit là triệu chứng liên quan đến việc sử dụng Barudon để giảm đau.&lt;SEP&gt;Khó tiêu axit là triệu chứng được điều trị bằng các thuốc kháng axit.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nTê Miệng: Tê miệng là triệu chứng có thể xảy ra khi nuốt Barudon.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nBan Đỏ, Phù Mặt, Khó Thở: Ban đỏ, phù mặt, khó thở là dấu hiệu bất thường cần ngừng thuốc và liên hệ bác sĩ.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTác Dụng Phản: Tác dụng phụ không được liệt kê cụ thể trong đoạn văn nhưng có thể bao gồm các vấn đề liên quan đến đường tiêu hóa.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nGiải Đáp: Giải đáp là phương pháp trả lời và giải thích cho thắc mắc của người dùng thuốc.\nNgười Dùng Thuốc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nPregabalin - Triệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nBarudon - Thuốc Nhẹ: Người dùng Barudon không nên uống thuốc nhẹ ngay sau khi dùng thuốc.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nBarudon - Giảm Vị Giác: Barudon có thể gây giảm vị giác khi sử dụng quá liều.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nBarudon - Loét Dạ Dày- Tá Tràng: Barudon được sử dụng để giảm đau nhanh trong các trường hợp liên quan đến loét dạ dày- tá tràng.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nBệnh Nhân - Tư Vấn Hỗ Trợ: Bệnh nhân cần liên hệ bác sĩ để được tư vấn hỗ trợ khi gặp tác dụng phụ của thuốc.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nBarudon - Khó Tiêu Axit: Barudon được sử dụng để điều trị khó tiêu axit.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBarudon - Tê Miệng: Tê miệng là triệu chứng có thể xảy ra khi sử dụng Barudon.\nBác Sĩ - Tác Dụng Phụ: Bác sĩ cần thông báo nếu có tác dụng phụ khi dùng thuốc.\nAzithromycin DHG - Tác Dụng Phản Ứng: Ngừng sử dụng Azithromycin DHG khi có tác dụng phản ứng không mong muốn.\nGiải Đáp - Người Dùng Thuốc: Giải đáp cung cấp thông tin phản hồi cho người dùng thuốc.\nBan Đỏ, Phù Mặt, Khó Thở - Ciprofloxacine: Ban đỏ, phù mặt, khó thở là dấu hiệu bất thường cần ngừng thuốc và liên hệ bác sĩ.\nAcritel - Tác Dụng Phụ: Thuốc Acritel có hướng dẫn sử dụng cụ thể về cách xử lý tác dụng phụ.\nKháng Sinh Phổ Rộng - Tác Dụng Phụ: Sử dụng kháng sinh có liên quan đến nhiều tác dụng phụ.']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Khi sử dụng Barudon, nếu gặp bất kỳ phản ứng phụ nào, người dùng cần liên hệ với cơ sở y tế để được thăm khám cụ thể. Các tác dụng phụ có thể gặp bao gồm:
+- Tăng magnesi huyết
+- Giảm chức năng thận
+- Khô miệng
+- Giảm vị giác
+Người dùng cũng cần chú ý đến các triệu chứng như tê miệng và khó tiêu axit khi sử dụng Barudon. Nếu gặp các triệu chứng này hoặc bất kỳ tác dụng phụ khác, cần đến ngay cơ sở y tế gần nhất để được tư vấn hoặc xử trí kịp thời, hạn chế tác dụng phụ của Barudon khi sử dụng.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần liên hệ với cơ sở y tế để được thăm khám cụ thể.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7532780269975768</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7716528400577276</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>['Mẫn Cảm Với Spironolactone: Mẫn cảm với spironolactone là tình trạng dị ứng với thành phần chính của Aldactone, chống chỉ định sử dụng Aldactone.\nCây Thuốc: Nghiên cứu lâm sàng cần thiết để phát huy tiềm năng của cây thuốc.\nThuốc Chặn Aldosterone: Thuốc chặn aldosterone là loại thuốc có thể dẫn đến tăng kali huyết khi sử dụng cùng spironolactone.\nĐộc Tính: Độc Tính là thuật ngữ mô tả nhiều tình trạng khác nhau liên quan đến tác dụng độc hại của các chất hoặc dược liệu. Trong y học và sinh học, độc tính thường được sử dụng để chỉ các triệu chứng có thể xảy ra khi sử dụng một số loại thuốc như Methotrexate, Sulphonylurea, Phenytoin, hoặc Acid Valproic cùng với Aspirin. Ngoài ra, độc tính cũng có thể xảy ra do việc tiêu thụ biển súc, một loài động vật biển, làm thức ăn cho động vật như ngựa, cừu hoặc chim bồ câu, gây ra rối loạn tiêu hóa. Điều này cho thấy rằng các loại thực phẩm và dược liệu khác nhau có thể mang lại tác dụng độc hại đối với cơ thể.\n\nTrong nghiên cứu khoa học, độc tính cũng được đề cập đến trong quá trình nghiên cứu về tác dụng độc hại của chiết xuất lá xương khỉ trên súc vật thí nghiệm. Một số loại cây như bồ bồ không có độc tính, vì đã thử nghiệm với liều lượng gấp 20 lần liều có tác dụng mà súc vật vẫn sống an toàn. Độc tính còn được sử dụng để mô tả tình trạng bị ảnh hưởng bởi chất độc, đây là một tình trạng phổ biến mà mọi người có thể gặp phải khi tiếp xúc với các chất độc hại. Chẳng hạn, dược liệu từ Chè dây có thể gây ra độc tính cấp tính, tức là gây ra tác dụng độc hại nhanh chóng. Cuối cùng, độc tính cũng được đề cập trong Nhựa Cóc, một loại nhựa tự nhiên, nơi mà độc tính có thể gây ra hậu quả nghiêm trọng, thậm chí có thể giết chết 4-5 người trưởng thành khỏe mạnh. Điều này nhấn mạnh sự cần thiết phải nghiên cứu kỹ lưỡng về độc tính của các chất tự nhiên và dược liệu để đảm bảo an toàn sức khỏe cho con người.\n\nĐộc tính cũng được đề cập trong nhiều trường hợp cụ thể khác. Ví dụ, độc tính từ dừa cạn, chất dầu trong hạt hoa đậu biếc, Hoàng nàn, Kê huyết đằng, Keo giậu, và La bạc tử đều có thể gây ra tác dụng độc hại. Đặc biệt, độc tính từ rễ và quả cây hương bài có thể gây tử vong nếu ăn nhầm. Những tác dụng độc hại này có thể xuất hiện khi tiêm hoặc uống với liều lượng cao. Do đó, việc giảm độc tính mạnh của Hoàng nàn trước khi sử dụng là rất quan trọng để đảm bảo an toàn cho người dùng.\n\nĐộc Tính còn được sử dụng để mô tả tác dụng phụ nghiêm trọng từ việc sử dụng một số dược liệu và thực phẩm. Lược vàng có thể gây ra tác dụng phụ khi sử dụng lâu dài hoặc ở liều cao. Mã tiền cũng có thể gây ra tác dụng phụ nghiêm trọng. Mướp sát có độc tính gây hại. Polysaccharides từ nấm có thể gây độc hại đối với gan, thận, tim, tuyến ức, và lá lách của chuột. Hạt Nhục đậu khấu có độc tính không chắc chắn, mặc dù các báo cáo trường hợp cho thấy rằng nếu uống đủ liều, độc tính cấp tính có thể xảy ra. Phụ tử cũng có độc tính đối với cơ thể con người. Sâu ban miêu có độc tính nguy hiểm gây ra tác hại lớn.\n\nTóm lại, Độc Tính là một khái niệm rộng lớn, bao gồm nhiều dạng tác dụng độc hại khác nhau từ các chất, thuốc, thực phẩm, và cả tự nhiên, đòi hỏi sự hiểu biết sâu sắc và nghiên cứu kỹ lưỡng để xác định và phòng ngừa các tác động độc hại.&lt;SEP&gt;Độc tính là yếu tố nguy hiểm có trong cây thuốc.\nSpironolactone (Aldactone): Spironolactone (Aldactone) là thuốc lợi tiểu có thể gây bất lực.&lt;SEP&gt;Spironolactone (Aldactone) là thuốc kháng androgen ngăn chặn tác động của hormone androgen trên da.\nHút Thuốc: Hút thuốc là hành vi có nhiều tác hại nghiêm trọng đến sức khỏe, bao gồm cả tác động đến hệ thống tim mạch, da, gan, và khả năng đáp ứng với các loại thuốc khác nhau. Đầu tiên, hút thuốc là yếu tố làm tăng nguy cơ mắc bệnh mạch máu ngoại biên, gây ra bệnh cước và tăng tốc độ xơ cứng động mạch. Nó cũng là yếu tố nguy cơ đối với ung thư thanh quản hầu (TNB) và có thể đóng vai trò gây ung thư TNB. Hút thuốc còn làm hỏng mạch máu, tăng nguy cơ mắc bệnh tim mạch và làm trầm trọng thêm hiệu ứng lạnh do lưu lượng máu giảm đến bàn tay và bàn chân. Ngoài ra, hút thuốc có thể làm tăng axit dạ dày và kích hoạt cơn co giật, gây thêm sự phức tạp trong việc quản lý các triệu chứng và bệnh lý liên quan đến hút thuốc.\n\nHút thuốc gây tổn hại cho da bằng cách làm hỏng collagen và elastin, thu hẹp các mạch máu, giảm cung cấp chất dinh dưỡng và oxy cho da. Điều này không chỉ làm xấu đi tình trạng của da mà còn góp phần vào việc làm suy yếu cấu trúc da. Hút thuốc lâu dài có thể làm phá hủy các động mạch, tạo ra các mảng xơ vữa do tích tụ cholesterol, dẫn đến tắc nghẽn động mạch vành, đây là một trong những nguyên nhân chính gây tử vong từ bệnh tim mạch.\n\nNgoài ra, hút thuốc còn gây tăng nguy cơ nhiễm trùng đường hô hấp trên, gây nấm thanh quản, góp phần tạo nên các nếp nhăn tĩnh và là yếu tố nguy cơ chính gây ra phình động mạch chủ. Hút thuốc cũng là yếu tố gây hại cho gan, được ngăn chặn bởi Cosele, và có thể ảnh hưởng đến sự tiến triển của bệnh u nhú thanh quản.\n\nHút thuốc là yếu tố nguy cơ chính gây ung thư phổi và ung thư thận. Nó cũng là nguyên nhân phổ biến của viêm phế quản mãn tính và khí phế thũng. Hút thuốc là một trong những yếu tố nguy cơ làm tăng khả năng mắc rối loạn nhận thức thần kinh và gây suy giảm nhận thức. Thói quen hút thuốc ở bà mẹ, bao gồm cả hút thuốc chủ động và thụ động, là hình thức lạm dụng chất kích thích và có thể gây ra tăng nguy cơ mắc hội chứng tăng trưởng intrauterine giảm (IUGR).&lt;SEP&gt;Hút thuốc có thể gây thiếu máu do thiếu vitamin C.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ liên quan đến xơ vữa động mạch.&lt;SEP&gt;Hút thuốc là yếu tố cần tránh khi sử dụng Aspilets EC.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ biến chứng tim mạch.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ làm tăng khả năng phát triển ung thư cổ tử cung.\nRối Loạn Tiêu Hóa, Buồn Nôn: Rối loạn tiêu hóa, buồn nôn là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nRối Loạn Nhận Thức Thần Kinh: Rối loạn nhận thức thần kinh là tình trạng suy giảm khả năng nhận biết và xử lý thông tin.&lt;SEP&gt;Rối loạn nhận thức thần kinh là tình trạng suy giảm khả năng nhận thức do nguyên nhân thần kinh.&lt;SEP&gt;Rối loạn nhận thức thần kinh là bệnh không có thuốc hoặc phương pháp điều trị được cấp phép.\nAldactone: Aldactone là thuốc chứa hoạt chất spironolactone, thuộc nhóm lợi tiểu, được chỉ định trong các trường hợp suy tim sung huyết, tăng huyết áp vô căn, kiểm soát chứng rậm lông, phối hợp với thuốc lợi tiểu gây giảm Kali/Magie máu, điều trị ngắn hạn chứng tăng aldosterone nguyên phát trước phẫu thuật, và các bệnh có thể gây tăng aldosterone thứ phát như xơ gan kết hợp với phù/cổ trướng, hội chứng thận hư và các trạng thái phù khác.&lt;SEP&gt;Aldactone (spironolactone) là thuốc được sử dụng để điều trị các tình trạng như suy tim, xơ gan, hội chứng thận hư, giảm kali/magie huyết, và tăng aldosterone nguyên phát.&lt;SEP&gt;Thuốc Aldactone được sử dụng để điều trị tăng huyết áp và một số tình trạng y tế khác, có thể tương tác với các thuốc khác như lợi tiểu và digoxin.&lt;SEP&gt;Aldactone là thuốc chứa hoạt chất spironolactone, thuộc nhóm lợi tiểu, được chỉ định để kiểm soát huyết áp hoặc hỗ trợ trong điều trị suy tim.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nThuốc Ngăn Chặn Aldosterone: Thuốc ngăn chặn aldosterone như spironolactone và eplerenone được sử dụng để điều trị bệnh aldosterone nguyên phát.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nThuốc Đối Kháng Angiotensin II: Thuốc đối kháng angiotensin II là loại thuốc có thể dẫn đến tăng kali huyết khi sử dụng cùng spironolactone.\nNguy Cơ Ung Thư: Nguy cơ ung thư có thể là tác dụng phụ của thuốc hóa trị.&lt;SEP&gt;Người bị bệnh thận lupus có nguy cơ cao mắc ung thư, đặc biệt là ung thư hạch bạch huyết tế bào lympho B.\nBất Thường Liên Quan Đến Chức Năng Gan: Bất thường liên quan đến chức năng gan là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Bất thường liên quan đến chức năng gan là triệu chứng hệ thống gan mật do thuốc Aldactone gây ra.\nThuốc Hóa Trị: Thuốc hóa trị là loại thuốc dùng trong điều trị ung thư, có khả năng tiêu diệt tế bào ung thư trong các bệnh như Ewing sarcoma. Tuy nhiên, thuốc hóa trị cũng có thể gây ra nhiều tác dụng phụ đáng kể. Chúng có thể làm hỏng mô phổi và gây ra sự nhạy cảm của da. Ngoài ra, một số loại thuốc hóa trị, ví dụ như cisplatin, có thể dẫn đến tình trạng hạ canxi máu. Thuốc hóa trị còn có khả năng làm giảm ham muốn tình dục và khả năng đạt cực khoái, đồng thời cũng ảnh hưởng đến khả năng sinh sản của người bệnh. Mặc dù thuốc hóa trị có khả năng ngăn chặn hệ thống miễn dịch, nhưng việc sử dụng chúng cần được cân nhắc kỹ lưỡng do những tác dụng phụ nghiêm trọng mà chúng có thể gây ra.\nThuốc Lợi Tiểu Giữ Kali: Thuốc lợi tiểu giữ kali, bao gồm spironolactone và amiloride, là nguyên nhân gây tăng kali máu.&lt;SEP&gt;Thuốc lợi tiểu giữ kali là loại thuốc có thể dẫn đến tăng kali huyết khi sử dụng cùng spironolactone.&lt;SEP&gt;Thuốc lợi tiểu giữ kali có thể tương tác với Candesartan.&lt;SEP&gt;Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.&lt;SEP&gt;Thuốc lợi tiểu giữ kali là loại thuốc có thể tương tác với Cozaar.\nAldactone - Buồn Nôn: Aldactone gây buồn nôn.\nCây Thuốc - Độc Tính: Cây thuốc chứa nhiều độc tính nguy hiểm.\nAldactone - Chóng Mặt: Aldactone gây chóng mặt.\nHút Thuốc - Rối Loạn Nhận Thức Thần Kinh: Hút thuốc có thể gây rối loạn nhận thức.\nAldactone - Tăng Huyết Áp: Aldactone được sử dụng để điều trị tăng huyết áp.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nThuốc Ngăn Chặn Aldosterone - Tăng Huyết Áp: Thuốc ngăn chặn aldosterone như spironolactone và eplerenone được sử dụng để điều trị tăng huyết áp.\nNguy Cơ Ung Thư - Thuốc Hóa Trị: Thuốc hóa trị có thể gây ra nguy cơ ung thư.\nAldactone - Suy Tim: Aldactone được sử dụng để điều trị suy tim.\nThuốc - Việc Sử Dụng Sai Lầm: Sử dụng thuốc sai cách có thể dẫn đến việc sử dụng sai thuốc.\nAldactone - Ngứa: Aldactone gây ngứa.\nQuá Liều - Thuốc A.T.P: Nguy cơ của việc dùng quá liều thuốc A.T.P.\nAldactone - Ung Thư: Thuốc Aldactone có thể tạo các khối u lành tính, ác tính và không đặc hiệu.\nThuốc lá - Ợ H nóng: Thuốc lá có thể gây ợ nóng.\nAldactone - Aspirin: Aspirin làm suy giảm tác dụng của Aldactone.\nDị Ứng - Vị Thuốc: Dị ứng với bất kỳ thành phần nào của vị thuốc là triệu chứng cần tránh.&lt;SEP&gt;Vị thuốc có thể gây dị ứng với một số người.\nAldactone - Rối Loạn Tiêu Hóa: Aldactone gây rối loạn tiêu hóa.\nThuốc - Tác Dụng Phụ Nghiêm Trọng: Một số loại thuốc có thể gây tác dụng phụ nghiêm trọng.\nAldactone - Phát Ban: Aldactone gây phát ban.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nAldactone - Rối Loạn Điện Giải: Rối loạn điện giải là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Phù: Aldactone được sử dụng để điều trị phù.\nAldactone - Hội Chứng Thận Hư: Aldactone được chỉ định điều trị hội chứng thận hư.&lt;SEP&gt;Aldactone được sử dụng để điều trị hội chứng thận hư.\nAldactone - Suy Thận Cấp: Aldactone gây suy thận cấp.\nAldactone - Suy Nhược: Aldactone gây suy nhược.\nAldactone - Mề Đay: Aldactone gây mề đay.\nAldactone - Xơ Gan: Aldactone được sử dụng để điều trị xơ gan.\nAldactone - Giảm Bạch Cầu: Giảm bạch cầu là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Rụng Tóc: Aldactone gây rụng tóc.\nSpironolactone (Aldactone) - Viêm Da: Spironolactone (Aldactone) được sử dụng để chữa trị viêm da.\nAldactone - Digoxin: Aldactone làm tăng thời gian bán thải của digoxin.\nAldactone - Bệnh Addison: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc bệnh Addison.\nAldactone - Spironolactone: Aldactone chứa hoạt chất spironolactone.\nAldactone - Suy Tim Sung Huyết: Aldactone được chỉ định điều trị suy tim sung huyết.\nAldactone - Tăng Huyết Áp Vô Căn: Aldactone được chỉ định điều trị tăng huyết áp vô căn.\nAldactone - Indomethacin: Indomethacin làm suy giảm tác dụng của Aldactone.\nAldactone - Tổn Thương Thận: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc tổn thương thận.\nAldactone - Rậm Lông: Aldactone gây rậm lông.\nCoversyl Plus - Thuốc Lợi Tiểu Giữ Kali: Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.\nAldactone - Vô Niệu: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc vô niệu.\nAldactone - Norepinephrine: Aldactone có tương tác với norepinephrine.\nAldactone - Tăng Kali Huyết: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc tăng kali huyết.&lt;SEP&gt;Tăng kali huyết là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nMụn Trứng Cà - Spironolactone (Aldactone): Spironolactone (Aldactone) được sử dụng để chữa trị mụn trứng cá.\nAldactone - Cholestyramine: Cholestyramine có thể gây nhiễm acid chuyển hóa tăng kali huyết khi sử dụng chung với Aldactone.\nAldactone - Suy Thận Cấp Tính: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc suy thận cấp tính.\nAldactone - Kali Huyết: Aldactone ảnh hưởng trực tiếp tới nồng độ kali máu.\nAldactone - Ammonium Chloride: Ammonium chloride có thể gây nhiễm acid chuyển hóa tăng kali huyết khi sử dụng chung với Aldactone.\nAldactone - Kiểm Soát Chứng Rậm Lông: Aldactone được chỉ định kiểm soát chứng rậm lông.\nAldactone - Phù/Cổ Trướng: Aldactone được chỉ định điều trị phù/cổ trướng.\nAldactone - Chứng Tăng Aldosterone Nguyên Phát: Aldactone được chỉ định điều trị chứng tăng aldosterone nguyên phát.\nAcid Mefenamic - Aldactone: Acid mefenamic làm suy giảm tác dụng của Aldactone.\nAldactone - Antipyrine: Aldactone có thể làm tăng chuyển hóa của antipyrine.\nAldactone - Carbenoxolone: Carbenoxolone có thể làm giảm hiệu quả của Aldactone khi sử dụng chung.\nAldactone - Thay Đổi Khả Năng Tình Dục: Thay đổi khả năng tình dục là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Aldactone gây thay đổi khả năng tình dục.\nAldactone - Bất Thường Liên Quan Đến Chức Năng Gan: Bất thường liên quan đến chức năng gan là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Aldactone gây bất thường liên quan đến chức năng gan.\nAldactone - Mẫn Cảm Với Spironolactone: Aldactone chống chỉ định sử dụng ở bệnh nhân mẫn cảm với spironolactone.\nAldactone - Rối Loạn Tiêu Hóa, Buồn Nôn: Rối loạn tiêu hóa, buồn nôn là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Lú Vẩn: Aldactone gây lú vẩn.\nAldactone - Bị Choáng Váng: Aldactone gây choáng váng.\nAldactone - Tình Trạng Chuột C rút Chân: Aldactone gây tình trạng chuột rút chân.\nAldactone - Bệnh Vú To Ở Đàn Ông: Aldactone gây bệnh vú to ở đàn ông.\nAldactone - Bị Choáng Váng, Chóng Mặt: Bị choáng váng, chóng mặt là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Rụng Tóc, Rậm Lông, Ngứa, Phát Ban: Rụng tóc, rậm lông, ngứa, phát ban là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Giảm Kali/Magie Huyết: Aldactone được sử dụng để điều trị giảm kali/magie huyết.\nAldactone - Tăng Aldosterone Nguyên Phát: Aldactone được sử dụng để điều trị tăng aldosterone nguyên phát.\nCandesartan - Thuốc Lợi Tiểu Giữ Kali: Việc sử dụng Candesartan cùng thuốc lợi tiểu giữ kali có thể làm tăng nguy cơ tăng kali huyết.\nSpironolactone - Thuốc Lợi Tiểu Giữ Kali: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc lợi tiểu giữ kali.\nSpironolactone - Thuốc Chặn Aldosterone: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc chặn aldosterone.\nSpironolactone - Thuốc Đối Kháng Angiotensin II: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc đối kháng angiotensin II.\nSpironolactone - Thuốc Ức Chế ACE: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc ức chế ACE.\nCozaar (Losartan) - Thuốc Lợi Tiểu Giữ Kali: Thuốc lợi tiểu giữ kali có thể tương tác với Cozaar.\nAldosterone - Thuốc Ngăn Chặn Aldosterone: Thuốc ngăn chặn aldosterone như spironolactone và eplerenone giúp giảm lượng aldosterone trong cơ thể.\nChứng Bất Lực - Spironolactone (Aldactone): Spironolactone (Aldactone) có thể gây bất lực.\nDị Tật Bẩm Sinh - Spironolactone (Aldactone): Spironolactone (Aldactone) có thể gây dị tật bẩm sinh.\nThuốc Lợi Tiểu Giữ Kali - Tăng Kali Máu: Thuốc lợi tiểu giữ kali gây tăng kali máu.\nMọc Nhiều Lông - Spironolactone (Aldactone): Spironolactone (Aldactone) được sử dụng để chữa trị mọc nhiều lông.\nSpironolactone (Aldactone) - Sản Xuất Androgen: Spironolactone (Aldactone) chống lại quá trình sản xuất androgen.']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone là hoàn toàn chống chỉ định. Khi một bệnh nhân bị mẫn cảm với spironolactone, việc sử dụng thuốc này có thể gây ra các phản ứng dị ứng nghiêm trọng, thậm chí có thể dẫn đến tình trạng mẫn cảm quá mẫn hoặc sốc phản vệ, gây nguy hiểm đến tính mạng.
+### Tác hại khi sử dụng Aldactone ở bệnh nhân mẫn cảm với spironolactone:
+- **Mẫn cảm quá mẫn**: Bệnh nhân có thể trải qua các triệu chứng dị ứng nghiêm trọng như phát ban, ngứa, phù nề, đặc biệt là phù mặt, môi, lưỡi và cổ họng.
+- **Sốc phản vệ**: Trong trường hợp nghiêm trọng nhất, mẫn cảm với spironolactone có thể dẫn đến phản ứng sốc phản vệ, gây ra các triệu chứng như huyết áp giảm đột ngột, nhịp tim tăng nhanh, khó thở và có thể dẫn đến tử vong nếu không được điều trị kịp thời.
+Do đó, việc sử dụng Aldactone ở bệnh nhân mẫn cảm với spironolactone là không an toàn và không nên được thực hiện.
+### Chống chỉ định:
+Aldactone chống chỉ định sử dụng ở bệnh nhân mắc bệnh Addison, tăng kali huyết, mẫn cảm với spironolactone, suy thận cấp tính, tổn thương thận, và vô niệu.
+### Lưu ý:
+Trước khi sử dụng Aldactone, cần đánh giá đầy đủ tiền sử dị ứng của bệnh nhân để tránh các tác hại nghiêm trọng.
+### Tham khảo:
+- [1] thuoc-aldactone-spironolactone.txt</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ở những bệnh nhân mẫn cảm với spironolactone, thuốc này có thể gây ra các phản ứng dị ứng nghiêm trọng, có thể mengan dọa tính mạng.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7027529274983023</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5580411730260462</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['Điều Trị Cơn Đau Tim: Điều trị cơn đau tim là phương pháp điều trị tình trạng đau tim.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nThuốc Điều Trị Nhịp Tim: Thuốc điều trị nhịp tim được sử dụng để ổn định tình trạng nhịp tim.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Lợi Tiếć: Thuốc lợi tiểu là thuốc tim mạch được sử dụng trong điều trị suy tim.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nTim Đập Hồi Hộp: Tim đập hồi hộp là triệu chứng được điều trị bằng Táo nhân.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nBệnh Nhân Suy Tim: Bệnh nhân suy tim cần thận trọng khi dùng Bisoprolol.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nQuá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nThuốc Trị Đái Tháo Đường Đường Uống: Thuốc trị đái tháo đường đường uống là thuốc dùng trong điều trị đái tháo đường.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nThuốc Uống Khác: Thuốc uống khác là phương pháp điều trị đái tháo đường.\ndược sĩ: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nThuốc Điều Trị Đái Tháo Đường Đường Uống: Thuốc điều trị đái tháo đường đường uống là thuốc dùng trong điều trị đái tháo đường.\nChỉ Định Thuốc: Chỉ định thuốc là hướng dẫn về cách sử dụng và liều dùng của Telmisartan và Cilzec.\nThuốc Trị Bệnh: Thuốc trị bệnh là các loại thuốc được sử dụng để điều trị các bệnh lý về tim mạch.\nCilzec: Cilzec là thuốc kê đơn dùng để điều trị cao huyết áp, được bào chế dưới dạng viên nén.&lt;SEP&gt;Cilzec là thuốc cần ngừng sử dụng khi gặp tác dụng không mong muốn.&lt;SEP&gt;Cilzec là thuốc được dùng để điều trị áp cao.&lt;SEP&gt;Cilzec là thuốc chống chỉ định sử dụng cho người bị dị ứng với bất kỳ thành phần nào của thuốc.&lt;SEP&gt;Cilzec là thuốc cần được bảo quản nơi khô ráo, thoáng mát, tránh ánh sáng và ẩm.&lt;SEP&gt;Cilzec là tên thương mại của thuốc Telmisartan, được dùng theo đơn của bác sĩ.\nbác sĩ: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nCorticosteroid: Corticosteroid là một loại thuốc tổng hợp thuộc nhóm steroid, thường được sử dụng trong y học vì khả năng chống viêm, chống dị ứng, và ức chế hệ thống miễn dịch. Corticosteroid bao gồm cả glucocorticoid và được sử dụng để điều trị nhiều loại bệnh khác nhau, từ bệnh Crohn đến viêm thận lupus và vảy phấn hồng. Corticosteroid là hoạt chất chính trong các sản phẩm như Benate Fort Ointment, Beprosone Ointment, và Bisilkon.\n\nKhi sử dụng cùng với một số loại thuốc khác như Amaryl 1 mg và Vildagliptin, corticosteroid có thể làm giảm tác dụng hạ đường huyết của chúng. Thuốc này cũng có thể tương tác với Agifuros 40 mg và một số loại thuốc khác như A.t Ibuprofen Syrup và Amaryl 1 mg. Khi sử dụng cùng với Babi B.O.N., corticosteroid có thể cản trở tác dụng của vitamin D. Sử dụng corticosteroid lâu dài có thể dẫn đến hội chứng Cushing do tích tụ steroid trong cơ thể, làm tăng lượng đường trong máu và tăng nguy cơ loét tiêu hóa hoặc xuất huyết khi dùng cùng Bart. Corticosteroid cũng có thể gây ra sự hấp thu toàn thân, dẫn đến ức chế trục vùng dưới đồi – tuyến yên – tuyến thượng thận (trục HPA).\n\nNgoài việc sử dụng để điều trị các bệnh mãn tính như viêm khớp dạng thấp và lupus, corticosteroid cũng được sử dụng để điều trị bệnh lý khớp gối thông qua tiêm nội khớp. Corticosteroid còn được kết hợp với Cloramphenicol trong một số trường hợp nhiễm khuẩn mắt. Corticosteroid được sử dụng bôi tại chỗ để giảm ngứa khi dùng Crotamiton. Ngoài ra, nó cũng được dùng để giảm phù não trong điều trị Hội chứng Reye. Corticosteroid là thuốc có tác dụng kháng viêm, sử dụng để ngăn chặn hệ miễn dịch tấn công hệ thần kinh. Nó cũng được sử dụng tại chỗ có thể ức chế chức năng tuyến thượng thận và tuyến yên. Corticosteroid là thành phần trong Beprosalic có thể gây tác dụng toàn thân.\n\nCuối cùng, corticosteroid là chế phẩm bôi ngoài da được sử dụng trong hầu hết các trường hợp nhiễm virus trên da, bệnh lao và trứng cá đỏ. Corticosteroid cũng được sử dụng kết hợp với cloramphenicol để điều trị nhiễm khuẩn bề mặt ở mắt hoặc tai. Corticosteroid đường uống, như prednison, có thể giúp giảm sưng, đỏ và ngứa, nhưng không nên sử dụng kéo dài vì có nhiều tác dụng phụ nghiêm trọng. Corticosteroid là loại thuốc được sử dụng để ức chế quá trình viêm trong bệnh phổi tắc nghẽn. Corticosteroid cũng là loại thuốc có thể gây rối loạn điện giải và là một trong những nguyên nhân gây hạ kali máu.\n\nCorticosteroid là loại thuốc mạnh với nhiều tác dụng và tương tác phức tạp cần được giám sát chặt chẽ khi sử dụng. Corticosteroid bao gồm metylprednisolone, prednisone, dexamethasone. Corticosteroid được sử dụng để thay thế cortisol và điều chỉnh liều lượng khi cơ thể gặp tình trạng bệnh lý. Corticosteroid là thuốc tiêm nội khớp và được tiêm vào khoang ngoài màng cứng của cột sống để giảm sưng và viêm dây thần kinh. Corticosteroid có thể gây hạ kali huyết nặng khi dùng cùng Acetazolamid và tương tác với Aspirin 81.\n\nNgoài ra, corticosteroid cũng được sử dụng trong điều trị triệu chứng liên quan đến Carbimazol. Corticosteroid được sử dụng kết hợp với CellCept trong điều trị cấy ghép tạng. Corticosteroid cũng có thể tương tác với moxifloxacin, gây viêm gân hoặc đứt gân gót. Corticosteroid được sử dụng để điều trị triệu chứng khi dùng quá liều moxifloxacin. Corticosteroid là nhóm thuốc, bao gồm Dexamethasone. Corticosteroid là thuốc chống viêm được sử dụng trong điều trị tăng canxi máu.&lt;SEP&gt;Việc thoa hoặc uống corticosteroid trong thời gian dài cũng là nguyên nhân gây rạn da.&lt;SEP&gt;Corticosteroid là nhóm hormone có nhiều tác dụng trong cơ thể.\nLiệt Kê Danh Sách Thuốc: Liệt kê danh sách những loại thuốc mà người dùng đang sử dụng, bao gồm cả thuốc không kê đơn.\nChỉ Định: Chỉ định là hướng dẫn về các bệnh lý mà thuốc Berberin được sử dụng để điều trị.&lt;SEP&gt;Chỉ định là hướng dẫn sử dụng Cù mạch.&lt;SEP&gt;Chỉ định là phương pháp sử dụng vacxin cho trẻ từ 6 tháng tuổi trở lên và người lớn.&lt;SEP&gt;Chỉ định là hướng dẫn của bác sĩ về việc cần phải đi khám bệnh và làm xét nghiệm.&lt;SEP&gt;Chỉ định là hướng dẫn về cách sử dụng thuốc, bao gồm loại thuốc, liều lượng và thời gian dùng.\nLiều Lượng: Liều lượng là số lượng thuốc hoặc chất hoạt chất được chỉ định sử dụng trong quá trình điều trị. Nó bao gồm cả số lượng thuốc được sử dụng và cách thức sử dụng nó, ví dụ như qua đường uống, tiêm hoặc thoa ngoài da. Liều lượng có thể được điều chỉnh dựa trên nhiều yếu tố khác nhau, bao gồm cân nặng, lối sống, và các yếu tố sức khỏe cá nhân khác. \n\nĐối với một số loại thuốc cụ thể, liều lượng cũng được quy định cụ thể cho từng độ tuổi. Ví dụ, liều lượng của Siro Bổ Phế Nam Hà và Viên Ngậm Bổ Phế Nam Hà được quy định cụ thể cho từng độ tuổi khác nhau. Điều này đảm bảo rằng mỗi người dùng nhận được liều lượng phù hợp với nhu cầu và tình trạng sức khỏe của họ.\n\nLiều lượng cũng có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc. Ví dụ, liều lượng corticoid sử dụng tại chỗ có thể được hấp thu vào máu, do đó việc xác định đúng liều lượng là rất quan trọng để tránh các tác dụng phụ không mong muốn.\n\nNgoài ra, liều lượng còn liên quan đến việc sử dụng thảo dược và hormone. Việc sử dụng thảo dược cần được chú ý về mức độ sử dụng, và liều lượng hormone là yếu tố ảnh hưởng đến việc lựa chọn liệu pháp hormon.&lt;SEP&gt;Liều lượng là yếu tố cần xem xét khi sử dụng dược liệu này để đảm bảo hiệu quả và an toàn.&lt;SEP&gt;Liều lượng là mức độ hoặc số lượng của một chất được đưa vào cơ thể, có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc.&lt;SEP&gt;Liều lượng là số lượng thuốc cần dùng trong một lần hoặc trong một khoảng thời gian.\nThuốc Uống Khác - Đái Tháo Đường: Thuốc uống khác là phương pháp điều trị đái tháo đường.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nBisoprolol - Bệnh Nhân Suy Tim: Bisoprolol chống chỉ định khi bệnh nhân có suy tim.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nAtenolol - Thuốc Lợi Tiếć: Atenolol và thuốc lợi tiểu đều là thuốc tim mạch được sử dụng trong điều trị suy tim.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nNgừng Tim Đột Ngột - Điều Trị Cơn Đau Tim: Ngừng tim đột ngột có thể liên quan đến điều trị cơn đau tim.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nNgừng Tim Đột Ngột - Thuốc Điều Trị Nhịp Tim: Thuốc điều trị nhịp tim được sử dụng để điều trị ngừng tim đột ngột.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nTim Đập Hồi Hộp - Táo Nhân: Táo nhân điều trị tim đập hồi hộp.\ndược sĩ - thuốc: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nEthinylestradiol - Thuốc Trị Đái Tháo Đường Đường Uống: Thuốc trị đái tháo đường đường uống có thể làm giảm nồng độ ethinylestradiol huyết thanh.\nChỉ Định Thuốc - Cilzec: Chỉ định thuốc là hướng dẫn về cách sử dụng Cilzec.\nThiếu Máu Cơ Tim - Thuốc Trị Bệnh: Thuốc trị bệnh được sử dụng để điều trị tình trạng thiếu máu cơ tim.\nbác sĩ - thuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nThuốc Điều Trị Đái Tháo Đường Đường Uống - Zofenopril: Thuốc điều trị đái tháo đường đường uống có thể tương tác với zofenopril.\nCorticosteroid - Liệt Kê Danh Sách Thuốc: Liệt kê danh sách thuốc giúp quản lý việc sử dụng corticosteroid.\nPhenylephrine HCl - Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nChỉ Định - Liều Lượng: Chỉ định liên quan đến liều lượng của thuốc.\nPhentolamin - Quá Liều Phenylephrine HCl: Phentolamin được dùng trong xử lý tăng huyết áp do quá liều phenylephrine HCl.']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nếu bạn quên uống một liều Cardilopin, bạn nên:
+- Dùng ngay sau khi nhớ ra đã quên liều.
+- Nếu liều đã quên gần với liều kế tiếp, hãy bỏ qua liều đã quên và tiếp tục dùng theo lịch trình dùng thuốc.
+- Không nên dùng gấp đôi liều để bù vào liều đã quên.
+### Cách bảo quản thuốc
+Bạn cần bảo quản thuốc Cardilopin ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc đặt thuốc ở những nơi ẩm ướt. Nhiệt độ bảo quản tốt nhất là dưới 30°C.
+### Lưu ý
+Hãy chắc chắn đọc kỹ hướng dẫn sử dụng trước khi bắt đầu sử dụng thuốc. Nếu bạn gặp bất kỳ triệu chứng bất thường nào, hãy gọi cho bác sĩ để được tư vấn và hỗ trợ kịp thời.
+### Xem thêm
+Thông tin cụ thể về cách sử dụng và bảo quản thuốc Cardilopin có thể được tìm thấy trong tài liệu hướng dẫn sử dụng của thuốc.
+### Tham khảo
+- [9] andol-s-imexpharm.txt</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bạn nên dùng bổ sung ngay khi nhớ ra, trường hợp nhớ ra trễ hơn 12 giờ so với giờ dùng thuốc hàng ngày, hãy bỏ qua liều đã quên và không dùng thêm thuốc để bù khi dùng liều tiếp theo.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8897297646326082</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2849324411581521</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['Suy Kiệt Thể Tích Nội Mạch: Suy kiệt thể tích nội mạch là bệnh lý cần theo dõi chặt chẽ khi sử dụng Cilzec.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nTiềm Năng Tác Dụng Phụ: Tiềm năng tác dụng phụ khi dùng Cefpodoxim trong thời kỳ cho con bú.\nTrẻ: Trẻ là đối tượng dễ mắc bệnh cúm do có hệ miễn dịch chưa hoàn thiện.&lt;SEP&gt;Trẻ là đối tượng sử dụng thuốc clotrimazole.\nTrẻ Em và Trẻ Vị Thành Niên: Trẻ em và trẻ vị thành niên là đối tượng sử dụng Ciprofloxacin với liều lượng cụ thể.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nTriệu Chứng Bất Lợi: Triệu chứng bất lợi là tác dụng phụ có thể xảy ra khi sử dụng Ceelin.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nTác Dụng Phản: Tác dụng phụ không được liệt kê cụ thể trong đoạn văn nhưng có thể bao gồm các vấn đề liên quan đến đường tiêu hóa.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nTiêu Chảy (ở trẻ): Tiêu chảy là triệu chứng của trẻ khi mẹ sử dụng Cefadroxil.\nA.T.P: Thuốc A.T.P được chỉ định trong hỗ trợ điều trị chứng đau lưng.&lt;SEP&gt;A.T.P là thuốc giãn cơ, chứa hoạt chất dinatri adenosin triphosphat.&lt;SEP&gt;A.T.P là thuốc được đề cập trong bài viết.\nRối Loạn Ở Da: Rối loạn ở da là tác dụng phụ thường gặp khi sử dụng Cebrex.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nPhụ Huynh: Phụ huynh là đối tượng cần theo dõi khi trẻ em sử dụng Calcigenol.\nCefadroxil - Tiêu Chảy (ở trẻ): Tiêu chảy là triệu chứng của trẻ khi mẹ sử dụng Cefadroxil.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nCiprofloxacin - Trẻ Em và Trẻ Vị Thành Niên: Ciprofloxacin được sử dụng cho trẻ em và trẻ vị thành niên với liều lượng cụ thể.\nDược Liệu - Trẻ Em: Trẻ em cần cẩn trọng khi dùng dược liệu.\nCefpodoxim - Tiềm Năng Tác Dụng Phụ: Tiềm năng tác dụng phụ khi dùng Cefpodoxim trong thời kỳ cho con bú.\nThuốc - Trẻ Em: Trẻ em không được phép sử dụng thuốc này.&lt;SEP&gt;Thuốc cần được giữ tránh xa tầm tay của trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nCalcigenol - Phụ Huynh: Phụ huynh cần theo dõi khi trẻ em sử dụng Calcigenol.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nBeprosone Ointment - Đối Tượng Dùng Thuốc Là Trẻ Em: Đối tượng dùng thuốc là trẻ em cần theo dõi kỹ khi sử dụng Beprosone Ointment.\nA.T.P - Trẻ Em: Bài viết cảnh báo bố mẹ để thuốc A.T.P tránh xa tầm tay trẻ em.\nCebrex - Rối Loạn Ở Da: Rối loạn ở da là tác dụng phụ thường gặp khi sử dụng Cebrex.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nPhụ Huynh - Rối Loạn Tâm Lý Tuổi Dậy Thì: Phụ huynh cần chăm sóc và hỗ trợ trẻ bị rối loạn tâm lý tuổi dậy thì.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nCeelin - Triệu Chứng Bất Lợi: Triệu chứng bất lợi là tác dụng phụ có thể xảy ra khi sử dụng Ceelin.\nAlphaDHG - Trẻ Em: Trẻ em cần đặc biệt chú ý khi dùng thuốc AlphaDHG.\nCilzec - Suy Kiệt Thể Tích Nội Mạch: Bệnh nhân suy kiệt thể tích nội mạch cần theo dõi chặt chẽ khi sử dụng Cilzec.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nBổ Phế Nam Hà Chỉ Khái Lộ - Trẻ Em Dưới 24 Tháng Tuổi: Trẻ em dưới 24 tháng tuổi cần thận trọng khi sử dụng thuốc Bổ Phế Nam Hà Chỉ Khái Lộ.\nTinh Dầu Húng Chanh - Trẻ Nhỏ: Trẻ nhỏ cần cẩn trọng khi sử dụng tinh dầu húng chanh.\nPhụ Huynh - Trò Chơi Bạo Lực: Phụ huynh cần nhắc nhở trẻ tránh các trò chơi bạo lực.\nPhụ Huynh - Văn Hóa Phẩm Đồi Trụy: Phụ huynh cần nhắc nhở trẻ tránh văn hóa phẩm đồi trụy.\nPhụ Huynh - Tệ Nạn Xã Hội: Phụ huynh cần nhắc nhở trẻ tránh tệ nạn xã hội.']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Cilzec cho trẻ em, cần đặc biệt chú ý đến khả năng gây suy kiệt thể tích nội mạch, một bệnh lý cần theo dõi chặt chẽ. Điều này nghĩa là việc sử dụng thuốc Cilzec có thể dẫn đến tình trạng suy kiệt thể tích nội mạch ở trẻ em, đòi hỏi sự giám sát và theo dõi chặt chẽ của bác sĩ.
+### Chú ý khi sử dụng Cilzec cho trẻ em:
+- **Theo dõi chặt chẽ**: Cần theo dõi trẻ chặt chẽ để phát hiện sớm bất kỳ dấu hiệu bất lợi nào có thể xuất hiện.
+- **Suy kiệt thể tích nội mạch**: Trẻ em có thể gặp phải tình trạng suy kiệt thể tích nội mạch, một tình trạng cần được theo dõi cẩn thận.
+- **Tuân thủ hướng dẫn**: Cần tuân thủ chặt chẽ hướng dẫn của bác sĩ về cách dùng và liều lượng của thuốc.
+### Tham chiếu:
+- [10] thuoc-avodart-dutasteride.txt
+Tuy nhiên, cần lưu ý rằng thông tin trong tài liệu tham khảo không đề cập cụ thể đến việc sử dụng Cilzec cho trẻ em. Việc theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ là rất quan trọng để đảm bảo an toàn và hiệu quả khi sử dụng thuốc này cho trẻ em.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Độ hiệu quả, an toàn của thuốc trên trẻ em chưa được làm rõ. Do đó, chỉ sử dụng thuốc cho trẻ em khi có sự chỉ định của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8121733850566467</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6137576319534475</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>['Methotrimeprazin: Methotrimeprazin là thuốc có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride): Atarax (hydroxyzine hydrochloride) là thuốc được sử dụng để điều trị các triệu chứng như khô miệng và đánh trống ngực.\nChất Ức Chế Acetylcholinesterase: Chất ức chế acetylcholinesterase là thuốc có tương tác với Atarax.\nPramlintid: Pramlintid là thuốc có tương tác với Atarax.\nEpinephrin (Adrenalin): Epinephrin (adrenalin) là thuốc có tương tác với Atarax.\nThuốc Opiat: Thuốc opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu có tương tác với Atarax.\nDroperidol: Droperidol là loại thuốc tương tác với Pregabalin.&lt;SEP&gt;Droperidol là thuốc có tương tác với Atarax.\nThuốc Kháng Acetylcholin Khác: Thuốc kháng acetylcholin khác có thể tăng thêm tác dụng khi dùng cùng Atarax.\nAmphetamin: Amphetamin là một trong những thuốc kiềm yếu mà sự thải trừ giảm khi dùng chung với nhôm phosphat.&lt;SEP&gt;Amphetamin là thuốc có thể bị ảnh hưởng bởi nhôm phosphat.&lt;SEP&gt;Amphetamin là thuốc có tính bazơ, mức độ bài tiết của nó bị ức chế bởi các thuốc kháng axit.&lt;SEP&gt;Amphetamin là thuốc có tính bazơ bị ức chế sự bài tiết bởi thuốc kháng axit.&lt;SEP&gt;Amphetamin là một trong những thuốc có tương tác với Barudon.&lt;SEP&gt;Amphetamin có tương tác với Acetazolamid.&lt;SEP&gt;Amphetamin là thuốc có tương tác với Atarax.\nHydroxyzine Hydrochloride: Hydroxyzine hydrochloride là hoạt chất chính trong Atarax.\nAtarax: Atarax là thuốc chứa hoạt chất hydroxyzine hydrochloride, được sử dụng trong các trường hợp ngăn cơn nôn, chống ngứa, lo âu, kiểm soát trạng thái kích động trong hội chứng cai rượu cấp.&lt;SEP&gt;Atarax là thuốc chống nôn, điều trị lo âu, làm dịu lo âu trước và sau gây mê, kiểm soát trạng thái kích động do cai rượu.&lt;SEP&gt;Thuốc Atarax được sử dụng để điều trị các tình trạng y tế cụ thể, có thể gây ra nhiều tác dụng phụ trong quá trình điều trị.&lt;SEP&gt;Atarax là thuốc kháng histamin, gây ra triệu chứng như co giật, cảm giác u ám và hạ huyết áp khi dùng quá liều.&lt;SEP&gt;Atarax là thuốc được sử dụng để điều chỉnh liều lượng cho bệnh nhân suy thận hoặc người đã từng bị co giật, động kinh.\nCảm Quang: Cảm quang là tác dụng phụ của Atarax.&lt;SEP&gt;Cảm quang là triệu chứng có thể xảy ra do sử dụng Atarax.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nAtidogrel: Atidogrel là thuốc được dùng để ngăn chặn sự kết tập tiểu cầu hình thành huyết khối, được chỉ định điều trị trong bệnh lý tim mạch như sau nhồi máu cơ tim.&lt;SEP&gt;Atidogrel là thuốc chống kết tập tiểu cầu, được sử dụng trong phòng ngừa biến cố huyết khối.&lt;SEP&gt;Atidogrel là thuốc dùng để phòng ngừa huyết khối tắc mạch, được chỉ định sau các phẫu thuật bắc cầu động mạch vành và trong các trường hợp hẹp động mạch cảnh có triệu chứng.&lt;SEP&gt;Atidogrel được chỉ định để điều trị hoặc dự phòng huyết khối, chống kết tập tiểu cầu.&lt;SEP&gt;Atidogrel được chỉ định cho việc điều trị hoặc dự phòng huyết khối, chống kết tập tiểu cầu.&lt;SEP&gt;Atidogrel là thuốc có thể gây ra nhiều triệu chứng bất lợi khi sử dụng.\nEffexor: Effexor là thuốc chống trầm cảm có thể tương tác với Atidogrel.\nDiclofenac: Diclofenac là một loại thuốc chống viêm không steroid (NSAID) được sử dụng rộng rãi trong việc điều trị các bệnh về khớp và bệnh phong thấp. Thuốc này không chỉ giúp giảm đau mà còn có tác dụng chống viêm hiệu quả. Diclofenac thường được dùng làm đối chứng trong các nghiên cứu lâm sàng, ví dụ khi so sánh với tenoxicam. \n\nDiclofenac cũng có thể tương tác với một số loại thuốc khác như Atidogrel, Atiso đỏ, và Carbocistein, đòi hỏi sự thận trọng khi sử dụng kết hợp chúng. Nó được biết đến với khả năng tương tác với thuốc chống đông máu và Bromelain. \n\nNgoài ra, Diclofenac còn được sử dụng như một chuẩn trong nghiên cứu về tác dụng của dịch chiết từ lá Muồng trâu. Thuốc này cũng có tác dụng tương đương với dịch chiết từ rễ Cơm rượu trong việc điều trị các vấn đề về khớp. \n\nDiclofenac bôi ngoài da chứa dầu jojoba, giúp tăng cường tác dụng chống viêm. Tuy nhiên, nó cũng có thể gây ra cảm giác nóng rát ở dạ dày. Diclofenac là hoạt chất chính trong Cataflam, một thuốc chống viêm không steroid.&lt;SEP&gt;Diclofenac là thuốc làm chậm đông máu.&lt;SEP&gt;Diclofenac là một loại thuốc có thể tương tác với Co-Diovan.&lt;SEP&gt;Diclofenac là thuốc giảm đau, kháng viêm không steroid.&lt;SEP&gt;Diclofenac là thuốc chống viêm không steroid.&lt;SEP&gt;Thuốc natri diclofenac được so sánh với tác dụng giảm đau và kháng viêm của tinh dầu.\nAtarax (Hydroxyzine Hydrochloride) - Suy Thận: Suy thận là tình trạng cần giảm liều Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Pramlintid: Pramlintid có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Mất Ngủ: Mất ngủ là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Methotrimeprazin: Methotrimeprazin có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Suy Gan: Suy gan là tình trạng cần giảm liều Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Epinephrin (Adrenalin): Epinephrin (adrenalin) có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hạ Huyết Áp: Hạ huyết áp là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Droperidol: Droperidol có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Trầm Cảm: Trầm cảm là triệu chứng có thể xảy ra do sử dụng Atarax.\nAmphetamin - Atarax (Hydroxyzine Hydrochloride): Amphetamin có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Khô Miệng: Atarax được sử dụng để điều trị khô miệng.\nAtarax (Hydroxyzine Hydrochloride) - Thuốc Kháng Acetylcholin Khác: Thuốc kháng acetylcholin khác có thể tăng thêm tác dụng khi dùng cùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Phát Ban: Phát ban là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Chất Ức Chế Acetylcholinesterase: Chất ức chế acetylcholinesterase có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Viêm Gan: Viêm gan là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax - Tác Dụng Phụ: Thuốc Atarax có thể gây ra nhiều tác dụng phụ trong quá trình điều trị.\nAtarax (Hydroxyzine Hydrochloride) - Phù: Phù là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtidogrel - Effexor: Effexor có thể tương tác với Atidogrel.\nAtarax (Hydroxyzine Hydrochloride) - Đau Cơ: Đau cơ là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtidogrel - Diclofenac: Diclofenac có thể tương tác với Atidogrel.\nAtarax (Hydroxyzine Hydrochloride) - Chảy Máu Cam: Chảy máu cam là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hen: Hen là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Huyết Khối: Huyết khối có thể xảy ra do tiêm Atarax dưới da, tiêm động mạch hay tĩnh mạch.\nAtarax (Hydroxyzine Hydrochloride) - Phù Mạch: Phù mạch là triệu chứng có thể xảy ra do sử dụng Atarax.\nDroperidol - Pregabalin: Pregabalin tương tác với Droperidol.\nAtarax (Hydroxyzine Hydrochloride) - Bí Tiểu: Bí tiểu là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Đánh Trống Ngực: Atarax được sử dụng để điều trị đánh trống ngực.\nAtarax (Hydroxyzine Hydrochloride) - Run: Run là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Co Thắt Phế Quản: Co thắt phế quản là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Nhìn Mờ: Nhìn mờ là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Phì Đại Tuyến Tiền Liệt: Phì đại tuyến tiền liệt là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Dị Cảm: Dị cảm là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hydroxyzin: Hydroxyzin là hoạt chất chính trong Atarax.\nAtarax - Cảm Quang: Cảm quang là tác dụng phụ của Atarax.\nAtarax - Hydroxyzine Hydrochloride: Atarax chứa hoạt chất hydroxyzine hydrochloride.\nAtarax (Hydroxyzine Hydrochloride) - Bệnh Phổi Tắc Nghẽn Mạn Tính: Bệnh phổi tắc nghẽn mạn tính là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Noradrenalin: Noradrenalin là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Glaucom Góc Hẹp: Glaucom góc hẹp là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Đờ Đẫn: Đờ đẫn là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hoại Thư: Hoại thư ngón chân, tay có thể xảy ra do tiêm Atarax dưới da, tiêm động mạch hay tĩnh mạch.\nAtarax (Hydroxyzine Hydrochloride) - Tắc Nghẽn Cổ Bàng Quang: Tắc nghẽn cổ bàng quang là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Kích Thích Nghịch Thường: Kích thích nghịch thường là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Cảm Quang: Cảm quang là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Metaraminol: Metaraminol là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Thuốc Opiat: Thuốc opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Tác Dụng Kháng Cholinergic: Tác dụng kháng cholinergic không được dung nạp tốt ở người cao tuổi.\nAtarax (Hydroxyzine Hydrochloride) - Thất Mạch: Thất mạch có thể gây áp xe vô khuẩn và cứng mô rõ rệt.']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Thuốc Atarax (hydroxyzine hydrochloride) có thể tương tác với một số loại thuốc khác, bao gồm:
+- **Epinephrin (adrenalin)**: Thuốc này có thể tương tác với Atarax.
+- **Droperidol**: Thuốc này tương tác với Atarax.
+- **Methotrimeprazin**: Thuốc này tương tác với Atarax.
+- **Pramlintid**: Thuốc này tương tác với Atarax.
+- **Amphetamin**: Thuốc này có tương tác với Atarax.
+- **Chất ức chế acetylcholinesterase**: Các chất này có thể tương tác với Atarax và tăng thêm tác dụng.
+- **Thuốc kháng acetylcholin khác**: Thuốc này cũng có thể tăng thêm tác dụng khi dùng cùng Atarax.
+- **Thuốc opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu**: Các loại thuốc này có tương tác với Atarax.
+Ngoài ra, Atarax có thể tương tác với các thuốc như Diclofenac và Atidogrel, đòi hỏi sự thận trọng khi sử dụng kết hợp chúng.
+### Lưu ý khi dùng
+- Nếu cần thiết phải dùng một thuốc co mạch thì phải dùng noradrenalin hoặc metaraminol, không được dùng epinephrin cho người đang dùng Atarax.
+### Tương tác khác
+- Thuốc Atarax có thể tương tác với Effexor, một loại thuốc chống trầm cảm.
+### Tham khảo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với các thuốc như epinephrin, barbiturat, thuốc an thần khác, droperidol, pramlintid, thuốc gây tê mê, rượu, các chất ức chế acetylcholinesterase, chất giảm đau và các thuốc opiat.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8509033241428315</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9627258310107079</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>['Nhiệt Độ Điều Hòa: Nhiệt độ điều hòa cần được điều chỉnh để cơ thể cảm thấy dễ chịu khi bị cảm cúm.\nBảo Quản Thuốc: Bảo Quản Thuốc là quá trình lưu trữ thuốc đúng cách nhằm duy trì chất lượng và hiệu quả của chúng. Mỗi loại thuốc có yêu cầu bảo quản riêng biệt, từ việc kiểm soát độ ẩm, nhiệt độ và ánh sáng để tránh ảnh hưởng đến chất lượng và tính năng của thuốc. Ví dụ, thuốc như At Domperidone, ATP, Acritel, Acyclovir, Alphachymotrypsin bk 4200 Mebiphar, AlphaDHG, Alzental, Ambroxol Boston, Amepox Soft Capsule, Ampicillin Brawn, Aspirin MKP OnClickListener, Avastin, Ba đậu và disulfiram đều có yêu cầu bảo quản cụ thể. Thuốc Bentarcin cần được bảo quản ở nơi thoáng mát, tránh ánh nắng trực tiếp. Thuốc Debby cần được bảo quản tránh tiếp xúc với ánh sáng, nhiệt độ dưới 30°C và ở nơi khô ráo, thoáng mát. Thuốc Atussin cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc môi trường ẩm ướt, với nhiệt độ tốt nhất là dưới 30ºC. Thuốc Diorophyl cần được bảo quản trong bao bì gốc, nơi khô ráo, tránh ánh sáng và nhiệt độ không quá 30°C. Thuốc Atocib cần được bảo quản theo hướng dẫn trên tờ hướng dẫn sử dụng thuốc, thông thường thuốc được bảo quản ở nhiệt độ phòng, tránh ẩm và ánh nắng trực tiếp.\n\nThuốc methylprednisolone cần được bảo quản theo hướng dẫn cụ thể về nhiệt độ và thời gian sử dụng. Thuốc Acarbose cần được bảo quản ở nơi khô ráo, thoáng mát, tránh nơi ẩm ướt, nhiệt độ dưới 25°C và không sử dụng thuốc sau ngày hết hạn. Thuốc Acemuc cần chú ý đến nhiệt độ, tránh ánh sáng trực tiếp và không để thuốc tiếp xúc với nước. Thuốc Amiodarone cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30°C, tránh ánh sáng trực tiếp. Thuốc axit axetic cần được bảo quản ở nhiệt độ phòng, dưới 30oC, tránh ánh sáng trực tiếp và hơi ẩm, nhiệt độ cao. Thuốc Baclofen cũng cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30oC, tránh ánh sáng trực tiếp. Thuốc Bisacodyl yêu cầu đựng thuốc trong bao bì kín, tránh nóng, ánh sáng và ẩm, bảo quản ở nhiệt độ dưới 25 °C, tránh xa tầm tay của trẻ em, đọc kỹ hướng dẫn trước khi dùng, và không dùng thuốc có dấu hiệu ẩm mốc, thay đổi màu sắc. Thuốc Bismuth cần được bảo quản ở nhiệt độ dưới 30oC, trong bao bì kín. Thuốc Bolutin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ Celsius, tránh ánh sáng trực tiếp. Thuốc Cefpodoxim cần được bảo quản trong bao bì kín, ở nhiệt độ dưới 25 độ Celsius và tránh ánh sáng. Thuốc Ceftriaxone cần được bảo quản ở nhiệt độ dưới 25ºC, nơi khô ráo và thông thoáng. Thuốc CellCept cần được bảo quản tránh xa tầm nhìn và tầm với của trẻ em, không sử dụng sau ngày hết hạn, không lưu trữ trên 30°C, và giữ trong thùng carton để tránh ánh sáng. Thuốc Cerebrolysin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 25°C, tránh ánh sáng trực tiếp. Thuốc Ceritine cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ C. Bảo quản thuốc Diane-35 cần được thực hiện dưới 30 độ Celsius, nơi khô ráo, tránh ánh sáng. Thuốc Benzalkonium Chloride cũng cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt, nhiệt độ bảo quản tốt nhất là dưới 30°C.\n\nQuá trình bảo quản thuốc còn bao gồm việc lưu trữ Irbesartan đúng cách để đảm bảo an toàn và hiệu quả. Bảo quản thuốc đúng cách là rất quan trọng để duy trì chất lượng và hiệu quả của chúng, đảm bảo an toàn khi sử dụng và ngăn chặn bất kỳ sự cố nào có thể xảy ra do bảo quản không đúng cách.\nĐiều Hòa Bài Tiết GH: Điều hòa bài tiết GH.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThiết Bị Bảo Quản Thuốc: Thiết bị bảo quản thuốc là nơi lưu trữ thuốc, cần bảo quản ở nhiệt độ dưới 30°C, tránh ánh nắng mặt trời.\nBa Đậu: Ba đậu là một loại cây gỗ nhỡ với chiều cao trung bình từ 3 đến 6 mét, cành nhẵn và thân tròn, không có lông. Hạt của cây này được sử dụng rộng rãi như một vị thuốc trong y học cổ truyền, đặc biệt là trong nền y học Đông y. Hạt ba đậu có vỏ cứng màu nâu xám, bên trong là nhân màu trắng giàu dầu. \n\nBa đậu được biết đến với nhiều tác dụng y tế, bao gồm cả khả năng nhuận tràng rất hiệu quả, mặc dù nó cũng có độc tính. Nó được sử dụng để điều trị các triệu chứng như bụng căng đầy, ngực đau, đại tiện không thông, hàn tích, ăn không tiêu, đại tiện bí, tích trệ, lở ngứa, lác đồng tiền, viêm niêm mạc dạ dày cấp tính, và đau bụng. Ngoài ra, ba đậu còn được sử dụng để điều trị các tình trạng khác như kích thích da và niêm mạc, và chống kết tập tiểu cầu.\n\nTrong y học cổ truyền, ba đậu đã được sử dụng từ lâu đời trong dân gian để điều trị nhiều loại bệnh khác nhau. Tuy nhiên, do tính độc của nó, việc sử dụng ba đậu cần phải hết sức thận trọng và dưới sự hướng dẫn của bác sĩ hoặc thầy thuốc chuyên môn.\nThời Tiết Bảo Quản: Thời tiết bảo quản yêu cầu nhiệt độ không quá 30°C, tránh ánh sáng và ẩm.\nBảo Quản Dược Liệu: Bảo quản dược liệu sau khi sơ chế cần được bảo quản ở những nơi khô.&lt;SEP&gt;Bảo quản dược liệu trong bọc kín, hũ nhựa hay thủy tinh, cất trữ nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.&lt;SEP&gt;Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.&lt;SEP&gt;Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ, tránh nơi ẩm mốc và ánh nắng trực tiếp.&lt;SEP&gt;Bảo quản dược liệu cần để nơi khô ráo, thông thoáng.\nThuốc Cotrimoxazol: Cotrimoxazol là thuốc cần được bảo quản đúng cách, tránh ánh sáng trực tiếp và nhiệt độ không quá 30 độ Celsius.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nVũ Khí Lạnh: Vũ khí lạnh như lưỡi lê, kiếm.\nDebby: Debby là thuốc kê đơn được sản xuất bởi Công ty TNHH Thai Nakorn Patana, với thành phần chính là nifuroxazide. Thuốc được chỉ định trong điều trị tiêu chảy cấp và mạn, bệnh lỵ trực khuẩn và chứng viêm ruột kết.&lt;SEP&gt;Debby là thuốc được sử dụng theo đơn thuốc, chống chỉ định với người mẫn cảm với thành phần và trẻ sơ sinh dưới 1 tháng tuổi.&lt;SEP&gt;Debby là loại kháng sinh chỉ được sử dụng theo đơn thuốc, không tự ý sử dụng khi chưa có chỉ định hoặc kê toa của bác sĩ.&lt;SEP&gt;Debby là thuốc được chỉ định điều trị tiêu chảy cấp và mạn, bệnh ly trực khuẩn, và viêm ruột kết.\nKhô Ráo: Khô ráo, nhiệt độ không quá 30 oC là yêu cầu bảo quản thuốc.\nDidicera: Didicera là thuốc thảo dược không kê toa, thuộc công ty Cổ phần Công nghệ cao Traphaco, điều chế dưới dạng viên hoàn và viên nang.&lt;SEP&gt;Viên nang Didicera chứa thành phần độc hoạt, tế tân, tang ký sinh, quế chi, tần giao, phòng phong, cam thảo, bạch linh và đảng sâm.&lt;SEP&gt;Didicera có công năng bổ khí huyết, trừ phong thấp, bổ can thận.&lt;SEP&gt;Didicera là thuốc được điều chế dưới dạng viên nang hoặc viên hoàn, dùng đường uống.&lt;SEP&gt;Didicera là thuốc được bán với giá trung bình khoảng 40.000 VNĐ/hộp 10 gói x viên hoàn 5g.&lt;SEP&gt;Didicera là thuốc cần tham khảo ý kiến dược sĩ hoặc bác sĩ về cách dùng và liều dùng trước khi sử dụng.\nĐiều Kiện Bảo Quản Thuốc: Điều kiện bảo quản thuốc bao gồm bảo quản nơi khô ráo, thoáng mát, nhiệt độ từ 15°C – 30°C, tránh ánh sáng trực tiếp.\nDiorophyl: Diorophyl là thuốc được sử dụng để điều trị các triệu chứng về thần kinh, chứa hoạt chất piracetam.&lt;SEP&gt;Diorophyl có thể điều trị triệu chứng chóng mặt ở người lớn và các triệu chứng như suy giảm trí nhớ, kém tập trung, rối loạn hành vi, thay đổi khí sắc, sa sút trí tuệ do nhồi máu não.&lt;SEP&gt;Diorophyl là thuốc được sử dụng để điều trị các triệu chứng liên quan đến nghiện rượu, nhưng có một số tác dụng không mong muốn và chống chỉ định.&lt;SEP&gt;Diorophyl là thuốc kê đơn được sử dụng theo chỉ định của bác sĩ, với các lưu ý về liều lượng, hạn sử dụng và cách bảo quản.\nNhiệt Độ Phòng: Bảo quản siro Appeton Lysine ở nhiệt độ phòng, tránh nhiệt và ánh sáng trực tiếp.\nIsotretinoin: Isotretinoin là một loại thuốc được kê đơn để điều trị mụn trứng cá nặng, thường được sử dụng kéo dài trong các trường hợp không đáp ứng với các phương pháp điều trị khác như thuốc kháng sinh tại chỗ. Thuốc này là thành phần chính trong các sản phẩm như Acnotin, bao gồm Acnotin 10 và Acnotin 20.\n\nIsotretinoin có tác dụng bình thường hóa lượng bã nhờn, ngăn chặn lỗ chân lông bị tắc nghẽn, giảm số lượng vi khuẩn trên da và giảm mẩn đỏ và sưng tấy. Tuy nhiên, khi sử dụng isotretinoin, cần phải thận trọng do thuốc có thể gây ra các tương tác với một số thành phần khác như Agirenyl và vitamin A trong Appeton Lysine Syrup cũng như Avi-O5. Việc sử dụng isotretinoin cùng với vitamin A có thể dẫn đến tình trạng dùng vitamin A quá liều.\n\nĐặc biệt, việc sử dụng isotretinoin trong thời kỳ mang thai có thể làm tăng nguy cơ dị tật tim bẩm sinh ở trẻ sơ sinh. Vì vậy, cần phải tránh sử dụng isotretinoin với liều cao đối với phụ nữ có thai. Isotretinoin được chỉ định trong những trường hợp mụn trứng cá nặng và có nguy cơ gây dị tật thai nhi cao.&lt;SEP&gt;Isotretinoin là thuốc điều trị da, có thể gây suy yếu sự cân bằng nước của da.&lt;SEP&gt;Isotretinoin là thuốc gây khô da và bong tróc, được cải thiện bằng cách bổ sung tinh dầu hoa anh thảo.\nHơi Hàn: Hơi hàn là tính chất nhiệt độ của mã tiên thảo.\nDây Gắm: Dây gắm là thảo dược được sử dụng trong bài thuốc chữa thấp khớp.&lt;SEP&gt;Dây gắm là một loài cây thân leo trườn hóa gỗ, thuộc họ Dây gắm (Gnetaceae).&lt;SEP&gt;Dây Gắm mọc tự nhiên trong rừng thường xanh, ở độ cao 200 – 1200 m, phân bố ở các tỉnh: Sapa, Hà Giang, Vĩnh Phúc (Tam Đảo), Hà Nội (Ba Vì), Quảng Trị, Đà Nẵng, Lâm Đồng, Tây Ninh, Long An, Bến Tre, An Giang, Kiên Giang (Đảo Phú Quốc).&lt;SEP&gt;Dây Gắm được sử dụng để điều trị các chứng đau nhức xương khớp, chữa phong tê thấp, hỗ trợ trong điều trị bệnh gout.&lt;SEP&gt;Dây Gắm có vị đắng, tính mát, có tác dụng giải độc, tiêu viêm, thư giãn gân cốt, hoạt huyết, sát trùng.\nCiticoline: Thuốc bổ não Citicoline là thuốc được bảo quản ở nơi khô ráo thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt.&lt;SEP&gt;Thuốc Citicoline được sử dụng để bổ não và có tương tác với các thuốc khác như Levodopa, Meclophenoxat, Centrophenoxine.&lt;SEP&gt;Citicoline là thuốc được dùng để điều trị bệnh Alzheimer, chứng mất trí, chấn thương đầu, bệnh mạch máu não như đột quỵ, mất trí nhớ liên quan đến tuổi, bệnh Parkinson, rối loạn tăng động giảm chú ý, và bệnh tăng nhãn áp.&lt;SEP&gt;Citicoline là thuốc được sử dụng trong điều trị bệnh rối loạn mạch máu não, rối loạn nhận thức, chấn thương đầu hoặc bệnh Parkinson.\nIsotretinoin - Thiết Bị Bảo Quản Thuốc: Isotretinoin cần được bảo quản đúng cách để đảm bảo chất lượng.\nBảo Quản Thuốc - Thuốc: Bảo quản thuốc là quá trình lưu trữ thuốc.\nBệnh Cúm - Nhiệt Độ Điều Hòa: Nhiệt độ điều hòa cần được điều chỉnh để cơ thể cảm thấy dễ chịu khi bị cảm cúm.\nBa Đậu - Bảo Quản Thuốc: Quá trình bảo quản thuốc giúp lưu giữ Ba đậu trong điều kiện thích hợp.\nCotrimoxazol - Thuốc Cotrimoxazol: Thuốc Cotrimoxazol cần được bảo quản đúng cách, tránh ánh sáng trực tiếp và nhiệt độ không quá 30 độ Celsius.\nBảo Quản Dược Liệu - Dược Liệu: Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ.\nHơi Hàn - Mã Tiên Thảo: Mã tiên thảo có tính chất hơi hàn.\nBảo Quản Thuốc - Debby: Thuốc Debby cần được bảo quản đúng cách để duy trì chất lượng và an toàn.\nAppeton Lysine Syrup - Nhiệt Độ Phòng: Siro Appeton Lysine cần được bảo quản ở nhiệt độ phòng.\nBảo Quản Thuốc - Didicera: Thuốc cần được bảo quản đúng cách để đảm bảo an toàn và hiệu quả.\nDương Vật - Vũ Khí Lạnh: Vũ khí lạnh gây tổn thương dương vật.\nBảo Quản Thuốc - Diorophyl: Thuốc Diorophyl cần được bảo quản đúng cách để duy trì chất lượng.\nCrotamiton - Khô Ráo: Thuốc Crotamiton cần được bảo quản trong điều kiện khô ráo.\nBổ Phế Nam Hà - Điều Kiện Bảo Quản Thuốc: Bổ phế Nam Hà cần được bảo quản tại nơi khô ráo, thoáng mát, nhiệt độ từ 15°C – 30°C, tránh ánh sáng trực tiếp.\nBảo Quản Dược Liệu - Dây Gắm: Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.\nAllerphast 60 mg - Thời Tiết Bảo Quản: Hướng dẫn bảo quản Allerphast 60 mg yêu cầu nhiệt độ không quá 30°C, tránh ánh sáng và ẩm.\nBảo Quản Thuốc - Citicoline: Citicoline cần được bảo quản đúng cách để đảm bảo chất lượng.\nBảo Quản Thuốc - Disulfiram: Bảo quản thuốc là cách bảo quản disulfiram tránh khỏi tầm tay của trẻ em và thú cưng, ở nơi khô ráo thoáng mát.']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Thuốc Comozol cần được bảo quản đúng cách để đảm bảo chất lượng và an toàn. Điều kiện bảo quản thuốc Comozol bao gồm:
+- Bảo quản thuốc ở nơi khô ráo, thoáng mát.
+- Tránh tiếp xúc trực tiếp với ánh sáng hoặc để thuốc ở những nơi ẩm ướt.
+- Nhiệt độ bảo quản tốt nhất là dưới 30°C.
+Theo dõi hạn sử dụng của thuốc và không sử dụng thuốc sau ngày hết hạn.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bạn cần tránh ánh sáng, bảo quản nơi khô mát và giữ thuốc ở nhiệt độ dưới 30°C để bảo quản thuốc Comozol tốt nhất.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7906945310802088</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6976736327450522</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>['Thay Đổi Hành Vi Bất Thường: Thay đổi hành vi bất thường có thể xảy ra khi sử dụng amitriptylin.\nThuốc Điều Trị: Thuốc Điều Trị là các loại thuốc được sử dụng để điều trị nhiều bệnh lý mạn tính, bao gồm cả những bệnh như lupus, bệnh teo đa hệ thống (MSA), và chảy dịch tai. Thuốc Điều Trị có thể cần dùng trong nhiều năm đối với những người mắc bệnh lupus ít bùng phát hoặc ít triệu chứng. Chúng giúp giảm triệu chứng trong bệnh MSA và làm cho cử động mềm hơn, ngăn ngừa tình trạng căng tức thành khi bị táo bón. \n\nTác dụng phụ phổ biến của Thuốc Điều Trị bao gồm mệt mỏi, đặc biệt khi sử dụng để điều trị động kinh. Thuốc Điều Trị có thể bị ảnh hưởng bởi Bibonlax khi sử dụng đồng thời, do đó cần lưu ý khi kê đơn và sử dụng cùng với các loại thuốc khác. Đối với trẻ sinh non có ống động mạch lớn, Thuốc Điều Trị có thể là một phần quan trọng trong quá trình điều trị.\n\nThuốc Điều Trị cũng được sử dụng để điều trị nấm da đầu, bao gồm cả thuốc uống và thuốc thoa. Tuy nhiên, Thuốc Điều Trị không được sử dụng để điều trị nang nước cạnh buồng trứng. Khi sử dụng Thuốc Điều Trị, cần thông báo cho bác sĩ về tình trạng bệnh lý phụ khoa. Ngoài ra, Thuốc Điều Trị cũng được sử dụng để điều trị rối loạn nhân cách phụ thuộc, cần được kê đơn bởi bác sĩ tâm lý.\n\nĐối với hội chứng Colic, không có thuốc điều trị cụ thể.&lt;SEP&gt;Thuốc điều trị rối loạn nhận thức thần kinh chưa được cấp phép.&lt;SEP&gt;Thuốc điều trị suy giáp bẩm sinh.&lt;SEP&gt;Thuốc được sử dụng nhằm mục đích ngăn chặn sự phát triển của các mạch máu mới và làm giảm sự rò rỉ dịch bên trong mắt gây nên bệnh thoái hóa điểm vàng thể ướt.\nTriệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nQuá Liều Thuốc Ameflu DAYTIME: Quá liều thuốc Ameflu DAYTIME là tình trạng cần xử lý kịp thời.\nTác Dụng Không Mơ Nguyện: Tác dụng không mong muốn có thể xảy ra khi sử dụng vị thuốc.\nNgừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.&lt;SEP&gt;Ngừng dùng thuốc là việc dừng việc sử dụng thuốc khi gặp các dấu hiệu không mong muốn.&lt;SEP&gt;Ngừng dùng thuốc Amiodarone khi gặp các triệu chứng quá liều.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nAn Thần Quá Mức: An thần quá mức là tác dụng phụ thường gặp khi sử dụng Amilavil.&lt;SEP&gt;An thần quá mức là tác dụng phụ của Amitriptylin.\nThuốc Quá Liều: Thuốc quá liều có thể gây triệu chứng bất thường.&lt;SEP&gt;Thuốc quá liều là việc sử dụng thuốc vượt quá liều lượng khuyến cáo.\nQuá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nTriệu Chứng Bất Thường: Triệu chứng bất thường là các dấu hiệu hoặc triệu chứng không bình thường có thể xuất hiện khi sử dụng nhiều loại thuốc khác nhau. Các triệu chứng này bao gồm hành vi lạ như vỗ tay, cắn tay, giảm khả năng giao tiếp bằng mắt, và cắn quần áo, đặc biệt là ở trẻ em bị bệnh tim bẩm sinh khi sử dụng một số loại thuốc cụ thể như Contractubex hoặc Clindamycin. Triệu chứng bất thường cũng có thể liên quan đến việc sử dụng nhiều loại thuốc khác nhau, bao gồm Acemol 325 mg, Agi-Calci, Agilosart, Agifuros, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, Alputine, Alzole, Ambroxol, Amiparen 5 Otsuka, Amlodipin Domesco, Amoxicillin Mekophar, thuốc Ampelop, Atiliver, axit glutamic, Adrenoxyl 10 mg, Bluemint, Bofit F, Cadifast 120, Citicoline, Calcium Boston, Cenditan, Cefuroxim, Cerecaps, Bromelain, và Chlorocina-H. Ngoài ra, các triệu chứng bất thường cũng có thể xuất hiện khi sử dụng các thuốc như Cotrimstada Forte, Danospan, Adagrin, Betadine, Cetirizine, Biosubtyl, kem Biafine, Bixicam, Albis, BoniDiabet, và Berberin. Việc phát hiện sớm các triệu chứng bất thường rất quan trọng để được điều trị kịp thời và tránh các biến cố y tế nghiêm trọng, đặc biệt là ở trẻ em.\n\nTriệu chứng bất thường cũng có thể liên quan đến việc sử dụng axit nalidixic và Alaxan, cũng như thuốc B Complex C và Aluvia. Hội chứng rối loạn sinh tủy cũng có thể gây ra triệu chứng bất thường cần được bác sĩ thăm khám. Khi gặp phải triệu chứng bất thường, người bệnh nên thông báo ngay lập tức cho bác sĩ hoặc nhân viên y tế để có thể xử lý và hỗ trợ kịp thời. Báo cáo những triệu chứng này giúp đảm bảo sức khỏe của người dùng thuốc và ngăn chặn các biến cố y tế có thể xảy ra.\n\nNgoài ra, triệu chứng bất thường có thể xuất hiện khi sử dụng thuốc Broncho-Vaxom, Candesartan, captopril, Carbogast, và Ceftriaxone. Đặc biệt, việc dùng quá liều Acetazolamid, Carbogast, và Cimetidin cũng có thể gây ra triệu chứng bất thường. Trong mọi trường hợp, việc báo cáo kịp thời về các triệu chứng bất thường là rất quan trọng để được xử lý đúng cách và tránh các biến cố y tế nghiêm trọng.\n\nTriệu chứng bất thường cũng có thể xuất hiện khi sử dụng Benzalkonium Chloride, Thuốc Bar, và vượt liều điều trị. Triệu chứng bất thường cũng có thể liên quan đến các bệnh lý tử cung, cần được khám với bác sĩ để tìm nguyên nhân và điều trị kịp thời.&lt;SEP&gt;Triệu chứng bất thường liên quan đến túi tinh và tinh trùng cần được kiểm tra bởi bác sĩ chuyên khoa.\nRối Loạn Điều Tế: Rối loạn điều tế là tác dụng phụ thường gặp khi sử dụng Amilavil.\nBạch Cầu Cấp: Bạch cầu cấp là thể bệnh ác tính ở trẻ em, chiếm khoảng 30% trong số các bệnh ung thư ở trẻ em. Nó bao gồm bạch cầu cấp dòng lympho và các thể khác như ung thư xương, ung thư não.&lt;SEP&gt;Bạch cầu cấp là một thể bệnh cấp tính nguy hiểm, cần điều trị kịp thời.&lt;SEP&gt;Bạch cầu cấp là bệnh lý gây giảm tiểu cầu, tăng nguy cơ chảy máu lâu cầm.&lt;SEP&gt;Bạch cầu cấp là tình trạng tăng nhanh bất thường của các tế bào máu trắng.\nTư Vấn Cụ Thể: Tư vấn cụ thể của bác sĩ/dược sĩ về việc sử dụng Amilavil.\nTác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.&lt;SEP&gt;Tác dụng phụ của một số thuốc có thể ảnh hưởng lên huyết áp.\nThiếu Huyết Não: Thông tin về triệu chứng bất thường liên quan đến việc sử dụng thuốc Bixicam.\nKháng Sinh Phổ Rộng: Kháng sinh phổ rộng là phương pháp điều trị nhiễm trùng huyết do thắt dây chun.&lt;SEP&gt;Kháng sinh phổ rộng được sử dụng để điều trị viêm nhiễm đường tiêu hóa.&lt;SEP&gt;Kháng sinh phổ rộng đôi khi được sử dụng để điều trị nhiễm trùng đường hô hấp trên do vi khuẩn.&lt;SEP&gt;Kháng sinh phổ rộng là loại thuốc được sử dụng để điều trị nhiễm trùng do nhiều loại vi khuẩn khác nhau.\nYếu Mệt: Yếu mệt là triệu chứng của quá liều Amilavil.&lt;SEP&gt;Yếu mệt là triệu chứng của quá liều Amitriptylin.\nAmiodarone - Ngừng Dùng Thuốc: Khi gặp các triệu chứng quá liều, bạn nên ngừng dùng thuốc Amiodarone và lập tức đến cơ sở y tế gần nhất.\nThuốc Điều Trị - Tác Dụng Phụ: Thuốc điều trị có thể có tác dụng phụ nhưng thường không đáng kể với hầu hết bệnh nhân.\nAmitriptylin - An Thần Quá Mức: An thần quá mức là tác dụng phụ của Amitriptylin.\nTác Dụng Không Mơ Nguyện - Vị Thuốc: Vị thuốc có thể gây ra các tác dụng không mong muốn.\nAmitriptylin - Yếu Mệt: Yếu mệt là triệu chứng của quá liều Amitriptylin.\nThuốc Quá Liều - Triệu Chứng Bất Thường: Triệu chứng bất thường có thể xảy ra khi sử dụng thuốc quá liều.\nAmitriptylin - Thay Đổi Hành Vi Bất Thường: Thay đổi hành vi bất thường có thể là tác dụng phụ của amitriptylin.\nBạch Cầu Cấp - Tác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.\nAmilavil - An Thần Quá Mức: An thần quá mức là tác dụng phụ thường gặp khi sử dụng Amilavil.\nKháng Sinh Phổ Rộng - Tác Dụng Phụ: Sử dụng kháng sinh có liên quan đến nhiều tác dụng phụ.\nAmilavil - Yếu Mệt: Yếu mệt là triệu chứng của quá liều Amilavil.\nThận - Triệu Chứng Bất Thường: Triệu chứng bất thường có thể ảnh hưởng đến chức năng thận.\nAmilavil - Rối Loạn Điều Tế: Rối loạn điều tế là tác dụng phụ thường gặp khi sử dụng Amilavil.\nTriệu Chứng Không Liên Quan - Tác Dụng Phụ Thuốc: Tác dụng phụ của thuốc là triệu chứng của triệu chứng không liên quan.\nAmilavil - Tư Vấn Cụ Thể: Sử dụng Amilavil cần tư vấn cụ thể của bác sĩ/dược sĩ.\nThuốc Chống Loạn Nhịp - Triệu Chứng Bất Thường: Sử dụng thuốc chống loạn nhịp có thể gây ra triệu chứng bất thường.\nPregabalin - Triệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nPhù Do Thuốc - Thuốc Điều Trị Tăng Huyết Áp: Phù do thuốc là tác dụng phụ của thuốc điều trị tăng huyết áp.\nAmpicillin Mekophar - Ngừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.\nMã Tiên Thảo - Tác Dụng Phụ: Mã Tiên Thảo có thể gây tác dụng phụ.\nAmeflu DAYTIME - Quá Liều Thuốc Ameflu DAYTIME: Khi xảy ra quá liều thuốc Ameflu DAYTIME, cần xử lý kịp thời.\nPhenylephrine HCl - Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nPhentolamin - Quá Liều Phenylephrine HCl: Phentolamin được dùng trong xử lý tăng huyết áp do quá liều phenylephrine HCl.\nLiệt Kê - Ngừng Dùng Thuốc: Khi gặp các dấu hiệu liệt kê, cần ngừng dùng thuốc.\nLên Cơ Sở Y Tế - Ngừng Dùng Thuốc: Sau khi ngừng dùng thuốc, cần lên cơ sở y tế để được xử lý kịp thời.']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Khi sử dụng Amitriptylin, nếu xuất hiện các triệu chứng bất thường, bạn cần thực hiện các bước sau:
+1. **Dừng Sử Dụng Thuốc**: Ngừng sử dụng Amitriptylin ngay lập tức và không nên tự ý điều chỉnh liều lượng hoặc ngừng sử dụng mà không có sự hướng dẫn của bác sĩ.
+2. **Hướng Dẫn Bác Sĩ**: Thông báo ngay cho bác sĩ hoặc nhân viên y tế về các triệu chứng bất thường mà bạn gặp phải. Bác sĩ sẽ đánh giá tình trạng và đưa ra hướng dẫn cụ thể.
+3. **Xử Trị Triệu Chứng**: Các triệu chứng bất thường có thể bao gồm thay đổi hành vi bất thường, như vỗ tay, cắn tay, giảm khả năng giao tiếp bằng mắt, và cắn quần áo. Cần xử lý triệu chứng cụ thể và hỗ trợ tổng trạng.
+4. **Theo Dõi Chức Năng Tim Mạch**: Nếu có rối loạn nhịp tim, cần theo dõi chặt chẽ chức năng tim mạch bằng cách ghi điện tâm đồ và theo dõi nhịp tim.
+5. **Giải Độc**: Nếu quá liều, cần thực hiện các biện pháp giải độc thông thường, như rửa dạ dày và dùng than hoạt tính.
+6. **Hỗ Trợ Tổng Trạng**: Hỗ trợ tổng trạng bằng cách duy trì chức năng hô hấp, tuần hoàn và thân nhiệt.
+7. **Cân Đo Liều Lượng**: Nếu cần thiết, bác sĩ có thể điều chỉnh liều lượng Amitriptylin hoặc chuyển sang một loại thuốc khác phù hợp hơn.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cần gọi ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8326883536664695</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5036266338461628</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">['Coversyl Plus: Coversyl Plus là thuốc dùng trong điều trị tăng huyết áp, chứa 2 hoạt chất là muối arginine của perindopril và indapamide.&lt;SEP&gt;Coversyl Plus là thuốc điều trị huyết áp cao, mỗi viên chứa 10mg/2,5mg.&lt;SEP&gt;Coversyl Plus là thuốc được sử dụng để kiểm soát huyết áp và có thể gây ra nhiều tác dụng phụ như sưng phù mặt, ho, khó thở, hạ huyết áp, chóng mặt, đau đầu.&lt;SEP&gt;Coversyl Plus là thuốc lợi tiểu giữ kali, được sử dụng trong điều trị huyết áp cao.&lt;SEP&gt;Coversyl Plus là thuốc cần được bảo quản ở nơi khô thoáng với nhiệt độ dưới 30°C.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nTăng Nồng Độ Kali: Tăng nồng độ kali huyết thanh là tác dụng phụ khi dùng Coversyl Plus cùng với thuốc lợi tiểu giữ kali.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nNguy Cơ Tụt Huyết Áp: Nguy cơ tụt huyết áp là tình trạng cần thận trọng khi dùng Coperil Plus.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nBệnh Não Do Gan: Bệnh não do gan là tình trạng sức khỏe cần ngừng sử dụng Coversyl Plus.&lt;SEP&gt;Bệnh não do gan là bệnh cần ngưng dùng Coversyl Plus.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Hạ Huyết Áp Khác: Thuốc hạ huyết áp khác có thể làm tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nBồ Công Anh: Bồ Công Anh, còn được gọi là rau mũi cày, là một loại dược liệu và thảo dược dân gian phổ biến tại Việt Nam. Loài này có vị ngọt, đắng và tính hàn, tác động vào nhiều kinh như tỳ, vị, thận, đại tràng, tiểu tràng, bàng quang, can đởm. Bồ Công Anh được sử dụng rộng rãi trong y học cổ truyền và hiện đại, thường kết hợp với thổ phục linh trong các bài thuốc đông y. Nó cũng là một thành phần quan trọng trong các bài thuốc hỗ trợ điều trị xơ gan và viêm bàng quang.\n\nBồ Công Anh còn được biết đến với nhiều tác dụng sức khỏe khác nhau. Nó được sử dụng để chữa sưng vú và cung cấp các chất dinh dưỡng quý như beta carotene, lutein, polyphenol, vitamin C và E, cùng các vi lượng như canxi, kali, phospho, magie, sắt. Tuy nhiên, cần phải thận trọng khi sử dụng Bồ Công Anh vì nó là một dược phẩm tự nhiên có nhiều tác dụng tích cực nhưng cũng tiềm ẩn nguy cơ nếu không được sử dụng đúng cách.\n\nBồ Công Anh được sử dụng trong nhiều bài thuốc điều trị khác nhau. Nó là thành phần trong bài thuốc điều trị thủy đậu ở trẻ em, mụn nhọt chốc lở, lở ngứa, mụn nhọt, viêm họng, viêm xoang, ung nhọt sưng tấy, viêm lở da, và ống tai ngoài. Ngoài ra, Bồ Công Anh còn được sử dụng trong bài thuốc trị đau nhức xương khớp, thấp nhiệt sinh lở và sưng chân, có tác dụng thanh nhiệt, giải độc, lợi tiểu. Nó cũng là một trong các vị thuốc được sử dụng trong bài thuốc chữa tràng nhạc, sưng tuyến giáp, quai bị, viêm tuyến vú, viêm hạch, và chữa hỏa bốc cao.\n\nNgoài ra, Bồ Công Anh còn được sử dụng trong bài thuốc điều trị viêm túi mật và thấp khớp mạn tính. Nó cũng được sử dụng trong bài thuốc sắc uống và điều trị cổ trướng do xơ gan và viêm gan do virus.&lt;SEP&gt;Bồ công anh là dược liệu được sử dụng trong các bài thuốc chữa mụn nhọt và đầu đinh.\nNồng Độ Creatinin: Nồng độ creatinin cần được theo dõi khi sử dụng Beatil ở người cao tuổi và người bị suy giảm chức năng thận.&lt;SEP&gt;Nồng độ creatinin trong huyết thanh được kiểm tra để loại trừ suy thận.&lt;SEP&gt;Nồng độ creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nThận Trọng Khi Sử Dụng: Thận trọng khi sử dụng Agimycob với những người có tiền sử dị ứng, bệnh thần kinh trung ương hay ngoại biên.&lt;SEP&gt;Thận trọng khi sử dụng Bồ công anh là phương pháp điều trị cần thiết để tránh tác dụng phụ.&lt;SEP&gt;Thận trọng khi sử dụng Canditral, phải xét nghiệm định kỳ enzyme gan ở bệnh nhân có tiền sử chức năng gan bất thường.\nCoperil Plus: Viên nén Coperil Plus có tác dụng điều trị tăng huyết áp nguyên phát cho các đối tượng huyết áp không kiểm soát được với đơn trị.&lt;SEP&gt;Coperil Plus là thuốc được sử dụng theo chỉ định của bác sĩ, có thể tương tác với các loại thuốc khác như thuốc kháng viêm không steroid, tetracosactid, corticoid, imipramin, thuốc an thần và thuốc uống hạ đường huyết.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nCung Lượng Tim Tăng: Cung lượng tim tăng là một triệu chứng huyết động thường gặp trong suy gan cấp.\nLưu Ý: Lưu ý là các hướng dẫn cần tuân thủ khi sử dụng Amiparen 5 Otsuka.&lt;SEP&gt;Lưu ý khi sử dụng thuốc Cenditan bao gồm việc thận trọng ở bệnh nhân suy giảm chức năng gan, chức năng thận, thông báo cho bác sĩ về bất thường hay tác dụng không mong muốn, đọc kỹ hướng dẫn sử dụng và xem hạn dùng của thuốc trước khi sử dụng.&lt;SEP&gt;Lưu ý là thông tin cần thiết trước khi sử dụng thuốc.&lt;SEP&gt;Lưu ý về việc lá của một loài cây có chứa độc tố.\nCoversyl: Coversyl là thuốc tim mạch chứa thành phần hoạt chất perindopril arginine, điều trị tăng huyết áp và suy tim.&lt;SEP&gt;Coversyl là tên thương mại của Perindopril.&lt;SEP&gt;Coversyl là biệt dược chứa hoạt chất perindopril, được chỉ định để điều trị các bệnh về tim mạch như tăng huyết áp, suy tim sung huyết.&lt;SEP&gt;Coversyl là thuốc chứa hoạt chất perindopril, được chỉ định để điều trị tăng huyết áp và suy tim sung huyết.&lt;SEP&gt;Coversyl là thuốc hạ huyết áp, có thể gây hạ huyết áp toàn thân khi sử dụng ở bệnh nhân suy tim.\nCoversyl Plus - Tiêu Chảy: Coversyl Plus có thể gây tiêu chảy.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nBuồn Nôn - Coversyl Plus: Coversyl Plus có thể gây buồn nôn.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nCoperil Plus - Đái Tháo Đường: Coperil Plus cần thận trọng khi dùng cho bệnh nhân đái tháo đường.\nBồ Công Anh - Thận Trọng Khi Sử Dụng: Thận trọng khi sử dụng Bồ công anh để tránh tác dụng phụ.\nBuồn Nôn - Coperil Plus: Buồn nôn là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nBác Sĩ - Tác Dụng Phụ: Bác sĩ cần thông báo nếu có tác dụng phụ khi dùng thuốc.\nChóng Mặt - Coversyl Plus: Coversyl Plus có thể gây chóng mặt.\nLưu Ý - Thuốc: Lưu ý đề cập rằng cần hỏi ý kiến bác sĩ trước khi sử dụng thuốc.\nCoversyl Plus - Táo Bón: Coversyl Plus có thể gây táo bón.\nBảo Vệ Gan - Thuốc: Khi sử dụng thuốc, cần hỏi ý kiến bác sĩ về tác dụng có hại đối với gan.\nCoversyl Plus - Đau Đầu: Coversyl Plus có thể gây đau đầu.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\nCoversyl Plus - Tăng Huyết Áp: Coversyl Plus được chỉ định dùng để điều trị tăng huyết áp.\nHậu Quả Không Mong Muốn - Người Bệnh: Người bệnh cần tránh hậu quả không mong muốn bằng cách sử dụng thuốc đúng cách.\nChóng Mặt - Coversyl: Chóng mặt là tác dụng phụ thường gặp khi sử dụng Coversyl.\nSử Dụng - Tùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc.\nCoversyl - Đau Đầu: Đau đầu là tác dụng phụ thường gặp khi sử dụng Coversyl.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nCoversyl - Tăng Huyết Áp: Coversyl được chỉ định điều trị tăng huyết áp.&lt;SEP&gt;Coversyl được chỉ định để điều trị tăng huyết áp.\nChóng Mặt - Coperil Plus: Chóng mặt là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoperil Plus - Đau Đầu: Đau đầu là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoversyl Plus - Suy Thận: Người suy thận cần thận trọng khi sử dụng Coversyl Plus.&lt;SEP&gt;Người suy thận cần thận trọng khi dùng Coversyl Plus.\nCoversyl Plus - Mệt Mỏi: Mệt mỏi là triệu chứng của quá liều Coversyl Plus.&lt;SEP&gt;Coversyl Plus có thể gây mệt mỏi.\nCoversyl Plus - Nôn: Nôn là triệu chứng của quá liều Coversyl Plus.\nCoperil Plus - Suy Thận: Coperil Plus cần thận trọng khi dùng cho bệnh nhân suy thận.\nCoversyl - Mệt Mỏi: Mệt mỏi là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl - Dị Ứng: Dị ứng là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl Plus - Ho: Coversyl Plus có thể gây ho.\nCoperil Plus - Nôn: Nôn là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nCoperil Plus - Suy Tim: Coperil Plus cần thận trọng khi dùng cho bệnh nhân suy tim.\nCoversyl Plus - Khó Thở: Coversyl Plus có thể gây khó thở.\nAspirin - Coversyl: Aspirin tương tác với Coversyl.\nCoversyl - Triệu Chứng: Coversyl có thể gây ra các triệu chứng không mong muốn.\nCoversyl Plus - Suy Gan: Người suy gan cần thận trọng khi sử dụng Coversyl Plus.&lt;SEP&gt;Người suy gan cần thận trọng khi dùng Coversyl Plus.\nCoversyl Plus - Hạ Huyết Áp: Coversyl Plus được chỉ định để điều trị hạ huyết áp.&lt;SEP&gt;Coversyl Plus có thể gây hạ huyết áp.\nCoversyl - Hạ Huyết Áp: Coversyl được sử dụng để điều trị hạ huyết áp.\nCoversyl Plus - Rối Loạn Tiêu Hóa: Coversyl Plus có thể gây rối loạn tiêu hóa.\nCoversyl - Rối Loạn Tiêu Hóa: Rối loạn tiêu hóa là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl Plus - Phụ Nữ Mang Thai: Phụ nữ mang thai không nên dùng Coversyl Plus.\nAmlodipin - Coversyl Plus: Coversyl Plus được so sánh với thuốc Amlodipin trong bài viết.\nQuá Liều - Rối Loạn Muối Và Nước: Quá liều Coversyl Plus có thể gây rối loạn muối và nước.\nBuồn Ngủ - Coversyl Plus: Buồn ngủ là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Trẻ Em: Trẻ em là đối tượng không nên sử dụng Coversyl Plus.\nCoversyl Plus - Khô Miệng: Coversyl Plus có thể gây khô miệng.\nCoversyl Plus - Perindopril: Perindopril là một trong hai hoạt chất chính của Coversyl Plus.\nCoversyl - Khô Miệng: Khô miệng là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nCoversyl - Perindopril: Coversyl chứa hoạt chất perindopril.\nCoperil Plus - Rối Loạn Giấc Ngủ: Rối loạn giấc ngủ là tác dụng phụ liên quан к тексту, но он не влияет на содержание или вывод. Давайте продолжим с русским переводом для ясности:\nCoperil Plus - Khô Miệng: Khô miệng là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoversyl Plus - Đau Họng: Coversyl Plus có thể gây đau họng.\nCoperil Plus - Phát Ban: Phát ban là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nCoperil Plus - Perindopril: Perindopril là thành phần chính trong Coperil Plus.\nAllopurinol - Coversyl Plus: Allopurinol có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Ù Tai: Coversyl Plus có thể gây ù tai.\nBaclofen - Coversyl Plus: Baclofen có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl - Suy Thận Cấp: Suy thận cấp là tác dụng phụ có thể xảy ra khi sử dụng Coversyl cùng với thuốc chống viêm không steroid.\nCoversyl - Ù Tai: Ù tai là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl Plus - Giảm Bạch Cầu: Allopurinol, eytostatic hoặc các thuốc hỗ trợ miễn dịch, các corticosteroid tổng hợp hoặc procainamid có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Người Cao Tuổi: Người cao tuổi là đối tượng sử dụng Coversyl Plus.\nCoversyl Plus - Phản Ứng Dị Ứng: Coversyl Plus có thể gây phản ứng dị ứng.\nCoversyl - Phù Mạch: Phù mạch là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nNồng Độ Creatinin - Thiếu Máu Não: Kiểm tra nồng độ creatinin trong huyết thanh có thể giúp loại trừ suy thận như nguyên nhân của thiếu máu não.\nCoversyl Plus - Rối Loạn Tâm Thần: Rối loạn tâm thần là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Hạ Kali Máu: Coversyl Plus có thể gây hạ kali máu.\nCoperil Plus - Phù Mạch: Phù mạch là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoversyl Plus - Người Lớn: Người lớn là đối tượng sử dụng Coversyl Plus.\nCoperil Plus - Hạ Natri Máu: Hạ natri máu là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nCo Thắt Phế Quản - Coversyl: Co thắt phế quản là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nCoversyl - Hoa Mắt: Hoa mắt là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl Plus - Ngất Xỉu: Ngất xỉu là triệu chứng của quá liều Coversyl Plus.\nCoperil Plus - Mẩn Ngứa: Mẩn ngứa là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nCoversyl - Thuốc Ức Chế Men Chuyển: Thuốc ức chế men chuyển tương tác với Coversyl.\nCoperil Plus - Đánh Trống Ngực: Đánh trống ngực là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nChuột Rút - Coversyl Plus: Chuột rút là triệu chứng của quá liều Coversyl Plus.&lt;SEP&gt;Coversyl Plus có thể gây chuột rút.\nCoversyl - Ho Khan: Ho khan là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl - Cyclosporin: Cyclosporin tương tác với Coversyl.\nCoversyl - Rối Loạn Thị Giác: Rối loạn thị giác là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl - Khó Ngủ: Khó ngủ là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nCoversyl - Suy Tim Sung Huyết: Coversyl được chỉ định điều trị suy tim sung huyết.&lt;SEP&gt;Coversyl được chỉ định để điều trị suy tim sung huyết.&lt;SEP&gt;Coversyl có thể gây hạ huyết áp toàn thân khi sử dụng ở bệnh nhân suy tim.\nCung Lượng Tim Tăng - Suy Gan Cấp: Suy gan cấp có thể gây ra cung lượng tim tăng.\nChoáng Váng - Coversyl: Choáng váng do tụt huyết áp là tác dụng phụ thường gặp khi sử dụng Coversyl.\nCoversyl Plus - Rối Loạn Vị Giác: Coversyl Plus có thể gây rối loạn vị giác.\nCoversyl Plus - Thanh Thải Creatinin: Thanh thải creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Procainamid: Procainamid có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Nhịp Tim Bất Thường: Coversyl Plus có thể gây nhịp tim bất thường.\nCoversyl Plus - Lithi: Lithi có thể gây tương tác với Coversyl Plus, làm tăng nồng độ lithi và nguy cơ độc hại.\nCoversyl Plus - Thuốc Chống Viêm Không Steroid: Thuốc chống viêm không steroid có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Thuốc Gây Mê: Thuốc gây mê có thể tăng tác dụng hạ huyết áp của Coversyl Plus.\nCoperil Plus - Ho Khan: Ho khan là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoversyl Plus - Hạ Huyết Áp Quá Mức: Thuốc hạ huyết áp khác có thể làm tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nBeatil - Nồng Độ Creatinin: Nồng độ creatinin cần được theo dõi khi sử dụng Beatil ở người cao tuổi và người bị suy giảm chức năng thận.\nCoversyl - Heparin: Heparin tương tác với Coversyl.\nCoversyl - Lú Lẩn: Lú lẫn là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nCoversyl Plus - Nhạy Cảm Ánh Sáng: Coversyl Plus có thể gây nhạy cảm ánh sáng.&lt;SEP&gt;Nhạy cảm ánh sáng là triệu chứng cần ngưng dùng Coversyl Plus.\nBệnh Nhân Suy Thận - Coversyl Plus: Bệnh nhân suy thận là đối tượng cần điều chỉnh liều dùng Coversyl Plus.\nBệnh Nhân Suy Gan - Coversyl Plus: Bệnh nhân suy gan là đối tượng cần điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Nồng Độ Kali: Nồng độ kali là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Indapamide: Indapamide là một trong hai hoạt chất chính của Coversyl Plus.\nCoperil Plus - Hạ Kali Máu: Hạ kali máu là tác dụng phụ liên quan đến indapamid trong Coperil Plus.\nCoversyl Plus - Thuốc Lợi Tiểu Giữ Kali: Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.\nCoversyl Plus - Vàng: Vàng có thể gây phản ứng nitritoid khi dùng cùng Coversyl Plus.\nCoversyl - Thuốc Ức Chế Miễn Dịch: Thuốc ức chế miễn dịch tương tác với Coversyl.\nCoversyl Plus - Nồng Độ Creatinin: Nồng độ creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nAxit Acetylsalicylic - Coversyl Plus: Axit acetylsalicylic có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Rối Loạn Muối Và Nước: Rối loạn muối và nước là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Thuốc Corticosteroid: Thuốc corticosteroid có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Thuốc Lợi Tiểu (Nhóm Thiazide Hoặc Lợi Tiểu Quai): Thuốc lợi tiểu (nhóm thiazide hoặc lợi tiểu quai) có thể làm giảm thể tích tuần hoàn và gây nguy cơ hạ huyết áp khi dùng cùng Coversyl Plus.\nCoversyl Plus - Sưng Phù Mặt: Coversyl Plus có thể gây sưng phù mặt.\nCoversyl Plus - Tia UVA: Người dùng Coversyl Plus cần tránh tiếp xúc với tia UVA.\nBệnh Não Do Gan - Coversyl Plus: Coversyl Plus có thể gây bệnh não do gan.&lt;SEP&gt;Bệnh não do gan là bệnh cần ngưng dùng Coversyl Plus.\nCoversyl Plus - Phụ Nữ Có Kế Hoạch Mang Thai: Phụ nữ có kế hoạch mang thai không nên dùng Coversyl Plus.\nCoversyl Plus - Thuốc Chống Trầm Cảm Giống Imipramine: Thuốc chống trầm cảm giống imipramine có thể tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nCoversyl Plus - Thuốc Hạ Huyết Áp Khác: Thuốc hạ huyết áp khác có thể làm tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nCoversyl Plus - Eytostatic: Eytostatic có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Thuốc Hỗ Trợ Miễn Dịch: Thuốc hỗ trợ miễn dịch có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Tăng Nồng Độ Kali: Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.\nCoversyl Plus - Giữ Nơi Khô Thoáng: Coversyl Plus cần được bảo quản ở nơi khô thoáng.\nCoversyl Plus - Dưới 30°C: Coversyl Plus cần được bảo quản ở nhiệt độ dưới 30°C.\nCoversyl Plus - Để Xa Tầm Với: Coversyl Plus cần được bảo quản xa tầm với của trẻ em.\nCoversyl Plus - Thạc Sĩ, Dược Sĩ Trương Văn Đạt: Thạc Sĩ, Dược Sĩ Trương Văn Đạt đã chia sẻ thông tin về Coversyl Plus.\nBất Lực - Coperil Plus: Bất lực là tác dụng phụ liên quan đến perindopril trong Coperil Plus.\nCoversyl - Tăng Kali Máu: Tăng kali máu là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nCoperil Plus - Thẩm Phân Máu: Coperil Plus cần thận trọng khi dùng cho bệnh nhân đang thẩm phân máu.\nCoperil Plus - Indapamid: Indapamid là thành phần chính trong Coperil Plus, được dùng để điều trị huyết áp cao, suy tim và phù nề.&lt;SEP&gt;Indapamid là thành phần chính trong Coperil Plus.\nCoversyl - Lithi: Lithi tương tác với Coversyl.&lt;SEP&gt;Tăng độc tính Lithi là tác dụng phụ khi sử dụng Coversyl cùng với Lithi.\nCoversyl - Thuốc Chống Viêm Không Steroid: Thuốc chống viêm không steroid tương tác với </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Coversyl Plus cho những người bị suy gan hoặc suy thận, cần lưu ý một số điểm sau:
+- Đối với người suy gan, việc sử dụng Coversyl Plus cần được thận trọng. Coversyl Plus chứa hoạt chất indapamide, một loại thuốc lợi tiểu giữ kali, có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng với thuốc lợi tiểu giữ kali khác. 
+- Đối với người suy thận, cần điều chỉnh liều dùng Coversyl Plus theo chỉ định của bác sĩ. Cần kết hợp việc tái khám thường xuyên và kiểm soát định kỳ nồng độ creatinin và kali. Coversyl Plus chống chỉ định dùng thuốc trên bệnh nhân suy thận nặng và vừa (độ thanh thải creatinin dưới 60ml/phút).
+- Cần theo dõi chặt chẽ các triệu chứng và tình trạng sức khỏe của bệnh nhân để phát hiện sớm bất kỳ tác dụng phụ nào có thể xảy ra.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thận trọng dùng thuốc Coversyl Plus ở người suy gan, suy thận.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.849236763961307</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.9623091909653267</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>['Rối Loạn Khó Tiêu: Rối loạn khó tiêu là tình trạng mà Argide hỗ trợ điều trị.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nBệnh Lý Về Gan: Bệnh lý về gan là các tình trạng bệnh liên quan đến gan được hỗ trợ điều trị bằng Argide.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nPhân Thủy: Phân thủy là tác dụng phụ khi dùng Argadin.\ndược sĩ: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTình Trạng Cương Dương: Tình trạng cương dương có thể xảy ra là tác dụng phụ khi dùng Argadin.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTổng Hợp: Tổng hợp là cách xử lý khi quên một liều Argide.\nDược Sĩ: Dược Sĩ là chuyên gia tư vấn sử dụng thuốc an toàn và hiệu quả. Họ cung cấp hướng dẫn cụ thể cho bệnh nhân về cách sử dụng các loại thuốc khác nhau, bao gồm cả việc tư vấn về Actiso Ladophar, Baby Septol, Bagocit, Belara và Calcium Boston. Dược sĩ không chỉ giới thiệu thông tin chi tiết về từng sản phẩm mà còn hỗ trợ bệnh nhân trong việc hiểu rõ cách sử dụng chúng một cách an toàn và hiệu quả nhất. \n\nNgoài ra, Dược Sĩ cũng là người tư vấn cách xử lý thuốc không còn sử dụng. Họ có chuyên môn về thuốc và hướng dẫn sử dụng thuốc, đồng thời cung cấp tư vấn về thuốc. Khi bệnh nhân sử dụng Boganic, Dược Sĩ sẽ được thông báo về tình trạng của họ để có thể đưa ra những lời khuyên phù hợp. \n\nDược sĩ cũng là người chuyên môn trong việc tư vấn và quản lý thuốc. Họ có kiến thức sâu rộng về thuốc và có thể tư vấn về việc sử dụng thuốc một cách hiệu quả và an toàn. Ví dụ, Dược sĩ Nguyễn Hoàng Bảo Duy là một chuyên gia về dược phẩm và thuốc, với khả năng tư vấn và hỗ trợ bệnh nhân trong việc sử dụng thuốc đúng cách.\nTăng Ammoniac Huyết: Tăng ammoniac huyết là tác dụng phụ của thuốc Argide, đặc biệt ở người có nhiễm acid hữu cơ trong máu.&lt;SEP&gt;Tăng ammoniac huyết là tình trạng mà arginin được chỉ định để điều trị.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nArgide: Thuốc Argide được bào chế dưới dạng viên nang cứng hoặc mềm chứa 200 mg hoạt chất Arginine, được sử dụng để điều trị bệnh lý tăng Amoniac máu và hỗ trợ điều trị rối loạn tiêu hóa.&lt;SEP&gt;Thuốc Argide được sử dụng để điều trị bệnh lý tăng Amoniac máu và hỗ trợ các rối loạn khó tiêu.&lt;SEP&gt;Argide là thuốc có chống chỉ định cho những người có tiền sử dị ứng với thành phần của thuốc, tăng amoniac huyết, rối loạn chu trình ure và thiếu hụt enzym arginase. Argide có thể gây tác dụng liên quan đến thần kinh như chóng mặt và có thể gây đau bụng, tiêu chảy khi dùng quá liều.&lt;SEP&gt;Thuốc Argide có tác dụng phụ như buồn nôn, nôn ói, nhức đầu và có thể tương tác với các thuốc khác như Thiazid, Xylitol, Aminophyllin, Sulfonylurea, và Spironolacton.&lt;SEP&gt;Argide là thuốc được sản xuất dưới dạng viên nang, dùng hỗ trợ các bệnh lý về gan.\nbác sĩ: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArginine Hydrochloride: Arginine hydrochloride là hoạt chất chính trong Argide, giúp ổn định nồng độ Arginine trong máu và ngăn chặn sự tăng Amoniac huyết.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nThông Báo Bác Sĩ: Cần thông báo cho bác sĩ về tình trạng sức khỏe khi sử dụng thuốc Agi-Calci.\nBệnh: Bệnh là thuật ngữ chung chỉ tình trạng sức khỏe không tốt, cần được điều trị. Bệnh có thể là kết quả của nhiều yếu tố khác nhau và có thể gây ra lo lắng, đặc biệt là đối với những người chưa có con. Bệnh có thể được phát hiện và điều trị kịp thời nếu nhận thấy dấu hiệu bất thường. Một số bệnh có tiên lượng khá tốt, với khoảng 90% người bệnh được chữa khỏi chỉ bằng kháng sinh và không còn để lại di chứng. Tuy nhiên, cũng có một số bệnh chưa được mô tả cụ thể và có thể tái phát nếu ngừng thuốc sớm.\n\nBệnh có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng các loại thảo dược như cây Đại, Cần Tây, cây Bòng Bong, lá dứa, dền gai, hoa đậu biếc, và hồi đầu thảo. Thông tin về tác dụng của một số loại cây này chưa có nhiều nghiên cứu khoa học rõ ràng. Bệnh có thể xảy ra khi pH nước bọt chệch khỏi phạm vi lý tưởng trong một thời gian dài.\n\nBệnh cũng có thể được điều trị bằng Lô căn hoặc Tiền. Bệnh là tình trạng sức khỏe không bình thường và có thể được theo dõi và điều trị tại nhà nếu nhẹ. Bệnh có thể gây ra triệu chứng ngứa và nổi mề đay.\n\nTóm lại, bệnh là tình trạng sức khỏe không tốt cần được điều trị, có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng các loại thảo dược và dược liệu, cũng như các phương pháp điều trị khác như Lô căn và Tiền.&lt;SEP&gt;Bệnh là thuật ngữ chung để chỉ các trạng thái bệnh lý.&lt;SEP&gt;Bệnh cần được đánh giá tình trạng thông qua các xét nghiệm và kiểm tra y tế.&lt;SEP&gt;Bệnh là tình trạng sức khỏe bất thường cần được điều trị.&lt;SEP&gt;Bệnh là tình trạng mà việc rửa tay kỹ có thể giúp ngăn ngừa.\nThuốc Động Kinh: Thuốc động kinh là các loại thuốc được sử dụng để điều trị động kinh.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nSử Dụng: Sử dụng cúc tần cần thận trọng và tham khảo ý kiến bác sĩ.\nTùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc mà không tham khảo ý kiến chuyên gia.\nArgide - Tiêu Chảy: Argide có thể gây tiêu chảy khi dùng quá liều.&lt;SEP&gt;Khi sử dụng Argide, cần chú ý đến triệu chứng tiêu chảy.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nArgide - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Argide.&lt;SEP&gt;Buồn nôn là tác dụng phụ thường gặp của thuốc Argide.\ndược sĩ - thuốc: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArgide - Chóng Mặt: Argide có thể gây tác dụng liên quan đến thần kinh như chóng mặt.\nDược Sĩ - Thuốc: Dược sĩ tư vấn về việc sử dụng thuốc.\nArgide - Đau Bụng: Argide có thể gây đau bụng khi dùng quá liều.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nArgide - Dị Ứng: Argide chống chỉ định cho những người có tiền sử dị ứng với thành phần của thuốc.\nbác sĩ - thuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArgide - Ngứa: Ngứa là tác dụng phụ hiếm gặp của thuốc Argide.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nArgide - Gan: Argide hỗ trợ điều trị các bệnh lý về gan.\nBệnh - Vị Thuốc: Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được dùng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng trong điều trị bệnh.\nArgide - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng và cân nhắc giữa lợi ích và nguy cơ trước khi sử dụng Argide.\nBệnh - Thuốc: Thuốc được sử dụng để chữa bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.\nArgide - Hạ Huyết Áp: Hạ huyết áp là tác dụng phụ của thuốc Argide.\nDược Liệu - Hướng Dẫn: Hướng dẫn của bác sĩ về cách sử dụng dược liệu để phát huy tác dụng và đảm bảo an toàn cho sức khỏe.\nArgide - Nhức Đầu: Nhức đầu là tác dụng phụ thường gặp của thuốc Argide.\nSử Dụng - Tùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc.\nArgide - Phụ Nữ Cho Con Bú: Phụ nữ cho con bú cần thận trọng và cân nhắc giữa lợi ích và nguy cơ trước khi sử dụng Argide.\nArgide - Đầy Hơi: Khi sử dụng Argide, cần chú ý đến triệu chứng đầy hơi.\nArgide - Trướng Bụng: Khi sử dụng Argide, cần chú ý đến triệu chứng trướng bụng.\nArgide - Nôn Ói: Nôn ói là tác dụng phụ thường gặp của thuốc Argide.\nArgide - Mề Đay: Mề đay là tác dụng phụ hiếm gặp của thuốc Argide.\nArgide - Giảm Tiểu Cầu: Giảm tiểu cầu là tác dụng phụ của thuốc Argide.\nThuốc Động Kinh - Động Kinh: Thuốc động kinh được sử dụng để điều trị động kinh.\nArginin - Tăng Ammoniac Huyết: Arginin được chỉ định để điều trị tăng ammoniac huyết.\nArgide - Vận Hành Máy Móc: Người vận hành máy móc cần dừng vận hành máy nếu gặp tác dụng phụ liên quan đến thần kinh khi sử dụng Argide.\nArgide - Ánh Sáng Mặt Trời: Argide cần tránh tiếp xúc trực tiếp với ánh nắng mặt trời.\nArgide - Người Lái Xe: Người lái xe cần dừng lái xe nếu gặp tác dụng phụ liên quan đến thần kinh khi sử dụng Argide.\nArgide - Thiazid: Argide có thể tương tác với Thiazid, làm tăng nồng độ insulin trong huyết tương.\nArgide - Tăng Kali Huyết: Tăng kali huyết là tác dụng phụ của thuốc Argide, đặc biệt ở người có bệnh lý về gan, thận, tiểu đường.\nArgide - Sulfonylurea: Argide có thể tương tác với Sulfonylurea, ức chế đáp ứng của glucagon huyết tương với Arginin.\nArgide - Viên Nang: Argide được sản xuất dưới dạng viên nang.\nArgide - Spironolacton: Argide có thể tương tác với Spironolacton, gây tăng kali huyết.\nArgide - Phù Não: Argide có thể gây phù não khi dùng quá liều ở trẻ em.\nArgide - Nhiễm Acid Chuyển Hóa: Argide có thể gây nhiễm acid chuyển hóa khi dùng quá liều.\nAgi-Calci - Thông Báo Bác Sĩ: Cần thông báo cho bác sĩ về tình trạng sức khỏe khi sử dụng thuốc Agi-Calci.\nArgide - Co Cứng Cơ Bụng: Co cứng cơ bụng là tác dụng phụ của thuốc Argide.\nArgide - Chu Trình Ure: Argide hỗ trợ điều trị rối loạn chuyển hóa Amoniac trong chu trình Urê.\nArgide - Rối Loạn Chu Trình Ure: Argide chống chỉ định cho người đang rối loạn chu trình ure và thiếu hụt enzym arginase.&lt;SEP&gt;Rối loạn chu trình ure là chống chỉ định của thuốc Argide.\nArgide - Tăng Ammoniac Huyết: Tăng ammoniac huyết là chống chỉ định của thuốc Argide.\nArgide - Tăng Amoniac Huyết: Argide chống chỉ định cho người đang bị tăng amoniac huyết do nhiễm acid hữu cơ trong máu.\nArgide - Thở Quá Nhanh: Argide có thể gây thở quá nhanh khi dùng quá liều.\nArgide - Arginine Hydrochloride: Argide chứa hoạt chất Arginine hydrochloride.\nArgide - Tăng Ammoniac Máu: Argide được sử dụng để điều trị bệnh lý tăng Ammoniac máu.\nArgide - Arginosuccinic Niệu: Argide được sử dụng để điều trị Arginosuccinic niệu.\nArgide - Mẫn Đỏ: Mẫn đỏ là tác dụng phụ hiếm gặp của thuốc Argide.\nArgide - Xylitol: Argide có thể tương tác với Xylitol, làm tăng nồng độ insulin trong huyết tương.\nAminophyllin - Argide: Argide có thể tương tác với Aminophyllin, làm tăng nồng độ insulin trong huyết tương.\nArgide - Rối Loạn Khó Tiêu: Argide hỗ trợ điều trị rối loạn khó tiêu.\nArgide - Bệnh Lý Về Gan: Argide được sử dụng hỗ trợ điều trị các bệnh lý về gan.\nActis - Argide: Argide có thành phần tương tự với Actis.\nArgide - Tăng Amoniac Máu: Argide được sử dụng để điều trị bệnh lý tăng Amoniac máu.\nArgide - Thiếu Enzyme Chuyển Hóa: Argide điều trị cho bệnh nhân thiếu enzyme chuyển hóa trong chu trình Ure.\nArgide - Citrulin Máu: Argide được sử dụng để điều trị Citrulin máu.\nArgide - Ornithine Carbamyl Transferase: Argide được sử dụng để điều trị bệnh nhân thiếu Ornithine carbamyl transferase.\nArgide - Carbamylphosphate Synthetase: Argide được sử dụng để điều trị bệnh nhân thiếu Carbamylphosphate synthetase.\nArgide - N-Acetyl Glutamate Synthetase: Argide hỗ trợ điều trị người thiếu N-acetyl glutamate synthetase.\nArgide - Thời Tiết Khô RáO: Argide cần được bảo quản ở nơi khô ráo.\nArgide - Nhiệt Độ Dưới 30ºC: Argide cần được bảo quản ở nhiệt độ dưới 30ºC.\nArgadin - Phân Thủy: Phân thủy là tác dụng phụ khi dùng Argadin.\nArgadin - Tình Trạng Cương Dương: Tình trạng cương dương có thể xảy ra là tác dụng phụ khi dùng Argadin.\nThuốc Chống Động Kinh - Thuốc Động Kinh: Thuốc chống động kinh có thể tương tác với các loại thuốc động kinh khác.\nArginine Hydrochloride - Tăng Ammoniac Máu: Arginine hydrochloride giúp ổn định nồng độ Arginine trong máu, ngăn chặn sự tăng Ammoniac huyết.']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong một số trường hợp cụ thể ngoài việc điều trị bệnh lý tăng Amoniac máu:
+1. **Hỗ trợ điều trị rối loạn tiêu hóa**: Argide hỗ trợ điều trị các chứng rối loạn khó tiêu, giúp cải thiện khả năng tiêu hóa của cơ thể.
+2. **Hỗ trợ các bệnh lý về gan**: Argide cũng được sử dụng để hỗ trợ điều trị các bệnh lý về gan, giúp cải thiện chức năng gan và hỗ trợ quá trình phục hồi.
+3. **Hỗ trợ điều trị các tình trạng liên quan đến rối loạn chu trình ure**: Argide hỗ trợ điều trị cho bệnh nhân thiếu các enzym chuyển hóa trong chu trình ure, như N-acetyl glutamate synthetase, carbamyl phosphat synthetase, ornithine carbamyl transferase, argininosuccinate synthetase, và argininosuccinate lyase.
+4. **Hỗ trợ điều trị Argininosuccinic niệu và Citrulin máu**: Argide được sử dụng để điều trị cho bệnh nhân tăng Amoniac máu bị Citrulin máu, Argininosuccinic niệu, và thiếu men N-acetyl glutamate synthetase.
+### Lưu ý
+Khi sử dụng Argide, người dùng cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo của bác sĩ. Người dùng cũng cần lưu ý đến các tác dụng phụ có thể xảy ra như buồn nôn, nôn ói, nhức đầu, và các phản ứng dị ứng như mẫn đỏ, mề đay, ngứa, giảm tiểu cầu, hạ huyết áp, co cứng cơ bụng, tăng kali huyết, và các triệu chứng khác. 
+### Bảo quản
+Argide cần được bảo quản đúng cách: trong bao bì kín, ở nơi khô ráo và thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời, và nhiệt độ bảo quản nên dưới 30°C.
+### Tham khảo
+- [1] argide.txt
+- [3] brudoxil.txt
+- [4] tac-dung-da-dang-cua-gang-tu-hu.txt</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide hỗ trợ điều trị các chứng rối loạn khó tiêu và hỗ trợ các bệnh lý về gan.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8110123770373304</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9152530942343327</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>['Người Bệnh Ca O Tuổi: Người bệnh cao tuổi là một trong những đối tượng cần thận trọng khi dùng Clindamycin.\nNgười Cao Tuổi: Người Cao Tuổi, từ 65 tuổi trở lên, là đối tượng cần được chăm sóc đặc biệt và điều chỉnh liều lượng của một số loại thuốc cụ thể. Họ thường gặp phải suy giảm chức năng thận, làm tăng nguy cơ nhiễm độc aspirin và yêu cầu điều chỉnh liều lượng của nhiều loại thuốc khác như Alchysin 8400, Allerphast, Allerphast 60 mg, Alpha-Chymotrypsin 4200 IU, và Amikacin Bidiphar. Trước khi sử dụng Alchysin 8400 trên người cao tuổi, cần thông báo cho bác sĩ biết về tình trạng sức khỏe hiện tại. Người cao tuổi cần đặc biệt chú ý khi sử dụng các loại thuốc như Acenocoumarol, Acritel, Aclasta, và Amiparen 5 Otsuka. Đối với Acritel, người cao tuổi cần thận trọng khi sử dụng nếu chức năng thận vẫn bình thường. Khi sử dụng Aclasta, người cao tuổi không cần điều chỉnh liều lượng, nhưng cần chú ý khi sử dụng cùng với thuốc lợi tiểu. Người cao tuổi cần bổ sung nước đầy đủ và điều chỉnh liều lượng phù hợp khi sử dụng Acyclovir để đảm bảo an toàn và hiệu quả của thuốc. Người cao tuổi thường có chỉ số BMI bình thường nhưng lượng mỡ cao do ít vận động. Họ cũng có nguy cơ tăng nhạy cảm với tác dụng chống tiết acetylcholin của thuốc Coldko khi lớn hơn 60 tuổi. Đặc biệt, người cao tuổi (trên 75 tuổi) không thích hợp để bắt đầu điều trị bằng Agilosart 100. Người cao tuổi cần cân nhắc lợi ích, nguy cơ khi sử dụng Cefurobiotic và Cefurich do suy giảm chức năng thận. Họ cũng cần cân nhắc khi sử dụng Cefpodoxim dựa trên hiệu quả và an toàn. Người cao tuổi thường được hỗ trợ cải thiện hệ miễn dịch bị suy giảm bởi Alputine 80mg và Bentarcin. Cuối cùng, người cao tuổi là đối tượng dễ nhạy cảm với các tác dụng không mong muốn của thuốc như Baby Septol, Batigan, và Coperil Plus. Họ cũng cần thận trọng khi dùng thuốc AlphaDHG và Amiparen 5 Otsuka do khả năng gây nhiễm độc aspirin. Người cao tuổi cũng dễ bị hạ huyết áp và cần đặc biệt lưu ý khi bị ngộ độc thực phẩm. Tuy nhiên, người cao tuổi không cần điều chỉnh liều dùng của Bilastine, nhưng cần điều chỉnh liều dùng khi sử dụng Bixicam. Người cao tuổi cũng là đối tượng có nguy cơ xuất huyết tiêu hóa cao khi sử dụng thuốc NSAID và có thể bị ảnh hưởng bởi quá liều Bisacodyl. Ngoài ra, người cao tuổi có nguy cơ mắc bệnh teo não và cần bồi bổ sức khỏe bằng 3B Medi. Người cao tuổi cần thận trọng khi dùng thuốc do có khả năng gặp tác dụng phụ và họ thường được điều trị bằng các thuốc chống ngứa.\n\nNgười cao tuổi cũng là đối tượng sử dụng Biviantac và có nguy cơ gặp tác dụng phụ khi dùng thuốc này kéo dài. Họ cũng là đối tượng mắc suy giảm trí nhớ và được điều trị bằng Bổ Huyết Ích Não. Người cao tuổi cần giảm liều Cordarone và theo dõi chặt chẽ. Ngoài ra, người cao tuổi là đối tượng sử dụng Coversyl Plus và thuốc Cozaar.&lt;SEP&gt;Người cao tuổi là đối tượng cần cân nhắc khi dùng thuốc moxifloxacin.&lt;SEP&gt;Người cao tuổi là đối tượng sử dụng Rosuvastatin không cần điều chỉnh liều.&lt;SEP&gt;Người cao tuổi là đối tượng không cần điều chỉnh liều Rosuvastatin.\nThuốc Valproic Acid (Depakene): Thuốc valproic acid (Depakene) là thuốc có thể gây ra yếu tố nguy cơ nghi ngờ mắc bệnh tự kỷ nếu thai nhi tiếp xúc.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nNgười Caо Tuổi: Người cao tuổi cần thận trọng khi sử dụng Amiparen 5 Otsuka.\nCorticoid: Corticoid là một loại thuốc corticosteroid được sử dụng rộng rãi trong nhiều lĩnh vực y tế, từ điều trị các bệnh lý da liễu cho đến các tình trạng viêm nhiễm và dị ứng khác. Corticoid hoạt động bằng cách giảm hoặc ức chế các hóa chất và con đường viêm trong cơ thể, giúp kháng viêm và ngăn ngừa sự hình thành của các bóng nước mới, đặc biệt trong điều trị Pemphigus. Ngoài ra, corticoid còn được sử dụng trong việc điều chỉnh nồng độ canxi trong máu và là thành phần chính của thuốc Begenderm, có khả năng ức chế vỏ thượng thận ở trẻ sơ sinh. Khi sử dụng toàn thân, corticoid có thể bài tiết qua sữa mẹ với hàm lượng nhỏ và không gây ảnh hưởng đến trẻ sơ sinh.\n\nViệc sử dụng corticoid kéo dài hoặc quá liều có thể gây ra nhiều tác dụng phụ nghiêm trọng, bao gồm suy thượng thận cấp và hội chứng Cushing. Một số tác dụng phụ khác của corticoid bao gồm tăng nhu cầu sử dụng calci, gây ra mụn, và có thể làm giảm tác dụng của Beatisl do nó giữ muối và nước trong cơ thể. Corticoid cũng có thể gây ra các triệu chứng như teo da, khô da, và viêm da quanh miệng. Việc sử dụng corticoid tại chỗ có thể gây ra các phản ứng bất lợi khi ngừng sử dụng, đòi hỏi sự giám sát chặt chẽ của bác sĩ.\n\nCorticoid là một nhóm thuốc nhân tạo hoặc tổng hợp được sử dụng rộng rãi trong hầu hết các chuyên khoa y tế, giúp cải thiện nhiều vấn đề sức khỏe nhưng cũng tiềm ẩn nhiều rủi ro nếu không được sử dụng đúng cách. Corticoid có thể gây ra tương tác với nhiều loại thuốc khác và cần thận trọng khi kết hợp với thuốc kháng nấm. Loại thuốc này cũng được sử dụng để điều trị khối u nang bì trong hội chứng Gardner và có thể gây ảnh hưởng đến việc giảm sản xuất testosterone. Corticoid cũng được sử dụng để điều trị bệnh có thể gây ra triệu chứng loạn thần và thường được sử dụng ngắn ngày trong trường hợp nặng.\n\nNgoài ra, corticoid còn được biết đến như một loại thuốc kháng viêm mạnh thường được dùng đầu tay trong điều trị Sarcoidosis. Corticoid cũng là một thành phần trong thuốc Anginovag. Tuy nhiên, cần lưu ý rằng việc sử dụng corticoid có thể làm nặng thêm tình trạng suy tim.\n\nCuối cùng, corticoid là loại steroid tổng hợp có tác dụng như Betamethasone và thường được bệnh nhân điều trị cùng với Bepanthen.&lt;SEP&gt;Corticoid là thuốc có tương tác với Brexin.&lt;SEP&gt;Corticoid có tương tác với Brexin.&lt;SEP&gt;Corticoid là một loại thuốc có thể tương tác với Co-Diovan.\nTác Dụng Kháng Cholinergic: Tác dụng kháng cholinergic không được dung nạp tốt ở người cao tuổi.\nNgười Già: Người già là đối tượng cần được chăm sóc đặc biệt và thận trọng trong nhiều khía cạnh sức khỏe. Họ cần được theo dõi chặt chẽ khi sử dụng một số loại thuốc và dược liệu, như Acenocoumarol 4 mg và dược liệu cóc. Người già cũng cần thận trọng khi sử dụng corticoid do dễ gặp phải tác dụng phụ. Bên cạnh đó, họ không bị ảnh hưởng bởi thuốc Air-X vì nó không hấp thụ vào máu qua đường tiêu hóa. Người già là đối tượng dễ bị ảnh hưởng nặng nề bởi bệnh cảm cúm và cần được theo dõi chặt chẽ trong quá trình điều trị bệnh này. Ngoài ra, người già có nguy cơ cao bị hóc xương.&lt;SEP&gt;Người già cần thận trọng khi sử dụng Cotrimoxazol.&lt;SEP&gt;Người già là đối tượng dễ mắc các bệnh đường hô hấp trên.&lt;SEP&gt;Người già là đối tượng cần thận trọng khi sử dụng Amitriptyline.&lt;SEP&gt;Người già cần lưu ý trước khi dùng thuốc Bolutin.&lt;SEP&gt;Người già là đối tượng cần đặc biệt chú ý khi sử dụng Deferasirox (Exjade).&lt;SEP&gt;Người già là đối tượng có nguy cơ cao xuất hiện biến chứng từ thủy đậu.\nNgười Già (Từ 65 Tuổi Trở Lên): Người già từ 65 tuổi trở lên có thể gặp nhiều tác dụng phụ khi sử dụng deferasirox.\nBiviantac: Biviantac là một loại thuốc được sử dụng trong việc điều trị các vấn đề về tiêu hóa như trướng bụng, đầy hơi, và tiêu chảy cấp. Thành phần chính của Biviantac là bismuth subsalicylate, một chất có khả năng bao phủ niêm mạc dạ dày, giúp giảm các triệu chứng khó chịu như nóng rát, đau vùng thượng vị, và tăng độ acid. \n\nNgoài ra, Biviantac cũng chứa các thành phần khác nhằm hỗ trợ điều trị các rối loạn thường gặp trong các bệnh lý như loét dạ dày tá tràng và thực quản. Thuốc này không chỉ giúp kiểm soát tình trạng tăng tiết acid mà còn có tác dụng chống đầy hơi thông qua sự kết hợp với simethicon.\n\nTuy nhiên, cần lưu ý rằng Biviantac có thể làm cản trở quá trình hấp thu của một số loại thuốc khác, đặc biệt là các thuốc kháng sinh như tetracyclin, ciprofloxacin, ketoconazol, chloroquin, cefpodoxim, và các vitamin. Điều này đòi hỏi người dùng phải tuân thủ hướng dẫn sử dụng thuốc và thông báo cho bác sĩ về tất cả các loại thuốc đang sử dụng để tránh bất kỳ tương tác có hại nào.\nAxit Valproic (Depakene): Axit valproic (Depakene) là thuốc chống động kinh có liên quan đến nguy cơ gây dị tật bẩm sinh ở trẻ sơ sinh.\nAmitriptyline: Amitriptyline là một loại thuốc chống trầm cảm ba vòng (tricyclic antidepressant) được sử dụng để điều trị trầm cảm. Thuốc này không chỉ giúp giảm các triệu chứng của trầm cảm mà còn có khả năng giảm đau vùng chậu. Tuy nhiên, việc sử dụng Amitriptyline cần phải được thực hiện một cách thận trọng do tiềm ẩn nhiều tương tác thuốc khác nhau.\n\nAmitriptyline có thể tương tác với một số loại thuốc khác như Combigan và Depakin. Khi sử dụng Amitriptyline cùng với Depakin, cần phải điều chỉnh liều lượng để tránh các tác dụng phụ không mong muốn. Ngoài ra, Amitriptyline cũng có thể tương tác với disulfiram, dẫn đến tăng cường phản ứng giữa rượu và disulfiram khi cả hai được sử dụng cùng nhau.\n\nThuốc này cũng cần được sử dụng cẩn thận khi dùng cùng với các thuốc ức chế monoamin oxydase (MAOIs). Bệnh nhân rối loạn lưỡng cực cũng cần đặc biệt chú ý khi sử dụng Amitriptyline, đặc biệt là trong giai đoạn hồi phục sau nhồi máu cơ tim. \n\nMột điểm đáng lưu ý khác là Amitriptyline có thể gây ra tác dụng phụ ở thai nhi và có thể ảnh hưởng đến trẻ sơ sinh. Điều này nhấn mạnh tầm quan trọng của việc thông báo cho bác sĩ về tình trạng mang thai hoặc đang cho con bú trước khi bắt đầu sử dụng Amitriptyline.&lt;SEP&gt;Amitriptyline là một trong những thuốc chống trầm cảm ba vòng được liệt kê trong văn bản.&lt;SEP&gt;Amitriptyline là thuốc chống trầm cảm ba vòng có thể tương tác với moxifloxacin.\nAcid Valproic: Acid valproic là một loại thuốc được sử dụng trong điều trị các rối loạn thần kinh và tâm thần, bao gồm cả việc điều trị rối loạn lưỡng cực và rối loạn động kinh. Thuốc này hoạt động như một thuốc chống co giật hiệu quả và cũng có tác dụng an thần. Acid valproic có thể gây độc tính khi dùng chung với aspirin và vidipha, đồng thời có khả năng tương tác với erythromycin, một loại kháng sinh. Thuốc này cũng tương tác với các chất như cimetidin và amitriptyline, trong đó amitriptyline có thể làm giảm tác dụng của acid valproic. Ngoài ra, acid valproic không bị ảnh hưởng bởi gabapentin, cho thấy rằng nó có thể hoạt động độc lập hoặc ít bị ảnh hưởng bởi một số loại thuốc khác.&lt;SEP&gt;Acid valproic là hoạt chất chính trong Depakin.\nAceclofenac Stada: Aceclofenac Stada là thuốc kháng viêm không steroid (NSAID).\nAtocib: Atocib là thuốc được sử dụng để điều trị các bệnh lý về khớp và các triệu chứng đau.&lt;SEP&gt;Thuốc Atocib 90 mg được chỉ định dùng trong các trường hợp như điều trị triệu chứng các bệnh lý viêm xương khớp, viêm cột sống dính khớp, Gout, giảm đau và đau bụng kinh nguyên phát.&lt;SEP&gt;Atocib là thuốc chống chỉ định nếu creatinin &lt; 30 ml/phút. Liều dùng cụ thể tùy thuộc vào tình trạng cụ thể của mỗi bệnh nhân.&lt;SEP&gt;Atocib là thuốc cần thận trọng khi sử dụng đối với bệnh nhân có nguy cơ phát triển biến chứng đường tiêu hóa với NSAID, người có tiền sử bệnh đường tiêu hóa như viêm loét và xuất huyết tiêu hóa, người bị nhồi máu cơ tim, suy tim sung huyết, đột quỵ, tăng huyết áp, tăng lipid máu, đái tháo đường, hút thuốc, người suy chức năng thận, xơ gan, người cao tuổi, và người lái xe hoặc vận hành máy móc.&lt;SEP&gt;Atocib là thuốc chứa thành phần tương tự với Arcoxia.\nValproic Acid: Valproic acid là thuốc chống co giật được sử dụng ở những bệnh nhân có tình trạng múa giật.&lt;SEP&gt;Valproic acid là thuốc điều trị giật.&lt;SEP&gt;Valproic acid là hoạt chất chính trong Depakin.&lt;SEP&gt;Valproic acid là hoạt chất chính của Depakin.\nAlphaDHG: Thuốc AlphaDHG được sản xuất bởi Công ty Cổ phần Dược Hậu Giang, có thành phần chính là Chymotrypsin (hay Alpha-chymotrypsine) với 4200 đơn vị IU, được chỉ định dùng trong chống viêm, chống phù nề dạng men.&lt;SEP&gt;AlphaDHG là thuốc cần tuân thủ hướng dẫn sử dụng, đặc biệt chú ý đến việc báo cáo với bác sĩ hoặc dược sĩ về tình trạng sức khỏe trước khi dùng.&lt;SEP&gt;AlphaDHG là thuốc kháng viêm và điều trị phù nề dạng men, được sử dụng trong các trường hợp tổn thương mô mềm, chấn thương cấp, nhiễm trùng, phù nề mí mắt và chấn thương do vận động.&lt;SEP&gt;AlphaDHG là thuốc được sử dụng để điều trị các rối loạn tiêu hóa như đầy hơi, nặng bụng, tiêu chảy, táo bón hoặc buồn nôn. Thuốc có thể gây ra phản ứng dị ứng nhẹ như đỏ da khi sử dụng liều cao.&lt;SEP&gt;AlphaDHG là thuốc được sử dụng trong điều trị, với giá bán khoảng 80.000 VNĐ cho mỗi hộp.\nDanapha Trihex: Danapha Trihex là thuốc được sử dụng để hỗ trợ hội chứng Parkinson và làm giảm hội chứng ngoại tháp do thuốc.&lt;SEP&gt;Danapha Trihex không được khuyến cáo sử dụng cho phụ nữ có thai trừ khi lợi ích lớn hơn nguy cơ. Thuốc này cũng không nên được sử dụng khi đang cho con bú.&lt;SEP&gt;Danapha Trihex là thuốc chứa hoạt chất trihexyphenidyl.\nNSAID: NSAID, viết tắt của Non-Steroidal Anti-Inflammatory Drugs, là một nhóm thuốc có tác dụng giảm đau và chống viêm. NSAID thuộc nhóm pyrazole có thể tương tác với Acenocoumarol, gây ra các tác dụng phụ như khó chịu ở thượng vị, ợ nóng, đau dạ dày, và loét dạ dày. Nhóm thuốc này cũng có khả năng tương tác với nhiều loại thuốc khác, tạo ra các rủi ro về sức khỏe khi sử dụng đồng thời với các thuốc như Clopidogrel và Aspirin.\n\nKhi NSAID được sử dụng cùng với Clopidogrel, nguy cơ xuất huyết đường tiêu hóa có thể tăng lên. Đặc biệt, việc sử dụng NSAID cùng với Atocib cần được thực hiện một cách thận trọng, đặc biệt đối với bệnh nhân có nguy cơ phát triển biến chứng đường tiêu hóa. Thuốc này cũng có thể gây chảy máu ẩn đường tiêu hóa khi sử dụng kết hợp với clopidogrel và aspirin.\n\nNSAID thường được sử dụng để điều trị các vấn đề liên quan đến đau và viêm, nhưng chúng cũng có thể gây ra tác dụng phụ cho người lớn tuổi hoặc những người có nguy cơ cao. Ngoài ra, NSAID còn được thay thế bằng Nhũ hương trong một số trường hợp điều trị bệnh lý khớp.&lt;SEP&gt;Thuốc NSAID là các loại thuốc giảm đau và chống viêm.&lt;SEP&gt;NSAID là thuốc có thể kéo dài thời gian chảy máu và gây ra các tác dụng phụ như tăng nguy cơ huyết khối động mạch.&lt;SEP&gt;NSAID là một loại thuốc tương tác với Ciprobay.\nThoái Hóa Khớp Gối: Thoái hóa khớp gối là tình trạng bệnh lý xương khớp thường gặp, ảnh hưởng đến đầu gối. Đây là bệnh lý mạn tính gây ra sự biến đổi bề mặt sụn khớp, tạo nên các gai xương và biến dạng khớp. Thoái hóa khớp gối xảy ra là do mất cân bằng giữa hai quá trình tái tạo và phá hủy của sụn khớp và xương dưới sụn, dẫn đến tổn thương khớp gối do sự lão hóa tự nhiên hoặc nhiều nguyên nhân khác nhau. Bệnh này được đánh giá thông qua các phương pháp hình ảnh như CT scanner, MRI và nội soi khớp.\n\nThoái hóa khớp gối gây đau và hạn chế vận động, là một trong những bệnh lý gây tàn tật hàng đầu ở người cao tuổi. Điều trị cho bệnh này thường bao gồm cả phẫu thuật và việc sử dụng các phương pháp điều trị không phẫu thuật như bổ sung chất bôi trơn axit hyaluronic, sử dụng khổ qua rừng để cải thiện mức độ thoái hóa khớp, giảm đau, và cải thiện chỉ số khối cơ thể BMI và đường huyết lúc đói trong 3 tháng.\nBisacodyl: Bisacodyl là thuốc nhuần tràng, sạch ruột và trị táo bón.&lt;SEP&gt;Bisacodyl là thuốc làm tăng nhu động ruột, tương tác với Artreil.&lt;SEP&gt;Bisacodyl là thuốc được chỉ định điều trị táo bón và chuẩn bị cho chụp X-quang đại tràng.&lt;SEP&gt;Thuốc Bisacodyl được sử dụng đường uống hoặc đường trực tràng dưới dạng viên đạn hay thụt rửa, giúp giảm kích ứng ở dạ dày và buồn nôn.&lt;SEP&gt;Bisacodyl là thuốc nhuận tràng kích thích, thường gây tác dụng phụ trên tiêu hóa như đau bụng, nôn, buồn nôn, tiêu chảy.&lt;SEP&gt;Bisacodyl là thuốc điều trị táo bón, giúp thải sạch ruột cho phẫu thuật hoặc chuẩn bị X-quang đại tràng.&lt;SEP&gt;Bisacodyl là thuốc điều trị táo bón, có thể gây kích ứng dạ dày và tá tràng khi phối hợp với các thuốc kháng acid.\nNgười Cao Tuổi - Tiêu Chảy: Người cao tuổi có nguy cơ mắc bệnh tiêu chảy.\nNgười Cao Tuổi - Tác Dụng Phụ: Người cao tuổi có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nNgười Cao Tuổi - Thận: Người cao tuổi có vấn đề với thận như suy giảm chức năng thận hoặc chạy thận nhân tạo.\nCorticoid - Người Già: Người già là đối tượng dễ bị tác dụng phụ khi sử dụng corticoid.\nAspirin - Người Cao Tuổi: Người cao tuổi có nguy cơ nhiễm độc Aspirin khi sử dụng thuốc.\nBiviantac - Người Cao Tuổi: Người cao tuổi là đối tượng sử dụng Biviantac.&lt;SEP&gt;Biviantac có thể gây tác dụng phụ ở người cao tuổi.\nAcid Valproic - Aspirin: Aspirin tăng nồng độ của Acid Valproic khi dùng chung, gây độc tính.&lt;SEP&gt;Acid Valproic khi dùng chung với Aspirin có thể gây độc tính.&lt;SEP&gt;Acid valproic có thể tương tác với Aspirin, làm tăng nồng độ Aspirin.&lt;SEP&gt;Aspirin có thể làm tăng nồng độ thuốc này trong huyết thanh và tăng độc tính khi dùng cùng Acid valproic.\nAmitriptyline - Người Già: Amitriptyline cần thận trọng khi sử dụng ở người già.\nCelecoxib - Người Cao Tuổi: Celecoxib không cần điều chỉnh liều cho người cao tuổi, ngoại trừ những trường hợp có trọng lượng cơ thể &lt;50 kg, bắt đầu điều trị với liều được khuyến cáo thấp nhất.\nAceclofenac Stada - Người Cao Tuổi: Aceclofenac Stada có thể gây tác dụng phụ trên người cao tuổi.\nMoxifloxacin - Người Cao Tuổi: Moxifloxacin cần được dùng cẩn trọng ở người cao tuổi.\nAtocib - Người Cao Tuổi: Người cao tuổi cần thận trọng khi sử dụng Atocib.\nAcyclovir - Người Cao Tuổi: Ở người cao tuổi, cần lưu ý bổ sung nước và điều chỉnh liều Acyclovir.&lt;SEP&gt;Người cao tuổi cần bổ sung nước đầy đủ khi sử dụng Acyclovir.&lt;SEP&gt;Người cao tuổi cần bổ sung nước đầy đủ khi sử dụng Acyclovir.\nAlphaDHG - Người Cao Tuổi: Người cao tuổi cần đặc biệt chú ý khi dùng thuốc AlphaDHG.\nAceclofenac - Người Cao Tuổi: Khả năng phân bố, chuyển hóa, hấp thu và thải trừ của Aceclofenac không thay đổi ở bệnh nhân cao tuổi, do đó không cần phải thay đổi liều hoặc tần suất sử dụng.\nDanapha Trihex - Người Cao Tuổi: Người cao tuổi dễ nhạy cảm với các dụng không mong muốn của thuốc.\nCefpodoxim - Người Cao Tuổi: Người cao tuổi dùng Cefpodoxim với liều dùng tương tự người trẻ tuổi.\nNSAID - Thoái Hóa Khớp Gối: NSAID là loại thuốc có thể gây tác dụng phụ cho người lớn tuổi hoặc những người có nguy cơ cao bị tác dụng phụ do NSAID gây ra.\nAcid Valproic - Amitriptylin: Amitriptylin giảm tác dụng của acid valproic.\nBisacodyl - Người Cao Tuổi: Bisacodyl có thể gây ảnh hưởng đến người cao tuổi khi sử dụng.\nClindamycin - Người Bệnh Ca O Tuổi: Thận trọng đối với người bệnh cao tuổi khi dùng Clindamycin.\nBixicam - Người Cao Tuổi: Người cao tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam.\nAcid Valproic - Cimetidin: Cimetidin có tương tác với Acid valproic.&lt;SEP&gt;Acid valproic tương tác với Cimetidin.\nNgười Cao Tuổi - Teo Não: Người cao tuổi có nguy cơ cao mắc bệnh teo não.\nBaby Septol - Người Cao Tuổi: Người cao tuổi cần thận trọng khi sử dụng Baby Septol do dễ bị thiếu acid folic.\nNgười Cao Tuổi - Rosuvastatin: Rosuvastatin không cần điều chỉnh liều ở người cao tuổi.&lt;SEP&gt;Người cao tuổi không cần điều chỉnh liều Rosuvastatin.\nAspirin Vidipha - Người Cao Tuổi: Aspirin Vidipha có thể gây nhiễm độc ở người cao tuổi do chức năng thận suy giảm.\nAmikacin Bidiphar - Người Cao Tuổi: Người cao tuổi cần thận trọng khi sử dụng Amikacin Bidiphar.\nCefurich - Người Cao Tuổi: Người cao tuổi cần cân nhắc an toàn và hiệu quả khi sử dụng Cefurich.\nCảm Cúm - Người Già: Người già dễ bị ảnh hưởng nặng nề bởi bệnh cảm cúm.\nCalcigenol - Người Cao Tuổi: Calcigenol được sử dụng để ngăn ngừa gãy xương do loãng xương ở người cao tuổi.\nCefurobiotic - Người Cao Tuổi: Người cao tuổi cần cân nhắc lợi ích, nguy cơ khi sử dụng Cefurobiotic.\nCoversyl Plus - Người Cao Tuổi: Người cao tuổi là đối tượng sử dụng Coversyl Plus.\nAcritel - Người Cao Tuổi: Acritel không cần chỉnh liều cho người cao tuổi có chức năng thận bình thường, nhưng cần thận trọng khi sử dụng.\nColdko - Người Cao Tuổi: Coldko cần thận trọng khi sử dụng ở người cao tuổi.\nNgười Cao Tuổi - Trihexyphenidyl: Trihexyphenidyl cần thận trọng khi sử dụng cho người cao tuổi.\nNgười Cao Tuổi - Tụt Huyết Áp: Người cao tuổi dễ mắc phải tình trạng tụt huyết áp.\nMethylprednisolone (Depo-Medrol) - Người Cao Tuổi: Người cao tuổi cần sử dụng methylprednisolone thận trọng với liều thấp nhất và trong thời gian ngắn nhất có thể.\nAmlodipine - Người Cao Tuổi: Người cao tuổi cần có bác sĩ giám sát cẩn thận khi sử dụng amlodipine.\nCarbocistein - Người Cao Tuổi: Người cao tuổi cần thận trọng khi dùng Carbocistein do có nguy cơ phản ứng bất thường.\nAcid Valproic - Amilavil: Amilavil giảm tác dụng của acid valproic.&lt;SEP&gt;Amilavil làm giảm tác dụng của acid valproic.\nBatigan - Người Cao Tuổi: Batigan cần được sử dụng thận trọng trên người cao tuổi.&lt;SEP&gt;Batigan cần thận trọng sử dụng trên người cao tuổi.\nNgười Cao Tuổi - Ngộ Độc Thực Phẩm: Người cao tuổi là đối tượng có nguy cơ cao khi bị ngộ độc thực phẩm.\nAclasta - Người Cao Tuổi: Aclasta không cần điều chỉnh liều cho người cao tuổi.&lt;SEP&gt;Người cao tuổi và những bệnh nhân đang dùng thuốc lợi tiểu cần chú ý khi dùng Aclasta.&lt;SEP&gt;Aclasta cần được cân nhắc khi bệnh nhân là người cao tuổi.\nAcenocoumarol - Người Cao Tuổi: Người cao tuổi có thể cần liều Acenocoumarol thấp hơn.&lt;SEP&gt;Acenocoumarol được sử dụng để điều trị cho người cao tuổi.\nCordarone - Người Cao Tuổi: Người cao tuổi cần giảm liều Cordarone và theo dõi chặt chẽ.\nNgười Già - Thủy Đậu: Người già có nguy cơ cao xuất hiện biến chứng từ thủy đậu.\nAcid Valproic - Erythromycin: Erythromycin làm tăng nồng độ acid valproic trong huyết tương.&lt;SEP&gt;Erythromycin làm tăng nồng độ Acid Valproic trong huyết tương.\nBệnh Cúm - Người Già: Người già có nguy cơ cao mắc phải các biến chứng do bệnh cúm gây ra.\nCotrimoxazol - Người Già: Người già cần thận trọng khi sử dụng Cotrimoxazol.\nAlchysin 8400 - Người Cao Tuổi: Thuốc Alchysin 8400 cần được báo với bác sĩ trước khi sử dụng trên người cao tuổi.\nAxit Glutamic - Người Cao Tuổi: Axit glutamic không nên sử dụng cho người cao tuổi.\nAlputine - Người Cao Tuổi: Alputine được sử dụng để hỗ trợ tăng cường hệ miễn dịch ở bệnh nhân cao tuổi.\nBMI - Người Cao Tuổi: Người cao tuổi có thể có chỉ số BMI bình thường nhưng lượng mỡ cao do ít vận động.\nAndol S Imexpharm - Người Cao Tuổi: Người cao tuổi cần thận trọng khi dùng Andol S Imexpharm.\nNgười Cao Tuổi - Thuốc Cedipect F: Người cao tuổi cần thận trọng khi dùng thuốc Cedipect F.\nNgười Cao Tuổi - Rối Loạn Khứu Giác: Rối loạn khứu giác là bệnh lý thường gặp ở người cao tuổi.\nRối Loạn Phổ Tự Kỷ - Thuốc Valproic Acid (Depakene): Thuốc valproic acid (Depakene) là yếu tố nguy cơ nghi ngờ mắc bệnh tự kỷ nếu thai nhi tiếp xúc.\nAlzyltex Mebiphar - Người Cao Tuổi: Liều dùng Alzyltex Mebiphar cần được điều chỉnh cho người cao tuổi.\nAtelec - Người Cao Tuổi: Atelec phù hợp với người cao tuổi.\nAxit Valproic (Depakene) - Động Kinh: Axit valproic (Depakene) là thuốc chống động kinh có liên quan đến nguy cơ gây dị tật bẩm sinh ở trẻ sơ sinh.\nNgười Cao Tuổi - Thừa Cân: Người cao tuổi thừa cân có nguy cơ mắc bệnh thất vị hoành.\nIndapamid - Người Cao Tuổi: Indapamid được chỉ định thận trọng khi dùng cho người cao tuổi.\nCozaar - Người Cao Tuổi: Người cao tuổi không cần điều chỉnh liều dùng khi sử dụng Cozaar.\nAlpha-Chymotrypsin 4200 IU - Người Cao Tuổi: Lưu ý khi dùng thuốc Alpha-Chymotrypsin 4200 IU cho người cao tuổi.\nAllerphast 60 mg - Người Cao Tuổi: Không cần điều chỉnh liều cho người cao tuổi.\nAcid Valproic - Depakin: Acid valproic là hoạt chất chính trong Depakin.\nAgimfast 60 - Người Cao Tuổi: Thận trọng khi dùng thuốc cho người cao tuổi (&gt; 65 tuổi) thường có suy giảm sinh lý chức năng thận.\nBentarcin - Người Cao Tuổi: Bentarcin được chỉ định để hỗ trợ tăng cường miễn dịch ở người cao tuổi.\nHydroxyzin - Người Cao Tuổi: Hydroxyzin không nên dùng như là một thuốc làm dịu ở người cao tuổi.\n3B Medi - Người Cao Tuổi: 3B Medi được sử dụng để bồi bổ sức khỏe cho người cao tuổi.\nAcid Valproic - Aspirin MKP 81: Khi dùng chung với Acid Valproic, Aspirin MKP 81 tăng nồng độ Acid Valproic trong huyết thanh.\nNgười Cao Tuổi - m lượng: Không cần thận trọng đặc biệt ở người cao tuổi khi uống m lượng.\nAgilosart 100 - Người Cao Tuổi: Agilosart 100 không thích hợp để bắt đầu điều trị cho bệnh nhân lớn tuổi (hơn 75 tuổi).\nLỗ Rò Động Tĩnh Mạch - Người Cao Tuổi: Người cao tuổi có thể làm tăng nguy cơ lỗ rò động tĩnh mạch.\nCefurich 500 - Người Cao Tuổi: Khi sử dụng Cefurich 500 ở người cao tuổi cần cân nhắc lợi ích và nguy cơ.\nDepakin - Valproic Acid: Depakin chứa hoạt chất valproic acid.\nNgười Cao Tuổi - Thymomodulin: Thymomodulin được chỉ định hỗ trợ cải thiện hệ miễn dịch bị suy giảm ở người cao tuổi.\nAlputine 80mg - Người Cao Tuổi: Alputine 80mg được chỉ định hỗ trợ cải thiện hệ miễn dịch bị suy giảm ở người cao tuổi.\nAmiparen 5 Otsuka - Người Caо Tuổi: Người cao tuổi cần thận trọng khi sử dụng Amiparen 5 Otsuka.\nAcid Valproic - Aspirin STELLA: Khi dùng Aspirin STELLA cùng Acid Valproic, sẽ tăng nồng độ Acid Valproic trong huyết thanh.\nBệnh Lý Hô Hấp Mãn Tính - Người Cao Tuổi: Người cao tuổi mắc bệnh lý hô hấp mãn tính có nguy cơ mắc bệnh thất vị hoành.\nCông Việc Nặng Nhọc - Người Cao Tuổi: Người cao tuổi làm công việc nặng nhọc có nguy cơ mắc bệnh thất vị hoành.\nNguy Cơ Xuất Huyết Tiêu Hóa - Người Cao Tuổi: Người cao tuổi có nguy cơ xuất huyết tiêu hóa cao khi sử dụng thuốc NSAID.\nNgười Cao Tuổi - Táo Bón Lâu Ngày: Người cao tuổi bị táo bón lâu ngày có nguy cơ mắc bệnh thất vị hoành.\nGiảm Khứu Sinh Lý - Người Cao Tuổi: Giảm khứu sinh lý do tuổi.\nBolutin - Người Già: Người già cần lưu ý trước khi dùng thuốc Bolutin.\nAcid Valproic - Rối Loạn Lưỡng Cực: Acid valproic được sử dụng trong điều trị rối loạn lưỡng cực.\nDeferasirox (Exjade) - Người Già: Người già cần đặc biệt chú ý khi sử dụng Deferasirox (Exjade).\nAcid Valproic - Cimetidine MKP: Cimetidine MKP làm tăng nồng độ trong huyết tương của Acid valproic.\nNgười Già - Nhiễm Trùng Đường Hô Hấp Trên: Người già có nguy cơ cao mắc các bệnh đường hô hấp trên.\nAcenocoumarol 4 mg - Người Già: Người già là đối tượng cần thận trọng khi sử dụng Acenocoumarol 4 mg.\nAcid Valproic - Thuốc An Thần: Acid valproic (Depakene) là thuốc an thần được sử dụng trong điều trị rối loạn lưỡng cực.\nDầu Giun - Người Già: Dầu giun không nên sử dụng cho người già.\nHóc Xương - Người Già: Người già có nguy cơ cao bị hóc xương.\nAcid Valproic - Độc Tính: Acid Valproic khi dùng chung với Aspirin có thể gây độc tính.\nAtarax (Hydroxyzine Hydrochloride) - Tác Dụng Kháng Cholinergic: Tác dụng kháng cholinergic không được dung nạp tốt ở người cao tuổi.\nDeferasirox - Người Già (Từ 65 Tuổi Trở Lên): Người già từ 65 tuổi trở lên có thể gặp nhiều tác dụng phụ khi sử dụng deferasirox.\nAcid Valproic - Gabapentin: Gabapentin không làm thay đổi dược động học của acid valproic.\nCóc - Người Già: Người già, gầy yếu, suy nhược cần cẩn trọng.&lt;SEP&gt;Người già cần cẩn trọng khi sử dụng dược liệu cóc.\nAir-X Hương Cam/Hương Bạc Hà - Người Già: Air-X không hấp thu vào máu qua đường tiêu hóa nên không gây ảnh hưởng đối với người già.\nBilastine - Người Caо Tuổi: Bilastine không cần điều chỉnh liều dùng trên người cao tuổi.\nAcid Valproic - Depakote: Depakote chứa hoạt chất acid valproic.\nAcid Valproic - Dalekine: Dalekine chứa hoạt chất acid valproic.\nAcid Valproic - Milepsy: Milepsy chứa hoạt chất acid valproic.\nGiật - Valproic Acid: Valproic acid được sử dụng để điều trị giật.\nMúa Giật - Valproic Acid: Valproic acid là thuốc chống co giật được sử dụng ở những bệnh nhân có tình trạng múa giật.\nValproic Acid - Động Kinh Cơn Lớn: Valproic acid được sử dụng trong điều trị động kinh cơn lớn.']</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra một số tác dụng phụ ở người cao tuổi, bao gồm:
+- **Buồn ngủ**: Người cao tuổi có thể gặp tình trạng buồn ngủ khi sử dụng Depakin.
+- **Tác dụng phụ về tiêu hóa**: Có thể gặp các triệu chứng như đau bụng, táo bón, buồn nôn, chóng mặt, và khó tiêu.
+- **Rụng tóc, mờ mắt, suy nhược, khó thở**: Đây là các tác dụng phụ có thể ảnh hưởng đến sức khỏe tổng thể của người cao tuổi.
+- **Rối loạn trí nhớ, nhức đầu, hồi hộp, rung giật nhãn cầu, phù ngoại biên**: Các triệu chứng này có thể làm giảm chất lượng cuộc sống của người cao tuổi.
+- **Viêm phế quản, viêm họng, viêm mũi**: Những tác dụng phụ này có thể làm tăng nguy cơ mắc các bệnh đường hô hấp ở người cao tuổi.
+- **Thiếu máu, giảm tiểu cầu**: Đây là các tác dụng phụ nghiêm trọng có thể gây ra các vấn đề về máu.
+- **Mất thính lực**: Thuốc có thể ảnh hưởng đến khả năng nghe của người cao tuổi.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ buồn ngủ ở người cao tuổi.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8451111739501894</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2425277934875474</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>['Acyclovir Stada 200 mg: Thuốc Acyclovir Stada 200 mg được sản xuất bởi Công ty TNHH Liên Doanh Stellapharm, dùng để điều trị và dự phòng nhiễm virus Herpes simplex, điều trị nhiễm virus Varicella Zoster.&lt;SEP&gt;Acyclovir Stada 200 mg là thuốc được chỉ định dùng trong các trường hợp nhiễm virus Herpes simplex và Varicella zoster.&lt;SEP&gt;Acyclovir Stada 200 mg được bán với giá tham khảo từ 40.000 – 50.000 VNĐ cho hộp 5 vỉ x 5 viên nén.&lt;SEP&gt;Thuốc Acyclovir Stada 200 mg được sử dụng để điều trị các bệnh như herpes simplex và herpes zoster.&lt;SEP&gt;Acyclovir Stada 200 mg là thuốc điều trị bệnh herpes simplex và zona, cần thận trọng khi sử dụng ở phụ nữ mang thai và cho con bú.&lt;SEP&gt;Acyclovir Stada 200 mg được sử dụng để điều trị các bệnh nhiễm trùng do virus.\nAcyclovir: Acyclovir là một hoạt chất chính được sử dụng trong nhiều loại thuốc điều trị các bệnh do virus herpes và varicella zoster gây ra. Nó là thành phần chính trong các loại thuốc như Acyclovir Boston 200, Acyclovir Boston 800, Acyclovir Stada 200 mg, Acyclovir Stella 400 mg, và Acyclovir Stella 800 mg. Acyclovir nổi tiếng với khả năng kháng virus mạnh mẽ nhất đối với virus Herpes simplex type 1, và tác dụng kém hơn đối với virus Herpes simplex type 2 và virus Varicella zoster. \n\nThuốc này được sử dụng để điều trị thủy đậu, bệnh zona, và các bệnh nhiễm herpes simplex và varicella zoster. Ngoài ra, nó cũng được sử dụng để dự phòng tái phát các bệnh này. Acyclovir có thể được sử dụng độc lập hoặc cùng với bữa ăn. Tuy nhiên, việc sử dụng thuốc có thể gây ra các tác dụng phụ như chóng mặt, vì vậy cần đánh giá kỹ lưỡng về phản ứng của bệnh nhân trước khi lái xe hoặc vận hành máy móc. \n\nAcyclovir còn là hoạt chất chính trong Acyclovir Stella Cream, được sử dụng để điều trị nhiễm trùng do virus, đặc biệt là nhiễm herpes simplex. Thuốc này được bài tiết qua sữa mẹ và đào thải qua thận. Do đó, cần chú ý đến việc sử dụng thuốc trong trường hợp bệnh nhân đang cho con bú. Thuốc này được ức chế đào thải bởi Probenecid và tăng hiệu lực khi dùng cùng Amphotericin B hoặc ketoconazole. Acyclovir là thuốc kháng virus có cấu trúc tương tự nucleosid, có tác dụng chọn lọc trên tế bào nhiễm virus Herpes, và có tác dụng ức chế tổng hợp ADN của virus Herpes.\n\nAcyclovir cũng được biết đến với khả năng bị kéo dài thời gian bài tiết bởi một số thuốc khác và có thể bị ảnh hưởng bởi Aspartam. Nó còn được sử dụng để điều trị triệu chứng của vảy phấn hồng dưới tên thương mại Zovirax. Acyclovir là thuốc điều trị và phòng ngừa nhiễm Herpes simplex, thủy đậu và bệnh zona. Nó có thể gây tác dụng phụ toàn thân nếu hấp thu quá mức qua da vào tuần hoàn.\n\nKem acyclovir được sử dụng trong điều trị và dự phòng nhiễm virus Herpes Simplex. Acyclovir là thuốc kháng vi-rút được sử dụng để điều trị giai đoạn bùng phát của Zona, giúp giảm mức độ nghiêm trọng và thời gian của cơn đau cấp tính. Nó cũng được sử dụng như một phương pháp hỗ trợ trong điều trị u nhú thanh quản.&lt;SEP&gt;Acyclovir là thuốc được Cơ quan Quản lý Thực phẩm và Dược phẩm Hoa Kỳ phân nhóm B, có thể sử dụng trong thai kỳ. Thuốc được khuyến nghị cho phụ nữ mang thai bị thủy đậu với các biến chứng nghiêm trọng.&lt;SEP&gt;Acyclovir là thuốc được khuyến nghị sử dụng để rút ngắn thời gian nhiễm trùng và giảm nguy cơ biến chứng thủy đậu.\nAciclovir 200mg: Acyclovir 200 mg Stada, đóng gói trong hộp 5 vỉ x 5 viên nén, giá tham khảo 32.000VNĐ/hộp.\nSự Nhân Lên Của Virus: Sự nhân lên của virus là quá trình được ức chế bởi Acyclovir.\nHerpes Zoster: Herpes zoster là bệnh được điều trị bằng Acyclovir Stada 200 mg.&lt;SEP&gt;Herpes zoster là bệnh nhiễm virus Herpes zoster.&lt;SEP&gt;Herpes zoster là bệnh nhiễm trùng do virus gây ra, được điều trị bằng Aciclovir 800 mg.&lt;SEP&gt;Herpes zoster là bệnh cần tránh khi dùng corticosteroid đường toàn thân.\nTế Bào Nhiễm Virus Herpes: Tế bào nhiễm virus herpes là mục tiêu điều trị của acyclovir.\nHerpes Simplex: Herpes simplex là bệnh nhiễm trùng do virus Herpes simplex gây ra. Bệnh này có thể ảnh hưởng đến da và niêm mạc, bao gồm cả bệnh Herpes sinh dục khởi phát và tái phát, thủy đậu, và bệnh zona. Điều trị cho bệnh herpes simplex thường được thực hiện bằng Acyclovir, một loại thuốc kháng virus phổ biến. Acyclovir có sẵn dưới nhiều dạng khác nhau như viên nén Acyclovir Boston 800, viên nén Acyclovir Stada 200 mg, viên nén Acyclovir Stella 400 mg, và kem Acyclovir Stella Cream. Thuốc này không chỉ giúp điều trị các triệu chứng của bệnh mà còn được sử dụng để phòng ngừa sự phát triển của bệnh herpes simplex. Ngoài ra, Acyclovir 5% Agimexpharm cũng được chỉ định để điều trị các trường hợp bệnh herpes simplex.\n\nBệnh herpes simplex được chống chỉ định sử dụng B – Sol. Bệnh này cũng được điều trị bằng *C. nutans* và được ức chế bởi kim vàng và Kim Ngân Hoa. Herpes simplex là vi rút gây bệnh da liễu và cũng được coi là bệnh nhiễm virus da.\nAciclovir: Aciclovir là thuốc chứa thành phần tương tự như Acyclovir Stella 400 mg.&lt;SEP&gt;Aciclovir là thuốc có tác dụng chống virus Herpes simplex và Varicella zoster.&lt;SEP&gt;Aciclovir là thuốc được chỉ định trong điều trị nhiễm virus Herpes simplex.&lt;SEP&gt;Aciclovir là thuốc chống virus được chỉ định trong điều trị và dự phòng nhiễm virus Herpes ở niêm da, não, mắt; nhiễm Varicella Zoster, Zona mắt, thủy đậu.&lt;SEP&gt;Aciclovir là thuốc kháng virus, có thể gây kết tủa trong thận nếu tiêm truyền tĩnh mạch với liều cao và không đủ nước.&lt;SEP&gt;Aciclovir là thuốc điều trị nhiễm virus Herpes ở niêm da, não, mắt; nhiễm Varicella Zoster, Zona mắt, thủy đậu.&lt;SEP&gt;Aciclovir là thuốc điều trị các bệnh do virus Herpes Simplex, có thể gây ra các tác dụng phụ như phát ban, ngứa, mề đay, sốt, đau, tăng men gan, viêm gan, vàng da, đau cơ, phù mạch, rụng tóc.\nAciclovir 800 mg: Thuốc Aciclovir 800 mg được sử dụng trong điều trị nhiễm Herpes simplex môi và sinh dục khởi phát và tái phát, cũng như nhiễm Herpes zoster.\nVirus Herpes: Virus Herpes là nguyên nhân gây ra các bệnh như nhiễm Herpes ở niêm da, não, mắt.\nAgiclovir 200: Agiclovir 200 là viên nén chứa aciclovir, được sử dụng trong điều trị và dự phòng nhiễm virus.\nTế Bào Nhiễm Virus: Tế bào nhiễm virus Herpes là đối tượng tác dụng của Acyclovir.&lt;SEP&gt;Tế bào nhiễm virus là tế bào bị tấn công bởi virut, được tiêu diệt bởi tế bào miễn dịch.\nViêm Nhiễm Do Virus Herpes Simplex: Viêm nhiễm do virus Herpes simplex là bệnh mà acyclovir được sử dụng để điều trị.\nTriệu Chứng: Triệu chứng là các dấu hiệu hoặc biểu hiện cụ thể của bệnh lý hoặc tình trạng y tế mà bệnh nhân có thể cảm nhận được. Chúng bao gồm cả dấu hiệu bệnh lý mà bác sĩ có thể quan sát được và các biểu hiện mà bệnh nhân cảm nhận được. Triệu chứng có thể xuất hiện do nhiều nguyên nhân khác nhau, từ các bệnh lý cụ thể như Hội chứng Klinefelter, Bệnh Brucellosis, Bệnh cơ bẩm sinh, Bệnh tim phì đại, Bệnh Crohn, Bệnh gan nhiễm mỡ không do rượu, Bệnh Huntington, Bệnh viêm phổi kẽ, Bệnh phổi tắc nghẽn mạn tính, và Bệnh rối loạn chuyển hóa tinh bột, đến các tác dụng phụ của thuốc như ngộ độc hoặc quá liều Acetazolamid và Atorvasan. \n\nHội chứng Klinefelter có thể biểu hiện qua chiều cao vượt trội, giảm khả năng phối hợp, thiếu testosterone, tinh hoàn nhỏ, và vô sinh. Bệnh Brucellosis bao gồm sốt cao đột ngột, đau cơ, yếu cơ bất thường, và mệt mỏi. Bệnh cơ bẩm sinh bao gồm trướng bụng, đầy hơi và tiêu chảy cấp. Bệnh tim phì đại có thể bao gồm khó thở, ngất xỉu, đánh trống ngực, chóng mặt, mệt mỏi do gắng sức, và phù chân. Bệnh Crohn bao gồm đau bụng, tiêu chảy, và mất cân nặng. Bệnh gan nhiễm mỡ không do rượu thường không rõ ràng. Bệnh Huntington bao gồm rối loạn vận động và tâm thần. Bệnh viêm phổi kẽ bao gồm khó thở, đau ngực và ho. Bệnh phổi tắc nghẽn mạn tính bao gồm tắc nghẽn luồng khí từ phổi. Bệnh rối loạn chuyển hóa tinh bột có thể gây tử vong ở giai đoạn sớm sau sinh (&lt;1 tuổi).\n\nTriệu chứng của Bệnh tế bào mast hệ thống bao gồm đau da, đỏ mắt, ngứa mũi, khó thở, huyết áp thấp, quặn đau dạ dày, buồn nôn và đau đầu. Bệnh Lupus ban đỏ hệ thống bao gồm tổn thương da, khớp, thận và não. Bệnh Thận IgA có thể xuất hiện nếu không được chẩn đoán và điều trị kịp thời. Amyloidosis có thể giống với các triệu chứng của các bệnh khác.\n\nTriệu chứng không chỉ giới hạn ở các bệnh cụ thể mà còn bao gồm các dấu hiệu bệnh lý mà bác sĩ dựa vào để kê toa thuốc thích hợp. Triệu chứng có thể xuất hiện ở nhiều bệnh khác nhau, từ bệnh tim thiếu máu cục bộ đến bệnh trĩ ngoại. Triệu chứng có thể không rõ ràng, bệnh thường không có triệu chứng, chỉ được phát hiện qua xét nghiệm hoặc chẩn đoán hình ảnh. Triệu chứng giúp bác sĩ trong việc chẩn đoán và điều trị bệnh. Triệu chứng cũng có thể xuất hiện ở trẻ bị còn ống động mạch. Triệu chứng như trướng bụng, đầy hơi và tiêu chảy cần được thăm khám để xác định nguyên nhân và phương pháp điều trị.\n\nTriệu chứng của bệnh tay chân miệng bao gồm sốt, đau họng và vết loét hoặc bóng nước trên nền hồng ban ở niêm mạc miệng, bàn tay, bàn chân và đầu gối, cùi chỏ, mông. Phát ban và đau họng cũng là triệu chứng phổ biến của bệnh này.\n\nTriệu chứng cũng bao gồm dấu hiệu của các bệnh khác như viêm phế quản cấp, bệnh nổi mề đay, bệnh u nhú thanh quản, và bệnh phì đại tuyến tiền liệt. Các triệu chứng điển hình của viêm phế quản cấp bao gồm ho, tức ngực, khó thở, thở khò khè, đau nhức mình mẩy, sốt nhẹ, chảy nước mũi, và nghẹt mũi.\n\nNgoài ra, triệu chứng rối loạn giấc ngủ có thể trở nên rõ rệt hơn khi trải qua chuyến bay dài và bay về hướng đông. Triệu chứng rối loạn điện giải thường không đặc hiệu và khó nhận biết. Triệu chứng rối loạn lên đồng bao gồm sự thay đổi tạm thời về danh tính và ý thức về môi trường xung quanh, thay đổi hành vi hoặc hành động khác, mất nhận thức về môi trường xung quanh, đánh mất bản sắc cá nhân, khó phân biệt thực tế với tưởng tượng, thay đổi giọng nói, sự chú ý bị gián đoạn, khó tập trung, mất tri giác về thời gian, mất trí nhớ và niềm tin rằng cơ thể đã thay đổi về ngoại hình. Triệu chứng rối loạn nhận thức thần kinh nhẹ bao gồm các dấu hiệu cụ thể của rối loạn nhận thức. Tuy nhiên, rối loạn nhận thức thần kinh chưa có thuốc điều trị hiệu quả. Triệu chứng rối loạn phổ tự kỷ bao gồm khó chịu với sự thay đổi nhỏ, vấn đề về cảm giác và hành vi bất thường.\n\nTriệu chứng của run vô căn bao gồm khó khăn trong các hoạt động hàng ngày như giữ ly nước, ăn uống, trang điểm, nói chuyện, viết chữ. Triệu chứng của sa sút trí tuệ bao gồm mất trí nhớ, gặp vấn đề trong ngôn ngữ, khả năng tập trung, giải quyết vấn đề.\n\nTriệu chứng sẹo lồi bao gồm tăng sinh da quá mức, có thể gây khó chịu và ảnh hưởng thẩm mỹ. Triệu chứng của bệnh sỏi mật bao gồm đau quặn mật, vàng da, ngứa, tiểu vàng sậm, khó tiêu, ợ hơi, buồn nôn, nôn.\n\nTriệu chứng của sốt xuất huyết bao gồm sốt cao, nôn ói, và các triệu chứng khác.\n\nTriệu chứng suy gan bao gồm các triệu chứng nặng đe dọa tính mạng. Triệu chứng suy gan là những biểu hiện nghiêm trọng của tình trạng gan suy yếu. Triệu chứng gan xơ hóa bao gồm mệt mỏi, ăn uống kém, cổ trướng, vàng da, nôn ra máu.\n\nTriệu chứng cũng bao gồm việc tim không còn khả năng bơm hiệu quả để duy trì dòng máu cung cấp cho các cơ quan, đặc biệt trong suy tim.\n\nTriệu chứng của suy tuyến yên bao gồm các biểu hiện bất thường không đặc hiệu. Triệu chứng là dấu hiệu của bệnh suy tuyến yên.\n\nTriệu chứng teo não bao gồm sự phối hợp kém các động tác, chuyển động mắt, khả năng ngôn ngữ, tư duy, trí nhớ và giải quyết vấn đề.\n\nTriệu chứng tắc ruột bao gồm các dấu hiệu sớm giúp nhận biết bệnh.\n\nTriệu chứng của tăng áp phổi thường xuất hiện khi bệnh đã nặng, có thể dẫn đến tử vong nếu không được điều trị.\n\nTriệu chứng của tăng huyết áp vô căn thường không rõ ràng và khó nhận biết.\n\nTriệu chứng của tăng tiểu cầu bao gồm đau đầu, hoa mắt, chóng mặt, đau ngực, tê yếu cơ, dị cảm đầu chi.\n\nTriệu chứng của tăng nhãn áp có thể bao gồm suy giảm thị lực không hồi phục.\n\nTriệu chứng của bệnh thoái hóa điểm vàng thường biểu hiện rất ít ở giai đoạn sớm.\n\nTriệu chứng thoát vị đĩa đệm có thể do phần nhân nhầy tràn ra ngoài gây kích ứng các dây thần kinh lân cận. Triệu chứng thoát vị đĩa đệm cột sống thắt lưng bao gồm đau, tê, và yếu ở chân.\n\nTriệu chứng cũng bao gồm dấu hiệu cần xử lý khi dùng quá liều thuốc Cialis.\n\nTriệu chứng tiểu không tự chủ bao gồm việc mất kiểm soát việc tiểu tiện.\n\nTriệu chứng cũng có thể giảm sau khi sử dụng trầu không.\n\nTriệu chứng của tràn dịch màng phổi có thể rất khác nhau, từ không có triệu chứng đến khó thở.\n\nTriệu chứng và dấu hiệu của trào ngược dạ dày thực quản và trào ngược dịch mật khá tương đồng.\n\nTriệu chứng của trật khớp háng chưa được mô tả chi tiết trong đoạn văn đã cho.\n\nTriệu chứng mà phì đại tuyến tiền liệt mang lại ảnh hưởng đến cuộc sống là yếu tố quyết định trong việc lựa chọn phương pháp điều trị.\n\nTriệu chứng của ung thư TTL có thể tương tự như phì đại lành tính TTL hoặc không có biểu hiện gì.\nNhiễm Trùng Do Vi-Rút Herpes: Thuốc kháng vi-rút như acyclovir được sử dụng để điều trị nhiễm trùng do vi-rút herpes HSV-1 và HSV-2.\nKem Acyclovir: Kem acyclovir là dạng thuốc tại chỗ của acyclovir.\nIkovir-200: Ikovir-200 là viên nén chứa aciclovir, được sử dụng trong điều trị và dự phòng nhiễm virus.\nAcyclovir Stada 200 mg - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Sự Nhân Lên Của Virus: Acyclovir ức chế sự nhân lên của virus.\nAcyclovir Stada 200 mg - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Buồn nôn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Tế Bào Nhiễm Virus Herpes: Acyclovir có tác dụng chọn lọc trên tế bào nhiễm virus Herpes.\nAcyclovir Stada 200 mg - Chóng Mặt: Chóng mặt là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAciclovir - Virus Herpes: Aciclovir được chỉ định trong điều trị và dự phòng nhiễm virus Herpes.\nAcyclovir Stada 200 mg - Đau Đầu: Đau đầu là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Đau đầu là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Tế Bào Nhiễm Virus: Acyclovir tác dụng chọn lọc trên tế bào nhiễm virus Herpes.\nAcyclovir Stada 200 mg - Sốt: Sốt là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Triệu Chứng: Acyclovir được sử dụng để điều trị triệu chứng của bệnh.\nAcyclovir Stada 200 mg - Suy Thận: Liều và số lần uống Acyclovir Stada 200 mg phải được điều chỉnh tùy theo mức độ tổn thương thận.&lt;SEP&gt;Bệnh nhân suy thận cần điều chỉnh liều acyclovir.\nAcyclovir - Kem Acyclovir: Kem acyclovir là dạng thuốc tại chỗ của acyclovir.\nAcyclovir Stada 200 mg - Đau Bụng: Đau bụng là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Da: Acyclovir được chỉ định điều trị nhiễm virus Herpes simplex trên da.\nAcyclovir Stada 200 mg - Mệt Mỏi: Mệt mỏi là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nNhiễm Trùng Do Vi-Rút Herpes - Thuốc Kháng Vi-Rút: Thuốc kháng vi-rút như acyclovir được sử dụng để điều trị nhiễm trùng do vi-rút herpes HSV-1 và HSV-2.\nAcyclovir Stada 200 mg - Nôn: Nôn là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Nôn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Niêm Mạc: Acyclovir được chỉ định điều trị nhiễm virus Herpes simplex trên niêm mạc.\nAcyclovir Stada 200 mg - Ngứa: Ngứa là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Tinh dầu đại hồi: Tinh dầu đại hồi có tác dụng với acyclovir trong việc kháng virus.\nDa - Herpes Simplex: Nhiễm virus Herpes simplex có thể ảnh hưởng đến da.\nAcyclovir Stada 200 mg - Quá Liều: Quá liều acyclovir có thể gây ra các triệu chứng trên đường tiêu hóa và thần kinh.\nAcyclovir Stada 200 mg - Phụ Nữ Mang Thai: Acyclovir Stada 200 mg chưa có nghiên cứu đầy đủ và có kiểm soát trên phụ nữ mang thai.\nAcyclovir Stada 200 mg - Buồn Ngủ: Buồn ngủ là tác dụng phụ thường gặp khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Cimetidin: Cimetidin cạnh tranh bài tiết chủ động qua các ống thận và làm giảm độ thanh thải của acyclovir ở thận khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Phát Ban: Phát ban là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nHerpes Simplex - Tỏi: Chiết xuất tỏi có tác dụng kháng virus Herpes simplex.\nAcyclovir - Acyclovir Stada 200 mg: Acyclovir là hoạt chất chính của thuốc Acyclovir Stada 200 mg.&lt;SEP&gt;Acyclovir là hoạt chất chính của Acyclovir Stada 200 mg.&lt;SEP&gt;Acyclovir Stada 200 mg thuộc loại thuốc Acyclovir.\nAcyclovir Stada 200 mg - Thần Kinh: Tác dụng không mong muốn của acyclovir có thể ảnh hưởng đến hệ thần kinh.\nBetamethasone - Herpes Zoster: Dùng Betamethasone đường toàn thân làm tăng nguy cơ bị herpes zoster.\nAcyclovir - Herpes Simplex: Quan hệ giữa Acyclovir và Herpes Simplex được mô tả như sau: Acyclovir được sử dụng để điều trị và phòng ngừa nhiễm Herpes simplex. Nó có tác dụng mạnh nhất đối với virus Herpes simplex type 1 và cũng có tác dụng chọn lọc trên tế bào bị nhiễm virus này. Acyclovir nhắm trúng đích vào virus Herpes simplex, giúp kiểm soát và ngăn chặn sự phát triển của bệnh.&lt;SEP&gt;Acyclovir tác dụng chọn lọc trên tế bào nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir được chỉ định dùng trong điều trị nhiễm Herpes simplex.\nAcyclovir Stada 200 mg - Cho Con Bú: Phụ nữ cho con bú cần chú ý khi sử dụng acyclovir.\nBetadine - Herpes Simplex: Betadine được dùng để điều trị herpes simplex.\nAciclovir - Herpes Simplex: Aciclovir được chỉ định trong điều trị nhiễm virus Herpes simplex.\nAcyclovir Stada 200 mg - Mang Thai: Acyclovir Stada 200 mg chưa có nghiên cứu đầy đủ và có kiểm soát trên phụ nữ mang thai.&lt;SEP&gt;Phụ nữ mang thai cần chú ý khi sử dụng acyclovir do thiếu nghiên cứu đầy đủ và có kiểm soát.\nHerpes Simplex - Mắt: Nhiễm virus Herpes simplex có thể ảnh hưởng đến mắt.\nAcyclovir - Herpes Simplex Type 2: Khoản quan hệ giữa Acyclovir và Herpes Simplex Type 2 được xác định để điều trị và dự phòng nhiễm virus Herpes simplex type 2. Acyclovir được chỉ định để điều trị cả nhiễm mới và ngăn chặn tái phát của Herpes simplex type 2. Tuy nhiên, cần lưu ý rằng Acyclovir có tác dụng kém hơn so với hiệu quả trên các loại virus khác đối với Herpes simplex type 2.\nAciclovir 800 mg - Mất Nước: Bệnh nhân mất nước cần chú ý khi dùng Aciclovir 800 mg.\nAcyclovir Stada 200 mg - Mẫn Cảm: Acyclovir Stada 200 mg chống chỉ định đối với bệnh nhân mẫn cảm với acyclovir và valacyclovir hay bất cứ thành phần nào của thuốc.\nAcyclovir - Herpes Zoster: Acyclovir được chỉ định dùng trong điều trị nhiễm Herpes zoster.\nHerpes Simplex - Kim Ngân Hoa: Kim Ngân Hoa có tác dụng chống virus Herpes simplex.\nAcyclovir - Viêm Nhiễm Do Virus Herpes Simplex: Acyclovir được sử dụng để điều trị viêm nhiễm do virus Herpes simplex.\nAcyclovir Stada 200 mg - Probenecid: Khi sử dụng đồng thời Probenecid và Acyclovir Stada 200 mg có thể gây ức chế cạnh.&lt;SEP&gt;Probenecid ức chế cạnh tranh đào thải acyclovir qua ống thận khi sử dụng cùng Acyclovir Stada 200 mg.\nAciclovir - Aciclovir 200mg: Aciclovir được chỉ định trong điều trị nhiễm virus Herpes simplex dưới dạng viên nén 200 mg.\nAciclovir - Agiclovir 200: Agiclovir 200 chứa aciclovir.\nAciclovir - Ikovir-200: Ikovir-200 chứa aciclovir.\nAcyclovir Stada 200 mg - Lú Lẫn: Lú lẫn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir Stada 200 mg - Cyclosporin: Cyclosporin có các dấu hiệu độc tính trên thận khi sử dụng cùng Acyclovir Stada 200 mg.\nGiác Mạc - Herpes Simplex: Nhiễm virus Herpes simplex có thể ảnh hưởng đến giác mạc.\nHerpes Simplex - Não: Nhiễm virus Herpes simplex có thể ảnh hưởng đến não.\nAcyclovir Stella 400 mg - Herpes Simplex: Thuốc Acyclovir Stella 400 mg được chỉ định điều trị nhiễm virus Herpes simplex da và niêm mạc.&lt;SEP&gt;Acyclovir Stella 400 mg được sử dụng để điều trị bệnh herpes simplex.\nHerpes Simplex - Niêm Mạc: Nhiễm virus Herpes simplex có thể ảnh hưởng đến niêm mạc.\nAcyclovir Stada 200 mg - Thẩm Phân Máu: Sau mỗi lần thẩm phân máu cần bổ sung ngay 1 liều Acyclovir Stada 200 mg.&lt;SEP&gt;Thẩm phân máu được sử dụng để kiểm soát độc tính khi dùng quá liều acyclovir.\nAcyclovir Stada 200 mg - Ketoconazol: Ketoconazol làm tăng hiệu lực chống virus của acyclovir khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Herpes Simplex: Thuốc Acyclovir Stada 200 mg được chỉ định điều trị và dự phòng nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir Stada 200 mg được sử dụng để điều trị herpes simplex.\nAcyclovir Stella 800 mg - Herpes Simplex: Acyclovir Stella 800 mg được chỉ định dùng trong điều trị nhiễm virus Herpes simplex.\nAcyclovir Boston 800 - Herpes Simplex: Thuốc Acyclovir Boston 800 được chỉ định dùng để điều trị và dự phòng nhiễm virus Herpes simplex.\nHerpes Simplex - Kim Vàng: Kim vàng kháng virus herpes simplex.\nAcyclovir Stada 200 mg - Amphotericin B: Amphotericin B làm tăng hiệu lực chống virus của acyclovir khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Thanh Thải Creatinin: Thanh thải creatinin giúp xác định liều dùng Acyclovir Stada 200 mg phù hợp với bệnh nhân suy thận.\nAcyclovir Stada 200 mg - Zidovudin: Khi sử dụng đồng thời Zidovudin và Acyclovir Stada 200 mg có thể gây trạng thái lơ mơ và ngủ lịm.&lt;SEP&gt;Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây trạng thái lơ mơ và ngủ lịm.\nAcyclovir Stada 200 mg - Viêm Giác Mạc: Acyclovir Stada 200 mg được chỉ định điều trị viêm giác mạc do nhiễm virus.\nAcyclovir Stada 200 mg - Theophyllin: Theophyllin tăng xấp xỉ 50% AUC của mình khi sử dụng cùng Acyclovir Stada 200 mg.\nB – Sol - Herpes Simplex: B – Sol chống chỉ định sử dụng đối với những người bị nhiễm herpes simplex.\nAcyclovir Stada 200 mg - Varicella Zoster: Thuốc Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Varicella zoster.&lt;SEP&gt;Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Varicella zoster.\nAcyclovir Stada 200 mg - Suy Chức Năng Thận: Bệnh nhân suy chức năng thận có thể gặp tác dụng phụ buồn ngủ và ngủ lơ mơ khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stella Cream - Herpes Simplex: Acyclovir Stella Cream được sử dụng để điều trị nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir Stella Cream được sử dụng để điều trị nhiễm Herpes simplex.\nAcyclovir Stada 200 mg - Valacyclovir: Acyclovir Stada 200 mg chống chỉ định đối với bệnh nhân mẫn cảm với acyclovir và valacyclovir hay bất cứ thành phần nào của thuốc.\nAcyclovir Stada 200 mg - Herpes Simplex Type 1: Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Herpes simplex type 1.\nAcyclovir Stada 200 mg - Herpes Simplex Type 2: Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Herpes simplex type 2.\nAcyclovir Stada 200 mg - Nhạy Cảm Với Ánh Sáng: Nhạy cảm với ánh sáng là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Ngủ Lơ Mơ: Ngủ lơ mơ là tác dụng phụ thường gặp khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stella 800 mg - Herpes Simplex Type 2: Thuốc Acyclovir Stella 800 mg được chỉ định điều trị nhiễm virus Herpes simplex type 2.\nAcyclovir Boston 800 - Herpes Simplex Type 2: Acyclovir Boston 800 được chỉ định điều trị nhiễm Herpes simplex type 2.\nAcyclovir Stada 200 mg - Bệnh Nhân Lớn Tuổi: Bệnh nhân lớn tuổi cần điều chỉnh liều acyclovir do thường có suy giảm chức năng thận.\nAcyclovir Stada 200 mg - Độc Tính Trên Thận: Sử dụng Acyclovir Stada 200 mg cùng Cyclosporin có thể gây độc tính trên thận.\nAcyclovir Stada 200 mg - Herpes Zoster: Acyclovir Stada 200 mg được sử dụng để điều trị herpes zoster.\nAcyclovir Stada 200 mg - Ngủ Lịm: Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây ngủ lịm.\nAciclovir 800 mg - Môi: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex ở môi.\nAcyclovir Stada 200 mg - Mycophenolat mofetil: Mycophenolat mofetil tăng AUC trong huyết tương của acyclovir và chất chuyển hóa không có hoạt tính của mình khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Trạng Thái Lơ Mơ: Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây trạng thái lơ mơ.\nC. Nutans - Herpes Simplex: *C. nutans* được sử dụng để điều trị tổn thương do Herpes simplex.\nAciclovir 800 mg - Tổn Thương Thận: Bệnh nhân có tổn thương thận cần chú ý khi dùng Aciclovir 800 mg.\nAcyclovir Boston 200 - Herpes Simplex Type 2: Thuốc Acyclovir Boston 200 được chỉ định dùng để điều trị và dự phòng nhiễm virus Herpes simplex type 2.&lt;SEP&gt;Acyclovir Boston 200 được chỉ định điều trị và phòng ngừa tái phát Herpes simplex type 2.\nAciclovir 800 mg - Creatinin: Bệnh nhân cần chú ý về creatinin khi dùng Aciclovir 800 mg.\nAgiclovir 5% Agimexpharm - Herpes Simplex: Agiclovir 5% Agimexpharm được sử dụng để điều trị nhiễm virus Herpes simplex.\nAciclovir 800 mg - Herpes Simplex: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex.\nAcyclovir 5% Agimexpharm - Herpes Simplex: Thuốc Acyclovir 5% Agimexpharm được chỉ định điều trị bệnh Herpes simplex.\nAcyclovir Stella Cream - Herpes Simplex Type 2: Acyclovir Stella Cream được chỉ định điều trị nhiễm virus Herpes simplex type 2 ở da.\nHerpes Simplex - Màng Não: Nhiễm virus Herpes simplex có thể ảnh hưởng đến màng não.\nHerpes Simplex - Ngăn Ngừa Tái Phát: Ngăn ngừa tái phát là phương pháp điều trị nhằm ngăn chặn sự tái phát của bệnh Herpes simplex.\nHerpes Simplex - Ngăn Ngừa Nhiễm: Ngăn ngừa nhiễm là phương pháp điều trị nhằm ngăn chặn sự nhiễm bệnh Herpes simplex.\nHerpes Simplex - Virus Kháng Thuốc: Virus kháng thuốc trở thành vấn đề lớn cho người bệnh suy giảm miễn dịch, đặc biệt là nhiễm virus Herpes simplex.\nAciclovir 800 mg - Nhiễm HIV: Bệnh nhân nhiễm HIV cần chú ý khi dùng Aciclovir 800 mg.\nAciclovir 800 mg - Tiêm Truyền Tĩnh Mạch: Aciclovir 800 mg được dùng qua tiêm truyền tĩnh mạch.\nAciclovir 800 mg - Thuốc Mỡ: Aciclovir 800 mg được dùng qua thuốc mỡ.\nAciclovir 800 mg - Herpes Zoster: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes zoster.\nAciclovir 800 mg - Sinh Dục: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex ở sinh dục.\nAciclovir 800 mg - Bôi: Aciclovir 800 mg được dùng qua bôi.\nAciclovir 800 mg - Độc Thận: Bệnh nhân cần chú ý về độc thận khi dùng Aciclovir 800 mg cùng với các thuốc khác.\nAciclovir 800 mg - Tra Mắt: Aciclovir 800 mg được dùng qua tra mắt.\nHerpes Simplex Type 2 - Valacyclovir: Valacyclovir được sử dụng trong điều trị nhiễm virus Herpes simplex type 2.']</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thuốc **Acyclovir Stada 200 mg** có tác dụng mạnh nhất đối với virus **Herpes simplex** type 1. Độ nhạy kém hơn đối với virus **Herpes simplex** type 2 và virus **Varicella zoster**.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Acyclovir Stada 200 mg có tác dụng mạnh nhất trên virus Herpes simplex type 1, kém hơn ở virus Herpes simplex 2 và virus Varicella zoster.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mix</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1666666666666667</v>
+      <c r="G24" t="n">
+        <v>0.8744558072438843</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8852806184526377</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>['Tăng Alanine: Tăng alanine là xét nghiệm đánh giá chức năng gan.\nDalacin T: Dalacin T là sản phẩm kem bôi da chứa clindamycin dùng trong điều trị mụn trứng cá.&lt;SEP&gt;Dalacin T là thuốc bôi chứa clindamycin, được sử dụng để điều trị các bệnh về da.&lt;SEP&gt;Dalacin T là thuốc bôi tại chỗ chứa clindamycin, được sử dụng để điều trị mụn trứng cá.&lt;SEP&gt;Dalacin T là thuốc bôi.&lt;SEP&gt;Dalacin T là thuốc có thành phần tương tự Clindamycin.\nXét Nghiệm Chức Năng Gan: Xét nghiệm chức năng gan giúp đánh giá hoạt động của gan.\nThông Tin Sử Dụng Thuốc: Thông tin sử dụng thuốc Acemol 325 mg bao gồm hướng dẫn bảo quản và cảnh báo về các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Thông tin hướng dẫn sử dụng Dalacin T nhằm đảm bảo hiệu quả và an toàn khi sử dụng.\nXét Nghiệm Đông Cầm Máu: Xét nghiệm đông cầm máu giúp đánh giá mức độ hoạt động của gan.\nAlzyltex: Alzyltex là thuốc cần thận trọng khi sử dụng cho bệnh nhân suy thận, người lái xe, và phụ nữ có thai.&lt;SEP&gt;Thuốc Alzyltex được sử dụng để điều trị viêm mũi dị ứng kéo dài, viêm mũi dị ứng theo mùa, và nổi mề đay mạn tính.&lt;SEP&gt;Alzyltex là thuốc chứa thành phần hoạt chất tương tự như Cetirizine.\nMen Gan Transaminase: Men gan transaminase là xét nghiệm đánh giá chức năng gan.\nĐộ Thanh Thải: Độ thanh thải là chỉ số đánh giá chức năng thận, cần dưới 10ml/phút khi sử dụng Alzyltex.&lt;SEP&gt;Độ thanh thải là chỉ số đánh giá khả năng đào thải thuốc của thận.\nKiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ, đặc biệt là chức năng gan, thận và hệ tạo máu nếu sử dụng Augmentin kéo dài.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ là việc khám sức khỏe theo lịch hẹn tái khám của bác sĩ hoặc khám ngay khi có dấu hiệu bất thường.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ để đánh giá chức năng gan và tầm soát viêm gan siêu vi B, C.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ giúp phát hiện tình trạng tăng huyết áp vô căn.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ là việc kiểm tra sức khỏe nhằm phát hiện sớm các vấn đề về sức khỏe.\nDaflon: Daflon là thuốc chứa thành phần tương tự như Agiosmin 500mg.&lt;SEP&gt;Daflon là thuốc điều trị bệnh trĩ.&lt;SEP&gt;Daflon là một trong những thuốc đang lưu hành trên thị trường điều trị bệnh hậu môn trực tràng.&lt;SEP&gt;Daflon là thuốc được chỉ định để điều trị bệnh trĩ và suy tĩnh mạch.&lt;SEP&gt;Daflon là thuốc chứa hoạt chất diosmin và hesperidin, được chỉ định điều trị bệnh trĩ và suy tĩnh mạch.&lt;SEP&gt;Daflon là thuốc được dùng để điều trị suy tĩnh mạch và bệnh trĩ.&lt;SEP&gt;Daflon là thuốc dùng để điều trị các vấn đề liên quan đến tĩnh mạch và trĩ.\nDiagnostic Test: Tăng creatinin phosphokinase huyết là xét nghiệm đánh giá chức năng cơ tim.\nTriglycerid: Triglycerid là một loại chất béo đóng vai trò quan trọng trong cơ thể, đặc biệt là trong việc dự trữ năng lượng. Nó cũng đóng vai trò trong quá trình hình thành mảng xơ vữa động mạch. Triglycerid là một chỉ số quan trọng trong máu và chịu ảnh hưởng bởi nhiều yếu tố khác nhau, bao gồm cả các tác nhân tự nhiên và thuốc. \n\nTriglycerid là thành phần chính của rối loạn lipid máu và là một dạng mỡ trong máu, góp phần gây rối loạn lipid máu, xơ vữa mạch máu, các bệnh lý mạch vành, và đột quỵ não. Tăng triglycerid máu là tình trạng rối loạn lipid máu. Việc kiểm soát mức độ triglycerid là cần thiết để ngăn ngừa các vấn đề sức khỏe liên quan đến xơ vữa động mạch và các bệnh tim mạch khác.\n\nMức độ triglycerid trong máu có thể bị ảnh hưởng bởi việc tiêu thụ mầm đậu nành, vì nó có khả năng giảm lượng triglycerid. Ngoài ra, nhiều thành phần tự nhiên như cây Chàm, cây mướp khía, và hà thủ ô cũng có khả năng kiểm soát mức độ triglycerid trong máu. Viên thuốc Vildagliptin và Atorvastatin cũng có thể giúp giảm mức độ triglycerid trong cơ thể.\n\nTriglycerid là một thành phần trong huyết thanh. Nó được coi là một chất béo gây hại cho sức khỏe tim mạch. Mức độ triglycerid trong máu có thể tăng lên do bổ sung vitamin D và cholesterol, cũng như việc sử dụng thuốc Aluvia. \n\nTriglycerid cũng là một thành phần lipid “xấu” trong máu được Atorvastatin giảm nồng độ. Nó là chất được kiểm tra trong các xét nghiệm liên quan đến Daflon và Rosuvastatin được sử dụng để điều trị tăng triglycerid.&lt;SEP&gt;Triglycerid trong huyết thanh được giảm bởi dịch chiết từ hạt nảy mầm cây tía tô.&lt;SEP&gt;Triglycerid là chất béo được tìm thấy trong huyết tương, tăng nồng độ do suy chức năng giáp.&lt;SEP&gt;Hormone giáp làm giảm nồng độ triglycerid trong huyết tương.\nTransaminase Huyết Thanh: Transaminase huyết thanh là xét nghiệm cần thiết để phát hiện men gan tăng cao.&lt;SEP&gt;Transaminase huyết thanh là xét nghiệm đánh giá chức năng gan.\nAmoxicillin: Amoxicillin là một loại thuốc kháng sinh thuộc nhóm Beta Lactam và Penicillin, được sử dụng rộng rãi trong nhiều phác đồ điều trị khác nhau. Nó có phổ kháng khuẩn rộng và thường được sử dụng để điều trị các bệnh nhiễm khuẩn, bao gồm cả nhiễm Helicobacter pylori gây ra loét dạ dày – tá tràng. Amoxicillin cũng được sử dụng trong việc điều trị nhiễm trùng tai, nhiễm trùng phế quản, và một số bệnh nhiễm trùng da và mô mềm. Thuốc này là thành phần chính của Augmentin và Augmentin 625 mg, trong đó Acid clavulanic giúp bảo vệ Amoxicillin khỏi sự phân hủy bởi men beta-lactamase. Amoxicillin cũng là hoạt chất chính trong Amoxicillin Mekophar và Amoxycilin Vidipha, được sử dụng để điều trị các bệnh nhiễm trùng do vi khuẩn gây ra. Khi sử dụng Amoxicillin lâu dài, cần theo dõi chức năng gan, thận và điều chỉnh liều lượng khi bệnh nhân suy thận. Amoxicillin thường được sử dụng kết hợp với các thuốc khác như Omeprazol để điều trị nhiễm Helicobacter Pylori hoặc kết hợp với Allopurinol 300 mg. Ngoài ra, nó cũng thường được sử dụng kết hợp với Ambroxol để tăng hiệu quả điều trị, và có thể tương tác với các phiên bản khác của Ambroxol như Ambroxol An Thiên và Ambroxol Boston. Amoxicillin còn được sử dụng kết hợp với Ampelop để tăng hiệu lực diệt Helicobacter pylori. Thuốc này có thể bị kéo dài thời gian đào thải bởi Probenecid. Tuy nhiên, Amoxicillin chống chỉ định cho người có tiền sử vàng da hoặc rối loạn gan mật do Amoxicillin.\n\nAmoxicillin cũng được sử dụng để dự phòng viêm nội tâm mạc nhiễm khuẩn và điều trị nhiễm khuẩn đường hô hấp nặng hoặc tái phát. Amoxicillin là thuốc kháng sinh, tiêu diệt vi khuẩn bằng cách cản trở quá trình tổng hợp peptidoglycan trong thành tế bào vi khuẩn. Thuốc này cũng là thành phần chính trong Augtipha và có thể gây mẩn đỏ kèm theo sốt nổi hạch, đặc biệt đối với những người đã từng bị dị ứng với Amoxicillin. Amoxicillin có khả năng tăng sự hấp thu khi dùng chung với Nifedipin. Đồng thời, nó cũng được sử dụng kết hợp với Barole trong điều trị loét dạ dày tá tràng do H.Pylori và kết hợp với Barole và Clarithromycin để điều trị loét dạ dày tá tràng.\n\nAmoxicillin là thành phần của Augmentin, có thể hình thành các tinh thể niệu nếu không uống đủ nước. Amoxicillin cũng có thể gây phát ban dạng sởi ở những người đã có tiền sử sau khi dùng Amoxicillin.\n\nAmoxicillin cũng được sử dụng như một kháng sinh uống điều trị bệnh Lyme giai đoạn sớm. Nó là một kháng sinh diệt Helicobacter pylori và không được khuyến nghị sử dụng trong bệnh tăng bạch cầu đơn nhân nhiễm khuẩn do nguy cơ gây phát ban.\n\nAmoxicillin là thành phần chính của Augmentin 500 mg/62,5 mg và Augtipha, thuộc nhóm penicillin. Thuốc này là thành phần hóa học trong Amoksiklav và cũng là hoạt chất chính trong Amoksiklav. Amoxicillin là thuốc kháng sinh được bảo vệ khỏi men beta-lactamase nhờ clavulanic và có phổ kháng khuẩn rộng, tác dụng được cả vi khuẩn Gram dương và Gram âm.\n\nAmoxicillin là thuốc kháng sinh dễ bị men beta-lactamase phân hủy. Amoxicillin là kháng sinh beta-lactam, được sử dụng trong điều trị nhiễm khuẩn. Amoxicillin làm giảm tái hấp thu oestrogen và giảm hiệu quả của thuốc tránh thai dạng uống. Amoxicillin cũng được dùng để điều trị nhiễm Chlamydia và đề phòng khi tiếp xúc với Bacillus anthracis ở phụ nữ mang thai. Amoxicillin là thuốc kháng sinh được sử dụng trong điều trị nhiễm khuẩn, có thể gây tiêu chảy và phát ban.&lt;SEP&gt;Amoxicillin là thành phần hoạt chất chính của thuốc Curam, được sử dụng để điều trị nhiễm khuẩn.&lt;SEP&gt;Amoxicillin là thuốc có thể chuyển sang sử dụng nếu nhiễm khuẩn nhạy cảm với nó.&lt;SEP&gt;Amoxicillin là kháng sinh được đề cập trong video chia sẻ chi tiết.&lt;SEP&gt;Amoxicillin có thể gây ra tình trạng dị ứng liên quan với bệnh tăng bạch cầu đơn nhân nhiễm khuẩn vi sự xuất hiện ban dạng sởi.\nAlanin-Aminotransferase (ALT): ALT là xét nghiệm đánh giá chức năng gan.\nTiền Sử Dị Ứng: Tiền Sử Dị Ứng là tình trạng mà một người đã từng gặp phải phản ứng dị ứng với một số thành phần cụ thể của thuốc, bao gồm cả các chất hoạt động như Ambroxol hoặc Bromhexin. Tình trạng này cũng có thể xuất hiện khi người bệnh đã từng gặp phản ứng dị ứng với các chất như penicillin hoặc cephalosporin. Tiền sử dị ứng với penicillin, cephalosporin, hoặc các dị nguyên khác là chống chỉ định khi sử dụng nhiều loại thuốc khác nhau, bao gồm Amoxicilin 500 mg, Amoxicillin Domesco, và Amoxicillin Mekophar. Điều này đòi hỏi việc kiểm tra kỹ lưỡng về tiền sử dị ứng trước khi dùng các loại thuốc này để đảm bảo an toàn cho người bệnh. Ngoài ra, tiền sử dị ứng với bất kỳ thành phần nào của thuốc cũng là chống chỉ định cho việc sử dụng Aspirin STELLA và thuốc Bambec. Việc xác định rõ ràng tiền sử dị ứng là rất quan trọng để tránh những phản ứng nghiêm trọng có thể xảy ra khi sử dụng các loại thuốc trên.\n\nTiền Sử Dị Ứng cũng là chống chỉ định khi sử dụng thuốc Bảo Thanh Hoa Linh, Betadine, và Cefurobiotic. Trước khi bắt đầu điều trị bằng Amoxicillin, tiền sử dị ứng cần được điều tra kỹ. Đối với thuốc Cefpodoxim, tiền sử dị ứng với cephalosporin, penicillin hoặc thuốc khác cần được kiểm tra trước khi bắt đầu điều trị. Tiền sử dị ứng với thiocolchicosid, colchicine, hoặc bất kỳ thành phần nào của thuốc cũng là chống chỉ định. Đặc biệt, tiền sử dị ứng với bất kỳ thành phần nào trong tinh dầu hoàng đàn có thể làm tăng nguy cơ phản ứng tiêu cực.\n\nTóm lại, Tiền Sử Dị Ứng là một yếu tố quan trọng cần được đánh giá kỹ lưỡng trước khi bắt đầu bất kỳ phương pháp điều trị nào nhằm đảm bảo an toàn cho người bệnh và ngăn chặn các phản ứng dị ứng nghiêm trọng có thể xảy ra.&lt;SEP&gt;Tiền sử dị ứng là tình trạng sức khỏe cần tham khảo ý kiến người có chuyên môn trước khi sử dụng tinh dầu quế.\nTỷ Lệ Albumin / Globulin: Tỷ lệ albumin / globulin là một xét nghiệm đánh giá tình trạng sức khỏe.\nDexacin: Dexacin là sản phẩm của Công ty liên doanh Meyer-BPC, được bào chế ở dạng viên nén với màu tím và chứa hoạt chất chính là Dexamethason.&lt;SEP&gt;Dexacin được chỉ định trong các bệnh lý như chống dị ứng, nhiễm trùng, tác dụng trên thần kinh và tai-mũi-họng. Thuốc này có tác dụng chống viêm mạnh mẽ và được sử dụng bằng đường uống.&lt;SEP&gt;Dexacin là thuốc chứa corticoid có thể gây ra nhiều tác dụng phụ.&lt;SEP&gt;Dexacin là thuốc có thể gây ra tương tác với một số loại thuốc khác.&lt;SEP&gt;Dexacin chứa Dexamethason, có chống chỉ định và cần thận trọng khi dùng.&lt;SEP&gt;Dexacin được sử dụng cho bệnh nhân không dung nạp galactose, rối loạn hấp thu glucose – galactose và thiếu hụt Lap lactase.&lt;SEP&gt;Dexacin là thuốc được đề cập đến cách bảo quản và giá bán.\nChuẩn Đoán Creatinin: Chuẩn đoán creatinin là xét nghiệm đánh giá chức năng thận.\nThận Trọng Khi Dùng: Thận trọng khi dùng Dexacin là các cảnh báo về việc sử dụng thuốc.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThăm Khám: Thăm khám là quy trình kiểm tra sức khỏe được thực hiện bởi bác sĩ và chuyên gia y tế, nhằm xác định tình trạng sức khỏe của bệnh nhân. Quá trình thăm khám bao gồm việc kiểm tra sức khỏe tổng quát cũng như việc phát hiện các bệnh lý cụ thể. Thăm khám đóng vai trò quan trọng trong việc xác định tình trạng bệnh và nguyên nhân gây bệnh, giúp phát hiện sớm các vấn đề sức khỏe như áp-xe phổi, viêm phổi kẽ, và bệnh nấm da đùi. \n\nThăm khám không chỉ giúp bác sĩ nắm bắt thông tin về bệnh nhân mà còn là bước kiểm tra cần thiết để đánh giá tình trạng sức khỏe của bệnh nhân và xác định tình trạng bệnh lý. Qua quá trình thăm khám, mọi dấu hiệu và triệu chứng đều được đánh giá một cách kỹ lưỡng và toàn diện, từ đó hỗ trợ việc chẩn đoán bệnh lichen xơ hóa và loạn sản khớp háng ở trẻ em. \n\nNgoài ra, thăm khám còn giúp phát hiện tác dụng phụ do quá liều của một số thuốc như Carsantin. Thăm khám cũng đóng vai trò quan trọng trong việc xác định nguyên nhân và phương pháp điều trị thích hợp cho nhiều tình trạng khác nhau như phì đại tiền liệt tuyến, rụng tóc vành khăn ở trẻ, và sỏi mật.&lt;SEP&gt;Thăm khám tại các cơ sở y tế để được điều trị kịp thời khi có triệu chứng suy gan.&lt;SEP&gt;Thăm khám là quy trình kiểm tra sức khỏe nhằm phát hiện sớm và điều trị suy gan.&lt;SEP&gt;Thăm khám là quá trình bác sĩ kiểm tra sức khỏe người bệnh.&lt;SEP&gt;Thăm khám là quy trình kiểm tra sức khỏe do bác sĩ chuyên khoa nội tiết thực hiện.\nChuẩn Đoán Creatinin - Suy Thận: Chuẩn đoán creatinin được sử dụng để đánh giá chức năng thận của bệnh nhân suy thận.\nDalacin T - Thông Tin Sử Dụng Thuốc: Thuốc Dalacin T được cung cấp thông tin hướng dẫn sử dụng.\nKiểm Tra Sức Khỏe Định Kỳ - Đau Bụng: Kiểm tra sức khỏe định kỳ giúp phát hiện và theo dõi dấu hiệu đau bụng.\nAlzyltex - Độ Thanh Thải: Độ thanh thải cần kiểm tra trước khi sử dụng Alzyltex.\nKiểm Tra Sức Khỏe Định Kỳ - Suy Gan: Kiểm tra sức khỏe định kỳ để đánh giá chức năng gan và tầm soát bệnh.\nDaflon - Triglycerid: Daflon yêu cầu kiểm tra triglycerid trong các xét nghiệm.\nDiagnostic Test - Huyết Áp: Huyết áp được đo để đánh giá tình trạng bệnh.\nAmoxicillin - Tiền Sử Dị Ứng: Tiền sử dị ứng cần được kiểm tra trước khi dùng Amoxicillin.\nAtorvastatin - Transaminase Huyết Thanh: Atorvastatin yêu cầu xét nghiệm transaminase huyết thanh trước và trong quá trình điều trị.\nDexacin - Thận Trọng Khi Dùng: Dexacin có cảnh báo thận trọng khi dùng.\nAugmentin - Kiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ, đặc biệt là chức năng gan, thận và hệ tạo máu nếu sử dụng Augmentin kéo dài.\nThuốc - Thăm Khám: Thăm khám nên được tiến hành trước khi sử dụng thuốc để ngăn chặn tác dụng phụ.\nDiagnostic Test - Xét Nghiệm Máu: Xét nghiệm máu được thực hiện để đánh giá tình trạng bệnh.\nDa - Dalacin T: Dalacin T được sử dụng để điều trị các bệnh về da.\nXét Nghiệm Máu - Xét Nghiệm Đông Cầm Máu: Xét nghiệm đông cầm máu là chỉ số đánh giá mức độ hoạt động của gan.\nDalfusin - Dị Ứng: Dị ứng với Dalfusin là một điều kiện cần thông báo cho bác sĩ trước khi sử dụng thuốc.\nDiagnostic Test - Mắt: Mắt được kiểm tra để xem các tổn thương.\nRửa Tay - Thuốc Bôi Âm Đạo: Rửa tay trước và sau khi sử dụng thuốc bôi âm đạo.\nMen Gan Transaminase - Rosuvastatin: Rosuvastatin được kiểm tra men gan transaminase trước khi sử dụng.\nIsotretinoin - Nhiễm Nấm: Kiểm tra cận lâm sàng cần thực hiện trước và sau khi sử dụng Isotretinoin cho bệnh nhân có nhiễm nấm.\nBệnh Tim Mạch - Kiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ giúp phát hiện sớm các vấn đề về sức khỏe, bao gồm cả bệnh tim mạch.\nStatin - Transaminase Huyết Thanh: Statin cần kiểm tra transaminase huyết thanh trước khi bắt đầu điều trị.\nKiểm Tra Sức Khỏe Định Kỳ - Tăng Huyết Áp Vô Căn: Kiểm tra sức khỏe định kỳ giúp phát hiện tình trạng tăng huyết áp vô căn.\nCúc Tần - Tỷ Lệ Albumin / Globulin: Cúc tần có thể được sử dụng để kiểm tra tỷ lệ albumin / globulin.\nAtorlog - Transaminase Huyết Thanh: Atorlog cần kiểm tra transaminase huyết thanh trước khi bắt đầu điều trị.\nKiểm Tra Sức Khỏe Định Kỳ - Nang Nước Cạnh Tai Vòi: Kiểm tra sức khỏe định kỳ giúp phát hiện sớm và theo dõi nang nước cạnh tai vòi.\nKiểm Tra Sức Khỏe Định Kỳ - Viêm Gan Siêu Vi B: Kiểm tra sức khỏe định kỳ để tầm soát viêm gan siêu vi B.\nKiểm Tra Sức Khỏe Định Kỳ - Viêm Gan Siêu Vi C: Kiểm tra sức khỏe định kỳ để tầm soát viêm gan siêu vi C.\nAlanin-Aminotransferase (ALT) - Thuốc Bỏng: Thuốc bỏng không gây độc tính đối với ALT trong chuột.\nDiagnostic Test - Xét Nghiệm Nước Tiếu: Xét nghiệm nước tiểu được thực hiện để đánh giá tình trạng bệnh.\nDiagnostic Test - Tăng Alanine: Tăng alanine là xét nghiệm đánh giá chức năng gan.\nDiagnostic Test - Tăng Creatinin Phosphokinase Huyết: Tăng creatinin phosphokinase huyết là xét nghiệm đánh giá chức năng cơ tim.']</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần:
+1. **Tham khảo ý kiến bác sĩ:** Dalacin T là thuốc bôi da chứa clindamycin, được sử dụng để điều trị mụn trứng cá. Trước khi bắt đầu sử dụng, bệnh nhân cần tham khảo ý kiến bác sĩ để đảm bảo rằng thuốc phù hợp với tình trạng sức khỏe của họ.
+2. **Kiểm tra tiền sử dị ứng:** Bệnh nhân cần thông báo cho bác sĩ nếu họ có tiền sử dị ứng với clindamycin hoặc bất kỳ thành phần nào khác trong thuốc Dalacin T. 
+3. **Hiểu rõ cách sử dụng:** Bệnh nhân nên đọc kỹ hướng dẫn sử dụng trên nhãn thuốc hoặc tham khảo tờ hướng dẫn sử dụng thuốc kèm theo để biết cách sử dụng thuốc một cách chính xác.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tham khảo ý kiến ​​bác sĩ hoặc chuyên gia y tế để đảm bảo liều dùng phù hợp.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7793774047283971</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7573443511570993</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>['Calci Milk - D: Calci Milk - D là thuốc chứa thành phần tương tự Calcigenol.\nCalcium Stada Vitamin D: Calcium Stada Vitamin D là hỗn dịch uống chứa calci và vitamin D, giúp điều chỉnh sự thiếu hụt đồng thời vitamin D và calci ở các đối tượng cao tuổi, điều trị loãng xương và cải thiện tình trạng thiếu calci cũng như vitamin D ở trẻ em.&lt;SEP&gt;Hỗn dịch Calcium Stada Vitamin D được dùng theo đường uống để bổ sung canxi và vitamin D.&lt;SEP&gt;Calcium Stada Vitamin D là hỗn dịch được bào chế ở dạng dung dịch dùng theo đường uống.&lt;SEP&gt;Calcium Stada Vitamin D là hỗn dịch chứa calci và vitamin D, cần được bảo quản tránh ánh nắng mặt trời và môi trường ẩm ướt.\nCalcigenol: Calcigenol là sự kết hợp giữa canxi và vitamin D, được sử dụng để bổ sung canxi và phòng ngừa còi xương.&lt;SEP&gt;Calcigenol là thuốc bổ/khoáng chất và vitamin, giúp bổ sung canxi và vitamin D, phòng ngừa và hỗ trợ điều trị thiếu canxi.&lt;SEP&gt;Calcigenol là thuốc chứa vitamin D2, được sử dụng trong điều trị tình trạng thiếu vitamin D.&lt;SEP&gt;Calcigenol là thuốc phòng ngừa còi xương, có thể gây quá liều vitamin D nếu sử dụng liều cao và kéo dài.&lt;SEP&gt;Calcigenol là thuốc cần được bảo quản ở nơi khô ráo, không quá 30°C và tránh tầm tay trẻ em.&lt;SEP&gt;Calcigenol là thuốc chứa vitamin D, có thể gây tăng canxi huyết nếu sử dụng quá liều.\nVitamin D: Vitamin D là một chất dinh dưỡng cần thiết cho cơ thể, đóng vai trò quan trọng trong việc kiểm soát các hormon tuyến cận giáp và nồng độ của một số khoáng chất như calci và phospho. Vitamin D giúp xương khớp chắc khỏe, hỗ trợ quá trình tạo xương và phát triển của trẻ, và là chất dinh dưỡng cần thiết cho bệnh nhân loãng xương. Nó cũng là thành phần chính trong nhiều loại thuốc như Agi-Calci, Appeton Lysine Syrup, Calci - D Mekophar, Calci D Hasan, và Babi B.O.N. Vitamin D được chuyển hóa thành calcitriol (D3) bởi thận, giúp tạo đủ Vitamin D khi dùng Calcitriol, đặc biệt là đối với bệnh nhân bị bệnh thận. Vitamin D cũng được sử dụng để phòng ngừa gãy xương lâm sàng sau gãy xương đùi do chấn thương nhẹ thông qua việc điều trị cho bệnh nhân. Đặc biệt, nó là chất bổ sung cần thiết khi dùng acid zolendronic và Aclasta, đặc biệt là đối với bệnh nhân mắc bệnh Paget. Khi sử dụng Aclasta, việc bổ sung đầy đủ Vitamin D là rất quan trọng để ngăn chặn tình trạng loãng xương nếu chế độ ăn uống không đảm bảo đủ lượng Vitamin D cần thiết.\n\nVitamin D đóng vai trò quan trọng trong quá trình tăng cường sức khỏe của động mạch và các cơ quan nội tạng khác, giúp xương và răng trở nên chắc khỏe hơn nhờ vào khả năng tăng cường hấp thu canxi. Tuy nhiên, việc sử dụng Vitamin D ở liều lượng cao hoặc kéo dài có thể dẫn đến tình trạng cường vitamin D, gây ra các tác dụng phụ như mụn và tăng canxi huyết khi quá liều. Vitamin D là thành phần chính trong Calcigenol, có thể gây quá liều nếu sử dụng không đúng cách. Vitamin D cần được thận trọng khi dùng cho người suy thận, bệnh tim, hoặc xơ vữa động mạch vì có thể gây tăng canxi huyết nếu sử dụng quá liều. Vitamin D cũng có thể gây tăng canxi huyết khi sử dụng đồng thời với Calcium Boston và có thể gây rối loạn chuyển hoá calci nếu quá liều và khi dùng đồng thời với rifampicin, phenobarbital, phenytoin.\n\nVitamin D là chất dinh dưỡng cần được kiểm tra khi điều trị tăng canxi huyết. Vitamin D cũng là thành phần chính trong Calcium Stada Vitamin D, giúp điều chỉnh sự thiếu hụt vitamin D. Cuối cùng, bổ sung vitamin D có thể giúp bảo vệ xương khi điều trị bằng corticosteroid dài hạn. Vitamin D là thành phần cần thiết để ngăn ngừa loãng xương và là thành phần hỗ trợ Calci vào xương trong Davita Bone Sugar free. Vitamin D là thành phần hóa học trong dầu jojoba và trong dầu bơ giúp cấp ẩm và bảo vệ da khỏi tia UV. Vitamin D là sản phẩm của quá trình tổng hợp từ cholesterol và là một chất được gan lưu trữ. Vitamin D là dưỡng chất cần thiết cho mật độ xương và là chất dinh dưỡng quan trọng cho khả năng hấp thụ và sử dụng canxi của cơ thể. Vitamin D là chất bổ sung giúp tăng cường hấp thu canxi trong cơ thể và đóng vai trò quan trọng trong việc tăng khả năng hấp thu canxi vào máu.\n\nVitamin D là một vitamin cần thiết cho sự hấp thu calci. Nó cũng là thành phần trong kem bôi trơn được sử dụng trong hỗ trợ điều trị lichen sclerosus. Vitamin D là chất dinh dưỡng giúp hấp thu canxi và hỗ trợ sức khỏe xương. Vitamin D là chất dinh dưỡng cần thiết cho sự hấp thu canxi và duy trì sức khỏe xương. Thiếu vitamin D có thể gây ra bệnh loãng xương. Vitamin D cũng là một loại vitamin có trong mía lau. Vitamin D từ trứng, sữa và ánh sáng mặt trời có thể giúp giảm co thắt cơ mặt. Vitamin D là hợp chất hữu cơ cần thiết cho sự phát triển và duy trì sức khỏe của cơ thể. Vitamin D là chất cần thiết để tổng hợp qua việc tắm nắng buổi sớm. Vitamin D là chất dinh dưỡng cần thiết cho sự phát triển của xương và tóc. Vitamin D là thành phần trong dầu bơ có lợi cho da.\n\nNgoài ra, Vitamin D được bổ sung cho bệnh nhân suy thận mãn tính để hạn chế vấn đề yếu xương. Vitamin D cũng là thành phần trong Tang diệp và được khuyến nghị cho người lớn từ 400-800 IU mỗi ngày. Vitamin D là thành phần chính trong D-Cure, giúp bổ sung vitamin D cho cơ thể. Vitamin D là thành phần có trong các chế phẩm cần ngừng sử dụng khi điều trị tăng calci huyết.&lt;SEP&gt;Vitamin D là chất dinh dưỡng cần thiết cho cơ thể.&lt;SEP&gt;Vitamin D là chất dinh dưỡng cần thiết cho cơ thể, có thể tăng lượng canxi trong máu nếu uống quá nhiều.&lt;SEP&gt;Vitamin D là chất cần kiểm soát liều lượng để giảm nguy cơ tăng canxi máu.&lt;SEP&gt;Vitamin D là một trong những nhóm vitamin có trong trà đông trùng hạ thảo.&lt;SEP&gt;Vitamin D là một trong những vitamin có trong Đông trùng hạ thảo.\nMẫn Cảm Với Vitamin D2: Mẫn cảm với vitamin D2 là triệu chứng chống chỉ định dùng Calcigenol.\nKê: Kê là loại ngũ cốc chứa nhiều chất dinh dưỡng như protein, lipid, carbohydrate, vitamin A, B1, B2, acid folic, carotenoids.\nCalcium Corbière: Calcium Corbière là thuốc chứa canxi và vitamin PP.\nVitamin B2: Vitamin B2, còn được biết đến với tên gọi Riboflavin natri phosphate, là một thành phần quan trọng trong nhiều nguồn thực phẩm và sản phẩm y tế. Vitamin B2 đóng vai trò trong quá trình chuyển hóa protein, chất béo và carbohydrate để tạo ra năng lượng cho cơ thể. Nó cũng giúp duy trì sức khỏe của mắt, cơ bắp và da. Ngoài ra, Vitamin B2 còn góp phần ngăn chặn sự phát triển của bệnh đục thủy tinh thể. \n\nVitamin B2 có mặt trong nhiều loại thực phẩm và sản phẩm như Appeton Lysine Syrup, hạt bạch biển đậu, cây bèo Nhật Bản, bụp giấm, kỷ tử, quả ổi, cây Hoàng Liên Ô Rô, cây Me đất, cây Ráy, thịt Cóc, thốt nốt, củ niễng, đông trùng hạ thảo, hải sâm, kê, khổ qua rừng, kim thất tai, cây lược vàng, mầm đậu nành, mía lau, mít, hạt mùi tàu, quả tươi, và nhụy hoa nghệ tây. Trong Appeton Lysine Syrup, Vitamin B2 không chỉ hỗ trợ chuyển hóa năng lượng và tổng hợp protein mà còn có thể tương tác với một số loại thuốc khác. Vitamin B2 cũng là một hợp chất hóa học cần thiết cho nhiều chức năng sinh lý của cơ thể, thể hiện tầm quan trọng của nó trong việc duy trì hoạt động bình thường của hệ thống cơ thể. Vitamin B2 cần thiết để giữ cho da, mắt, dây thần kinh và hồng cầu khỏe mạnh.\n\nNgoài ra, Vitamin B2 còn được tìm thấy trong quả Tầm Xuân, Thiên lý, lá trầu không, và củ tỏi tươi. Vitamin B2 cũng là thành phần hoạt chất trong thuốc B Complex C và là một trong những vitamin chính trong tỏi. Vitamin B2 không chỉ hỗ trợ chuyển hóa năng lượng và tổng hợp protein mà còn góp phần ngăn ngừa ung thư và giảm cholesterol xấu.\nCá Ngừ: Cá ngừ là nguồn cung cấp vitamin D.\nMầm Đậu Nành: Mầm đậu nành là nguồn cung cấp nội tiết tố nữ dồi dào từ thiên nhiên, chứa isoflavon có cấu trúc tương tự với estrogen.&lt;SEP&gt;Mầm đậu nành chứa vitamin B, folate và isoflavon, có tác dụng bảo vệ chống ung thư vú trên động vật thí nghiệm.&lt;SEP&gt;Mầm đậu nành có thể ăn sống hoặc chế biến với các thực phẩm khác như xào với thịt, nấu canh, làm lẩu, hoặc làm thành bột mầm đậu nành pha nước uống hay tinh chất mầm đậu nành.&lt;SEP&gt;Mầm đậu nành gồm một rễ với ba bộ phận: lá, mầm rễ, thân mầm. Thân mầm dài ra, khoảng 3-7 cm và là bộ phận chủ yếu được sử dụng.&lt;SEP&gt;Mầm đậu nành có thể làm giảm khó tiêu, đầy hơi và tiêu chảy nếu dùng vừa phải.\nCanxi - D Mekophar: Canxi - D Mekophar là thuốc chứa canxi và vitamin D.\nQuả Ổi: Quả Ổi mọng có nhiều hình dáng tùy giống, chủ yếu là hình trứng, hình quả lê, hình cầu. Đầu quả có vết sẹo hình tròn do lá đài để lại. Thường có màu xanh đậm khi còn non và chuyển xanh nhạt pha trắng khi về già. Mỗi quả có chứa rất nhiều hạt, màu hơi hung, hình thân, không đều. Quả vị chua ngọt hay ngọt và có mùi thơm đặc trưng.&lt;SEP&gt;Quả ổi có nhiều hình dáng, chủ yếu là hình trứng, hình quả lê, hình cầu. Đầu quả có vết sẹo hình tròn do lá đài để lại. Quả thường có màu xanh đậm khi còn non và chuyển xanh nhạt pha trắng khi về già. Quả chứa rất nhiều hạt màu hơi hung, hình thân, không đều. Quả vị chua ngọt hay ngọt và có mùi thơm đặc trưng. Quả có thể ăn tươi, làm mứt hay làm nước giải khát.&lt;SEP&gt;Quả Ổi là bộ phận của Cây Ổi được sử dụng làm thuốc.&lt;SEP&gt;Quả ổi được dùng trong bài thuốc giải độc ba đậu.&lt;SEP&gt;Quả ổi chứa pectin, vitamin C, tinh dầu với hàm lượng cao hơn trong lá.\nLiều Vitamin D: Liều vitamin D là lượng vitamin D cần thiết cho cơ thể.\nBạch Hạc: Bạch hạc là dược liệu thường được sử dụng để điều trị bệnh trong Đông y, đặc biệt hỗ trợ các bệnh về khớp, da liễu.&lt;SEP&gt;Bạch hạc là cây được sử dụng làm dược liệu, có đặc điểm là lá mọc đối, cuống dài khoảng 2 – 5mm, phiến hình trứng, mặt trên lá nhẵn, mặt dưới có lông mịn.&lt;SEP&gt;Bạch hạc là thảo dược dùng trong hỗ trợ điều trị đau nhức xương khớp.&lt;SEP&gt;Bạch hạc là vị thuốc cổ truyền được sử dụng từ lâu trong dân gian, hỗ trợ điều trị đau nhức xương khớp và lao phổi thời kỳ đầu.&lt;SEP&gt;Bạch hạc là vị thuốc giảm đau hiệu quả và có nhiều tác dụng y học hiện đại.&lt;SEP&gt;Bạch hạc là loài cây có tác dụng trị bệnh hiệu quả.&lt;SEP&gt;Bạch Hạc là thành phần gia thêm vào Cồn Bằng Lăng để tăng kết quả điều trị nấm ngoài da.\nVitamin D2: Vitamin D2, còn gọi là ergocalciferol, có vai trò làm tăng hấp thu canxi ở đường tiêu hóa và điều chỉnh loạn dưỡng xương do thận.&lt;SEP&gt;Vitamin D2, còn gọi là ergocalciferol, là vitamin được sử dụng để hỗ trợ hấp thu canxi.\nVitamines: Vitamines là hợp chất hóa học tìm thấy trong thân cây bạch hạc.\nVitamin Tan Trong Chất Béo: Vitamin tan trong chất béo bao gồm vitamin A, D, E, và K.\nHải Sâm: Hải sâm là loài động vật sống ở đáy biển, có khả năng tái sinh phần cơ thể bị mất.&lt;SEP&gt;Hải sâm là một món ăn từ biển ngon lành và bổ dưỡng, thuộc ngành động vật Da gai (Echinodermata). Nó là loại động vật biển thân mềm nhũn, dài trung bình khoảng 20cm.&lt;SEP&gt;Hải sâm là nguồn chứa các chất sinh học như lectin, saponin glucoside và các triterpene. Nó có khả năng chống ung thư, kháng khuẩn, cải thiện gan và tim mạch.&lt;SEP&gt;Hải sâm là loài động vật bậc thấp, được thu bắt trước mùa mưa để đảm bảo chất lượng. Hải sâm chứa nhiều thành phần dinh dưỡng như protein, các axit amin, yếu tố vi lượng, vitamin và các chất có hoạt tính sinh học.&lt;SEP&gt;Hải sâm là một vị thuốc rất bổ ích cho sức khỏe, nhưng không nên dùng cho những người đang bị tiêu chảy, lỵ, viêm đại tràng cấp tính, hoạt tinh, hoặc người có thể tạng đàm thấp (mập phì).&lt;SEP&gt;Hải sâm là vị thuốc tính ấm, vị mặn ngọt, không độc, giúp bổ thận tráng dương, bổ ích tinh tủy, giáng hỏa, điều hòa việc đi tiểu tiện, làm tiêu đờm dãi ứ đọng trong cơ thể, nhuận những chỗ khô ráo vón kết, chữa mọi chứng hư nhược cơ thể gầy còm ốm yếu, có tính sát trùng, chữa những chứng lở loét.\nCalcium Corbière Extra: Calcium Corbière Extra là thuốc chứa canxi.\nMật Ong: Mật ong là mật của con ong mật gốc châu Á hoặc châu Âu, thường được sử dụng trong thực phẩm và như một loại thuốc tự nhiên. Mật ong nổi tiếng với nhiều công dụng đa dạng, bao gồm khả năng kháng khuẩn, kháng nấm, chống ký sinh trùng, kháng viêm, và giúp chữa cảm cúm nhanh chóng và hiệu quả hơn. Nó cũng được sử dụng trong bài thuốc chữa âm hư và các vấn đề về sức khỏe miệng như loét mồm, viêm họng đỏ, mụn lở, sưng lợi và viêm chân răng có mủ.\n\nMật ong là thành phần chính trong thuốc Bảo Thanh Hoa Linh, một loại thuốc có tác dụng kháng khuẩn và hỗ trợ điều trị các bệnh lý như ho, viêm họng và viêm phế quản. Ngoài ra, mật ong còn được sử dụng để luyện viên thuốc, giúp giảm vị chua trong các hỗn hợp như rượu hoa bụp giấm và cải thiện hương vị của thuốc sắc. Nó còn được dùng để ngâm gừng tươi hoặc pha chế với nước nóng và chanh. Mật ong cũng được biết đến với khả năng trị và phòng viêm loét dạ dày, giúp tan đờm, dịu cảm giác khó chịu, và làm sạch răng miệng.\n\nNgoài việc điều trị các bệnh lý, mật ong còn được sử dụng trong nhiều bài thuốc khác. Nó là thành phần hỗ trợ trong bài thuốc điều trị tưa lưỡi ở trẻ em và cũng được sử dụng trong bài thuốc chữa chứng người bị lạnh, di tinh, hoạt tinh, đau lưng mỏi gối khi kết hợp với Thục địa và Cao ban long. Mật ong còn được sử dụng để trộn với nhựa cây Bồ Đề và luyện viên thuốc chữa sỏi thận, sỏi bàng quang. Mật ong cũng được sử dụng như nguyên liệu để làm thành viên với các vị thuốc khác, được hòa loãng bằng nước sôi, trộn đều với Tỳ Bà diệp thái sợi để điều chế Chích mật. Mật ong cũng được sử dụng để phủ lên cam thảo sống để tạo hương vị và hòa với các thành phần trong bài thuốc Thiên vương bổ tâm đan.\n\nMật ong được phối hợp với lá xạ hương khô để điều trị ho và viêm phế quản. Mật ong còn được sử dụng như một dung dịch phổ biến để ngâm tỏi và là thành phần trong bài thuốc điều trị kinh bổ huyết. Mật ong cũng được sử dụng trong các bài thuốc từ Hoa Bách Hợp và hoa đào. Mật ong có vị ngọt, tính bình, quy kinh Tâm Tỳ, Vị, Đại trường. Nó là một tác nhân có khả năng chống oxy hóa và nhiều đặc tính sinh học quan trọng khác. Mật ong cũng được sử dụng để ngâm đông trùng hạ thảo, tăng cường công dụng của cả hai thành phần này khi sử dụng cùng nhau.\n\nNgoài ra, mật ong còn được sử dụng trong bài thuốc chữa trĩ, lở loét, đại tiện xuất huyết. Mật ong được sử dụng như một thành phần trong bài thuốc dân gian. Mật ong được sử dụng kết hợp với rau bìm bìm nước để điều trị mụn nhọt. Mật ong cũng được sử dụng kết hợp với nước ép lá rau ngót để điều trị tưa lưỡi. Mật ong được sử dụng để tẩm sâm vũ diệp. Mật ong là nguyên liệu dùng để trộn với bột từ rễ sương sâm lông, bột gừng và hạt tiêu. Mật ong là một thành phần trong bài thuốc đại bổ huyết, ích thận tinh, bổ tiêu hóa.\n\nMật ong cũng được sử dụng như chất kết dính trong các bài thuốc bổ thận, ích tủy, sinh tinh, giúp tăng cường hiệu quả của các bài thuốc này. Ngoài ra, mật ong còn được sử dụng để điều trị táo bón và có thể sử dụng cùng CumarGold để nâng cao hiệu quả.&lt;SEP&gt;Mật ong có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Mật ong được pha với bột nghệ để tăng cường tác dụng.&lt;SEP&gt;Mật ong được sử dụng kết hợp với dịch chiết lá trầu không để tạo ra một loại thuốc bổ tốt.&lt;SEP&gt;Mật ong được sử dụng cùng với lá trầu trong các bài thuốc.&lt;SEP&gt;Mật ong có thể thêm vào trà đông trùng hạ thảo để dễ uống hơn.&lt;SEP&gt;Mật ong là một loại thực phẩm có thể ăn được khi bị trào ngược dạ dày thực quản.\nBạch Biển Đậu: Bạch biển đậu là một loại cây dây leo, sống từ 1-3 năm, với dây trưởng thành có thể dài tới 4-5 mét. Thân cây của nó có góc, hình trụ, màu xanh, nhỏ, bề mặt hơi có rãnh, và có lông thưa, dài và mềm. Cây này được trồng phổ biến tại nhiều tỉnh ở Việt Nam, đặc biệt là Tiền Giang, Bến Tre, Hậu Giang, An Giang, và Kiên Giang. Nó được sử dụng để lấy quả, hạt để ăn và hạt già dùng làm thuốc.\n\nBạch biển đậu được biết đến với nhiều tác dụng y tế. Nó được sử dụng để điều trị nhiều loại bệnh, bao gồm tiêu chảy, viêm dạ dày ruột cấp tính, ngộ độc rượu, độc thạch tín, độc cá nóc, và nhiều triệu chứng khác. Vị thuốc này có vị ngọt, tính hơi ấm, và được sử dụng trong nhiều bài thuốc khác nhau để điều trị các chứng bệnh như giải cảm nắng, khô khát họng, bổ tỳ vị hư yếu, ra huyết trắng ở phụ nữ, đau bụng, tiêu chảy, kiết lỵ, viêm dạ dày và ruột cấp tính, giải ngộ độc rượu, độc thạch tín, độc cá nóc, ngộ độc thức ăn mà sinh nôn mửa, hóc xương, yết hầu sưng đau, tiểu ra máu, và rắn cắn.\n\nNgoài ra, bạch biển đậu còn là một thành phần quan trọng trong bài thuốc Sâm linh bạch truật tán và một số bài thuốc khác. Nó đóng vai trò như một vị thuốc và món ăn quen thuộc, được sử dụng rộng rãi trong các bài thuốc hỗ trợ điều trị.\nCalci: Calci là một nguyên tố hóa học quan trọng, cần thiết cho sự phát triển và duy trì sức khỏe của xương. Nó đóng vai trò như một chất điện phân cần thiết, giúp xương trở nên chắc khỏe và phòng ngừa loãng xương. Calci là thành phần chính trong nhiều sản phẩm như Agi-Calci, Calcium Stada Vitamin D, và Davita Bone Sugar free, giúp duy trì sức khỏe xương và cải thiện khả năng hấp thụ của cơ thể nhờ vào Vitamin D3 trong Siro Appeton. Ngoài ra, Calci còn được tìm thấy trong thịt cóc và cây bèo Nhật Bản, chiếm khoảng 40,8mg%.\n\nCalci cũng được bổ sung cùng với vitamin D để phòng ngừa gãy xương lâm sàng ở những bệnh nhân đã từng bị gãy xương đùi do chấn thương nhẹ. Việc sử dụng Calci cần được cân nhắc kỹ lưỡng dựa trên tình trạng sức khỏe cụ thể của mỗi người vì nó có thể gây tăng độc tính đối với tim khi kết hợp với glycoside digitalis và có thể làm giảm nồng độ của các thuốc fluoroquinolon khi dùng cùng. Calci cũng có thể tương tác với các cation khác như magnesi, nhôm, sucralfat và các cation hóa trị 2 hoặc 3 như kẽm, sắt, có thể ảnh hưởng đến hấp thu acid nalidixic.\n\nCalci được xem là chất điện giải cần bổ sung khi dùng Betamethasone. Khi sử dụng betamethasone, Calci là khoáng chất cần bổ sung thêm vào cơ thể. Ngoài ra, Calci cũng là nguyên tố có thể gây nguy cơ kết tủa với Ceftriaxone tại thận và phổi ở trẻ sơ sinh. Calci là nguyên tố hóa học, thường được bổ sung trong điều trị.\n\nCalci cũng là thành phần trong thuốc D-Cure, tăng nồng độ trong máu và nước tiểu khi dùng quá liều. Calci có thể làm giảm khả năng hấp thu sắt trong cơ thể khi uống cùng với Avisure Safoli. Khi uống cùng với Avisure Safoli, Calci có thể tương tác với sắt, làm giảm khả năng hấp thu của cả hai dưỡng chất.&lt;SEP&gt;Calci là một trong những chất bị giảm hấp thu khi dùng neomycin.&lt;SEP&gt;Calci được bổ sung để phòng ngừa tiền sản giật.&lt;SEP&gt;Calci là nguyên tố hóa học có thể ảnh hưởng đến hấp thu của Ciprofloxacin.\nBuồn Nôn - Calcigenol: Calcigenol có thể gây buồn nôn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây buồn nôn do tăng canxi huyết.\nCalcium Stada Vitamin D - Vitamin D: Calcium Stada Vitamin D chứa vitamin D.\nCalcium Corbière - Đái Tháo Đường: Calcium Corbière cần quan tâm lượng đường trong thuốc.\nKê - Vitamin B2: Kê chứa nhiều vitamin B2.\nCalcigenol - Chóng Mặt: Calcigenol có thể gây chóng mặt nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây chóng mặt do tăng canxi huyết.\nMầm Đậu Nành - Vitamin B2: Mầm đậu nành chứa vitamin B2.\nCalcigenol - Táo Bón: Calcigenol có thể gây táo bón nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây táo bón do tăng canxi huyết.\nQuả Ổi - Vitamin B2: Quả ổi chứa vitamin B2.\nCalcigenol - Đau Đầu: Calcigenol có thể gây đau đầu nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây đau đầu do tăng canxi huyết.\nBạch Hạc - Vitamines: Bạch hạc chứa vitamines.\nCalcigenol - Thận: Calcigenol có thể gây tổn thương thận nếu sử dụng không đúng cách.\nHải Sâm - Vitamin B2: Hải sâm chứa vitamin B2.\nCalcigenol - Suy Thận: Calcigenol cần thận trọng khi dùng cho người suy thận.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người suy thận do có thể tăng canxi huyết.\nMật Ong - Vitamin B2: Vitamin B2 là một trong những vitamin có trong mật ong.&lt;SEP&gt;Vitamin B2 là một trong số các vitamin giàu trong mật ong.\nCalcigenol - Đau Bụng: Calcigenol có thể gây đau bụng nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây đau bụng do tăng canxi huyết.\nBạch Biển Đậu - Vitamin B2: Hạt Bạch biển đậu chứa vitamin B2.\nCalcigenol - Mệt Mỏi: Calcigenol có thể gây mệt mỏi nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây mệt mỏi do tăng canxi huyết.\nCalci - Calcium Stada Vitamin D: Calcium Stada Vitamin D chứa calci.\nCalcigenol - Nôn: Calcigenol có thể gây nôn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây nôn do tăng canxi huyết.\nTang Diệp - Vitamin D: Tang diệp chứa vitamin D.\nCalcium Corbière - Suy Thận: Calcium Corbière cần thận trọng khi sử dụng cho người có suy thận.&lt;SEP&gt;Calcium Corbière không nên sử dụng cho người có suy thận.\nCalcigenol - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng khi dùng Calcigenol.\nCalcium Corbière - Suy Tim: Calcium Corbière không nên sử dụng cho người có suy tim.\nCalcigenol - Canxi: Calcigenol chứa canxi làm tăng mức canxi trong máu.\nCalcigenol - Phụ Nữ Cho Con Bú: Phụ nữ cho con bú cần thận trọng khi dùng Calcigenol.\nCanxi - Canxi - D Mekophar: Canxi là thành phần chính trong thuốc Calci - D Mekophar.\nCalcigenol - Loãng Xương: Calcigenol được dùng để ngăn ngừa và điều trị loãng xương.\nCalcigenol - Sỏi Thận: Calcigenol chống chỉ định dùng cho người bị sỏi thận.&lt;SEP&gt;Calcigenol có thể gây sỏi thận nếu sử dụng không đúng cách.\nCalcigenol - Khô Miệng: Calcigenol có thể gây khô miệng nếu sử dụng không đúng cách.\nCalcigenol - Phát Ban: Calcigenol có thể gây phát ban nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây phát ban do tăng canxi huyết.\nCalcigenol - Đau Cơ: Calcigenol có thể gây đau cơ do tăng canxi huyết.\nCanxi - D Mekophar - Loãng Xương: Canxi - D Mekophar chống chỉ định ở người bị loãng xương.\nCalcium Corbière - Sỏi Thận: Calcium Corbière cần thận trọng khi sử dụng cho người có sỏi thận.\nCalcigenol - Xơ Vữa Động Mạch: Calcigenol cần thận trọng khi dùng cho người mắc xơ vữa động mạch.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người xơ vữa động mạch do có thể tăng canxi huyết.\nCalcigenol - Chán Ăn: Calcigenol có thể gây chán ăn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây chán ăn do tăng canxi huyết.\nCanxi - D Mekophar - Sỏi Thận: Canxi - D Mekophar chống chỉ định ở người bị sỏi thận.\nCalcigenol - Tăng Canxi Máu: Calcigenol chống chỉ định dùng cho người bị tăng canxi máu.&lt;SEP&gt;Calcigenol có thể gây tăng canxi máu nếu sử dụng quá liều.\nCalcigenol - Ù Tai: Calcigenol có thể gây ù tai nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây ù tai do tăng canxi huyết.\nAdrenalin - Calcium Corbière: Calcium Corbière không nên sử dụng cho người đang dùng adrenalin.\nCalcigenol - Yếu Cơ: Calcigenol có thể gây yếu cơ nếu sử dụng không đúng cách.\nCalcigenol - Vitamin D: Calcigenol chứa vitamin D làm tăng mức vitamin D trong cơ thể.&lt;SEP&gt;Calcigenol chứa vitamin D, cần thận trọng khi dùng cho người suy thận, bệnh tim, hoặc xơ vữa động mạch.&lt;SEP&gt;Calcigenol chứa vitamin D, có thể gây tăng canxi huyết nếu sử dụng quá liều.\nCalcigenol - Glucocorticoid: Calcigenol được sử dụng để điều trị loãng xương do glucocorticoid.\nCalcigenol - Người Cao Tuổi: Calcigenol được sử dụng để ngăn ngừa gãy xương do loãng xương ở người cao tuổi.\nCalcigenol - Tăng Canxi Huyết: Calcigenol cần thận trọng khi dùng cho người có tăng canxi huyết.&lt;SEP&gt;Calcigenol có thể gây tăng canxi huyết nếu sử dụng quá liều.\nBệnh Tim - Calcigenol: Calcigenol cần thận trọng khi dùng cho người mắc bệnh tim.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người bệnh tim do có thể tăng canxi huyết.\nCalcigenol - Loạn Nhịp Tim: Calcigenol cần thận trọng khi dùng cho người đang dùng glycosid trợ tim.&lt;SEP&gt;Calcigenol có thể gây loạn nhịp tim ở người đang dùng glycosid trợ tim.\nCalcigenol - Ngủ Gà: Calcigenol có thể gây ngủ gà nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây ngủ gà do tăng canxi huyết.\nCalcium Corbière - Tăng Canxi Máu: Calcium Corbière có thể gây tăng canxi máu trong một số trường hợp.\nCalcigenol - Suy Thận Mạn: Calcigenol được sử dụng để điều trị loạn dưỡng xương do suy thận mạn.\nCalcigenol - Người Lớn: Người lớn cần theo dõi khi trẻ em sử dụng Calcigenol.\nCalcigenol - Tổn Thương Thận: Calcigenol có thể gây tổn thương thận nếu sử dụng không đúng cách.\nChất Béo - Vitamin Tan Trong Chất Béo: Chất béo giúp tăng hấp thụ vitamin tan trong chất béo.\nCalcigenol - Phospho: Calcigenol chứa phospho làm tăng mức phospho trong máu.\nCalcigenol - Tá Dược: Calcigenol chứa tá dược để tạo ra dạng thuốc phù hợp.\nCalcigenol - Còi Xương: Calcigenol được sử dụng để điều trị và phòng ngừa còi xương.\nCalcigenol - Đau Xương: Calcigenol có thể gây đau xương do tăng canxi huyết.\nCalcigenol - Cơ: Calcigenol có thể gây yếu cơ nếu sử dụng không đúng cách.\nCanxi - D Mekophar - Tăng Canxi Huyết: Canxi - D Mekophar có thể gây tăng canxi huyết.\nCalcigenol - Thiếu Canxi: Calcigenol được sử dụng để phòng ngừa và hỗ trợ điều trị thiếu canxi.\nCalcigenol - Thiếu Vitamin D: Calcigenol được sử dụng để điều trị và phòng ngừa thiếu vitamin D.\nCalcigenol - Giảm Trương Lực Cơ: Calcigenol có thể gây giảm trương lực cơ do tăng canxi huyết.\nCalcigenol - Thời Kỳ Mãn Kinh: Calcigenol được sử dụng để điều trị và phòng ngừa loãng xương ở phụ nữ thời kỳ mãn kinh.\nCalcigenol - Vị Kim Loại: Calcigenol có thể gây vị kim loại do tăng canxi huyết.\nCalcigenol - PTH: Calcigenol giúp giảm nồng độ PTH trong máu.\nCá Ngừ - Vitamin D: Cá ngừ là nguồn cung cấp vitamin D.\nCalcigenol - Tăng Canxi Niệu: Calcigenol chống chỉ định dùng cho người bị tăng canxi niệu.\nCalcigenol - Phụ Huynh: Phụ huynh cần theo dõi khi trẻ em sử dụng Calcigenol.\nCalcigenol - Chứng Co Giật: Calcigenol được sử dụng để điều trị chứng co giật do giảm canxi máu.\nCalcigenol - Phản Ứng Phụ: Khi sử dụng Calcigenol, nếu có bất kỳ phản ứng phụ nào thì nên liên hệ cơ sở y tế để được điều trị hợp lý.\nCalcigenol - Dương Thị Kim Ngân: Dược sĩ Dương Thị Kim Ngân hy vọng bài viết này đã cung cấp những thông tin cơ bản nhất về Calcigenol cho bạn đọc.\nCalcigenol - Glycosid Trợ Tim: Calcigenol có thể gây loạn nhịp tim ở người đang dùng glycosid trợ tim.\nCalcigenol - Vitamin D2: Calcigenol bao gồm vitamin D2 để tăng hấp thu canxi.&lt;SEP&gt;Calcigenol chứa Vitamin D2 làm thành phần chính.\nCalcigenol - Quá Liều Vitamin D: Calcigenol có thể gây quá liều vitamin D nếu sử dụng không đúng cách.\nCalcigenol - Tricanxi Photphat: Calcigenol chứa Tricanxi photphat làm thành phần chính.\nCalci Milk - D - Calcigenol: Calci Milk - D là thuốc chứa thành phần tương tự Calcigenol.\nCalcigenol - Khô Mồm: Calcigenol có thể gây khô mồm do tăng canxi huyết.\nCalcigenol - Mất Phối Hợp Động Tác: Calcigenol có thể gây mất phối hợp động tác do tăng canxi huyết.\nCalcigenol - Dược Sĩ Dương Thị Kim Ngân: Dược sĩ Dương Thị Kim Ngân đã viết bài viết này cung cấp thông tin cơ bản về Calcigenol.\nCalcigenol - Canxi Photphat: Calcigenol bao gồm canxi photphat để bổ sung canxi.\nCalcigenol - Giảm Canxi Máu: Calcigenol được sử dụng để điều trị chứng giảm canxi máu.\nCalcigenol - Người Nằm Viện: Calcigenol được sử dụng để ngăn ngừa gãy xương do loãng xương ở người nằm viện.\nCalcigenol - Người Suy Thận Mạn: Calcigenol được sử dụng để điều trị loạn dưỡng xương do thận ở người suy thận mạn.\nCalcigenol - Người Dùng Glucocorticoid: Calcigenol được sử dụng để điều trị loãng xương do glucocorticoid ở người dùng glucocorticoid.\nCalcigenol - Vôi Hóa Thận: Calcigenol có thể gây vôi hóa thận nếu sử dụng không đúng cách.\nCalcigenol - Có Vị Kim Loại: Calcigenol có thể gây có vị kim loại nếu sử dụng không đúng cách.\nCalcigenol - Co Giật Do Giảm Canxi Huyết: Calcigenol được sử dụng để hỗ trợ điều trị co giật do giảm canxi huyết.\nCalcigenol - Calciumgeral: Calciumgeral là thuốc chứa thành phần tương tự Calcigenol.\nCalcigenol - Mẫn Cảm Với Vitamin D2: Calcigenol chống chỉ định dùng cho người bị mẫn cảm với vitamin D2.\nBệnh Gút - Calcium Corbière: Calcium Corbière cần thận trọng khi sử dụng cho người có bệnh gút.\nDầu Bơ - Vitamin Tan Trong Chất Béo: Dầu bơ giúp hấp thụ tốt hơn các vitamin tan trong chất béo như vitamin A, D, E, và K.\nBệnh Gút - Calcium Corbière Extra: Calcium Corbière Extra cần thận trọng khi sử dụng cho người có bệnh gút.\nCalcium Corbière - Vitamin PP: Calcium Corbière chứa vitamin PP.\nBệnh Gan Nặng - Calcium Corbière: Calcium Corbière không nên sử dụng cho người có bệnh gan nặng.\nCalcium Corbière - Hạ Huyết Áp Nặng: Calcium Corbière không nên sử dụng cho người có hạ huyết áp nặng.\nCanxi - D Mekophar - Vitamin D3: Vitamin D3 là thành phần chính trong thuốc Calci - D Mekophar.\nCalcium Corbière - Tăng Canxi Niệu: Calcium Corbière có thể gây tăng canxi niệu trong một số trường hợp.\nCalcium Corbière - Loét Dạ Dày Tiến Triển: Calcium Corbière không nên sử dụng cho người có loét dạ dày tiến triển.\nAcid Oxalic - Canxi - D Mekophar: Canxi - D Mekophar tương tác với acid oxalic.\nCalcium Corbière - Viêm Khớp Do Gút: Calcium Corbière cần thận trọng khi sử dụng cho người có viêm khớp do gút.\nCanxi - D Mekophar - Thiếu Canxi: Canxi - D Mekophar điều trị thiếu canxi ở phụ nữ mang thai.\nCalcium Corbière - Dư Galactose Trong Máu: Calcium Corbière không nên sử dụng cho người có dư galactose trong máu.\nCalcium Corbière - Sử Dụng Quá Liều Vitamin D: Calcium Corbière không nên sử dụng cho người sử dụng quá liều vitamin D.\nCalcium Corbière - Thuốc Digitalis: Calcium Corbière không nên sử dụng cho người đang dùng thuốc digitalis.\nCalcium Corbière - Xuất Huyết Động Mạch: Calcium Corbière không nên sử dụng cho người có xuất huyết động mạch.\nBệnh Túi Mật - Calcium Corbière: Calcium Corbière cần thận trọng khi sử dụng cho người có bệnh túi mật.\nCalcium Corbière - U Ác Tính Phá Huỷ Xương: Calcium Corbière không nên sử dụng cho người có u ác tính phá hủy xương.\nCalcium Corbière - Galactosemia: Calcium Corbière không nên sử dụng cho người có bệnh galactosemia.\nCalcium Corbière - Tăng Nhẹ Canxi Niệu: Calcium Corbière cần thận trọng khi sử dụng cho người có tăng nhẹ canxi niệu.\nCalcium Corbière - Tiền Sử Loét Dạ Dày: Calcium Corbière cần thận trọng khi sử dụng cho người có tiền sử loét dạ dày.\nCalcium Corbière - Tiền Sử Có Vàng Da Hoặc Bệnh Gan: Calcium Corbière cần thận trọng khi sử dụng cho người có tiền sử có vàng da hoặc bệnh gan.\nCalcium Corbière - Liều Vitamin D: Calcium Corbière cần quan tâm liều vitamin D nếu có vitamin D trong các thuốc khác.\nAcid Phytic - Canxi - D Mekophar: Canxi - D Mekophar tương tác với acid phytic.\nCanxi - D Mekophar - U Tủy: Canxi - D Mekophar chống chỉ định ở người mắc u tủy.\nCanxi - D Mekophar - Quá Liều Vitamin D: Canxi - D Mekophar chống chỉ định ở người mắc quá liều vitamin D.\nCanxi - D Mekophar - Canxi Huyết: Canxi - D Mekophar có thể làm tăng canxi huyết.\nCanxi - D Mekophar - U Xương Di Căn: Canxi - D Mekophar chống chỉ định ở người mắc u xương di căn.\nBệnh U Xương Ác Tính - Canxi - D Mekophar: Canxi - D Mekophar chống chỉ định ở người mắc bệnh u xương ác tính.\nCanxi - D Mekophar - Suy Thận Nghiêm Trọng: Canxi - D Mekophar chống chỉ định ở người mắc suy thận nghiêm trọng.\nCanxi - D Mekophar - Thiếu Vitamin D3: Canxi - D Mekophar điều trị thiếu vitamin D3 ở phụ nữ mang thai.\nCanxi - D Mekophar - Thực Phẩm Có Acid Oxalic: Canxi - D Mekophar tương tác với thực phẩm có acid oxalic.\nCanxi - D Mekophar - Thực Phẩm Có Acid Phytic: Canxi - D Mekophar tương tác với thực phẩm có acid phytic.\nThiếu Canxi - Vitamin D2: Vitamin D2 hỗ trợ hấp thu canxi, giúp phòng ngừa thiếu canxi.\nCalcium Corbière Extra - Viêm Khớp Do Gút: Calcium Corbière Extra cần thận trọng khi sử dụng cho người có viêm khớp do gút.']</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa 72,000 UI (International Units) của Vitamin D2.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa 72000UI Vitamin D2.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8070504835658935</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4517626208664733</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>['Rửa Tay: Rửa Tay là một biện pháp vệ sinh cá nhân quan trọng, được thực hiện trước khi ăn uống, sau khi đi vệ sinh, và trước khi sử dụng thuốc như Comozol. Rửa Tay bằng nước và xà phòng không chỉ giúp làm sạch bàn tay mà còn đóng vai trò quan trọng trong việc ngăn chặn sự lây lan của vi khuẩn và các bệnh truyền nhiễm khác. Việc rửa tay thường xuyên bằng xà phòng có thể giúp phòng ngừa các bệnh hô hấp và tiêu hóa, như quai bị và báng bụng. Đây là một biện pháp phòng ngừa hiệu quả giúp duy trì sức khỏe và vệ sinh cá nhân.\n\nRửa Tay cũng là phương pháp đơn giản và hiệu quả để ngăn ngừa bệnh truyền nhiễm. Nó giúp phòng ngừa đau họng bằng cách loại bỏ các tác nhân gây bệnh. Khi chế biến thức ăn, trước khi ăn và sau khi vệ sinh, rửa tay là phương pháp đơn giản nhưng rất có hiệu quả trong việc phòng ngừa nhiễm ký sinh trùng. Ngoài ra, rửa tay cũng là biện pháp phòng ngừa để giảm nguy cơ lây nhiễm các bệnh đường hô hấp trên.\n\nRửa Tay cũng đóng vai trò quan trọng trong việc ngăn ngừa nhiễm trùng đường tiêu hóa. Nó giúp ngăn chặn sự lây lan của vi khuẩn gây nhiễm trùng đường ruột và thậm chí là biện pháp giúp phòng ngừa và điều trị nhiễm trùng đường ruột.&lt;SEP&gt;Rửa tay thường xuyên và đúng cách, đặc biệt sau khi trẻ đi vệ sinh hoặc sau khi hắt hơi, ho.&lt;SEP&gt;Rửa tay thường xuyên với nước ấm và xà phòng, đặc biệt là trước khi ăn hoặc khi chế biến thức ăn.&lt;SEP&gt;Rửa tay là quá trình vệ sinh trước và sau khi sử dụng thuốc âm đạo.&lt;SEP&gt;Rửa tay kỹ là biện pháp giúp ngăn ngừa lây lan bệnh.&lt;SEP&gt;Rửa tay thường xuyên bằng xà phòng và nước ấm giúp giảm nguy cơ mắc hoặc lây lan các bệnh nhiễm trùng.&lt;SEP&gt;Rửa tay thường xuyên để tránh nhiễm trùng.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nTrẻ Em Và Thiếu Niên: Trẻ em và thiếu niên không khuyến cáo dùng Combigan.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nVệ Sinh Bàn Tay: Vệ sinh bàn tay là việc làm quan trọng để ngăn ngừa vi khuẩn.\nGăng Tay: Găng tay là phương tiện phòng hộ cá nhân khi chăm sóc bệnh nhân cảm cúm.&lt;SEP&gt;Găng tay được sử dụng để bảo vệ bàn tay khỏi hóa chất và các chất bẩn.\nThuốc Bôi Âm Đạo: Thuốc bôi âm đạo được sử dụng để điều trị tình trạng âm đạo.\nDung Dịch Vệ Sinh Tay Nhanh: Dung dịch vệ sinh tay nhanh là sản phẩm dùng để vệ sinh tay nhằm giảm nguy cơ mắc đau họng.\nViệc Sử Dụng Sai Lầm: Việc sử dụng sai là hành vi sử dụng thuốc không đúng cách hoặc không tuân theo hướng dẫn.\nAcid Hydrochlorid: Acid hydrochlorid là tá dược trong thuốc nhỏ mắt Combigan.\nÝ Kiến Thầy Thuốc: Ý kiến thầy thuốc là lời khuyên từ chuyên gia y tế về việc sử dụng thuốc.\nNatri Hydroxid: Natri hydroxid là tá dược trong thuốc nhỏ mắt Combigan.\nBệnh Nhân: Bệnh nhân là một cá nhân đang mắc phải nhiều loại bệnh khác nhau và cần được chăm sóc y tế. Bệnh nhân có tiền sử bệnh và gia đình cũng có lịch sử về bệnh tật. Người này đang mắc bệnh giả u não và cần được điều trị. Ngoài ra, bệnh nhân cũng được điều trị bằng các bài thuốc truyền thống.\n\nBệnh nhân còn mắc phải chứng sợ khoảng rộng (agoraphobia) và các rối loạn liên quan. Điều này cho thấy bệnh nhân đang đối mặt với nhiều vấn đề sức khỏe tâm thần. Bệnh nhân cũng có triệu chứng loạn thần, bao gồm hoang tưởng, ảo giác, lời nói không mạch lạc hoặc vô nghĩa và hành vi không phù hợp với tình huống.\n\nNgoài những vấn đề về sức khỏe tâm thần, bệnh nhân cũng gặp phải một số vấn đề về thể chất. Bệnh nhân đã bị đứt dây chằng đầu gối, một tình trạng gây đau đớn và hạn chế khả năng di chuyển. Đồng thời, bệnh nhân cũng bị nghi ngờ mắc mụn rộp sinh dục và cần tới gặp bác sĩ để được điều trị kịp thời.\n\nĐể đảm bảo vệ sinh cá nhân, bệnh nhân cần được tắm rửa sạch sẽ bằng xà phòng, rửa sạch hết các vảy da và lau khô người. Việc giữ gìn vệ sinh cá nhân là rất quan trọng đối với sức khỏe tổng thể của bệnh nhân.&lt;SEP&gt;Bệnh nhân là người sử dụng kem Biafine.&lt;SEP&gt;Bệnh nhân là người mắc suy thận mạn tính và cần được điều trị.&lt;SEP&gt;Bệnh nhân là người mắc suy tim trái và có các triệu chứng liên quan.&lt;SEP&gt;Bệnh nhân cần quan tâm đến việc thuốc Amiodarone được đào thải chậm ra khỏi cơ thể sau khi đã ngừng thuốc.&lt;SEP&gt;Bệnh nhân cần thông báo ngay cho bác sĩ, dược sĩ hoặc khoa cấp cứu gần nhất nếu uống quá liều thuốc Bifril.&lt;SEP&gt;Bệnh nhân là người bị chấn thương cần được sơ cứu.\nViêm Mũi, Khô Mũi, Khô Miệng: Viêm mũi, khô mũi, khô miệng là tác dụng phụ có thể gặp khi sử dụng Combigan.\nHậu Quả Không Mong Muốn: Hậu quả không mong muốn là những kết quả tiêu cực có thể xảy ra nếu người bệnh không sử dụng thuốc đúng cách.\nTiệt Khuẩn Tay: Tiệt khuẩn tay là quy trình sử dụng Betadine để diệt khuẩn tay trước khi tiến hành các hoạt động y tế.&lt;SEP&gt;Tiệt khuẩn tay là phương pháp dùng Betadine để vệ sinh và sát khuẩn tay trước khi phẫu thuật.\nNgười Bệnh: Người bệnh cần có sự thăm khám, kê đơn của y bác sĩ để sử dụng bán chi liên một cách hiệu quả nhất.&lt;SEP&gt;Người bệnh là đối tượng cần tham khảo ý kiến từ thầy thuốc để sử dụng thuốc đúng cách.&lt;SEP&gt;Người bệnh rối loạn nhân cách phụ thuộc thường cần sự yên tâm khi đưa ra quyết định và chịu đựng sự lạm dụng từ người khác.&lt;SEP&gt;Người bệnh là đối tượng mắc phải các loại sỏi mật khác nhau.&lt;SEP&gt;Người bệnh là đối tượng sử dụng thuốc Chymobest.&lt;SEP&gt;Người bệnh cần được nghỉ ngơi và theo dõi chặt chẽ.\nTăng Sinh Nang Bạch Huyết Kết Mạc: Tăng sinh nang bạch huyết kết mạc là tác dụng phụ có thể gặp khi sử dụng Combigan.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nTrẻ: Trẻ là đối tượng dễ mắc bệnh cúm do có hệ miễn dịch chưa hoàn thiện.&lt;SEP&gt;Trẻ là đối tượng sử dụng thuốc clotrimazole.\nSử Dụng: Sử dụng cúc tần cần thận trọng và tham khảo ý kiến bác sĩ.\nTùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc mà không tham khảo ý kiến chuyên gia.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nSức Khỏe: Sức khỏe là trạng thái tổng thể của cơ thể, bao gồm cả thể chất, tinh thần và xã hội. Trạng thái này được đánh giá qua các chỉ số như BMI và vòng eo, cũng như thông qua chế độ ăn uống và tập luyện. Sức khỏe cũng liên quan đến tình trạng huyết áp và có thể bị ảnh hưởng bởi tình trạng mất trí nhớ thoáng qua. \n\nĐể nâng cao sức khỏe, việc sử dụng các vị thuốc như Bồ đề, bạc hà, cây hoa cút lợn, cây Đước, Trường sinh thảo, và đông trùng hạ thảo ngâm mật ong được xem là phương pháp hiệu quả. Những vị thuốc này giúp tránh các tương tác có hại và cải thiện tình trạng tổng thể của cơ thể. Sức khỏe không chỉ là trạng thái tổng thể về thể chất mà còn bao gồm cả tinh thần và xã hội của con người. Nó được đề cập trong bài thuốc cổ truyền và cần được bảo vệ thông qua các thói quen sinh hoạt lành mạnh. Việc sử dụng lá Thường xuân cũng được biết đến với khả năng cải thiện sức khỏe. Ngoài ra, sức khỏe còn được coi là trạng thái tổng thể về thể chất và tinh thần, được ảnh hưởng bởi việc sử dụng Hoàng Nàn và bổ sung DHEA.\n\nSức khỏe cũng là yếu tố ảnh hưởng đến lượng protein cần thiết trong chế độ ăn uống, nhấn mạnh tầm quan trọng của việc duy trì một chế độ ăn uống cân bằng và hợp lý để nâng cao và duy trì sức khỏe tổng thể. Tình trạng sức khỏe cần được theo dõi cẩn thận khi sử dụng thuốc Aspegic, một yếu tố được điều trị bởi Aspegic. \n\nNgoài ra, cần lưu ý rằng có một tạp chí y tế tên là "Sức khỏe", nhưng đây không phải là định nghĩa chính cho thuật ngữ sức khỏe trong ngữ cảnh này.&lt;SEP&gt;Sức khỏe là trạng thái tổng thể của cơ thể và tâm trí, có thể được cải thiện thông qua việc sử dụng tinh dầu hoa cam.&lt;SEP&gt;Sức khỏe được cải thiện nhờ tác dụng của tinh dầu quế.&lt;SEP&gt;Sức khỏe được cải thiện nhờ việc ăn tỏi mỗi ngày.&lt;SEP&gt;Sức khỏe được cải thiện thông qua việc sử dụng vị thuốc đúng cách.&lt;SEP&gt;Sức khỏe được tăng cường nhờ bài thuốc ngâm trái quách.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nRửa Tay - Tiêu Chảy: Rửa tay thường xuyên bằng xà phòng và nước ấm giúp giảm nguy cơ mắc hoặc lây lan các bệnh tiêu chảy.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nRửa Tay - Thiếu Máu: Rửa tay thường xuyên giúp kiểm soát bệnh thiếu máu.\nRửa Tay - Thuốc Bôi Âm Đạo: Rửa tay trước và sau khi sử dụng thuốc bôi âm đạo.\nVi Khuẩn - Vệ Sinh Bàn Tay: Vệ sinh bàn tay ngăn ngừa sự phát triển của vi khuẩn.\nViệc Sử Dụng Sai Lầm - Ý Kiến Thầy Thuốc: Tham khảo ý kiến thầy thuốc có thể giúp phòng ngừa việc sử dụng thuốc sai cách.\nQuai Bị - Rửa Tay: Rửa tay bằng nước và xà phòng thường xuyên là biện pháp phòng ngừa lây nhiễm quai bị.\nBệnh Nhân - Thuốc: Bệnh nhân cần sử dụng thuốc đúng giờ và đúng liều.\nRửa Tay - Đau Họng: Rửa tay là phương pháp phòng ngừa đau họng.\nHậu Quả Không Mong Muốn - Người Bệnh: Người bệnh cần tránh hậu quả không mong muốn bằng cách sử dụng thuốc đúng cách.\nBetadine - Tiệt Khuẩn Tay: Betadine được chỉ định để tiệt khuẩn tay trước khi tiến hành các hoạt động y tế.&lt;SEP&gt;Betadine được chỉ định để tiệt khuẩn tay trước khi phẫu thuật.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nDung Dịch Vệ Sinh Tay Nhanh - Đau Họng: Dung dịch vệ sinh tay nhanh là sản phẩm dùng để phòng ngừa đau họng.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nBệnh Tay Chân Miệng - Rửa Tay: Rửa tay thường xuyên và đúng cách giúp phòng ngừa bệnh tay chân miệng.\nSử Dụng - Tùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc.\nBệnh - Rửa Tay: Rửa tay kỹ là biện pháp giúp ngăn ngừa lây lan bệnh.\nHướng Dẫn - Sức Khỏe: Hướng dẫn của bác sĩ giúp đảm bảo an toàn cho sức khỏe khi sử dụng dược liệu.\nNhiễm Trùng Đường Ruột - Rửa Tay: Rửa tay giúp ngăn chặn sự lây lan của vi khuẩn gây nhiễm trùng đường ruột.&lt;SEP&gt;Rửa tay kỹ càng giúp phòng ngừa và điều trị nhiễm trùng đường ruột.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nHội Chứng Rối Loạn Sinh Tủy - Rửa Tay: Rửa tay thường xuyên giúp phòng ngừa và ngăn chặn sự lây lan của hội chứng rối loạn sinh tủy.\nPhế Quản - Rửa Tay: Thường xuyên rửa tay bằng xà phòng để bảo vệ phế quản.\nBáng Bụng - Rửa Tay: Rửa tay giúp phòng ngừa báng bụng.\nNhiễm Ký Sinh Trùng - Rửa Tay: Rửa tay khi chế biến, khi ăn, sau khi vệ sinh là phương pháp đơn giản nhưng rất có hiệu quả trong phòng ngừa nhiễm ký sinh trùng.\nNhiễm Trùng Đường Hô Hấp Trên - Rửa Tay: Rửa tay là biện pháp phòng ngừa để giảm nguy cơ lây nhiễm các bệnh đường hô hấp trên.\nCombigan - Trẻ Em Và Thiếu Niên: Combigan không được khuyến cáo dùng cho trẻ em và thiếu niên.\nCombigan - Viêm Mũi, Khô Mũi, Khô Miệng: Viêm mũi, khô mũi, khô miệng là tác dụng phụ có thể gặp khi sử dụng Combigan.\nCombigan - Tăng Sinh Nang Bạch Huyết Kết Mạc: Tăng sinh nang bạch huyết kết mạc là tác dụng phụ có thể gặp khi sử dụng Combigan.\nComozol - Rửa Tay: Rửa tay là bước tiền điều trị khi sử dụng Comozol.&lt;SEP&gt;Rửa tay trước khi sử dụng Comozol.\nBàn Tay - Rửa Tay: Rửa tay giúp bảo vệ bàn tay khỏi tác nhân gây hại.\nHệ Hô Hấp - Rửa Tay: Rửa tay bằng xà phòng là biện pháp vệ sinh cá nhân giúp ngăn chặn sự lây lan của vi khuẩn.\nBàn Tay - Găng Tay: Găng tay bảo vệ bàn tay khỏi hóa chất và các chất bẩn.\nDịch Bệnh - Rửa Tay: Rửa tay là biện pháp phòng ngừa bệnh truyền nhiễm.\nNước Rửa Tay - Rửa Tay: Nước rửa tay chứa ít nhất 60 độ cồn giúp ngăn ngừa bệnh truyền nhiễm.\nGăng Tay - Tiếp Xúc Với Người Bệnh: Găng tay là phương tiện phòng hộ khi tiếp xúc với người bệnh.']</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rửa tay trước khi sử dụng thuốc là một bước quan trọng để đảm bảo vệ sinh và ngăn chặn sự lây lan của vi khuẩn. Đối với thuốc nhỏ mắt như Combigan, việc rửa tay trước khi sử dụng là cần thiết để tránh mang vi khuẩn từ tay vào mắt, nơi có thể dễ dàng bị nhiễm trùng.
+Để sử dụng Combigan một cách an toàn và hiệu quả, bạn nên:
+- Rửa tay kỹ bằng xà phòng và nước ấm trước khi nhỏ thuốc vào mắt.
+- Tránh để đầu nhỏ giọt chạm vào bất kỳ bề mặt nào để không làm nhiễm khuẩn thuốc.
+- Nếu cần dùng nhiều hơn một loại thuốc nhỏ mắt, đợi ít nhất 5 phút trước khi sử dụng các thuốc khác mà bác sĩ kê đơn.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Có, bạn cần rửa sạch tay trước khi sử dụng thuốc Combigan để tránh nhiễm trùng mắt.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7814910681758147</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8203727670189537</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>['Tai Biến Mạch Não: Tai biến mạch não là tình trạng rối loạn tuần hoàn máu não.&lt;SEP&gt;Tai biến mạch não là một trong những bệnh lý mà thuốc An Cung Ngưu Hoàng Hoàn được sử dụng.&lt;SEP&gt;Tai biến mạch não là triệu chứng xuất hiện khi phình động mạch chủ ngực chèn ép vào mạch cảnh.\nAn Cung Ngưu Hoàng Hoàn: An Cung Ngưu Hoàng Hoàn là thuốc quý trong y học cổ truyền, có tác dụng cấp cứu hữu hiệu.&lt;SEP&gt;An Cung Ngưu Hoàng Hoàn là thuốc được sử dụng để điều trị các tình trạng như viêm não, viêm màng não, tai biến mạch não và các triệu chứng liên quan như sốt cao, huyết áp tăng.&lt;SEP&gt;An Cung Ngưu Hoàng Hoàn là thuốc được phát triển bởi Công ty TNHH Dược phẩm Diên An, chứa nhiều thành phần thảo dược và dưỡng chất.&lt;SEP&gt;An Cung Ngưu Hoàng Hoàn giúp ôn nhiệt bệnh, hạ sốt, nhưng không phải là thần dược chữa được mọi trường hợp đột quỵ.&lt;SEP&gt;An Cung Ngưu Hoàng Hoàn là thuốc được sử dụng trong điều trị tai biến mạch máu não, nhưng có chống chỉ định và thận trọng trong một số trường hợp cụ thể.&lt;SEP&gt;An cung ngưu hoàng hoàn là bài thuốc điều trị tai biến có thành phần từ Ngưu hoàng.\nTai Biến Xuất Huyết Não Diện Rộng: Tai biến xuất huyết não diện rộng là tình trạng chống chỉ định sử dụng An Cung Ngưu Hoàng Hoàn.\nTai Biến Mạch Máu Não: Tai biến mạch máu não là một tình trạng sức khỏe khẩn cấp liên quan đến hệ thống mạch máu não, thường xuất hiện do rối loạn tuần hoàn máu não hoặc sự hình thành cục máu đông đột ngột trong động mạch cung cấp máu cho não. Bệnh lý này có thể dẫn đến nhiều hậu quả nghiêm trọng như sa sút trí tuệ và tăng nguy cơ sa sút trí tuệ. Tai biến mạch máu não cũng được biết đến là một biến chứng nghiêm trọng của huyết áp không ổn định, tăng huyết áp trong thai kỳ, và là một trong các tình trạng nhiễm khuẩn ít gặp.\n\nTriệu chứng của tai biến mạch máu não bao gồm méo miệng, yếu hoặc tê ở tay, và khó khăn trong việc nói. Bệnh lý này có thể xảy ra khi dòng máu tới não bị chặn hoặc bị chảy máu, gây tổn thương tế bào não. Tai biến mạch máu não là nguyên nhân chính gây tử vong cho người bệnh sa sút trí tuệ và là một tình trạng y học gây tử vong và tàn tật.\n\nTai biến mạch máu não được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng thảo dược như Bạch cương tàm và quả Bạch tật lê sắc thành thuốc, cũng như sử dụng thuốc hiện đại như Cebrex và Cebraton. Ngoài ra, tai biến mạch máu não còn được hỗ trợ khắc phục di chứng bằng nấm lim xanh và nụ hoa tam thất giúp phòng ngừa biến chứng này. Thuốc bổ thần kinh H5000 cũng được sử dụng để giảm nhẹ và điều trị tai biến mạch máu não.\n\nNgoài ra, tai biến mạch máu não cũng là tác dụng phụ hiếm gặp khi sử dụng Celecoxib. Bệnh lý này có thể được phòng ngừa bằng Aspirin 81 ở những người có tiền sử thoáng mất não (TIA).\n\nTai biến mạch máu não là một tình trạng nghiêm trọng cần được phát hiện và điều trị kịp thời để giảm thiểu hậu quả và ngăn chặn tình trạng tái phát.&lt;SEP&gt;Tai biến mạch máu não là tình trạng nghiêm trọng cần tránh khi sử dụng Cialis.&lt;SEP&gt;Tai biến mạch máu não là triệu chứng trong vòng 6 tháng gần đây không được chỉ định dùng thuốc Cialis.\nRối Loạn Trên Mạch Máu: Rối loạn trên mạch máu liên quan đến viêm mạch, đột quỵ.\nThương Tổn Hệ Thần Kinh: Thương tổn hệ thần kinh bao gồm bệnh não tăng huyết áp, tai biến mạch máu não, chảy máu nội sọ.\nĐột Quỵ: Đột quỵ, còn được gọi là tai biến mạch máu não, là một tình trạng y học nghiêm trọng xảy ra khi não bị thiếu nguồn cung cấp máu đột ngột, thường do tắc nghẽn hoặc vỡ của mạch máu não. Đây là một tình trạng sức khỏe khẩn cấp và nghiêm trọng, có thể dẫn đến tử vong cao và di chứng nặng nề. Đột quỵ không chỉ là bệnh lý não mà còn liên quan đến các vấn đề về tim mạch và có thể là nguyên nhân gây ra bệnh động kinh thùy thái dương và thùy trán. Nguyên nhân của đột quỵ rất đa dạng, bao gồm tăng huyết áp, bệnh tim Ebstein, bệnh bụi phổi, bệnh cơ tim phì đại, chứng aldosterone nguyên phát, tình trạng béo phì, và nhiều yếu tố khác. Đột quỵ cũng có thể xảy ra do cục máu đông di chuyển đến động mạch não và gây tắc nghẽn. Tình trạng này diễn tiến rất nhanh và thường để lại nhiều di chứng trầm trọng.\n\nQuản lý và điều trị đột quỵ đòi hỏi sự chăm sóc y tế chuyên nghiệp và điều trị tích cực, bao gồm việc phục hồi chức năng sau khi xảy ra tình trạng này. Đột quỵ cũng được biết đến như một tình trạng bệnh tim mạch có thể được ngăn chặn bằng Telmisartan. Đột quỵ cũng có thể gây ra cơn động kinh toàn thể và là tình trạng cấp cứu liên quan đến não, bao gồm cả xuất huyết dưới nhện và rối loạn tuần hoàn não cấp tính. Đột quỵ có thể gây đau dây thần kinh sinh ba và là chống chỉ định cho Crinone, và nó có thể xảy ra do cục máu đông. Đột quỵ cũng là một trong những rối loạn tim mạch được cải thiện nhờ củ lùn, và cũng được ngăn chặn bởi Perindopril Erbumine trong Coperil Plus. Bệnh này cũng được hỗ trợ điều trị bằng củ nén và Đan sâm, và được xác định là bệnh liên quan đến yếu tố gây ra bởi cholesterol LDL.\n\nĐột quỵ cũng có thể được dự phòng và điều trị dự phòng bằng aspirin, cụ thể là Aspirin STELLA và Aspirin Vidipha. Tuy nhiên, Adagrin không nên được sử dụng trong điều trị đột quỵ. Đột quỵ cũng là bệnh tim mạch được ngăn ngừa bởi Bisoprolol và được điều trị bằng Furosemide trong trường hợp do huyết áp cao gây ra. Đột quỵ cũng được coi là biến chứng nguy hiểm của huyết áp không ổn định và cần thận trọng khi sử dụng Atocib. Đột quỵ cũng được đề cập trong phần về chất chống oxy hóa. Đột quỵ còn có thể gây nhiễu loạn cảm xúc và hậu quả của phì đại thất trái, cũng như gây bất lực. Đột quỵ là tình trạng thiếu máu não cấp tính, có thể được gây ra bởi rối loạn lipid máu, và cũng là tình trạng xảy ra khi huyết khối di chuyển đến động mạch não và gây tắc mạch. Đột quỵ cũng có thể gây ra run và là nguyên nhân có thể gây ra rung nhĩ. Đột quỵ là biến chứng nghiêm trọng của bệnh rung nhĩ và là bệnh cần được phòng ngừa bằng thuốc chống đông.\n\nĐột quỵ cũng có thể xảy ra do tình trạng tăng huyết áp ác tính, bệnh tăng huyết áp vô căn, và có thể gây ra táo bón. Đột quỵ là một tình trạng cấp cứu liên quan đến thiếu máu não và có thể là nguyên nhân gây tê lưỡi. Đột quỵ là nguyên nhân phổ biến gây thương tật cao, thậm chí là tử vong cho bệnh nhân, ảnh hưởng nhiều tới chất lượng cuộc sống người bệnh. Đột quỵ cũng được điều trị và dự phòng bằng Aspegic, Rosuvastatin, và Crestor.&lt;SEP&gt;Đột quỵ là một trong những nguyên nhân gây tổn thương thùy đỉnh.&lt;SEP&gt;Đột quỵ có thể gây tổn thương cho thùy trán.&lt;SEP&gt;Đột quỵ là nguyên nhân gây tổn thương cho thùy trán.&lt;SEP&gt;Đột quỵ là bệnh lý có thể gây bất động và là yếu tố nguy cơ thuyên tắc tĩnh mạch sâu.&lt;SEP&gt;Đột quỵ là biến chứng của tiền đái tháo đường nếu không được điều trị.&lt;SEP&gt;Turmerone hỗ trợ trong việc cải thiện các tình trạng sau đột quỵ.\nThiếu Oxy Não: Thiếu oxy não là triệu chứng của các bệnh như thiếu máu não, đột quỵ.\nTai Bién Máu Máu Não: Tai biến mạch máu não bao gồm tình trạng xuất huyết não.\nViêm Màng Não: Viêm màng não là tình trạng bệnh lý liên quan đến hệ thống màng não, bao gồm màng bao quanh não và tủy sống. Bệnh này thường do vi khuẩn hoặc virus gây ra và có thể dẫn đến các biến chứng nghiêm trọng như bệnh động kinh thùy thái dương, bệnh giang mai, biến chứng sau phẫu thuật điều trị bệnh khổng lồ, biến chứng của bệnh lậu ở trẻ sơ sinh, và triệu chứng của bệnh Lyme. Viêm màng não cũng có thể gây ra các triệu chứng như buồn nôn, cứng cổ, rối loạn tâm thần, co giật, tê hoặc khó nói.\n\nViệc phát hiện viêm màng não thường được thực hiện thông qua các xét nghiệm y tế, bao gồm cả siêu âm tim để xác định tình trạng bệnh lý. Việc điều trị viêm màng não thường sử dụng nhiều loại thuốc khác nhau, bao gồm penicillin kết hợp với erythromycin, ampicillin, và ampicillin Mekophar. Trong một số trường hợp, thuốc An Cung Ngưu Hoàng Hoàn cũng được sử dụng. Điều trị kịp thời và chính xác là rất quan trọng để ngăn chặn các biến chứng nghiêm trọng và đảm bảo phục hồi hoàn toàn.\n\nViêm màng não cần được phân biệt với các bệnh lý khác như quai bị để tránh nhầm lẫn trong quá trình chẩn đoán và điều trị. Ngoài ra, viêm màng não cũng có thể là biến chứng của viêm tai giữa và một số trẻ sơ sinh có thể tiến triển viêm màng não. Bệnh viêm màng não được xem là một trong những bệnh tiềm ẩn nghiêm trọng, đòi hỏi sự chú ý và can thiệp y tế kịp thời để hạn chế các hậu quả tiêu cực.\n\nViêm màng não cũng được điều trị bằng Hoàng Bá và Clorocid. Bệnh này là một bệnh nhiễm khuẩn do Haemophilus influenzae, không nên dùng Chloramphenicol làm thuốc chọn lựa đầu tiên. Viêm màng não là bệnh nhiễm trùng được tiêm phòng để phòng ngừa và có thể làm ảnh hưởng đến ốc tai. Viêm màng não cũng có thể là biến chứng nặng nề có thể xảy ra nếu vi khuẩn vào trong máu. Viêm màng não còn có thể là biến chứng thần kinh do nấm Cryptococcosis gây ra.&lt;SEP&gt;Viêm màng não là bệnh gây viêm màng não.\nMạch Máu Não Bị Tắc Nghẽn: Mạch máu não bị tắc nghẽn là triệu chứng của nhồi máu não.\nViêm Não: Viêm Não là bệnh lý về não gây ra bởi các tác nhân như virus, vi khuẩn, và ký sinh trùng. Đây là một bệnh nhiễm trùng ảnh hưởng đến não, gây ra hiện tượng viêm trong não. Viêm Não có thể dẫn đến nhiều biến chứng nghiêm trọng, bao gồm cả bệnh động kinh thùy thái dương, biến chứng từ bệnh lậu ở trẻ sơ sinh, hội chứng Parkinson, và các vấn đề liên quan đến tổn thương não như bệnh tay chân miệng. Bệnh này cũng được biết đến như một dạng nhiễm trùng tại não, gây ra tình trạng viêm màng não.\n\nViệc chẩn đoán Viêm Não thường được thực hiện thông qua các phương pháp y tế như siêu âm tim. Bệnh này cần được phân biệt với quai bị để tránh nhầm lẫn trong quá trình điều trị. Các triệu chứng phổ biến của Viêm Não bao gồm buồn nôn, cứng cổ, rối loạn tâm thần, co giật, tê hoặc khó nói, và trong một số trường hợp, nó có thể gây ra triệu chứng hoang tưởng.\n\nViêm Não có thể là biến chứng của bệnh cúm, sốt thung lũng, sốt xuất huyết, và thủy đậu ở người bị suy giảm miễn dịch. Nó cũng có thể là biến chứng nặng nề có thể xảy ra nếu vi khuẩn vào trong máu. Viêm Não được xem là nguyên nhân gây bệnh teo não và các biến chứng thần kinh khác.\n\nĐiều trị Viêm Não thường bao gồm việc sử dụng thuốc như An Cung Ngưu Hoàng Hoàn, cùng với các loại dược liệu truyền thống như cây Ba chạc, rau má, đơn buốt và cúc chỉ thiên. Việc sử dụng các loại thuốc và dược liệu này giúp giảm nhẹ triệu chứng và hỗ trợ quá trình hồi phục của bệnh nhân. Ngoài ra, Viêm Não cũng được điều trị bằng thuốc kháng virus, đặc biệt là acyclovir truyền tĩnh mạch trong trường hợp biến chứng nghiêm trọng của thủy đậu.&lt;SEP&gt;Viêm não là bệnh do muỗi Culex gây ra.&lt;SEP&gt;Viêm não là bệnh theo mùa do muỗi Aedes aegypti và Culex quinquefasciatus gây ra.&lt;SEP&gt;Việc kích hoạt microglia là dấu hiệu báo trước của bệnh lý thuộc não bộ.\nỔ Đột Quỵ: Ổ đột quỵ là vùng não bị tổn thương do thiếu máu.\nHàn Bế: Hàn bế là tình trạng có các dấu hiệu như hôn mê, da môi tái nhợt, chân tay lạnh, mồ hôi, lơ mơ, hạn chế hoạt động, lưỡi trắng nhớt.\nHuyết Khối Tim Mạch: Huyết khối tim mạch như nhồi máu cơ tim hoặc đột quỵ là một rối loạn mạch máu.\nChống Co Giật: Chống co giật là một thuật ngữ mô tả khả năng giảm thiểu tình trạng co giật thông qua việc sử dụng các loại thuốc hoặc thảo dược cụ thể. Tác dụng này có thể được tìm thấy trong nhiều thành phần khác nhau như An Cung Ngưu Hoàng Hoàn, ngưu hoàng, muối HgSe trong Chu sa, đại hồi, hắc sâm, và lá hoa sen. Trong đó, An Cung Ngưu Hoàng Hoàn được biết đến với tác dụng chống co giật nhờ vào thành phần ngưu hoàng của nó. Ngoài ra, muối HgSe trong Chu sa cũng được ghi nhận có tác dụng chống co giật. Đại hồi và hắc sâm đều được sử dụng để tạo ra các phương pháp điều trị chống co giật. Cuối cùng, lá hoa sen cũng được biết đến với tác dụng chống co giật.&lt;SEP&gt;Chống co giật là tác dụng của ngưu hoàng.&lt;SEP&gt;Chống co giật là phương pháp điều trị động kinh và các tình trạng liên quan.&lt;SEP&gt;Chống co giật là tác dụng của tinh dầu.&lt;SEP&gt;Chống co giật là tác dụng của việc sử dụng tinh dầu hoa cam.\nĐột Quỵ Não: Đột quỵ não là tình trạng thiếu máu não cục bộ có thể gây ra triệu chứng hoang tưởng.&lt;SEP&gt;Đột quỵ não là tình trạng cấp cứu y tế nghiêm trọng, gây ra bởi sự gián đoạn lưu thông máu đến não.&lt;SEP&gt;Đột quỵ não là tình trạng thiếu máu não cấp tính, liên quan chặt chẽ với rối loạn lipid máu.&lt;SEP&gt;Đột quỵ não là triệu chứng nghiêm trọng của bệnh nhân rung nhĩ, ảnh hưởng đến chất lượng cuộc sống.\nSốt: Sốt là tình trạng tăng nhiệt độ cơ thể, thường được coi là sốt khi thân nhiệt đạt hoặc vượt quá 38°C. Đây là một phản ứng của hệ miễn dịch nhằm chống lại các tác nhân gây sốt, thường là dấu hiệu đầu tiên cho thấy cơ thể đang gặp vấn đề. Sốt có thể xuất hiện như một triệu chứng của nhiều bệnh khác nhau, bao gồm bệnh viêm khớp dạng thấp, sỏi thận, sỏi đường niệu, bệnh bạch cầu cấp, bệnh Crohn, bệnh dại (tiền triệu), bệnh giang mai giai đoạn 2, bệnh Lyme, bệnh Brucellosis, bệnh Pemphigus, bệnh phóng xạ cấp tính và do nhiễm phóng xạ, bệnh quai bị, bệnh Thalassemia, bệnh viêm mạch và đa u hạt dị ứng, và bệnh viêm xung huyết dạ dày. Nó cũng là tác dụng phụ thường gặp khi sử dụng nhiều loại thuốc như Amikacin Bidiphar, Aminoplasmal 10%, Amiparen 5 Otsuka, AT Desloratadin ở trẻ em, ibuprofen syrup, Acecyst, Aclasta, Acyclovir Stada 200 mg, Acyclovir Stella 400 mg, và Acyclovir Stella 800 mg.\n\nSốt cũng là một trong những triệu chứng của bệnh cúm, bệnh bạch hầu, bệnh tay chân miệng, bệnh lý do liên cầu nhóm B gây ra ở trẻ sơ sinh, và bệnh nhiệt miệng. Việc điều trị sốt cần dựa trên nguyên nhân gốc rễ gây ra tình trạng này, từ việc sử dụng thuốc hạ sốt đến các phương pháp điều trị khác tùy thuộc vào nguyên nhân cụ thể gây ra sốt. Sốt cũng là triệu chứng của nhiễm khuẩn huyết, cảm lạnh, viêm xoang, viêm họng, và nhiễm trùng đường hô hấp trên. Nó cũng là triệu chứng điển hình của nhiễm trùng thận, với nhiệt độ đo trên 38°C, có thể lên đến 39 đến 40°C.\n\nNgoài ra, sốt còn là triệu chứng thường gặp của bệnh sốt rét, sốt thung lũng, viêm họng do liên cầu khuẩn và sốt thấp khớp. Sốt cũng là triệu chứng đầu tiên và phổ biến nhất của sốt xuất huyết. Nó có thể là một triệu chứng cần được lưu ý, đôi khi đi kèm với triệu chứng khác như đau một bên hông, nôn mửa, cảm thấy rất khát nước, và cần gặp bác sĩ. Sốt cũng là một triệu chứng của viêm lưỡi gà.\n\nSốt cũng có thể xảy ra trước tình trạng sốc trong suy thượng thận cấp. Nó cũng là triệu chứng của tắc ruột, có thể bắt đầu từ sốt nhẹ do mất nước và tiến triển thành sốt do độc tố vi khuẩn. Ngoài ra, sốt còn là triệu chứng được điều trị bằng tai chua. Sốt cũng là một trong các triệu chứng của tăng bạch cầu đơn nhân nhiễm khuẩn và là triệu chứng nhiệt độ cơ thể tăng cao. Cuối cùng, sốt là một triệu chứng có thể đi kèm với tê bì tay chân và là yếu tố gây ra bệnh và chống chỉ định sử dụng thạch hộc.\n\nTrong Đông y, sốt được điều trị bằng Thài lài trắng, Thành ngạnh, vỏ rễ và vỏ thân Thanh táo. Sốt cũng là một trong những bệnh được điều trị bằng Thông đỏ. Sốt cũng là triệu chứng cần báo cáo bác sĩ trước khi dùng Amoksiklav và Aspegic, cũng như Aspirin trong giai đoạn đầu của bệnh Kawasaki.\n\nSốt là tác dụng phụ thường gặp khi sử dụng Advil và thuốc xịt mũi Aladka. Sốt cũng là biểu hiện của quá liều mạn tính của thuốc. Sốt là triệu chứng của nhiều bệnh, bao gồm cả viêm họng, ho sốt. Sốt là triệu chứng của bệnh cảm mạo được điều trị bằng bài thuốc Sâm tô ẩm. Sốt là triệu chứng khi bị tiểu buốt có mủ. Sốt là triệu chứng có thể xảy ra khi trẻ bị tiêu chảy. Sốt kéo dài hơn 3 ngày là triệu chứng cần chú ý khi trẻ bị tiêu chảy. Sốt là triệu chứng thường gặp khi trẻ bị tiêu chảy do dùng kháng sinh hoặc nhiễm siêu vi, vi khuẩn, ký sinh trùng.\n\nTình trạng sốt cần được xử lý y tế ngay lập tức vì nó là triệu chứng của nhiễm trùng đường tiêu hóa trên. Sốt cũng là một trong những triệu chứng được điều trị bằng tinh dầu húng chanh. Sốt cũng là triệu chứng của viêm tinh hoàn. Sốt là triệu chứng được điều trị bằng Tía tô. Sốt được chữa bằng bài thuốc từ Tô diệp, Nhân sâm, Trần bì và các thảo dược khác. Sốt là triệu chứng liên quan đến cảm lạnh, nhức đầu, và đau các khớp xương. Sốt có thể là một trong những triệu chứng của u nang buồng trứng bị vỡ. Sốt là triệu chứng có thể kèm theo đau bụng dưới.\n\nTri Mẫu được dùng để chữa sốt, đặc biệt sốt do viêm phổi.&lt;SEP&gt;Sốt là nguyên nhân gây mất nước.\nAn tức hương: An tức hương có tác dụng kháng vi nấm, kháng sinh, ức chế sự phát triển của Escherichia coli, bảo vệ thần kinh, giảm tỷ lệ nhồi máu não.\nNhồi Máu Não: Nhồi máu não, còn được gọi là đột quỵ do thiếu máu não, là một tình trạng y tế nghiêm trọng xảy ra khi một phần não bị thiếu máu do tắc nghẽn động mạch. Đây là dạng tai biến mạch máu não nghiêm trọng, chiếm khoảng 25% tổng số trường hợp đột quỵ. Tình trạng này thường biểu hiện qua các triệu chứng như đột quỵ và có thể là một biến chứng nghiêm trọng của tăng huyết áp. \n\nNhồi máu não xảy ra khi có sự tắc nghẽn ở động mạch não, dẫn đến việc não không nhận được đủ máu để duy trì chức năng bình thường. Các nguyên nhân gây ra tình trạng này bao gồm việc hình thành huyết khối trong hệ thống tuần hoàn, mảng xơ vữa, hoặc tắc động mạch thân nền hoàn toàn. Ngoài ra, nhồi máu não cũng có thể xuất hiện do tình trạng suy thượng thận thứ phát hoặc tăng huyết áp cấp cứu.\n\nTrong quá trình điều trị, nhồi máu não thường được quản lý thông qua việc sử dụng thuốc như Aspirin trong phác đồ trị liệu ban đầu. Tuy nhiên, người bệnh cần tránh sử dụng một số loại thuốc khác như Cerecaps. Nghiên cứu đã chỉ ra rằng đương quy có tác dụng giảm kích thước của tổn thương não, trong khi hà thủ ô có thể giúp ngăn chặn sự phát triển của bệnh. \n\nTóm lại, nhồi máu não là một tình trạng y tế nghiêm trọng đòi hỏi sự chăm sóc y tế kịp thời và đúng cách.\nViêm Não Nhật Bản B: Viêm não Nhật Bản B là một trong những bệnh lý mà thuốc An Cung Ngưu Hoàng Hoàn được sử dụng.\nAmlodipin - Rối Loạn Trên Mạch Máu: Amlodipin gây ra rối loạn trên mạch máu như viêm mạch, đột quỵ.\nAn Cung Ngưu Hoàng Hoàn - Tai Biến Mạch Máu Não: An Cung Ngưu Hoàng Hoàn không thể dùng cho tất cả các trường hợp tai biến mạch máu não.\nPerindopril - Rối Loạn Trên Mạch Máu: Perindopril gây ra rối loạn trên mạch máu như viêm mạch, đột quỵ.\nAn Cung Ngưu Hoàng Hoàn - Tai Biến Xuất Huyết Não Diện Rộng: An Cung Ngưu Hoàng Hoàn chống chỉ định ở bệnh nhân tai biến xuất huyết não diện rộng.\nHuyết Khối Tim Mạch - Mạch Máu: Huyết khối tim mạch như nhồi máu cơ tim hoặc đột quỵ là một rối loạn mạch máu.\nAn Cung Ngưu Hoàng Hoàn - Đột Quỵ: An Cung Ngưu Hoàng Hoàn không thể dùng cho tất cả các trường hợp đột quỵ.\nThiếu Máu Não - Thiếu Oxy Não: Thiếu oxy não là triệu chứng của thiếu máu não.\nAn Cung Ngưu Hoàng Hoàn - Tai Biến Mạch Não: An Cung Ngưu Hoàng Hoàn được sử dụng để điều trị tai biến mạch não.&lt;SEP&gt;Thuốc An Cung Ngưu Hoàng Hoàn được sử dụng trong điều trị tai biến mạch não.\nRối Loạn Lipid Máu - Đột Quỵ Não: Rối loạn lipid máu liên quan chặt chẽ với biến cố đột quỵ não.\nAn Cung Ngưu Hoàng Hoàn - Viêm Màng Não: An Cung Ngưu Hoàng Hoàn được sử dụng để điều trị viêm màng não.&lt;SEP&gt;Thuốc An Cung Ngưu Hoàng Hoàn được sử dụng trong điều trị viêm màng não.\nHương Thảo - Đột Quỵ Não: Chiết xuất Hương Thảo có tác dụng bảo vệ thần kinh ở động vật bị thiếu máu cục bộ não.\nAn Cung Ngưu Hoàng Hoàn - Viêm Não: An Cung Ngưu Hoàng Hoàn được sử dụng để điều trị viêm não.&lt;SEP&gt;Thuốc An Cung Ngưu Hoàng Hoàn được sử dụng trong điều trị viêm não.\nAn Cung Ngưu Hoàng Hoàn - Hàn Bế: An Cung Ngưu Hoàng Hoàn chống chỉ định ở người có tình trạng hàn bế.\nChống Co Giật - Sốt: Thuốc An Cung Ngưu Hoàng Hoàn có tác dụng chống co giật trong trường hợp sốt cao.\nThương Tổn Hệ Thần Kinh - Tăng Huyết Áp Cấp Cứu: Tăng huyết áp cấp cứu gây thương tổn hệ thần kinh.\nAn tức hương - Nhồi Máu Não: An tức hương được dùng để điều trị nhồi máu não.\nSa Sút Trí Tuệ Do Mạch Máu - Ổ Đột Quỵ: Ổ đột quỵ là nguyên nhân gây ra sa sút trí tuệ do mạch máu.\nAn Cung Ngưu Hoàng Hoàn - Viêm Não Nhật Bản B: Thuốc An Cung Ngưu Hoàng Hoàn được sử dụng trong điều trị viêm não Nhật Bản B.\nThuốc Chống Đông - Đột Quỵ Não: Thuốc chống đông được sử dụng để dự phòng đột quỵ não.\nTai Bién Máu Máu Não - Xuất Huyết Não: Tai biến mạch máu não bao gồm tình trạng xuất huyết não.\nMạch Máu Não Bị Tắc Nghẽn - Nhồi Máu Não: Mạch máu não bị tắc nghẽn là triệu chứng của nhồi máu não.\nTổn Thương Não - Đột Quỵ Não: Tổn thương não có thể bao gồm đột quỵ não.\nPhình Động Mạch Chủ Ngực - Tai Biến Mạch Não: Tai biến mạch não là triệu chứng xuất hiện khi phình động mạch chủ ngực chèn ép vào mạch cảnh.\nKhám Mắt - Thương Tổn Hệ Thần Kinh: Khám mắt giúp phát hiện thương tổn hệ thần kinh.\nĐột Quỵ Não - Đột Quỵ Xuất Huyết: Đột quỵ xuất huyết là một loại hình của đột quỵ não, gây ra bởi sự vỡ mạch máu trong não.']</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Thuốc **An Cung Ngưu Hoàng Hoàn** có thể được sử dụng trong điều trị một số tình trạng đột quỵ hoặc tai biến mạch máu não, nhưng không thể dùng cho tất cả các trường hợp. Thuốc này được sử dụng để điều trị các triệu chứng sốt cao, huyết áp tăng, và tình trạng hôn mê do đàm nhiệt ủng bế tâm khiếu. 
+Tuy nhiên, An Cung Ngưu Hoàng Hoàn không thể dùng cho tất cả các trường hợp đột quỵ hay tai biến mạch máu não. Đặc biệt, thuốc này chống chỉ định ở những bệnh nhân bị tai biến xuất huyết não diện rộng, chảy máu nhiều, hoặc người có tình trạng hàn bế.
+### Các trường hợp được chỉ định sử dụng:
+- **Viêm não, viêm màng não**: Thuốc này được sử dụng để điều trị viêm não, viêm màng não, đặc biệt là trong giai đoạn cấp tính.
+- **Tai biến mạch não**: Thuốc được sử dụng để điều trị tai biến mạch não (tai biến mạch não là tình trạng rối loạn tuần hoàn máu não).
+### Các trường hợp chống chỉ định sử dụng:
+- **Tai biến xuất huyết não diện rộng**: Thuốc không nên được sử dụng cho những bệnh nhân bị tai biến xuất huyết não diện rộng.
+- **Chứng hàn bế**: Thuốc chống chỉ định ở những người có tình trạng hàn bế, thể hàn, dương hư, tỳ vị hư hàn, suy giảm chức năng gan thận.
+### Lưu ý khi sử dụng:
+- Khi sử dụng thuốc, cần tuân thủ chỉ định của bác sĩ và không được tự ý sử dụng thuốc.
+- Cần tuân thủ hướng dẫn về cách dùng, liều dùng và cách bảo quản thuốc để đảm bảo an toàn và hiệu quả điều trị.
+### Kết luận:
+An Cung Ngưu Hoàng Hoàn có thể được sử dụng trong điều trị một số tình trạng đột quỵ hoặc tai biến mạch máu não, nhưng cần tuân thủ chặt chẽ chỉ định của bác sĩ và tránh sử dụng cho những trường hợp chống chỉ định.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Không thể dùng cho tất cả các trường hợp đột quỵ hay tai biến mạch máu não, việc dùng thuốc cần được chỉ định và theo dõi của chuyên gia y tế.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8274002570320862</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.8526833975663549</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>['Avelox: Avelox là thương hiệu của thuốc kháng sinh moxifloxacin.&lt;SEP&gt;Avelox là thương hiệu của thuốc moxifloxacin.&lt;SEP&gt;Avelox là tên thương mại của thuốc moxifloxacin.\nThuốc Chẹn Beta: Thuốc chẹn beta là một loại thuốc được sử dụng trong việc điều trị bệnh tim mạch và tăng huyết áp. Thuốc này hoạt động bằng cách ức chế thụ thể beta-adrenergic, giúp kiểm soát phản ứng của cơ thể đối với căng thẳng và tăng huyết áp. Nó làm giảm nhịp tim và huyết áp, từ đó giúp kiểm soát các vấn đề liên quan đến tim mạch. Thuốc chẹn beta bao gồm nhiều loại thuốc khác nhau như Carvedilol, Metoprolol, Propranolol, Bisoprolol, và Acebutolol. Mỗi loại thuốc có thể có tác dụng phụ khác nhau, bao gồm khả năng gây ra liệt dương và ác mộng. Thuốc chẹn beta không chỉ giúp kiểm soát tăng huyết áp mà còn có thể giúp giảm run ở một số người. \n\nThuốc chẹn beta có thể tương tác với một số loại thuốc khác như Amaryl 1 mg và Carbimazol, đồng thời cũng tương tác với aspirin 81. Ngoài ra, nó cũng có thể làm giảm tác dụng hạ đường huyết của một số loại thuốc khác. Tuy nhiên, cần lưu ý rằng thuốc chẹn beta cũng có thể tăng nguy cơ mắc bệnh BPH (tăng kích thước tuyến tiền liệt lành tính).\n\nThuốc chẹn beta là một trong những loại thuốc hạ huyết áp phổ biến, thường được sử dụng để điều trị bệnh tim mạch và tăng huyết áp.&lt;SEP&gt;Thuốc chẹn beta là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Sử dụng thuốc chẹn beta trong điều trị bệnh tim mạch có thể làm tăng nguy cơ mắc phì đại lành tính tuyến tiền liệt.\nThuốc Chống Loạn Nhịp Tim: Thuốc chống loạn nhịp tim là loại thuốc có thể tương tác với moxifloxacin.\nTim Mạch: Tim mạch là hệ thống cơ quan gồm tim và mạch máu chịu trách nhiệm tuần hoàn máu khắp cơ thể. Đây không chỉ là một hệ thống cơ quan đơn thuần mà còn là một đối tượng cần được theo dõi chặt chẽ khi sử dụng nhiều loại thuốc khác nhau, bao gồm Atropine, Domperidone, Agietoxib gst, Fexofenadine, Amlor 5 của Pfizer, Atelec, Artrodar, Austriol Mebiphar, Atorhasan 20, Atorpa-E, và nhiều loại thuốc khác. Hệ thống tim mạch chịu ảnh hưởng từ việc hút thuốc lá, tình trạng béo phì, và sử dụng bạc hà. Bệnh nhân tim mạch cũng có thể gặp biến cố khi sử dụng Belara. Tim mạch còn có thể bị ảnh hưởng bởi chứng aldosterone nguyên phát và bệnh thận đa nang. Bệnh tim mạch có thể xảy ra do độ pH cơ thể bị quá axit và tăng axit dạ dày. Estrogen duy trì sự đàn hồi của mạch máu, giảm nguy cơ mắc các bệnh lý tim mạch do xơ vữa.\n\nHệ thống tim mạch liên quan đến bệnh tăng huyết áp, suy tim, bệnh mạch vành, và biến chứng đái tháo đường. Nó cũng chịu ảnh hưởng từ việc sử dụng các loại thuốc như Celecoxib, dầu bơ, dầu hạt cải, dầu hạnh nhân, và đậu mèo. Tim mạch cũng chịu ảnh hưởng từ việc sử dụng các loại thảo dược như Rau đắng đất, Biển súc, Ginkgo biloba, Biginol, Bisoplus, trà Bụp giấm, và dịch chiết từ dền cơm. Các thảo dược này có thể giúp cải thiện tình trạng tim mạch và bảo vệ hệ thống tim mạch khỏi biến cố tim mạch và bệnh tật.\n\nTim mạch cần được kiểm tra trước khi sử dụng Cadifast 120 và các loại thuốc khác. Hệ thống này cũng chịu ảnh hưởng từ việc kéo dài khoảng QT và bị ảnh hưởng bởi hút thuốc lá và cholesterol xấu. Tim mạch chịu ảnh hưởng tích cực từ Hắc sâm, giúp tăng lưu lượng máu và hạ huyết áp. Hệ thống tim mạch cũng chịu ảnh hưởng tích cực từ hạt Bo Bo, cải thiện tình trạng xơ vữa mạch máu và tăng độ đàn hồi mạch máu. Tim mạch cũng chịu ảnh hưởng từ các yếu tố nguy cơ chính như xơ vữa động mạch, tăng huyết áp mà Hoàng Liên có tác dụng bảo vệ. Tim mạch cũng có thể bị ảnh hưởng bởi hội chứng Carcinoid, gây ra lắng đọng mô xơ trên nội mạc buồng tim, van tim, buồng động mạch phổi và động mạch chủ. Tim mạch là hệ thống cơ quan gặp bất thường trong Hội chứng Edwards và Trisomy 18.\n\nNgười phụ nữ mắc hội chứng thiểu sản thất trái có nguy cơ gặp vấn đề về tim mạch khi mang thai. Hệ thống tim mạch cũng chịu ảnh hưởng bởi các hợp chất hóa học trong Huyền sâm. Tim mạch là đối tượng thử nghiệm tác dụng hạ huyết áp của nước sắc Kê huyết đằng. Tim mạch là hệ thống được bảo vệ bởi các hoạt chất trong Kha tử. Khế hỗ trợ tim mạch nhờ chứa vitamin A và kali. Tim mạch cũng chịu ảnh hưởng bởi khí phế thũng. Tim mạch là hệ thống mà Lô hội có tiềm năng bảo vệ. Hệ thống tim mạch cũng chịu ảnh hưởng bởi các biến chứng liên quan đến bệnh lây truyền qua đường tình dục. Bệnh tim mạch được ngăn ngừa nhờ Vitamin PP. Tim mạch là cơ quan được bảo vệ bởi các axit béo lành mạnh và các chất khác trong hạt gai dầu. Tim mạch là hệ thống mạch máu và tim, được nghiên cứu về tác dụng của phytoestrogen từ mầm đậu nành.\n\nTim mạch cũng được hỗ trợ bởi mít. Hệ thống tim mạch cần được bảo vệ khỏi tác hại của muối. Ngoài ra, Tim mạch được Ngân Hạnh bảo vệ. Nghệ trắng có tác dụng tốt đối với các bệnh lý tim mạch và cải thiện hệ thống tim mạch.\n\nBệnh tim mạch có thể là nguyên nhân của hình dùi trống trên móng. Tim mạch là hệ thống chịu ảnh hưởng bởi biến chứng của đái tháo đường type 2. Tim mạch cũng được bảo vệ khỏi biến chứng tiểu đường nhờ Kẽm. Bệnh tim mạch là vấn đề phổ biến trên toàn thế giới, liên quan đến rối loạn lipid máu.\n\nTim mạch cũng chịu tác động của độc tính từ Ô đầu và Phụ tử, làm tăng nguy cơ mắc các bệnh lý tim mạch và ảnh hưởng đến chức năng tổng thể của hệ thống tim mạch. Tim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi cả bệnh cúm mùa và bệnh cúm A/H1N1.\n\nHệ thống tim mạch chịu ảnh hưởng từ purin thông qua nhiều chức năng tim: lưu lượng máu và phân phối oxy. Hệ thống tim mạch chịu ảnh hưởng từ purin thông qua các thụ thể purinergic. Tim mạch là hệ thống mạch máu liên quan đến tim, nơi mùi tây có tác dụng tốt. Tim mạch là hệ thống được bảo vệ bởi hoạt tính ức chế kết tập tiểu cầu từ lá rau mùi tây. Tim mạch được điều trị bằng mùi tây.\n\nHệ thống tim mạch cũng dễ bị ảnh hưởng bởi gốc tự do và các bệnh liên quan. Bệnh tim mạch có thể là bệnh mạn tính có thể liên quan đến rối loạn tiền đình. Tim mạch cũng có thể được gây ra bởi stress. Rong biển giúp bảo vệ tim mạch.\n\nTim mạch cũng liên quan đến bệnh rung nhĩ. Tim mạch là hệ thống chịu ảnh hưởng từ bệnh lý tăng huyết áp. Tim mạch chịu tác động từ Đông trùng hạ thảo. Bộ phận này cần được tham khảo ý kiến bác sĩ trước khi sử dụng rượu Đông trùng hạ thảo.\n\nTim mạch là hệ thống cơ quan chịu sự kiểm soát của tuyến giáp. Suy giáp làm chậm nhịp tim và giảm chức năng co bóp của tim. Tim mạch là hệ thống cơ quan chịu chống chỉ định đối với xét nghiệm hạ đường huyết bằng insulin.\n\nTim mạch là hệ thống chịu ảnh hưởng tích cực từ dịch chiết rễ Tầm Xuân và tác dụng của Xuân. Tim mạch cũng là chuyên khoa y học tập trung vào việc điều trị các vấn đề về tim và mạch máu. Hệ thống tim mạch chịu ảnh hưởng trong tăng huyết áp cấp cứu.\n\nTim mạch là hệ thống gồm tim và mạch máu được Thạch lựu bảo vệ. Thiên ma cũng cải thiện chức năng của hệ thống tim mạch.\n\nHệ thống tim mạch chịu tác động độc hại từ Taxane. Tim mạch là hệ thống cơ quan liên quan đến việc truyền máu trong cơ thể, cần được thông báo cho bác sĩ khi dùng Ameflu DAYTIME.\n\nTim mạch cũng chịu ảnh hưởng của Amilavil. Tim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi việc sử dụng Arcoxia với liều cao, trong thời gian dài.\n\nTim mạch chịu ảnh hưởng của Brufen, đặc biệt đối với bệnh nhân lớn tuổi, có tiền sử bệnh tim mạch. Candesartan được sử dụng để điều trị các tình trạng liên quan đến tim mạch.\n\nTim mạch là hệ thống cơ quan liên quan đến việc điều trị rối loạn cương dương.\n\nTim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi tác dụng phụ của Combivent®, sử dụng Combivent® có thể dẫn đến bệnh tim mạch.\n\nBệnh tim mạch là bệnh mà Cozaar được dùng để điều trị.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng bởi bệnh tim mạch.\n\nRosuvastatin giảm nguy cơ bệnh tim mạch.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng từ tiền đái tháo đường.\n\nTim mạch là hệ thống gồm tim và các mạch máu.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng từ việc bỏ hút thuốc lá.\n\nTim mạch cũng chịu ảnh hưởng từ tăng canxi máu, thể hiện qua tình trạng nhịp tim bất thường.\n\nTim mạch là hệ thống mạch máu, tim sen giúp làm tan huyết khối trong lòng mạch.\n\nTim mạch là hệ thống mạch máu chịu ảnh hưởng từ việc điều hòa lipid và đường huyết.\n\nTim mạch là hệ thống được bảo vệ khỏi bệnh tim mạch nhờ tinh dầu Bergamot.\n\nTim mạch là hệ thống tuần hoàn được bảo vệ khỏi nguy cơ bởi tinh dầu Bergamot.\n\nTim mạch là hệ thống cơ quan được hỗ trợ bởi tác dụng giảm huyết áp của tinh dầu xá xị.\n\nTim mạch chịu ảnh hưởng từ các hợp chất phenolic trong tinh dầu cỏ xạ hương.\n\nTỏi đen cũng có khả năng bảo vệ hệ thống tim mạch.\n\nTim mạch là hệ thống được bảo vệ bởi axit folic và các chất chống oxy hóa.\n\nSử dụng nước trà xanh thường xuyên có thể duy trì sức khỏe tim mạch và ngăn ngừa các bệnh lý về tim mạch. Tim mạch là hệ thống cơ quan được hỗ trợ bởi việc uống nước trà xanh thường xuyên.\n\nTuỷ sống tham gia và thực hiện các phản xạ vận động phức tạp liên quan đến tim mạch. Hệ thống tim mạch chịu ảnh hưởng từ hormon tuyến giáp.\nAviflox: Aviflox là thuốc kháng sinh có hoạt chất tương tự moxifloxacin.\nCiprofloxacin: Ciprofloxacin là một hoạt chất chính trong thuốc Ciprobay, thuộc nhóm quinolon và fluoroquinolon với phổ tác động rộng lên cả vi khuẩn gram âm và gram dương. Đây là một loại thuốc kháng sinh kê đơn, có khả năng thấm sâu vào nhiều mô, đạt nồng độ điều trị cao tại phổi, đường tiết niệu – tuyến tiền liệt, da – mô mềm, xương – khớp và mô ổ bụng. Thuốc này được chỉ định trong việc điều trị nhiều loại bệnh nhiễm trùng, bao gồm cả bệnh hạ cam mềm và bệnh hạ cam, cũng như các bệnh nhiễm khuẩn nghiêm trọng như bệnh than, dịch hạch, nhiễm Rickettsia, và nhiễm nhóm HACEK gây viêm nội tâm mạc.\n\nCiprofloxacin có thể được sử dụng dưới dạng viên nén hoặc hỗn dịch uống và cần được sử dụng kèm theo đủ nước. Thuốc này có khả năng tương tác với một số loại thuốc khác, bao gồm Biviantac, A.T Calci Plus, và Amiodarone. Đặc biệt, Ciprofloxacin có thể ức chế quá trình đào thải canxi qua thận, tức là nó ngăn chặn thận đào thải calci ra khỏi cơ thể.\n\nThuốc này đã được FDA chấp thuận cho mục đích dự phòng và điều trị bệnh than.\nLoạn nhịp tim: Loạn nhịp tim là một rối loạn trên tim.&lt;SEP&gt;Loạn nhịp tim là triệu chứng điện tâm đồ cần theo dõi khi dùng quá liều moxifloxacin.\nRối Loạn Tim Mạch: Rối loạn tim mạch là tác dụng phụ hiếm gặp khi sử dụng Coversyl.&lt;SEP&gt;Rối loạn tim mạch là bệnh mạn tính được ngăn chặn bởi chiết xuất từ dây ký ninh.&lt;SEP&gt;Rối loạn tim mạch là triệu chứng được điều trị bằng tỏi.&lt;SEP&gt;Rối loạn tim mạch, bao gồm tụt huyết áp, loạn nhịp tim, khó thở, là biểu hiện nguy hiểm của ngộ độc thực phẩm.&lt;SEP&gt;Rối loạn tim mạch là tác dụng không mong muốn khi ăn hạt hoặc quả Ngô đồng.&lt;SEP&gt;Rối loạn tim mạch là tác dụng phụ của Ciprofloxacin.&lt;SEP&gt;Rối loạn tim mạch là tình trạng bệnh mà Actemra có thể tăng nguy cơ mắc phải.\nNhóm Điều Trị Loạn Thần: Nhóm điều trị loạn thần là loại thuốc có thể tương tác với moxifloxacin.\nNSAID: NSAID, viết tắt của Non-Steroidal Anti-Inflammatory Drugs, là một nhóm thuốc có tác dụng giảm đau và chống viêm. NSAID thuộc nhóm pyrazole có thể tương tác với Acenocoumarol, gây ra các tác dụng phụ như khó chịu ở thượng vị, ợ nóng, đau dạ dày, và loét dạ dày. Nhóm thuốc này cũng có khả năng tương tác với nhiều loại thuốc khác, tạo ra các rủi ro về sức khỏe khi sử dụng đồng thời với các thuốc như Clopidogrel và Aspirin.\n\nKhi NSAID được sử dụng cùng với Clopidogrel, nguy cơ xuất huyết đường tiêu hóa có thể tăng lên. Đặc biệt, việc sử dụng NSAID cùng với Atocib cần được thực hiện một cách thận trọng, đặc biệt đối với bệnh nhân có nguy cơ phát triển biến chứng đường tiêu hóa. Thuốc này cũng có thể gây chảy máu ẩn đường tiêu hóa khi sử dụng kết hợp với clopidogrel và aspirin.\n\nNSAID thường được sử dụng để điều trị các vấn đề liên quan đến đau và viêm, nhưng chúng cũng có thể gây ra tác dụng phụ cho người lớn tuổi hoặc những người có nguy cơ cao. Ngoài ra, NSAID còn được thay thế bằng Nhũ hương trong một số trường hợp điều trị bệnh lý khớp.&lt;SEP&gt;Thuốc NSAID là các loại thuốc giảm đau và chống viêm.&lt;SEP&gt;NSAID là thuốc có thể kéo dài thời gian chảy máu và gây ra các tác dụng phụ như tăng nguy cơ huyết khối động mạch.&lt;SEP&gt;NSAID là một loại thuốc tương tác với Ciprobay.\nDofetilid: Dofetilid là một loại thuốc chống loạn nhịp tim, có thể tương tác với Amiodarone.&lt;SEP&gt;Dofetilid là một loại thuốc cần lưu ý khi sử dụng chung với Daktarin.&lt;SEP&gt;Dofetilid là thuốc chống loạn nhịp tim có thể tương tác với moxifloxacin.\nSuy Tim: Suy tim là tình trạng bệnh lý tim mạch nghiêm trọng, trong đó chức năng tim suy giảm, khiến tim không thể bơm đủ máu để đáp ứng nhu cầu của cơ thể. Tình trạng này có thể xuất hiện như hậu quả của nhiều yếu tố, bao gồm cả tăng tiết Adrenaline nội sinh trong cơ thể, dẫn đến tăng nhịp tim và tăng nguy cơ suy tim. Suy tim cũng là biến chứng của nhiều bệnh khác nhau như bệnh bụi phổi, bệnh cơ tim phì đại, chứng aldosterone nguyên phát, bệnh hẹp van tim hai lá, và bệnh hẹp van động mạch chủ. Nó cũng là biến chứng của ứ sắt trong bệnh Thalassemia và bệnh tim Ebstein.\n\nTriệu chứng của suy tim bao gồm khó thở, đau ngực, tim đập mạnh, dễ mệt mỏi, da xanh tím quanh môi và phù chân. Suy tim cũng là nguyên nhân phổ biến gây ra liệt dương và là biến chứng nghiêm trọng của bệnh viêm mạch và đa u hạt dị ứng. Trong quá trình điều trị, suy tim thường được điều trị bằng các loại thuốc như Losartan, Agifuros 40 mg, amlodipine, và nhóm chặn kênh canxi. Tuy nhiên, việc sử dụng một số loại thuốc cụ thể như Agietoxib và Acenocoumarol 4 mg cũng có thể gây ra suy tim và đòi hỏi sự thận trọng đặc biệt. Việc sử dụng Bisoloc ở bệnh nhân suy tim sung huyết cần được giám sát đặc biệt. Sử dụng Amlor 5 Pfizer hoặc Amlodipin cũng cần thận trọng do có thể làm tăng tỷ lệ phù phổi. Suy tim cũng có thể ảnh hưởng đến việc sử dụng Antacil và Aphaxan, và có thể tăng cường khi kết hợp Atenolol với Nifedipine. Ngoài ra, suy tim cũng là một trong những triệu chứng chính của đái tháo đường và là một biến chứng nghiêm trọng của huyết áp không ổn định.\n\nSuy tim cũng có thể là nguyên nhân gây huyết áp không ổn định và cũng là một trong những yếu tố nguy cơ của bệnh huyết khối tĩnh mạch. Tình trạng này cũng có thể xảy ra khi lượng máu chảy đến phổi quá nhiều do tật thông liên thất. Việc sử dụng Ma hoàng cần thận trọng đối với bệnh nhân suy tim. Một số nguồn thông tin đề cập rằng suy tim cũng có thể liên quan đến tỷ lệ hồng cầu cao hơn bình thường, và tình trạng này cũng có thể xuất hiện do tăng huyết áp, dẫn đến suy giảm chức năng tim. Điều trị suy tim cũng có thể bao gồm việc sử dụng các loại thuốc truyền thống như glycosid tim, các thành phần như mạch môn, nhân sâm hoặc đảng sâm, và ngũ vị tử.\n\nSuy tim cũng là một trong những nguy cơ của bệnh rung nhĩ và cần tránh lạm dụng rong nho do hàm lượng muối cao. Tình trạng này cũng là yếu tố nguy cơ của ngưng tim đột ngột và có thể được phát hiện bởi xét nghiệm X-Quang ngực thẳng. Suy tim cần được điều trị tại phòng cấp cứu do tim không thể bơm máu hiệu quả.\n\nSuy tim là một căn bệnh mãn tính có thể xảy ra ở mọi lứa tuổi, đặc biệt là ở người già. Bệnh không có biện pháp điều trị triệt để, chỉ có thể làm giảm triệu chứng và ngăn ngừa tiến triển. Suy tim cũng là biến chứng của trẻ sinh non do vấn đề tim.\n\nSuy tim mức độ từ vừa đến nặng là một trong những bệnh lý không nên sử dụng Aspirin hay Aspilets EC. Suy tim là chống chỉ định dùng Brufen, đặc biệt nếu bệnh nhân có suy tim nặng. Suy tim là tình trạng bệnh lý cần điều chỉnh liều dùng Candesartan. Suy tim là bệnh lý được điều trị bằng Candesartan. Suy tim cũng là chống chỉ định khi sử dụng moxifloxacin. Suy tim là bệnh có thể xảy ra do tác dụng độc hại của Thương lục. Suy tim là một trong các biểu hiện ngộ độc hoặc quá liều Thương lục.\n\nNgoài ra, suy tim cũng là biến chứng của thuyên tắc động mạch phổi, do tim phải hoạt động nhiều để bơm máu lên phổi. Tình trạng này làm tăng nguy cơ thuyên tắc phổi và gây phù toàn thân. Suy tim cũng là bệnh lý có thể gây bất động và là yếu tố nguy cơ thuyên tắc tĩnh mạch sâu.&lt;SEP&gt;Suy tim là triệu chứng của biến chứng tim do thiếu máu.&lt;SEP&gt;Suy tim là nguyên nhân phổ biến nhất gây tràn dịch màng phổi.&lt;SEP&gt;Suy tim là tình trạng cần được kiểm soát bằng các phương pháp hỗ trợ trước phẫu thuật.&lt;SEP&gt;Suy tim là tình trạng tim không thể bơm đủ máu vào cơ thể, thường là hậu quả của bệnh tim mạch.&lt;SEP&gt;Suy tim là bệnh tim mạch có thể làm hạ huyết áp đột ngột.\nSắt, Sucralfat, Kẽm, Multivitamin: Sắt, sucralfat, kẽm, multivitamin là thành phần của các thuốc có thể tương tác với moxifloxacin.\nAmitriptyline: Amitriptyline là một loại thuốc chống trầm cảm ba vòng (tricyclic antidepressant) được sử dụng để điều trị trầm cảm. Thuốc này không chỉ giúp giảm các triệu chứng của trầm cảm mà còn có khả năng giảm đau vùng chậu. Tuy nhiên, việc sử dụng Amitriptyline cần phải được thực hiện một cách thận trọng do tiềm ẩn nhiều tương tác thuốc khác nhau.\n\nAmitriptyline có thể tương tác với một số loại thuốc khác như Combigan và Depakin. Khi sử dụng Amitriptyline cùng với Depakin, cần phải điều chỉnh liều lượng để tránh các tác dụng phụ không mong muốn. Ngoài ra, Amitriptyline cũng có thể tương tác với disulfiram, dẫn đến tăng cường phản ứng giữa rượu và disulfiram khi cả hai được sử dụng cùng nhau.\n\nThuốc này cũng cần được sử dụng cẩn thận khi dùng cùng với các thuốc ức chế monoamin oxydase (MAOIs). Bệnh nhân rối loạn lưỡng cực cũng cần đặc biệt chú ý khi sử dụng Amitriptyline, đặc biệt là trong giai đoạn hồi phục sau nhồi máu cơ tim. \n\nMột điểm đáng lưu ý khác là Amitriptyline có thể gây ra tác dụng phụ ở thai nhi và có thể ảnh hưởng đến trẻ sơ sinh. Điều này nhấn mạnh tầm quan trọng của việc thông báo cho bác sĩ về tình trạng mang thai hoặc đang cho con bú trước khi bắt đầu sử dụng Amitriptyline.&lt;SEP&gt;Amitriptyline là một trong những thuốc chống trầm cảm ba vòng được liệt kê trong văn bản.&lt;SEP&gt;Amitriptyline là thuốc chống trầm cảm ba vòng có thể tương tác với moxifloxacin.\nChống Trầm Cảm Ba Vòng: Chống trầm cảm ba vòng là loại thuốc có thể tương tác với moxifloxacin.\nAmiodarone - Dofetilid: Thuốc Amiodarone có thể tương tác với Dofetilid.\nThuốc Chẹn Beta - Tim Mạch: Tác dụng phụ của thuốc chẹn beta có thể bao gồm các vấn đề về tim mạch.\nAmlodipin - Loạn nhịp tim: Amlodipin có thể gây loạn nhịp tim như một phản ứng có hại.\nCiprofloxacin - Rối Loạn Tim Mạch: Ciprofloxacin có thể gây rối loạn tim mạch.\nLoạn nhịp tim - Perindopril: Perindopril có thể gây loạn nhịp tim như một phản ứng có hại.\nNSAID - Suy Tim: Suy tim là tác dụng phụ có thể gặp khi sử dụng NSAID.\nLoạn nhịp tim - Moxifloxacin: Loạn nhịp tim là nguy cơ cần theo dõi khi dùng quá liều moxifloxacin.\nAmitriptyline - Bệnh Tim Mạch: Amitriptyline có thể làm tăng nguy cơ rối loạn nhịp tim ở bệnh nhân tim mạch.\nDofetilid - Moxifloxacin: Moxifloxacin có thể tương tác với dofetilid.\nAdrenalin - Tim Mạch: Adrenalin có thể gây tác dụng phụ liên quan đến tim mạch.\nAvelox - Moxifloxacin: Avelox là thương hiệu của thuốc kháng sinh moxifloxacin.&lt;SEP&gt;Avelox là thương hiệu của thuốc moxifloxacin.\nA.t Domperidon - Tim Mạch: A.t Domperidon có thể tăng nguy cơ loạn nhịp thất do tim mạch.\nMoxifloxacin - Thuốc Chống Loạn Nhịp Tim: Moxifloxacin có thể tương tác với các thuốc chống loạn nhịp tim.\nSuy Tim Mạn - Thuốc Lá: Thuốc lá là yếu tố nguy cơ đối với bệnh lý tim mạch.\nAviflox - Moxifloxacin: Moxifloxacin có hoạt chất tương tự Aviflox.\nThăm Khám - Tác Dụng Phụ: Thăm khám nhằm chẩn đoán và xử lý các tác dụng phụ của thuốc.\nMoxifloxacin - Nhóm Điều Trị Loạn Thần: Moxifloxacin có thể tương tác với các thuốc điều trị loạn thần.\nDược Liệu - Y Bác Sĩ: Y bác sĩ giúp kiểm soát rủi ro và tư vấn về tác dụng không mong muốn khi sử dụng dược liệu.\nMoxifloxacin - Sắt, Sucralfat, Kẽm, Multivitamin: Moxifloxacin có thể tương tác với các thuốc chứa sắt, sucralfat, kẽm, multivitamin.\nFexofenadine - Tim Mạch: Bệnh nhân có nguy cơ tim mạch cần thận trọng khi dùng Fexofenadine.\nChống Trầm Cảm Ba Vòng - Moxifloxacin: Moxifloxacin có thể tương tác với các thuốc chống trầm cảm ba vòng.\nMoxifloxacin - Thuốc Chống Virus/Vi Khuẩn: Moxifloxacin có thể tương tác với các thuốc chống virus/vi khuẩn.\nBeprid - Moxifloxacin: Moxifloxacin có thể tương tác với beprid.\nDaktarin - Dofetilid: Daktarin có thể tương tác với Dofetilid khi sử dụng cùng.\nLoạn nhịp tim - QT kéo dài: QT kéo dài có thể dẫn đến loạn nhịp tim.']</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể gặp rủi ro khi sử dụng Avelox nếu họ đang gặp vấn đề với tim. Avelox là thương hiệu của thuốc kháng sinh moxifloxacin và có thể gây ra một số tác dụng phụ liên quan đến tim mạch. 
+Một số tác dụng phụ liên quan đến tim mạch có thể bao gồm loạn nhịp tim. Điều này có nghĩa là việc sử dụng Avelox cần được theo dõi chặt chẽ nếu bệnh nhân đang gặp vấn đề về tim hoặc đang dùng các loại thuốc khác có tác động đến tim mạch.
+Do đó, trước khi sử dụng Avelox, bệnh nhân nên thông báo cho bác sĩ về tình trạng tim mạch hiện tại của họ. Việc này giúp bác sĩ có thể đánh giá xem việc sử dụng Avelox có an toàn cho bệnh nhân hay không.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Không, nếu bệnh nhân đã từng được chẩn đoán rối loạn nhịp tim, suy tim hoặc nhịp tim chậm thì không được sử dụng thuốc này.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8903210090955828</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.7538302522488957</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>['Thuốc Trị Viêm Da: Thuốc trị viêm da chứa axit salicylic, được sử dụng để điều trị các tình trạng viêm da.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nThuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic được sử dụng để điều trị viêm da, có thể gây tác dụng phụ như kích ứng da.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nAxit Salicylic: Axit salicylic là một hợp chất hóa học được tìm thấy trong rễ cây Hoàng tinh. Đây là thành phần chính của aspirin và cũng là hoạt chất trong nhiều loại thuốc trị viêm da, thuốc không kê đơn điều trị mụn trứng cá, và kem tiêu sừng tại chỗ. Axit salicylic có tác dụng làm tróc lớp sừng da và sát khuẩn nhẹ khi bôi lên da, giúp điều trị tại chỗ một số bệnh da tăng sừng hóa và bong da như viêm da tiết bã nhờn, trứng cá, gàu, bệnh vảy nến, hột cơm, và chai gan bàn chân. Nó cũng được sử dụng để đào thải mụn đầu đen và mụn đầu trắng, giảm viêm và sưng tấy. Axit salicylic giúp loại bỏ tế bào da chết và hỗ trợ điều trị bệnh nhân nhiễm trùng nấm da bàn chân. Tuy nhiên, cần lưu ý rằng axit salicylic có thể gây kích ứng và ngộ độc nếu sử dụng quá liều hoặc sai cách. Các sản phẩm chứa axit salicylic thường có nhiều nồng độ khác nhau tùy thuộc vào mục đích sử dụng cụ thể.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nNhững Triệu Chứng Ngộ Độc Axit Salicylic: Những triệu chứng ngộ độc axit salicylic là các triệu chứng biểu hiện khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nTác Dụng Phụ Khi Sử Dụng Thuốc Trị Viêm Da Axit Salicylic: Tác dụng phụ khi sử dụng thuốc trị viêm da axit salicylic bao gồm các triệu chứng như kích ứng da, nổi mề đay, khó thở, loét hoặc ăn mòn da.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nSuy Giảm Tuần Hoàn Ngoại Vi: Suy giảm tuần hoàn ngoại vi là bệnh cần thận trọng khi sử dụng axit salicylic.\nLiều Lượng: Liều lượng là số lượng thuốc hoặc chất hoạt chất được chỉ định sử dụng trong quá trình điều trị. Nó bao gồm cả số lượng thuốc được sử dụng và cách thức sử dụng nó, ví dụ như qua đường uống, tiêm hoặc thoa ngoài da. Liều lượng có thể được điều chỉnh dựa trên nhiều yếu tố khác nhau, bao gồm cân nặng, lối sống, và các yếu tố sức khỏe cá nhân khác. \n\nĐối với một số loại thuốc cụ thể, liều lượng cũng được quy định cụ thể cho từng độ tuổi. Ví dụ, liều lượng của Siro Bổ Phế Nam Hà và Viên Ngậm Bổ Phế Nam Hà được quy định cụ thể cho từng độ tuổi khác nhau. Điều này đảm bảo rằng mỗi người dùng nhận được liều lượng phù hợp với nhu cầu và tình trạng sức khỏe của họ.\n\nLiều lượng cũng có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc. Ví dụ, liều lượng corticoid sử dụng tại chỗ có thể được hấp thu vào máu, do đó việc xác định đúng liều lượng là rất quan trọng để tránh các tác dụng phụ không mong muốn.\n\nNgoài ra, liều lượng còn liên quan đến việc sử dụng thảo dược và hormone. Việc sử dụng thảo dược cần được chú ý về mức độ sử dụng, và liều lượng hormone là yếu tố ảnh hưởng đến việc lựa chọn liệu pháp hormon.&lt;SEP&gt;Liều lượng là yếu tố cần xem xét khi sử dụng dược liệu này để đảm bảo hiệu quả và an toàn.&lt;SEP&gt;Liều lượng là mức độ hoặc số lượng của một chất được đưa vào cơ thể, có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc.&lt;SEP&gt;Liều lượng là số lượng thuốc cần dùng trong một lần hoặc trong một khoảng thời gian.\nThuốc Dán: Thuốc dán chứa axit salicylic được sử dụng để điều trị mụn cơm và chai ở gan bàn chân.\nThảo Dược: Thảo Dược là thuật ngữ chung chỉ các loại cây cỏ, hạt, củ, lá được sử dụng làm dược liệu trong y học cổ truyền. Thảo dược bao gồm nhiều loại cây khác nhau như cà dăm, cây Nổ gai, cây Rau Dớn, và cả quả, lá, và rễ của chanh. Thảo dược đóng vai trò quan trọng như các thành phần chính trong nhiều bài thuốc, đặc biệt là trong việc sắc uống hỗ trợ điều trị các chứng bế kinh, ứ huyết. Thảo dược từ cây Nổ gai có tác dụng khu phong, trừ thấp, thanh nhiệt, giải độc, chỉ huyết, giảm đau, và giảm ngứa. Thảo dược cũng được sử dụng trong chè dưỡng nhan có nguồn gốc từ cung đình Trung Quốc.\n\nThảo dược có nhiều công dụng trong việc phòng ngừa và điều trị các bệnh và triệu chứng, đồng thời cũng được sử dụng rộng rãi trong các bài thuốc cổ truyền. Thảo dược có thể tương tác với các loại thuốc hiện đại như Aleucin 500 mg và có tác dụng chống viêm rõ rệt. Thảo dược là nguồn gốc của các thành phần hóa học như coumarin trong nghiên cứu về tác dụng bảo vệ tế bào gan và chống viêm. Tuy nhiên, cần lưu ý rằng thảo dược có thể là con dao hai lưỡi nếu không sử dụng đúng cách, vì chúng có thể gây ra nhiều tương tác thuốc và tác dụng phụ tiềm ẩn.\n\nNgoài ra, thảo dược còn được sử dụng như một dạng thuốc thay thế có thể được sử dụng để điều trị bệnh đau chi ma. Thảo dược cũng được xem là một loại thực phẩm chức năng, mặc dù chưa được chứng minh có hiệu quả trong điều trị lo âu. Thảo dược là lĩnh vực chuyên môn cần tham vấn ý kiến của bác sĩ hoặc các chuyên gia. Cây sachi là một loại thảo dược có thể phát triển ở những vùng khí hậu ẩm ướt. Thảo dược là nguyên liệu dược liệu, cần bảo quản cẩn thận. Thảo dược là nguyên liệu quý được sử dụng trong y học cổ truyền và ngành hóa dược.\n\nThảo dược cũng được sử dụng để điều trị các bệnh ngoài da, bao gồm viêm lộ tuyến và viêm loét cổ tử cung. Thảo dược này có tác dụng cải thiện tế bào beta tụy và giảm lượng đường trong máu. Thảo dược là nguyên liệu trong bài thuốc hỗ trợ điều trị bệnh đái tháo đường và bệnh Gout. Thảo dược là thành phần tự nhiên trong BoniDiabet.\n\nThảo dược còn được biết đến như một phương pháp điều trị bệnh bằng các loại cây thuốc, bao gồm cả huyết rồng. Thảo dược là một trong hai phương pháp chính để chữa u mềm lây thông qua việc thoa lên bề mặt. Thảo dược là thuật ngữ chung cho các vị thuốc tự nhiên, bao gồm cả rau đắng đất, và cũng là nguyên liệu trong bài thuốc thanh can giải độc. Thảo dược là thuật ngữ dùng để chỉ các loại cây có tác dụng chữa bệnh và là thuật ngữ chung cho các loại cây thuốc.&lt;SEP&gt;Thảo dược là thuật ngữ chỉ các loại cây thuốc quý.&lt;SEP&gt;Thảo dược là nguyên liệu tự nhiên từ cây cỏ.&lt;SEP&gt;Thảo dược là các chất hóa học tự nhiên từ thực vật, có thể được sử dụng trong điều trị.&lt;SEP&gt;Thảo dược là tên chung cho các loại cây được sử dụng làm thuốc, trong đó có Tía tô.\nNgộ Độc Axit Salicylic: Ngộ độc axit salicylic là tình trạng sức khỏe xảy ra khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nSử Dụng: Sử dụng cúc tần cần thận trọng và tham khảo ý kiến bác sĩ.\nInfection Acid Due to Kidney: Infection acid due to kidney là tình trạng bệnh lý không thích hợp để sử dụng Acetazolamid.\nTùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc mà không tham khảo ý kiến chuyên gia.\nAxit Salicylic - Đái Tháo Đường: Người bệnh đái tháo đường không nên sử dụng axit salicylic.&lt;SEP&gt;Đái tháo đường là yếu tố nguy cơ khi sử dụng axit salicylic.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nThuốc Trị Viêm Da - Đái Tháo Đường: Đái tháo đường là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nAxit Salicylic - Chóng Mặt: Chóng mặt là triệu chứng của ngộ độc axit salicylic.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nAxit Salicylic - Đau Đầu: Đau đầu nặng hoặc liên tục là triệu chứng của ngộ độc axit salicylic.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\nChóng Mặt - Thuốc Trị Viêm Da: Chóng mặt là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nSử Dụng - Tùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc.\nChóng Mặt - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng chóng mặt.\nThuốc - Việc Sử Dụng Sai Lầm: Sử dụng thuốc sai cách có thể dẫn đến việc sử dụng sai thuốc.\nThuốc Trị Viêm Da - Đau Đầu: Đau đầu nặng hoặc liên tục là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nLưu Ý - Thuốc: Lưu ý đề cập rằng cần hỏi ý kiến bác sĩ trước khi sử dụng thuốc.\nAxit Salicylic - Da: Axit salicylic có thể tác động lên da.\nViệc Sử Dụng Sai Lầm - Ý Kiến Thầy Thuốc: Tham khảo ý kiến thầy thuốc có thể giúp phòng ngừa việc sử dụng thuốc sai cách.\nAspirin - Axit Salicylic: Axit salicylic là thành phần chính của aspirin.\nRủi Ro - Vị Thuốc: Việc sử dụng vị thuốc có thể dẫn đến rủi ro cần được kiểm soát.&lt;SEP&gt;Kiểm soát rủi ro khi sử dụng vị thuốc cần tham khảo ý kiến bác sĩ.&lt;SEP&gt;Việc sử dụng vị thuốc có thể mang lại rủi ro.&lt;SEP&gt;Y bác sĩ đề nghị kiểm soát rủi ro khi sử dụng vị thuốc.\nDa - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên da.\nLiều Lượng Khuyến Nghị - Tác Dụng Không Mông Muôn: Sử dụng vượt quá liều lượng khuyến nghị có thể dẫn đến tác dụng không mong muốn.\nKhó Thở - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây khó thở.\nAxit Salicylic - Viêm Da: Axit salicylic có nhiều nồng độ khác nhau, cần bắt đầu với nồng độ thấp và tăng dần theo đáp ứng bệnh.&lt;SEP&gt;Axit salicylic được sử dụng để điều trị viêm da.\nAxit Salicylic - Mắt: Axit salicylic có thể tác động lên mắt.\nAxit Salicylic - Ngộ Độc: Axit salicylic có thể gây ngộ độc nếu sử dụng sai cách.\nAxit Salicylic - Cho Con Bú: Sử dụng axit salicylic cần thận trọng trong thời kỳ cho con bú.\nAxit Salicylic - Hoàng Tinh: Hoàng tinh chứa axit salicylic như thành phần hóa học.\nAxit Salicylic - Mẫn Cảm: Người bị mẫn cảm với axit salicylic không nên sử dụng thuốc này.\nAxit Salicylic - Mụn Trứng Cá: Axit salicylic được dùng để điều trị mụn trứng cá.\nAxit Salicylic - Mũi: Axit salicylic có thể tác động lên mũi.\nMắt - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên mắt.\nAxit Salicylic - Mụn Trứng Cà: Axit salicylic được sử dụng để điều trị mụn trứng cá ở dạng nhẹ.\nAxit Salicylic - Lú Lẫn: Lú lẫn là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Niêm Mạc: Không nên bôi axit salicylic lên niêm mạc.&lt;SEP&gt;Axit salicylic có thể tác động lên niêm mạc.\nNgộ Độc - Thuốc Trị Viêm Da: Thuốc trị viêm da chứa axit salicylic có thể gây ngộ độc nếu sử dụng sai cách.\nNgộ Độc Axit Salicylic - Ù Tai: Ngộ độc axit salicylic biểu hiện triệu chứng ù tai.\nAcid Salicylic - Viêm Da: Acid salicylic trong thuốc Beprosalic có thể gây viêm da.\nAxit Salicylic - Da Đầu: Axit salicylic được sử dụng để điều trị các vấn đề da đầu như vảy da đầu.\nAxit Salicylic - Miệng: Axit salicylic có thể tác động lên miệng.\nAxit Salicylic - Trứng Cá: Axit salicylic được sử dụng để điều trị trứng cá.&lt;SEP&gt;Axit salicylic được dùng để điều trị trứng cá.\nNổi Mề Đay - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây nổi mề đay.\nAxit Salicylic - Thuốc Kháng Nấm: Axit salicylic hỗ trợ phương pháp điều trị bằng thuốc kháng nấm.\nAxit Salicylic - Tay: Axit salicylic có thể tác động lên tay.\nAxit Salicylic - Thời Kỳ Mang Thai: Sử dụng axit salicylic cần thận trọng trong thời kỳ mang thai.\nAxit Salicylic - Liều Thuốc: Phải sử dụng axit salicylic theo đúng liều lượng và hướng dẫn của bác sĩ.\nAcid Salicylic - Benzoyl Peroxide: Benzoyl peroxide có thể tương tác không tốt khi dùng chung với acid salicylic.\nMũi - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên mũi.\nAxit Salicylic - Thuốc Trị Viêm Da: Axit salicylic là thành phần chính của thuốc trị viêm da.\nAxit Salicylic - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic xảy ra khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nAxit Salicylic - Thở Nhanh: Thở nhanh là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Mụn Dai Dẳng: Axit salicylic giúp loại bỏ tế bào da chết.\nAcetazolamid - Infection Acid Due to Kidney: Nhiễm acid do thận là tình trạng bệnh lý không thích hợp để sử dụng Acetazolamid.\nAxit Salicylic - Bệnh Vảy Nến: Axit salicylic được dùng để điều trị bệnh vảy nến.\nAxit Salicylic - Gàu: Axit salicylic được dùng để điều trị gàu.\nAxit Salicylic - Thuốc Mỡ: Thuốc mỡ chứa axit salicylic.\nLú Lẫn - Thuốc Trị Viêm Da: Lú lẫn là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nLú Lẫn - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng lú lẫn.\nNiêm Mạc - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên niêm mạc.\nAxit Salicylic - Suy Tuần Hoàn: Người bệnh suy tuần hoàn không nên sử dụng axit salicylic.\nAxit Salicylic - Thuốc Trị Viêm Da Axit Salicylic: Axit salicylic là thành phần chính trong thuốc trị viêm da.\nAxit Salicylic - Thuốc Khác: Axit salicylic có thể xảy ra tương tác với các loại thuốc khác.\nAxit Salicylic - Viêm Da Tiết Bã Nhờn: Axit salicylic được dùng để điều trị viêm da tiết bã nhờn.\nAxit Salicylic - Tăng Tiết Bã Nhờn: Axit salicylic được dùng để điều trị tăng tiết bã nhờn.\nAxit Salicylic - Mụn Cơm: Axit salicylic giúp loại bỏ mụn cơm.&lt;SEP&gt;Axit salicylic được sử dụng để điều trị mụn cơm.\nAxit Salicylic - Dày Sừng Da Bàn Chân: Axit salicylic là hợp chất hóa học được sử dụng trong kem tiêu sừng để điều trị dày sừng da bàn chân.\nAxit Salicylic - Dầu Parafin: Dầu parafin được sử dụng để bảo vệ da khỏi kích ứng do axit salicylic.\nAxit Salicylic - Trí Tuệ: Axit salicylic có thể tác động lên trí tuệ.\nAxit Salicylic - Đầu Chi: Axit salicylic cần thận trọng khi bôi lên đầu chi của người bệnh suy giảm tuần hoàn ngoại vi hoặc đái tháo đường.\nAxit Salicylic - Thuốc Dán: Thuốc dán chứa axit salicylic.\nAcid Salicylic - Lô Hội: Lô hội chứa acid salicylic.&lt;SEP&gt;Acid salicylic là thành phần của Lô hội.\nAxit Salicylic - Tăng Sừng: Axit salicylic được sử dụng trong kem tiêu sừng tại chỗ để điều trị tăng sừng.\nAxit Salicylic - Tiêu Sừng Tại Chỗ: Axit salicylic là hoạt chất trong kem tiêu sừng tại chỗ.\nAxit Salicylic - Tiếng Rung Trong Tai: Tiếng rung hoặc tiếng vo vo trong tai liên tục là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Suy Giảm Tuần Hoàn Ngoại Vi: Suy giảm tuần hoàn ngoại vi là yếu tố nguy cơ khi sử dụng axit salicylic.\nAxit Salicylic - Đa Dây Thần Kinh Ngoại Vi: Đa dây thần kinh ngoại vi rõ là yếu tố nguy cơ khi sử dụng axit salicylic.\nAxit Salicylic - Thuốc Kem: Thuốc kem chứa axit salicylic.\nAxit Salicylic - Thuốc Nước: Thuốc nước chứa axit salicylic.\nAxit Salicylic - Thuốc Gel: Thuốc gel chứa axit salicylic.\nAxit Salicylic - Chai Ở Gan Bàn Chân: Axit salicylic được sử dụng để điều trị chai ở gan bàn chân.\nAxit Salicylic - Gan Bàn Chân: Axit salicylic điều trị chứng tăng sừng khu trú ở gan bàn chân.\nAxit Salicylic - Bệnh Da Tróc Vảy: Axit salicylic được dùng để điều trị bệnh da tróc vảy.\nAxit Salicylic - Hột Cơm: Axit salicylic được dùng để điều trị hột cơm.\nAxit Salicylic - Chai Gan Bàn Chân: Axit salicylic được dùng để điều trị chai gan bàn chân.\nAxit Salicylic - Niêm Mạc Tiêu Hóa: Axit salicylic đường toàn thân gây kích ứng mạnh niêm mạc tiêu hóa.\nAxit Salicylic - Tăng Sừng Khu Trú: Axit salicylic được dùng để điều trị tăng sừng khu trú.\nAxit Salicylic - Gan Bàn Tay: Axit salicylic điều trị chứng tăng sừng khu trú ở gan bàn tay.\nAxit Salicylic - Da Bị Nứt Nẻ: Không nên bôi axit salicylic trên da bị nứt nẻ.\nAxit Salicylic - Chứng Tăng Sừng Khu Trú: Axit salicylic được sử dụng để điều trị chứng tăng sừng khu trú.\nMiệng - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên miệng.\nAcid Salicylic - Azaduo: Azaduo thận trọng khi dùng chung với các chế phẩm chứa acid salicylic.\nKích Ứng Da - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây kích ứng da.\nTay - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên tay.\nNgộ Độc Axit Salicylic - Sưng Mặt: Ngộ độc axit salicylic biểu hiện triệu chứng sưng mặt.\nAcid Salicylic - Quả Mâm Xôi: Quả mâm xôi chứa acid salicylic.\nNgộ Độc Axit Salicylic - Ra Mồ Hôi: Ngộ độc axit salicylic biểu hiện triệu chứng ra mồ hôi.\nAcid Salicylic - Beprosalic: Beprosalic chứa hoạt chất acid salicylic.&lt;SEP&gt;Beprosalic chứa acid salicylic.\nGiãn Mạch - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng giãn mạch.\nThuốc Trị Viêm Da - Thở Nhanh: Thở nhanh là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nNgộ Độc Axit Salicylic - Thở Nhanh: Ngộ độc axit salicylic biểu hiện triệu chứng thở nhanh.\nNgộ Độc Axit Salicylic - Điếc: Ngộ độc axit salicylic biểu hiện triệu chứng điếc.\nNgộ Độc Axit Salicylic - Sưng Môi: Ngộ độc axit salicylic biểu hiện triệu chứng sưng môi.\nNgộ Độc Axit Salicylic - Sưng Cổ Họng: Ngộ độc axit salicylic biểu hiện triệu chứng sưng cổ họng.\nNgộ Độc Axit Salicylic - Sưng Lưỡi: Ngộ độc axit salicylic biểu hiện triệu chứng sưng lưỡi.\nDầu Parafin - Thuốc Trị Viêm Da: Dầu parafin được sử dụng để bảo vệ da khỏi kích ứng do thuốc trị viêm da.\nThuốc Trị Viêm Da - Trí Tuệ: Thuốc trị viêm da có thể tác động lên trí tuệ.\nThuốc Trị Viêm Da - Đầu Chi: Thuốc trị viêm da cần thận trọng khi bôi lên đầu chi của người bệnh suy giảm tuần hoàn ngoại vi hoặc đái tháo đường.\nThuốc Trị Viêm Da - Tiếng Rung Trong Tai: Tiếng rung hoặc tiếng vo vo trong tai liên tục là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nSuy Giảm Tuần Hoàn Ngoại Vi - Thuốc Trị Viêm Da: Suy giảm tuần hoàn ngoại vi là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nThuốc Trị Viêm Da - Đa Dây Thần Kinh Ngoại Vi: Đa dây thần kinh ngoại vi rõ là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nNgộ Độc Axit Salicylic - Thở Sâu: Ngộ độc axit salicylic biểu hiện triệu chứng thở sâu.\nHấp Thu Thuốc - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic xảy ra do hấp thu quá nhiều axit salicylic.\nNgộ Độc Axit Salicylic - Tác Dụng Phụ Khi Sử Dụng Thuốc Trị Viêm Da Axit Salicylic: Ngộ độc axit salicylic là một trong những tác dụng phụ khi sử dụng thuốc trị viêm da axit salicylic.\nNgộ Độc Axit Salicylic - Tiếng Rung: Ngộ độc axit salicylic biểu hiện triệu chứng tiếng rung.\nNgộ Độc Axit Salicylic - Tiếng Vo Vo: Ngộ độc axit salicylic biểu hiện triệu chứng tiếng vo vo.\nNgộ Độc Axit Salicylic - Đau Đầu Nặng Hoặc Liên Tục: Ngộ độc axit salicylic biểu hiện triệu chứng đau đầu nặng hoặc liên tục.\nCảm Thấy Nhẹ Đầu - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng cảm thấy nhẹ đầu.\nAcid Salicylic - Ngộ Độc Salicylate: Acid Salicylic khi dùng quá lâu có thể gây ngộ độc Salicylate.&lt;SEP&gt;Acid salicylic trong thuốc Beprosalic có thể gây ngộ độc salicylate.\nLoét Hoặc Ăn Mòn Da - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây loét hoặc ăn mòn da.\nNhững Triệu Chứng Kích Ứng Da - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây kích ứng da.\nNhững Triệu Chứng Ngộ Độc Axit Salicylic - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây ngộ độc axit salicylic.\nMụn Cơm - Thuốc Dán: Thuốc dán chứa axit salicylic được sử dụng để điều trị mụn cơm.\nChai Ở Gan Bàn Chân - Thuốc Dán: Thuốc dán chứa axit salicylic được sử dụng để điều trị chai ở gan bàn chân.']</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Thuốc trị viêm da axit salicylic có nồng độ trên 10% không được sử dụng cho các đối tượng sau:
+- Vùng da bị nhiễm khuẩn, viêm, hoặc kích ứng.
+- Mặt, bộ phận sinh dục, mũi, miệng, trên nốt ruồi, vết chàm, mụn cơm có lông mọc.
+- Người bệnh bị đái tháo đường hoặc suy giảm tuần hoàn ngoại vi.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nồng độ trên 10% của thuốc trị viêm da axit salicylic không được sử dụng cho đối tượng bệnh nhân bị bẹnh tiểu đường hoặc suy tuần hoàn.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.7056344861207696</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7389086215051924</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>['Alphathepham: Alphathepham là thuốc chứa thành phần tương tự như Alphalysosine.\nBệnh: Bệnh là thuật ngữ chung chỉ tình trạng sức khỏe không tốt, cần được điều trị. Bệnh có thể là kết quả của nhiều yếu tố khác nhau và có thể gây ra lo lắng, đặc biệt là đối với những người chưa có con. Bệnh có thể được phát hiện và điều trị kịp thời nếu nhận thấy dấu hiệu bất thường. Một số bệnh có tiên lượng khá tốt, với khoảng 90% người bệnh được chữa khỏi chỉ bằng kháng sinh và không còn để lại di chứng. Tuy nhiên, cũng có một số bệnh chưa được mô tả cụ thể và có thể tái phát nếu ngừng thuốc sớm.\n\nBệnh có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng các loại thảo dược như cây Đại, Cần Tây, cây Bòng Bong, lá dứa, dền gai, hoa đậu biếc, và hồi đầu thảo. Thông tin về tác dụng của một số loại cây này chưa có nhiều nghiên cứu khoa học rõ ràng. Bệnh có thể xảy ra khi pH nước bọt chệch khỏi phạm vi lý tưởng trong một thời gian dài.\n\nBệnh cũng có thể được điều trị bằng Lô căn hoặc Tiền. Bệnh là tình trạng sức khỏe không bình thường và có thể được theo dõi và điều trị tại nhà nếu nhẹ. Bệnh có thể gây ra triệu chứng ngứa và nổi mề đay.\n\nTóm lại, bệnh là tình trạng sức khỏe không tốt cần được điều trị, có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng các loại thảo dược và dược liệu, cũng như các phương pháp điều trị khác như Lô căn và Tiền.&lt;SEP&gt;Bệnh là thuật ngữ chung để chỉ các trạng thái bệnh lý.&lt;SEP&gt;Bệnh cần được đánh giá tình trạng thông qua các xét nghiệm và kiểm tra y tế.&lt;SEP&gt;Bệnh là tình trạng sức khỏe bất thường cần được điều trị.&lt;SEP&gt;Bệnh là tình trạng mà việc rửa tay kỹ có thể giúp ngăn ngừa.\nAlphachymotrypsin: Alphachymotrypsin là thuốc được sử dụng trong một số trường hợp y tế.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nViêm Nhiễm Sau Phẫu Thuật: Viêm nhiễm sau phẫu thuật là tình trạng mà Alphalysosine được sử dụng để điều trị.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nViêm Nhiễm Sau Chấn Thương: Viêm nhiễm sau chấn thương là tình trạng mà Alphalysosine được sử dụng để điều trị.\nBác Sĩ Chuyên Môn: Bác sĩ chuyên môn là người cung cấp ý kiến và chỉ định về việc sử dụng thổ phục linh.\nCăng Tuyến Vú: Căng tuyến vú là triệu chứng được điều trị bằng Alphalysosine.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nLiệu Phá Hoá Trị: Liệu pháp hoá trị được sử dụng để điều trị AL amyloidosis.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nAL Amyloidosis: AL amyloidosis là dạng bệnh thoái hoá tinh bột được điều trị bằng liệu pháp hoá trị.\nThuốc Hóa Trị: Thuốc hóa trị là loại thuốc dùng trong điều trị ung thư, có khả năng tiêu diệt tế bào ung thư trong các bệnh như Ewing sarcoma. Tuy nhiên, thuốc hóa trị cũng có thể gây ra nhiều tác dụng phụ đáng kể. Chúng có thể làm hỏng mô phổi và gây ra sự nhạy cảm của da. Ngoài ra, một số loại thuốc hóa trị, ví dụ như cisplatin, có thể dẫn đến tình trạng hạ canxi máu. Thuốc hóa trị còn có khả năng làm giảm ham muốn tình dục và khả năng đạt cực khoái, đồng thời cũng ảnh hưởng đến khả năng sinh sản của người bệnh. Mặc dù thuốc hóa trị có khả năng ngăn chặn hệ thống miễn dịch, nhưng việc sử dụng chúng cần được cân nhắc kỹ lưỡng do những tác dụng phụ nghiêm trọng mà chúng có thể gây ra.\nThiểu Năng Gan: Thiểu năng gan là bệnh lý mà Altamin được chỉ định điều trị.\nUng Thư: Ung Thư là một loạt các bệnh liên quan đến sự phát triển không kiểm soát của tế bào, gây ra nhiều biến chứng nghiêm trọng. Đây là bệnh lý nghiêm trọng liên quan đến sự tăng sinh bất thường và mất kiểm soát của tế bào, có thể bắt nguồn từ nhiều nguyên nhân khác nhau, bao gồm cả các tổn thương ngoại sinh dục do bệnh lichen xơ hóa, mặc dù trường hợp này rất hiếm gặp. Ung thư có thể phát triển từ nốt ruồi ác tính và là bệnh rối loạn chuyển hóa tế bào. Nó có thể dẫn đến các triệu chứng như đổ mồ hôi toàn thân và chảy máu tiêu hóa dưới. Bệnh này cũng có thể gây đau ngực sau phẫu thuật cắt lồng ngực và cần được loại trừ khi chẩn đoán đau ngực. Việc sử dụng dầu có điểm sôi thấp trong chiên rán liên tục có thể dẫn đến phát triển ung thư. Ung thư có thể không có triệu chứng ở giai đoạn đầu, nhưng khi nghiêm trọng, nó có thể gây tắc nghẽn, khiến việc nuốt thực phẩm rắn trở nên khó khăn và gây sụt cân. Bệnh ung thư có thể gây lách to, có thể không thể tránh khỏi, và có thể là biến chứng hiếm gặp của loạn sản xơ xương, thường ảnh hưởng đến những người đã từng xạ trị trước đó.\n\nTrong y học hiện đại, ung thư được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng các loại thuốc như Aclasta và Zometa. Trong y học cổ truyền, nhiều loại thảo dược được sử dụng để phòng ngừa và điều trị ung thư, bao gồm Bạch Hoa Xà Thiệt Thảo, Bán Chi Liên, Actiso và chiết xuất từ Atiso đỏ. Ngoài ra, BelafCap, Stevia, và một số thảo dược khác cũng được đề cập như những phương pháp điều trị và phòng chống ung thư. Đông trùng hạ thảo được cho là có khả năng bảo vệ cơ thể chống lại một số loại ung thư và hỗ trợ điều trị bệnh. Dừa cạn cũng được cho là có khả năng điều trị ung thư, với Vinblastin sulfat và Vincristin sulfat chiết xuất từ dừa cạn được sử dụng trong việc hỗ trợ điều trị ung thư. Đương quy được biết đến với tác dụng phòng chống ung thư. Hạt gấc được nghiên cứu như một vị thuốc triển vọng để điều trị ung thư. Hoa đậu biếc, hoa đu đủ đực, lá, hoa và hạt cây hoa phấn, và hoa sói giúp giảm mệt mỏi trong điều trị ung thư. Ngoài ra, ung thư còn có thể được ngăn ngừa và điều trị bằng cách sử dụng kiều mạch và lá bàng tươi. Lô hội cũng được cho là có tiềm năng chống lại ung thư.\n\nNgoài ra, ung thư còn được hỗ trợ điều trị bằng nấm Chaga, triterpenes trong nấm lim xanh, và chiết xuất từ Ngân hạnh. Nghệ được biết đến với khả năng ngăn ngừa ung thư, và Ngọc trúc được sử dụng để ức chế sự tăng sinh của tế bào ung thư vú. Ung thư là bệnh cần loại trừ khả năng khi có tình trạng loét dạ dày trước khi điều trị bằng ranitidin. Ung thư cũng được đề cập trong phần về chất chống oxy hóa và được điều trị bằng axit gallic trong ngũ bội tử. Ung thư cũng có thể là nguyên nhân gây ra triệu chứng nổi hạch dưới hàm và tình trạng nổi hạch cổ, mặc dù đây là triệu chứng hiếm gặp nhưng cũng đáng lưu ý. Ung thư có thể gây ra nổi hạch ở tay và chân. Bệnh này cũng có thể liên quan đến nổi mề đay kéo dài và được phát hiện qua nổi hạch. Ung thư là bệnh lý hiếm gặp nhưng cũng rất nguy hiểm, có thể biểu hiện qua triệu chứng hạch sưng. Bệnh này cũng được hỗ trợ điều trị bằng chiết xuất cồn từ rễ cây sim và rhodomyrtone từ lá sim, cũng như nước ép quýt. Cam quýt có tác dụng chống lại ung thư.\n\nMột số bệnh ung thư có thể gây suy thận mạn tính và suy thượng thận thứ phát. Ung thư là bệnh mà mía dò có hoạt tính tiềm năng chống lại. Tầm bóp rất độc đối với nhiều loại ung thư. Ung thư là tình trạng liên quan đến kích ứng oxy hóa, gây hại cho các tế bào và chức năng hoạt động của cơ thể. Ung thư có thể làm giảm sản xuất men pseudocholinesterase. Ung thư là bệnh mạn tính có thể làm tăng nguy cơ thiếu vitamin C. Chiết xuất tinh dầu từ Thông đỏ được sử dụng để hỗ trợ điều trị một số loại ung thư. Thuốc Aldactone có thể tạo các khối u lành tính, ác tính và không đặc hiệu. Ung thư là bệnh lý có nguy cơ tiềm ẩn từ việc sử dụng Bismuth. Ung thư là bệnh có thể được gây ra bởi thuốc Bismuth, nhưng chưa rõ ràng.\n\nKiểm tra sức khỏe định kỳ nhằm sàng lọc các giai đoạn sớm của ung thư và bệnh ung thư cần được sàng lọc trong khám sức khỏe định kỳ. Ung thư có thể ảnh hưởng đến nhiều bộ phận của cơ thể, bao gồm cả tử cung và cổ tử cung.\nChứng Tăng Aldosterone Nguyên Phát: Chứng tăng aldosterone nguyên phát là bệnh lý được điều trị bằng Aldactone.\nAlpha-Glucosidase Inhibitors - Đái Tháo Đường: Chất ức chế alpha-glucosidase là phương pháp điều trị đái tháo đường.\nBệnh - Thuốc: Thuốc được sử dụng để chữa bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.\nAlphachymotrypsin - Phụ Nữ Mang Thai: Không nên dùng Alphachymotrypsin trên phụ nữ mang thai.\nBệnh - Vị Thuốc: Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được dùng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng trong điều trị bệnh.\nAlphachymotrypsin - Sữa Mẹ: Không nên dùng Alphachymotrypsin trên phụ nữ đang cho con bú.\nBác Sĩ Chuyên Môn - Thuốc: Bác sĩ chuyên môn tư vấn về chỉ định và liều lượng của thuốc.\nAlphalysosine - Viêm Nhiễm Sau Phẫu Thuật: Alphalysosine được sử dụng để điều trị viêm nhiễm sau phẫu thuật.\nBệnh - Dược Liệu: Dược liệu được dùng để điều trị bệnh.&lt;SEP&gt;Dược liệu được sử dụng trong các bài thuốc chữa bệnh.\nAlphalysosine - Viêm Nhiễm Sau Chấn Thương: Alphalysosine được sử dụng để điều trị viêm nhiễm sau chấn thương.\nBác Sĩ - Thuốc: Bác sĩ chỉ định và điều chỉnh liều lượng thuốc cho bệnh nhân.&lt;SEP&gt;Bác sĩ hỗ trợ và xử trí các triệu chứng không mong muốn khi sử dụng thuốc.&lt;SEP&gt;Bác sĩ tư vấn về việc sử dụng thuốc.\nAlphalysosine - Căng Tuyến Vú: Alphalysosine được sử dụng để điều trị căng tuyến vú.\nThuốc Hóa Trị - Ung Thư: Thuốc hóa trị được sử dụng để điều trị ung thư.\nAldactone - Chứng Tăng Aldosterone Nguyên Phát: Aldactone được chỉ định điều trị chứng tăng aldosterone nguyên phát.\nTác Dụng Phụ - Điều Trị: Điều trị nhằm khắc phục và xử lý các tác dụng phụ của thuốc.\nChứng Tăng Aldosterone Nguyên Phát - Spironolactone: Spironolactone được chỉ định điều trị chứng tăng aldosterone nguyên phát.\nDược Sĩ - Thuốc: Dược sĩ tư vấn về việc sử dụng thuốc.\nAltamin - Thiểu Năng Gan: Altamin được chỉ định điều trị thiểu năng gan.\nBệnh Về Tiêu Hóa - Vị Thuốc: Vị thuốc được sử dụng để chữa bệnh về tiêu hóa.\nAlphachymotrypsin - Mebiphar: Mebiphar là công ty sản xuất Alphachymotrypsin.\nThuốc Kháng Sinh - Thủy Đậu Bội Nhiễm: Thuốc kháng sinh được kê toa cho các bệnh nhiễm trùng da và viêm phổi.\nAL Amyloidosis - Liệu Phá Hoá Trị: AL amyloidosis được điều trị bằng liệu pháp hoá trị.']</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp sau:
+- **Viêm nhiễm sau phẫu thuật**: Alphalysosine được sử dụng để điều trị viêm nhiễm sau phẫu thuật.
+- **Viêm nhiễm sau chấn thương**: Alphalysosine cũng được sử dụng để điều trị viêm nhiễm sau chấn thương.
+- **Căng tuyến vú**: Thuốc này được dùng để điều trị triệu chứng căng tuyến vú.
+- **Bệnh trĩ**: Thuốc Alphalysosine có thể được sử dụng trong việc điều trị các bệnh trĩ (bao gồm cả trĩ ngoại và trĩ nội), và sa hậu môn.
+- **Viêm xoang, viêm tai giữa, viêm họng, polyp mũi**: Thuốc cũng được sử dụng để điều trị các bệnh lý về đường hô hấp như viêm xoang, viêm tai giữa, viêm họng, và polyp mũi.
+- **Viêm nha chu, áp xe ổ răng, viêm túi lợi răng khôn**: Thuốc Alphalysosine được sử dụng để điều trị các bệnh về răng miệng như viêm nha chu, áp xe ổ răng, và viêm túi lợi răng khôn.
+- **Xuất huyết ở mắt, đục thủy tinh thể**: Thuốc cũng được sử dụng trong các trường hợp xuất huyết ở mắt, hoặc đục thủy tinh thể.
+- **Những bệnh đường tiết niệu**: Thuốc Alphalysosine có thể được sử dụng trong việc điều trị các bệnh về đường tiết niệu như viêm bàng quang hay viêm mào tinh.
+### Cách dùng và liều dùng
+- **Người lớn**: Sử dụng 1 – 2 viên trong 2 – 3 lần/ngày.
+- **Trẻ em**: Sử dụng theo chỉ dẫn của bác sĩ nhi khoa.
+Người bệnh cần phải sử dụng thuốc Alphalysosine theo đúng như sự kê toa của bác sĩ.
+### Tác dụng phụ
+Trong quá trình điều trị bằng thuốc Alphalysosine, người bệnh có thể gặp phải một số tác dụng phụ ngoài ý muốn như:
+- Hoa mắt, buồn ngủ hoặc chóng mặt.
+- Gây ra tình trạng rối loạn nghiêm trọng chức năng gan/thận.
+- Gây rối loạn tiêu hóa, đau bụng, tiêu chảy, buồn nôn hay nôn.
+### Lưu ý
+Người bệnh cần phải sử dụng thuốc Alphalysosine theo đúng như sự kê toa của bác sĩ để đảm bảo hiệu quả và an toàn.
+### Cách bảo quản
+Thuốc nên được bảo quản ở nhiệt độ không quá 30°C. Bao bì kín, nơi khô, tránh ánh sáng.
+### Tham khảo
+- [1] alphalysosine.txt
+- [2] thuoc-avodart-dutasteride.txt
+- [3] khoai-nua.txt
+- [4] alphachymotrypsin-4200-mebiphar.txt
+- [5] hung-que.txt
+- [6] aluminium-phosphate-gel.txt
+- [7] cong-dung-cua-thot-not.txt
+- [8] ban-co-biet-gi-ve-thuoc-allopurinol-trong-dieu-tri-gout.txt
+- [9] thuoc-bo-than-kinh-h5000-co-tot-khong-gia-thanh-phan-va-cach-su-dung-hieu-qua.txt</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp viêm nhiễm sau phẫu thuật hay sau chấn thương.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.8315580892704135</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.7814189340573092</v>
       </c>
     </row>
   </sheetData>
@@ -664,279 +3928,2102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>question_text</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Naive_Mean</t>
+          <t>user_input</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Naive_Median</t>
+          <t>retrieved_contexts</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Naive_Std</t>
+          <t>response</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Naive_Min</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Naive_Max</t>
+          <t>faithfulness</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mix_Mean</t>
+          <t>answer_relevancy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Mix_Median</t>
+          <t>context_recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Mix_Std</t>
+          <t>context_precision</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mix_Min</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Mix_Max</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Winner</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Difference</t>
+          <t>ragas_score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Faithfulness</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>0.5</v>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Có bắt buộc phải sử dụng thuốc Carbogast trong khi mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>['Carbocistein: Carbocistein là thuốc cốm pha hỗn dịch uống, chứa carbocistein, được chỉ định chính cho các bệnh lý đường hô hấp.&lt;SEP&gt;Carbocistein là sản phẩm có tác dụng làm tan đờm và điều trị bổ trợ các tình trạng rối loạn hô hấp, được chỉ định đơn trị/phối hợp với các bệnh lý như bệnh phổi tắc nghẽn mạn tính (COPD), viêm phế quản, viêm phổi.&lt;SEP&gt;Carbocistein là thuốc được sử dụng để điều trị các vấn đề về hô hấp và tiêu hóa. Cần thận trọng khi sử dụng Carbocistein trên những đối tượng cụ thể như người cao tuổi, người có tiền sử loét dạ dày tá tràng, và người kém hấp thu glucose – galactose.&lt;SEP&gt;Carbocistein là thuốc được bảo quản ở nơi thoáng mát, tránh ẩm thấp, nhiệt độ dưới 25°C. Sản phẩm thường được đóng gói trong 1 hộp 30 gói cốm pha hỗn dịch.&lt;SEP&gt;Carbocistein là thuốc cần thận trọng khi sử dụng do có khả năng gây tác dụng phụ nghiêm trọng và tương tác với một số loại thuốc khác.&lt;SEP&gt;Carbocistein là hoạt chất chính trong Carflem, có tác dụng làm loãng đàm và giảm tiết chất nhầy đường hô hấp.&lt;SEP&gt;Carbocistein là thành phần của các thuốc tương tác với Carflem.\nMẹ Cho Con Bú: Mẹ cho con bú là giai đoạn quan trọng trong cuộc đời của một người mẹ, đòi hỏi sự cẩn trọng khi sử dụng nhiều loại thuốc khác nhau. Trong thời gian này, mẹ có thể sử dụng một số loại thuốc như A.t Ascorbic Syrup, Augtipha, và Azithromycin DHG theo chỉ định của chuyên gia y tế. Tuy nhiên, mẹ cho con bú cần thận trọng khi sử dụng các loại thuốc như A.T.P, A.t Ibuprofen Syrup, Adalat LA 20 mg, và Augbidil. Đặc biệt, mẹ cho con bú không được sử dụng Acnequidt 20 ml, An Cung Ngưu Hoàng Hoàn, Anapa, Andol S Imexpharm, Atinila, Avastin, Becozyme, và thuốc Baby Septol do trẻ sơ sinh rất nhạy cảm với tác dụng độc của những loại thuốc này. Ngoài ra, mẹ cho con bú cũng cần thận trọng khi sử dụng một số loại thuốc khác như Atiliver, Belaf, Benate Fort Ointment, và Azibiotic do chúng có thể đi vào sữa mẹ hoặc chưa có nghiên cứu cụ thể về việc sử dụng chúng trong thời kỳ mẹ cho con bú. Trước khi sử dụng thuốc Antacil, mẹ cho con bú cần hỏi ý kiến bác sĩ. Mẹ cho con bú cũng có thể sử dụng một số loại thuốc an toàn như Adkold – New, Aibezym, Aluminium Phosphate Gel, Aspirin ở liều điều trị bình thường, Aspirin pH8, và Atopiclair dạng lotion.\n\nTrong quá trình cho con bú, mẹ cần cân nhắc giữa lợi ích và nguy cơ trước khi sử dụng bất kỳ loại thuốc nào, đặc biệt là thuốc như Banitase, Babi B.O.N., và Benzyl benzoate. Việc này đòi hỏi mẹ cần tham khảo ý kiến bác sĩ trước khi sử dụng bất kỳ loại thuốc nào để đảm bảo an toàn cho cả mẹ và bé. Mẹ cho con bú là đối tượng cần thận trọng khi sử dụng thuốc chứa corticosteroid và Bilgrel, cần hỏi ý kiến bác sĩ trước khi sử dụng. Mẹ cho con bú không nên sử dụng Bilomag và chỉ nên dùng Bluemint khi thật sự cần thiết và dưới sự theo dõi chặt chẽ của bác sĩ. Chưa có thông tin và minh chứng về việc sử dụng Carbocistein cho mẹ cho con bú, mặc dù mẹ cho con bú cần thận trọng khi sử dụng Carbocistein. Mẹ cho con bú có thể sử dụng Carflem khi cần thiết và có chỉ định của bác sĩ.\n\nMẹ cho con bú là đối tượng không nên sử dụng Cebrex do thiếu dữ liệu lâm sàng về an toàn. Mẹ cho con bú cũng cần cân nhắc về việc ngừng uống thuốc hoặc ngừng cho con bú khi sử dụng Chronol. Mẹ cho con bú có thể sử dụng Cloviracinob khi lợi ích lớn hơn nhiều so với rủi ro. Mẹ cho con bú cũng không được sử dụng Cofidec. Mẹ cho con bú là đối tượng cần thận trọng khi sử dụng clindamycin, vì hiện chưa có dữ liệu về việc thuốc có bài tiết vào sữa mẹ hay không. Không khuyến cáo sử dụng Pregabalin ở phụ nữ đang cho con bú.&lt;SEP&gt;Mẹ cho con bú có thể sử dụng Dentanalgi.\nPhụ Nữ Cho Con Bú: Phụ nữ cho con bú là giai đoạn mà phụ nữ đang nuôi con bằng sữa mẹ. Trong thời gian này, phụ nữ cần đặc biệt chú ý đến việc sử dụng các loại thuốc để đảm bảo an toàn cho cả mẹ và bé. Theo khuyến nghị y tế, phụ nữ cho con bú được khuyên sử dụng A.T Calmax và Acecyst. Tuy nhiên, họ không nên sử dụng A.t Vildagliptin vì hiện tại chưa rõ liệu thuốc này có bài tiết vào sữa mẹ hay không. Các thuốc khác như Acritel, Acnequidt bdd cq 20 ml, và Agietoxib, Agimycob không nên sử dụng vì không có dữ liệu về việc thuốc có vào sữa mẹ. Phụ nữ cho con bú cũng không nên dùng thuốc Alchysin 8400, Aleucin 500 mg, và Etoricoxib do thiếu nghiên cứu về tác động của chúng lên phụ nữ cho con bú. Thuốc Albutein chưa có nghiên cứu về việc sử dụng trên người trong giai đoạn cho con bú. Phụ nữ cho con bú cần thận trọng khi sử dụng thuốc Alpha-Chymotrypsin 4200 IU, AlphaDHG, và Altamin. Họ cũng cần tránh sử dụng Amlodipin, Atorpa-E, và Itraconazole vì những thuốc này có thể gây ra tác dụng phụ nghiêm trọng cho trẻ.\n\nNgoài ra, phụ nữ cho con bú cần cân nhắc giữa nguy cơ và lợi ích khi sử dụng acetylcystein và ranitidin. Họ cũng cần thận trọng khi sử dụng Berberin và thảo dược Bằng Lăng. Phụ nữ cho con bú không phù hợp để sử dụng Acarbose. Việc sử dụng nhiều loại thuốc khác nhau như Ambroxol Boston, Amiparen 5 Otsuka, Amoxicillin Mekophar, Ampicillin, An Thảo, Antacil, Antanazol, Argide, Arthrorein Pharmanel, Artrodar, Atorvastatin, Axit Glutamic, Azaduo, Bactamox, Bagocit, Bisoloc, Allopurinol, Bảo Thanh Hoa Linh, Bảo Thanh, Barudon, Calcigenol, Cefurobiotic, Chalme, Bromelain, Cao Sao Vàng, Ciacca, cỏ Chân vịt, cỏ mật, Cồn Boric, Cosele, Crotamiton, Decolgen Forte, Didicera, Dừa cạn, hoa đậu biếc, Hương thảo, Amoxicillin Brawn, Azicine, Cotrimoxazol, Atocib 90, Mật nhân, men vi sinh Antibio, và Nhũ hương cần được cân nhắc kỹ lưỡng giữa lợi ích và nguy cơ tiềm ẩn. Phụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi dùng bất kỳ loại thuốc nào để đảm bảo an toàn cho trẻ.\n\nPhụ nữ cho con bú cũng nên tránh sử dụng Aceclofenac, Acnotin, Albendazol, và Aluvia trong giai đoạn đang cho con bú. Họ cũng cần hết sức thận trọng khi dùng Amiodarone và Amitriptyline. Phụ nữ cho con bú cần cân nhắc giữa lợi ích điều trị cho người mẹ và nguy cơ cho trẻ. Ngoài ra, phụ nữ cho con bú là chống chỉ định khi sử dụng Antituss Plus và Hydroxyzin. Phụ nữ cho con bú cũng cần lưu ý khi sử dụng Bepanthen vì hiện chưa có dữ liệu cụ thể về ảnh hưởng của Bepanthen đến phụ nữ cho con bú. Phụ nữ cho con bú cần thận trọng khi dùng Betahistine và không được khuyến nghị sử dụng thuốc Bifril.\n\nPhụ nữ cho con bú nên thận trọng khi sử dụng Bisacodyl vì thuốc có thể đi qua sữa mẹ. Phụ nữ cho con bú cần sử dụng thuốc Bổ Huyết Ích Não một cách cẩn thận. Phụ nữ cho con bú có thể sử dụng Boganic. Phụ nữ cho con bú cần lưu ý trước khi dùng thuốc Bolutin. Vẫn chưa có nghiên cứu đặc biệt nào về việc bài tiết thuốc này qua sữa. Phụ nữ cho con bú có thể truyền thuốc Brufen qua sữa mẹ với hàm lượng thấp. Phụ nữ cho con bú nên tránh sử dụng Brufen do thuốc có thể đi qua sữa mẹ.\n\nPhụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Cafein và Candesartan. Họ cũng cần cân nhắc việc ngừng cho con bú hay ngừng thuốc Captopril. Phụ nữ cho con bú cần cân nhắc kỹ giữa lợi ích và nguy cơ khi dùng Casalmux. Họ cũng cần thận trọng khi sử dụng Cefaclor do thiếu bằng chứng đầy đủ về tác động của thuốc. Phụ nữ cho con bú cần thận trọng khi sử dụng Cefadroxil vì thuốc này có thể bài tiết trong sữa mẹ với nồng độ thấp. Họ cũng cần cân nhắc việc ngừng cho con bú nhất thời khi dùng cefalexin.\n\nPhụ nữ cho con bú cần thận trọng khi sử dụng Clonazepam. Phụ nữ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Chophytol. Phụ nữ cho con bú cần tránh dùng thuốc để đảm bảo an toàn cho trẻ nhỏ. Phụ nữ cho con bú cần tránh dùng Cimetidin để đảm bảo an toàn cho trẻ. Phụ nữ cho con bú cần thận trọng khi dùng thuốc cisaprid vì thuốc bài tiết qua sữa mẹ. Phụ nữ cho con bú cần cân nhắc giữa nguy cơ và lợi ích khi sử dụng Clotrimazole do chưa biết liệu Clotrimazole có bài tiết qua sữa mẹ hay không.\n\nPhụ nữ cho con bú không nên sử dụng Coltramyl. Đặc biệt, phụ nữ cho con bú chống chỉ định sử dụng Diane-35. Phụ nữ cho con bú là đối tượng đặc biệt cần tư vấn và đồng ý từ bác sĩ trước khi sử dụng benzalkonium chloride. Phụ nữ cho con bú cần cân nhắc kỹ lưỡng khi sử dụng tocilizumab và Actemra. Phụ nữ cho con bú không nên sử dụng thuốc Aescin. Phụ nữ cho con bú cũng không nên sử dụng Advil. Phụ nữ cho con bú không nên sử dụng moxifloxacin.\n\nPhụ nữ cho con bú là đối tượng chống chỉ định sử dụng Rosuvastatin và cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hoa cam. Phụ nữ cho con bú không khuyến khích sử dụng tinh dầu hồi. Phụ nữ cho con bú cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hương thảo. Phụ nữ cho con bú cần thận trọng khi sử dụng tinh dầu.\n\nPhụ nữ cho con bú cần tránh sử dụng tragacanth. Phụ nữ cho con bú cần thận trọng khi sử dụng Tỳ giải.\nPhụ Nữ Mang Thai: Phụ nữ mang thai là giai đoạn đặc biệt trong đó phụ nữ đang怀上怀孕，并 cần phải chú ý đến việc sử dụng các loại thuốc và phương pháp điều trị để đảm bảo an toàn cho cả mẹ và thai nhi. Trong thời gian mang thai, phụ nữ nên tránh sử dụng một số loại thuốc cụ thể vì chúng có thể gây hại cho sức khỏe của mẹ và thai nhi. Các loại thuốc cần tránh bao gồm Vildagliptin (A.t Vildagliptin), Bagocit, Azaduo, Acecyst, Acetylcysteine 200mg Stada, Aclasta, Acritel, Acyclovir Stada 200 mg, Agiclovir 5% Agimexpharm, Alchysin 8400, Agimycob, Ampicillin, An Thảo, Atorvastatin, Pregabalin, Decolgen Forte, Didicera, và nhiều loại khác. Đặc biệt, phụ nữ mang thai nên tránh sử dụng Agimycob và Alchysin 8400 trong ba tháng đầu tiên vì những loại thuốc này có thể ảnh hưởng đến sự phát triển bình thường của thai nhi.\n\nNgoài ra, phụ nữ mang thai cũng cần thận trọng khi sử dụng một số loại thuốc khác như Acetylcysteine 200mg Stada, Acyclovir Stada 200 mg, Agiclovir 5% Agimexpharm, Amoxicillin Brawn, Chloramphenicol, Captopril, Cefadroxil, Cefalexin, và một số loại thảo dược như Đông trùng hạ thảo, Long diệp, Mộc hoa. Việc sử dụng những loại thuốc và thảo dược này cần được giám sát chặt chẽ bởi bác sĩ vì chưa có đủ nghiên cứu về tác động của chúng lên thai nhi.\n\nPhụ nữ mang thai còn cần lưu ý đến một số vấn đề sức khỏe khác ngoài việc sử dụng thuốc. Họ có nguy cơ cao mắc phải biến chứng từ thủy đậu, đặc biệt là trong ba tháng đầu tiên. Nếu nhiễm thủy đậu trong ba tháng đầu, phụ nữ mang thai có thể đối mặt với rủi ro sinh non, sẩy thai, hoặc thai chết lưu. Ngoài ra, họ cũng cần được kiểm tra và điều trị kịp thời nếu mắc bệnh lây truyền qua đường tình dục như lậu và giang mai để ngăn ngừa việc truyền bệnh cho thai nhi.\n\nDo sự thay đổi hormone trong cơ thể, phụ nữ mang thai dễ bị mắc các bệnh da liễu như nhiễm nấm và bệnh Listeria. Nguy cơ mắc bệnh Listeria và các bệnh liên quan khác cũng cao hơn. Họ cần tránh ăn mận da và sử dụng kháng sinh một cách thận trọng. Việc tiêu thụ quá nhiều đường đỏ và syrup ngô ngọt cũng có thể gây rủi ro. Phụ nữ mang thai cũng cần tránh sử dụng nấm Linh chi và các loại thuốc như Hoàng Liên và Chloroquine vì chúng không an toàn trong thai kỳ. Họ cũng có thể truyền virus Rubella cho thai nhi thông qua nhau.\n\nBên cạnh việc chú ý đến việc sử dụng thuốc, phụ nữ mang thai cũng cần quan tâm đến một số vấn đề sức khỏe khác như co bóp tử cung, nguy cơ mắc bệnh sốt rét tăng cao, và suy giảm chức năng tuyến yên. Trong một số trường hợp, phụ nữ mang thai có thể cần sử dụng insulin để duy trì mức đường huyết ổn định, đặc biệt là khi chế độ ăn uống không thể đạt được mục tiêu đường huyết. Họ cũng cần tránh sử dụng các loại thuốc như Giao Thái Minh, Ngũ Gia Bì, và Acid Ipratropium vì chúng không an toàn trong thai kỳ. Khi sử dụng Amitriptyline và Erythromycin, phụ nữ mang thai cần đặc biệt cẩn trọng và nên tham khảo ý kiến của bác sĩ trước khi sử dụng.\n\nCuối cùng, phụ nữ mang thai cũng cần cân nhắc kỹ trước khi sử dụng Alpha Brain, một chất bổ sung não, vì nó có thể gây ra các tác động tiềm ẩn không rõ ràng. Phụ nữ mang thai cũng cần thận trọng khi sử dụng tinh dầu oải hương, tinh dầu hồi, tinh dầu hương thảo, và tinh dầu Agarwood. Đặc biệt, phụ nữ mang thai cần tránh sử dụng tinh dầu hồi và Agarwood, và cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu oải hương và hương thảo. Phụ nữ mang thai cũng cần tránh sử dụng tragacanth.\n\nPhụ nữ mang thai là đối tượng nhạy cảm cần được bổ sung nguyên liệu tạo máu và tầm soát các bệnh lý di truyền.\nCho Con Bú: Cho con bú là giai đoạn sau sinh sản mà phụ nữ nuôi dưỡng trẻ sơ sinh bằng sữa mẹ. Đây là một thời kỳ quan trọng đòi hỏi người mẹ phải đặc biệt chú ý đến chế độ dinh dưỡng và việc sử dụng thuốc. Trong thời gian này, người mẹ cần bổ sung canxi để đáp ứng nhu cầu cao của cơ thể, được hỗ trợ bằng Calcium Corbiere Extra. Oxytocin kích thích tiết sữa, giúp duy trì nguồn sữa mẹ ổn định.\n\nCho con bú là giai đoạn chống chỉ định sử dụng nhiều loại thuốc như Acyclovir Boston 800, Adalat LA 20 mg, Alpha-Chymotrypsin 4200 IU, Alpha-Kiisin, Ameflu đa triệu chứng, Amlor 5 Pfizer, Atorhasan, Atorlog, Avarino 300 Mega, Atiso đỏ, Bibonlax, và Clopidogrel vì chúng có thể gây hại cho trẻ sơ sinh. Một số loại thuốc khác như Cefimbrano, Coldko, Coveram, và Crinone cũng được khuyến nghị tránh sử dụng hoặc cần thận trọng khi sử dụng. Các loại thuốc như amoxicillin kết hợp với acid clavulanid được cho phép sử dụng trong thời kỳ cho con bú vì chúng không gây hại cho trẻ sơ sinh. Phụ nữ cho con bú cũng cần tham khảo ý kiến của bác sĩ trước khi sử dụng Cerecaps và Children’s Tylenol để đảm bảo an toàn cho cả mẹ và bé. Ngoài ra, phụ nữ cho con bú có thể sử dụng thuốc Auclanityl nhưng cần thận trọng vì thuốc có thể truyền vào sữa mẹ. Cho con bú cũng là thời kỳ cần cân nhắc kỹ lưỡng khi sử dụng gel Contractubex và không nên dùng hoắc hương hoặc hồng bì vì những loại thuốc này có thể gây hại hoặc không được khuyến nghị trong giai đoạn này.\n\nThời kỳ cho con bú cũng cần thận trọng khi sử dụng thuốc Ameflu, Arcoxia, và Betmiga 50 mg do thiếu bằng chứng về việc etoricoxib bài tiết qua sữa ở người và khả năng thuốc có thể bài tiết vào sữa mẹ. Cho con bú cũng là giai đoạn không khuyến nghị sử dụng Khúc khắc và Aerius. Ngoài ra, phụ nữ cho con bú cần kiêng kỵ khi sử dụng Rau Càng cua và Cà độc dược vì những loại thực phẩm này có thể gây bất lợi cho sự phát triển của trẻ. Đồng thời, việc sử dụng Sa kê chưa có bằng chứng về sự an toàn. Cho con bú cũng là giai đoạn cần thận trọng khi sử dụng thuốc 3B Medi và Acid nalidixic. Phụ nữ cho con bú không nên sử dụng nhân trần trừ khi có vấn đề về gan, và cũng không nên sử dụng nhũ hương. Việc sử dụng lá Thường xuân trong giai đoạn này cần được bác sĩ tư vấn. Cuối cùng, người đang cho con bú không nên sử dụng rau mùi tây và không nên thực hiện hành động cho con bú khi sử dụng Meloxicam.\n\nBifril không được khuyến cáo sử dụng trong giai đoạn đang cho con bú. Cho con bú cũng là chống chỉ định của thuốc Bismuth. Người cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango. Phụ nữ cho con bú không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi. Đang cho con bú là yếu tố cần báo với bác sĩ khi sử dụng Carbotrim. Cho con bú là tình trạng cần thận trọng khi sử dụng Cefprozil và Ceftriaxone. Cho con bú là giai đoạn mà việc sử dụng celecoxib có thể bài tiết vào sữa mẹ và gây tác dụng xấu đối với trẻ nhỏ. Người mẹ đang cho con bú cần tránh sử dụng Ceritine. Mẹ đang cho con bú có thể bị ảnh hưởng bởi việc sử dụng Chymobest. Cho con bú là giai đoạn mà việc sử dụng Clarityne cần được đánh giá cẩn thận.\n\nCho con bú là tình trạng cần thông báo cho bác sĩ trước khi sử dụng CoAprovel. Cho con bú là chống chỉ định khi sử dụng Co aprovel. Phụ nữ cho con bú không nên sử dụng Co-Diovan. Cho con bú là giai đoạn mà phụ nữ đang nuôi dưỡng trẻ sơ sinh bằng sữa mẹ. Cho con bú là giai đoạn cần thận trọng khi sử dụng thuốc. Người đang cho con bú không nên sử dụng Coldi B. Cho con bú cũng là giai đoạn chống chỉ định sử dụng Irbesartan.&lt;SEP&gt;Người đang cho con bú cần cẩn trọng khi sử dụng tinh dầu.&lt;SEP&gt;Cho con bú là tình trạng cần thận trọng khi sử dụng tinh dầu quýt.\nSử Dụng Thuốc: Sử dụng thuốc cần tuân thủ hướng dẫn sử dụng về liều dùng, cách dùng của nhà sản xuất hoặc theo chỉ định của bác sĩ.&lt;SEP&gt;Sử dụng thuốc, rượu hoặc đồ ăn để đối phó là một dấu hiệu hành vi của kiệt sức.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị bệnh.&lt;SEP&gt;Sử dụng thuốc có thể gây khô miệng.&lt;SEP&gt;Sử dụng thuốc có thể gây tác dụng phụ như mất thăng bằng hoặc mất vững.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị nội khoa, giúp kiểm soát triệu chứng.&lt;SEP&gt;Sử dụng thuốc Benzalkonium Chloride theo hướng dẫn cụ thể.\nCarbomango: Carbomango là thuốc cần có sự hướng dẫn của bác sĩ điều trị.&lt;SEP&gt;Carbomango là thuốc cần được điều chỉnh liều lượng phù hợp với độ tuổi và triệu chứng bệnh của từng bệnh nhân.&lt;SEP&gt;Carbomango là thuốc cần được hỏi ý kiến bác sĩ trước khi sử dụng, đặc biệt đối với phụ nữ có thai và cho con bú. Thuốc không ảnh hưởng đến khả năng lái xe và vận hành máy móc.&lt;SEP&gt;Carbomango là thuốc thuộc nhóm thuốc giải độc cơ thể, chứa các thành phần như than hoạt tính, kha tử, măng cụt, gelatin, natri benzoat, và tinh bột sắn.&lt;SEP&gt;Carbomango là thuốc không kê đơn được sử dụng để điều trị tiêu chảy cấp.\nAspartam: Aspartam là một loại đường nhân tạo ít calo, có độ ngọt cao gấp 200 lần đường bình thường. Nó được sử dụng như một chất tạo vị ngọt chính trong nhiều sản phẩm khác nhau, bao gồm cả Aspartam Pharmedic và Acnekyn. Aspartam có thể chuyển hóa thành phenylalanin trong hệ thống tiêu hóa. Chất này cũng có thể chứa trong một số dạng acetaminophen.\n\nNgười bị mắc bệnh phenylceton niệu cần đặc biệt thận trọng khi sử dụng Aspartam vì nó có thể gây ra các phản ứng bất lợi. Điều này là do khả năng chuyển hóa của Aspartam thành phenylalanin có thể ảnh hưởng đến sức khỏe của những người mắc bệnh này.&lt;SEP&gt;Aspartam là tá dược trong Boston C 1000.&lt;SEP&gt;Aspartam là chất tạo ngọt chứa phenylalanin, có thể gây hại cho những người bị phenylceton niệu.&lt;SEP&gt;Aspartam là chất có chứa phenylalanin cần tránh sử dụng cùng với Paracetamol.&lt;SEP&gt;Aspartam là chất tạo ngọt có thể chuyển hóa trong đường tiêu hóa thành phenylalanin, cần được kiểm soát lượng phenylalanin khi sử dụng.\nBreastfeeding mothers: Phụ nữ cho con bú cần thận trọng khi sử dụng Aspartam do thành phần chuyển hóa của nó có thể xuất hiện trong sữa mẹ.\nCarbocistein - Mẹ Cho Con Bú: Chưa có thông tin và minh chứng về việc sử dụng Carbocistein cho mẹ cho con bú.&lt;SEP&gt;Nên tránh sử dụng Carbocistein cho mẹ cho con bú.\nPhụ Nữ Cho Con Bú - Phụ Nữ Mang Thai: Phụ nữ mang thai và cho con bú cần tránh dùng thuốc để đảm bảo an toàn cho trẻ nhỏ.\nCho Con Bú - Sử Dụng Thuốc: Người đang cho con bú cần cẩn thận khi sử dụng thuốc.&lt;SEP&gt;Người đang cho con bú cần tham khảo ý kiến bác sĩ trước khi sử dụng thuốc.\nCarbomango - Cho Con Bú: Người cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango.\nAspartam - Breastfeeding mothers: Phụ nữ cho con bú cần thận trọng khi sử dụng Aspartam.\nSữa Mẹ - Thai Nhi: Thuốc có thể được bài tiết qua sữa mẹ ảnh hưởng đến thai nhi.\nDược Liệu - Người Đang Cho Con Bú: Người đang cho con bú cần cẩn trọng khi dùng dược liệu.\nPhụ Nữ Có Thai - Phụ Nữ Đang Cho Con Bú: Phụ nữ có thai và phụ nữ đang cho con bú đều cần thông báo với bác sĩ trước khi dùng thuốc.\nCarbotrim - Cho Con Bú: Đang cho con bú là yếu tố cần báo với bác sĩ khi sử dụng Carbotrim.\nCarbimazol - Chức Năng Giáp: Carbimazol cần sử dụng liều thấp nhất để duy trì chức năng giáp của người mẹ.']</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Theo tài liệu cung cấp, thuốc Carbogast có thể được sử dụng cho phụ nữ trong giai đoạn mang thai và cho con bú với liều lượng cho phép. Tuy nhiên, việc sử dụng thuốc này trong hai giai đoạn này cần được sự chấp thuận của bác sĩ. Điều này nhằm đảm bảo rằng việc sử dụng thuốc sẽ không gây hại cho sức khỏe của mẹ và thai nhi.
+Việc sử dụng Carbogast trong thời kỳ mang thai và cho con bú không được bắt buộc, nhưng nếu cần thiết, người mẹ cần hỏi ý kiến bác sĩ để được tư vấn kỹ lưỡng về việc sử dụng thuốc này.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Không bắt buộc, nên dùng thuốc theo đúng chỉ định của bác sĩ.</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6667</v>
+        <v>0.8150201504201028</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
       </c>
       <c r="K2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Mix</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1667</v>
+        <v>0.8912550375800257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Answer Relevancy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ngoài giảm đau, Acepron 250 mg còn có thêm tác dụng nào khác?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>["Hệ Máu: Hệ máu là hệ thống chịu ảnh hưởng từ tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg: Acepron 250 mg là thuốc được sản xuất bởi Công ty Cổ phần Dược phẩm Cửu Long, chứa paracetamol, được chỉ định để điều trị các chứng đau và sốt từ nhẹ đến vừa.&lt;SEP&gt;Acepron 250 mg là thuốc dùng để điều trị sốt và giảm các triệu chứng đau từ nhẹ tới vừa.&lt;SEP&gt;Acepron 250 mg là sản phẩm chứa acetaminophen có chống chỉ định sử dụng ở người bệnh tim, thận, phổi, gan và nhiều lần thiếu máu.&lt;SEP&gt;Acepron 250 mg là thuốc có tác dụng phụ như giảm bạch cầu, giảm toàn thể huyết cầu, giảm tiểu cầu, nôn, ban da, buồn nôn, loạn tạo máu, thiếu máu, bệnh thận và độc tính trên thận.&lt;SEP&gt;Acepron 250 mg là thuốc cần được sử dụng đúng liều lượng và thời gian theo hướng dẫn.\nPhenylceton – niệu: Phenylceton – niệu là tình trạng cần thận trọng khi sử dụng Acepron 250 mg.\nGiảm Tiểu Cầu: Giảm Tiểu Cầu là một tình trạng y tế hiếm gặp, đặc trưng bởi sự giảm sút số lượng tiểu cầu trong máu, gây ra các vấn đề về sức khỏe liên quan đến máu. Tình trạng này thường xuất hiện như một tác dụng phụ khi sử dụng một số loại thuốc cụ thể, bao gồm Acepron 250 mg, Alzental, Alzental Shinpoong, Alzole, Alzyltex, Amikacin Bidiphar, Amoxicillin Domesco, Ampicillin, Ampicillin Brawn, Ampicillin Mekophar, Andol S, Argide, Aspirin pH8, Aspirin STELLA, Aspirin Vidipha, Aticef, Ayite, Mebendazole, Buclapoxime Tablets, acid tranexamic, Cefimbrano 100, Celecoxib, Coldacmin, trimethoprim, Diamicron, Cotrimoxazol, Chloramphenicol, Bixicam, Acid nalidixic, Isotretinoin, Albendazol, và Amitriptylin. Coldacmin được ghi nhận là có tác dụng phụ Giảm Tiểu Cầu thường gặp hơn so với Celecoxib và Diamicron, mà hai loại thuốc này được ghi nhận với tác dụng phụ Giảm Tiểu Cầu hiếm gặp. \n\nGiảm Tiểu Cầu cũng được coi là một chống chỉ định khi sử dụng một số loại thuốc như Aspirin pH8, Aspirin STELLA, và Aspirin Vidipha do khả năng gây ra tình trạng thiếu hụt số lượng tiểu cầu trong máu. Tình trạng này cũng được mô tả là một tác dụng phụ ít gặp, không phổ biến trong quá trình điều trị bằng các loại thuốc nêu trên. Ngoài ra, Giảm Tiểu Cầu còn được xem như là một rối loạn hệ máu và hệ bạch huyết, thể hiện qua các triệu chứng liên quan đến máu và bạch huyết.\n\nNgoài việc là tác dụng phụ của một số loại thuốc, Giảm Tiểu Cầu cũng có thể xảy ra do nhiễm khuẩn ít gặp. Tình trạng này được đặc trưng bởi các triệu chứng liên quan đến máu và bạch huyết, thể hiện qua sự giảm sút số lượng tiểu cầu trong máu. Một số tác dụng phụ khác của Giảm Tiểu Cầu bao gồm giảm bạch cầu, tăng bạch cầu ưu eosin, và thiếu máu tan máu, nhất là ở người thiếu hụt glucose 6 phosphat dehydrogenase. Giảm Tiểu Cầu cũng có thể là tác dụng phụ của các loại thuốc khác như Augmentin 500 mg/62,5 mg, Carbotrim, Cataflam, và Cefaclor. Tác dụng phụ này cũng được ghi nhận là hiếm gặp khi sử dụng Ceritine.&lt;SEP&gt;Giảm tiểu cầu là triệu chứng liên quan đến việc sử dụng thuốc.&lt;SEP&gt;Giảm tiểu cầu là một triệu chứng của tiền sản giật.&lt;SEP&gt;Giảm tiểu cầu là triệu chứng liên quan đến bệnh lý.\nGiảm Toàn Thể Huyết Cầu: Giảm toàn thể huyết cầu là một tác dụng phụ có thể xảy ra khi sử dụng một số loại thuốc như Acepron 250 mg, Andol S, và Coldacmin. Đây là tác dụng phụ thường gặp của Coldacmin và cũng là triệu chứng của tác dụng không mong muốn của Cloramphenicol. Ngoài ra, giảm toàn thể huyết cầu còn là tác dụng phụ hiếm gặp khi sử dụng các thuốc khác như Albendazol, Chloramphenicol, Celecoxib, và Cimetidin. Tác dụng phụ này có thể xuất hiện với tần suất khác nhau tùy thuộc vào loại thuốc được sử dụng.\nĐộc Tính Trên Thận: Độc tính trên thận là tác dụng phụ của Acepron 250 mg.&lt;SEP&gt;Độc tính trên thận là tác dụng phụ có thể xảy ra khi sử dụng Acyclovir Stada 200 mg cùng với Cyclosporin.&lt;SEP&gt;Độc tính trên thận là tác dụng phụ thường gặp khi sử dụng thuốc.\nĐau Cơ: Đau Cơ là một triệu chứng đa dạng và phức tạp, có thể xuất hiện do nhiều nguyên nhân khác nhau, bao gồm cả tác dụng phụ của thuốc và các bệnh lý cụ thể. Đây là một triệu chứng phổ biến và tác dụng phụ thường gặp khi sử dụng nhiều loại thuốc khác nhau như Aclasta, Agietoxib, Agilosart, Atorhasan, Atorvastatin T.V Pharm, Audocals, Bagocit, và Desloratadine. Đặc biệt, Desloratadine trong Audocals được ghi nhận là tác dụng phụ hiếm gặp, trong khi Rosuvastatin trong Bonzacim gây đau cơ nghiêm trọng và cần được báo cáo với bác sĩ trước khi sử dụng Bonzacim. Đau Cơ cũng là một trong những triệu chứng của bệnh cúm, bệnh Lyme, và bệnh dại.\n\nĐau Cơ cũng là một rối loạn hệ cơ xương khớp và mô liên kết, đồng thời là một dấu hiệu của kiệt sức và có thể xảy ra do tăng canxi huyết. Đau Cơ là tác dụng không mong muốn của Calcium Corbiere Extra và Cilzec. Trong cuộc sống hàng ngày, Đau Cơ là triệu chứng thường gặp và có thể được giảm đau bằng cao dán Yaguchi hoặc Children's Tylenol. Các nguyên nhân khác của Đau Cơ bao gồm sự co lại liên tục của cơ, tư thế sai, sự yếu cơ, chấn thương, hoặc chiều dài chân không đều. Đau Cơ cũng là một trong các tác dụng không mong muốn sau tiêm vaccine và là triệu chứng của hội chứng sốc nhiễm độc. Ngoài ra, Đau Cơ còn có thể xuất hiện khi ngừng sử dụng Dexamethasone và Argadin.\n\nĐau Cơ cũng được biết đến là tác dụng phụ hiếm gặp khi sử dụng aciclovir, aerius, và atarax. Thuốc khác như isotretinoin và Atorvastatin cũng có thể gây ra triệu chứng này. Tại Ấn Độ, lá Rau Mương được sử dụng để điều trị triệu chứng Đau Cơ.\n\nNgoài ra, Đau Cơ còn có thể liên quan đến tình trạng thiếu hụt Biotin và là tác dụng phụ của các thuốc như Captopril, Carbimazol, Cialis, Tadalafil, Cimetidin, và Co-Diovan. Tuy nhiên, mức độ phổ biến của Đau Cơ như tác dụng phụ của Co-Diovan có thể thay đổi từ ít gặp đến thường gặp tùy thuộc vào từng trường hợp cụ thể.\n\nĐau Cơ có thể xuất hiện do nhiều nguyên nhân khác nhau, cần tới bác sĩ chuyên khoa Cơ – Xương khớp để được chẩn đoán và điều trị đúng bệnh.&lt;SEP&gt;Đau cơ là biểu hiện của quá liều mạn tính của thuốc.&lt;SEP&gt;Đau cơ là triệu chứng được tinh dầu hương thảo hỗ trợ điều trị.\nĐau Nhức Do Cảm Cúm: Đau nhức do cảm cúm là một trong những chứng đau được điều trị bằng Acepron 250 mg.&lt;SEP&gt;Đau nhức do cảm cúm là triệu chứng đau từ nhẹ tới vừa, được điều trị bằng Acepron 250 mg.\nBan Da: Ban da là một tác dụng phụ thường gặp hoặc ít gặp khi sử dụng nhiều loại thuốc khác nhau. Nó có thể xuất hiện dưới nhiều hình thức như ban đỏ, mày đay, hồng ban đa dạng, hội chứng Stevens-Johnson, và hoại tử thượng bì nhiễm độc. Ban da là một trong những tác dụng phụ phổ biến nhất khi sử dụng một loạt các loại thuốc như Acepron 250 mg, Acnekyn, Acyclovir Stella 400 mg, Acyclovir Stella 800 mg, Allopurinol, Alzental, và Alzental Shinpoong. Ngoài ra, nó cũng là tác dụng phụ có thể gặp khi sử dụng Arthrorein Pharmanel, Ayite, Cedipect F, và Diamicron. Tuy nhiên, cần lưu ý rằng ban da cũng có thể là một tác dụng phụ hiếm gặp của một số loại thuốc khác, như Bolutin, Carbimazol, Cordarone, và Irbesartan. \n\nBan da còn có thể là triệu chứng của vảy nến, được biểu hiện qua ban da màu hồng tươi, giới hạn khá rõ, kèm theo tróc vảy trắng, mịn. Đồng thời, ban da cũng có thể giúp chẩn đoán bệnh Pellagra. Trong một số trường hợp, ban da có thể được xem như một triệu chứng để điều trị bằng Canh châu.\n\nTrên đây là tổng hợp về ban da, bao gồm cả tác dụng phụ của nhiều loại thuốc khác nhau và các tình trạng y tế cụ thể mà ban da có thể là dấu hiệu của.\nG6PD: Acepron 250 mg chống chỉ định sử dụng ở người thiếu hụt G6PD.&lt;SEP&gt;G6PD là enzym thiếu hụt có thể gây nguy hiểm khi sử dụng vitamin C quá liều.\nĐau Đầu: Đau đầu là một triệu chứng cảm giác đau tại vùng đầu, có thể xuất hiện do nhiều nguyên nhân khác nhau. Đây là triệu chứng của nhiều bệnh lý khác nhau, bao gồm bệnh Brucellosis, bệnh Lyme, rối loạn chuyển hóa, bệnh cảm cúm, bệnh COVID-19, bệnh phóng xạ cấp tính, bệnh Menière, suy thượng thận thứ phát, suy nhược thần kinh, u tuyến yên hoặc hạ đồi, tăng huyết áp ác tính, và tăng bạch cầu đơn nhân nhiễm khuẩn. Đau đầu cũng là triệu chứng tiền triệu của bệnh dại và giả u não, và có thể là tác dụng phụ của việc sử dụng quá liều nhiều loại thuốc khác nhau. Đau đầu còn là triệu chứng của nhiều bệnh lý khác, bao gồm bệnh Listeria, thể bệnh Tăng huyết áp thể Âm hư dương vượng, viêm phần phụ hoặc các bệnh lý khác liên quan đến ngứa vùng kín khi mang thai, nhiễm trùng hô hấp trên và viêm họng. Ngoài ra, đau đầu còn là triệu chứng của nhịp tim chậm và ung thư vòm mũi họng. Nó cũng là triệu chứng của hội chứng serotonin và hội chứng sốc nhiễm độc. Trong các trường hợp khác, đau đầu là triệu chứng của tăng huyết áp, tăng canxi huyết và quá liều vitamin D, bệnh Brucellosis và Lyme, rối loạn chuyển hóa, mất máu hoặc thiếu máu, hội chứng sốc nhiễm độc, và tình trạng khớp hàm thái dương (TMJ).\n\nĐau đầu cũng là triệu chứng của nhiều tình trạng khác, bao gồm hội chứng sốc nhiễm độc, tăng huyết áp, bệnh Brucellosis, Lyme, rối loạn chuyển hóa, mất máu hoặc thiếu máu, hội chứng sốc nhiễm độc, tăng canxi huyết và quá liều vitamin D, bệnh Brucellosis và Lyme, rối loạn chuyển hóa, và mức kali thấp do cường aldosterone nguyên phát. Đau đầu cũng là triệu chứng của nhiễm độc từ việc sử dụng Ô đầu hoặc Phụ tử, và nó cũng là triệu chứng của nhiễm độc từ Ô đầu và Phụ tử. Đau đầu cũng là triệu chứng của nghiến răng, đặc biệt khi ngủ. Đau đầu cũng là triệu chứng của ăng magiê và rối loạn cân bằng bicarbonate, và cũng là triệu chứng thực thể của rối loạn lo âu chia ly. Đau đầu cũng là triệu chứng của suy hô hấp do tăng nồng độ CO2 trong máu, và cũng là triệu chứng của suy thượng thận thứ phát.\n\nĐau đầu cũng là tác dụng phụ thường gặp khi sử dụng nhiều loại thuốc khác nhau, như Betahistine, Betaserc, Aspegic, Augen Extra, Biotin, Bolutin, Betex, Betmiga, Bifril, và nhiều loại thuốc khác. Đau đầu cũng là triệu chứng phổ biến của nhiều bệnh lý, bao gồm bệnh Menière, suy tuần hoàn não, hội chứng HELLP, mất nước và tiêu chảy, tiền kinh nguyệt, và nhiều bệnh lý khác. Đau đầu cũng là triệu chứng ở giai đoạn cuối của ung thư phổi, cùng với các triệu chứng khác như yếu hoặc tê cánh tay hoặc chân, chóng mặt, các vấn đề cân bằng hoặc co giật.\n\nĐau đầu cũng có thể là triệu chứng của tụt huyết áp.\nMọc Răng: Mọc răng là một dạng sốt do mọc răng, được điều trị bằng Acepron 250 mg.\nGiảm Bạch Cầu: Giảm bạch cầu là một tình trạng y tế nghiêm trọng và hiếm gặp, liên quan đến việc số lượng bạch cầu trong máu giảm xuống mức thấp nguy hiểm. Tình trạng này thường xuất hiện như một tác dụng phụ của nhiều loại thuốc khác nhau, bao gồm Amoxicillin Flamingo, Ampicillin Brawn, Ampicillin Mekophar, Ampicillin, Apitim, Aspirin Vidipha, Augbactam, Augtipha, Ayite, Mebendazole, Biseptol, Prozil, Brudoxil, Brodicef, Buclapoxime Tablets, Clopidogrel, Cefimbrano 100, Cefurobiotic, và Cefuroxim. Ngoài ra, nó cũng được xác định là tác dụng phụ hiếm gặp khi sử dụng Celecoxib, Diamicron, Adagrin, và Argadin. Giảm bạch cầu cũng được ghi nhận là tác dụng phụ của Cotrimoxazol, liệu pháp kháng u, và thuốc Berberin. Chloramphenicol, Bixicam, và Isotretinoin cũng được ghi nhận là nguyên nhân gây ra tình trạng giảm bạch cầu. Tình trạng này cũng có thể xảy ra khi sử dụng Albendazol và được coi là một trong những triệu chứng máu hiếm gặp.\n\nGiảm bạch cầu không chỉ liên quan đến việc số lượng bạch cầu giảm mà còn có thể đi kèm với các tác dụng phụ khác như giảm tiểu cầu, ức chế tủy xương, thiếu máu, và mất bạch cầu hạt khi sử dụng thuốc như Diurefar. Tình trạng này cần được theo dõi chặt chẽ bởi các bác sĩ và y tá để đảm bảo sức khỏe của bệnh nhân, đặc biệt là trong trường hợp sử dụng Ampicillin, được xác định là một trong những nguyên nhân chính gây ra tình trạng giảm bạch cầu. Ngoài ra, giảm bạch cầu còn được ghi nhận là tác dụng phụ của Aldactone, Aluvia, Aspirin, và Augmentin 500 mg/62,5 mg. Nó cũng được xác định là tác dụng phụ của Amitriptylin. Tuy nhiên, cần lưu ý rằng giảm bạch cầu không chỉ liên quan đến việc sử dụng thuốc mà còn có thể xuất hiện như một triệu chứng liên quan đến máu hoặc do tăng huyết áp.\n\nĐáng chú ý, Đông trùng hạ thảo có thể giúp đảo ngược tình trạng giảm bạch cầu liên quan đến liệu pháp điều trị ung thư. Giảm bạch cầu cũng là tác dụng phụ của Carbimazol, Cataflam, và Cefprozil. Ngoài ra, tình trạng này còn là tác dụng phụ hiếm gặp khi dùng Celecoxib và là tác dụng phụ khi dùng Coversyl Plus cùng với allopurinol, eytostatic hoặc các thuốc hỗ trợ miễn dịch, các corticosteroid tổng hợp hoặc procainamid.&lt;SEP&gt;Giảm bạch cầu là tình trạng số lượng bạch cầu giảm dưới 4000 tế bào/mm3.\nThủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là triệu chứng liên quan đến việc sử dụng thuốc NSAID.&lt;SEP&gt;Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nBệnh Thận: Bệnh Thận là tình trạng tổn thương chức năng của thận, bao gồm cả tình trạng lọc máu kém và các vấn đề liên quan đến chức năng thận. Bệnh thận có thể xuất hiện như một biến chứng của chứng aldosterone nguyên phát hoặc như một tác dụng phụ của một số loại thuốc như Acepron 250 mg, Acnekyn, Batigan, và Asakoya Mediplantex. Đối với bệnh nhân tăng huyết áp kèm đái tháo đường, Agilosart VERTEX 100 được sử dụng để điều trị bệnh thận. Người mắc bệnh thận cần tuân thủ chỉ định của bác sĩ khi sử dụng thuốc, đặc biệt là A.T Calci Plus, Agietoxib, Atorvastatin T.V Pharm, và Bactamox, vì những loại thuốc này có thể làm tình trạng bệnh trở nên nghiêm trọng hơn. \n\nNgười mắc bệnh thận có thể gặp khó khăn trong việc tạo đủ Vitamin D như bình thường, do đó cần dùng Calcitriol để điều trị. Bệnh thận cũng được coi là chống chỉ định khi sử dụng các loại thuốc như A.T Calci Plus và Bactamox, đặc biệt khi độ thanh thải Creatinin CrCl dưới 30 ml/phút. Bệnh thận có thể gây tăng áp lực nội sọ thứ phát và cần được thận trọng khi dùng aspirin. Ngoài ra, bệnh thận còn có thể gây ra tình trạng mất ngủ ở người già và cần thận trọng khi sử dụng Betaloc và acid tranexamic. Bệnh thận cũng được khuyến khích tránh hoàn toàn các sản phẩm cam thảo có chứa glycyrrhizin.\n\nBệnh thận cũng có thể được gây ra bởi liên cầu khuẩn tan máu và có thể gây ra tình trạng phù nề, được điều trị bằng Diurefar. Bệnh thận là một bệnh mạn tính có thể làm tăng nguy cơ mắc bệnh gout và cũng có thể gây ra hạ huyết áp. Bệnh thận là một biến chứng phổ biến của bệnh tiểu đường và cũng là một biến chứng của chứng không lỗ van ba lá. Bệnh thận cũng có thể được phát hiện qua ước tiểu màu hồng/đỏ và là một yếu tố nguy cơ tăng nguy cơ mắc bệnh suy thận cấp. Bệnh thận là tình trạng sức khỏe cần báo cáo trước khi sử dụng thuốc nhỏ mắt, Chloramphenicol, Dalfusin, và Dầu giun.\n\nBệnh thận là một trong những bệnh cần thận trọng khi sử dụng Alaxan, và bệnh thận tiến triển là nguyên nhân khiến bệnh nhân không nên dùng thuốc Alaxan. Bệnh thận ở mức độ vừa hoặc nặng là chống chỉ định khi sử dụng deferasirox. Bệnh thận cũng được điều trị bằng Losartan ở bệnh nhân có tăng huyết áp và đái tháo đường tuýp 2.&lt;SEP&gt;Bệnh thận là bệnh lý thận gây ra phù toàn thân.&lt;SEP&gt;Bệnh thận là một trong những bệnh lý ảnh hưởng đến chức năng sinh sản nam.&lt;SEP&gt;Bệnh thận là bệnh lý có thể làm giảm khả năng sản xuất hồng cầu.&lt;SEP&gt;Bệnh thận có thể làm cho hồng cầu bị phá hủy.&lt;SEP&gt;Bệnh thận là tình trạng bệnh lý của thận, có thể gây tụt huyết áp.\nAceclofenac: Thuốc Aceclofenac được chỉ định để giảm đau và kháng viêm trong bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.&lt;SEP&gt;Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg, có tác dụng kháng viêm không steroid.&lt;SEP&gt;Aceclofenac là thuốc giảm đau và chống viêm không steroid (NSAID), có thể gây tác dụng phụ như tăng men gan, khó tiêu, đau bụng, buồn nôn, tiêu chảy, đầy hơi, viêm dạ dày, táo bón, nôn, loét miệng, ngứa, phát ban, viêm da, nổi mề đay, tăng urê huyết, tăng creatinin huyết, thiếu máu, phản ứng phản vệ, rối loạn thị giác, tình trạng khó thở, phân đen, phù mặt.&lt;SEP&gt;Aceclofenac là thuốc gây ra các tác dụng phụ trên hệ thần kinh, bao gồm triệu chứng như choáng váng, buồn ngủ, mệt mỏi, và rối loạn thị giác.\nAceclofenac - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tiêu chảy là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAcepron 250 mg - Giảm Tiểu Cầu: Giảm tiểu cầu là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Giảm Toàn Thể Huyết Cầu: Giảm toàn thể huyết cầu là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Buồn Nôn: Buồn nôn là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Đau Cơ: Acepron 250 mg được chỉ định để điều trị đau cơ.\nAceclofenac - Táo Bón: Táo bón là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Ban Da: Ban da là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Suy Thận: Không nên sử dụng Aceclofenac trên các đối tượng bị suy thận mức độ vừa đến nặng.&lt;SEP&gt;Suy thận là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Đau Đầu: Acepron 250 mg được chỉ định để điều trị đau đầu.\nAcepron 250 mg - Giảm Bạch Cầu: Giảm bạch cầu là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Sốt: Acepron 250 mg được chỉ định để điều trị sốt.&lt;SEP&gt;Acepron 250 mg được dùng để điều trị sốt.\nAcepron 250 mg - Bệnh Thận: Bệnh thận là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Đau Bụng: Đau bụng là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Nhức Đầu: Acepron 250 mg được dùng để điều trị nhức đầu.\nAceclofenac - Mệt Mỏi: Mệt mỏi là tác dụng phụ của Aceclofenac.\nAcepron 250 mg - Tác Dụng Phụ: Khi sử dụng Acepron 250 mg cần chú ý đến tác dụng phụ nếu có.\nAceclofenac - Nôn: Nôn là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Nôn: Nôn là tác dụng phụ của Acepron 250 mg.\nAceclofenac - Suy Tim: Suy tim là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Ngứa: Ngứa là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Thận: Acepron 250 mg chống chỉ định sử dụng ở người bệnh thận.\nAceclofenac - Phụ Nữ Có Thai: Aceclofenac chống chỉ định trong thai kỳ trừ khi lợi ích điều trị cho mẹ vượt trội nguy cơ gây hại cho thai nhi.\nAceclofenac - Thiếu Máu: Thiếu máu là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Thiếu máu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Tim: Acepron 250 mg chống chỉ định sử dụng ở người bệnh tim.\nAceclofenac - Suy Gan: Suy gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Gan: Acepron 250 mg chống chỉ định sử dụng ở người bệnh gan.\nAceclofenac - Hạ Huyết Áp: Hạ huyết áp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nhức Đầu: Nhức đầu là triệu chứng khi quá liều Aceclofenac.\nAcepron 250 mg - Thiếu Máu: Acepron 250 mg chống chỉ định sử dụng ở người bệnh thiếu máu.&lt;SEP&gt;Thiếu máu là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Phẫu Thuật: Acepron 250 mg được dùng để điều trị sốt sau khi phẫu thuật.\nAceclofenac - Suy Hô Hấp: Suy hô hấp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Co Giật: Co giật là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAceclofenac - Phụ Nữ Cho Con Bú: Aceclofenac không nên dùng trong giai đoạn đang cho con bú.\nAceclofenac - Đầy Hơi: Đầy hơi là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Khớp Dạng Thấp: Aceclofenac được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac - Khó Tiêu: Khó tiêu là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Buồn Ngủ: Buồn ngủ là tác dụng phụ của Aceclofenac.\nAceclofenac - Phát Ban: Phát ban là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Da: Viêm da là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Suy Thận Cấp: Suy thận cấp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAcepron 250 mg - Phổi: Acepron 250 mg chống chỉ định sử dụng ở người bệnh phổi.\nAceclofenac - Ù Tai: Ù tai là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nổi Mề Đay: Nổi mề đay là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Dạ Dày: Viêm dạ dày là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Paracetamol: Acepron 250 mg chứa paracetamol như hoạt chất chính.\nAcepron 250 mg - Sốt Xuất Huyết: Acepron 250 mg được dùng để điều trị sốt xuất huyết.\nAceclofenac - Hôn Mê: Hôn mê là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Người Cao Tuổi: Khả năng phân bố, chuyển hóa, hấp thu và thải trừ của Aceclofenac không thay đổi ở bệnh nhân cao tuổi, do đó không cần phải thay đổi liều hoặc tần suất sử dụng.\nAceclofenac - Thuốc Lợi Tiểu: Thuốc lợi tiểu có thể tương tác với Aceclofenac.\nAceclofenac - Phản Ứng Phản Vệ: Phản ứng phản vệ là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Hệ Thần Kinh: Aceclofenac gây ra các tác dụng phụ trên hệ thần kinh.\nAceclofenac - Rửa Dạ Dày: Rửa dạ dày là biện pháp dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Corticosteroids: Corticosteroids có thể tương tác với Aceclofenac.\nAceclofenac - Rối Loạn Thị Giác: Rối loạn thị giác là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Rối loạn thị giác là tác dụng phụ của Aceclofenac.\nAceclofenac - Viêm Xương Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm xương khớp.\nAceclofenac - Prostaglandin: Aceclofenac ức chế tổng hợp prostaglandin.\nAceclofenac - Loét Miệng: Loét miệng là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Chống Đông: Thuốc chống đông có thể tương tác với Aceclofenac.\nAceclofenac - Nôn Ra Máu: Nôn ra máu là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Tăng Men Gan: Tăng men gan là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAcepron 250 mg - Thấp Khớp: Acepron 250 mg không có tác dụng trong điều trị thấp khớp.\nAceclofenac - Choáng Váng: Choáng váng là tác dụng phụ của Aceclofenac.\nAceclofenac - Kích Động: Kích động là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Ngất: Ngất là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Xuất Huyết Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng nghi ngờ có xuất huyết tiêu hóa.&lt;SEP&gt;Xuất huyết tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.&lt;SEP&gt;Xuất huyết tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Methotrexat: Methotrexat có thể tương tác với Aceclofenac.\nAcepron 250 mg - Nhiễm Khuẩn: Acepron 250 mg được dùng để điều trị nhiễm khuẩn.\nAceclofenac - Suy Giảm Chức Năng Gan: Liều dùng khởi đầu được đề nghị là 100 mg/ngày (1 viên/ngày) cho những bệnh nhân suy gan.\nAceclofenac - Tổn Thương Gan: Tổn thương gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Glycosid Tim: Glycosid tim có thể tương tác với Aceclofenac.\nAceclofenac - Tacrolimus: Tacrolimus có thể tương tác với Aceclofenac.\nAceclofenac - Than Hoạt Tính: Than hoạt tính được dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Phù Mặt: Phù mặt là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Đau Vùng Thượng Vị: Đau vùng thượng vị là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Phân Đen: Phân đen là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Ciclosporin: Ciclosporin có thể tương tác với Aceclofenac.\nAceclofenac - Zidovudin: Zidovudin có thể tương tác với Aceclofenac.\nAceclofenac - Lithi: Lithi có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Điều Trị Tăng Huyết Áp: Thuốc điều trị tăng huyết áp có thể tương tác với Aceclofenac.\nAceclofenac - Buồn Nôn, Nôn: Buồn nôn và nôn là triệu chứng khi quá liều Aceclofenac.\nAcepron 250 mg - Đau Răng: Acepron 250 mg được chỉ định để điều trị đau răng.&lt;SEP&gt;Acepron 250 mg được dùng để điều trị đau răng.\nAceclofenac - Aceclofenac STADA 100mg: Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg.\nAceclofenac - Cyclooxygenase: Aceclofenac ức chế cyclooxygenase.\nAceclofenac - Kích Ứng Tiêu Hóa: Kích ứng tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Loét Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng đã từng bị loét tiêu hóa tiến triển trước đó.\nAceclofenac - Tăng Creatinin Huyết: Tăng creatinin huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Đốt Sống Dính Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm đốt sống dính khớp.\nAceclofenac - Thủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Suy Thai: Suy thai là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiêu Hóa: Suy tiêu hóa là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Mifepriston: Mifepriston có thể tương tác với Aceclofenac.\nAceclofenac - Kháng Sinh Nhóm Quinolon: Kháng sinh nhóm quinolon có thể tương tác với Aceclofenac.\nAceclofenac - Loxoprofen: Loxoprofen có tác dụng giảm đau và kháng viêm tương tự như Aceclofenac.\nAceclofenac - Bị Mất Phương Hướng: Bị mất phương hướng là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Não: Suy não là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Viêm: Suy viêm là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Khớp: Suy khớp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Mi: Suy mi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Phổi: Suy phổi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Thần Kinh: Suy thần kinh là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Niệu: Suy tiết niệu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Dịch: Suy tiết dịch là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Protein: Suy tiết protein là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone: Suy tiết hormone là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid: Suy tiết hormone tiroid là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B12: Suy tiết hormone tiroid B12 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B13: Suy tiết hormone tiroid B13 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B14: Suy tiết hormone tiroid B14 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B15: Suy tiết hormone tiroid B15 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B16: Suy tiết hormone tiroid B16 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B17: Suy tiết hormone tiroid B17 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B18: Suy tiết hormone tiroid B18 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B19: Suy tiết hormone tiroid B19 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B20: Suy tiết hormone tiroid B20 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Gàn: Liều dùng Aceclofenac cần được giảm cho những bệnh nhân suy gan.\nAceclofenac - Aceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac.\nAceclofenac - Tình Trạng Khó Thở: Tình trạng khó thở là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Giảm Đau Khác: Thuốc giảm đau khác bao gồm các thuốc ức chế chọn lọc cyclooxygenase-2 có thể tương tác với Aceclofenac.\nAceclofenac - Tác Nhân Kháng Tiểu Phần: Tác nhân kháng tiểu phần có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Ức Chế Chọn Lọc Thu Hồi Serotonin (SSRI): Thuốc ức chế chọn lọc thu hồi serotonin (SSRI) có thể tương tác với Aceclofenac.\nAceclofenac - Nhóm Thuốc Trị Đái Tháo Đường: Nhóm thuốc trị đái tháo đường có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Kháng Viêm Không Steroid (NSAID) Khác: Thuốc kháng viêm không steroid (NSAID) khác có thể tương tác với Aceclofenac, tạo ra nguy cơ xuất huyết tiêu hóa.\nTrimethoprim - Độc Tính Trên Thận: Độc毒性肾脏是使用trimethoprim的副作用。\nAcepron 250 mg - Phản Ứng Quá Mẫn: Phản ứng quá mẫn là tác dụng phụ hiếm gặp của Acepron 250 mg.\nAcepron 250 mg - Thận Trọng: Acepron 250 mg cần được sử dụng thận trọng ở một số đối tượng.\nGiảm Tiểu Cầu - Hệ Máu: Giảm tiểu cầu là rối loạn hệ máu và hệ bạch huyết.\nAcepron 250 mg - Thân Nhiệt: Acepron 250 mg điều chỉnh thân nhiệt ở người bệnh sốt.\nAcyclovir Stada 200 mg - Độc Tính Trên Thận: Sử dụng Acyclovir Stada 200 mg cùng Cyclosporin có thể gây độc tính trên thận.\nAcepron 250 mg - Loạn Tạo Máu: Loạn tạo máu là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Nhiệt Độ Dưới 30°C: Acepron 250 mg cần được bảo quản ở nơi có nhiệt độ dưới 30°C.\nAcepron 250 mg - Nhiễm Siêu Vi: Acepron 250 mg được dùng để điều trị nhiễm siêu vi.\nAcepron 250 mg - Tiêm Chủng: Acepron 250 mg được dùng để điều trị sốt sau khi tiêm chủng.\nAcepron 250 mg - Liều: Thuốc Acepron 250 mg cần được sử dụng đúng liều lượng theo hướng dẫn.\nAcepron 250 mg - Độc Tính Trên Thận: Độc tính trên thận là tác dụng phụ của Acepron 250 mg.\nAcepron 250 mg - Nơi Thoáng Mát: Acepron 250 mg cần được bảo quản ở nơi thoáng mát.\nAcepron 250 mg - Panactol 500mg Khapharco: Acepron 250 mg có thành phần tương tự như Panactol 500mg Khapharco.\nAcepron 250 mg - Actadol 500mg Medipharco: Acepron 250 mg có thành phần tương tự như Actadol 500mg Medipharco.\nAcepron 250 mg - Hapacol DHG Pharma: Acepron 250 mg có thành phần tương tự như Hapacol DHG Pharma.\nAcepron 250 mg - Đau Nhức Do Cảm Cúm: Acepron 250 mg được chỉ định để điều trị đau nhức do cảm cúm.&lt;SEP&gt;Acepron 250 mg được dùng để điều trị đau nhức do cảm cúm.\nAcepron 250 mg - Phenylceton – niệu: Acepron 250 mg cần thận trọng ở người bị phenylceton – niệu.\nAcepron 250 mg - G6PD: Acepron 250 mg chống chỉ định sử dụng ở người thiếu hụt G6PD.\nAcepron 250 mg - Mọc Răng: Acepron 250 mg được dùng để điều trị mọc răng.\nAcnekyn - Hapacol DHG Pharma: Acnekyn có thành phần tương tự như Hapacol DHG Pharma.\nSulfamethoxazole - Độc Tính Trên Thận: Độc毒性肾脏是使用sulfamethoxazole的副作用。\nGiảm Bạch Cầu Trung Tính - Hệ Máu: Giảm bạch cầu trung tính là rối loạn hệ máu và hệ bạch huyết.\nHệ Máu - Tăng Bạch Cầu: Tăng bạch cầu là rối loạn hệ máu và hệ bạch huyết.\nAceclofenac Stada - Thủng Loét Đường Tiêu Hóa: Aceclofenac Stada có thể gây thủng loét đường tiêu hóa.\nGiảm Bạch Cầu Đa Nhân Trung Tính - Hệ Máu: Giảm bạch cầu đa nhân trung tính là rối loạn hệ máu và hệ bạch huyết."]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ngoài tác dụng giảm đau, **Acepron 250 mg** còn có thêm các tác dụng khác như:
+- **Điều trị sốt**: Acepron 250 mg được chỉ định để điều trị sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật...
+- **Giảm các triệu chứng đau**: Thuốc giúp giảm các triệu chứng đau từ nhẹ đến vừa như đau đầu, đau răng, đau nhức do cảm cúm, đau cơ.
+- **Giảm thân nhiệt**: Thuốc có tác dụng làm giảm thân nhiệt ở người bệnh sốt.
+Acepron 250 mg không có tác dụng trong điều trị thấp khớp và các cơn đau bắt nguồn từ nội tạng.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ngoài tác dụng giảm đau, Acepron 250 mg còn có thêm tác dụng giảm thân nhiệt ở những người có triệu chứng sốt do cảm cúm, sốt xuất huyết, nhiễm khuẩn, nhiễm siêu vi, mọc răng, sau khi tiêm chủng, sau phẫu thuật.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.8495687079694294</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+        <v>0.9022371883374288</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Context Recall</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>1</v>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Có thể tự ý sử dụng Calci D Hasan khi đang mang thai và cho con bú không?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>['Thiếu Calci: Thiếu calci là tình trạng cần bổ sung calci trong trẻ em thời kỳ phát triển, phụ nữ có thai và cho con bú.&lt;SEP&gt;Thiếu calci là tình trạng dinh dưỡng kém được Calci D Hasan giúp cải thiện.\nCalci D Hasan: Calci D Hasan là sản phẩm thuốc của Công ty TNHH Hasan – Dermapharm với thành phần hoạt chất là calci (dạng calci carbonat) và cholecalciferol (vitamin D3).&lt;SEP&gt;Calci D Hasan là thuốc chứa muối calci qua đường uống, có thể gây kích ứng hệ tiêu hóa, táo bón và khó chịu ở dạ dày.&lt;SEP&gt;Calci D Hasan là thuốc chứa calci và vitamin D, cần được sử dụng dưới sự giám sát của bác sĩ.&lt;SEP&gt;Calci D Hasan là thuốc chứa muối calci, có thể gây tăng calci huyết nếu sử dụng quá liều.&lt;SEP&gt;Calci D Hasan là thuốc cần được bảo quản trong bao lọ kín, ở nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời, nhiệt độ dưới 25ºC và độ ẩm dưới 70ºC.\nGặm Nhấm: Gặm nhấm ăn quả Dướng khi chín.\nPhụ Nữ Có Thai: Phụ nữ có thai là giai đoạn mà phụ nữ đang mang thai và cần đặc biệt chú ý đến việc sử dụng nhiều loại thuốc và thảo dược khác nhau để đảm bảo an toàn cho cả mẹ và thai nhi. Trong thời kỳ này, nhu cầu về vitamin C tăng cao do vitamin C có khả năng đi qua nhau thai. Việc sử dụng nhiều loại thuốc cần được thực hiện một cách thận trọng, bao gồm cả những thuốc như A.T Calmax, A.T.P, A.t Ibuprofen Syrup, Vildagliptin, Adalat LA, Acnequidt 20 ml, Alchysin 8400, Alpha-Chymotrypsin, AlphaDHG, Alsiful S.R., Altamin (do thành phần Actiso và Rau đắng đất có tác dụng tăng co bóp tử cung), Alvesin (do thiếu nghiên cứu cụ thể), Amaryl 1 mg (cần chuyển sang sử dụng Insulin), Ambroxol Boston, Amepox Soft Capsule, Amikacin Bidiphar, Amiparen 5 Otsuka, amlodipine, Amlor 5 Pfizer, và Amoxicillin (do thiếu dữ liệu về tính an toàn).\n\nPhụ nữ có thai có thể sử dụng Agimfast 60 nếu lợi ích cho mẹ vượt trội nguy cơ đối với thai nhi và Amoxicillin khi đã được bác sĩ chỉ định và đánh giá lợi ích so với nguy cơ. Đối với Alchysin 840, phụ nữ có thai được khuyến nghị không nên dùng vì thuốc có thể ảnh hưởng đến sự phát triển của thai kỳ. Đối với Alvesin, chưa có nghiên cứu cụ thể về việc sử dụng của phụ nữ có thai, và quyết định sử dụng nên dựa trên đánh giá của bác sĩ về lợi ích và nguy cơ. Đối với Amaryl 1 mg, phụ nữ có thai cần chuyển sang sử dụng Insulin.\n\nPhụ nữ có thai hoặc có kế hoạch mang thai cần thông báo với bác sĩ trước khi dùng thuốc. Đặc biệt, phụ nữ có thai cần trao đổi với bác sĩ trước khi sử dụng Amoxicillin Mekophar và Ampelop. Phụ nữ có thai cũng tuyệt đối không dùng An Cung Ngưu Hoàng Hoàn. Cần tham khảo ý kiến bác sĩ trước khi sử dụng các thuốc như An Thảo, Anapa, và Andol S Imexpharm. Phụ nữ có thai nên hỏi ý kiến thầy thuốc trước khi sử dụng Antacil. Phụ nữ có thai là đối tượng cần thận trọng khi sử dụng Antanazol, Appeton Lysine Syrup, Argide, Arthrorein Pharmanel, và Artrodar. Phụ nữ có thai không được sử dụng Asakoya Mediplantex do có thể gây ảnh hưởng nghiêm trọng đến sức khỏe của người mẹ và thai nhi. Ngoài ra, phụ nữ có thai không được sử dụng Asevictoria Mediplantex do nguy cơ tác dụng xấu lên thai nhi.\n\nPhụ nữ có thai, đặc biệt là trong 3 tháng đầu của thai kỳ, cần tránh sử dụng Bactamox, Augtipha, và Debby. Phụ nữ có thai cần thận trọng khi sử dụng Betasiphon do có thể gây tác dụng phụ tiêu chảy. Phụ nữ có thai cần cân nhắc giữa lợi ích và nguy cơ khi sử dụng Clopidogrel, Carbocistein, và Bromelain. Phụ nữ có thai cần thận trọng khi sử dụng các thảo dược như cây huyết rồng, đông trùng hạ thảo, và nấm lim xanh do có thể gây hại.\n\nPhụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược và thuốc có thể gây tác động xấu đến sức khỏe của thai nhi như: Pregabalin, Differin, Saffron, và Rau Mùi. Phụ nữ có thai cần thận trọng khi sử dụng các sản phẩm chứa glycyrrhizin, hoa đậu biếc, và các sản phẩm có chứa acetylcystein.\n\nPhụ nữ có thai cần lưu ý rằng một số thảo dược như cây đại, xạ can, và trường sinh thảo là những thảo dược cần kiêng kỵ trong thai kỳ. Phụ nữ có thai cần đặc biệt thận trọng khi sử dụng các loại thảo dược như chùm ngây, cỏ sữa, và cây huyết rồng.\n\nPhụ nữ có thai cần tuân thủ hướng dẫn của bác sĩ và không nên tự ý sử dụng bất kỳ loại thuốc hay thảo dược nào mà không có sự đồng ý của bác sĩ. Phụ nữ có thai cần lưu ý khi sử dụng Sơn Nại, lá cây mâm xôi, thảo dược Bàng Lăng, tam thất nam, và Thạch lựu. Phụ nữ có thai cũng dễ mắc bệnh thiếu máu thiếu sắt.\n\nNgoài ra, phụ nữ có thai không nên sử dụng Albendazole, Amilavil, và Amiodarone do có thể gây ảnh hưởng đến sức khỏe của mẹ và thai nhi. Phụ nữ có thai cần cân nhắc khi sử dụng Arginin do thiếu nghiên cứu đầy đủ và được kiểm chứng tốt. Phụ nữ có thai không nên sử dụng Artreil do thuốc này chống chỉ định cho phụ nữ mang thai và cho con bú.\n\nPhụ nữ có thai cần thảo luận với bác sĩ về việc sử dụng thuốc Bifril. Hiện chưa có dữ liệu cụ thể về ảnh hưởng của Bepanthen đến phụ nữ có thai. Phụ nữ có thai cần thận trọng khi dùng Betahistine. Phụ nữ có thai cần thận trọng khi sử dụng Biotin. Phụ nữ mang thai không nên sử dụng Bisacodyl vì thiếu dữ liệu về sự an toàn.\n\nPhụ nữ có thai là chống chỉ định của thuốc Bismuth. Phụ nữ có thai là một trong những đối tượng không được khuyến nghị sử dụng thuốc Cebraton. Phụ nữ có thai cần thận trọng khi sử dụng Boganic.\n\nThuốc Piroxicam không được dùng trong giai đoạn thai kỳ vì có thể gây ra các vấn đề sức khỏe cho thai nhi.\n\nPhụ nữ có thai cũng cần cân nhắc việc sử dụng Bricanyl, một loại thuốc mà phụ nữ có thai có thể phải cân nhắc trong quá trình mang thai. Vẫn chưa có dữ liệu lâm sàng có giá trị về việc sử dụng thuốc này ở phụ nữ mang thai.\n\nPhụ nữ có thai không nên sử dụng Brosafe vì thuốc có thể gây tác dụng xấu đến sức khỏe của người mẹ và thai nhi. Phụ nữ có thai cũng cần thận trọng khi sử dụng Brufen trong giai đoạn cuối thai kỳ.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Candesartan. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Carbomango. Phụ nữ có thai cần cân nhắc kỹ giữa lợi ích và nguy cơ khi dùng Casalmux. Phụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Ceritine.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Chophytol. Phụ nữ có thai có thể sử dụng Claminat khi thật cần thiết.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Clonazepam. Phụ nữ mang thai có thể sử dụng Clorpheniramin trong 3 tháng cuối thai kỳ, nhưng cần thận trọng vì có thể gây ra phản ứng nghiêm trọng ở trẻ sơ sinh.\n\nPhụ nữ có thai không nên sử dụng CumarGold vì sản phẩm có thể qua nhau thai gây ảnh hưởng đến thai nhi.\n\nPhụ nữ có thai cần hỏi ý kiến bác sĩ trước khi sử dụng Curam.\n\nPhụ nữ có thai không được sử dụng Cyclo Progynova. Cyclo Progynova là một tình trạng chống chỉ định khi sử dụng cho phụ nữ có thai.\n\nPhụ nữ có thai cần tránh sử dụng thuốc nhóm imidazol như Daktarin. Phụ nữ có thai là đối tượng đặc biệt cần tư vấn và đồng ý từ bác sĩ trước khi sử dụng benzalkonium chloride.\n\nPhụ nữ có thai là đối tượng sử dụng Actemra cần được đánh giá kỹ lưỡng.\n\nPhụ nữ có thai không thể sử dụng thuốc Aescin.\n\nPhụ nữ có thai là đối tượng chống chỉ định sử dụng Rosuvastatin.\n\nPhụ nữ có thai không nên sử dụng Coldi B.\n\nPhụ nữ có thai không được dùng Thuyền thoại.\n\nPhụ nữ có thai là đối tượng cần tham khảo ý kiến bác sĩ trước khi sử dụng tinh dầu hoa cam và tinh dầu hoàng đàn. Phụ nữ có thai cần cẩn trọng khi sử dụng tinh dầu húng chanh. Phụ nữ có thai cần thận trọng khi sử dụng Trầm hương.\n\nPhụ nữ có thai cần thận trọng khi sử dụng Tỳ giải.\nKích Ứng Hệ Tiêu Hóa: Kích ứng hệ tiêu hóa là tác dụng phụ của Calci D Hasan.\nThuốc Điều Trị: Thuốc Điều Trị là các loại thuốc được sử dụng để điều trị nhiều bệnh lý mạn tính, bao gồm cả những bệnh như lupus, bệnh teo đa hệ thống (MSA), và chảy dịch tai. Thuốc Điều Trị có thể cần dùng trong nhiều năm đối với những người mắc bệnh lupus ít bùng phát hoặc ít triệu chứng. Chúng giúp giảm triệu chứng trong bệnh MSA và làm cho cử động mềm hơn, ngăn ngừa tình trạng căng tức thành khi bị táo bón. \n\nTác dụng phụ phổ biến của Thuốc Điều Trị bao gồm mệt mỏi, đặc biệt khi sử dụng để điều trị động kinh. Thuốc Điều Trị có thể bị ảnh hưởng bởi Bibonlax khi sử dụng đồng thời, do đó cần lưu ý khi kê đơn và sử dụng cùng với các loại thuốc khác. Đối với trẻ sinh non có ống động mạch lớn, Thuốc Điều Trị có thể là một phần quan trọng trong quá trình điều trị.\n\nThuốc Điều Trị cũng được sử dụng để điều trị nấm da đầu, bao gồm cả thuốc uống và thuốc thoa. Tuy nhiên, Thuốc Điều Trị không được sử dụng để điều trị nang nước cạnh buồng trứng. Khi sử dụng Thuốc Điều Trị, cần thông báo cho bác sĩ về tình trạng bệnh lý phụ khoa. Ngoài ra, Thuốc Điều Trị cũng được sử dụng để điều trị rối loạn nhân cách phụ thuộc, cần được kê đơn bởi bác sĩ tâm lý.\n\nĐối với hội chứng Colic, không có thuốc điều trị cụ thể.&lt;SEP&gt;Thuốc điều trị rối loạn nhận thức thần kinh chưa được cấp phép.&lt;SEP&gt;Thuốc điều trị suy giáp bẩm sinh.&lt;SEP&gt;Thuốc được sử dụng nhằm mục đích ngăn chặn sự phát triển của các mạch máu mới và làm giảm sự rò rỉ dịch bên trong mắt gây nên bệnh thoái hóa điểm vàng thể ướt.\nKhó Chịu Ở Dạ Dày: Khó chịu ở dạ dày là tác dụng phụ của Calci D Hasan.\nQuá Liều: Quá Liều là tình trạng xảy ra khi sử dụng lượng thuốc vượt quá liều lượng được chỉ định hoặc khuyến nghị, dẫn đến các triệu chứng bất thường và cần được điều trị kịp thời để tránh hậu quả nghiêm trọng. Tình trạng này có thể xảy ra với nhiều loại thuốc khác nhau, bao gồm At Domperidone, thuốc A.T.P., Vildagliptin, Acecyst, Acenocoumarol, Aclasta, acyclovir, acetaminophen, Alchysin cq cq 8400, Ambroxol Boston, Aminoplasmal 10%, Amoxicilin, Amoxicillin Flamingo, Alzental, nhôm phosphat, Ambroco, Ampicillin Brawn, thuốc An Thảo, Anaferon Materia, Asevictoria Mediplantex, Aspartam Pharmedic, Aspirin pH8, Atorhasan, Atorlog, Atorvastatin T.V Pharm, Augbactam, B - Sol, Babi B.O.N., Bisoloc, và Banitase Bảo Thanh. Việc sử dụng quá liều Vildagliptin có thể gây ra các triệu chứng như đau cơ, dị cảm, sốt, phù và tăng lipase thoáng qua. Quá liều Acecyst có thể dẫn đến các triệu chứng nghiêm trọng hơn như giảm huyết áp, suy hô hấp, tan máu, đông máu rải rác nội mạch, suy thận và sốc phản vệ. Sử dụng quá nhiều acetaminophen cũng có thể gây ra hoại tử gan. Quá liều acyclovir có thể gây ra các triệu chứng trên đường tiêu hóa và hệ thống thần kinh. Quá liều Agimfast 60 có thể gây ra các triệu chứng như buồn ngủ, chóng mặt, khô miệng. Ngoài ra, việc sử dụng quá liều Acenocoumarol 4 mg và Aclasta vượt quá liều lượng quy định cũng được ghi nhận.\n\nQuá liều cũng có thể xảy ra do người bệnh vô ý hoặc cố tình sử dụng quá liều thuốc. Trong một số trường hợp, việc sử dụng quá liều thuốc Alzental có thể dẫn đến các tác hại không mong muốn. Quá liều nhôm phosphat có thể gây ra táo bón, tắc ruột, và sỏi thận. Tình trạng quá liều Ambroco chưa được ghi nhận thông tin cụ thể, nhưng cần báo bác sĩ ngay lập tức. Quá liều Ampicillin Brawn cần ngưng dùng thuốc ngay và đến cơ sở y tế gần nhất để kiểm tra, theo dõi và xử lý kịp thời. Quá liều thuốc An Thảo cũng cần đến cơ sở y tế ngay để được theo dõi và xử lý. Quá liều thuốc Anaferon Materia cần dừng ngay và đến trung tâm y tế để xử lý kịp thời. Gel Anapa bôi tại chỗ chưa có ghi nhận cụ thể về quá liều.\n\nĐối phó với tình trạng quá liều thường yêu cầu sự can thiệp của bác sĩ để kiểm soát và điều trị triệu chứng. Trong một số trường hợp nghiêm trọng, việc điều trị có thể yêu cầu đưa bệnh nhân vào bệnh viện để điều trị hạ huyết áp và các triệu chứng khác. Quá liều có thể xảy ra nếu người dùng cố gắng uống gấp đôi liều để bù đắp cho liều đã quên. Sử dụng thuốc quá liều có thể dẫn đến những phản ứng có hại cho cơ thể. Quá liều Asevictoria Mediplantex có thể gây ra tác dụng xấu nghiêm trọng. Quá liều Aspartam Pharmedic và Aspirin pH8 cũng có thể dẫn đến cần cấp cứu. Quá liều Atorhasan, Atorlog, và Atorvastatin T.V Pharm cần được xử lý bằng cách điều trị triệu chứng và theo dõi chức năng gan và CPK huyết thanh. Quá liều Augbactam không gây tai biến nếu dung nạp tốt nhưng có thể gây tăng kali huyết.\n\nNgoài ra, quá liều Corticoid có thể gây suy thượng thận cấp. Quá liều Bluemint có thể gây ra các dấu hiệu bất thường. Quá liều Bonzacim cần được xử lý kịp thời. Quá liều Boston C 1000 cũng có thể gây ra tác dụng phụ. Quá liều Brudoxil có thể gây ra triệu chứng bất thường và cần được xử lý kịp thời.\n\nQuá liều Calci - D Mekophar cần được xử lý kịp thời. Quá liều Itraconazole chưa có nhiều dữ liệu lâm sàng về xử trí. Quá liều Carbocistein gây ra rối loạn tiêu hóa. Quá liều Carbomint cần ngừng sử dụng và theo dõi triệu chứng. Hiện tại chưa ghi nhận dữ liệu về các trường hợp quá liều của Carbomint.\n\nQuá liều Cefimbrano có thể gây ra triệu chứng co giật. Quá liều Cerecaps chưa được báo cáo nhưng cần dừng sử dụng và báo cáo cho bác sĩ. Quá liều Bromelain là tình huống chưa có báo cáo cụ thể nhưng cần xử lý kịp thời. Quá liều Chlorocina-H chưa được ghi nhận hay báo cáo. Quá liều Cholapan chưa được báo cáo cụ thể. Quá liều là tình trạng sử dụng quá nhiều thuốc Ciacca. Chưa có báo cáo về trường hợp quá liều nào xảy ra khi dùng kem acyclovir.\n\nQuá liều cũng có thể xảy ra với dung dịch nhỏ tai, mặc dù chi tiết cụ thể về tác dụng của quá liều đối với các dung dịch nhỏ tai này chưa được mô tả rõ ràng. Quá liều cũng có thể xảy ra với Cosele, cần liên hệ cơ quan y tế nếu gặp vấn đề nghiêm trọng. Quá liều Cotilam là tình huống cần liên hệ nhân viên y tế. Quá liều Crotamiton chưa được ghi nhận tác hại khi sử dụng bôi ngoài, nhưng có thể gây đau rát, kích ứng miệng, thực quản, niêm mạc dạ dày, buồn nôn, đau bụng và co giật.\n\nQuá liều Dalfusin cần được xử lý kịp thời bằng cách đưa bệnh nhân đến cơ sở y tế gần nhất. Quá liều cũng là tình trạng sử dụng quá nhiều Danospan, gây ra các triệu chứng như buồn nôn, ói mửa, tiêu chảy và kích thích.\n\nNgoài ra, còn có một tình trạng khác được gọi là "Quá Liều" liên quan đến việc sử dụng Debby vượt quá liều lượng được chỉ định. Quá liều Dentanalgi và quá liều Didicera chưa được ghi nhận phản ứng không mong muốn.\n\nQuá liều thuốc Auclanityl có thể gây ra các triệu chứng bất thường và cần được xử lý tại bệnh viện. Chưa có thông tin cụ thể về tình trạng quá liều Differin.\n\nQuá liều Diurefar có thể gây mất nước và điện giải, giảm thể tích máu dẫn đến hạ huyết áp, hạ kali huyết, nhiễm kiềm giảm clor.\n\nTình trạng quá liều Atocib cũng cần xử lý bằng các biện pháp hỗ trợ thông thường.\n\nQuá liều BoniDiabet cũng là tình trạng cần được xử lý khi dùng quá liều thuốc này.\n\nCuối cùng, quá liều cũng có thể xảy ra với Acarbose, cần tránh việc uống đồ uống hoặc thức ăn chứa nhiều carbohydrate trong 4 – 6 giờ.\n\nQuá liều Acid nalidixic cũng có thể gây ra các triệu chứng như loạn tâm thần nhiễm độc, tình trạng co giật, tăng áp lực nội sọ, và toan chuyển hóa buồn nôn, nôn.\n\nQuá liều Albendazol gây ra các triệu chứng cần được điều trị triệu chứng và các biện pháp hồi sức cấp cứu.\n\nQuá liều Betamethasone cũng là một tình trạng liên quan đến việc sử dụng quá nhiều Betamethasone.\n\nQuá liều Betex rất hiếm gặp nhưng có thể gây ra các triệu chứng như bệnh thần kinh cảm giác liên quan đến chứng mất điều hòa.\n\nQuá liều cũng có thể xảy ra khi dùng quá nhiều Bisacodyl.\n\nQuá liều Alpha Brain có thể gây ra triệu chứng bất thường cần được xử lý cấp cứu.\n\nChưa có báo cáo về trường hợp quá liều Broncho-Vaxom.\n\nQuá liều Brosafe cũng là tình trạng sử dụng thuốc Brosafe vượt quá liều lượng khuyến nghị.\n\nQuá liều là tình trạng dùng quá nhiều thuốc trong một khoảng thời gian. Dùng quá liều Carbomango cũng có thể gây hại và cần được xử lý kịp thời tại cơ sở y tế.\n\nQuá liều Cavinton có thể gây ra các triệu chứng bất thường cần được xử lý tại trạm y tế hoặc bệnh viện.\n\nQuá liều cũng là tình trạng sử dụng quá liều thuốc Ceelin hoặc vitamin C.\n\nQuá liều cũng cần xử lý các triệu chứng mà không có thuốc giải độc đặc trị.\n\nQuá liều là tình trạng cần ngừng sử dụng Chophytol và đến cơ sở y tế gần nhất để được xử lý kịp thời.\n\nQuá liều cũng có thể xảy ra khi dùng quá nhiều Chymobest.\n\nQuá liều cũng bao gồm tình trạng cần xử lý khi dùng quá nhiều thuốc Cialis.\n\nQuá liều cũng có thể gây ra chóng mặt nghiêm trọng hoặc suy nhược cơ thể khi sử dụng Co-Diovan.\n\nQuá liều cũng là tình trạng xảy ra khi dùng quá nhiều Concor®. Đặc biệt, tình trạng quá liều có thể gây tác hại khác nhau ở mỗi người, đặc biệt nhạy cảm với bệnh nhân suy tim.\n\nQuá liều Coversyl Plus có thể gây hạ huyết áp, choáng váng, nôn, chuột rút, buồn ngủ, rối loạn tâm thần.\n\nQuá liều cũng có thể xảy ra khi dùng Cyclo-Progynova.\n\nQuá liều là tình trạng dùng quá liều Irbesartan, có thể gây hạ huyết áp và nhịp tim nhanh.\n\nQuá liều Bar là tình trạng dùng quá nhiều thuốc Bar, chưa có báo cáo cụ thể về trường hợp này.\n\nQuá liều thuốc xịt mũi Aladka có thể gây ra các triệu chứng như mạch đập nhanh và không đều, tăng huyết áp, rối loạn nhận thức.\n\nDùng quá liều Coldi B có thể gây suy giảm chức năng hệ thần kinh trung ương.\nLàm Ấm Bụng: Tiêu làm ấm bụng.\nSử Dụng Thuốc: Sử dụng thuốc cần tuân thủ hướng dẫn sử dụng về liều dùng, cách dùng của nhà sản xuất hoặc theo chỉ định của bác sĩ.&lt;SEP&gt;Sử dụng thuốc, rượu hoặc đồ ăn để đối phó là một dấu hiệu hành vi của kiệt sức.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị bệnh.&lt;SEP&gt;Sử dụng thuốc có thể gây khô miệng.&lt;SEP&gt;Sử dụng thuốc có thể gây tác dụng phụ như mất thăng bằng hoặc mất vững.&lt;SEP&gt;Sử dụng thuốc là phương pháp điều trị nội khoa, giúp kiểm soát triệu chứng.&lt;SEP&gt;Sử dụng thuốc Benzalkonium Chloride theo hướng dẫn cụ thể.\nThuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để phòng ngừa và điều trị loãng xương và nhuyễn xương.\nThái: Thái là dược liệu không nên dùng cùng với Bạch truật.\nBồi Bổ Sức Khỏe Cho Trẻ Nhỏ: Bồi bổ sức khỏe cho trẻ nhỏ là tác dụng của dền cơm.\nNgười Lái Xe: Người Lái Xe là người điều khiển phương tiện giao thông. Họ cần phải thận trọng khi sử dụng một số loại thuốc vì chúng có thể gây ra các tác dụng phụ ảnh hưởng đến khả năng lái xe. Cụ thể, Người Lái Xe không nên sử dụng thuốc Acecyst do có thể gây tác động lên hệ thần kinh và cũng không nên sử dụng Acnequidt 20 ml. Khi sử dụng thuốc Argide, nếu gặp tác dụng phụ liên quan đến thần kinh, Người Lái Xe nên dừng lái xe. Tương tự, nếu gặp tác dụng phụ như chóng mặt hoặc nhức đầu sau khi sử dụng Citalopram, họ cũng cần tạm dừng lái xe để đảm bảo an toàn. Tuy nhiên, chưa có ghi nhận về việc thuốc Bảo Thanh có ảnh hưởng tới khả năng lái xe của Người Lái Xe.&lt;SEP&gt;Người lái xe cần thận trọng khi sử dụng Cefurich.&lt;SEP&gt;Người lái xe cần thận trọng khi dùng Cefurobiotic.&lt;SEP&gt;Người lái xe cần thận trọng khi sử dụng Diurefar.&lt;SEP&gt;Người lái xe là đối tượng cần thận trọng khi sử dụng Clonazepam.\nCanh Móng Giò Heo Và Mướp Khía: Canh móng giò heo và mướp khía tươi là bài thuốc lợi sữa.\nCanh Cá Diếc - Nôn: Canh cá diếc nấu với quả Sấu được dùng để chữa trị nôn trong thời kỳ thai nghén.\nCalci D Hasan - Phụ Nữ Có Thai: Phụ nữ có thai cần được theo dõi chặt chẽ khi sử dụng Calci D Hasan.\nLoãng Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị loãng xương.\nCalci D Hasan - Thuốc Điều Trị: Calci D Hasan là một trong những thuốc điều trị được đề cập.\nLàm Ấm Bụng - Tiêu: Tiêu làm ấm bụng.\nCalci D Hasan - Quá Liều: Người dùng cần chú ý đến các biểu hiện lâm sàng khi sử dụng quá liều Calci D Hasan.\nBồi Bổ Sức Khỏe Cho Trẻ Nhỏ - Dền Cơm: Dền cơm có tác dụng bồi bổ sức khỏe cho trẻ nhỏ.\nSử Dụng Thuốc - Thái: Phụ nữ có thai cần cẩn thận khi sử dụng thuốc.\nAgi-Calci - Thiếu Calci: Agi-Calci được chỉ định dùng trong trường hợp thiếu calci.\nCalci D Hasan - Người Lái Xe: Người lái xe cần tuân thủ liều lượng khuyến cáo khi sử dụng Calci D Hasan.\nCalci D Hasan - Thiếu Calci: Calci D Hasan giúp cải thiện tình trạng thiếu calci.\nSử Dụng Thuốc - Thai: Phụ nữ có thai cần tham khảo ý kiến bác sĩ trước khi sử dụng thuốc.\nCalci D Hasan - Kích Ứng Hệ Tiêu Hóa: Calci D Hasan có thể gây kích ứng hệ tiêu hóa.\nCalci D Hasan - Cho Con Buu: Người cho con bú cần được theo dõi chặt chẽ khi sử dụng Calci D Hasan.\nCalci D Hasan - Khó Chịu Ở Dạ Dày: Calci D Hasan có thể gây khó chịu ở dạ dày.\nPhụ Nữ Có Thai - Quế Chi: Thận trọng khi dùng Quế chi cho phụ nữ có thai.\nCây Dướng - Gặm Nhấm: Gặm nhấm ăn quả Dướng khi chín.\nCalcigenol - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng khi dùng Calcigenol.\nCanh Móng Giò Heo Và Mướp Khía - Lợi Sữa: Canh móng giò heo và mướp khía được sử dụng để điều trị lợi sữa.\nThuốc Nam - Thủ Thuật Y Khoa: Thuốc Nam cần tránh tự ý sử dụng trong thai kỳ.\nCháo Cá Mè Và Mướp Khía - Lợi Sữa: Cháo cá mè và mướp khía được sử dụng để điều trị lợi sữa.\nCanh Cá Diếc - Quả Sấu: Quả Sấu là thành phần chính trong canh cá diếc.\nNhuyễn Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị nhuyễn xương.']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Không, phụ nữ mang thai và cho con bú không nên tự ý sử dụng Calci D Hasan. Thuốc này cần được sử dụng dưới sự giám sát của bác sĩ để đảm bảo an toàn cho cả mẹ và thai nhi. Calci và vitamin D trong thuốc có thể được bài tiết vào sữa mẹ, vì vậy cần thận trọng khi sử dụng.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Không, không nên tự ý sử dụng thuốc.</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.9555697066399924</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Naive</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>-1</v>
+        <v>0.8388924266349981</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Context Precision</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uống thuốc Comiaryl đúng cách như thế nào?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>['Trường Hợp Quá Liều: Trường hợp quá liều là tình trạng dùng quá liều thuốc Comiaryl, cần gọi ngay cho trung tâm cấp cứu.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nNgứa, Nổi Ban Đỏ: Ngứa, nổi ban đỏ là tác dụng phụ của thuốc Comiaryl.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nHạ Đường Huyết Quá Mức: Hạ đường huyết quá mức là tác dụng phụ có thể xảy ra khi điều trị bằng thuốc Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức là một tác dụng phụ có thể xảy ra khi sử dụng Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức là tác dụng phụ của thuốc Comiaryl.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nComiaryl: Thuốc Comiaryl được sản xuất bởi Công ty TNHH Hasan – Dermapharm, có công dụng điều trị đái tháo đường type 2 kết hợp với chế độ ăn kiêng và luyện tập thể dục.&lt;SEP&gt;Thuốc Comiaryl được chỉ định dùng trong các trường hợp điều trị đái tháo đường type 2 kết hợp với chế độ ăn kiêng và luyện tập thể dục.&lt;SEP&gt;Thuốc Comiaryl được sử dụng trong điều trị bệnh, cần tuân thủ chế độ ăn kiêng và luyện tập thể dục.&lt;SEP&gt;Thuốc Comiaryl có thể gây rối loạn tiêu hóa, hạ đường huyết quá mức, rối loạn thị giác thoáng qua và ngứa, nổi ban đỏ. Thuốc cũng có thể gây nhiễm toan lactic do tích lũy metformin ở người suy thận, suy gan, nghiện rượu và giảm oxy huyết.&lt;SEP&gt;Comiaryl là thuốc được sử dụng trong điều trị đái tháo đường, nhưng chống chỉ định đối với bệnh nhân suy thận, suy gan, ngộ độc rượu cấp tính, hoại thư, thiếu dinh dưỡng.&lt;SEP&gt;Comiaryl là thuốc chứa glimepirid và metformin.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nThực Hiện Liều Dùng Thuốc: Thực hiện liều dùng thuốc là cách sử dụng thuốc Berodual đúng cách.\nCo-Diovan: Co-Diovan là thuốc gồm hai hoạt chất là valsartan và hydrochlorothiazide, được sử dụng trong điều trị tăng huyết áp.&lt;SEP&gt;Co-Diovan là thuốc chứa valsartan và hydrochlorothiazide.&lt;SEP&gt;Co-Diovan là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Thuốc Co-Diovan chứa valsartan và hydrochlorothiazide.\nHướng Dẫn Sử Dụng Thuốc: Hướng dẫn sử dụng thuốc cần được đọc kỹ trước khi dùng và tốt nhất là xin ý kiến bác sĩ.&lt;SEP&gt;Hướng dẫn sử dụng thuốc là chỉ dẫn về cách sử dụng thuốc đúng cách.\nLiều Thuốc: Liều thuốc là lượng thuốc cần thiết và được sử dụng trong mỗi lần uống hoặc tiêm, cũng như trong một khoảng thời gian cụ thể. Không chỉ đơn thuần là lượng thuốc cần dùng trong mỗi lần uống, liều thuốc còn là lượng thuốc cần thiết để đạt hiệu quả điều trị. Nó có thể được sử dụng để điều trị bằng cách áp dụng phương pháp điều trị với các loại thuốc khác nhau, ví dụ như Aibezym, theo đúng liều lượng. Liều thuốc cũng đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, như tăng canxi huyết, đòi hỏi việc xác định đúng liều lượng cho từng trường hợp cụ thể để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn.\n\nĐể đạt hiệu quả tốt nhất, liều thuốc cần được tuân thủ theo đúng hướng dẫn sử dụng hoặc chỉ định của bác sĩ và khuyến nghị của nhà sản xuất. Điều này bao gồm việc sử dụng đúng liều lượng cho từng loại thuốc cụ thể, ví dụ như Betadine Throat Spray. Việc quên liều hoặc cố gắng bù đắp bằng cách dùng gấp đôi liều đều không được khuyến khích. Thay vào đó, nếu bạn quên một liều thuốc, bạn nên tiếp tục lịch trình sử dụng thuốc của mình và không nên dùng gấp đôi liều để bù vào liều đã quên.\n\nLiều thuốc Diorophyl cần được tuân thủ theo chỉ định của bác sĩ, không nên sử dụng quá liều khuyến cáo. Liều thuốc cũng là cách sử dụng thuốc theo lịch trình đã xác định, như khi sử dụng Atocib hoặc Ceritine. Liều thuốc đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, đòi hỏi sự chính xác và tuân thủ chặt chẽ về liều lượng.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc Co-Diovan, bao gồm hướng dẫn về việc quên thuốc và sử dụng liều kế tiếp.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc theo đúng hướng dẫn của bác sĩ để đảm bảo an toàn.\nDavyca: Davyca là thuốc cần được uống đúng liều và đúng thời điểm mỗi ngày để đạt hiệu quả tốt nhất.\nCách Dùng Và Liều Dùng: Cách dùng và liều dùng của mướp tây bao gồm việc sử dụng trong chế biến thức ăn như luộc, xào, nấu canh, nấu nước uống hoặc dùng ngoài.&lt;SEP&gt;Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nTuân Thủ Liều Thuốc: Tuân thủ liều thuốc là việc cần thiết để đảm bảo hiệu quả và an toàn khi sử dụng Ampicillin Domesco.\nPhụ TỬ: Phụ tử là một vị thuốc được sử dụng kết hợp với Khoai nưa trong hỗ trợ điều trị liệt nửa người.\nKhí Dung: Khí dung là cách dùng của Combivent®.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nBerberin Mộc Hương: Berberin Mộc Hương là thuốc được sản xuất tại Việt Nam, có công dụng trị lỵ trực khuẩn, hội chứng lỵ, tiêu chảy, viêm ruột, viêm ống mật, đầy bụng khó tiêu.&lt;SEP&gt;Berberin Mộc Hương là dạng thuốc chứa thành phần Berberin.&lt;SEP&gt;Berberin Mộc Hương là thuốc có các tác dụng phụ và tương tác thuốc cần lưu ý.&lt;SEP&gt;Berberin Mộc Hương là thuốc có giá 7.000 VNĐ một lọ 100 viên.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nCách Dùng: Cách Dùng là hướng dẫn chi tiết về cách thức sử dụng các loại thuốc khác nhau, bao gồm Aleucin, Berberin, Bofit F, cây Thuốc Mọi, Brosafe, Chophytol, và Combivent®. Hướng dẫn này cung cấp thông tin về cách sử dụng mỗi loại thuốc một cách chính xác để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn.\n\nĐối với Aleucin và Berberin, Cách Dùng hướng dẫn người dùng về cách sử dụng thuốc đúng cách. Đối với Bofit F, Cách Dùng mô tả cách thức sử dụng sản phẩm này. Đối với cây Thuốc Mọi, Cách Dùng và Liều Dùng đều tùy thuộc vào mục đích sử dụng cụ thể và từng bài thuốc cụ thể.\n\nTrong trường hợp Brosafe, thuốc được sử dụng qua đường uống và nên được uống sau bữa ăn để đạt hiệu quả điều trị cao nhất. Đối với Chophytol, thuốc cũng được sử dụng qua đường uống nhưng cần uống trước bữa ăn để đạt hiệu quả điều trị tốt nhất. \n\nCuối cùng, Cách Dùng của Combivent® bao gồm việc lắp ống thuốc vào dụng cụ khí dung và kích hoạt chuẩn bị cho lần sử dụng đầu tiên. Cách này giúp đảm bảo rằng người dùng có thể sử dụng Combivent® một cách chính xác và hiệu quả.\n\nNgười dùng được khuyến nghị uống nguyên viên với nước, uống thuốc sau ăn để tránh các tác dụng không mong muốn. Điều này giúp đảm bảo rằng người dùng có thể tận dụng tối đa hiệu quả của thuốc mà vẫn duy trì sự an toàn.\nCánh Kiến Trắng: Cánh kiến trắng là vị thuốc khác cần tránh nhầm lẫn với Cánh kiến đỏ.&lt;SEP&gt;Cánh kiến trắng là tên gọi khác của cây Bồ đề, được sử dụng trong y học cổ truyền với tác dụng khai khiếu, trấn tĩnh, chữa ho.&lt;SEP&gt;Cánh kiến trắng, còn gọi là cây Bồ đề, là vị thuốc có tác dụng trị các bệnh đường hô hấp, hôn mê, bệnh ngoài da.&lt;SEP&gt;Nhựa Cánh kiến trắng được sử dụng để chữa ho, viêm phế quản mạn tính, hen suyễn, trúng phong, hôn mê, đau bụng, nôn ói, làm mau lành vết thương, chữa nẻ vú, viêm nha chu.&lt;SEP&gt;Cánh kiến trắng, còn gọi là An tức hương (Benzoin Gum), được sử dụng để thu nhựa cây.&lt;SEP&gt;Cánh kiến trắng cũng là vị thuốc quý trong điều trị.&lt;SEP&gt;Cánh kiến trắng là vị thuốc quý trong điều trị.\nHuyền Hồ: Huyền hồ là dược liệu được sử dụng kết hợp với cỏ roi ngựa để điều trị kinh nguyệt không thông, huyết ứ, đau bụng dưới.&lt;SEP&gt;Chiết xuất từ Huyền hồ có tác dụng giảm đau, giảm tỷ lệ tâm thất trái/ trọng lượng cơ thể, ức chế kích hoạt tế bào thần kinh, và chống lại sự di căn của ung thư vú.&lt;SEP&gt;Huyền hồ, còn gọi là Huyền hồ sách, Diên hồ sách, Nguyên hồ, là vị thuốc trong Đông y có tác dụng làm tan máu ứ, cầm máu, giảm đau.&lt;SEP&gt;Huyền hồ là một loại dược liệu, rễ củ hình cầu dẹt không đều, mặt ngoài màu vàng hay vàng nâu, mùi nhẹ, vị đắng.&lt;SEP&gt;Huyền hồ là thành phần trong bài thuốc chữa đau do lạnh.&lt;SEP&gt;Huyền hồ là thành phần trong nhiều bài thuốc chữa đau.\nComiaryl - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp khi sử dụng thuốc Comiaryl.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nComiaryl - Đái Tháo Đường: Thuốc Comiaryl được chỉ định điều trị đái tháo đường.&lt;SEP&gt;Comiaryl được sử dụng trong điều trị đái tháo đường.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nBuồn Nôn - Comiaryl: Buồn nôn là tác dụng phụ thường gặp khi sử dụng thuốc Comiaryl.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nComiaryl - Suy Thận: Comiaryl chống chỉ định dùng cho bệnh nhân suy thận.\nCo-Diovan - Liều Thuốc: Hướng dẫn về cách sử dụng liều thuốc Co-Diovan.\nComiaryl - Đau Bụng: Đau bụng có thể xảy ra khi sử dụng Comiaryl.\nCách Dùng Và Liều Dùng - Phụ TỬ: Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nComiaryl - Rượu: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của rượu.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nComiaryl - Suy Gan: Comiaryl chống chỉ định dùng cho bệnh nhân suy gan.\nBerberin Mộc Hương - Hướng Dẫn Sử Dụng: Người dùng cần tuân thủ hướng dẫn sử dụng về liều lượng và cách dùng thuốc Berberin Mộc Hương.\nComiaryl - Rối Loạn Tiêu Hóa: Thuốc Comiaryl có thể gây rối loạn tiêu hóa, bao gồm buồn nôn, nôn, đau bụng, tiêu chảy.\nCách Dùng - Cánh Kiến Trắng: Cách dùng và liều dùng của cây Thuốc mọi tùy thuộc vào mục đích sử dụng và từng bài thuốc.\nComiaryl - Nôn Mửa: Nôn mửa có thể xảy ra khi sử dụng Comiaryl.\nHuyền Hồ - Liều Dùng: Liều dùng chỉ dẫn liều lượng sử dụng Huyền hồ.\nComiaryl - Hạ Đường Huyết: Comiaryl có thể gây hạ đường huyết khi sử dụng.\nComiaryl - Insulin: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của insulin.\nChloramphenicol - Comiaryl: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của chloramphenicol.\nComiaryl - Đái Tháo Đường Type 2: Thuốc Comiaryl được chỉ định dùng trong các trường hợp điều trị đái tháo đường type 2 kết hợp với chế độ ăn kiêng và luyện tập thể dục.&lt;SEP&gt;Thuốc Comiaryl được chỉ định dùng trong các trường hợp điều trị đái tháo đường type 2.\nChức Năng Thận - Comiaryl: Comiaryl có thể ảnh hưởng cấp tính đến chức năng thận.\nComiaryl - Thuốc Lợi Tiểu: Thuốc Comiaryl có thể làm giảm tác dụng hạ đường huyết của thuốc lợi tiểu.\nComiaryl - Probenecid: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của probenecid.\nComiaryl - Quên Liều: Nếu quên liều, tiếp tục uống trong bữa ăn kế tiếp.\nComiaryl - Coumarin: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của coumarin.\nComiaryl - Suy Tim Sung Huyết: Comiaryl chống chỉ định dùng cho bệnh nhân suy tim sung huyết.\nComiaryl - Glimepirid: Thuốc Comiaryl thay thế cho việc sử dụng phối hợp rời hai thuốc glimepirid và metformin.&lt;SEP&gt;Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của glimepirid.&lt;SEP&gt;Comiaryl chứa glimepirid.\nComiaryl - Tetracyclin: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của tetracyclin.\nComiaryl - Thuốc Chẹn Beta: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của thuốc chẹn beta.\nComiaryl - Metformin: Thuốc Comiaryl thay thế cho việc sử dụng phối hợp rời hai thuốc glimepirid và metformin.&lt;SEP&gt;Comiaryl chứa metformin.\nComiaryl - Thuốc Kháng Nấm: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của thuốc kháng nấm.\nComiaryl - Quinolon: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của quinolon.\nChế Độ Ăn Kiêng - Comiaryl: Thuốc Comiaryl yêu cầu bệnh nhân tuân thủ chế độ ăn kiêng.&lt;SEP&gt;Chế độ ăn kiêng là phương pháp điều trị đi kèm khi sử dụng Comiaryl.\nComiaryl - Glimepiride: Glimepiride là một trong hai hoạt chất chính trong thuốc Comiaryl.\nComiaryl - Thiếu Dinh Dưỡng: Comiaryl chống chỉ định dùng cho bệnh nhân thiếu dinh dưỡng.\nComiaryl - Thuốc Lợi Tiểu Thiazid: Thuốc Comiaryl có thể làm giảm tác dụng hạ đường huyết của thuốc lợi tiểu Thiazid.\nComiaryl - Luyện Tập Thể Dục: Thuốc Comiaryl yêu cầu bệnh nhân luyện tập thể dục.&lt;SEP&gt;Luyện tập thể dục là phương pháp điều trị đi kèm khi sử dụng Comiaryl.\nComiaryl - Disopyramid: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của disopyramid.\nComiaryl - Rối Loàn Tiêu Hóa: Rối loạn tiêu hóa là tác dụng phụ thường gặp khi sử dụng thuốc Comiaryl.\nComiaryl - Sulfonamide: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của sulfonamide.\nComiaryl - Đường Niệu: Đường niệu cần được theo dõi khi sử dụng Comiaryl.&lt;SEP&gt;Cần theo dõi đường niệu thường xuyên khi sử dụng Comiaryl.\nComiaryl - Glucose Huyết: Glucose huyết cần được theo dõi khi sử dụng Comiaryl.&lt;SEP&gt;Cần theo dõi glucose huyết thường xuyên khi sử dụng Comiaryl.\nComiaryl - Hoại Thư: Comiaryl chống chỉ định dùng cho bệnh nhân hoại thư.\nChụp X Quang - Comiaryl: Chụp X-quang cần tạm thời ngừng sử dụng Comiaryl.\nComiaryl - Trụy Tim Mạch: Comiaryl chống chỉ định dùng cho bệnh nhân trụy tim mạch.\nComiaryl - Vọp Bẻ: Vọp bẻ có thể xảy ra khi sử dụng Comiaryl.\nComiaryl - Ngộ Độc Rượu Cấp Tính: Comiaryl chống chỉ định dùng cho bệnh nhân ngộ độc rượu cấp tính.\nComiaryl - Nhiễm Toan Lactic: Thuốc Comiaryl có thể gây nhiễm toan lactic, đặc biệt ở người suy thận, suy gan, nghiện rượu và giảm oxy huyết.\nComiaryl - Metformin Hydrochlorid: Metformin hydrochlorid là một trong hai hoạt chất chính trong thuốc Comiaryl.\nComiaryl - Rối Loạn Thị Giác Thoáng Qua: Thuốc Comiaryl có thể gây rối loạn thị giác thoáng qua, bao gồm nhìn mờ thoáng qua, cảm giác khô rát mắt.&lt;SEP&gt;Comiaryl có thể gây rối loạn thị giác thoáng qua khi sử dụng.\nComiaryl - Monoamine Oxidase Inhibitor (MAOI): Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của monoamine oxidase inhibitor (MAOI).\nComiaryl - Thuốc Ức Chế Men Chuyển (ACEi): Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của thuốc ức chế men chuyển (ACEi).\nComiaryl - Nhồi Máu Cơ Tim Cấp Tính: Comiaryl chống chỉ định dùng cho bệnh nhân nhồi máu cơ tim cấp tính.\nComiaryl - Hạ Đường Huyết Quá Mức: Hạ đường huyết quá mức là tác dụng phụ có thể xảy ra khi điều trị bằng thuốc Comiaryl.&lt;SEP&gt;Hạ đường huyết quá mức có thể xảy ra khi sử dụng Comiaryl.&lt;SEP&gt;Thuốc Comiaryl có thể gây hạ đường huyết quá mức.\nComiaryl - Trường Hợp Quá Liều: Trong trường hợp quá liều, cần gọi ngay cho trung tâm cấp cứu.\nComiaryl - Ngứa, Nổi Ban Đỏ: Thuốc Comiaryl có thể gây ngứa, nổi ban đỏ.\nAmaryl M - Comiaryl: Thuốc Comiaryl có thành phần tương tự với thuốc Amaryl M.\nAzulix MF Forte - Comiaryl: Thuốc Comiaryl có thành phần tương tự với thuốc Azulix MF Forte.\nBigonyl - Comiaryl: Thuốc Comiaryl có thành phần tương tự với thuốc Bigonyl.\nComiaryl - Daoryl: Thuốc Comiaryl có thành phần tương tự với thuốc Daoryl.\nComiaryl - Ifosfamid: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của ifosfamid.\nComiaryl - Cytophosphane: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của cytophosphane.\nComiaryl - Non-Steroid Anti-Inflammatory Drug (NSAID): Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của non-steroid anti-inflammatory drug (NSAID).\nComiaryl - Steroid Đồng Hóa Và Nội Tiết Tố Sinh Dục Nam: Thuốc Comiaryl có thể làm tăng tác dụng hạ đường huyết của steroid đồng hóa và nội tiết tố sinh dục nam.\nComiaryl - Diaz: Thuốc Comiaryl có thể làm giảm tác dụng hạ đường huyết của diaz.\nComiaryl - Nhiễm Toan Chuyển Hóa Cấp: Comiaryl chống chỉ định dùng cho bệnh nhân nhiễm toan chuyển hóa cấp.\nChất Cản Quang Chứa Iod - Comiaryl: Comiaryl cần tạm dừng sử dụng trước và sau khi chụp X-quang với chất cản quang chứa iod.\nBệnh Hô Hấp Nặng Giảm Oxy Máu - Comiaryl: Comiaryl chống chỉ định dùng cho bệnh nhân mắc bệnh hô hấp nặng giảm oxy máu.\nBệnh Phổi Thiếu Oxy Mãn Tính - Comiaryl: Comiaryl chống chỉ định dùng cho bệnh nhân mắc bệnh phổi thiếu oxy mãn tính.\nComiaryl - Tiêm Chất Cản Quang: Tiêm chất cản quang chứa iod cần tạm thời ngừng sử dụng Comiaryl.\nDavyca - Quên Liều: Davyca cần được uống đúng liều, nếu quên liều thì uống càng sớm càng tốt.\nBerodual - Thực Hiện Liều Dùng Thuốc: Berodual được sử dụng theo cách thực hiện liều dùng thuốc.\nAmpicillin Domesco - Tuân Thủ Liều Thuốc: Ampicillin Domesco yêu cầu người dùng tuân thủ đúng liều mà bác sĩ đã kê đơn.\nAmpicillin Vidiphar - Hướng Dẫn Sử Dụng Thuốc: Thuốc Ampicillin Vidiphar cần được sử dụng theo hướng dẫn từ bác sĩ.\nDavyca - Ngừng Thuốc: Davyca không nên bị ngừng sử dụng mà không có sự chỉ định của bác sĩ.\nHướng Dẫn Sử Dụng Thuốc - Thuốc Bôi Âm Đạo: Thuốc bôi âm đạo được sử dụng theo hướng dẫn trên nhãn thuốc hoặc theo chỉ định của bác sĩ.\nDavyca - Liều: Davyca cần được uống đúng liều lượng theo chỉ định của bác sĩ.\nDavyca - Lưu Trữ Thuốc: Davyca cần được lưu trữ ở nơi khô ráo, tránh ánh sáng trực tiếp và nhiệt độ không vượt quá 30°C.\nDavyca - Tránh Tầm Tay Trẻ Em: Davyca cần được bảo quản tránh xa tầm tay trẻ em.\nCombivent® Respimat® - Khí Dung: Combivent® Respimat® được dùng qua khí dung.']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thuốc Comiaryl được chỉ định dùng trong các trường hợp điều trị đái tháo đường type 2 kết hợp với chế độ ăn kiêng và luyện tập thể dục. Để sử dụng thuốc Comiaryl một cách hiệu quả, bạn cần tuân thủ các hướng dẫn sau:
+### 1. Thời điểm uống thuốc
+Bạn nên uống thuốc Comiaryl ngay trước hoặc trong bữa ăn. Điều này giúp giảm thiểu tác dụng phụ như buồn nôn và nôn.
+### 2. Liều lượng
+- Nên bắt đầu điều trị với liều thấp nhất có tác dụng trị liệu.
+- Điều chỉnh liều theo từng trường hợp cụ thể của mỗi bệnh nhân.
+- Liều tối đa hàng ngày của thuốc Comiaryl không nên vượt quá 2 viên (bệnh nhân chỉ được uống tối đa một ngày 2 lần, mỗi lần uống 1 viên).
+### 3. Lưu ý khi sử dụng
+- Tránh sử dụng thuốc Comiaryl cho bệnh nhân suy thận, người bệnh lý cấp tính có nguy cơ gây suy thận, người bị suy gan, ngộ độc rượu cấp tính, suy tim sung huyết, trụy tim mạch, nhồi máu cơ tim cấp tính, người mắc bệnh hô hấp nặng giảm oxy máu, bệnh phổi thiếu oxy mãn tính, hoại thư, người nghiện rượu, thiếu dinh dưỡng.
+- Trong quá trình sử dụng thuốc Comiaryl, bệnh nhân cần tuân thủ chế độ ăn kiêng và luyện tập thể dục.
+- Thường xuyên theo dõi glucose huyết và đường niệu.
+- Tránh quên liều, nếu quên liều thì uống càng sớm càng tốt. Không nên uống gấp đôi liều để bù vào liều đã quên.
+### 4. Bảo quản
+- Bảo quản thuốc Comiaryl ở nơi khô thoáng, nhiệt độ dưới 30°C.
+- Tránh ánh sáng.
+### 5. Tác dụng phụ
+- Rối loạn tiêu hóa: buồn nôn, nôn, đau bụng, tiêu chảy.
+- Hạ đường huyết quá mức.
+- Rối loạn thị giác thoáng qua: nhìn mờ thoáng qua, cảm giác hơi khô rát mắt.
+- Ngứa, nổi ban đỏ.
+### 6. Xử lý khi quá liều
+Trong trường hợp bị quá liều khi sử dụng thuốc Comiaryl, hãy gọi ngay cho trung tâm cấp cứu hoặc đến cơ sở y tế địa phương gần nhất.
+### 7. Lưu ý
+- Trong quá trình điều trị, không nên ngừng thuốc khi chưa có sự chỉ định của bác sĩ.
+- Không nên sử dụng thuốc sau khi đã hết hạn ghi trên bao bì.
+### 8. Giá bán
+Giá tham khảo của thuốc Comiaryl là 89.000 VNĐ/hộp thuốc Comiaryl (3 vỉ x 10 viên). Giá có thể thay đổi theo từng thời điểm.
+### 9. Tham khảo ý kiến bác sĩ
+Trước khi sử dụng thuốc Comiaryl, bạn cần đọc kỹ hướng dẫn sử dụng thuốc Comiaryl. Đồng thời, tham khảo ý kiến của bác sĩ hoặc chuyên gia để được tư vấn kỹ hơn.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nên uống nguyên viên thuốc Comiaryl với một cốc nước đầy.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.7253906293947594</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="I5" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>0.5751302097649198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Calci D Hasan có thể gây ảnh hưởng gì đến bệnh nhân mắc bệnh lý nền?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>['Thiếu Calci: Thiếu calci là tình trạng cần bổ sung calci trong trẻ em thời kỳ phát triển, phụ nữ có thai và cho con bú.&lt;SEP&gt;Thiếu calci là tình trạng dinh dưỡng kém được Calci D Hasan giúp cải thiện.\nBệnh Lý Nền: Người mắc bệnh lý nền cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng khi sử dụng Calci D Hasan.&lt;SEP&gt;Bệnh lý nền là các tình trạng bệnh lý sẵn có làm tăng khả năng gặp tác dụng phụ khi dùng thuốc.\nThuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để phòng ngừa và điều trị loãng xương và nhuyễn xương.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nGãy Xương Do Bệnh Lý: Gãy xương do bệnh lý là triệu chứng của tăng canxi máu.\nTác Dụng Không Mơ Nguyện: Tác dụng không mong muốn có thể xảy ra khi sử dụng vị thuốc.\nCanxi Huyết: Canxi huyết tăng có thể xảy ra ở người mắc các bệnh hoặc tình trạng có thể làm tăng canxi huyết.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nHội Chứng Tăng Canxi Huyết: Hội chứng tăng canxi huyết là tình trạng tăng canxi trong máu.\nBạch Cầu Cấp: Bạch cầu cấp là thể bệnh ác tính ở trẻ em, chiếm khoảng 30% trong số các bệnh ung thư ở trẻ em. Nó bao gồm bạch cầu cấp dòng lympho và các thể khác như ung thư xương, ung thư não.&lt;SEP&gt;Bạch cầu cấp là một thể bệnh cấp tính nguy hiểm, cần điều trị kịp thời.&lt;SEP&gt;Bạch cầu cấp là bệnh lý gây giảm tiểu cầu, tăng nguy cơ chảy máu lâu cầm.&lt;SEP&gt;Bạch cầu cấp là tình trạng tăng nhanh bất thường của các tế bào máu trắng.\nU Xương Di Căn: U xương di căn là bệnh có thể làm tăng canxi huyết.\nTác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.&lt;SEP&gt;Tác dụng phụ của một số thuốc có thể ảnh hưởng lên huyết áp.\nHội Chứng Tăng Calci Trong Máu: Hội chứng tăng calci trong máu có thể xảy ra ở những người có tiền sử bệnh như bệnh tăng năng cận giáp, quá liều do vitamin D, hoặc u ác tính tiêu xương.\nKháng Sinh Phổ Rộng: Kháng sinh phổ rộng là phương pháp điều trị nhiễm trùng huyết do thắt dây chun.&lt;SEP&gt;Kháng sinh phổ rộng được sử dụng để điều trị viêm nhiễm đường tiêu hóa.&lt;SEP&gt;Kháng sinh phổ rộng đôi khi được sử dụng để điều trị nhiễm trùng đường hô hấp trên do vi khuẩn.&lt;SEP&gt;Kháng sinh phổ rộng là loại thuốc được sử dụng để điều trị nhiễm trùng do nhiều loại vi khuẩn khác nhau.\nGãy Xương Bất Thường: Gãy xương bất thường là triệu chứng do tăng canxi máu.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nTăng PTH Huyết Thanh: Tăng PTH huyết thanh là triệu chứng của loạn chuyển hóa calcium và phospho.\nTác Dụng Phụ Nghiêm Trọng: Tác dụng phụ nghiêm trọng là biểu hiện có thể xảy ra khi sử dụng quá liều Amlor 5 Pfizer.&lt;SEP&gt;Tác dụng phụ nghiêm trọng có thể xảy ra khi sử dụng Ciacca, đặc biệt đối với phụ nữ trong độ tuổi sinh sản không có biện pháp tránh thai phù hợp.&lt;SEP&gt;Tác dụng phụ nghiêm trọng xảy ra khi uống rượu cùng với một số loại thuốc.\nCanxi Máu Tăng: Canxi máu tăng là tình trạng nồng độ canxi trong máu tăng cao.\nNiêm Mạc Dạ Dày: Niêm Mạc Dạ Dày là bề mặt trong cùng của dạ dày, đóng vai trò như một lớp niêm mạc bảo vệ dạ dày khỏi các tác nhân gây hại. Lớp niêm mạc này có cấu trúc dạng nếp gấp, giúp tiêu hóa thức ăn và là vị trí dễ bị tổn thương do nhiều nguyên nhân khác nhau. Niêm mạc dạ dày chịu tác động tiêu cực từ các hoạt chất như Guaifenesin trong Cedipect F, Saponin triterpen từ quả bồ kết, tinh dầu sả, và Crotamiton. Ngoài ra, nó còn bị ảnh hưởng bởi thuốc NSAIDs, đặc biệt là những thuốc ức chế COX-1.\n\nNiêm mạc dạ dày được bảo vệ bởi nhiều yếu tố khác nhau, bao gồm cả các hoạt chất tự nhiên từ thảo dược như cây Bồ bồ, cây Nổ, và cây Thất diệp nhất chi hoa. Các hoạt chất Bergenin từ cây Nổ, Biviantac, và kim vàng đều giúp bảo vệ niêm mạc dạ dày. Enzim Cyclooxygenase – 1 (COX – 1), các thuốc giảm tiết, và các thuốc bảo vệ niêm mạc cũng đóng vai trò quan trọng trong việc bảo vệ niêm mạc dạ dày. Niêm mạc dạ dày còn được bảo vệ bởi Codonopsis pilosula, ngọc cẩu, và Sài đất. Các nghiên cứu cho thấy chiết xuất quả sung cũng giúp bảo vệ niêm mạc dạ dày khỏi tổn thương oxy hóa.\n\nNiêm mạc dạ dày là vị trí bị tổn thương trong các tình trạng như hội chứng Zollinger-Ellison và loét dạ dày, cũng như là vị trí tác dụng của thuốc bao phủ niêm mạc dạ dày. Nó có thể bị tổn thương bởi rượu hoặc thuốc indomethacin, và có thể bị kích thích bởi việc sử dụng rau diếp sống hoặc acid acetylsalicylic. Niêm mạc dạ dày cũng bị tổn thương khi dùng thuốc Chymodok và bị ảnh hưởng bởi việc sử dụng thuốc nói chung.\n\nNiêm mạc dạ dày bị tổn thương bởi nhiều yếu tố, trong đó có bệnh viêm loét dạ dày. Curcumin được biết đến với khả năng tái tạo niêm mạc dạ dày trong bệnh này. Ngoài ra, các sản phẩm như CumarGold cũng hỗ trợ bảo vệ niêm mạc dạ dày. Chất xơ trong trái tắc cũng được đề cập đến như một yếu tố bảo vệ niêm mạc dạ dày, tuy nhiên niêm mạc dạ dày cũng có thể bị kích thích bởi acid hữu cơ trong trái tắc.\n\nNhìn chung, niêm mạc dạ dày là một cấu trúc phức tạp, chịu tác động từ nhiều yếu tố khác nhau, bao gồm cả các tác nhân tự nhiên và thuốc. Việc bảo vệ niêm mạc dạ dày là rất quan trọng để duy trì sức khỏe tổng thể của dạ dày.\nThần Kinh Trung Ương: Thần kinh trung ương là hệ thống gồm não và tủy sống, chịu trách nhiệm kiểm soát và điều khiển các chức năng cơ bản của cơ thể. Hệ thống này đóng vai trò quan trọng trong việc điều khiển và phối hợp các hoạt động của cơ thể. Thần kinh trung ương có thể bị ảnh hưởng bởi nhiều yếu tố khác nhau, bao gồm cả việc sử dụng một số loại thuốc và thực vật nhất định. \n\nCụ thể, sử dụng đồng thời ma hoàng và yohimbin có thể gây kích thích cho thần kinh trung ương. Bạc hà cũng có thể ảnh hưởng đến hệ thống này khi được sử dụng. Ngoài ra, việc uống nhầm Benzyl benzoate hoặc lạm dụng bình vôi cũng có thể gây kích thích cho thần kinh trung ương. Một số loại thuốc như Rotudin, khi được sử dụng trong thời gian dài, cũng có thể gây kích thích cho hệ thống này. Độc tố từ thân và rễ cây Cơm nguội cũng có thể tác động đến thần kinh trung ương.\n\nNgoài ra, thần kinh trung ương còn chịu ảnh hưởng từ strychnin và hoạt chất xanthumin trong ké đầu ngựa. Tuy nhiên, hệ thống này không bị ảnh hưởng bởi tác dụng phụ của Alpha Brain. Thần kinh trung ương có thể bị tổn thương do Sarcoidosis và được kiểm tra bằng PET hoặc MRI.&lt;SEP&gt;Thuốc Broncho-Vaxom có thể tác động lên thần kinh trung ương.&lt;SEP&gt;Thần kinh trung ương có thể bị ảnh hưởng bởi việc sử dụng thuốc.&lt;SEP&gt;Thần kinh trung ương là hệ thống thần kinh có thể bị ảnh hưởng bởi moxifloxacin, gây ra co giật.\nLái Xe: Lái xe là một nghề nghiệp đòi hỏi sự tập trung cao độ và tầm nhìn rõ ràng. Hoạt động lái xe có thể bị ảnh hưởng bởi nhiều yếu tố, bao gồm cả tác dụng phụ của một số loại thuốc. Các tác dụng phụ của thuốc như A.T.P., Acecyst, Fexofenadine, Agirenyl, Appeton Lysine Syrup, Amiodarone, Cavinton, và Clorpheniramin có thể gây ra các triệu chứng như buồn ngủ, đau đầu, chóng mặt, ù tai, mất thính lực, và thậm chí ảnh hưởng đến khả năng tập trung. Đặc biệt, việc sử dụng thuốc Auclanityl có thể gây buồn ngủ và ảnh hưởng thị lực. Trong khi đó, việc sử dụng Amepox Soft Capsule, Allopurinol, và Albendazol không được cho là sẽ ảnh hưởng đến khả năng lái xe. Tuy nhiên, việc sử dụng Citicoline, Cholapan, sulfamethoxazol, và Decolgen Forte không được khuyến nghị khi lái xe do tác dụng an thần hoặc các tác dụng phụ khác có thể ảnh hưởng đến khả năng lái xe.\n\nNgười lái xe cần kiểm tra kỹ để xác định liệu các loại thuốc cụ thể có ảnh hưởng đến khả năng tập trung hay không. Ví dụ, việc sử dụng acetylcystein không yêu cầu người lái xe phải tránh lái xe đặc biệt. Tuy nhiên, việc sử dụng thuốc Bifril có thể gây chóng mặt và làm giảm khả năng lái xe an toàn.\n\nTóm lại, lái xe là một hoạt động cần được kiểm soát chặt chẽ về mặt sức khỏe và an toàn, đặc biệt là liên quan đến tác dụng phụ của thuốc.&lt;SEP&gt;Lái xe là hoạt động cần thận trọng khi sử dụng thuốc Daflon.&lt;SEP&gt;Lái xe là công việc đòi hỏi sự tập trung cao độ.&lt;SEP&gt;Lái xe là hoạt động mà Advil không gây ảnh hưởng.&lt;SEP&gt;Thuốc không gây ảnh hưởng đến khả năng lái xe.\nCanxi Máu Tăng - Suy Thận: Tăng canxi máu có thể gây ra suy thận.\nBệnh Lý Nền - Tác Dụng Phụ: Bệnh lý nền làm tăng khả năng gặp tác dụng phụ khi dùng thuốc.\nCanxi Máu Tăng - Ung Thư: Ung thư có thể gây ra tăng canxi máu.\nTác Dụng Không Mơ Nguyện - Vị Thuốc: Vị thuốc có thể gây ra các tác dụng không mong muốn.\nCanxi Máu Tăng - Loãng Xương: Tăng canxi máu có thể gây ra loãng xương.\nBạch Cầu Cấp - Tác Dụng Phụ Của Thuốc: Tác dụng phụ của thuốc là một vấn đề cần lưu ý trong quá trình điều trị bệnh bạch cầu cấp.\nCanxi Máu Tăng - Sỏi Thận: Tăng canxi máu có thể gây ra sỏi thận.\nKháng Sinh Phổ Rộng - Tác Dụng Phụ: Sử dụng kháng sinh có liên quan đến nhiều tác dụng phụ.\nLoãng Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị loãng xương.\nThuốc - Tác Dụng Phụ Nghiêm Trọng: Một số loại thuốc có thể gây tác dụng phụ nghiêm trọng.\nCanxi Máu Tăng - Corticosteroid: Corticosteroid được sử dụng trong điều trị tăng canxi máu.\nNiêm Mạc Dạ Dày - Thuốc: Thuốc có thể ảnh hưởng đến niêm mạc dạ dày.\nGãy Xương Do Bệnh Lý - Tăng Canxi Máu: Tăng canxi máu gây ra gãy xương do bệnh lý.\nThuốc - Thần Kinh Trung Ương: Thuốc có thể ảnh hưởng đến thần kinh trung ương.\nGãy Xương Bất Thường - Tăng Canxi Máu: Gãy xương bất thường là triệu chứng do tăng canxi máu.\nLái Xe - Thuốc: Thuốc có thể ảnh hưởng bất lợi đến khả năng lái xe.\nBriozcal - Hội Chứng Tăng Canxi Huyết: Briozcal bị chống chỉ định trong hội chứng tăng canxi huyết.\nThận - Triệu Chứng Bất Thường: Triệu chứng bất thường có thể ảnh hưởng đến chức năng thận.\nAgi-Calci - Thiếu Calci: Agi-Calci được chỉ định dùng trong trường hợp thiếu calci.\nBác Sĩ - Tác Dụng Phụ: Bác sĩ cần thông báo nếu có tác dụng phụ khi dùng thuốc.\nCalci D Hasan - Thiếu Calci: Calci D Hasan giúp cải thiện tình trạng thiếu calci.\nCalci - Hội Chứng Tăng Calci Trong Máu: Calci có thể gây ra hội chứng tăng calci trong máu ở những người có tiền sử bệnh.\nCanxi Máu Tăng - Lọc Máu: Lọc máu loại bỏ canxi và chất thải thừa trong máu khi bị tổn thương thận.\nCanxi Máu Tăng - Nhịp Tim Không Đều: Tăng canxi máu có thể gây ra nhịp tim không đều.\nCalcitonin - Canxi Máu Tăng: Calcitonin được sử dụng trong điều trị tăng canxi máu.\nCanxi - D Mekophar - Canxi Huyết: Canxi - D Mekophar có thể làm tăng canxi huyết.\nCanxi - D Mekophar - U Xương Di Căn: Canxi - D Mekophar chống chỉ định ở người mắc u xương di căn.\nCanxi Máu Tăng - Thuốc Lợi Tiểu Quai: Thuốc lợi tiểu quai giúp thận di chuyển chất lỏng và loại bỏ thêm canxi.\nCanxi Máu Tăng - Dịch Truyền Tĩnh Mạch: Dịch truyền tĩnh mạch giúp giảm nồng độ canxi trong máu.\nCanxi Máu Tăng - Cường Cận Giáp Nguyên Phát: Cường cận giáp nguyên phát có thể gây ra tăng canxi máu.\nCanxi Máu Tăng - Lú Lẫn Hoặc Mất Trí Nhớ: Tăng canxi máu có thể gây ra lú lẫn hoặc mất trí nhớ.\nBisphosphonat Tiêm Tĩnh Mạch - Canxi Máu Tăng: Bisphosphonat tiêm tĩnh mạch làm giảm nồng độ canxi trong máu.\nNhuyễn Xương - Thuốc Calci D Hasan: Thuốc Calci D Hasan được sử dụng để điều trị nhuyễn xương.\nLoạn Chuyển Hóa Calcium Và Phospho - Tăng PTH Huyết Thanh: Tăng PTH huyết thanh là triệu chứng của loạn chuyển hóa calcium và phospho.']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Người mắc bệnh lý nền cần thông báo với bác sĩ về tiền sử bệnh và các thuốc đang dùng khi sử dụng Calci D Hasan. Bệnh lý nền làm tăng khả năng gặp tác dụng phụ khi dùng thuốc. Điều này có nghĩa là nếu bạn đang mắc một bệnh lý nền, việc sử dụng Calci D Hasan có thể dẫn đến một số tác dụng phụ không mong muốn.
+Việc sử dụng Calci D Hasan có thể gây kích ứng hệ tiêu hóa, có khả năng gây táo bón và khó chịu ở dạ dày. Đặc biệt, Calci D Hasan có thể không phù hợp với những người có tiền sử quá mẫn với bất kỳ thành phần nào của thuốc, hoặc những người mắc bệnh kèm theo hội chứng tăng calci trong máu (như bệnh tăng năng cận giáp, quá liều do vitamin D, có u ác tính tiêu xương…), sỏi thận và suy thận nặng, tăng calci niệu nặng, loãng xương do bất động.
+Do đó, nếu bạn đang mắc một bệnh lý nền, bạn cần thông báo cho bác sĩ về tình trạng sức khỏe hiện tại của mình trước khi bắt đầu sử dụng Calci D Hasan để đảm bảo rằng thuốc này an toàn cho bạn.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ở bệnh nhân mắc bệnh lý nền, Calci D Hasan có thể gây tăng nhạy cảm với vitamin D, làm tăng nguy cơ gây hại cho sức khỏe.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8088076452345828</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6139666171659987</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Những điều kiện cần tránh khi bảo quản sản phẩm Bổ thần kinh H5000 là gì?</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>['Cao Bình Vôi: Cao bình vôi là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Cao bình vôi là thành phần trong thuốc bổ thần kinh H5000.\nBảo Quản Dược Liệu: Bảo quản dược liệu sau khi sơ chế cần được bảo quản ở những nơi khô.&lt;SEP&gt;Bảo quản dược liệu trong bọc kín, hũ nhựa hay thủy tinh, cất trữ nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.&lt;SEP&gt;Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.&lt;SEP&gt;Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ, tránh nơi ẩm mốc và ánh nắng trực tiếp.&lt;SEP&gt;Bảo quản dược liệu cần để nơi khô ráo, thông thoáng.\nCảm Nắng Nóng: Cảm nắng nóng là triệu chứng của các bệnh như sốt cao, viêm dạ dày cấp.&lt;SEP&gt;Cảm nắng nóng là triệu chứng do thời tiết nắng nóng.\nQuả: Quả là thuật ngữ chung để chỉ các loại quả khác nhau từ nhiều loài thực vật. Mỗi loại quả này đều có những đặc điểm riêng biệt về hình dạng, kích thước, màu sắc và cấu trúc, giúp phân biệt chúng dễ dàng hơn. Ví dụ, quả An nam tử là một loại quả nang, có thể chứa từ 1 đến 5 quả đại, cao từ 10 đến 24cm, mặt ngoài của quả này có màu đỏ, còn mặt trong thì có màu lục ánh bạc, vỏ quả rất mỏng và hạt của nó to bằng ngón tay, có hình bầu dục hoặc thuôn dài. Quả Hương Bạch Chỉ là một loại quả bế đôi dẹt, chiều dài khoảng 6mm, có hình bầu dục hoặc hơi tròn. Quả của Bạch đồng nữ là quả hạch đen, có hình cầu. Thực vật thuộc họ cải thường có quả lông phủ bên ngoài, có dạng mỏ dài và chứa từ 4 đến 6 hạt nhỏ màu vàng nâu. Quả của Bàn long sâm cũng có lông mịn bao phủ. Dong riềng đỏ có nhiều quả có nhiều gai mềm, chứa nhiều hạt hình cầu màu đen. Thổ phục linh cũng có quả nhỏ tròn, mọng, đường kính trung bình khoảng 10mm, chứa khoảng 3-4 hạt hình trứng. Quả cây biển súc mọc ở cạnh, chứa một hạt đầu đen. Quả cây bóng nước có dạng hình bầu dục, đầu nhọn, có chia khía, lớp da ngoài có lông nhám. Quả của cà dại hoa tím mọng, hình cầu, màu đỏ hay vàng da cam khi chín, nhẵn, hạt hình đĩa màu vàng. Quả của cà dại hoa trắng là quả mọng, hình cầu nhẵn, màu vàng, hạt hình dĩa, có mang. Quả của cà độc dược có hình cầu, màu xanh và có gai. Quả của Cát sâm dẹt trong, chứa từ 1-10 hạt hình thấu kính, rốn rộng và ngắn. Quả của cây Câu đằng là quả nang dài và dẹt, có chứa nhiều hạt có cánh. Quả cây Bần là phần dùng để điều trị các vết thương, có hình cầu, dẹt, có mũi thuôn nhọn ở đầu. Quả cây Báng có thể sử dụng để làm thuốc. Quả cây Bồng bồng hình giáo, chứa nhiều hạt có mào lông. Quả cây Chàm hình dải, thẳng hay cong, dài 3 – 4 cm, rộng 0,3 cm. Quả của cây chây có vị chua, tính bình. Quả cây Đước có hình trứng, màu nâu lục nhạt, mỗi quả chứa 1 hạt. Quả Me đất là bộ phận của cây Me đất. Quả của cây một lá hình thoi, có múi trông giống như quả khế con, dài 2-3cm, thường cho quả vào các tháng 4, tháng 5 và tháng 6. Ngoài ra, quả của cây mướp khía lớn hình chùy dài khoảng 30-40cm, đường kính từ 7-10cm, có 10 cạnh nhọn dọc theo quả. Quả nang, hình cầu, màu trắng; hạt màu đỏ nâu, bóng. Quả nhẵn, bao bọc bởi mày hoa. Quả Thuốc Mọi có màu đỏ sau khi chín chuyển sang màu đen, hình cầu, đường kính 2 – 3 mm, bên trong chứa 2 – 3 hạt nhỏ và dẹt.\n\nMột số quả mọng có hình gần tròn, đường kính khoảng 3 – 5cm, thường chỉ chứa một hạt. Quả của cây hồi có mùi thơm dễ chịu và vị ngọt. Tất cả các loại quả trên đều đóng vai trò quan trọng trong việc duy trì sự sống của cây trồng và cung cấp nguồn thức ăn quý giá cho nhiều loài động vật khác nhau. Ngoài ra, còn có một số quả nhỏ, dài 3mm, rộng 1,5mm.\n\nQuả của dây bông xanh có hình nang nhẵn, có mũi nhọn dài. Quả dây đau xương hình bầu dục hoặc hình tròn, khi chín có màu đỏ, chứa chất nhày bao quanh hạt hình bán cầu. Quả có hình bầu dục, bóng, mặt ngoài phủ một lớp như sáp, khi chín có màu vàng đỏ, có cuống ngắn. Quả dài 5,5cm, rộng ở nửa dưới, hạt dẹt, lông mào dài 3cm. Một số quả mọng hình trứng hoặc hình tròn, dài 20-25 cm, khi chín màu vàng. Ngoài ra, quả hình cầu, khi non có màu trắng, chín có màu đen, đường kính 5 – 9mm, không ăn được. Đặc biệt, quả Giảo cổ lam hình cầu, khi non có màu trắng, chín có màu đen, đường kính 5 – 9mm, chứa 2 – 3 hạt, không mở. Quả của cây Hạ khô thảo nhỏ và cứng. Quả hình thoi, màu xám nhiều lông, dài 7-11cm, rộng 8mm. Hạt dẹt, phồng ở lưng, dài 5-7mm, rộng 2mm, có chùm lông mịn dài 2cm. Quả nang đường kính 3-5 cm, quả non màu xanh lá, chín có màu nâu đen, hình sao 4-7 thùy. Quả đu đủ to tròn, dài, khi chín mềm, hạt màu nâu hoặc đen tùy từng loại giống, có nhiều hạt. Quả quỳnh có thể dùng để ăn, hình bầu dục, dài khoảng 4 cm. Quả hoa sói là dạng quả mọng, kích thước nhỏ, đường kính từ 3-4mm, thường mọc thành chùm ở đầu cành. Quả khi chín có màu đỏ gạch đẹp mắt. Quả hình cầu, đường kính 4 – 5cm, vỏ ngoài cứng, dày 4mm, trong chứa nhiều hạt hình khuy áo, đường kính 22mm hay hơn, dày 18mm, có lông mượt vàng ánh bạc. Quả hồi đầu thảo dạng nang, đỉnh quả mở không đều, bên trong chứa hạt nhỏ có vỏ ngoài màu nâu, hình thoi. Quả của Huyền sâm là quả nang, hình trứng, có nhiều hạt nhỏ màu đen. Quả của kê huyết đằng hình trứng dài 8 – 12mm, khi chín có màu lam đen. Quả ké đầu ngựa có gai móc, giúp cây phát tán. Quả bế đôi, dạng hình trứng, kích thước rộng 7mm, dài 12 mm, có hai sừng nhọn ở đầu quả, còn gai móc phủ xung quanh. Quả đóng vai trò quan trọng không chỉ đối với cây trồng mà còn là nguồn thức ăn chính của nhiều loài động vật, bao gồm cả loài gấu. Quả mùi tàu gần hình cầu, hơi dẹt, đường kính 2mm, chứa nhiều hạt bên trong. Quả của cây Mướp gai hình trứng vuông, màu nâu, có gai ngắn rậm ở đỉnh, chứa hạt dẹp. Quả Nam sâm hình cầu, đường kính 3 – 4mm, khi chín màu tím đen, chứa 6 – 8 hạt. Quả Náng hoa trắng chứa Criasbetaine, lycorine-1,2-O-D-diglucoside, ungeremine. Quả của Ngấy hương có dạng kép, hình trứng hoặc hình cầu, có đài tồn tại. Gồm nhiều quả hạch con bên trong, khi chín màu đỏ hay đen nhạt, ăn được.\n\nQuả ngọc lan tây là chùm quả, mỗi chùm chứa 10-12 hạt cứng, dẹt, hình trứng màu nâu nhạt, đường kính 6mm.\n\nQuả nhân sâm là quả mọng hơi dẹt, to bằng hạt đậu xanh, màu đỏ khi chín và chứa 2 hạt. Quả mỏng như giấy, dài 2 – 3mm, hạt có vảy ở trên mặt.\n\nQuả của Rau mương hình trụ, nhẵn, hơi phình ra ở đỉnh, chứa nhiều hạt, các hạt này ẩn sâu và chỉ xếp 1 dãy trong ¾ dưới, rời nhau và xếp nhiều dãy ở phần trên, mỗi quả dài 2-3cm.\n\nQuả bế hình trụ, có mào lông ở đỉnh, ra quả khoảng từ tháng 10 đến tháng 3.\n\nQuả có hình cầu, màu tím, đường kính 1,5 – 2cm, mặt ngoài có gai ngắn, chia thành 3 ô.\n\nQuả của cây sa nhân hình cầu, màu tím, đường kính 1,5-2cm.\n\nNgoài những loại quả đã mô tả, quả còn có hình dạng bầu dục, dài khoảng 5mm, ống tinh dầu nằm ở mặt tiếp giáp.\n\nQuả sâm vũ diệp mọng, khi chín màu đỏ.\n\nQuả Sổ Bà mang đài tồn tại, phát triển thành bản dày, mọng nước, đường kính 10cm hay hơn, vị chua, ăn được.\n\nQuả Sử quân tử chín vào tháng 8.\n\nQuả sương sâm trơn hình tròn nhỏ, kích thước 10-12mm, chín vào tháng 7 và chuyển màu tím.\n\nQuả ngũ gia bì gai có hình cầu dẹt, đường kính khoảng 2,5mm, chuyển sang màu đen khi chín và có 2 hạt.\n\nQuả Phèn đen hình cầu khi chín quả có màu đen, bên trong hạt có màu nâu nhạt. Mùa ra hoa quả thường vào tháng 8 – 10.\n\nQuả của Thầu dầu là loại quả nang có màu tím nhạt hoặc lục, có gai mềm xung quanh.\n\nQuả của Khúc khắc mọng, hình cầu, gần 3 cạnh, có 3 hạt, khi chín có màu đỏ hay tím đen.\n\nQuả tam thất mọng, hình cầu dẹt, khi chín có màu đỏ, hạt màu trắng.\n\nQuả Tang ký sinh có hình bầu dục, có vết tích của đài tồn tại, mùa hoa quả vào tháng 1- tháng 3.\n\nQuả thạch xương bồ mọng, màu đỏ nhạt, bên trong chứa hạt được bao phủ bởi chất nhầy.\n\nNgoài ra, quả còn được sử dụng trong điều trị các chứng bệnh. Một số quả có đường kính 1,5 – 1,8mm, bao hoa mang lông, quả mang 9 đường gân hoặc 4 cạnh, đỉnh quả có 2 nhánh như 2 răng nhọn, màu trắng, sáng, màu vàng tối hoặc màu sáng nâu, hình trứng.\n\nQuả cây xá xị có tác dụng giải biểu, thanh nhiệt, giảm ho.\n\nMột số quả dẹt có hình trứng ngược, dày, dai, cứng, dài từ 7-10cm, rộng từ 3,5-4cm, trong đó có 3-4 hạt màu nâu.\n\nQuả của cây chúc hình cầu lớn hoặc hình trứng, nhiều màu, ban đầu màu xanh lục, sau chuyển màu xanh vàng khi chín.\n\nQuả của cây tỏi độc là một nang to 3 ngăn, chứa nhiều hạt màu nâu nhạt.\n\nQuả có kích thước khá nhỏ, hình cầu, vỏ có nhiều túi tinh dầu, màu xanh khi còn non và chuyển dần thành vàng khi chín, vị chua dịu đặc trưng.\n\nQuả hình trứng ngược, phủ lông mềm, màu vàng xám, khi chín nứt thành 2 mảng, chứa 1-2 hạt.\n\nQuả của Tử uyển khô, hơi dẹt có lông trắng.\n\nQuả tây là quả thịt, hơi hình cầu, hơi có lông, chín có màu vàng, dài 3 – 4cm, có 4 hạch đơn, mỗi hạch mang 1 – 2 hạt không phôi nhũ.\nNổi Nóng: Nổi nóng là triệu chứng của suy nhược thần kinh.\nBảo Quản: Bảo Quản là quy trình lưu trữ các loại thuốc, dược liệu, và thực phẩm một cách đúng đắn nhằm đảm bảo chất lượng và tính hiệu quả của chúng. Quy trình này đòi hỏi việc bảo quản trong bao bì kín, tránh ẩm, ánh sáng, và nhiệt độ dưới 30°C. Mỗi loại thuốc và dược liệu có yêu cầu bảo quản cụ thể: thuốc Domperidone cần được bảo quản đúng cách để duy trì tính hiệu quả; thuốc Acyclovir 5% Agimexpharm cần được bảo quản ở nhiệt độ không quá 30°C, tránh ánh sáng và phải được đặt xa tầm tay trẻ em; thuốc Amaryl cũng cần được bảo quản ở nhiệt độ không quá 30°C; thuốc Arthrorein Pharmanel cần được lưu trữ trong bao bì kín, ở nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp; dược liệu Bạch Hạc cần được cất trữ ở nơi thoáng mát, với nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời; thuốc Adrenoxyl 10 mg cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng và nhiệt độ dưới 30ºC; Beatil cần được bảo quản ở nhiệt độ dưới 30°C, trong bao bì gốc để tránh ẩm và ánh sáng. \n\nĐiều kiện chung cho việc bảo quản thuốc và dược liệu là cần phải tránh ẩm, ánh sáng trực tiếp và nhiệt độ cao hơn 30°C để đảm bảo rằng các thành phần hoạt động chính của chúng không bị phân hủy hoặc biến đổi. Dược liệu Hoa Cút Lợn tươi nên dùng ngay để giữ dược tính, tránh ẩm ướt. Nếu bảo quản trong tủ lạnh, phải để ráo nước, cho vào túi ni lông đục vài lỗ nhỏ, chỉ giữ được 2 – 3 ngày. Bảo quản lá dứa sau khi sơ chế, rửa sạch, để ráo nước, lưu trữ ở nơi mát mẻ, thoáng mát, tránh ánh nắng mặt trời trực tiếp và nơi có nhiều côn trùng, ruồi bọ. Bảo quản dược liệu ở nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời, nếu quả trải qua sơ chế cần để nơi khô ráo, thông thoáng. Bảo quản dược liệu Trường sinh thảo sau khi sơ chế bằng cách cho vào túi kín, bảo quản ở những nơi khô mát, đề phòng mối mọt, ẩm mốc. Cách bảo quản thuốc Cenditan là bảo quản nơi khô ráo, thoáng mát, nhiệt độ dưới 30°C và tránh ánh sáng trực tiếp từ mặt trời, để xa tầm tay của trẻ em. Bảo quản thuốc đúng cách, tránh ẩm ướt và ánh sáng trực tiếp, giữ thuốc xa tầm với của trẻ em và thú cưng, bảo quản ở nhiệt độ không quá 30°C. Bảo quản những phần dược liệu đã qua khâu chế biến trong bọc kín, cất trữ nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.\n\nThuốc Dentanalgi cần được bảo quản ở nơi khô mát, tránh tiếp xúc ánh sáng trực tiếp và nhiệt độ dưới 30°C. Thuốc Cloramphenicol cần được bảo quản tránh xa tầm tay của trẻ em và thú cưng, ở nhiệt độ 15 – 25°C. Bảo quản dược liệu sau khi chế biến trong bọc kín, cất trữ nơi thoáng mát, nhiệt độ phòng, tránh tiếp xúc trực tiếp với ánh nắng mặt trời. Bảo quản dược liệu ở nơi khô ráo và thoáng mát, tránh mối mọt. Bảo quản dược liệu ở nơi thoáng mát, tránh để dược liệu ở nơi ẩm ướt để tránh tình trạng nổi mốc meo.&lt;SEP&gt;Bảo quản sài hồ cần được cất giữ ở nơi kín đáo, khô ráo, thoáng mát, sạch sẽ.&lt;SEP&gt;Bảo quản Tế tân tránh phơi trực tiếp dưới nắng.&lt;SEP&gt;Bảo quản là cách lưu trữ Thạch hộc để đảm bảo chất lượng.&lt;SEP&gt;Bảo quản Depakin ở nơi khô ráo, nhiệt độ không quá 25°C.&lt;SEP&gt;Bảo quản chiết xuất hương thảo trong lọ tối màu, kín, đặt nơi khô thoáng, tránh ánh sáng mặt trời hay bụ.\nTỉnh Giác Hay: Tỉnh giấc hay là triệu chứng được điều trị bằng thuốc bổ thần kinh H5000.\nNhung: Nhung là dược liệu được thu hoạch từ hươu, qua quá trình xử lý như cưa, rửa, sấy khô.\nMôi Trường Nhiệt Độ Cao: Môi trường nhiệt độ cao có thể gây kích ứng da và tăng nguy cơ viêm nang lông.\nBảo Quản Sản Phẩm: Bảo quản sản phẩm đúng cách bao gồm giữ nơi khô ráo, thoáng mát, tránh ánh sáng trực tiếp và không dùng sản phẩm đã quá hạn sử dụng.&lt;SEP&gt;Bảo quản sản phẩm là quá trình cần thiết để duy trì hiệu quả của Cồn Boric.\nStress Nhiệt: Stress nhiệt là một rối loạn do nhiệt độ cao.\nDầu Cao Sao Vàng: Dầu Cao Sao Vàng từng được coi là “thần dược” vì tính hiệu quả trong điều trị cảm cúm, đau bụng, đau đầu.&lt;SEP&gt;Dầu Cao Sao Vàng là sản phẩm dùng ngoài hoặc có thể dùng để xông, được làm từ thảo dược thiên nhiên.\nNắng Gắt: Loài quỳnh tránh nắng gắt, quá nóng.\nTế Tân: Tế Tân là một thảo dược quan trọng trong y học cổ truyền, được biết đến với nhiều công dụng đa dạng. Tế Tân là một loại cây cỏ nhỏ, có nguồn gốc từ Trung Quốc và phân bố rộng rãi tại các tỉnh như Triết Giang, Hồ Bắc, Tứ Xuyên, Cát Lâm, Hắc Long Giang, An Huy, Thiểm Tây, Liêu Ninh, Giang Tây, và Cam Túc. Thảo dược này có mùi vị cay nồng, tính ấm và được ứng dụng trong nhiều bài thuốc khác nhau.\n\nTế Tân đóng vai trò quan trọng trong An Thảo Nam Dược, một loại thuốc quý được sử dụng để điều trị nhiều chứng bệnh khác nhau. Thảo dược này cũng là thành phần chính trong Didicera, một sản phẩm khác được sử dụng trong y học cổ truyền. Tế Tân được sử dụng như một thành phần trong nhiều bài thuốc, bao gồm cả bài thuốc kinh nghiệm, giúp điều trị hiệu quả các triệu chứng như ho, sốt, cảm mạo, và đau thần kinh tọa.\n\nNgoài ra, Tế Tân còn được sử dụng trong bài thuốc Tiểu Thanh Long Thang và bài thuốc "Độc Hoạt Tang Ký Sinh" khi kết hợp với tang ký sinh. Thảo dược này còn được sử dụng trong bài thuốc chữa cảm nắng mùa hè. Tế Tân có tác dụng chữa trúng phong hàn, đau nhức đầu, phong thấp, buồn nôn, hen suyễn, đau răng, nghẹt mũi, bí mồ hôi, và ứ huyết. Khi sử dụng bên ngoài, Tế Tân còn giúp giảm tình trạng hôi miệng.\n\nThảo dược này cũng được biết đến với khả năng điều trị các vấn đề về xương khớp, đặc biệt là trong bài thuốc trị khớp sưng đỏ, đau và khó co duỗi. Tế Tân còn được sử dụng để nấu nước thuốc trong y học cổ truyền, với mục đích điều trị nhiều bệnh lý khác nhau thông qua các bài thuốc khác nhau. Tế Tân là một vị thuốc trong kho tàng thuốc quý của Đông y, được sử dụng để điều trị đau răng kèm sưng đỏ.&lt;SEP&gt;Tế tân là thành phần trong bài thuốc chữa ho hen có nhiều đờm.&lt;SEP&gt;Tế tân là vị thuốc dùng phối hợp với Tử uyển để chữa trẻ em ho, có tiếng khò khè trong cổ, thở khó.&lt;SEP&gt;Tế tân là một vị thuốc trong y học cổ truyền, thường được sử dụng để chữa ho và cảm lạnh.\nĐau Mỏi Cổ: Đau mỏi cổ là triệu chứng được hỗ trợ điều trị bởi Thuốc bổ thần kinh H5000.\nChế Phẩm: Chế phẩm là sản phẩm dược phẩm, có thể bảo quản được tới 3 năm ở nhiệt độ ≤ 37 °C và tới 5 năm ở 2 – 8 °C.&lt;SEP&gt;Chế phẩm là thuật ngữ chung chỉ sản phẩm thuốc.\nCăng Thẳng Nhiệt: Nhịp tim nhanh là triệu chứng của căng thẳng nhiệt.\nÁnh Sáng: Ánh Sáng là một yếu tố đa chức năng, đóng vai trò quan trọng trong nhiều khía cạnh cuộc sống, từ y tế đến nông nghiệp và cả trong lĩnh vực không liên quan đến y tế hay nông nghiệp. Trong lĩnh vực y tế, ánh sáng là một yếu tố cần tránh khi bảo quản nhiều loại thuốc khác nhau, bao gồm Acyclovir Stella Cream, Adrenalin, Albiomin 20%, Alvesin, Amiparen 5 Otsuka, Amoxicilin 500 mg, Ampicillin Mekophar, Batigan, Bisilkon, Bluemint, Clesspra DX, Comozol, Betadine, Aceclofenac STADA, và Ameflu DAYTIME. Tiếp xúc trực tiếp với ánh sáng có thể gây ra những ảnh hưởng xấu đến chất lượng của các loại thuốc này, dẫn đến việc phân hủy hoặc thay đổi cấu trúc của các thành phần thuốc, làm giảm hiệu quả điều trị và tăng nguy cơ sử dụng thuốc không đúng cách. Việc bảo quản các loại thuốc này cần được thực hiện trong điều kiện tránh ánh sáng để duy trì chất lượng và hiệu quả của chúng.\n\nTrong nông nghiệp, ánh sáng thích hợp hỗ trợ sự phát triển của cây trồng, đặc biệt là đối với cây trồng như Bán chi liên, cà gai leo, và cúc mốc. Nó cũng ảnh hưởng đến tốc độ sinh trưởng và chiều cao của Cỏ mật, thể hiện rõ ràng vai trò của nó trong việc định hình môi trường tự nhiên. Ngoài ra, ánh sáng mặt trời ảnh hưởng đến cánh hoa Khiên ngưu và là điều kiện sinh trưởng của lạc tiên. Ánh sáng cũng đóng vai trò quan trọng trong việc phát triển cây húng quế và cây sương sâm, sinh trưởng tốt ở môi trường ánh sáng từ 70-80%.\n\nÁnh sáng từ phía sau người xem có thể giúp giảm mỏi mắt khi đọc sách, tạo ra một môi trường thuận lợi hơn cho việc đọc và học tập. Đồng thời, ánh sáng còn được sử dụng như một phương pháp an toàn để loại bỏ lông thừa. Ánh sáng buổi sáng có thể giúp điều chỉnh đồng hồ sinh học. Tuy nhiên, tiếp xúc quá nhiều với ánh sáng có thể dẫn đến mất ngủ. Ngoài ra, ánh sáng cũng khiến Giun đất sợ hãi và hạn chế di chuyển lên mặt đất.\n\nMực cũng tập trung đông khi có ánh sáng, nhưng Bioflora cần tránh tiếp xúc với ánh sáng.&lt;SEP&gt;Ánh sáng trực tiếp có thể ảnh hưởng đến thuốc Brain và cần được tránh.&lt;SEP&gt;Ánh sáng là yếu tố cần tránh khi bảo quản thuốc Broncho-Vaxom.&lt;SEP&gt;Ánh sáng là yếu tố cần tránh khi bảo quản thuốc Cialis.&lt;SEP&gt;Ánh sáng là yếu tố thu hút côn trùng.\nNổi Nóng - Suy Nhược Thần Kinh: Nổi nóng là triệu chứng của suy nhược thần kinh.\nBảo Quản Dược Liệu - Quả: Quả cần được bảo quản theo quy tắc để tránh hỏng hóc.\nMôi Trường Nhiệt Độ Cao - Viêm Nang Lông: Môi trường nhiệt độ cao có thể gây kích ứng da và tăng nguy cơ viêm nang lông.\nBảo Quản - Nhung: Bảo quản nhung ở nơi khô ráo và thoáng mát, tránh mối mọt.\nCảm Nắng Nóng - Lô Căn: Lô căn được chỉ định để chữa trị cảm nắng nóng.&lt;SEP&gt;Lô căn được sử dụng để điều trị cảm nắng nóng.\nBảo Quản Sản Phẩm - Dầu Cao Sao Vàng: Dầu Cao Sao Vàng cần được bảo quản đúng cách theo hướng dẫn.\nCăng Thẳng Nhiệt - Nhịp Tim Nhanh: Nhịp tim nhanh là triệu chứng của căng thẳng nhiệt.\nBảo Quản - Tế Tân: Bảo quản Tế tân tránh phơi trực tiếp dưới nắng.\nCao Bình Vôi - Thuốc Bổ Thần Kinh H5000: Cao bình vôi là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Cao bình vôi là một trong những thành phần của Thuốc bổ thần kinh H5000.\nChế Phẩm - Ánh Sáng: Tránh ánh sáng khi bảo quản chế phẩm.\nChiết Xuất Huyền Hồ Sách Đông Khô - Thuốc Bổ Thần Kinh H5000: Chiết xuất huyền hồ sách đông khô là thành phần hoạt chất trong thuốc bổ thần kinh H5000.&lt;SEP&gt;Chiết xuất huyền hồ sách đông khô là một trong những thành phần của Thuốc bổ thần kinh H5000.\nChất Bay Tinh Đầu - Đại Hồi: Đại hồi cần tránh chất bay tinh dầu trong bảo quản.\nThuốc Bổ Thần Kinh H5000 - Tỉnh Giác Hay: Thuốc bổ thần kinh H5000 được dùng cho người hay tỉnh giấc.\nBảo Quản Sản Phẩm - Cồn Boric: Cồn Boric cần được bảo quản đúng cách để duy trì hiệu quả.\nThuốc Bổ Thần Kinh H5000 - Đau Mỏi Cổ: Thuốc bổ thần kinh H5000 hỗ trợ giảm đau mỏi cổ.\nBảo Quản - Dầu Cao Sao Vàng: Bảo quản là quy trình bảo quản sản phẩm Dầu Cao Sao Vàng đúng cách.\nStress Nhiệt - Sốc Nhiệt: Stress nhiệt là một rối loạn tiền thân của sốc nhiệt.\nBromelain - Bảo Quản Thuốc: Bromelain cần được bảo quản đúng cách để duy trì chất lượng.\nNắng Gắt - Quỳnh: Loài quỳnh tránh nắng gắt, quá nóng.\nBảo Quản - Lộc Nhung: Bảo quản lộc nhung ở nơi khô ráo và thoáng mát, tránh mối mọt.\nCăng Thẳng Nhiệt - Hạ Huyết Áp Thế Hoặc Gần Ngất: Hạ huyết áp thế hoặc gần ngất là triệu chứng của căng thẳng nhiệt.\nBù Dịch, Điện Giải Theo Kết Quả Xét Nghiệm - Căng Thẳng Nhiệt: Bù dịch và điện giải theo kết quả xét nghiệm là phương pháp điều trị căng thẳng nhiệt.']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Khi bảo quản sản phẩm Bổ thần kinh H5000, cần tránh những điều kiện sau:
+1. **Ánh sáng**: Sản phẩm cần được bảo quản tránh xa ánh sáng mặt trời để duy trì chất lượng và hiệu quả.
+2. **Nhiệt độ cao**: Sản phẩm cần được bảo quản ở nơi khô ráo, thoáng mát và nhiệt độ không quá 30°C. Tránh để sản phẩm ở nơi có nhiệt độ cao.
+3. **Ẩm ướt**: Tránh để sản phẩm tiếp xúc với ẩm ướt. Sản phẩm cần được bảo quản ở nơi khô ráo.
+4. **Tiếp xúc với trẻ em**: Sản phẩm cần được bảo quản xa tầm tay của trẻ em để đảm bảo an toàn.
+### Cách bảo quản:
+- Bảo quản sản phẩm trong bao bì kín.
+- Đặt sản phẩm ở nơi khô ráo, thoáng mát.
+- Tránh để sản phẩm tiếp xúc trực tiếp với ánh sáng.
+- Đảm bảo nhiệt độ bảo quản dưới 30°C.
+### Lưu ý:
+- Sản phẩm có hạn dùng là 36 tháng kể từ ngày sản xuất.
+- Không sử dụng sản phẩm khi đã quá hạn sử dụng.
+### Tham chiếu:
+- [1] "thuoc-bo-than-kinh-h5000-co-tot-khong-gia-thanh-phan-va-cach-su-dung-hieu-qua.txt"
+- [8] "suy-nhuoc-than-kinh-nguy-co-dan-den-tram-cam.txt"</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sản phẩm cần tránh bảo quản ở nơi ẩm ướt, có ánh sáng mặt trời, nhiệt độ cao hơn 30°C.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9141463429976372</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7285365857244093</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ở đâu là nơi thích hợp để Biosubtyl tránh xa tầm tay trẻ em và vật nuôi?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>['Con Trẻ: Lối sống an toàn giúp bảo vệ con trẻ.\nBảo Quản Thuốc: Bảo Quản Thuốc là quá trình lưu trữ thuốc đúng cách nhằm duy trì chất lượng và hiệu quả của chúng. Mỗi loại thuốc có yêu cầu bảo quản riêng biệt, từ việc kiểm soát độ ẩm, nhiệt độ và ánh sáng để tránh ảnh hưởng đến chất lượng và tính năng của thuốc. Ví dụ, thuốc như At Domperidone, ATP, Acritel, Acyclovir, Alphachymotrypsin bk 4200 Mebiphar, AlphaDHG, Alzental, Ambroxol Boston, Amepox Soft Capsule, Ampicillin Brawn, Aspirin MKP OnClickListener, Avastin, Ba đậu và disulfiram đều có yêu cầu bảo quản cụ thể. Thuốc Bentarcin cần được bảo quản ở nơi thoáng mát, tránh ánh nắng trực tiếp. Thuốc Debby cần được bảo quản tránh tiếp xúc với ánh sáng, nhiệt độ dưới 30°C và ở nơi khô ráo, thoáng mát. Thuốc Atussin cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc môi trường ẩm ướt, với nhiệt độ tốt nhất là dưới 30ºC. Thuốc Diorophyl cần được bảo quản trong bao bì gốc, nơi khô ráo, tránh ánh sáng và nhiệt độ không quá 30°C. Thuốc Atocib cần được bảo quản theo hướng dẫn trên tờ hướng dẫn sử dụng thuốc, thông thường thuốc được bảo quản ở nhiệt độ phòng, tránh ẩm và ánh nắng trực tiếp.\n\nThuốc methylprednisolone cần được bảo quản theo hướng dẫn cụ thể về nhiệt độ và thời gian sử dụng. Thuốc Acarbose cần được bảo quản ở nơi khô ráo, thoáng mát, tránh nơi ẩm ướt, nhiệt độ dưới 25°C và không sử dụng thuốc sau ngày hết hạn. Thuốc Acemuc cần chú ý đến nhiệt độ, tránh ánh sáng trực tiếp và không để thuốc tiếp xúc với nước. Thuốc Amiodarone cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30°C, tránh ánh sáng trực tiếp. Thuốc axit axetic cần được bảo quản ở nhiệt độ phòng, dưới 30oC, tránh ánh sáng trực tiếp và hơi ẩm, nhiệt độ cao. Thuốc Baclofen cũng cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30oC, tránh ánh sáng trực tiếp. Thuốc Bisacodyl yêu cầu đựng thuốc trong bao bì kín, tránh nóng, ánh sáng và ẩm, bảo quản ở nhiệt độ dưới 25 °C, tránh xa tầm tay của trẻ em, đọc kỹ hướng dẫn trước khi dùng, và không dùng thuốc có dấu hiệu ẩm mốc, thay đổi màu sắc. Thuốc Bismuth cần được bảo quản ở nhiệt độ dưới 30oC, trong bao bì kín. Thuốc Bolutin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ Celsius, tránh ánh sáng trực tiếp. Thuốc Cefpodoxim cần được bảo quản trong bao bì kín, ở nhiệt độ dưới 25 độ Celsius và tránh ánh sáng. Thuốc Ceftriaxone cần được bảo quản ở nhiệt độ dưới 25ºC, nơi khô ráo và thông thoáng. Thuốc CellCept cần được bảo quản tránh xa tầm nhìn và tầm với của trẻ em, không sử dụng sau ngày hết hạn, không lưu trữ trên 30°C, và giữ trong thùng carton để tránh ánh sáng. Thuốc Cerebrolysin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 25°C, tránh ánh sáng trực tiếp. Thuốc Ceritine cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ C. Bảo quản thuốc Diane-35 cần được thực hiện dưới 30 độ Celsius, nơi khô ráo, tránh ánh sáng. Thuốc Benzalkonium Chloride cũng cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt, nhiệt độ bảo quản tốt nhất là dưới 30°C.\n\nQuá trình bảo quản thuốc còn bao gồm việc lưu trữ Irbesartan đúng cách để đảm bảo an toàn và hiệu quả. Bảo quản thuốc đúng cách là rất quan trọng để duy trì chất lượng và hiệu quả của chúng, đảm bảo an toàn khi sử dụng và ngăn chặn bất kỳ sự cố nào có thể xảy ra do bảo quản không đúng cách.\nTầm Với Trẻ Em: Thuốc cần được bảo quản tránh xa tầm với của trẻ em.\nDidicera: Didicera là thuốc thảo dược không kê toa, thuộc công ty Cổ phần Công nghệ cao Traphaco, điều chế dưới dạng viên hoàn và viên nang.&lt;SEP&gt;Viên nang Didicera chứa thành phần độc hoạt, tế tân, tang ký sinh, quế chi, tần giao, phòng phong, cam thảo, bạch linh và đảng sâm.&lt;SEP&gt;Didicera có công năng bổ khí huyết, trừ phong thấp, bổ can thận.&lt;SEP&gt;Didicera là thuốc được điều chế dưới dạng viên nang hoặc viên hoàn, dùng đường uống.&lt;SEP&gt;Didicera là thuốc được bán với giá trung bình khoảng 40.000 VNĐ/hộp 10 gói x viên hoàn 5g.&lt;SEP&gt;Didicera là thuốc cần tham khảo ý kiến dược sĩ hoặc bác sĩ về cách dùng và liều dùng trước khi sử dụng.\nGiữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nGiữ Thuốc Xa Tầm Tay Trẻ Nhỏ: Giữ thuốc xa tầm tay trẻ nhỏ nhằm tránh bé sử dụng sai cách, sai liều gây nguy hiểm.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nPhụ Nữ Mang Thai Hoặc Cho Con Bú: Nhóm đối tượng có thể sử dụng Biosubtyl.\nSức Khỏe: Sức khỏe là trạng thái tổng thể của cơ thể, bao gồm cả thể chất, tinh thần và xã hội. Trạng thái này được đánh giá qua các chỉ số như BMI và vòng eo, cũng như thông qua chế độ ăn uống và tập luyện. Sức khỏe cũng liên quan đến tình trạng huyết áp và có thể bị ảnh hưởng bởi tình trạng mất trí nhớ thoáng qua. \n\nĐể nâng cao sức khỏe, việc sử dụng các vị thuốc như Bồ đề, bạc hà, cây hoa cút lợn, cây Đước, Trường sinh thảo, và đông trùng hạ thảo ngâm mật ong được xem là phương pháp hiệu quả. Những vị thuốc này giúp tránh các tương tác có hại và cải thiện tình trạng tổng thể của cơ thể. Sức khỏe không chỉ là trạng thái tổng thể về thể chất mà còn bao gồm cả tinh thần và xã hội của con người. Nó được đề cập trong bài thuốc cổ truyền và cần được bảo vệ thông qua các thói quen sinh hoạt lành mạnh. Việc sử dụng lá Thường xuân cũng được biết đến với khả năng cải thiện sức khỏe. Ngoài ra, sức khỏe còn được coi là trạng thái tổng thể về thể chất và tinh thần, được ảnh hưởng bởi việc sử dụng Hoàng Nàn và bổ sung DHEA.\n\nSức khỏe cũng là yếu tố ảnh hưởng đến lượng protein cần thiết trong chế độ ăn uống, nhấn mạnh tầm quan trọng của việc duy trì một chế độ ăn uống cân bằng và hợp lý để nâng cao và duy trì sức khỏe tổng thể. Tình trạng sức khỏe cần được theo dõi cẩn thận khi sử dụng thuốc Aspegic, một yếu tố được điều trị bởi Aspegic. \n\nNgoài ra, cần lưu ý rằng có một tạp chí y tế tên là "Sức khỏe", nhưng đây không phải là định nghĩa chính cho thuật ngữ sức khỏe trong ngữ cảnh này.&lt;SEP&gt;Sức khỏe là trạng thái tổng thể của cơ thể và tâm trí, có thể được cải thiện thông qua việc sử dụng tinh dầu hoa cam.&lt;SEP&gt;Sức khỏe được cải thiện nhờ tác dụng của tinh dầu quế.&lt;SEP&gt;Sức khỏe được cải thiện nhờ việc ăn tỏi mỗi ngày.&lt;SEP&gt;Sức khỏe được cải thiện thông qua việc sử dụng vị thuốc đúng cách.&lt;SEP&gt;Sức khỏe được tăng cường nhờ bài thuốc ngâm trái quách.\nXa Tầm Tay Của Trẻ Em: Xa tầm tay của trẻ em là khuyến nghị về vị trí lưu trữ thuốc để tránh tiếp cận của trẻ em.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nTrạng Thái Xa Tầm Tay Trẻ Em: Thuốc cần được bảo quản xa tầm tay trẻ em.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Ho Thảo Dược: Thuốc ho thảo dược an toàn cho trẻ được khuyến nghị sử dụng.&lt;SEP&gt;Thuốc ho thảo dược an toàn cho trẻ.\nViệc Sử Dụng Sai Lầm: Việc sử dụng sai là hành vi sử dụng thuốc không đúng cách hoặc không tuân theo hướng dẫn.\nHo - Thuốc Ho Thảo Dược: Thuốc ho thảo dược được dùng để điều trị ho cho trẻ.\nBảo Quản Thuốc - Didicera: Thuốc cần được bảo quản đúng cách để đảm bảo an toàn và hiệu quả.\nKháng Sinh Cho Bé - Nhiễm Trùng: Kháng sinh cho bé được sử dụng để điều trị nhiễm trùng do vi khuẩn.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nAmaryl - Tầm Tay Trẻ Em: Thuốc Amaryl cần được bảo quản ở nơi ngoài tầm tay trẻ em.\nHướng Dẫn - Sức Khỏe: Hướng dẫn của bác sĩ giúp đảm bảo an toàn cho sức khỏe khi sử dụng dược liệu.\nAmbroxol - Tầm Tay Trẻ Em: Thuốc Ambroxol cần được bảo quản tránh xa tầm tay trẻ em.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nAmoxicillin Domesco - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nViệc Sử Dụng Sai Lầm - Ý Kiến Thầy Thuốc: Tham khảo ý kiến thầy thuốc có thể giúp phòng ngừa việc sử dụng thuốc sai cách.\nBaby Septol - Tầm Tay Trẻ Em: Thuốc cần được đặt tránh xa tầm tay trẻ em.\nCon Trẻ - Lối Sống An Toàn: Lối sống an toàn giúp bảo vệ con trẻ.\nBofit F - Tầm Tay Trẻ Em: Bofit F cần được bảo quản tránh tầm tay trẻ em.\nThuốc - Trẻ Em: Trẻ em không được phép sử dụng thuốc này.&lt;SEP&gt;Thuốc cần được giữ tránh xa tầm tay của trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nCavinton - Tầm Tay Trẻ Em: Thuốc Cavinton cần được bảo quản tránh xa tầm tay của trẻ em.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nCarbocistein - Tầm Tay Trẻ Em: Tránh xa tầm tay trẻ em khi bảo quản Carbocistein.\nBảo Quản Thuốc - Thuốc: Bảo quản thuốc là quá trình lưu trữ thuốc.\nIrbesartan - Tầm Tay Trẻ Em: Thuốc Irbesartan cần được giữ tránh xa tầm tay của trẻ em và trẻ nhỏ.\nAxit Axetic - Bảo Quản Thuốc: Thuốc axit axetic cần được bảo quản đúng cách để đảm bảo hiệu quả và an toàn.\nBetadine Vaginal Douche - Tầm Tay Trẻ Em: Betadine Vaginal Douche cần được bảo quản xa tầm tay của trẻ em.\nAsevictoria Mediplantex - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nDidicera - Tầm Tay Trẻ Em: Giữ thuốc Didicera tránh xa tầm tay trẻ em.\nHo Gà - Thuốc Ho Thảo Dược: Thuốc ho thảo dược an toàn cho trẻ được khuyến nghị sử dụng.\nAspirin MKP 81 - Trạng Thái Xa Tầm Tay Trẻ Em: Thuốc Aspirin MKP 81 cần được bảo quản xa tầm tay trẻ em.\nAlpha-Kiisin - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay trẻ em.\nContractubex - Tầm Tay Trẻ Em: Tầm tay trẻ em là vị trí cần tránh khi bảo quản Contractubex.\nAxit Glutamic - Tầm Tay Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nAzithromycin DHG - Giữ Thuốc Xa Tầm Tay Trẻ Nhỏ: Thuốc cần được giữ xa tầm tay trẻ nhỏ nhằm tránh bé sử dụng sai cách, sai liều gây nguy hiểm.\nCarbogast - Tầm Tay Trẻ Em: Thuốc Carbogast cần tránh xa tầm tay trẻ em.\nAcyclovir Stella Cream - Tầm Tay Trẻ Em: Thuốc Acyclovir Stella Cream cần được giữ xa tầm tay trẻ em.\nClarityne - Tầm Tay Trẻ Em: Thuốc Clarityne cần được bảo quản tránh xa tầm tay của trẻ em.\nBioflora - Tầm Tay Trẻ Em: Flora cần được bảo quản xa tầm tay trẻ em.\nCilzec - Tầm Tay Trẻ Em: Giữ thuốc Cilzec xa tầm tay trẻ em.\nBảo Thanh Hoa Linh - Tầm Tay Trẻ Em: Thuốc cần được đặt xa tầm tay trẻ em để đảm bảo an toàn.\nAmpicillin Vidiphar - Tầm Tay Trẻ Em: Thuốc Ampicillin Vidiphar cần được đặt xa tầm tay trẻ em.\nBilgrel - Giữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nColdi B - Tầm Với Trẻ Em: Coldi B cần được bảo quản tránh xa tầm với của trẻ em.\nCenditan - Xa Tầm Tay Của Trẻ Em: Thuốc Cenditan nên được lưu trữ xa tầm tay của trẻ em để đảm bảo an toàn.\nThuốc Bisoloc (Bisoprolol) - Tầm Tay Trẻ Em: Thuốc Bisoloc cần được giữ xa tầm tay trẻ em.\nBiosubtyl - Phụ Nữ Mang Thai Hoặc Cho Con Bú: Biosubtyl có thể được dùng bởi phụ nữ mang thai hoặc cho con bú.']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Men vi sinh Biosubtyl cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc để thuốc ở những nơi ẩm ướt. Đặc biệt, thuốc phải được giữ xa tầm tay của trẻ em và vật nuôi trong nhà để đảm bảo an toàn.
+### Cách bảo quản
+- Để thuốc Biosubtyl tránh xa tầm tay của trẻ em và thú cưng trong nhà.
+- Bảo quản men ở nơi khô ráo thoáng mát. Tránh tiếp xúc trực tiếp với ánh sáng hoặc để thuốc ở những nơi ẩm ướt.
+- Nhiệt độ tốt nhất được khuyến nghị để bảo quản là dưới 30°C.
+### Lưu ý
+- Không để thuốc ở những nơi có thể tiếp cận được bởi trẻ em hoặc vật nuôi.
+- Đảm bảo rằng vị trí bảo quản thuốc an toàn và không dễ dàng tiếp cận.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Để xa men vi sinh Biosubtyl khỏi tầm với của trẻ nhỏ và động vật để đảm bảo an toàn.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4876028682277829</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7330118281430569</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trong trường hợp đau nhiều, liều dùng Cholapan sẽ thay đổi như thế nào?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>["Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nQuá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nQuá Liều Clopidogrel: Quá liều clopidogrel là tình trạng có thể xảy ra khi dùng clopidogrel.\nĐiều Trị: Điều trị là quá trình sử dụng các phương pháp y tế như thuốc và các biện pháp khác để khắc phục hoặc cải thiện tình trạng sức khỏe của bệnh nhân. Điều trị có thể tập trung vào việc giảm đau, kiểm soát triệu chứng, ngăn chặn sự tiến triển của bệnh, và cải thiện chất lượng cuộc sống. Ví dụ, tinh dầu Bạc hà được sử dụng để điều trị, trong khi điều trị bệnh Parkinson nhằm kiểm soát triệu chứng và ngăn chặn sự tiến triển của bệnh. Điều trị đau vùng chậu mãn tính tập trung vào việc giảm đau và cải thiện chất lượng cuộc sống của bệnh nhân. Việc điều trị phụ thuộc vào một loạt các yếu tố và có thể được thực hiện bởi bác sĩ chuyên môn.\n\nĐiều trị cũng được sử dụng để khắc phục nhiều loại bệnh cụ thể. Nó là phương pháp khắc phục bệnh lang ben, xử lý và khắc phục các vấn đề về màng nhĩ và tai, và điều trị bệnh nấm da đầu. Đối với bệnh tay chân miệng, việc điều trị cần dựa trên việc nhận biết sớm và thực hiện các biện pháp phòng ngừa, xử trí ban đầu tại nhà, và khi cần thiết phải nhờ đến sự giúp đỡ của nhân viên y tế. Đối với bệnh phì đại thất trái, điều trị bao gồm việc kiểm soát huyết áp và điều chỉnh lối sống. Cuối cùng, điều trị cũng nhằm cải thiện tình trạng rối loạn trí nhớ và tư duy của người bệnh.\n\nTrong một số trường hợp, điều trị run vô căn có thể không cần thiết nếu triệu chứng nhẹ. Ngoài ra, việc điều trị sốt xuất huyết nhằm giảm triệu chứng và ngăn chặn biến chứng, trong khi điều trị suy gan cần được thực hiện kịp thời tại các cơ sở y tế.&lt;SEP&gt;Điều trị suy tim cấp được thực hiện ngay lập tức sau khi có chẩn đoán.&lt;SEP&gt;Điều trị là quá trình sử dụng thuốc Benzalkonium Chloride để điều trị các triệu chứng.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nSự Đau Đớn: Sự đau đớn là một trong những giác quan soma được xử lý bởi thùy đỉnh.\nQuá Liều Thuốc Ameflu DAYTIME: Quá liều thuốc Ameflu DAYTIME là tình trạng cần xử lý kịp thời.\nThùy Đỉnh: Thùy Đỉnh là một phần của não, nằm gần phần sau trên của hộp sọ, gần với xương đỉnh. Thùy này là một trong những thùy cấu thành nên bộ não của con người, nằm giữa thùy trán và thùy chẩm, phía trên thùy thái dương trên mỗi bán cầu đại não. Thùy Đỉnh chịu trách nhiệm chính cho các cảm giác xúc giác của cơ thể, xử lý thông tin giác quan theo nhiều cách thức, bao gồm cả cảm giác về không gian và định hướng. Thùy Đỉnh cũng là một phần của não có chức năng giải thích về thế giới cảm giác xung quanh cơ thể, và nó chịu trách nhiệm chính cho các cảm giác xúc giác như nhiệt độ và đau. Ngoài ra, khu vực giữa thùy đỉnh và thùy đỉnh có thể gây ra những thiếu hụt đặc biệt về trí nhớ và nhân cách.&lt;SEP&gt;Thùy đỉnh là một trong bốn thùy chính của não, được ngăn cách với thùy trán bằng rãnh trung tâm.\nThuốc Quá Liều: Thuốc quá liều có thể gây triệu chứng bất thường.&lt;SEP&gt;Thuốc quá liều là việc sử dụng thuốc vượt quá liều lượng khuyến cáo.\nGiảm Đau: Giảm Đau là mục đích điều trị và sử dụng phổ biến của nhiều loại thuốc, phương pháp điều trị, và thành phần tự nhiên khác nhau nhằm giúp giảm cảm giác đau. Giảm Đau là một trong những công dụng của nhiều loại tinh dầu như tinh dầu hoa hồng, tinh dầu húng quế, và tinh dầu quýt. Tinh dầu húng quế có khả năng giảm đau và được sử dụng trong các phương pháp điều trị theo y học cổ truyền. Tinh dầu còn được biết đến với khả năng giảm đau nhờ vào các hoạt chất tự nhiên của chúng.\n\nCác loại thuốc như A.t Ibuprofen Syrup, Agietoxib bcm, Etoricoxib, Aphaxan Armephaco, Aspirin Vidipha, dầu Ba đậu, Bạch chỉ, Menthol, Bạch đồng nữ, Men Myroxin, cao chiết lạnh của Bạch tật lê, và Bạch thược đều có tác dụng giảm đau. Đặc biệt, Etoricoxib được sử dụng để điều trị các bệnh lý như thoái hóa khớp, viêm khớp dạng thấp, và viêm cột sống dính khớp. Menthol góp phần vào quá trình giảm đau bằng cách gây ra cảm giác mát và tê tại chỗ, giúp giảm đau dây thần kinh. Ngoài việc sử dụng thuốc, giảm đau còn là tác dụng của một số thực vật và thành phần tự nhiên khác như cà gai leo, cam thảo nam, dầu trung tính Cảo Bản, cây Bần, thành phần bìm bịp, Na rừng, cây Nàng nàng, cây Nổ gai, tinh dầu sả, cây Ráy, vỏ cây Sảng, thân và lá Cánh kiến trắng, tỏi trời, và chìa vôi. Children's Tylenol và chùm ruột cũng có tác dụng giảm đau nhờ chứa nhiều hợp chất chống oxy hóa.\n\nThuốc Cofidec cũng được biết đến với tác dụng giảm đau, đặc biệt là trong việc điều trị viêm xương khớp. Củ dòm và cây Dây gân cũng được biết đến với tác dụng giảm đau. Tần giao cũng giúp giảm cảm giác đau. Giảm Đau cũng là tác dụng của corticosteroid, chiết xuất củ Chóc, và củ nén khi sử dụng trong bài thuốc. Tác dụng giảm đau có tính chất thuộc trung ương, liên quan đến aconitin và hệ thống catecholamin trung ương. Giảm Đau là tác dụng của Đại tướng quân và dền gai trong điều trị bệnh. Các chất chiết xuất từ rễ, lá, hoa đậu biếc đã được báo cáo chứng minh các hoạt động giảm đau. Dầu giun có tác dụng giảm đau. Giảm đau là quá trình sinh học được hỗ trợ bởi một số thuốc chống viêm. Giảm Đau là mục tiêu của điều trị khi không thể xác định được nguyên nhân gây đau.\n\nĐịa cốt bì và Địa liền cũng có tác dụng giảm đau, đặc biệt là đối với các bệnh lý nội tạng. Viên Bạch Địa Can có tác dụng giảm đau. Đơn lá đỏ giúp giảm cảm giác đau. Giảm Đau là mục tiêu đầu tiên của vật lý trị liệu sau chấn thương và vật lý trị liệu nói chung. Giảm Đau cũng là phương pháp điều trị sử dụng Hắc sâm. Giảm Đau là tác dụng của hoa đậu biếc. Giảm Đau là triệu chứng được điều trị bằng hoạt chất từ cây này. Giảm Đau là phương pháp điều trị bằng rễ hoa nhài và rễ nhài. Giảm Đau cũng là phương pháp điều trị bằng hoa quỳnh. Giảm Đau còn được áp dụng trong việc điều trị gù cột sống để giảm triệu chứng đau. Hoàng nàn giúp giảm đau và là công dụng của nó. Húng quế được sử dụng để giảm đau. Giảm Đau là mục tiêu của một số loại thuốc, trong đó chiết xuất Hương thảo có tiềm năng kiểm soát cơn đau. Giảm Đau là một trong những tác dụng của hương phụ. Giảm Đau là tác dụng của Huyết lình khi sử dụng ngoài da. Giảm Đau là tác dụng của cây khế khi sử dụng làm thuốc. Khổ qua rừng giúp giảm đau trong bệnh nhân bị thoái hóa khớp gối. Giảm Đau là tác dụng của các thành phần trong Khương hoạt. Giảm Đau là tác dụng của lá lốt khi dùng ngậm hoặc uống.\n\nNgoài ra, giảm đau cũng là công dụng của trầm hương trong đông y, giúp giảm các triệu chứng đau. Giảm đau cũng là tác dụng của lá cây xá xị, tía tô, tô mộc, và trà tiên.&lt;SEP&gt;Giảm đau là một trong những tác dụng của tinh dầu trầm.\nNghiên Thuốc: Nghiện thuốc là triệu chứng có thể xảy ra khi sử dụng Clonazepam.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nBác Sĩ - Thuốc: Bác sĩ chỉ định và điều chỉnh liều lượng thuốc cho bệnh nhân.&lt;SEP&gt;Bác sĩ hỗ trợ và xử trí các triệu chứng không mong muốn khi sử dụng thuốc.&lt;SEP&gt;Bác sĩ tư vấn về việc sử dụng thuốc.\nAspirin - Quá Liều Aspirin: Aspirin có thể gây quá liều, gây nhiễm kiềm hoặc acid hô hấp.\nTác Dụng Phụ - Điều Trị: Điều trị nhằm khắc phục và xử lý các tác dụng phụ của thuốc.\nThuốc Quá Liều - Triệu Chứng Bất Thường: Triệu chứng bất thường có thể xảy ra khi sử dụng thuốc quá liều.\nSự Đau Đớn - Thùy Đỉnh: Thùy đỉnh xử lý sự đau đớn.\nClopidogrel - Quá Liều Clopidogrel: Clopidogrel có thể gây quá liều, kéo dài thời gian chảy máu.\nGiảm Đau - Tâm: Giảm đau tác động lên cơ quan tâm.\nAerius - Liều Lượng Thuốc: Liều lượng thuốc Aerius được điều chỉnh dựa trên nhiều yếu tố.\nDược Sĩ - Triệu Chứng Bất Thường: Dược sĩ xử trí và hỗ trợ khi xuất hiện triệu chứng bất thường.\nAmeflu DAYTIME - Quá Liều Thuốc Ameflu DAYTIME: Khi xảy ra quá liều thuốc Ameflu DAYTIME, cần xử lý kịp thời.\nThăm Khám - Tác Dụng Phụ: Thăm khám nhằm chẩn đoán và xử lý các tác dụng phụ của thuốc.\nClonazepam - Nghiên Thuốc: Clonazepam có thể gây nghiện thuốc.\nSâu Ban Miêu - Đau Nhức: Sâu ban miêu gây đau nhức.\nAgi-Calci - Ngừng Sử Dụng Thuốc: Ngừng sử dụng thuốc Agi-Calci và hỏi ý kiến bác sĩ nếu có dấu hiệu bất thường xảy ra.\nBiểu Hiện Bệnh Lý - Thuốc Quá Lượng: Thuốc quá lượng có thể dẫn đến biểu hiện bệnh lý.\nCholapan - Ngừng Sử Dụng Thuốc: Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.\nPhản Ứng Quá Mẫn - Thuốc: Phản ứng quá mẫn là tác dụng phụ của thuốc, gây tăng bạch cầu, huyết khối tắc mạch.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nKiểm Soát Stress - Thuốc: Thuốc được chỉ định để kiểm soát stress hoặc các vấn đề cảm xúc khác.\nClorpheniramin Maleat - Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nNgừng Sử Dụng Thuốc - Viêm Gân: Nếu có bất cứ dấu hiệu nào của viêm gân (ví dụ sưng đau, viêm) nên ngưng sử dụng thuốc và tham khảo bác sĩ.\nBilbroxol Syrup - Thuốc Quá Liều: Không nên sử dụng Bilbroxol Syrup quá liều khuyến cáo.\nPhenylephrine HCl - Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nNgừng Sử Dụng Thuốc - Tác Dụng Phụ Nghiêm Trọng: Khi có tác dụng phụ nghiêm trọng, có thể cần phải ngừng sử dụng thuốc.\nKích Ứng Tại Chỗ - Ngừng Sử Dụng Thuốc: Khi có kích ứng tại chỗ, có thể cần phải ngừng sử dụng thuốc.\nLiều Lượng Thuốc - Trọng Lượng Cơ Thể: Trọng lượng cơ thể là yếu tố quyết định liều lượng thuốc Aerius.\nPhentolamin - Quá Liều Phenylephrine HCl: Phentolamin được dùng trong xử lý tăng huyết áp do quá liều phenylephrine HCl.\nEthicone - Thuốc Quá Liều: Ethicone là thành phần của thuốc quá liều và không hấp thu qua đường tiêu hóa."]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Khi gặp tình trạng đau nhiều, liều dùng của Cholapan có thể được điều chỉnh để đáp ứng nhu cầu cụ thể của bệnh nhân. Theo hướng dẫn sử dụng, trong trường hợp đau nhiều, có thể uống liều gấp đôi so với liều dùng thông thường. Liều dùng thông thường cho người lớn là 2 viên/lần, 2 lần/ngày. Vậy, khi đau nhiều, người lớn có thể uống 4 viên/lần, 2 lần/ngày.
+Tuy nhiên, việc tăng liều cần được thực hiện dưới sự giám sát của bác sĩ để đảm bảo an toàn và hiệu quả điều trị. 
+### Lưu ý:
+- Không nên tự ý tăng liều mà không có sự hướng dẫn của bác sĩ.
+- Cần tuân thủ hướng dẫn sử dụng và xem kỹ hạn sử dụng trước khi dùng.
+- Nếu xuất hiện bất kỳ triệu chứng nào bất thường, hãy thông báo cho bác sĩ hoặc nhân viên y tế để được xử trí kịp thời.
+### Tham khảo:
+- [1] cholapan.txt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Có thể uống liều gấp đôi (4 viên/lần, ngày 2 lần).</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7955192894100728</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2301298223525182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tác dụng của thuốc cisapride trên trẻ em như thế nào?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>['Chức Năng Dạ Dày Bình Thường: Chức năng dạ dày bình thường không bị ảnh hưởng bởi Cisaprid.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nTác Dụng Phản: Tác dụng phụ không được liệt kê cụ thể trong đoạn văn nhưng có thể bao gồm các vấn đề liên quan đến đường tiêu hóa.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nTiểu Tiện Nhiều Lần: Tiểu tiện nhiều lần là tác dụng phụ hiếm gặp khi dùng cisaprid.&lt;SEP&gt;Tiểu tiện nhiều lần là triệu chứng của việc quá liều Cisaprid.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Cisaprid: Thuốc cisaprid là thuốc được sử dụng điều trị các triệu chứng liên quan đến đường tiêu hóa.\nTrẻ: Trẻ là đối tượng dễ mắc bệnh cúm do có hệ miễn dịch chưa hoàn thiện.&lt;SEP&gt;Trẻ là đối tượng sử dụng thuốc clotrimazole.\nTiết Nhiều Sữa: Tiết nhiều sữa là tác dụng phụ hiếm gặp khi dùng cisaprid.\nBạch Cầu Cấp Trẻ Em: Bạch cầu cấp trẻ em là bệnh lý ác tính ở trẻ em, đặc trưng bởi tăng sinh các tế bào non trong tủy xương.&lt;SEP&gt;Bạch cầu cấp trẻ em là bệnh lý ác tính phổ biến nhất ở lứa tuổi con nít.\nTắc Cơ Học Đường Tiêu Hóa: Tắc cơ học đường tiêu hóa là triệu chứng không nên dùng thuốc cisaprid.&lt;SEP&gt;Tắc cơ học đường tiêu hóa là tình trạng không nên dùng cisaprid.\nTác Dụng Phụ Thuốc: Tác dụng phụ của thuốc là vấn đề chính trong quá trình điều trị bệnh bạch cầu cấp trẻ em.&lt;SEP&gt;Tác dụng phụ của thuốc.&lt;SEP&gt;Tác dụng phụ của thuốc được đánh giá để loại trừ nguyên nhân gây ra triệu chứng tương tự như run vô căn.&lt;SEP&gt;Tác dụng phụ của thuốc có thể gây bệnh tiêu chảy.\nTác Dụng Phụ Ciprofloxacin: Tác dụng phụ của Ciprofloxacin có thể bao gồm cả triệu chứng nhẹ và nghiêm trọng.\nHậu Quả Khôn Lường: Hậu quả khôn lường có thể xảy ra nếu trẻ em ăn phải thuốc.\nQT Kéo Dài: QT kéo dài là tác dụng phụ hiếm gặp khi dùng cisaprid.\nSuy Gan - Thuốc Cisaprid: Thuốc cisaprid cần giảm liều lượng khi bệnh nhân mắc suy gan.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nCiprofloxacin - Tác Dụng Phụ Ciprofloxacin: Ciprofloxacin có thể gây ra nhiều tác dụng phụ.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nCisaprid - Tắc Cơ Học Đường Tiêu Hóa: Tắc cơ học đường tiêu hóa là tình trạng không nên dùng cisaprid.\nBạch Cầu Cấp Trẻ Em - Tác Dụng Phụ Thuốc: Bệnh bạch cầu cấp trẻ em có tác dụng phụ của thuốc.\nCisaprid - Tiểu Tiện Nhiều Lần: Cisaprid có thể gây tiểu tiện nhiều lần.&lt;SEP&gt;Tiểu tiện nhiều lần là triệu chứng của việc quá liều Cisaprid.\nHậu Quả Khôn Lường - Trẻ Em: Trẻ em ăn phải thuốc có thể dẫn đến hậu quả khôn lường.\nChức Năng Dạ Dày Bình Thường - Cisaprid: Cisaprid không có tác dụng lên chức năng dạ dày bình thường.\nSữa Mẹ - Thuốc: Cần chú ý những thuốc bà mẹ đang sử dụng có tiết qua sữa gây ảnh hưởng tới em bé hay không.\nCisaprid - Tiết Nhiều Sữa: Cisaprid có thể gây tiết nhiều sữa.\nTrẻ Bú Mẹ - Tác Dụng Phụ: Trẻ bú mẹ đang dùng thuốc có thể gặp tác dụng trực tiếp đến cơ thể trẻ.&lt;SEP&gt;Trẻ bú mẹ đang dùng thuốc có thể gặp kết quả nuôi cấy vi khuẩn sẽ sai.&lt;SEP&gt;Trẻ bú mẹ đang dùng thuốc có thể gặp rối loạn hệ vi khuẩn đường ruột.\nCisaprid - QT Kéo Dài: Cisaprid có thể gây QT kéo dài.\nAspirin - Trẻ Nhỏ: Aspirin có thể gây tác dụng phụ ở trẻ nhỏ.\nCisaprid - Thủng Đường Tiêu Hóa: Thủng đường tiêu hóa là tình trạng không nên dùng cisaprid.\nRối Loạn Thách Thức Chống Đối - Thuốc: Thuốc có thể được sử dụng để cải thiện tình trạng bệnh ở trẻ có nhiều bệnh đồng mắc.\nHậu Phác - Rối Loạn Tiêu Hóa Chức Năng: Hậu phác được sử dụng để điều trị rối loạn tiêu hóa chức năng.\nTác Dụng Không Mơ Nguyện - Vị Thuốc: Vị thuốc có thể gây ra các tác dụng không mong muốn.\nThuốc Cisaprid - Thẩm Tách Máu: Thuốc cisaprid không cần tăng liều lượng sau thẩm tách máu.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nThuốc Cisaprid - Trào Ngược Dạ Dày: Thuốc cisaprid được sử dụng để điều trị triệu chứng trào ngược dạ dày.\nChảy Máu Đường Tiêu Hóa - Thuốc Cisaprid: Thuốc cisaprid không nên dùng cho bệnh nhân chảy máu đường tiêu hóa.\nThuốc Cisaprid - Táo Bón Mạn Tính: Thuốc cisaprid được sử dụng để điều trị táo bón mạn tính.\nThuốc Cisaprid - Ợ Nóng Về Đêm: Thuốc cisaprid được sử dụng để điều trị ợ nóng về đêm.\nThuốc Cisaprid - Viêm Thực Quản Do Trào Ngược Dạ Dày: Thuốc cisaprid được sử dụng để điều trị viêm thực quản do trào ngược dạ dày.\nRối Loạn Tiêu Hóa Chức Năng - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị rối loạn tiêu hóa chức năng.\nThuốc Cisaprid - Tắc Cơ Học Đường Tiêu Hóa: Thuốc cisaprid không nên dùng cho bệnh nhân tắc cơ học đường tiêu hóa.\nHội Chứng QT Kéo Dài - Thuốc Cisaprid: Thuốc cisaprid có thể gây ra hội chứng QT kéo dài.\nGiảm Trương Lực Cơ Thắt Hậu Môn - Thuốc Cisaprid: Thuốc cisaprid có thể gây ra giảm trương lực cơ thắt hậu môn.\nDạ Dày Giảm Co Bóp - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị dạ dày giảm co bóp.\nGiả Tắc Ruột Kiểu Thần Kinh - Thuốc Cisaprid: Thuốc cisaprid được sử dụng để điều trị giả tắc ruột kiểu thần kinh.']</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thuốc cisapride là một loại thuốc được sử dụng để tăng cường vận động đường tiêu hóa, bao gồm cả dạ dày và ruột. Tuy nhiên, việc sử dụng thuốc này trên trẻ em cần được thực hiện rất thận trọng vì có nhiều tác dụng phụ và rủi ro tiềm ẩn.
+### Liều dùng và cách sử dụng
+- **Liều dùng:** Đối với trẻ em, liều dùng thường là 0,15–0,3 mg/kg/lần, 3–4 lần/ngày. Liều tối đa là 10 mg/lần.
+- **Cách sử dụng:** Thuốc cần được sử dụng theo hướng dẫn của bác sĩ và cần được theo dõi chặt chẽ để phát hiện sớm các tác dụng phụ.
+### Tác dụng phụ
+Thuốc cisapride có thể gây ra nhiều tác dụng phụ trên trẻ em, bao gồm:
+- **Tiểu tiện nhiều lần:** Đây là tác dụng phụ hiếm gặp nhưng có thể xảy ra.
+- **Tiết nhiều sữa:** Tác dụng phụ này cũng khá hiếm gặp nhưng cần được chú ý.
+- **QT kéo dài:** Đây là tác dụng phụ nghiêm trọng có thể dẫn đến loạn nhịp tim.
+### Rủi ro và cảnh báo
+- **Tắc cơ học đường tiêu hóa:** Thuốc cisapride không nên được sử dụng cho bệnh nhân có tắc cơ học đường tiêu hóa.
+- **Suy gan nặng:** Trong trường hợp trẻ em có suy gan nặng, liều lượng cần được giảm xuống 50% liều thông thường.
+- **Trẻ sơ sinh:** Thuốc không nên được sử dụng cho trẻ sơ sinh dưới 3 tháng tuổi.
+### Bảo quản và lưu ý
+- **Bảo quản:** Thuốc cần được bảo quản ở nhiệt độ 15–25°C, tránh ẩm và ánh sáng.
+- **Lưu ý:** Thuốc cần được bảo quản tránh xa tầm tay trẻ em để tránh trường hợp trẻ ăn phải thuốc gây hậu quả khôn lường.
+### Tổng kết
+Việc sử dụng thuốc cisapride trên trẻ em cần được cân nhắc kỹ lưỡng và chỉ nên được thực hiện dưới sự giám sát chặt chẽ của bác sĩ. Các tác dụng phụ có thể xảy ra và cần được theo dõi cẩn thận.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tác dụng trên trẻ em chưa được rõ.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.7847021004858167</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5949007001286056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bôi thuốc Bisilkon bao nhiêu lần/ngày?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>['20 mg: Liều dùng 20 mg bisoprolol 1 lần/ngày là liều tối đa được khuyến nghị.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nThực Hiện 1 Lần/ Ngày: Thực hiện 1 lần/ngày là phương pháp sử dụng bài thuốc hỗ trợ điều trị da lở ngứa.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\n10 mg: Liều dùng 10 mg bisoprolol 1 lần/ngày được sử dụng để điều trị suy tim mãn ổn định.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\n2,5 mg: Liều dùng 2,5 mg bisoprolol 1 lần/ngày được sử dụng để điều trị huyết áp nhẹ.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nHàng Ngày: Hàng ngày là chu kỳ thời gian trong hướng dẫn sử dụng bài thuốc chữa viêm hang vị dạ dày.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nBệnh Lý Về Da: Bệnh lý về da là các bệnh lý da được điều trị bằng Bisilkon.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBisilkon: Bisilkon là kem bôi ngoài da điều trị một số bệnh lý về da, chứa clotrimazol, betamethason dipropionat và gentamicin.&lt;SEP&gt;Bisilkon được chỉ định trong các bệnh lý da đáp ứng với corticosteroid khi có biến chứng nhiễm trùng do nấm (nhạy cảm với clotrimazol) và vi khuẩn (nhạy cảm với gentamicin).&lt;SEP&gt;Bisilkon là thuốc được sử dụng để điều trị bệnh nhân, nếu không thấy cải thiện sau 3-4 tuần điều trị thì nên ngưng thuốc.&lt;SEP&gt;Bisilkon là thuốc có chứa corticosteroid dùng tại chỗ, có thể gây ức chế trục HPA và các tác dụng phụ khác.&lt;SEP&gt;Bisilkon là thuốc có đối tượng chống chỉ định sử dụng.&lt;SEP&gt;Bisilkon là thuốc cần được bảo quản nơi khô ráo, nhiệt độ không quá 30°C, tránh ánh sáng và không nên nuốt.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nChỉnh Liều Bisoprolol: Chỉnh liều bisoprolol là phương pháp điều chỉnh liều lượng thuốc trong quá trình điều trị.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nBismuth Subcitrat: Bismuth subcitrat là hoạt chất chính trong thuốc Bismuth, thường dùng 240 mg x 2 lần/ ngày hoặc 120 mg x 4 lần/ ngày.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nChỉnh Liều: Chỉnh liều Bisoprolol bắt đầu từ liều thấp và tăng dần liều nếu thuốc được dung nạp tốt.\nHuyền Hồ: Huyền hồ là dược liệu được sử dụng kết hợp với cỏ roi ngựa để điều trị kinh nguyệt không thông, huyết ứ, đau bụng dưới.&lt;SEP&gt;Chiết xuất từ Huyền hồ có tác dụng giảm đau, giảm tỷ lệ tâm thất trái/ trọng lượng cơ thể, ức chế kích hoạt tế bào thần kinh, và chống lại sự di căn của ung thư vú.&lt;SEP&gt;Huyền hồ, còn gọi là Huyền hồ sách, Diên hồ sách, Nguyên hồ, là vị thuốc trong Đông y có tác dụng làm tan máu ứ, cầm máu, giảm đau.&lt;SEP&gt;Huyền hồ là một loại dược liệu, rễ củ hình cầu dẹt không đều, mặt ngoài màu vàng hay vàng nâu, mùi nhẹ, vị đắng.&lt;SEP&gt;Huyền hồ là thành phần trong bài thuốc chữa đau do lạnh.&lt;SEP&gt;Huyền hồ là thành phần trong nhiều bài thuốc chữa đau.\nLiều Dùng: Liều Dùng là hướng dẫn về lượng thuốc cần sử dụng dựa trên nhiều yếu tố như cân nặng, độ tuổi, tình trạng sức khỏe của bệnh nhân, và chức năng thận. Đối với một số loại thuốc cụ thể, liều dùng được quy định rõ ràng cho từng đối tượng. Ví dụ, N-Acetylcystein có liều dùng được quy định cụ thể cho người lớn và trẻ em từ 2-6 tuổi. Thuốc Acyclovir cũng có liều dùng được điều chỉnh dựa trên tình trạng sức khỏe của bệnh nhân. \n\nThuốc Aleucin 500 mg có thể được sử dụng với liều lượng tăng lên tới 6 – 8 viên/ngày, chia làm 2 đến 3 lần sử dụng trong ngày. Đối với Aticef, liều dùng phụ thuộc vào cân nặng của bệnh nhân, mức độ thanh thải creatinin, và tình trạng nhiễm trùng. Các loại thuốc khác như Becozyme có liều dùng là 1 – 2 ống mỗi ngày, trong khi Bisoprolol có liều dùng được điều chỉnh dựa trên tình trạng dung nạp của bệnh nhân. \n\nCây Thuốc Mọi có liều dùng tham khảo là 30 – 60g/ngày (lá và thân), 10 – 12g/ngày (quả và vỏ). Liều dùng của Cenditan là mỗi lần uống 2 viên, mỗi ngày 3 lần. Đối với Children’s Tylenol, liều dùng khuyến cáo là 10 – 15 mg/kg/lần mỗi 4 – 6 giờ nhưng không được quá 75 mg/kg/ngày.\n\nLiều dùng của Cilzec được điều chỉnh tùy thuộc vào tình trạng cụ thể của bệnh nhân. Liều dùng cọ lùn đường uống là 320 mg một lần/ngày hoặc 160 mg hai lần một ngày. Liều dùng Pregabalin được điều chỉnh dựa trên tình trạng sức khỏe và tiến triển bệnh của mỗi bệnh nhân. Liều dùng của Dexacin phụ thuộc vào mức độ nghiêm trọng và đáp ứng trên từng cá thể.\n\nDạng viên hoàn 5g được nhà sản xuất khuyến cáo sử dụng với liều lượng 1-2 gói 5g/lần, dùng 3 lần mỗi 24 giờ. Liều dùng Atocib phụ thuộc vào tình trạng bệnh lý cụ thể của mỗi bệnh nhân. Liều dùng Atorvastatin 10 – 40 mg/ngày, có thể điều chỉnh lên đến 80 mg/ngày. \n\nLiều dùng của thuốc Bolutin cần được điều chỉnh phù hợp với độ tuổi và triệu chứng bệnh của từng bệnh nhân. Liều dùng Brosafe cũng cần được điều chỉnh tương tự. Liều dùng là cách sử dụng thuốc với liều lượng cụ thể và là hướng dẫn về liều lượng sử dụng thuốc. Tóm lại, Liều Dùng là hướng dẫn chi tiết về lượng thuốc cần sử dụng dựa trên nhiều yếu tố khác nhau để đảm bảo hiệu quả và an toàn trong việc điều trị.&lt;SEP&gt;Liều dùng của Chophytol cần được điều chỉnh phù hợp với độ tuổi và triệu chứng bệnh của từng bệnh nhân.&lt;SEP&gt;Liều dùng của Claminat cần được điều chỉnh phù hợp với độ tuổi và triệu chứng của từng bệnh nhân.&lt;SEP&gt;Liều dùng của Combivent® là 1 hít x 4 lần/ngày.&lt;SEP&gt;Liều dùng của Cravit thường là mỗi lần nhỏ 1 giọt và có thể dùng 3 lần trong ngày.\ndược sĩ: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nLiều Lượng: Liều lượng là số lượng thuốc hoặc chất hoạt chất được chỉ định sử dụng trong quá trình điều trị. Nó bao gồm cả số lượng thuốc được sử dụng và cách thức sử dụng nó, ví dụ như qua đường uống, tiêm hoặc thoa ngoài da. Liều lượng có thể được điều chỉnh dựa trên nhiều yếu tố khác nhau, bao gồm cân nặng, lối sống, và các yếu tố sức khỏe cá nhân khác. \n\nĐối với một số loại thuốc cụ thể, liều lượng cũng được quy định cụ thể cho từng độ tuổi. Ví dụ, liều lượng của Siro Bổ Phế Nam Hà và Viên Ngậm Bổ Phế Nam Hà được quy định cụ thể cho từng độ tuổi khác nhau. Điều này đảm bảo rằng mỗi người dùng nhận được liều lượng phù hợp với nhu cầu và tình trạng sức khỏe của họ.\n\nLiều lượng cũng có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc. Ví dụ, liều lượng corticoid sử dụng tại chỗ có thể được hấp thu vào máu, do đó việc xác định đúng liều lượng là rất quan trọng để tránh các tác dụng phụ không mong muốn.\n\nNgoài ra, liều lượng còn liên quan đến việc sử dụng thảo dược và hormone. Việc sử dụng thảo dược cần được chú ý về mức độ sử dụng, và liều lượng hormone là yếu tố ảnh hưởng đến việc lựa chọn liệu pháp hormon.&lt;SEP&gt;Liều lượng là yếu tố cần xem xét khi sử dụng dược liệu này để đảm bảo hiệu quả và an toàn.&lt;SEP&gt;Liều lượng là mức độ hoặc số lượng của một chất được đưa vào cơ thể, có thể ảnh hưởng đến hiệu quả và an toàn của việc sử dụng thuốc.&lt;SEP&gt;Liều lượng là số lượng thuốc cần dùng trong một lần hoặc trong một khoảng thời gian.\nThảo Dược: Thảo Dược là thuật ngữ chung chỉ các loại cây cỏ, hạt, củ, lá được sử dụng làm dược liệu trong y học cổ truyền. Thảo dược bao gồm nhiều loại cây khác nhau như cà dăm, cây Nổ gai, cây Rau Dớn, và cả quả, lá, và rễ của chanh. Thảo dược đóng vai trò quan trọng như các thành phần chính trong nhiều bài thuốc, đặc biệt là trong việc sắc uống hỗ trợ điều trị các chứng bế kinh, ứ huyết. Thảo dược từ cây Nổ gai có tác dụng khu phong, trừ thấp, thanh nhiệt, giải độc, chỉ huyết, giảm đau, và giảm ngứa. Thảo dược cũng được sử dụng trong chè dưỡng nhan có nguồn gốc từ cung đình Trung Quốc.\n\nThảo dược có nhiều công dụng trong việc phòng ngừa và điều trị các bệnh và triệu chứng, đồng thời cũng được sử dụng rộng rãi trong các bài thuốc cổ truyền. Thảo dược có thể tương tác với các loại thuốc hiện đại như Aleucin 500 mg và có tác dụng chống viêm rõ rệt. Thảo dược là nguồn gốc của các thành phần hóa học như coumarin trong nghiên cứu về tác dụng bảo vệ tế bào gan và chống viêm. Tuy nhiên, cần lưu ý rằng thảo dược có thể là con dao hai lưỡi nếu không sử dụng đúng cách, vì chúng có thể gây ra nhiều tương tác thuốc và tác dụng phụ tiềm ẩn.\n\nNgoài ra, thảo dược còn được sử dụng như một dạng thuốc thay thế có thể được sử dụng để điều trị bệnh đau chi ma. Thảo dược cũng được xem là một loại thực phẩm chức năng, mặc dù chưa được chứng minh có hiệu quả trong điều trị lo âu. Thảo dược là lĩnh vực chuyên môn cần tham vấn ý kiến của bác sĩ hoặc các chuyên gia. Cây sachi là một loại thảo dược có thể phát triển ở những vùng khí hậu ẩm ướt. Thảo dược là nguyên liệu dược liệu, cần bảo quản cẩn thận. Thảo dược là nguyên liệu quý được sử dụng trong y học cổ truyền và ngành hóa dược.\n\nThảo dược cũng được sử dụng để điều trị các bệnh ngoài da, bao gồm viêm lộ tuyến và viêm loét cổ tử cung. Thảo dược này có tác dụng cải thiện tế bào beta tụy và giảm lượng đường trong máu. Thảo dược là nguyên liệu trong bài thuốc hỗ trợ điều trị bệnh đái tháo đường và bệnh Gout. Thảo dược là thành phần tự nhiên trong BoniDiabet.\n\nThảo dược còn được biết đến như một phương pháp điều trị bệnh bằng các loại cây thuốc, bao gồm cả huyết rồng. Thảo dược là một trong hai phương pháp chính để chữa u mềm lây thông qua việc thoa lên bề mặt. Thảo dược là thuật ngữ chung cho các vị thuốc tự nhiên, bao gồm cả rau đắng đất, và cũng là nguyên liệu trong bài thuốc thanh can giải độc. Thảo dược là thuật ngữ dùng để chỉ các loại cây có tác dụng chữa bệnh và là thuật ngữ chung cho các loại cây thuốc.&lt;SEP&gt;Thảo dược là thuật ngữ chỉ các loại cây thuốc quý.&lt;SEP&gt;Thảo dược là nguyên liệu tự nhiên từ cây cỏ.&lt;SEP&gt;Thảo dược là các chất hóa học tự nhiên từ thực vật, có thể được sử dụng trong điều trị.&lt;SEP&gt;Thảo dược là tên chung cho các loại cây được sử dụng làm thuốc, trong đó có Tía tô.\nBismuth Subcitrat - Tiêu Chảy: Bismuth subcitrat được chỉ định trong điều trị tiêu chảy.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nBisilkon - Ngứa: Ngứa là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nBisilkon - Phụ Nữ Có Thai: Bisilkon chống chỉ định sử dụng ở phụ nữ mang thai.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nChỉnh Liều Bisoprolol - Suy Tim: Chỉnh liều bisoprolol là phương pháp điều chỉnh liều lượng thuốc trong quá trình điều trị suy tim.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBisilkon - Tiểu Đường: Bisilkon có thể gây ra tiểu đường do sử dụng kéo dài.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nBisilkon - Phụ Nữ Mang Thai: Không nên dùng Bisilkon cho phụ nữ mang thai.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nBisilkon - Loãng Xương: Bisilkon có thể gây ra loãng xương do sử dụng kéo dài.\nHuyền Hồ - Liều Dùng: Liều dùng chỉ dẫn liều lượng sử dụng Huyền hồ.\n20 mg - Bisoprolol: Bisoprolol được sử dụng với liều tối đa 20 mg 1 lần/ngày.\ndược sĩ - thuốc: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\n10 mg - Bisoprolol: Bisoprolol được sử dụng với liều 10 mg 1 lần/ngày để điều trị suy tim mãn ổn định.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\n2,5 mg - Bisoprolol: Bisoprolol được sử dụng với liều 2,5 mg 1 lần/ngày để điều trị huyết áp nhẹ.\nCách Dùng - Cánh Kiến Trắng: Cách dùng và liều dùng của cây Thuốc mọi tùy thuộc vào mục đích sử dụng và từng bài thuốc.\nBisoprolol - Chỉnh Liều: Chỉnh liều Bisoprolol bắt đầu từ liều thấp và tăng dần liều nếu thuốc được dung nạp tốt.\nBisilkon - Corticosteroid: Bisilkon chứa corticosteroid để điều trị các bệnh lý da.&lt;SEP&gt;Bisilkon chứa corticosteroid, có thể gây ức chế trục HPA.\nBisilkon - Thủy Đậu: Bisilkon chống chỉ định sử dụng ở người bị thủy đậu.\nBisilkon - Nhiễm Khuẩn: Bisilkon cần được bảo quản tránh tiếp xúc với các nguồn gây nhiễm khuẩn hoặc tái nhiễm.\nBisilkon - Mụn Trứng Cá: Bisilkon chống chỉ định sử dụng ở người bị mụn trứng cá.\nBisilkon - Mẹ Cho Con Bú: Bisilkon chống chỉ định sử dụng ở mẹ cho con bú.\nBisilkon - Giang Mai: Bisilkon chống chỉ định sử dụng ở người bị giang mai.\nBisilkon - Tác Dụng Không Mong Muốn: Người dùng cần thông báo với bác sĩ hoặc dược sĩ về bất kỳ tác dụng không mong muốn nào gặp phải khi sử dụng Bisilkon.\nBan Đỏ - Bisilkon: Ban đỏ là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Gentamicin: Gentamicin là thành phần chính của Bisilkon, là kháng sinh thuộc nhóm aminoglycosid.&lt;SEP&gt;Bisilkon được chỉ định khi có biến chứng nhiễm trùng do vi khuẩn nhạy cảm với gentamicin.\nBisilkon - Ánh Sáng: Bisilkon cần được bảo quản tránh ánh sáng.\nBisilkon - Hội Chứng Cushing: Bisilkon có thể gây ra hội chứng Cushing do sử dụng kéo dài.\nBismuth Subcitrat - Thực Quản: Bismuth subcitrat được sử dụng để bảo vệ thực quản khỏi kích ứng.\nBisilkon - Clotrimazol: Clotrimazol là thành phần chính của Bisilkon, dùng để điều trị tại chỗ các bệnh nấm về da.&lt;SEP&gt;Bisilkon được chỉ định khi có biến chứng nhiễm trùng do nấm nhạy cảm với clotrimazol.\nBisilkon - Nấm Candida: Bisilkon chống chỉ định sử dụng ở người bị nấm Candida.\nBisilkon - Thời Kỳ Mang Thai: Tính an toàn của Bisilkon cho phụ nữ mang thai chưa được thiết lập, do đó không nên dùng thuốc cho họ.\nBisilkon - Eczema: Bisilkon được chỉ định để điều trị eczema có rỉ dịch.\nBisilkon - Hạn Dùng: Bisilkon có hạn dùng là 36 tháng kể từ ngày sản xuất.\nAminoglycosid - Bisilkon: Khi sử dụng đồng thời với aminoglycosid toàn thân có thể gây độc do tích lũy kháng sinh.\nBisilkon - Thời Kỳ Cho Con Bú: Cần thận trọng khi dùng Bisilkon ở phụ nữ đang cho con bú.\nBisilkon - Nóng Bừng: Nóng bừng là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Ghẻ Ngứa: Bisilkon chống chỉ định sử dụng ở người bị ghẻ ngứa.\nBệnh Lý Về Da - Gentamicin: Gentamicin là kháng sinh thuộc nhóm aminoglycosid, dùng để điều trị bệnh lý về da.\nBisilkon - Dược Sĩ Trần Việt Linh: Dược sĩ Trần Việt Linh đã cung cấp thông tin về sản phẩm Bisilkon.\nBisilkon - Viêm Da Quanh Miệng: Bisilkon chống chỉ định sử dụng ở người bị viêm da quanh miệng.\nBisilkon - Chấy Rận: Bisilkon chống chỉ định sử dụng ở người bị chấy rận.\nBisilkon - Nhiễm Trùng Vi Khuẩn: Bisilkon được chỉ định để điều trị nhiễm trùng vi khuẩn.\nBisilkon - Tiền Sử Mẫn Cảm: Bisilkon chống chỉ định sử dụng ở người có tiền sử mẫn cảm với bất kỳ thành phần nào của thuốc.\nBidiphar - Bisilkon: Bidiphar sản xuất Bisilkon, kem bôi ngoài da điều trị một số bệnh lý về da.\nBisilkon - Giảm Sắc Tố: Giảm sắc tố là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBệnh Lý Về Da - Clotrimazol: Clotrimazol được dùng để điều trị tại chỗ các bệnh nấm về da.\nBisilkon - Rỉ Dịch: Rỉ dịch là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBetamethason Dipropionat - Bisilkon: Betamethason dipropionat là thành phần chính của Bisilkon, có tác dụng chống viêm, chống dị ứng, chống thấp khớp và ức chế miễn dịch.\nBisilkon - Rộp Da: Bisilkon chống chỉ định sử dụng ở người bị rộp da.\nBisilkon - Đậu Mùa: Bisilkon chống chỉ định sử dụng ở người bị đậu mùa.\nBisilkon - Trục HPA: Bisilkon có thể gây ức chế trục HPA.\nBisilkon - Đổi Màu Da: Đổi màu da là tác dụng không mong muốn hiếm khi xảy ra khi sử dụng Bisilkon.\nBisilkon - Mụn Nói Chung: Bisilkon chống chỉ định sử dụng ở người bị mụn nói chung.\nBisilkon - Lao Da: Bisilkon chống chỉ định sử dụng ở người bị lao da.\nBisilkon - Giời Leo: Bisilkon chống chỉ định sử dụng ở người bị giời leo.\nBisilkon - Nhiễm Trùng Nấm: Bisilkon được chỉ định để điều trị nhiễm trùng nấm.\nBisilkon - Kích Thích ACTH: Kiểm tra sự ức chế trục HPA thông qua kích thích ACTH.\nBisilkon - Băng Kín: Bisilkon có thể gây ra tác dụng không mong muốn khi dùng băng kín.\nBismuth Subcitrat - Loét Dạ Dày Tá Tràng: Bismuth subcitrat được chỉ định trong điều trị loét dạ dày tá tràng.\nBismuth Subcitrat - H. Pylori: Bismuth subcitrat được sử dụng để diệt trừ H. pylori.\nBismuth Subcitrat - Chứng Khó Tiêu: Bismuth subcitrat được chỉ định trong điều trị chứng khó tiêu.\nBài Thuốc Chữa Viêm Hang Vị Dạ Dày - Hàng Ngày: Hàng ngày lấy 1 nhúm cho vào chai trà, hãm với nước sôi, uống thay trà liên tục 2 tháng.\nBetamethason Dipropionat - Bệnh Lý Về Da: Betamethason dipropionat có tác dụng chống viêm, chống dị ứng, chống thấp khớp và �ức chế miễn dịch.\nChỉnh Liều Bisoprolol - Thời Gian Thải Rối: Chỉnh liều bisoprolol liên quan đến thời gian thải trừ của thuốc.']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thuốc Bisilkon thường được sử dụng 1 lần/ngày. Tuy nhiên, việc sử dụng thuốc cần tuân theo hướng dẫn cụ thể của bác sĩ hoặc dược sĩ, dựa trên tình trạng sức khỏe và tình trạng bệnh lý cụ thể của từng bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thuốc Bisilkon bôi 2 lần/ngày vào buổi sáng và buổi tối.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8391224207853462</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6472806051713366</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng thuốc Atorpa-E đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>['Atorpa-E: Atorpa-E là thuốc chữa bệnh tim mạch chứa Atorvastatin và Ezetimibe.&lt;SEP&gt;Atorpa-E là thuốc kết hợp Atorvastatin và Ezetimibe, dùng để giảm nguy cơ các biến cố tim mạch và điều trị tăng cholesterol máu.&lt;SEP&gt;Atorpa-E là thuốc được chỉ định điều trị tăng cholesterol máu và rối loạn lipid máu hỗn hợp.&lt;SEP&gt;Atorpa-E là thuốc được sử dụng trong điều trị bệnh gan, chống chỉ định ở bệnh nhân có bệnh gan đang hoạt động.&lt;SEP&gt;Atorpa-E là thuốc cần thận trọng khi sử dụng ở bệnh nhân uống nhiều rượu, có tiền sử bệnh gan, yếu tố ảnh hưởng đến hội chứng tiêu cơ vân, người lớn tuổi và đang điều trị với cyclosporin.&lt;SEP&gt;Atorpa-E là thuốc có công dụng, cách dùng và tác dụng phụ được đề cập trong bài viết.&lt;SEP&gt;Atorpa-E là thuốc chứa Atorvastatin và Ezetimibe.\nCholesterol: Cholesterol là một hợp chất sinh học đóng vai trò quan trọng trong cơ thể, tồn tại trong hầu hết các tế bào và được tạo ra bởi gan. Nó không chỉ là một thành phần cần thiết cho cơ thể mà còn có thể trở thành nguyên nhân gây ra tình trạng tăng cholesterol máu, một yếu tố nguy cơ gây bệnh tim mạch. Cholesterol đóng vai trò trong cấu trúc của màng tế bào và các chức năng khác của cơ thể, đồng thời là một hợp chất hóa học có trong máu, liên quan đến nhiều vấn đề sức khỏe.\n\nCholesterol có thể được chuyển đổi thành acid mật và kiểm soát lượng cholesterol trong cơ thể có thể được thực hiện thông qua nhiều phương pháp khác nhau, bao gồm việc sử dụng Atorvastatin, một loại thuốc hạ cholesterol, thông qua việc ức chế quá trình tổng hợp cholesterol trong cơ thể. Điều này giúp giảm nồng độ cholesterol trong máu và tế bào, đồng thời giúp kiểm soát lượng cholesterol, giảm chất xơ trong Actiso, góp phần vào việc giảm cân và hỗ trợ hệ tiêu hóa. Ngoài ra, trà Atiso đỏ cũng có thể giúp kiểm soát lượng cholesterol trong cơ thể. Các chất khác như Bạch linh, cà dại hoa tím, Betaine hydrochloride trong kỷ tử và cây Ba chạc cũng giúp giảm đáng kể nồng độ cholesterol.\n\nCholesterol cũng là chất béo hòa tan trong máu và được giảm nhờ sự tác động của saponin, làm giảm nồng độ cholesterol trong huyết tương. Cholesterol còn được biết đến như một thành phần mỡ trong máu bị ức chế bởi chiết xuất Actiso. Một số thảo dược khác như khổ qua, liên翘, vỏ quả mít đỏ, và đu đủ cũng được chứng minh có khả năng giảm mức cholesterol trong máu.\n\nCholesterol là một trong những thành phần hóa học của ngưu hoàng và cũng là một hợp chất liên quan đến glucose và khả năng dung nạp đường. Cholesterol là một loại chất béo có thể gây ra bệnh xơ vữa động mạch khi tồn tại trong máu. Sử dụng các chất tự nhiên như nấm Linh Chi có thể giúp kiểm soát mức cholesterol trong máu. Adenosine trong nấm Linh Chi có thể giúp điều chỉnh lượng cholesterol trong máu, từ đó giảm mức cholesterol.\n\nCholesterol bị bài tiết tăng từ Sơn tra, có thể làm hạ lipid máu. Cholesterol là thành phần của lipid máu được hạ thấp bởi quả quýt. Cholesterol là chất trong máu, có thể bị ảnh hưởng bởi rau đắng biển. Mỡ máu (chủ yếu là cholesterol) là yếu tố cần kiểm tra khi chẩn đoán rối loạn cương dương. Tăng cholesterol là một dạng rối loạn lipid máu. Cholesterol là thành phần chính của HDL. Cholesterol là thành phần trong máu cần được kiểm soát trong điều trị rối loạn lipid máu. Cholesterol là chất béo trong máu, thường tăng cùng với bệnh nhân bị tăng triglycerid.\n\nCholesterol là một chất béo dạng sáp, có trong thức ăn và được cơ thể tổng hợp. Xét nghiệm cholesterol là phương pháp chẩn đoán để đánh giá mức độ cholesterol trong máu. Cholesterol cao là triệu chứng cần được kiểm soát để ngăn ngừa tai biến mạch máu não. Cholesterol là hợp chất được nhóm thuốc statins kiểm soát.\n\nNgoài ra, cholesterol cũng là nguồn nguyên liệu để tổng hợp các nội tiết tố tại tuyến thượng thận. Cholesterol được tìm thấy trong máu và được thạch lựu tác động làm giảm mức. Cholesterol là chất được tìm thấy ở thạch lựu có khả năng làm giảm mức cholesterol trong máu. Cholesterol là chất béo hòa tan trong máu, có thể tăng lên do bổ sung vitamin D và cholesterol. Chiết xuất hạt Thanh Yên có hoạt tính giảm cholesterol. Cholesterol là chất béo đóng vai trò trong quá trình xơ vữa động mạch.\n\nMức độ cholesterol trong máu có thể tăng khi sử dụng Aluvia. Arginin giúp làm giảm mức cholesterol. Rối loạn chuyển hóa lipid được điều trị bằng Atorvastatin. Cholesterol là thành phần lipid “xấu” trong máu được Atorvastatin giảm nồng độ. Cholesterol là hợp chất có thể bị ảnh hưởng bởi Brufen, mặc dù không được đề cập cụ thể trong văn bản. Cholesterol là chất được kiểm tra trong các xét nghiệm liên quan đến Daflon. Cholesterol là hợp chất hóa học được điều chỉnh mức bằng cholestyramine.\n\nCholesterol là một chất bị giảm hấp thu khi dùng neomycin. Cholesterol cũng được giảm bởi tinh dầu Bergamot. Cholesterol trong máu có thể được cải thiện bởi tinh dầu húng quế. Cholesterol là một dạng bệnh liên quan đến mức cholesterol cao trong máu. Cholesterol là một thành phần hóa học trong nọc bọ cạp. Cholesterol là chất được kiểm soát bởi việc uống nước trà xanh thường xuyên. Cholesterol là một thành phần trong dịch mật có thể kết tụ thành dạng rắn gây sỏi mật. Cholesterol là chất béo có thể tích tụ và tạo thành sỏi cholesterol trong cơ thể.&lt;SEP&gt;Cholesterol là chất béo được tìm thấy trong huyết tương, tăng nồng độ do suy chức năng giáp.&lt;SEP&gt;Hormone giáp làm giảm nồng độ cholesterol trong huyết tương.\nTiền Sử Bệnh Cơ Do Dùng Statin Hoặc Fibrat: Tiền sử bệnh cơ do dùng statin hoặc fibrat là yếu tố ảnh hưởng đến hội chứng tiêu cơ vân, cần thận trọng khi sử dụng Atorpa-E.\nNgăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não là việc giảm thiểu tỉ lệ mắc phải TBMMN thông qua việc dùng thuốc đúng chỉ định và liều lượng.\nEzetimibe: Ezetimibe là thành phần chính trong Atorpa-E.&lt;SEP&gt;Ezetimibe là thuốc ức chế hấp thu cholesterol ở ruột, giảm mỡ máu.&lt;SEP&gt;Ezetimibe là thuốc ức chế hấp thu cholesterol từ ruột.&lt;SEP&gt;Ezetimibe là thuốc không có dữ liệu lâm sàng về việc dùng ở phụ nữ có thai và không nên sử dụng ở phụ nữ cho con bú.&lt;SEP&gt;Ezetimibe là thuốc được đề cập.&lt;SEP&gt;Ezetimibe là thuốc có thể tương tác với Atorvastatin.&lt;SEP&gt;Ezetimibe là thuốc ức chế hấp thu cholesterol, được sử dụng để điều trị rối loạn lipid máu.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nTăng Men Gan Transaminase Huyết Thanh Kéo Dài Không Rõ Nguyên Nhân: Tăng men gan transaminase huyết thanh kéo dài không rõ nguyên nhân là tình trạng chống chỉ định khi dùng Atorpa-E.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nNgười Lớn Tuổi: Người lớn tuổi là đối tượng cần thận trọng khi sử dụng Atorpa-E.&lt;SEP&gt;Người lớn tuổi (trên 70 tuổi) cần thận trọng khi sử dụng Atorvastatin do có yếu tố nguy cơ bị tiêu cơ vân.&lt;SEP&gt;Người lớn tuổi thường có mỡ tích tụ.&lt;SEP&gt;Người lớn tuổi có nguy cơ cao mắc bướu giáp keo.&lt;SEP&gt;Người lớn tuổi là nhóm đối tượng có nhu cầu về canxi nhiều hơn do nguy cơ loãng xương.&lt;SEP&gt;Người lớn tuổi là đối tượng sử dụng đông trùng hạ thảo ngâm mật ong.&lt;SEP&gt;Người lớn tuổi có nguy cơ cao bị biến chứng sau phẫu thuật.\nTim mạch: Tim mạch là hệ thống gồm tim và mạch máu, liên quan đến các chống chỉ định sử dụng thuốc.\nTiền Sử Bệnh Gan: Tiền sử bệnh gan là tình trạng thận trọng khi dùng Atorpa-E.&lt;SEP&gt;Tiền sử bệnh gan là tình trạng cần thận trọng khi sử dụng Atorvastatin.\nBệnh Động Mạch: Bệnh động mạch là bệnh liên quan đến LDL cholesterol.\nPhòng Ngừa Xơ Vữa Động Mạch: Atorvastatin phòng ngừa xơ vữa động mạch.\nLDL Cholesterol: LDL cholesterol là lipoprotein cholesterol tỷ trọng thấp liên quan đến yếu tố gây đột quỵ và các bệnh về tim và động mạch.&lt;SEP&gt;LDL cholesterol là dạng cholesterol xấu được giảm bởi việc tiêu thụ mầm đậu nành.&lt;SEP&gt;LDL cholesterol là loại cholesterol xấu, góp phần gây rối loạn lipid máu, xơ vữa mạch máu, các bệnh lý mạch vành, và đột quỵ não.\nAtorhasan 20: Atorhasan 20 được sử dụng trong điều trị rối loạn lipid máu, hỗ trợ liệu pháp ăn uống ở người lớn và trẻ em bị tăng cholesterol máu nguyên phát và rối loạn lipid máu hỗn hợp.\nThuốc Giảm Cholesterol: Thuốc giảm cholesterol được sử dụng để ngăn ngừa xơ vữa động mạch.&lt;SEP&gt;Thuốc giảm cholesterol là loại thuốc được sử dụng để điều trị tăng cholesterol và ngăn ngừa sa sút trí tuệ do mạch máu.\nUống Nhiều Rượu: Uống nhiều rượu là tình trạng thận trọng khi dùng Atorpa-E.&lt;SEP&gt;Uống nhiều rượu là tình trạng cần thận trọng khi sử dụng Atorvastatin.&lt;SEP&gt;Uống nhiều rượu là hành vi tiêu thụ rượu quá mức.\nXơ Vữa Động Mạch: Xơ vữa động mạch là bệnh lý của hệ thống tim mạch liên quan đến sự tích tụ cholesterol, chất béo trung tính, và các mảng bám khác trên thành mạch máu. Tình trạng này tạo nên lớp cặn cứng và dày ở bên trong động mạch, làm thu hẹp đường kính của chúng và làm cho động mạch kém chuyển động hơn. Bệnh lý này thường xuất hiện do giảm viêm, stress oxy hóa, và tăng huyết áp. Xơ vữa động mạch không chỉ là bệnh lý về động mạch mà còn có thể dẫn đến các vấn đề về thận thứ phát, gây tổn thương các cơ quan như tim, não, và thận.\n\nĐể ngăn chặn và phòng ngừa xơ vữa động mạch, người ta thường sử dụng các loại thuốc như Atorvasan VLC, Atorvastatin, Altamin, Clopidogrel, Bonzacim, và Bồ hoàng. Atorvastatin không chỉ giúp phòng ngừa xơ vữa động mạch mà còn làm chậm quá trình tiến triển của bệnh mạch vành. Clopidogrel được sử dụng để kiểm soát bệnh xơ vữa động mạch thứ phát. Tuy nhiên, cần phải thận trọng khi sử dụng các loại thuốc chứa canxi, vitamin D, và Calcigenol vì chúng có thể gây tăng canxi huyết và tạo ra các vấn đề liên quan đến xơ vữa động mạch. Ngoài việc sử dụng thuốc, các biện pháp tự nhiên như sử dụng Bạch linh, Biển súc, và dây ký ninh cũng được biết đến với khả năng ngăn ngừa xơ vữa động mạch. Tuy nhiên, người bệnh cần thận trọng khi sử dụng Babi B.O.N. do khả năng gây ra các vấn đề liên quan đến xơ vữa động mạch.\n\nXơ vữa động mạch còn được điều trị thử nghiệm bằng cách sử dụng cỏ xước, aconitin, và Đan sâm. Aconitin đã được thử nghiệm trên thỏ và Đan sâm được sử dụng trong điều trị bệnh tim mạch. Xơ vữa động mạch là quá trình lắng đọng chất béo trong thành động mạch, làm thu hẹp lòng mạch. Nó cũng là nguyên nhân phổ biến nhất của bệnh động mạch ngoại biên. Tình trạng này còn được ngăn chặn bởi hàm lượng chất xơ trong đậu và chiết xuất từ dây ký ninh. Rutin cũng được biết đến với khả năng đề phòng biến cố do xơ vữa động mạch. Một số thảo dược khác như La bạc tử cũng được sử dụng trong điều trị xơ vữa động mạch nhờ vào thành phần linolenic acid và linoleic acid của nó. Xơ vữa động mạch cũng được khắc phục nhờ tác dụng kháng viêm của mật mông hoa và chiết xuất cây. Saponin cũng được biết đến với khả năng ức chế sự phát triển của xơ vữa động mạch. Ngoài ra, tình trạng này còn được ngăn chặn nhờ tác dụng của mộc nhĩ.\n\nXơ vữa động mạch là hậu quả của tăng huyết áp và rối loạn mỡ máu. Bệnh lý này cũng là biến chứng của tiểu đường và được ngăn ngừa nhờ mướp đắng và BoniDiabet. Xơ vữa động mạch cũng được điều trị bằng Sâm vũ diệp và Tam lăng nhờ tác dụng chống lại quá trình xơ vữa. Xơ vữa động mạch là biến chứng của bệnh tăng huyết áp vô căn, có thể dẫn đến đau tim. Xơ vữa động mạch cũng là một nguyên nhân gây bệnh teo não và là một trong những bệnh nội khoa góp phần thúc đẩy tình trạng thiếu máu não cục bộ dẫn đến teo não. Xơ vữa động mạch là tình trạng tích tụ mảng bám trong thành mạch máu, được giảm nguy cơ bởi tác dụng của thiên ma. Xơ vữa động mạch là bệnh liên quan đến việc làm giảm cholesterol toàn phần và LDL. Xơ vữa động mạch là quá trình tích tụ cholesterol và canxi trong lòng mạch vành, gây xơ cứng và khó dẫn máu đến nuôi tim.&lt;SEP&gt;Xơ vữa động mạch là bệnh tim mạch do tăng cholesterol máu kéo dài do suy chức năng giáp.&lt;SEP&gt;Xơ vữa động mạch nặng thường liên quan đến suy chức năng giáp.\nGiảm Tiểu Паuл: Giảm tiểu cầu là tác dụng phụ của Atorpa-E.\nCholesterol Máu: Cholesterol máu là một hợp chất sinh học quan trọng, đóng vai trò trung tâm trong nhiều rối loạn lipid máu và các bệnh liên quan đến sức khỏe. Cholesterol máu có thể tăng lên do nhiều nguyên nhân khác nhau, dẫn đến tình trạng tăng hàm lượng cholesterol trong máu. Điều này đòi hỏi sự kiểm soát chặt chẽ thông qua các phương pháp điều trị như sử dụng Atorhasan 20, Cosele, dầu jojoba, Địa cốt bì, và Dứa dại.\n\nNgoài ra, cholesterol máu còn được tác động bởi Bồ hoàng để giúp giảm mức cholesterol. Việc kiểm soát nồng độ cholesterol máu là một trong những phương pháp phòng ngừa hiệu quả đối với bệnh suy thận và cũng là một triệu chứng cần được kiểm soát trong bệnh cầu thận màng.&lt;SEP&gt;Cholesterol máu cao là bệnh được điều trị bằng Kiều mạch.&lt;SEP&gt;Cholesterol máu là bệnh rối loạn chuyển hóa cholesterol, có thể được điều trị bằng chất berbagia trong lá ổi.&lt;SEP&gt;Ngưu tất được ghi nhận có tác dụng hạ cholesterol máu.&lt;SEP&gt;Cholesterol máu là vấn đề sức khỏe được điều trị bằng Sa nhân.&lt;SEP&gt;Cholesterol máu là một trong những yếu tố góp phần vào hình thành các mảng xơ vữa trong động mạch.\nDứa Dại: Dứa dại là cây được sử dụng trong bài thuốc trị sỏi thận.&lt;SEP&gt;Dứa dại, còn gọi là Dứa gỗ, Dứa gai, được dùng trong dân gian để trị bí tiểu, sỏi thận.&lt;SEP&gt;Cây Dứa dại được trồng và mọc dại ở nhiều nơi tại Việt Nam và các nước khác trên thế giới.&lt;SEP&gt;Dứa Dại được sử dụng để trị bí tiểu, tiểu khó, sỏi thận và bồi bổ cơ thể.&lt;SEP&gt;Dứa dại là cây được sử dụng trong dân gian để điều trị một số bệnh.&lt;SEP&gt;Dứa dại là thảo dược được sử dụng trong bài thuốc sắc điều trị thấp khớp.\nAtorpa-E - Tăng Huyết Áp: Tăng huyết áp là tác dụng phụ của Atorpa-E.\nCholesterol - Ngăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não thông qua việc kiểm soát cholesterol.\nAtorpa-E - Suy Thận: Không cần chỉnh liều Atorpa-E ở bệnh nhân suy thận.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nAtorpa-E - Ho: Ho, đau thanh quản là tác dụng phụ của Atorpa-E.\nCholesterol - Tim mạch: Cholesterol cao là một trong những chống chỉ định sử dụng thuốc.\nAtorpa-E - Tim Mạch: Atorpa-E được sử dụng để điều trị các bệnh về tim mạch.\nBệnh Động Mạch - LDL Cholesterol: LDL cholesterol liên quan đến bệnh động mạch.\nAtorpa-E - Phụ Nữ Có Thai: Atorpa-E không nên sử dụng ở phụ nữ có thai do nguy cơ tiềm ẩn của các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Phụ nữ có thai không được sử dụng Atorpa-E.&lt;SEP&gt;Atorpa-E được chống chỉ định ở phụ nữ có thai.\nThuốc Giảm Cholesterol - Xơ Vữa Động Mạch: Thuốc giảm cholesterol được sử dụng để điều trị xơ vữa động mạch.\nAtorhasan 20 - Tim Mạch: Atorhasan 20 bảo vệ hệ thống mạch máu từ biến cố tim mạch.\nCholesterol Máu - Dứa Dại: Dứa dại điều trị cholesterol máu.\nAtorpa-E - Suy Gan: Atorpa-E chống chỉ định ở bệnh nhân suy gan.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\nAtorpa-E - Quá Liều: Trường hợp quá liều Atorpa-E cần điều trị triệu chứng và theo dõi chức năng gan và CPK huyết thanh.\nSuy Tim Mạn - Thuốc Lá: Thuốc lá là yếu tố nguy cơ đối với bệnh lý tim mạch.\nAtorpa-E - Rối Loạn Tiêu Hóa: Rối loạn tiêu hóa là tác dụng phụ của Atorpa-E.\nCholesterol - Cỏ Xước: Cỏ xước giảm cholesterol.\nAtorhasan 20 - Tiểu Đường: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch ở bệnh nhân tiểu đường.\nCholesterol Cao - Van Tim: Cholesterol cao có thể làm trầm trọng thêm một số vấn đề về van tim.\nAtorpa-E - Atorvastatin: Atorpa-E chứa Atorvastatin như một thành phần chính.\nAtorpa-E - Phụ Nữ Cho Con Bú: Atorpa-E không nên sử dụng ở phụ nữ cho con bú do nguy cơ tiềm ẩn của các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Atorpa-E được chống chỉ định ở phụ nữ cho con bú.\nAtorhasan 20 - Hạ Huyết Áp: Atorhasan 20 có tác dụng hạ huyết áp.\nAtorhasan 20 - Huyết Áp: Atorhasan 20 có tác dụng hạ huyết áp.\nAtorpa-E - Hạ Đường Huyết: Hạ đường huyết là tác dụng phụ của Atorpa-E.\nCanxi - Người Lớn Tuổi: Người lớn tuổi có nhu cầu về canxi nhiều hơn do nguy cơ loãng xương.\nAtorvastatin - Ezetimibe: Sử dụng Atorvastatin cùng với Ezetimibe tăng nguy cơ mắc bệnh cơ.&lt;SEP&gt;Ezetimibe có thể tương tác với Atorvastatin.\nAtorvastatin - Người Lớn Tuổi: Atorvastatin cần thận trọng khi sử dụng trên người lớn tuổi (trên 70 tuổi).\nAtorpa-E - Viêm Gan: Viêm gan, ứ mật, sỏi mật là tác dụng phụ của Atorpa-E.\nCholesterol - Ezetimibe: Ezetimibe ức chế hấp thu cholesterol ở ruột.\nAtorvastatin - Uống Nhiều Rượu: Uống nhiều rượu là tình trạng thận trọng khi dùng Atorvastatin.&lt;SEP&gt;Atorvastatin cần thận trọng khi sử dụng trên người uống nhiều rượu.\nAtorvastatin - Tiền Sử Bệnh Gan: Tiền sử bệnh gan là tình trạng thận trọng khi dùng Atorvastatin.&lt;SEP&gt;Atorvastatin cần thận trọng khi sử dụng trên người có tiền sử bệnh gan.\nAtorvastatin - Tăng Men Gan Transaminase Huyết Thanh Kéo Dài Không Rõ Nguyên Nhân: Tăng men gan transaminase huyết thanh kéo dài không rõ nguyên nhân là tác dụng phụ khi dùng Atorvastatin.\nAtorpa-E - Chán Ăn: Chán ăn là tác dụng phụ của Atorpa-E.\nLoãng Xương - Uống Nhiều Rượu: Uống nhiều rượu làm giảm khả năng tạo xương và tăng nguy cơ gãy xương.\nAtorpa-E - Ù Tai: Ù tai, mất thính lực là tác dụng phụ của Atorpa-E.\nAtorpa-E - Chảy Máu Cam: Chảy máu cam là tác dụng phụ của Atorpa-E.\nAtorpa-E - Bệnh Tim Mạch: Atorpa-E phòng ngừa bệnh tim mạch.\nAtorhasan 20 - Đái Tháo Đường Type 2: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch ở bệnh nhân đái tháo đường type 2.\nAtorpa-E - Quá Mẫn: Quá mẫn, bao gồm sốc phản vệ, phù mạch, nổi mày đay, phát ban, là tác dụng phụ của Atorpa-E.\nAtorhasan 20 - Hút Thuốc Lá: Atorhasan 20 được sử dụng để tránh tác hại của hút thuốc lá.\nAtorpa-E - Tăng Đường Huyết: Tăng đường huyết là tác dụng phụ của Atorpa-E.\nNgười Lớn Tuổi - Tắc Ruột: Tắc ruột là triệu chứng phổ biến ở người lớn tuổi.\nAtorhasan 20 - Rối Loạn Lipid Máu: Atorhasan 20 được sử dụng để điều trị rối loạn lipid máu.\nAtorpa-E - Statin: Atorpa-E được sử dụng kết hợp với statin trong điều trị tăng cholesterol máu.\nAtorhasan 20 - Xơ Vữa Động Mạch: Atorhasan 20 được sử dụng để dự phòng xơ vữa động mạch.\nAtorpa-E - Bệnh Gan: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh gan.\nEzetimibe - Rối Loạn Lipid Máu: Ezetimibe được sử dụng để điều trị rối loạn lipid máu.\nAtorpa-E - Cyclosporin: Atorpa-E được sử dụng đồng thời với Cyclosporin.\nAtorpa-E - Rối Loạn Thị Giác: Rối loạn thị giác, mờ mắt là tác dụng phụ của Atorpa-E.\nAtorpa-E - Suy Giảm Chức Năng Thận: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có suy giảm chức năng thận.\nAtorpa-E - Lipid: Atorpa-E cần kiểm soát hàm lượng lipid trong chế độ ăn kiêng của bệnh nhân.\nEzetimibe - Warfarin: Hoạt chất Ezetimibe có thể tương tác với Warfarin.\nAtorhasan 20 - Kháng Viêm: Atorhasan 20 có tác dụng kháng viêm.\nAtorpa-E - Viêm Tụy: Viêm tụy là tác dụng phụ của Atorpa-E.\nAtorhasan 20 - Bệnh Mạch Vành: Atorhasan 20 được sử dụng để dự phòng bệnh mạch vành.\nAtorpa-E - Trào Ngược Dạ Dày: Trào ngược dạ dày, ợ hơi, buồn nôn, nôn, khô miệng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Phụ Nữ Đang Cho Con Bú: Phụ nữ đang cho con bú không được sử dụng Atorpa-E.\nAtorpa-E - Mất Trí Nhớ: Mất trí nhớ là tác dụng phụ của Atorpa-E.\nAtorpa-E - Biếng Ăn: Biếng ăn là tác dụng phụ của Atorpa-E.\nAtorpa-E - Ezetimibe: Atorpa-E chứa Ezetimibe như một thành phần chính.&lt;SEP&gt;Atorpa-E được sử dụng kết hợp với ezetimibe trong điều trị tăng cholesterol máu.\nAtorpa-E - Chế Độ Ăn Kiêng: Atorpa-E được chỉ định như một liệu pháp hỗ trợ trong chế độ ăn kiêng của bệnh nhân HoFH.\nAtorpa-E - Nhược Giáp: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có nhược giáp.\nAtorpa-E - Người Lớn Tuổi: Atorpa-E cần thận trọng khi sử dụng ở người lớn tuổi.\nAtorpa-E - Tăng Cholesterol Máu: Atorpa-E điều trị tăng cholesterol máu.\nAcid Mật - Atorpa-E: Atorpa-E cần được uống trước 22 giờ hoặc sau 24 giờ so với thời điểm dùng thuốc hấp thu acid mật.\nCoumarin - Ezetimibe: Hoạt chất Ezetimibe có thể tương tác với Coumarin.\nAtorpa-E - Ánh Sáng Trực Tiếp: Ánh sáng trực tiếp cần tránh khi bảo quản Atorra-E.\nAtorpa-E - Viêm Mũi Họng: Viêm mũi họng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Thức Uống: Thức uống cần tránh xa tầm tay của trẻ em và thú nuôi khi bảo quản Atorpa-E.\nAtorpa-E - Viên Nén Bao Phim: Atorpa-E được bào chế dạng viên nén bao phim.\nAtorpa-E - Rối Loạn Lipid Máu Hỗn Hợp: Atorpa-E được chỉ định điều trị rối loạn lipid máu hỗn hợp.\nAtorpa-E - Uống Nhiều Rượu: Atorpa-E cần thận trọng khi dùng ở bệnh nhân uống nhiều rượu.\nAnti-HCV - Atorpa-E: Khi sử dụng Atorpa-E cùng với thuốc chống-HCV, liều dùng Atorpa-E cần được điều chỉnh.&lt;SEP&gt;Atorpa-E chống chỉ định ở bệnh nhân đang dùng thuốc anti-HCV chứa elbasvir hoặc grazoprevir.\nAtorpa-E - Tiền Sử Bệnh Cơ Di Truyền: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh cơ di truyền.\nAtorpa-E - Elbasvir: Khi sử dụng Atorpa-E cùng với elbasvir, liều dùng Atorpa-E cần được điều chỉnh.\nAtorpa-E - Grazoprevir: Khi sử dụng Atorpa-E cùng với grazoprevir, liều dùng Atorpa-E cần được điều chỉnh.\nAtorpa-E - Bệnh Gan Đang Hoạt Động: Atorpa-E được chống chỉ định ở bệnh nhân mắc bệnh gan đang hoạt động.\nAtorpa-E - Tăng Men Gan Transaminase Huyết Thanh Kéo Dài Không Rõ Nguyên Nhân: Atorpa-E được chống chỉ định ở bệnh nhân có tăng men gan transaminase huyết thanh kéo dài không rõ nguyên nhân.\nAtorpa-E - Tiền Sử Bệnh Gan: Atorpa-E cần thận trọng khi dùng ở bệnh nhân có tiền sử bệnh gan.\nAtorpa-E - Tăng Cholesterol Máu Đồng Hợp Tử Gia Đình (HoFH): Atorpa-E điều trị tăng cholesterol máu đồng hợp tử gia đình (HoFH).&lt;SEP&gt;Atorpa-E được chỉ định như một liệu pháp hỗ trợ trong điều trị tăng cholesterol máu đồng hợp tử gia đình.\nAtorpa-E - Giảm Tiểu Паuл: Giảm tiểu cầu là tác dụng phụ của Atorpa-E.\nAtorpa-E - Gặp Ác Mộng: Gặp ác mộng là tác dụng phụ của Atorpa-E.\nAtorpa-E - Giảm Xúc Cảm: Giảm xúc cảm là tác dụng phụ của Atorpa-E.\nAtorpa-E - Đau Thần Kinh Ngoại Переводческая_ошибка: Đau thần kinh ngoại vi là tác dụng phụ của Atorpa-E.\nAtorpa-E - Hội Chứng Tiêu Cơ Vân: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có yếu tố ảnh hưởng đến hội chứng tiêu cơ vân.\nAtorpa-E - Tiền Sử Bệnh Cơ Do Dùng Statin Hoặc Fibrat: Atorpa-E cần thận trọng khi sử dụng ở bệnh nhân có tiền sử bệnh cơ do dùng statin hoặc fibrat.\nAtorpa-E - Toa: Toa là hướng dẫn sử dụng thuốc Atorpa-E từ bác sĩ.\nAtorpa-E - Lọc Bỏ LDL: Atorpa-E được sử dụng kết hợp với phương pháp lọc bỏ LDL trong điều trị tăng cholesterol máu.\nAtorpa-E - Bệnh Nhân Có Bệnh Mạch Vành: Atorpa-E được chỉ định điều trị tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành.\nAtorpa-E - Mạch Vành (CHD): Atorpa-E điều trị mạch vành (CHD).\nAtorpa-E - Hội Chứng Mạch Andh Cấp Tính (ACS): Atorpa-E điều trị hội chứng mạch vành cấp tính (ACS).\nCyclosporin - Ezetimibe: Hoạt chất Ezetimibe có thể tương tác với Cyclosporin.\nGãy Xương Cổ Chân - Người Lớn Tuổi: Người lớn tuổi có nguy cơ cao bị biến chứng sau phẫu thuật gãy xương cổ chân.\nCholestyramin - Ezetimibe: Hoạt chất Ezetimibe có thể tương tác với Cholestyramin.\nHạ Huyết Áp Tư Thế - Người Lớn Tuổi: Hạ huyết áp tư thế đặc biệt phổ biến ở nhóm người lớn tuổi.\nEzetimibe - Mỡ Máu: Ezetimibe giảm mỡ máu.\nBướu Giáp Keo - Người Lớn Tuổi: Người lớn tuổi có nguy cơ cao mắc bướu giáp keo.\nAtorhasan 20 - Cholesterol Máu: Atorhasan 20 điều chỉnh mức cholesterol máu.\nAtorhasan 20 - Biến Cố Tim Mạch: Atorhasan 20 được sử dụng để dự phòng biến cố tim mạch.\nAtorhasan 20 - Tăng Triglycerid Máu: Atorhasan 20 được sử dụng để điều trị tăng triglycerid máu.\nAtorhasan 20 - Thụ Thể LDL-Cholesterol: Atorhasan 20 tác động lên thụ thể LDL-cholesterol trên màng tế bào gan.\nBệnh Cơ - Ezetimibe: Ezetimibe có thể gây bệnh cơ khi dùng cùng Atorvastatin.\nMỡ - Người Lớn Tuổi: Mỡ thường xuất hiện ở người lớn tuổi.\nAtorhasan 20 - Tăng Cholesterol Máu Gia Đình Đồng Hợp Tử: Atorhasan 20 được sử dụng để điều trị tăng cholesterol máu gia đình đồng hợp tử.\nAtorhasan 20 - Cholesterol Máu Kém: Atorhasan 20 được sử dụng để điều trị cholesterol máu cao.\nAtorhasan 20 - Giảm LDL-Cholesterol: Atorhasan 20 có hiệu quả giảm LDL-cholesterol.\nAtorhasan 20 - Tăng Mật Độ Xương: Atorhasan 20 có tác dụng phụ tăng mật độ xương.\nAtorhasan 20 - Trứng Loạn Lipid Máu Hỗn Hợp: Atorhasan 20 được sử dụng để điều trị rối loạn lipid máu hỗn hợp.\nCholesterol Toàn Phần (TC) - Ezetimibe: Ezetimibe giúp giảm lượng cholesterol toàn phần trong máu.\nEzetimibe - Triglycerid (TG): Ezetimibe giúp giảm lượng triglycerid trong máu.\nCholesterol Xấu (LDL-C) - Ezetimibe: Ezetimibe giúp giảm lượng cholesterol xấu trong máu.\nEzetimibe - Fluindion: Hoạt chất Ezetimibe có thể tương tác với Fluindion.\nEzetimibe - Fibrat: Hoạt chất Ezetimibe có thể tương tác với fibrat.\nNgười Lớn Tuổi - Đông Trùng Hạ Thảo Ngâm Mật Ong: Người lớn tuổi sử dụng đông trùng hạ thảo ngâm mật ong.']</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Đối với bệnh nhân tăng cholesterol máu và/hoặc bệnh nhân có bệnh mạch vành, liều dùng thông thường của Atorpa-E là từ 10/10 mg đến 80/10 mg mỗi ngày. Liều dùng cụ thể sẽ được xác định dựa trên hiệu quả của các xét nghiệm và đáp ứng với liệu pháp điều trị. Liều dùng thường dùng là 10/10 mg một lần/ngày.
+### Tham chiếu:
+- [1] atorpa-e.txt</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tỉ lệ liều dùng Atorpa-E cho bệnh nhân tăng mỡ và/hoặc có bệnh mạch vành dao động từ 10/10 mg đến 80/10 mg một ngày.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8259721123204598</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4564930280551149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nên làm gì nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>['Nguy Hiểm Tính Mạng: Nguy hiểm tính mạng là hậu quả nghiêm trọng có thể xảy ra khi uống quá liều Aceclofenac STADA.\nDị Ứng: Dị Ứng là tình trạng mà cơ thể phản ứng quá mức với các tác nhân gây dị ứng, bao gồm cả các thành phần trong thuốc, môi trường tự nhiên, và dược liệu. Đây là phản ứng miễn dịch bất thường và không mong muốn đối với các chất lạ như kháng sinh và các tá dược có trong thuốc. Dị Ứng có thể xuất hiện khi sử dụng nhiều loại thuốc khác nhau, gây ra các triệu chứng như nổi mẩn ngứa, mề đay, và khó thở. Tình trạng này cũng là chống chỉ định khi sử dụng nhiều loại thuốc cụ thể, như Acemol 325 mg, Acehasan, Acetylcysteine VERTEX, Actiso Ladophar, Agifivit, Ambron Vaco, Aphaxan, Alpha Brain, Boganic, Brosafe, Carbimazol, và Casalmux. Các thuốc này chứa các thành phần như propacetamol hydrochloride, paracetamol, ambroxol, bromhexin, aspirin, adapalene, celecoxib, carbocystein, salbutamol, và các tá dược khác.\n\nDị Ứng cũng có thể xảy ra khi sử dụng các dược liệu như Bồ đề, Trường sinh thảo, Tỳ bà diệp, Xấu Hổ, và cây huyết rồng. Ngoài ra, dị ứng có thể xuất hiện khi tiếp xúc với các tác nhân gây dị ứng như phấn hoa, lông chó mèo, mạt bụi nhà, cần tây, hạt kê, và hạt sachi. Đặc biệt, dị ứng có thể xảy ra khi ăn sachi, đặc biệt đối với những người có cơ địa dị ứng. Dị Ứng cũng là phản ứng miễn dịch khi tiếp xúc với hạt sachi.\n\nTrong y học, dị ứng là một trong những dấu hiệu được tìm kiếm trong khám sức khỏe và là triệu chứng cần kiêng kỵ khi sử dụng các vị thuốc. Dị Ứng cũng được điều trị bằng các phương pháp khác nhau, bao gồm hỗn hợp hoa hương giới, hoa húng quế và lá đơn đỏ, cũng như bằng Mogrosid. Tuy nhiên, Bepanthen Balm không nên sử dụng đối với người đã từng bị dị ứng với bất kỳ thành phần nào trong sản phẩm. Người dị ứng với các cây khác thuộc họ bầu bí nên tránh dùng khổ qua rừng và cần thận trọng khi sử dụng kiều mạch.\n\nDị Ứng cũng có thể xảy ra khi sử dụng lá thúi địch và được điều trị bằng Liên kiều. Tuy nhiên, dị ứng với bất kỳ thành phần nào khác của thuốc methylprednisolone là một tình trạng không được dùng methylprednisolone. Dị Ứng cũng được điều trị bằng methylprednisolone (Depo-Medrol) trong một số trường hợp.\n\nDị Ứng cũng có thể gây sưng môi âm hộ do tiếp xúc với hóa chất gây kích ứng và cũng là phản ứng miễn dịch của cơ thể đối với các thành phần trong thuốc nhuộm. Dị Ứng cũng có thể gây viêm quanh mắt và góp phần tạo nên nếp nhăn vùng mắt. Dị Ứng là một tác dụng phụ có thể xảy ra khi tiêm chất làm đầy và cũng là một trong những nguyên nhân gây bệnh nghiến răng.\n\nDị Ứng còn được biết đến là một trong những nguyên nhân gây polyp mũi và cũng là phản ứng của cơ thể với một số thành phần hoặc hoạt chất có trong rượu ba kích. Dị Ứng với thức ăn hoặc thuốc có thể gây ra phản ứng phản vệ, và cũng là triệu chứng không mong muốn khi sử dụng rau mùi tây và rượu ba kích. Dị Ứng cũng có thể gây sốt và đổ mồ hôi. Một số trường hợp dị ứng có thể dẫn đến suy thận cấp.\n\nDị Ứng là tình trạng phản ứng miễn dịch, có thể dẫn đến các triệu chứng như sưng lưỡi gà, viêm quanh mắt, và gây ra các phản ứng nghiêm trọng như phản ứng phản vệ. Dị Ứng cũng có thể xảy ra khi sử dụng thuốc 3B Medi và Acid nalidixic hoặc các quinolon khác.\n\nDị Ứng với vinpocetin hoặc bất kỳ thành phần nào khác là chống chỉ định dùng Cavinton. Dị Ứng với các kháng sinh nhóm cephalosporin khác là chống chỉ định dùng thuốc này. Dị Ứng với Cefprozil có thể dẫn đến phản ứng quá mẫn cấp trầm trọng.\n\nDị Ứng với mycophenolate mofetil, axit mycophenolic hoặc các thành phần khác trong thuốc là lý do không sử dụng CellCept. Ceritine được sử dụng để điều trị dị ứng. Dị Ứng là phản ứng miễn dịch không mong muốn đối với bất kỳ thành phần nào có trong công thức của Chymobest. Dị Ứng với guaifenensin, ceritizin hoặc dextromethorphan là trường hợp không nên dùng Cidetuss. Dị Ứng là triệu chứng có thể xảy ra khi dùng Cimetidin. Dị Ứng với bất kỳ thành phần nào của thuốc là chống chỉ định sử dụng Claminat.\n\nDị Ứng là triệu chứng cần tránh khi sử dụng Trà Tiên và cũng là phản ứng cơ thể khi tiếp xúc với một số thành phần có trong dược liệu Trư Linh.&lt;SEP&gt;Dị ứng là phản ứng miễn dịch đối với bất kỳ thành phần nào của vị thuốc Tỳ giải.\nBất Thường: Bất thường trong lúc sử dụng cần báo cho bác sĩ hoặc chuyên gia y tế.&lt;SEP&gt;Bất thường là triệu chứng cần báo cáo cho bác sĩ khi sử dụng thuốc Aceclofenac STADA.&lt;SEP&gt;Bất thường là triệu chứng bất lợi có thể xuất hiện khi sử dụng thuốc Chymodk.\nQuan Y Tế: Quan y tế hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.\nAceclofenac Stada: Aceclofenac Stada là thuốc kháng viêm không steroid (NSAID).\nThuốc Ức Chế Men Chuyển: Thuốc ức chế men chuyển (ACE-i) là một loại thuốc có tác dụng ức chế enzym chuyển đổi angiotensin trong cơ thể, giúp thư giãn động mạch và giảm huyết áp. Thuốc này được chỉ định để điều trị tăng huyết áp và giúp hạ huyết áp. Thuốc ức chế men chuyển còn được sử dụng để điều trị suy tim, giúp giảm tử vong và tăng cường khả năng bơm máu của tim.\n\nNgoài tác dụng chính, thuốc ức chế men chuyển có thể tương tác với nhiều loại thuốc khác như Allopurinol 300 mg, Amaryl 1 mg (tăng nguy cơ hạ đường huyết), Agietoxib, và Agilosart 100 (bệnh nhân không dung nạp được khi dùng cùng với thuốc ức chế men chuyển). Thuốc này cũng có thể sử dụng cùng với Apitim và Coversyl. Tuy nhiên, khi phối hợp với Telmisartan, thuốc ức chế men chuyển có thể gây thay đổi chức năng thận.\n\nThuốc ức chế men chuyển đóng vai trò quan trọng trong việc kiểm soát huyết áp và hỗ trợ điều trị các bệnh liên quan đến tim mạch.&lt;SEP&gt;Thuốc ức chế men chuyển có tương tác với Alaxan.&lt;SEP&gt;Thuốc ức chế men chuyển là thuốc tương tác khi dùng chung với Alaxan.&lt;SEP&gt;Thuốc ức chế men chuyển là một loại thuốc điều trị tăng huyết áp, có thể gây ra dị ứng và phù mạch thần kinh.&lt;SEP&gt;Thuốc ức chế men chuyển là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Thuốc ức chế men chuyển là một trong những loại thuốc kết hợp với thuốc Concor để điều trị bệnh suy tim mãn tính ổn định.\nAceclofenac STADA: Aceclofenac STADA là thuốc chống viêm, giảm đau, cần được bảo quản đúng cách và tuân thủ hướng dẫn sử dụng.&lt;SEP&gt;Aceclofenac STADA là thuốc giảm đau và chống viêm không steroid (NSAID).\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nAceclofenac: Thuốc Aceclofenac được chỉ định để giảm đau và kháng viêm trong bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.&lt;SEP&gt;Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg, có tác dụng kháng viêm không steroid.&lt;SEP&gt;Aceclofenac là thuốc giảm đau và chống viêm không steroid (NSAID), có thể gây tác dụng phụ như tăng men gan, khó tiêu, đau bụng, buồn nôn, tiêu chảy, đầy hơi, viêm dạ dày, táo bón, nôn, loét miệng, ngứa, phát ban, viêm da, nổi mề đay, tăng urê huyết, tăng creatinin huyết, thiếu máu, phản ứng phản vệ, rối loạn thị giác, tình trạng khó thở, phân đen, phù mặt.&lt;SEP&gt;Aceclofenac là thuốc gây ra các tác dụng phụ trên hệ thần kinh, bao gồm triệu chứng như choáng váng, buồn ngủ, mệt mỏi, và rối loạn thị giác.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nAceclofenac STADA 100mg: Aceclofenac STADA 100mg là thuốc kháng viêm không steroid với đặc tính giảm đau và kháng viêm, được chỉ định để điều trị bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.\nMẫn Cảm: Mẫn Cảm là một tình trạng sức khỏe liên quan đến phản ứng bất lợi hoặc dị ứng của cơ thể với một hoặc nhiều thành phần cụ thể của thuốc. Tình trạng này có thể biểu hiện dưới dạng phản ứng dị ứng khi tiếp xúc với các thành phần cụ thể của thuốc như acyclovir, valacyclovir, hoặc các thành phần khác trong các loại thuốc như A.T Calci Plus, Acnequidt 20 ml, Actiso Ladophar, Acyclovir Stada 200 mg, và Acyclovir Stella Cream. Mẫn cảm với thuốc hoặc các thành phần của thuốc là chống chỉ định đối với việc sử dụng nhiều loại thuốc khác nhau, bao gồm Agi-Calci, Agiclovir bk 5% Agimexpharm, Altamin, và Alzole. Nếu một bệnh nhân bị mẫn cảm với bất kỳ thành phần nào của những loại thuốc này, việc sử dụng chúng sẽ không được khuyến nghị do có thể gây ra các tác dụng phụ nghiêm trọng hoặc thậm chí đe dọa tính mạng.\n\nMẫn cảm cũng được ghi nhận là tình trạng bệnh nhân bị dị ứng với bất kỳ thành phần nào của Ampicillin Brawn hoặc Ampelop. Tình trạng này cũng xuất hiện khi bệnh nhân bị dị ứng hoặc không dung nạp với bất kỳ thành phần nào của thuốc hoặc với các anthraquinon glycosid khác, tạo nên một danh sách dài các thuốc chống chỉ định sử dụng trong trường hợp này, bao gồm Arthrorein Pharmanel, Asakoya Mediplantex, Bisoloc, và Bisoprolol. Việc kiểm tra kỹ lưỡng về mẫn cảm trước khi bắt đầu sử dụng bất kỳ loại thuốc nào là rất quan trọng để tránh các tác dụng phụ nghiêm trọng hoặc nguy hiểm đến tính mạng.\n\nMẫn cảm cũng được ghi nhận là phản ứng dị ứng với một số thành phần của thuốc Barudon và mẫn cảm với tenoxicam hoặc bất kỳ thành phần nào của Bart là đối tượng chống chỉ định sử dụng thuốc này. Mẫn cảm với peridopril hoặc các thuốc ức chế men chuyển khác là chống chỉ định sử dụng Beatil. Mẫn cảm với hoạt chất hoặc bất cứ thành phần nào của thuốc là triệu chứng cần được giám sát đặc biệt khi sử dụng Belara. Mẫn cảm cũng có thể xảy ra khi sử dụng Betadine Gargle &amp; Mouth Wash. Cuối cùng, mẫn cảm với cao khô lá Ginkgo biloba hoặc bất kỳ thành phần nào của thuốc Bilomag là chống chỉ định. Trong tất cả các trường hợp, việc sử dụng thuốc khi có mẫn cảm với bất kỳ thành phần nào của thuốc là chống chỉ định và có thể dẫn đến các rủi ro sức khỏe nghiêm trọng, bao gồm cả việc sử dụng thuốc amoxicillin + acid clavulanid trong thời kỳ cho con bú, có thể dẫn đến các rủi ro sức khỏe cho cả mẹ và trẻ sơ sinh.\n\nNgoài ra, mẫn cảm còn được ghi nhận là phản ứng không mong muốn khi dùng cỏ mật, tình trạng dị ứng hoặc phản ứng bất lợi với một số thành phần trong kem, tình trạng dị ứng kéo dài sau điều trị bằng Crotamiton, tình trạng không nên sử dụng củ nén, chống chỉ định khi sử dụng trihexyphenidyl, và tình trạng mẫn cảm với bất kỳ thành phần nào trong Danospan hay Davita Bone Sugar Free đều là chống chỉ định.\n\nMẫn cảm cũng được ghi nhận là tình trạng dị ứng hoặc phản ứng dị ứng với một số thành phần của thuốc Betmiga 50 mg, mẫn cảm với thuốc hoặc các chất ức chế ACE như Captopril, mẫn cảm với carbimazol hoặc các dẫn chất thioimidazol như thiamazol, mẫn cảm với cefpodoxim, mẫn cảm với penicillin, và mẫn cảm với Clonazepam hoặc các chất thuộc nhóm benzodiazepin.\n\nTóm lại, mẫn cảm là một tình trạng sức khỏe nghiêm trọng cần được phát hiện và quản lý cẩn thận để ngăn ngừa các tác dụng phụ nguy hiểm. Tình trạng này có thể xảy ra khi sử dụng thuốc và có thể là dấu hiệu của phản ứng miễn dịch, dị ứng hoặc không dung nạp với pregabalin hoặc các thành phần khác của thuốc.&lt;SEP&gt;Mẫn cảm là tình trạng dị ứng hoặc nhạy cảm với một số thành phần trong thuốc.&lt;SEP&gt;Mẫn cảm là một triệu chứng phản ứng dị ứng với axit salicylic.&lt;SEP&gt;Mẫn cảm với bất kỳ thành phần nào của thuốc là chống chỉ định.&lt;SEP&gt;Người có trạng thái mẫn cảm với bất kỳ dược chất nào trong tinh dầu hương thảo cần tham khảo ý kiến bác sĩ trước khi sử dụng.&lt;SEP&gt;Mẫn cảm là tình trạng dị ứng hoặc nhạy cảm với các dược chất trong tinh dầu hương thảo.&lt;SEP&gt;Mẫn cảm là phản ứng cơ thể khi tiếp xúc với một số thành phần có trong dược liệu Trư linh.\nAceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac, được chỉ định để giảm đau và kháng viêm trong bệnh viêm xương khớp, viêm khớp dạng thấp và viêm đốt sống dính khớp.\nSymptom: Mẫn cảm là phản ứng dị ứng với một số thuốc.\nSuy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nDị Ứng Thuốc: Phản ứng dị ứng thuốc là tác dụng phụ ít gặp khi sử dụng Alzental.&lt;SEP&gt;Dị ứng thuốc là biểu hiện cần phải ngừng dùng thuốc và thông báo cho bác sĩ.\nSuy Tiết Dịch: Suy tiết dịch là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tiêu chảy là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nDị Ứng - Quan Y Tế: Quan y tế hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.\nAceclofenac - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nDị Ứng - Thuốc Ức Chế Men Chuyển: Thuốc ức chế men chuyển có thể gây dị ứng.\nAceclofenac - Táo Bón: Táo bón là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nDị Ứng - Vị Thuốc: Dị ứng với bất kỳ thành phần nào của vị thuốc là triệu chứng cần tránh.&lt;SEP&gt;Vị thuốc có thể gây dị ứng với một số người.\nAceclofenac - Suy Thận: Không nên sử dụng Aceclofenac trên các đối tượng bị suy thận mức độ vừa đến nặng.&lt;SEP&gt;Suy thận là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nDị Ứng - Thuốc: Nếu xuất hiện dị ứng khi dùng thuốc, bạn hãy báo ngay cho bác sĩ.&lt;SEP&gt;Dị ứng là triệu chứng miễn dịch ít gặp khi sử dụng thuốc.&lt;SEP&gt;Dị ứng với thuốc có thể gây ra mề đay.\nAceclofenac - Đau Bụng: Đau bụng là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nMẫn Cảm - Symptom: Mẫn cảm là phản ứng dị ứng với một số thuốc.\nAceclofenac - Mệt Mỏi: Mệt mỏi là tác dụng phụ của Aceclofenac.\nDị Ứng Thuốc - Khó Nuốt: Khó nuốt là triệu chứng của dị ứng thuốc.\nAceclofenac Stada - Tăng Huyết Áp: Aceclofenac Stada có thể gây tăng huyết áp.\nDị Ứng - Thuốc Chống Dị Ứng: Thuốc chống dị ứng được sử dụng để điều trị dị ứng.\nAceclofenac - Nôn: Nôn là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nAceclofenac - Suy Tim: Suy tim là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nChất Gây Dị Ứng - Dấu Hiệu Dị Ứng: Dấu hiệu dị ứng cần được chú ý bởi người lớn.\nAceclofenac - Ngứa: Ngứa là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nDị Ứng Thuốc - Nổi Mề Đay: Nổi mề đay là triệu chứng của dị ứng thuốc.\nAceclofenac - Phụ Nữ Có Thai: Aceclofenac chống chỉ định trong thai kỳ trừ khi lợi ích điều trị cho mẹ vượt trội nguy cơ gây hại cho thai nhi.\nAceclofenac - Thiếu Máu: Thiếu máu là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Thiếu máu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac Stada - Mệt Mỏi: Aceclofenac Stada có thể gây mệt mỏi.\nAceclofenac - Suy Gan: Suy gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac Stada - Suy Tim: Aceclofenac Stada có thể gây suy tim.\nAceclofenac - Hạ Huyết Áp: Hạ huyết áp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nhức Đầu: Nhức đầu là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Hô Hấp: Suy hô hấp là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Co Giật: Co giật là triệu chứng hiếm gặp khi quá liều Aceclofenac.\nAceclofenac - Phụ Nữ Cho Con Bú: Aceclofenac không nên dùng trong giai đoạn đang cho con bú.\nAceclofenac - Đầy Hơi: Đầy hơi là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Khớp Dạng Thấp: Aceclofenac được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac - Khó Tiêu: Khó tiêu là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Buồn Ngủ: Buồn ngủ là tác dụng phụ của Aceclofenac.\nAceclofenac - Phát Ban: Phát ban là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac STADA - Quá Liều: Quá liều Aceclofenac STADA có thể gây nguy hiểm tính mạng.\nAceclofenac - Viêm Da: Viêm da là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Suy Thận Cấp: Suy thận cấp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Ù Tai: Ù tai là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Nổi Mề Đay: Nổi mề đay là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac STADA - Giảm Đau: Aceclofenac STADA được chỉ định để giảm đau.\nAceclofenac - Viêm Dạ Dày: Viêm dạ dày là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Hôn Mê: Hôn mê là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Người Cao Tuổi: Khả năng phân bố, chuyển hóa, hấp thu và thải trừ của Aceclofenac không thay đổi ở bệnh nhân cao tuổi, do đó không cần phải thay đổi liều hoặc tần suất sử dụng.\nAceclofenac - Thuốc Lợi Tiểu: Thuốc lợi tiểu có thể tương tác với Aceclofenac.\nAceclofenac STADA 100mg - Viêm Khớp Dạng Thấp: Aceclofenac STADA 100mg được chỉ định để điều trị bệnh viêm khớp dạng thấp.\nAceclofenac Stada - Buồn Ngủ: Aceclofenac Stada có thể gây buồn ngủ.\nAceclofenac - Phản Ứng Phản Vệ: Phản ứng phản vệ là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Hệ Thần Kinh: Aceclofenac gây ra các tác dụng phụ trên hệ thần kinh.\nAceclofenac - Rửa Dạ Dày: Rửa dạ dày là biện pháp dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac STADA - Trẻ Em: Aceclofenac STADA cần được bảo quản tránh xa tầm tay của trẻ em.\nAceclofenac - Corticosteroids: Corticosteroids có thể tương tác với Aceclofenac.\nAceclofenac - Rối Loạn Thị Giác: Rối loạn thị giác là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Rối loạn thị giác là tác dụng phụ của Aceclofenac.\nAceclofenac - Viêm Xương Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm xương khớp.\nAceclofenac - Prostaglandin: Aceclofenac ức chế tổng hợp prostaglandin.\nAceclofenac - Loét Miệng: Loét miệng là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Chống Đông: Thuốc chống đông có thể tương tác với Aceclofenac.\nAceclofenac - Nôn Ra Máu: Nôn ra máu là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Tăng Men Gan: Tăng men gan là tác dụng phụ thường gặp khi sử dụng Aceclofenac.\nAceclofenac - Choáng Váng: Choáng váng là tác dụng phụ của Aceclofenac.\nBác Sĩ - Bất Thường: Người dùng cần báo bất thường cho bác sĩ.&lt;SEP&gt;Bác sĩ sẽ đưa ra hướng xử lý phù hợp và kịp thời nhất đối với bất thường.\nAceclofenac - Kích Động: Kích động là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Ngất: Ngất là triệu chứng khi quá liều Aceclofenac.\nAceclofenac STADA - Chống Viêm: Aceclofenac STADA được chỉ định để chống viêm.\nAceclofenac - Xuất Huyết Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng nghi ngờ có xuất huyết tiêu hóa.&lt;SEP&gt;Xuất huyết tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.&lt;SEP&gt;Xuất huyết tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Methotrexat: Methotrexat có thể tương tác với Aceclofenac.\nAceclofenac - Suy Giảm Chức Năng Gan: Liều dùng khởi đầu được đề nghị là 100 mg/ngày (1 viên/ngày) cho những bệnh nhân suy gan.\nAceclofenac - Tổn Thương Gan: Tổn thương gan là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Glycosid Tim: Glycosid tim có thể tương tác với Aceclofenac.\nAceclofenac - Tacrolimus: Tacrolimus có thể tương tác với Aceclofenac.\nAceclofenac - Than Hoạt Tính: Than hoạt tính được dùng để xử lý khi quá liều Aceclofenac.\nAceclofenac - Phù Mặt: Phù mặt là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Đau Vùng Thượng Vị: Đau vùng thượng vị là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Phân Đen: Phân đen là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Ciclosporin: Ciclosporin có thể tương tác với Aceclofenac.\nAceclofenac - Zidovudin: Zidovudin có thể tương tác với Aceclofenac.\nAceclofenac - Lithi: Lithi có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Điều Trị Tăng Huyết Áp: Thuốc điều trị tăng huyết áp có thể tương tác với Aceclofenac.\nAceclofenac - Buồn Nôn, Nôn: Buồn nôn và nôn là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Aceclofenac STADA 100mg: Aceclofenac là hoạt chất chính trong Aceclofenac STADA 100mg.\nAceclofenac - Cyclooxygenase: Aceclofenac ức chế cyclooxygenase.\nAceclofenac - Kích Ứng Tiêu Hóa: Kích ứng tiêu hóa là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Loét Tiêu Hóa: Không nên sử dụng Aceclofenac trên các đối tượng đã từng bị loét tiêu hóa tiến triển trước đó.\nAceclofenac - Tăng Creatinin Huyết: Tăng creatinin huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Viêm Đốt Sống Dính Khớp: Aceclofenac được chỉ định để điều trị bệnh viêm đốt sống dính khớp.\nAceclofenac - Suy Thai: Suy thai là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiêu Hóa: Suy tiêu hóa là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nAceclofenac - Mifepriston: Mifepriston có thể tương tác với Aceclofenac.\nAceclofenac - Kháng Sinh Nhóm Quinolon: Kháng sinh nhóm quinolon có thể tương tác với Aceclofenac.\nAceclofenac - Thủng Loét Đường Tiêu Hóa: Thủng loét đường tiêu hóa là tác dụng phụ cần lưu ý khi sử dụng Aceclofenac.\nAceclofenac - Loxoprofen: Loxoprofen có tác dụng giảm đau và kháng viêm tương tự như Aceclofenac.\nAceclofenac - Bị Mất Phương Hướng: Bị mất phương hướng là triệu chứng khi quá liều Aceclofenac.\nAceclofenac - Suy Não: Suy não là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Viêm: Suy viêm là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Khớp: Suy khớp là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Mi: Suy mi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Phổi: Suy phổi là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Thần Kinh: Suy thần kinh là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Chất: Suy tiết chất là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Niệu: Suy tiết niệu là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Dịch: Suy tiết dịch là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Protein: Suy tiết protein là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone: Suy tiết hormone là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid: Suy tiết hormone tiroid là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B12: Suy tiết hormone tiroid B12 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B13: Suy tiết hormone tiroid B13 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B14: Suy tiết hormone tiroid B14 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B15: Suy tiết hormone tiroid B15 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B16: Suy tiết hormone tiroid B16 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B17: Suy tiết hormone tiroid B17 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B18: Suy tiết hormone tiroid B18 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B19: Suy tiết hormone tiroid B19 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Tiết Hormone Tiroid B20: Suy tiết hormone tiroid B20 là tình trạng có thể xảy ra khi quá liều Aceclofenac.\nAceclofenac - Suy Gàn: Liều dùng Aceclofenac cần được giảm cho những bệnh nhân suy gan.\nAceclofenac - Aceclofenac STADA 100 mg: Aceclofenac STADA 100 mg là dạng viên nén bao phim của Aceclofenac.\nAceclofenac - Tình Trạng Khó Thở: Tình trạng khó thở là tác dụng phụ hiếm gặp khi sử dụng Aceclofenac.\nAceclofenac - Thuốc Giảm Đau Khác: Thuốc giảm đau khác bao gồm các thuốc ức chế chọn lọc cyclooxygenase-2 có thể tương tác với Aceclofenac.\nAceclofenac - Tác Nhân Kháng Tiểu Phần: Tác nhân kháng tiểu phần có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Ức Chế Chọn Lọc Thu Hồi Serotonin (SSRI): Thuốc ức chế chọn lọc thu hồi serotonin (SSRI) có thể tương tác với Aceclofenac.\nAceclofenac - Nhóm Thuốc Trị Đái Tháo Đường: Nhóm thuốc trị đái tháo đường có thể tương tác với Aceclofenac.\nAceclofenac - Thuốc Kháng Viêm Không Steroid (NSAID) Khác: Thuốc kháng viêm không steroid (NSAID) khác có thể tương tác với Aceclofenac, tạo ra nguy cơ xuất huyết tiêu hóa.\nAceclofenac Stada - Người Cao Tuổi: Aceclofenac Stada có thể gây tác dụng phụ trên người cao tuổi.\nAceclofenac Stada - Phù Nề: Aceclofenac Stada có thể gây phù nề.\nAceclofenac Stada - Rối Loạn Thị Giác: Aceclofenac Stada có thể gây rối loạn thị giác.\nAceclofenac STADA - Ánh Sáng: Aceclofenac STADA cần được bảo quản tránh tiếp xúc trực tiếp với ánh sáng.\nAceclofenac Stada - Nôn Ra Máu: Aceclofenac Stada có thể gây nôn ra máu.\nAceclofenac Stada - Choáng Váng: Aceclofenac Stada có thể gây choáng váng.\nBất Thường - Chymodk: Khi xuất hiện bất kỳ triệu chứng bất thường nào, cần gọi ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.\nAceclofenac Stada - Xuất Huyết Tiêu Hóa: Aceclofenac Stada có thể gây xuất huyết tiêu hóa.\nAceclofenac STADA 100mg - Viêm Xương Khớp: Aceclofenac STADA 100mg được chỉ định để điều trị bệnh viêm xương khớp.\nAcetylcysteine 200mg Stada - Phản Ức: Acetylcysteine 200mg Stada có thể gây ra phản ứng dị ứng nghiêm trọng.\nAceclofenac Stada - Phân Đen: Aceclofenac Stada có thể gây phân đen.\nAceclofenac STADA - Thú Cưng: Aceclofenac STADA cần được bảo quản tránh xa tầm tay của thú cưng.\nAceclofenac Stada - Khả Năng Sinh Sản: Aceclofenac Stada có thể suy giảm khả năng sinh sản.\nAceclofenac Stada - Thuốc NSAID: Aceclofenac Stada thuộc nhóm thuốc NSAID.\nAceclofenac Stada - Nguy Cơ Xuất Huyết Tiêu Hóa: Aceclofenac Stada có nguy cơ gây xuất huyết tiêu hóa.\nAceclofenac Stada - Thủng Loét Đường Tiêu Hóa: Aceclofenac Stada có thể gây thủng loét đường</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nếu bạn nghi ngờ bị dị ứng với thuốc Aceclofenac STADA, bạn cần báo ngay cho bác sĩ. Dị ứng là một tình trạng sức khỏe nghiêm trọng cần được phát hiện và quản lý cẩn thận để ngăn ngừa các tác dụng phụ nguy hiểm. Dị ứng với bất kỳ thành phần nào của thuốc là chống chỉ định và có thể dẫn đến các rủi ro sức khỏe nghiêm trọng.
+### Xử lý khi gặp dị ứng với thuốc Aceclofenac STADA
+- **Thông báo cho bác sĩ:** Nếu xuất hiện dị ứng khi dùng thuốc, bạn hãy báo ngay cho bác sĩ.
+- **Hướng dẫn từ quan y tế:** Quan y tế sẽ hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.
+### Triệu chứng dị ứng
+Dị ứng có thể biểu hiện dưới dạng các triệu chứng như:
+- Nổi mề đay.
+- Khó thở.
+- Ngứa.
+- Phát ban.
+- Khó nuốt.
+### Lời khuyên
+- **Báo cáo ngay:** Nếu bạn gặp bất kỳ triệu chứng dị ứng nào, hãy báo cáo ngay cho bác sĩ hoặc dược sĩ.
+- **Tránh sử dụng tiếp:** Tránh tiếp tục sử dụng thuốc Aceclofenac STADA nếu bạn nghi ngờ bị dị ứng.
+### Tham khảo
+- **Quan y tế:** Hướng dẫn về việc xử lý các trường hợp dị ứng xảy ra.
+### Tham khảo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nếu nghi ngờ bị dị ứng với thuốc Aceclofenac STADA, hãy ngừng dùng thuốc và đến gặp bác sĩ để được tư vấn và điều trị kịp thời.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8637242039459098</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9450977176281441</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>['Thuốc Nhẹ: Thuốc nhẹ là loại thuốc cần tránh uống ngay sau khi dùng Barudon.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nGiảm Vị Giác: Giảm vị giác là tác dụng phụ có thể xảy ra khi sử dụng quá liều Barudon.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nTác Dụng Phản Ứng: Tác dụng phản ứng không mong muốn cần được dừng sử dụng và đến cơ sở y tế.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nLoét Dạ Dày- Tá Tràng: Loét dạ dày- tá tràng là tình trạng bệnh liên quan đến việc sử dụng Barudon để giảm đau.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nKhó Tiêu Axit: Khó tiêu axit là triệu chứng liên quan đến việc sử dụng Barudon để giảm đau.&lt;SEP&gt;Khó tiêu axit là triệu chứng được điều trị bằng các thuốc kháng axit.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nNgừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.&lt;SEP&gt;Ngừng dùng thuốc là việc dừng việc sử dụng thuốc khi gặp các dấu hiệu không mong muốn.&lt;SEP&gt;Ngừng dùng thuốc Amiodarone khi gặp các triệu chứng quá liều.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nBan Đỏ, Phù Mặt, Khó Thở: Ban đỏ, phù mặt, khó thở là dấu hiệu bất thường cần ngừng thuốc và liên hệ bác sĩ.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nTriệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nTư Vấn Hỗ Trợ: Bệnh nhân cần liên hệ bác sĩ để được tư vấn hỗ trợ khi gặp tác dụng phụ của thuốc.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTiêu Chảy Do Hàn: Tiêu chảy do hàn là tình trạng mà Thuốc Bar không nên được sử dụng.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nGiải Đáp: Giải đáp là phương pháp trả lời và giải thích cho thắc mắc của người dùng thuốc.\nNgười Dùng Thuốc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nAmiodarone - Ngừng Dùng Thuốc: Khi gặp các triệu chứng quá liều, bạn nên ngừng dùng thuốc Amiodarone và lập tức đến cơ sở y tế gần nhất.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nPregabalin - Triệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nAmpicillin Mekophar - Ngừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nBarudon - Thuốc Nhẹ: Người dùng Barudon không nên uống thuốc nhẹ ngay sau khi dùng thuốc.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nBarudon - Giảm Vị Giác: Barudon có thể gây giảm vị giác khi sử dụng quá liều.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nBarudon - Loét Dạ Dày- Tá Tràng: Barudon được sử dụng để giảm đau nhanh trong các trường hợp liên quan đến loét dạ dày- tá tràng.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nBarudon - Khó Tiêu Axit: Barudon được sử dụng để điều trị khó tiêu axit.\nBác Sĩ - Tác Dụng Phụ: Bác sĩ cần thông báo nếu có tác dụng phụ khi dùng thuốc.\nBệnh Nhân - Tư Vấn Hỗ Trợ: Bệnh nhân cần liên hệ bác sĩ để được tư vấn hỗ trợ khi gặp tác dụng phụ của thuốc.\nGiải Đáp - Người Dùng Thuốc: Giải đáp cung cấp thông tin phản hồi cho người dùng thuốc.\nAzithromycin DHG - Tác Dụng Phản Ứng: Ngừng sử dụng Azithromycin DHG khi có tác dụng phản ứng không mong muốn.\nAcritel - Tác Dụng Phụ: Thuốc Acritel có hướng dẫn sử dụng cụ thể về cách xử lý tác dụng phụ.\nBan Đỏ, Phù Mặt, Khó Thở - Ciprofloxacine: Ban đỏ, phù mặt, khó thở là dấu hiệu bất thường cần ngừng thuốc và liên hệ bác sĩ.\nKháng Sinh Phổ Rộng - Tác Dụng Phụ: Sử dụng kháng sinh có liên quan đến nhiều tác dụng phụ.\nThuốc Bar - Tiêu Chảy Do Hàn: Tiêu chảy do hàn là tình trạng mà Thuốc Bar không nên được sử dụng.\nLiệt Kê - Ngừng Dùng Thuốc: Khi gặp các dấu hiệu liệt kê, cần ngừng dùng thuốc.\nLên Cơ Sở Y Tế - Ngừng Dùng Thuốc: Sau khi ngừng dùng thuốc, cần lên cơ sở y tế để được xử lý kịp thời.']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Khi sử dụng Barudon, nếu người dùng gặp phải bất kỳ phản ứng phụ nào, họ cần liên hệ với cơ sở y tế để được thăm khám cụ thể. Điều này giúp đảm bảo rằng bất kỳ tác dụng phụ nào cũng được đánh giá và xử lý kịp thời. 
+### Tham chiếu
+- [1] barudon.txt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trong quá trình sử dụng Barudon, nếu có bất kỳ phản ứng phụ nào thì người dùng cần liên hệ với cơ sở y tế để được thăm khám cụ thể.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7832529503691984</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8208132375672996</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone sẽ gây ra tác hại gì?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>['Mẫn Cảm Với Spironolactone: Mẫn cảm với spironolactone là tình trạng dị ứng với thành phần chính của Aldactone, chống chỉ định sử dụng Aldactone.\nCây Thuốc: Nghiên cứu lâm sàng cần thiết để phát huy tiềm năng của cây thuốc.\nSpironolactone (Aldactone): Spironolactone (Aldactone) là thuốc lợi tiểu có thể gây bất lực.&lt;SEP&gt;Spironolactone (Aldactone) là thuốc kháng androgen ngăn chặn tác động của hormone androgen trên da.\nĐộc Tính: Độc Tính là thuật ngữ mô tả nhiều tình trạng khác nhau liên quan đến tác dụng độc hại của các chất hoặc dược liệu. Trong y học và sinh học, độc tính thường được sử dụng để chỉ các triệu chứng có thể xảy ra khi sử dụng một số loại thuốc như Methotrexate, Sulphonylurea, Phenytoin, hoặc Acid Valproic cùng với Aspirin. Ngoài ra, độc tính cũng có thể xảy ra do việc tiêu thụ biển súc, một loài động vật biển, làm thức ăn cho động vật như ngựa, cừu hoặc chim bồ câu, gây ra rối loạn tiêu hóa. Điều này cho thấy rằng các loại thực phẩm và dược liệu khác nhau có thể mang lại tác dụng độc hại đối với cơ thể.\n\nTrong nghiên cứu khoa học, độc tính cũng được đề cập đến trong quá trình nghiên cứu về tác dụng độc hại của chiết xuất lá xương khỉ trên súc vật thí nghiệm. Một số loại cây như bồ bồ không có độc tính, vì đã thử nghiệm với liều lượng gấp 20 lần liều có tác dụng mà súc vật vẫn sống an toàn. Độc tính còn được sử dụng để mô tả tình trạng bị ảnh hưởng bởi chất độc, đây là một tình trạng phổ biến mà mọi người có thể gặp phải khi tiếp xúc với các chất độc hại. Chẳng hạn, dược liệu từ Chè dây có thể gây ra độc tính cấp tính, tức là gây ra tác dụng độc hại nhanh chóng. Cuối cùng, độc tính cũng được đề cập trong Nhựa Cóc, một loại nhựa tự nhiên, nơi mà độc tính có thể gây ra hậu quả nghiêm trọng, thậm chí có thể giết chết 4-5 người trưởng thành khỏe mạnh. Điều này nhấn mạnh sự cần thiết phải nghiên cứu kỹ lưỡng về độc tính của các chất tự nhiên và dược liệu để đảm bảo an toàn sức khỏe cho con người.\n\nĐộc tính cũng được đề cập trong nhiều trường hợp cụ thể khác. Ví dụ, độc tính từ dừa cạn, chất dầu trong hạt hoa đậu biếc, Hoàng nàn, Kê huyết đằng, Keo giậu, và La bạc tử đều có thể gây ra tác dụng độc hại. Đặc biệt, độc tính từ rễ và quả cây hương bài có thể gây tử vong nếu ăn nhầm. Những tác dụng độc hại này có thể xuất hiện khi tiêm hoặc uống với liều lượng cao. Do đó, việc giảm độc tính mạnh của Hoàng nàn trước khi sử dụng là rất quan trọng để đảm bảo an toàn cho người dùng.\n\nĐộc Tính còn được sử dụng để mô tả tác dụng phụ nghiêm trọng từ việc sử dụng một số dược liệu và thực phẩm. Lược vàng có thể gây ra tác dụng phụ khi sử dụng lâu dài hoặc ở liều cao. Mã tiền cũng có thể gây ra tác dụng phụ nghiêm trọng. Mướp sát có độc tính gây hại. Polysaccharides từ nấm có thể gây độc hại đối với gan, thận, tim, tuyến ức, và lá lách của chuột. Hạt Nhục đậu khấu có độc tính không chắc chắn, mặc dù các báo cáo trường hợp cho thấy rằng nếu uống đủ liều, độc tính cấp tính có thể xảy ra. Phụ tử cũng có độc tính đối với cơ thể con người. Sâu ban miêu có độc tính nguy hiểm gây ra tác hại lớn.\n\nTóm lại, Độc Tính là một khái niệm rộng lớn, bao gồm nhiều dạng tác dụng độc hại khác nhau từ các chất, thuốc, thực phẩm, và cả tự nhiên, đòi hỏi sự hiểu biết sâu sắc và nghiên cứu kỹ lưỡng để xác định và phòng ngừa các tác động độc hại.&lt;SEP&gt;Độc tính là yếu tố nguy hiểm có trong cây thuốc.\nThuốc Chặn Aldosterone: Thuốc chặn aldosterone là loại thuốc có thể dẫn đến tăng kali huyết khi sử dụng cùng spironolactone.\nHút Thuốc: Hút thuốc là hành vi có nhiều tác hại nghiêm trọng đến sức khỏe, bao gồm cả tác động đến hệ thống tim mạch, da, gan, và khả năng đáp ứng với các loại thuốc khác nhau. Đầu tiên, hút thuốc là yếu tố làm tăng nguy cơ mắc bệnh mạch máu ngoại biên, gây ra bệnh cước và tăng tốc độ xơ cứng động mạch. Nó cũng là yếu tố nguy cơ đối với ung thư thanh quản hầu (TNB) và có thể đóng vai trò gây ung thư TNB. Hút thuốc còn làm hỏng mạch máu, tăng nguy cơ mắc bệnh tim mạch và làm trầm trọng thêm hiệu ứng lạnh do lưu lượng máu giảm đến bàn tay và bàn chân. Ngoài ra, hút thuốc có thể làm tăng axit dạ dày và kích hoạt cơn co giật, gây thêm sự phức tạp trong việc quản lý các triệu chứng và bệnh lý liên quan đến hút thuốc.\n\nHút thuốc gây tổn hại cho da bằng cách làm hỏng collagen và elastin, thu hẹp các mạch máu, giảm cung cấp chất dinh dưỡng và oxy cho da. Điều này không chỉ làm xấu đi tình trạng của da mà còn góp phần vào việc làm suy yếu cấu trúc da. Hút thuốc lâu dài có thể làm phá hủy các động mạch, tạo ra các mảng xơ vữa do tích tụ cholesterol, dẫn đến tắc nghẽn động mạch vành, đây là một trong những nguyên nhân chính gây tử vong từ bệnh tim mạch.\n\nNgoài ra, hút thuốc còn gây tăng nguy cơ nhiễm trùng đường hô hấp trên, gây nấm thanh quản, góp phần tạo nên các nếp nhăn tĩnh và là yếu tố nguy cơ chính gây ra phình động mạch chủ. Hút thuốc cũng là yếu tố gây hại cho gan, được ngăn chặn bởi Cosele, và có thể ảnh hưởng đến sự tiến triển của bệnh u nhú thanh quản.\n\nHút thuốc là yếu tố nguy cơ chính gây ung thư phổi và ung thư thận. Nó cũng là nguyên nhân phổ biến của viêm phế quản mãn tính và khí phế thũng. Hút thuốc là một trong những yếu tố nguy cơ làm tăng khả năng mắc rối loạn nhận thức thần kinh và gây suy giảm nhận thức. Thói quen hút thuốc ở bà mẹ, bao gồm cả hút thuốc chủ động và thụ động, là hình thức lạm dụng chất kích thích và có thể gây ra tăng nguy cơ mắc hội chứng tăng trưởng intrauterine giảm (IUGR).&lt;SEP&gt;Hút thuốc có thể gây thiếu máu do thiếu vitamin C.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ liên quan đến xơ vữa động mạch.&lt;SEP&gt;Hút thuốc là yếu tố cần tránh khi sử dụng Aspilets EC.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ biến chứng tim mạch.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ làm tăng khả năng phát triển ung thư cổ tử cung.\nAldactone: Aldactone là thuốc chứa hoạt chất spironolactone, thuộc nhóm lợi tiểu, được chỉ định trong các trường hợp suy tim sung huyết, tăng huyết áp vô căn, kiểm soát chứng rậm lông, phối hợp với thuốc lợi tiểu gây giảm Kali/Magie máu, điều trị ngắn hạn chứng tăng aldosterone nguyên phát trước phẫu thuật, và các bệnh có thể gây tăng aldosterone thứ phát như xơ gan kết hợp với phù/cổ trướng, hội chứng thận hư và các trạng thái phù khác.&lt;SEP&gt;Aldactone (spironolactone) là thuốc được sử dụng để điều trị các tình trạng như suy tim, xơ gan, hội chứng thận hư, giảm kali/magie huyết, và tăng aldosterone nguyên phát.&lt;SEP&gt;Thuốc Aldactone được sử dụng để điều trị tăng huyết áp và một số tình trạng y tế khác, có thể tương tác với các thuốc khác như lợi tiểu và digoxin.&lt;SEP&gt;Aldactone là thuốc chứa hoạt chất spironolactone, thuộc nhóm lợi tiểu, được chỉ định để kiểm soát huyết áp hoặc hỗ trợ trong điều trị suy tim.\nRối Loạn Nhận Thức Thần Kinh: Rối loạn nhận thức thần kinh là tình trạng suy giảm khả năng nhận biết và xử lý thông tin.&lt;SEP&gt;Rối loạn nhận thức thần kinh là tình trạng suy giảm khả năng nhận thức do nguyên nhân thần kinh.&lt;SEP&gt;Rối loạn nhận thức thần kinh là bệnh không có thuốc hoặc phương pháp điều trị được cấp phép.\nRối Loạn Tiêu Hóa, Buồn Nôn: Rối loạn tiêu hóa, buồn nôn là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nSpironolactone: Spironolactone, còn được biết đến với tên thương mại Aldactone, là một loại thuốc đối kháng thụ thể mineralocorticoid được sử dụng rộng rãi trong y học. Nó chủ yếu được sử dụng để điều trị bệnh cường aldosterone và các tình trạng liên quan đến suy thận, bao gồm cả tăng kali huyết. Spironolactone cũng được chỉ định trong các trường hợp suy tim sung huyết, tăng huyết áp vô căn, kiểm soát chứng rậm lông, và các bệnh có thể gây tăng aldosterone thứ phát như xơ gan kết hợp với phù/cổ trướng, hội chứng thận hư, và các trạng thái phù khác.\n\nThuốc này là hoạt chất chính trong Aldactone và thuộc nhóm lợi tiểu. Tác dụng phụ của spironolactone có thể liên quan đến hormone giới tính, do đó nó đôi khi được thay thế bằng eplerenone. Spironolactone có thể bài tiết qua sữa mẹ và tương tác với thuốc Aspilets EC.\n\nNhư vậy, spironolactone đóng vai trò quan trọng trong việc điều trị nhiều tình trạng y tế khác nhau, từ bệnh cường aldosterone đến các vấn đề liên quan đến suy thận và suy tim.&lt;SEP&gt;Spironolactone là một loại thuốc.&lt;SEP&gt;Spironolactone là thuốc lợi tiểu giữ kali có thể tương tác với Cozaar.\nViệc Sử Dụng Sai Lầm: Việc sử dụng sai là hành vi sử dụng thuốc không đúng cách hoặc không tuân theo hướng dẫn.\nHội Chứng Tăng Kali Huyết Trầm Trọng: Hội chứng tăng kali huyết trầm trọng là tình trạng bệnh lý có thể xảy ra khi sử dụng spironolactone.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nBất Thường Liên Quan Đến Chức Năng Gan: Bất thường liên quan đến chức năng gan là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Bất thường liên quan đến chức năng gan là triệu chứng hệ thống gan mật do thuốc Aldactone gây ra.\nAldactone - Buồn Nôn: Aldactone gây buồn nôn.\nCây Thuốc - Độc Tính: Cây thuốc chứa nhiều độc tính nguy hiểm.\nAldactone - Chóng Mặt: Aldactone gây chóng mặt.\nHút Thuốc - Rối Loạn Nhận Thức Thần Kinh: Hút thuốc có thể gây rối loạn nhận thức.\nChóng Mặt - Spironolactone: Spironolactone có thể gây chóng mặt.\nThuốc - Việc Sử Dụng Sai Lầm: Sử dụng thuốc sai cách có thể dẫn đến việc sử dụng sai thuốc.\nAldactone - Tăng Huyết Áp: Aldactone được sử dụng để điều trị tăng huyết áp.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nSpironolactone - Tăng Huyết Áp: Spironolactone được sử dụng để điều trị tăng huyết áp.\nNguy Cơ Ung Thư - Thuốc Hóa Trị: Thuốc hóa trị có thể gây ra nguy cơ ung thư.\nThuốc Ngăn Chặn Aldosterone - Tăng Huyết Áp: Thuốc ngăn chặn aldosterone như spironolactone và eplerenone được sử dụng để điều trị tăng huyết áp.\nDị Ứng - Vị Thuốc: Dị ứng với bất kỳ thành phần nào của vị thuốc là triệu chứng cần tránh.&lt;SEP&gt;Vị thuốc có thể gây dị ứng với một số người.\nAldactone - Suy Tim: Aldactone được sử dụng để điều trị suy tim.\nNgộ Độc Thuốc - Rượu Thuốc: Ngộ độc thuốc (quá liều) là một trong những nguy cơ khi sử dụng rượu thuốc.\nAldactone - Ngứa: Aldactone gây ngứa.\nQuá Liều - Thuốc A.T.P: Nguy cơ của việc dùng quá liều thuốc A.T.P.\nSpironolactone - Suy Tim: Spironolactone được chỉ định để hỗ trợ trong điều trị suy tim.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nAldactone - Ung Thư: Thuốc Aldactone có thể tạo các khối u lành tính, ác tính và không đặc hiệu.\nThuốc lá - Ợ H nóng: Thuốc lá có thể gây ợ nóng.\nAldactone - Aspirin: Aspirin làm suy giảm tác dụng của Aldactone.\nAspirin - Spironolactone: Spironolactone có thể bị suy giảm tác dụng khi sử dụng cùng aspirin.\nHuyết Áp - Spironolactone: Spironolactone giúp điều chỉnh huyết áp cao.\nAldactone - Rối Loạn Tiêu Hóa: Aldactone gây rối loạn tiêu hóa.\nAldactone - Phát Ban: Aldactone gây phát ban.\nAldactone - Rối Loạn Điện Giải: Rối loạn điện giải là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Phù: Aldactone được sử dụng để điều trị phù.\nAldactone - Hội Chứng Thận Hư: Aldactone được chỉ định điều trị hội chứng thận hư.&lt;SEP&gt;Aldactone được sử dụng để điều trị hội chứng thận hư.\nAldactone - Suy Thận Cấp: Aldactone gây suy thận cấp.\nAldactone - Suy Nhược: Aldactone gây suy nhược.\nKali - Spironolactone: Spironolactone giúp điều chỉnh nồng độ kali.\nAldactone - Mề Đay: Aldactone gây mề đay.\nHội Chứng Thận Hư - Spironolactone: Spironolactone được chỉ định điều trị hội chứng thận hư.\nChất Điện Giải - Spironolactone: Spironolactone có thể gây tăng kali huyết và cần đánh giá định kỳ chất điện giải.\nAldactone - Xơ Gan: Aldactone được sử dụng để điều trị xơ gan.\nAldactone - Giảm Bạch Cầu: Giảm bạch cầu là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nKinh Nguyệt Không Đều - Spironolactone: Spironolactone có thể gây kinh nguyệt không đều ở phụ nữ.\nAldactone - Rụng Tóc: Aldactone gây rụng tóc.\nAspilets EC - Spironolactone: Aspilets EC có thể tương tác với spironolactone.\nSpironolactone (Aldactone) - Viêm Da: Spironolactone (Aldactone) được sử dụng để chữa trị viêm da.\nAldactone - Digoxin: Aldactone làm tăng thời gian bán thải của digoxin.\nAldactone - Bệnh Addison: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc bệnh Addison.\nAldactone - Spironolactone: Aldactone chứa hoạt chất spironolactone.\nDigoxin - Spironolactone: Spironolactone có thể tăng thời gian bán thải của digoxin.\nBệnh Addison - Spironolactone: Spironolactone chống chỉ định ở bệnh nhân mắc bệnh Addison.\nAldactone - Suy Tim Sung Huyết: Aldactone được chỉ định điều trị suy tim sung huyết.\nNgủ Gà - Spironolactone: Spironolactone có thể gây ngủ gà.\nAldactone - Tăng Huyết Áp Vô Căn: Aldactone được chỉ định điều trị tăng huyết áp vô căn.\nAldactone - Indomethacin: Indomethacin làm suy giảm tác dụng của Aldactone.\nAldactone - Tổn Thương Thận: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc tổn thương thận.\nSpironolactone - Suy Tim Sung Huyết: Spironolactone được chỉ định điều trị suy tim sung huyết.\nSpironolactone - Tăng Huyết Áp Vô Căn: Spironolactone được chỉ định điều trị tăng huyết áp vô căn.\nIndomethacin - Spironolactone: Spironolactone có thể bị suy giảm tác dụng khi sử dụng cùng indomethacin.\nAldactone - Rậm Lông: Aldactone gây rậm lông.\nAldactone - Vô Niệu: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc vô niệu.\nCozaar - Spironolactone: Cozaar có thể tương tác với spironolactone, tăng kali trong huyết thanh.\nAldactone - Norepinephrine: Aldactone có tương tác với norepinephrine.\nAldactone - Tăng Kali Huyết: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc tăng kali huyết.&lt;SEP&gt;Tăng kali huyết là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nSpironolactone - Vô Niệu: Spironolactone chống chỉ định ở bệnh nhân vô niệu.\nMụn Trứng Cà - Spironolactone (Aldactone): Spironolactone (Aldactone) được sử dụng để chữa trị mụn trứng cá.\nAldactone - Cholestyramine: Cholestyramine có thể gây nhiễm acid chuyển hóa tăng kali huyết khi sử dụng chung với Aldactone.\nAldactone - Suy Thận Cấp Tính: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc suy thận cấp tính.\nAldactone - Kali Huyết: Aldactone ảnh hưởng trực tiếp tới nồng độ kali máu.\nAldactone - Ammonium Chloride: Ammonium chloride có thể gây nhiễm acid chuyển hóa tăng kali huyết khi sử dụng chung với Aldactone.\nNorepinephrine - Spironolactone: Spironolactone có tương tác với norepinephrine.\nAldactone - Kiểm Soát Chứng Rậm Lông: Aldactone được chỉ định kiểm soát chứng rậm lông.\nAldactone - Phù/Cổ Trướng: Aldactone được chỉ định điều trị phù/cổ trướng.\nAldactone - Chứng Tăng Aldosterone Nguyên Phát: Aldactone được chỉ định điều trị chứng tăng aldosterone nguyên phát.\nAcid Mefenamic - Aldactone: Acid mefenamic làm suy giảm tác dụng của Aldactone.\nAldactone - Antipyrine: Aldactone có thể làm tăng chuyển hóa của antipyrine.\nAldactone - Carbenoxolone: Carbenoxolone có thể làm giảm hiệu quả của Aldactone khi sử dụng chung.\nSpironolactone - Tăng Kali Huyết: Spironolactone có thể gây tăng kali huyết.\nChất Ức Chế Carbonic Anhydrase - Spironolactone: Spironolactone và chất ức chế carbonic anhydrase là hai loại thuốc.\nAldactone - Thay Đổi Khả Năng Tình Dục: Thay đổi khả năng tình dục là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Aldactone gây thay đổi khả năng tình dục.\nAldactone - Bất Thường Liên Quan Đến Chức Năng Gan: Bất thường liên quan đến chức năng gan là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.&lt;SEP&gt;Aldactone gây bất thường liên quan đến chức năng gan.\nAldactone - Mẫn Cảm Với Spironolactone: Aldactone chống chỉ định sử dụng ở bệnh nhân mẫn cảm với spironolactone.\nAldactone - Lú Vẩn: Aldactone gây lú vẩn.\nAldactone - Bị Choáng Váng: Aldactone gây choáng váng.\nAldactone - Tình Trạng Chuột C rút Chân: Aldactone gây tình trạng chuột rút chân.\nAldactone - Bệnh Vú To Ở Đàn Ông: Aldactone gây bệnh vú to ở đàn ông.\nAldactone - Bị Choáng Váng, Chóng Mặt: Bị choáng váng, chóng mặt là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Rối Loạn Tiêu Hóa, Buồn Nôn: Rối loạn tiêu hóa, buồn nôn là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Rụng Tóc, Rậm Lông, Ngứa, Phát Ban: Rụng tóc, rậm lông, ngứa, phát ban là tác dụng phụ có thể xảy ra khi sử dụng Aldactone.\nAldactone - Giảm Kali/Magie Huyết: Aldactone được sử dụng để điều trị giảm kali/magie huyết.\nAldactone - Tăng Aldosterone Nguyên Phát: Aldactone được sử dụng để điều trị tăng aldosterone nguyên phát.\nSpironolactone - Xơ Gan Mất Bù: Spironolactone có thể gây tăng kali huyết ở bệnh nhân xơ gan mất bù.\nSpironolactone - Thời Gian Bán Thải: Spironolactone có thể tăng thời gian bán thải của digoxin.\nSpironolactone - Suy Tim Nặng: Spironolactone có thể gây tăng kali huyết ở bệnh nhân suy tim nặng.\nEplerenone - Spironolactone: Eplerenone giúp loại bỏ tác dụng phụ của hormone giới tính liên quan đến spironolactone.&lt;SEP&gt;Eplerenone thay thế spironolactone để khắc phục tác dụng phụ của hormone giới tính.\nSpironolactone - Suy Thận Cấp Tính: Spironolactone chống chỉ định ở bệnh nhân suy thận cấp tính.\nSpironolactone - Thuốc Lợi Tiểu Giữ Kali: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc lợi tiểu giữ kali.\nBệnh Aldosterone Nguyên Phát - Spironolactone: Spironolactone được sử dụng để điều trị bệnh aldosterone nguyên phát.\nPhì Đại Tuyến Vú Nam - Spironolactone: Spironolactone có thể gây phì đại tuyến vú nam.\nKiểm Soát Chứng Rậm Lông - Spironolactone: Spironolactone được chỉ định kiểm soát chứng rậm lông.\nPhù/Cổ Trướng - Spironolactone: Spironolactone được chỉ định điều trị phù/cổ trướng.\nChứng Tăng Aldosterone Nguyên Phát - Spironolactone: Spironolactone được chỉ định điều trị chứng tăng aldosterone nguyên phát.\nAcid Mefenamic - Spironolactone: Spironolactone có thể bị suy giảm tác dụng khi sử dụng cùng acid mefenamic.\nSpironolactone - Thuốc Chặn Aldosterone: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc chặn aldosterone.\nChế Độ Ăn Giàu Kali - Spironolactone: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng chế độ ăn giàu kali.\nHội Chứng Tăng Kali Huyết Trầm Trọng - Spironolactone: Spironolactone có thể gây hội chứng tăng kali huyết trầm trọng khi sử dụng cùng thuốc gây tăng kali huyết.\nSpironolactone - Tăng Clo Huyết Phục Hồi: Spironolactone có thể gây tăng clo huyết phục hồi.\nSpironolactone - Thuốc Ức Chế ACE: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc ức chế ACE.\nSpironolactone - Thuốc Đối Kháng Angiotensin II: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng thuốc đối kháng angiotensin II.\nMuối Chứa Kali - Spironolactone: Spironolactone có thể gây tăng kali huyết khi sử dụng cùng muối chứa kali.\nCản Trở Định Lượng - Spironolactone: Spironolactone có thể cản trở việc định lượng nồng độ digoxin trong huyết tương.\nAldosterone - Thuốc Ngăn Chặn Aldosterone: Thuốc ngăn chặn aldosterone như spironolactone và eplerenone giúp giảm lượng aldosterone trong cơ thể.\nChứng Bất Lực - Spironolactone (Aldactone): Spironolactone (Aldactone) có thể gây bất lực.\nDị Tật Bẩm Sinh - Spironolactone (Aldactone): Spironolactone (Aldactone) có thể gây dị tật bẩm sinh.\nMọc Nhiều Lông - Spironolactone (Aldactone): Spironolactone (Aldactone) được sử dụng để chữa trị mọc nhiều lông.\nSpironolactone (Aldactone) - Sản Xuất Androgen: Spironolactone (Aldactone) chống lại quá trình sản xuất androgen.']</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sử dụng Aldactone (spironolactone) ở bệnh nhân mẫn cảm với spironolactone là chống chỉ định vì có thể gây ra một loạt tác dụng phụ nghiêm trọng. Khi bệnh nhân mẫn cảm với spironolactone sử dụng Aldactone, họ có thể gặp phải các tác dụng phụ như:
+- **Bất thường liên quan đến chức năng gan**: Aldactone có thể gây ra các bất thường liên quan đến chức năng gan.
+- **Rối loạn điện giải**: Aldactone có thể gây rối loạn điện giải, đặc biệt là tăng kali huyết.
+- **Ngứa, phát ban, mề đay**: Aldactone có thể gây ra các triệu chứng da như ngứa, phát ban, và mề đay.
+- **Rụng tóc, rậm lông**: Aldactone có thể gây rụng tóc và rậm lông.
+- **Bệnh vú to ở đàn ông**: Aldactone có thể gây ra tình trạng vú to ở nam giới.
+- **Bệnh Addison**: Aldactone chống chỉ định sử dụng ở bệnh nhân mắc bệnh Addison.
+- **Tăng kali huyết**: Aldactone có thể gây tăng kali huyết, đặc biệt ở bệnh nhân suy tim nặng.
+Đặc biệt, việc sử dụng Aldactone ở bệnh nhân mẫn cảm với spironolactone có thể dẫn đến tình trạng mẫn cảm nghiêm trọng, gây nguy hiểm đến sức khỏe và thậm chí có thể dẫn đến tử vong.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ở những bệnh nhân mẫn cảm với spironolactone, thuốc này có thể gây ra các phản ứng dị ứng nghiêm trọng, có thể mengan dọa tính mạng.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7060465098004555</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9056782940917805</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nếu tôi quên uống một liều Cardilopin, tôi nên làm gì?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>['Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nQuá Liều Clopidogrel: Quá liều clopidogrel là tình trạng có thể xảy ra khi dùng clopidogrel.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nQuá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nĐau Ngực Nặng Hơn: Đau ngực nặng hơn là tác dụng phụ nghiêm trọng có thể gặp khi dùng Cardilopin.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nViên Uống Bổ Sung Kali: Viên uống bổ sung kali là thuốc bổ sung kali.\ntờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nĐiều Trị Cơn Đau Tim: Điều trị cơn đau tim là phương pháp điều trị tình trạng đau tim.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nNgười Dùng Thuốc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nCách Dùng Và Liều Dùng: Cách dùng và liều dùng của mướp tây bao gồm việc sử dụng trong chế biến thức ăn như luộc, xào, nấu canh, nấu nước uống hoặc dùng ngoài.&lt;SEP&gt;Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nThuốc Lợi Tiểu Spinorolactone: Thuốc lợi tiểu spinorolactone.\nPhụ TỬ: Phụ tử là một vị thuốc được sử dụng kết hợp với Khoai nưa trong hỗ trợ điều trị liệt nửa người.\nQuá Liều Thuốc Ameflu DAYTIME: Quá liều thuốc Ameflu DAYTIME là tình trạng cần xử lý kịp thời.\nCo-Diovan: Co-Diovan là thuốc gồm hai hoạt chất là valsartan và hydrochlorothiazide, được sử dụng trong điều trị tăng huyết áp.&lt;SEP&gt;Co-Diovan là thuốc chứa valsartan và hydrochlorothiazide.&lt;SEP&gt;Co-Diovan là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Thuốc Co-Diovan chứa valsartan và hydrochlorothiazide.\nThuốc Động Kinh: Thuốc động kinh là các loại thuốc được sử dụng để điều trị động kinh.\nLiều Thuốc: Liều thuốc là lượng thuốc cần thiết và được sử dụng trong mỗi lần uống hoặc tiêm, cũng như trong một khoảng thời gian cụ thể. Không chỉ đơn thuần là lượng thuốc cần dùng trong mỗi lần uống, liều thuốc còn là lượng thuốc cần thiết để đạt hiệu quả điều trị. Nó có thể được sử dụng để điều trị bằng cách áp dụng phương pháp điều trị với các loại thuốc khác nhau, ví dụ như Aibezym, theo đúng liều lượng. Liều thuốc cũng đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, như tăng canxi huyết, đòi hỏi việc xác định đúng liều lượng cho từng trường hợp cụ thể để đảm bảo hiệu quả điều trị và giảm thiểu tác dụng phụ không mong muốn.\n\nĐể đạt hiệu quả tốt nhất, liều thuốc cần được tuân thủ theo đúng hướng dẫn sử dụng hoặc chỉ định của bác sĩ và khuyến nghị của nhà sản xuất. Điều này bao gồm việc sử dụng đúng liều lượng cho từng loại thuốc cụ thể, ví dụ như Betadine Throat Spray. Việc quên liều hoặc cố gắng bù đắp bằng cách dùng gấp đôi liều đều không được khuyến khích. Thay vào đó, nếu bạn quên một liều thuốc, bạn nên tiếp tục lịch trình sử dụng thuốc của mình và không nên dùng gấp đôi liều để bù vào liều đã quên.\n\nLiều thuốc Diorophyl cần được tuân thủ theo chỉ định của bác sĩ, không nên sử dụng quá liều khuyến cáo. Liều thuốc cũng là cách sử dụng thuốc theo lịch trình đã xác định, như khi sử dụng Atocib hoặc Ceritine. Liều thuốc đóng vai trò quan trọng trong việc điều trị các tình trạng y tế cụ thể, đòi hỏi sự chính xác và tuân thủ chặt chẽ về liều lượng.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc Co-Diovan, bao gồm hướng dẫn về việc quên thuốc và sử dụng liều kế tiếp.&lt;SEP&gt;Liều thuốc là cách sử dụng thuốc theo đúng hướng dẫn của bác sĩ để đảm bảo an toàn.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nCà Độc Dược: Cà độc dược là loại thuốc độc bảng A được Bộ Y tế xếp loại và sử dụng rộng rãi.&lt;SEP&gt;Cà độc dược là một loại cây có hoa đốm tím, thân và cành xanh, được dùng làm thuốc và cây cảnh.&lt;SEP&gt;Cà độc dược là loại thuốc độc bảng A, có tác dụng của hyoxin và atropine, được dùng trong chuyên khoa thần kinh và chống nấm Aspergillus.&lt;SEP&gt;Cà độc dược là thuốc có tác dụng tiêu diệt nấm Aspergillus, thuốc trừ sâu sinh học, thuốc kháng nấm trên cây, thuốc diệt nhện rệp, diệt mối, đuổi muỗi và côn trùng.&lt;SEP&gt;Cà độc dược là loài cây phổ biến, được xếp vào danh sách thuốc độc bảng A.&lt;SEP&gt;Cà độc dược là một loại thuốc được dùng với cùng những chỉ định như thuốc độc bảng.\nThầy Thuốc: Thầy thuốc là người chuyên môn trong y học, tư vấn và điều trị bệnh tật theo phương pháp Đông y. Họ không chỉ đưa ra hướng dẫn sử dụng thuốc cho bệnh nhân mà còn tư vấn về việc sử dụng nhiều loại thảo dược khác nhau như bạch cương tàm, cây Đại, chè vằng, và củ gấu tàu. Thầy thuốc cũng đưa ra lời khuyên về những trường hợp cần kiêng kỵ khi sử dụng các loại thảo dược này. Trong văn bản, thầy thuốc được mô tả như một nguồn tư vấn đáng tin cậy cho người bệnh.&lt;SEP&gt;Thầy thuốc là người có kiến thức y khoa, hỗ trợ người bệnh trong việc sử dụng thuốc và điều trị bệnh.&lt;SEP&gt;Thầy thuốc là người có chuyên môn y tế, được đào tạo để chẩn đoán và điều trị bệnh.&lt;SEP&gt;Thầy thuốc là người chuyên môn trong việc thăm khám và tư vấn sử dụng thuốc.&lt;SEP&gt;Thầy thuốc là người tư vấn về cách sử dụng Rau ôm đúng cách.&lt;SEP&gt;Thầy thuốc cung cấp chẩn đoán và tư vấn để sử dụng sương sâm chính xác.&lt;SEP&gt;Thầy thuốc là người tư vấn và hướng dẫn sử dụng Thông đất.\nChỉ Định Thuốc: Chỉ định thuốc là hướng dẫn về cách sử dụng và liều dùng của Telmisartan và Cilzec.\nCilzec: Cilzec là thuốc kê đơn dùng để điều trị cao huyết áp, được bào chế dưới dạng viên nén.&lt;SEP&gt;Cilzec là thuốc cần ngừng sử dụng khi gặp tác dụng không mong muốn.&lt;SEP&gt;Cilzec là thuốc được dùng để điều trị áp cao.&lt;SEP&gt;Cilzec là thuốc chống chỉ định sử dụng cho người bị dị ứng với bất kỳ thành phần nào của thuốc.&lt;SEP&gt;Cilzec là thuốc cần được bảo quản nơi khô ráo, thoáng mát, tránh ánh sáng và ẩm.&lt;SEP&gt;Cilzec là tên thương mại của thuốc Telmisartan, được dùng theo đơn của bác sĩ.\nTiêu Chảy - Viên Uống Bổ Sung Kali: Viên uống bổ sung kali được sử dụng để bổ sung kali trong điều trị tiêu chảy.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nCortisol - Thuốc Lợi Tiểu Spinorolactone: Thuốc lợi tiểu spinorolactone có thể làm tăng nồng độ cortisol trong máu.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nClopidogrel - Quá Liều Clopidogrel: Clopidogrel có thể gây quá liều, kéo dài thời gian chảy máu.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nThuốc Động Kinh - Động Kinh: Thuốc động kinh được sử dụng để điều trị động kinh.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nAmeflu DAYTIME - Quá Liều Thuốc Ameflu DAYTIME: Khi xảy ra quá liều thuốc Ameflu DAYTIME, cần xử lý kịp thời.\nCách Dùng Và Liều Dùng - Phụ TỬ: Cách dùng và liều dùng Phụ TỬ được hướng dẫn cụ thể trong tài liệu.\nNgừng Tim Đột Ngột - Điều Trị Cơn Đau Tim: Ngừng tim đột ngột có thể liên quan đến điều trị cơn đau tim.\nCo-Diovan - Liều Thuốc: Hướng dẫn về cách sử dụng liều thuốc Co-Diovan.\nThuốc Chống Động Kinh - Thuốc Động Kinh: Thuốc chống động kinh có thể tương tác với các loại thuốc động kinh khác.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nCardilopin - Đau Ngực Nặng Hơn: Đau ngực nặng hơn là tác dụng phụ nghiêm trọng có thể gặp khi dùng Cardilopin.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nClorpheniramin Maleat - Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nCà Độc Dược - Thầy Thuốc: Thầy thuốc đưa ra hướng dẫn sử dụng Cà độc dược cho bệnh nhân.\nPhenylephrine HCl - Quá Liều Phenylephrine HCl: Quá liều phenylephrine HCl cần được xử lý triệu chứng và hỗ trợ tổng trạng.\nChỉ Định Thuốc - Cilzec: Chỉ định thuốc là hướng dẫn về cách sử dụng Cilzec.\nPhentolamin - Quá Liều Phenylephrine HCl: Phentolamin được dùng trong xử lý tăng huyết áp do quá liều phenylephrine HCl.\nNgười Dùng Thuốc - Thắc Mắc: Người dùng thuốc đặt thắc mắc về việc sử dụng thuốc.\nGiải Đáp - Người Dùng Thuốc: Giải đáp cung cấp thông tin phản hồi cho người dùng thuốc.']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nếu bạn quên uống một liều Cardilopin, bạn nên:
+- Dùng thuốc ngay khi nhớ ra đã quên liều.
+- Nếu liều đã quên gần với liều kế tiếp, hãy bỏ qua liều đã quên và dùng theo đúng lịch trình dùng thuốc.
+- Không nên uống gấp đôi liều để bù vào liều đã quên.
+### Cách bảo quản
+Cardilopin cần được bảo quản ở nhiệt độ dưới 25°C, nơi khô ráo và tránh ánh sáng.
+### Lưu ý
+Bạn nên tham khảo sự tư vấn cụ thể hơn của bác sĩ nếu gặp bất kỳ vấn đề nào trong quá trình sử dụng thuốc.
+### Tham khảo
+- [1] cardilopin.txt</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bạn nên dùng bổ sung ngay khi nhớ ra, trường hợp nhớ ra trễ hơn 12 giờ so với giờ dùng thuốc hàng ngày, hãy bỏ qua liều đã quên và không dùng thêm thuốc để bù khi dùng liều tiếp theo.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8897297646326082</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7474324411331521</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Đối với trẻ em, cần chú ý gì khi sử dụng thuốc Cilzec?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>['Chỉ Định Thuốc: Chỉ định thuốc là hướng dẫn về cách sử dụng và liều dùng của Telmisartan và Cilzec.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nLưu Ý Sử Dụng Thuốc: Lưu ý sử dụng thuốc bao gồm việc giữ thuốc xa tầm tay trẻ em và đọc kỹ hướng dẫn trước khi dùng.\nTrẻ: Trẻ là đối tượng dễ mắc bệnh cúm do có hệ miễn dịch chưa hoàn thiện.&lt;SEP&gt;Trẻ là đối tượng sử dụng thuốc clotrimazole.\nTrẻ Em và Trẻ Vị Thành Niên: Trẻ em và trẻ vị thành niên là đối tượng sử dụng Ciprofloxacin với liều lượng cụ thể.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nTầm Với Trẻ Em: Thuốc cần được bảo quản tránh xa tầm với của trẻ em.\nTrẻ Em: Trẻ Em là đối tượng cần đặc biệt chú ý trong việc sử dụng các loại thuốc để đảm bảo an toàn và hiệu quả. Đối với một số loại thuốc cụ thể như A.t Ibuprofen Syrup và A.t Zinc, trẻ em cần tránh xa để tránh nguy cơ không mong muốn. Đối với một số loại thuốc khác như Aclasta, trẻ em và thiếu niên dưới 18 tuổi không được khuyến nghị sử dụng do các rủi ro tiềm ẩn. Tuy nhiên, trẻ em có thể sử dụng Acyclovir Stella Cream một cách an toàn. Khi sử dụng Agifuros 40 mg, trẻ em cần hết sức cẩn thận. Đặc biệt, đối với trẻ em dưới 6 tháng tuổi, việc sử dụng thuốc vẫn chưa được xác định rõ về mặt hiệu quả và độ an toàn. Ngoài ra, trẻ em cần đặc biệt chú ý khi sử dụng một số loại thuốc khác như Alchysin 8400, Alpha-Chymotrypsin 4200 IU, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, và Alputine. Việc sử dụng những loại thuốc này cần được báo với bác sĩ trước khi sử dụng trên trẻ em. Trẻ em từ 5-10 tuổi là đối tượng sử dụng thuốc Ambroxol với liều lượng và cách dùng cụ thể. Trẻ em dưới 2 tuổi cần được cân nhắc cẩn thận trước khi dùng Ambroxol. Trẻ em cần tránh tiếp xúc với thuốc Amlor 5 Pfizer, Amlodipin Domesco, và An Thảo. Trẻ em cần tránh xa tầm tay của thuốc để đảm bảo an toàn. Trẻ Em cũng cần tránh tiếp xúc trực tiếp với thuốc Antanazol và Aphaxan Armephaco. Họ cũng cần tránh xa thuốc Arthrorein Pharmanel và Asevictoria Mediplantex. Trẻ em cần tránh tiếp xúc với thuốc Aspartam Pharmedic và Atorhasan để đảm bảo an toàn. Thuốc cần được bảo quản tránh xa tầm với của trẻ em. Đặc biệt, trẻ em dưới 6 tháng tuổi cần đặc biệt thận trọng khi sử dụng thuốc vì độ an toàn và hiệu quả chưa được xác định rõ ràng. Trẻ em không nên sử dụng axit glutamic. Họ cũng cần tránh xa tầm tay thuốc Babi B.O.N để đảm bảo an toàn. Trẻ em cần tránh xa thuốc Adrenoxyl để đảm bảo an toàn. Trẻ em cần được bảo vệ khỏi tiếp cận thuốc Allopurinol. Trẻ em cần tránh xa tầm tay thuốc Atussin. Trẻ em không nên tiếp cận với thuốc Differin. Trẻ em là đối tượng cần thận trọng khi sử dụng Diurefar, đặc biệt khi dùng trong thời gian dài.\n\nTrẻ em là đối tượng cần được theo dõi chặt chẽ trong vấn đề trị cảm cúm. Trẻ em là đối tượng sử dụng Bảo Thanh Hoa Linh siro và viên ngậm. Trẻ em cần tránh tiếp xúc với Batigan. Trẻ em có thể sử dụng Benzyl benzoate nhưng cần tham khảo ý kiến bác sĩ. Trẻ em cần tránh xa tầm tay của Beprosone Ointment. Trẻ em cần tránh tiếp xúc với thuốc Berberin Mộc Hương. Trẻ em cần giữ thuốc xa tầm tay để tránh sử dụng sai cách, sai liều. Trẻ em là đối tượng cần tránh tiếp xúc với sản phẩm Bilomag. Trẻ em là đối tượng thận trọng khi sử dụng Bluemint. Trẻ em dưới 6 tuổi được khuyến cáo không nên dùng Bluemint. Bofit F được chỉ định điều trị thiếu máu do thiếu sắt ở trẻ em. Trẻ em là đối tượng sử dụng Calcium Stada Vitamin D với liều lượng khác so với người lớn. Trẻ em là đối tượng cần thận trọng khi sử dụng Calcium Stada Vitamin D. Trẻ em là đối tượng sử dụng Rotudin từ 13 tháng tuổi trở lên. Trẻ em dưới 15 tuổi được sử dụng rễ Gai cua với liều giảm một nửa so với người lớn. Trẻ em là đối tượng cần cẩn trọng khi dùng dược liệu. Trẻ em là đối tượng dễ nhạy cảm với các dụng không mong muốn của thuốc. Trẻ em là đối tượng cần theo dõi đặc biệt trong điều trị viêm tai giữa. Trẻ em là đối tượng cần thận trọng khi sử dụng Pregabalin do thiếu thông tin an toàn và hiệu quả. Trẻ em cần tránh xa tầm tay đối với Dentanalgi. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Diamicron.\n\nNgoài ra, trẻ em là đối tượng dễ mắc bệnh thiếu máu thiếu sắt. Trẻ em là đối tượng dễ gặp gãy xương do cấu trúc xương chưa hoàn thiện. Trẻ em không nên dùng hoắc hương. Trẻ em cần tránh xa cây hương bài vì quả cây có màu tím rất bắt mắt và có độc tính. Trẻ em là đối tượng cần cẩn trọng khi sử dụng cây huyết rồng. Trẻ em từ 6 tuổi trở lên là đối tượng sử dụng Glargine. Trẻ em cần tránh xa thuốc Azithromycin để đảm bảo an toàn. Trẻ em là đối tượng có thể gặp nhiều nguy cơ khi bổ sung DHEA với liều lượng lớn. Trẻ em là đối tượng dễ gặp nguy cơ do liều lượng sử dụng càng cao khi dùng DHEA. Trẻ em không được dùng Mật nhân. Trẻ em cần được bảo vệ khỏi tiếp xúc với men vi sinh Antibio. Trẻ em là đối tượng sử dụng men vi sinh Antibio với liều lượng khác nhau so với người lớn.\n\nTrẻ em dưới 5 tuổi không nên sử dụng nấm lim xanh do thiếu nghiên cứu về mức độ an toàn. Trẻ em dưới 7 tuổi không nên sử dụng Anginovag. Trẻ em từ 12-18 tuổi cần điều chỉnh liều dùng khi sử dụng Bixicam. Trẻ em cần tránh xa thuốc Bixicam để đảm bảo an toàn.\n\nĐối với trẻ em, khí huyết đang trong giai đoạn phát triển, chưa định hình rõ ràng, do đó việc sử dụng thuốc cần được theo dõi chặt chẽ và tuân thủ hướng dẫn của bác sĩ. Trẻ em là nhóm người dễ bị ảnh hưởng bởi bệnh cúm A/H1N1.\n\nTrẻ em không nên sử dụng rau mùi tây. Trẻ em cần tránh tiếp xúc với thuốc Aceclofenac STADA. Trẻ em cần tránh xa tầm tay thuốc Acetazolamid. Trẻ em cần tránh xa thuốc Ameflu DAYTIME để đảm bảo an toàn. Trẻ em là đối tượng được điều trị bằng các thuốc chống ngứa.\n\nTrẻ em dưới 12 tuổi cần sử dụng Bổ Huyết Ích Não một cách cẩn thận.\n\nNgoài ra, trẻ em có thể bị vàng da do dùng Carbotrim trong thời kỳ chu sinh. Trẻ em là đối tượng sử dụng Claminat. Trẻ em là đối tượng cần tránh tiếp xúc với thuốc Clotrimazole. Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\n\nTrẻ em từ 2 tuổi trở lên là đối tượng sử dụng Deferasirox (Exjade). Trẻ em từ 10 tuổi trở lên có thể sử dụng deferasirox, đặc biệt là những trẻ cần truyền máu thường xuyên. Trẻ em không nên sử dụng Coversyl Plus.\n\nTrẻ em cần được bảo vệ khỏi tiếp xúc với thuốc Dexamethasone.\n\nTrẻ em cần tránh xa thuốc Benzalkonium Chloride. Trẻ em cần tránh xa sản phẩm chứa Benzalkonium Chloride để tránh trường hợp trẻ uống nhầm gây nguy hiểm.\n\nTrẻ em là đối tượng cần điều chỉnh liều dùng Cefoxitin dựa trên cân nặng và độ tuổi.\n\nNgoài ra, trẻ em cần tránh xa sản phẩm thuốc sắt cho bà bầu Avisure Safoli.\n\nTrẻ em nhỏ tuổi cần tham khảo ý kiến chuyên gia trước khi sử dụng tinh dầu hoàng đàn. Trẻ em cần được bảo vệ khỏi tiếp xúc trực tiếp với tinh dầu.\nGiữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nA.T.P: Thuốc A.T.P được chỉ định trong hỗ trợ điều trị chứng đau lưng.&lt;SEP&gt;A.T.P là thuốc giãn cơ, chứa hoạt chất dinatri adenosin triphosphat.&lt;SEP&gt;A.T.P là thuốc được đề cập trong bài viết.\nThuốc Ho Thảo Dược: Thuốc ho thảo dược an toàn cho trẻ được khuyến nghị sử dụng.&lt;SEP&gt;Thuốc ho thảo dược an toàn cho trẻ.\nTrẻ Em Dưới 24 Tháng Tuổi: Trẻ em dưới 24 tháng tuổi là đối tượng cần thận trọng khi sử dụng thuốc.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nThuốc - Trẻ: Thuốc cần được sử dụng nghiêm ngặt theo hướng dẫn của bác sĩ để tránh tác dụng phụ.\nHo - Thuốc Ho Thảo Dược: Thuốc ho thảo dược được dùng để điều trị ho cho trẻ.\nDược Liệu - Trẻ Em: Trẻ em cần cẩn trọng khi dùng dược liệu.\nCiprofloxacin - Trẻ Em và Trẻ Vị Thành Niên: Ciprofloxacin được sử dụng cho trẻ em và trẻ vị thành niên với liều lượng cụ thể.\nThuốc - Trẻ Em: Trẻ em không được phép sử dụng thuốc này.&lt;SEP&gt;Thuốc cần được giữ tránh xa tầm tay của trẻ em.&lt;SEP&gt;Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nHo Gà - Thuốc Ho Thảo Dược: Thuốc ho thảo dược an toàn cho trẻ được khuyến nghị sử dụng.\nTrẻ Em - Tác Dụng Phụ: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nAzithromycin DHG - Giữ Thuốc Xa Tầm Tay Trẻ Nhỏ: Thuốc cần được giữ xa tầm tay trẻ nhỏ nhằm tránh bé sử dụng sai cách, sai liều gây nguy hiểm.\nA.T.P - Trẻ Em: Bài viết cảnh báo bố mẹ để thuốc A.T.P tránh xa tầm tay trẻ em.\nChỉ Định Thuốc - Telmisartan: Chỉ định thuốc là hướng dẫn về cách sử dụng Telmisartan.\nBanitase - Lưu Ý Sử Dụng Thuốc: Người dùng cần lưu ý khi sử dụng thuốc Banitase.\nBảo Quản Thuốc - Trẻ Em: Thuốc cần được bảo quản tránh xa tầm tay của trẻ em.\nBilgrel - Giữ Thuốc Tránh Tầm Tay Trẻ Em: Thuốc cần được giữ tránh xa tầm tay của trẻ em.\nAlphaDHG - Trẻ Em: Trẻ em cần đặc biệt chú ý khi dùng thuốc AlphaDHG.\nColdi B - Tầm Với Trẻ Em: Coldi B cần được bảo quản tránh xa tầm với của trẻ em.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nClorpheniramin Maleat - Quá Liều Clorpheniramin Maleat: Quá liều clorpheniramin maleat cần được xử lý triệu chứng và hỗ trợ chức năng sống.\nTinh Dầu Húng Chanh - Trẻ Nhỏ: Trẻ nhỏ cần cẩn trọng khi sử dụng tinh dầu húng chanh.\nChỉ Định Thuốc - Cilzec: Chỉ định thuốc là hướng dẫn về cách sử dụng Cilzec.\nBổ Phế Nam Hà Chỉ Khái Lộ - Trẻ Em Dưới 24 Tháng Tuổi: Trẻ em dưới 24 tháng tuổi cần thận trọng khi sử dụng thuốc Bổ Phế Nam Hà Chỉ Khái Lộ.']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Cilzec cho trẻ em, cần lưu ý một số điểm sau:
+1. **Giữ thuốc xa tầm tay trẻ em**: Thuốc Cilzec cần được bảo quản tránh xa tầm tay của trẻ em để đảm bảo an toàn và tránh việc trẻ sử dụng sai cách hoặc sai liều.
+2. **Tuân thủ hướng dẫn của bác sĩ**: Khi sử dụng thuốc cho trẻ em, cần tuân thủ chính xác cách dùng và liều lượng theo chỉ định của bác sĩ.
+3. **Lưu ý về tác dụng phụ**: Trẻ em có nguy cơ gặp tác dụng phụ khi dùng thuốc. Do đó, cần theo dõi chặt chẽ tình trạng sức khỏe của trẻ khi sử dụng Cilzec.
+4. **Kiểm tra màu sắc thuốc**: Không sử dụng thuốc khi có bất kỳ sự thay đổi bất thường nào về màu sắc.
+5. **Bảo quản đúng cách**: Bảo quản thuốc nơi khô ráo, thoáng mát, nhiệt độ dưới 25°C, tránh ánh sáng và ẩm.
+### Cách bảo quản
+- **Bảo quản nơi khô ráo, thoáng mát**: Nhiệt độ dưới 25°C.
+- **Tránh ánh sáng trực tiếp**: Bảo quản thuốc tránh ánh sáng và ẩm.
+- **Giữ thuốc xa tầm tay trẻ em**: Điều này đặc biệt quan trọng để tránh việc trẻ sử dụng thuốc không đúng cách.
+### Giá cả tham khảo
+Thuốc Cilzec có giá khoảng 110.000 – 140.000 VNĐ/hộp. Tuy nhiên, giá cả có thể thay đổi tùy thuộc vào cơ sở bán và nhà phân phối thuốc.
+### Lưu ý cuối cùng
+Việc sử dụng thuốc Cilzec cho trẻ em cần được giám sát chặt chẽ bởi người lớn và tuân thủ chặt chẽ hướng dẫn của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Độ hiệu quả, an toàn của thuốc trên trẻ em chưa được làm rõ. Do đó, chỉ sử dụng thuốc cho trẻ em khi có sự chỉ định của bác sĩ.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8387407675626201</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6203994775799407</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với thuốc nào?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>['Atarax (Hydroxyzine Hydrochloride): Atarax (hydroxyzine hydrochloride) là thuốc được sử dụng để điều trị các triệu chứng như khô miệng và đánh trống ngực.\nChất Ức Chế Acetylcholinesterase: Chất ức chế acetylcholinesterase là thuốc có tương tác với Atarax.\nMethotrimeprazin: Methotrimeprazin là thuốc có tương tác với Atarax.\nHydroxyzine Hydrochloride: Hydroxyzine hydrochloride là hoạt chất chính trong Atarax.\nEpinephrin (Adrenalin): Epinephrin (adrenalin) là thuốc có tương tác với Atarax.\nChống Ngứa: Chống ngứa là phương pháp điều trị nhằm giảm và ngăn chặn cảm giác ngứa.&lt;SEP&gt;Chống ngứa là quá trình �ức chế cảm giác ngứa.&lt;SEP&gt;Chống ngứa (dị ứng) là chỉ định của Atarax.\nPramlintid: Pramlintid là thuốc có tương tác với Atarax.\nThuốc Cảm Lạnh Và Dị Ứng: Thuốc cảm lạnh và dị ứng là một loại thuốc có thể khiến người bệnh khó đi vào giấc ngủ.\nThuốc Kháng Acetylcholin Khác: Thuốc kháng acetylcholin khác có thể tăng thêm tác dụng khi dùng cùng Atarax.\nDroperidol: Droperidol là loại thuốc tương tác với Pregabalin.&lt;SEP&gt;Droperidol là thuốc có tương tác với Atarax.\nThuốc Antihistamine: Thuốc antihistamine được sử dụng để điều trị mề đay và phù mạch.\nThuốc Opiat: Thuốc opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu có tương tác với Atarax.\nAmphetamin: Amphetamin là một trong những thuốc kiềm yếu mà sự thải trừ giảm khi dùng chung với nhôm phosphat.&lt;SEP&gt;Amphetamin là thuốc có thể bị ảnh hưởng bởi nhôm phosphat.&lt;SEP&gt;Amphetamin là thuốc có tính bazơ, mức độ bài tiết của nó bị ức chế bởi các thuốc kháng axit.&lt;SEP&gt;Amphetamin là thuốc có tính bazơ bị ức chế sự bài tiết bởi thuốc kháng axit.&lt;SEP&gt;Amphetamin là một trong những thuốc có tương tác với Barudon.&lt;SEP&gt;Amphetamin có tương tác với Acetazolamid.&lt;SEP&gt;Amphetamin là thuốc có tương tác với Atarax.\nAtarax: Atarax là thuốc chứa hoạt chất hydroxyzine hydrochloride, được sử dụng trong các trường hợp ngăn cơn nôn, chống ngứa, lo âu, kiểm soát trạng thái kích động trong hội chứng cai rượu cấp.&lt;SEP&gt;Atarax là thuốc chống nôn, điều trị lo âu, làm dịu lo âu trước và sau gây mê, kiểm soát trạng thái kích động do cai rượu.&lt;SEP&gt;Thuốc Atarax được sử dụng để điều trị các tình trạng y tế cụ thể, có thể gây ra nhiều tác dụng phụ trong quá trình điều trị.&lt;SEP&gt;Atarax là thuốc kháng histamin, gây ra triệu chứng như co giật, cảm giác u ám và hạ huyết áp khi dùng quá liều.&lt;SEP&gt;Atarax là thuốc được sử dụng để điều chỉnh liều lượng cho bệnh nhân suy thận hoặc người đã từng bị co giật, động kinh.\nA.T Desloratadin: A.T Desloratadin là thuốc kháng histamin và chống dị ứng, chứa hoạt chất desloratadine.&lt;SEP&gt;Thuốc A.T Desloratadin có tác dụng làm giảm triệu chứng của dị ứng, như viêm mũi dị ứng, nổi mề đay mãn tính, ngứa, phát ban.&lt;SEP&gt;A.T Desloratadin là thuốc kháng histamin thứ hai thế hệ, dùng để điều trị triệu chứng dị ứng.\nNoradrenalin: Noradrenalin là một chất dẫn truyền thần kinh có thể làm tăng huyết áp trầm trọng do tác dụng co mạch khi tác dụng lên thụ thể alpha.&lt;SEP&gt;Noradrenalin là thuốc tim mạch được sử dụng trong điều trị hạ huyết áp.&lt;SEP&gt;Noradrenalin là thuốc dùng để điều trị hạ huyết áp do dùng Atenolol.&lt;SEP&gt;Noradrenalin là monoamin được ức chế tái hấp thu bởi Amitriptylin.&lt;SEP&gt;Noradrenalin là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.&lt;SEP&gt;Noradrenalin là thuốc dùng để điều trị hạ huyết áp khi quá liều Atarax.\nMetaraminol: Metaraminol là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.&lt;SEP&gt;Metaraminol là thuốc dùng để điều trị hạ huyết áp khi quá liều Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Suy Thận: Suy thận là tình trạng cần giảm liều Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Methotrimeprazin: Methotrimeprazin có tương tác với Atarax.\nA.T Desloratadin - Dị Ứng: A.T Desloratadin được chỉ định điều trị dị ứng.\nAtarax (Hydroxyzine Hydrochloride) - Epinephrin (Adrenalin): Epinephrin (adrenalin) có tương tác với Atarax.\nA.T Desloratadin - Ngứa: A.T Desloratadin giúp làm giảm triệu chứng ngứa.\nAtarax (Hydroxyzine Hydrochloride) - Pramlintid: Pramlintid có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Mất Ngủ: Mất ngủ là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Thuốc Kháng Acetylcholin Khác: Thuốc kháng acetylcholin khác có thể tăng thêm tác dụng khi dùng cùng Atarax.\nMất Ngủ - Thuốc Cảm Lạnh Và Dị Ứng: Thuốc cảm lạnh và dị ứng có thể khiến người bệnh khó đi vào giấc ngủ.\nAtarax (Hydroxyzine Hydrochloride) - Droperidol: Droperidol có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Suy Gan: Suy gan là tình trạng cần giảm liều Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Chất Ức Chế Acetylcholinesterase: Chất ức chế acetylcholinesterase có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hạ Huyết Áp: Hạ huyết áp là triệu chứng có thể xảy ra do sử dụng Atarax.\nAmphetamin - Atarax (Hydroxyzine Hydrochloride): Amphetamin có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Trầm Cảm: Trầm cảm là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax - Hydroxyzine Hydrochloride: Atarax chứa hoạt chất hydroxyzine hydrochloride.\nAtarax (Hydroxyzine Hydrochloride) - Khô Miệng: Atarax được sử dụng để điều trị khô miệng.\nAtarax (Hydroxyzine Hydrochloride) - Noradrenalin: Noradrenalin là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Phát Ban: Phát ban là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Metaraminol: Metaraminol là thuốc co mạch có thể dùng thay thế epinephrin khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Viêm Gan: Viêm gan là triệu chứng có thể xảy ra do sử dụng Atarax.\nA.T Desloratadin - Phát Ban: A.T Desloratadin giúp làm giảm triệu chứng phát ban.\nAtarax (Hydroxyzine Hydrochloride) - Phù: Phù là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Đau Cơ: Đau cơ là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Chảy Máu Cam: Chảy máu cam là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hen: Hen là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Huyết Khối: Huyết khối có thể xảy ra do tiêm Atarax dưới da, tiêm động mạch hay tĩnh mạch.\nA.T Desloratadin - Viêm Mũi Dị Ứng: A.T Desloratadin giúp điều trị viêm mũi dị ứng.\nAtarax (Hydroxyzine Hydrochloride) - Phù Mạch: Phù mạch là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Bí Tiểu: Bí tiểu là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Đánh Trống Ngực: Atarax được sử dụng để điều trị đánh trống ngực.\nAtarax (Hydroxyzine Hydrochloride) - Run: Run là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Co Thắt Phế Quản: Co thắt phế quản là triệu chứng có thể xảy ra do sử dụng Atarax.\nMề Đay - Thuốc Antihistamine: Thuốc antihistamine được sử dụng để điều trị mề đay.\nAtarax (Hydroxyzine Hydrochloride) - Nhìn Mờ: Nhìn mờ là triệu chứng có thể xảy ra do sử dụng Atarax.\nA.T Desloratadin - Sổ Mũi: A.T Desloratadin giúp làm giảm triệu chứng sổ mũi.\nAtarax (Hydroxyzine Hydrochloride) - Phì Đại Tuyến Tiền Liệt: Phì đại tuyến tiền liệt là tình trạng cần thận trọng khi dùng Atarax.\nA.T Desloratadin - Nghẹt Mũi: A.T Desloratadin giúp làm giảm triệu chứng nghẹt mũi.\nPhù Mạch - Thuốc Antihistamine: Thuốc antihistamine được sử dụng để điều trị phù mạch.\nAtarax (Hydroxyzine Hydrochloride) - Dị Cảm: Dị cảm là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hydroxyzin: Hydroxyzin là hoạt chất chính trong Atarax.\nA.T Desloratadin - Desloratadin: A.T Desloratadin chứa hoạt chất desloratadin.\nA.T Desloratadin - Hắt Hơi: A.T Desloratadin giúp làm giảm triệu chứng hắt hơi.\nAtarax - Chống Ngứa: Atarax được chỉ định chống ngứa (dị ứng).\nAtarax (Hydroxyzine Hydrochloride) - Bệnh Phổi Tắc Nghẽn Mạn Tính: Bệnh phổi tắc nghẽn mạn tính là tình trạng cần thận trọng khi dùng Atarax.\nA.T Desloratadin - Histamine: A.T Desloratadin ức chế histamine.\nAtarax (Hydroxyzine Hydrochloride) - Glaucom Góc Hẹp: Glaucom góc hẹp là tình trạng cần thận trọng khi dùng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Đờ Đẫn: Đờ đẫn là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Hoại Thư: Hoại thư ngón chân, tay có thể xảy ra do tiêm Atarax dưới da, tiêm động mạch hay tĩnh mạch.\nAtarax (Hydroxyzine Hydrochloride) - Tắc Nghẽn Cổ Bàng Quang: Tắc nghẽn cổ bàng quang là tình trạng cần thận trọng khi dùng Atarax.\nA.T Desloratadin - Chảy Nước Mắt: A.T Desloratadin giúp làm giảm triệu chứng chảy nước mắt.\nAtarax (Hydroxyzine Hydrochloride) - Kích Thích Nghịch Thường: Kích thích nghịch thường là triệu chứng có thể xảy ra do sử dụng Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Cảm Quang: Cảm quang là triệu chứng có thể xảy ra do sử dụng Atarax.\nA.T Desloratadin - Desloratadine: A.T Desloratadin chứa hoạt chất desloratadine.\nA.T Desloratadin - Acid Citric: Acid citric là tá dược trong A.T Desloratadin.&lt;SEP&gt;A.T Desloratadin chứa tá dược acid citric.\nAtarax (Hydroxyzine Hydrochloride) - Thuốc Opiat: Thuốc opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu có tương tác với Atarax.\nAtarax (Hydroxyzine Hydrochloride) - Tác Dụng Kháng Cholinergic: Tác dụng kháng cholinergic không được dung nạp tốt ở người cao tuổi.\nAtarax (Hydroxyzine Hydrochloride) - Thất Mạch: Thất mạch có thể gây áp xe vô khuẩn và cứng mô rõ rệt.\nA.T Desloratadin - Sucralose: Sucralose là tá dược trong A.T Desloratadin.&lt;SEP&gt;A.T Desloratadin chứa tá dược sucralose.\nA.T Desloratadin - Methyl Paraben: Methyl paraben là tá dược trong A.T Desloratadin.&lt;SEP&gt;A.T Desloratadin chứa tá dược methyl paraben.\nA.T Desloratadin - Nước Cất: A.T Desloratadin chứa tá dược nước cất.\nA.T Desloratadin - Sorbitol 70%: Sorbitol 70% là tá dược trong A.T Desloratadin.&lt;SEP&gt;A.T Desloratadin chứa tá dược sorbitol 70%.\nA.T Desloratadin - Propylen Glycol: A.T Desloratadin chứa tá dược propylen glycol.\nA.T Desloratadin - Propyl Paraben: A.T Desloratadin chứa tá dược propyl paraben.\nA.T Desloratadin - Ngứa Mũi Họng: A.T Desloratadin giúp làm giảm triệu chứng ngứa mũi họng.\nA.T Desloratadin - Nổi Mề Đay Mãn Tính: A.T Desloratadin giúp làm giảm triệu chứng nổi mề đay mãn tính.\nA.T Desloratadin - Pseudoephedrin Sulfat: A.T Desloratadin có thể dùng phối hợp với Pseudoephedrin sulfat.\nA.T Desloratadin - Đỏ Erythrosin: A.T Desloratadin chứa tá dược đỏ erythrosin.\nA.T Desloratadin - Hương Dâu: A.T Desloratadin chứa tá dược hương dâu.\nA.T Desloratadin - Dung Dịch Uống: Dung dịch uống là dạng bào chế của A.T Desloratadin.\nChống Ngứa - Clobetasol Propionate: Clobetasol propionate có tác dụng chống ngứa.']</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Thuốc Atarax (hydroxyzine hydrochloride) có thể tương tác với một số loại thuốc khác, bao gồm:
+- **Epinephrin (Adrenalin)**: Thuốc này có tương tác với Atarax.
+- **Droperidol**: Thuốc này có tương tác với Atarax.
+- **Methotrimeprazin**: Thuốc này có tương tác với Atarax.
+- **Pramlintid**: Thuốc này có tương tác với Atarax.
+- **Amphetamin**: Thuốc này có tương tác với Atarax.
+- **Thuốc kháng acetylcholin khác**: Sử dụng cùng Atarax có thể tăng thêm tác dụng.
+- **Thuốc Opiat, giảm đau, barbiturat, thuốc an thần khác, các thuốc gây tê mê hoặc rượu**: Những loại thuốc này có tương tác với Atarax.
+Ngoài ra, Atarax cũng có thể tương tác với các chất ức chế acetylcholinesterase.
+### Lưu ý khi sử dụng Atarax cùng các thuốc khác
+Nếu cần phải dùng một thuốc co mạch, thì nên dùng **noradrenalin** hoặc **metaraminol**, thay vì **epinephrin** cho người đang dùng Atarax.
+### Cách xử lý
+Việc sử dụng Atarax cùng với những loại thuốc trên cần được theo dõi chặt chẽ bởi bác sĩ để đảm bảo an toàn và hiệu quả điều trị.
+### Tài liệu tham khảo
+- [1] thuoc-atarax-hydroxyzine-hydrochloride.txt
+- [3] atorpa-e.txt</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Atarax tương tác với các thuốc như epinephrin, barbiturat, thuốc an thần khác, droperidol, pramlintid, thuốc gây tê mê, rượu, các chất ức chế acetylcholinesterase, chất giảm đau và các thuốc opiat.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8509033241428315</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9399985582834351</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Những điều kiện nào cần thiết để bảo quản thuốc Comozol tốt nhất?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>['Nhiệt Độ Môi Trường: Nhiệt độ môi trường là mức độ nóng của môi trường xung quanh, ảnh hưởng đến khả năng tỏa nhiệt của cơ thể.\nBảo Quản Thuốc: Bảo Quản Thuốc là quá trình lưu trữ thuốc đúng cách nhằm duy trì chất lượng và hiệu quả của chúng. Mỗi loại thuốc có yêu cầu bảo quản riêng biệt, từ việc kiểm soát độ ẩm, nhiệt độ và ánh sáng để tránh ảnh hưởng đến chất lượng và tính năng của thuốc. Ví dụ, thuốc như At Domperidone, ATP, Acritel, Acyclovir, Alphachymotrypsin bk 4200 Mebiphar, AlphaDHG, Alzental, Ambroxol Boston, Amepox Soft Capsule, Ampicillin Brawn, Aspirin MKP OnClickListener, Avastin, Ba đậu và disulfiram đều có yêu cầu bảo quản cụ thể. Thuốc Bentarcin cần được bảo quản ở nơi thoáng mát, tránh ánh nắng trực tiếp. Thuốc Debby cần được bảo quản tránh tiếp xúc với ánh sáng, nhiệt độ dưới 30°C và ở nơi khô ráo, thoáng mát. Thuốc Atussin cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc môi trường ẩm ướt, với nhiệt độ tốt nhất là dưới 30ºC. Thuốc Diorophyl cần được bảo quản trong bao bì gốc, nơi khô ráo, tránh ánh sáng và nhiệt độ không quá 30°C. Thuốc Atocib cần được bảo quản theo hướng dẫn trên tờ hướng dẫn sử dụng thuốc, thông thường thuốc được bảo quản ở nhiệt độ phòng, tránh ẩm và ánh nắng trực tiếp.\n\nThuốc methylprednisolone cần được bảo quản theo hướng dẫn cụ thể về nhiệt độ và thời gian sử dụng. Thuốc Acarbose cần được bảo quản ở nơi khô ráo, thoáng mát, tránh nơi ẩm ướt, nhiệt độ dưới 25°C và không sử dụng thuốc sau ngày hết hạn. Thuốc Acemuc cần chú ý đến nhiệt độ, tránh ánh sáng trực tiếp và không để thuốc tiếp xúc với nước. Thuốc Amiodarone cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30°C, tránh ánh sáng trực tiếp. Thuốc axit axetic cần được bảo quản ở nhiệt độ phòng, dưới 30oC, tránh ánh sáng trực tiếp và hơi ẩm, nhiệt độ cao. Thuốc Baclofen cũng cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30oC, tránh ánh sáng trực tiếp. Thuốc Bisacodyl yêu cầu đựng thuốc trong bao bì kín, tránh nóng, ánh sáng và ẩm, bảo quản ở nhiệt độ dưới 25 °C, tránh xa tầm tay của trẻ em, đọc kỹ hướng dẫn trước khi dùng, và không dùng thuốc có dấu hiệu ẩm mốc, thay đổi màu sắc. Thuốc Bismuth cần được bảo quản ở nhiệt độ dưới 30oC, trong bao bì kín. Thuốc Bolutin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ Celsius, tránh ánh sáng trực tiếp. Thuốc Cefpodoxim cần được bảo quản trong bao bì kín, ở nhiệt độ dưới 25 độ Celsius và tránh ánh sáng. Thuốc Ceftriaxone cần được bảo quản ở nhiệt độ dưới 25ºC, nơi khô ráo và thông thoáng. Thuốc CellCept cần được bảo quản tránh xa tầm nhìn và tầm với của trẻ em, không sử dụng sau ngày hết hạn, không lưu trữ trên 30°C, và giữ trong thùng carton để tránh ánh sáng. Thuốc Cerebrolysin cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 25°C, tránh ánh sáng trực tiếp. Thuốc Ceritine cần được bảo quản ở nơi khô ráo, thoáng mát, nhiệt độ không quá 30 độ C. Bảo quản thuốc Diane-35 cần được thực hiện dưới 30 độ Celsius, nơi khô ráo, tránh ánh sáng. Thuốc Benzalkonium Chloride cũng cần được bảo quản ở nơi khô ráo, thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt, nhiệt độ bảo quản tốt nhất là dưới 30°C.\n\nQuá trình bảo quản thuốc còn bao gồm việc lưu trữ Irbesartan đúng cách để đảm bảo an toàn và hiệu quả. Bảo quản thuốc đúng cách là rất quan trọng để duy trì chất lượng và hiệu quả của chúng, đảm bảo an toàn khi sử dụng và ngăn chặn bất kỳ sự cố nào có thể xảy ra do bảo quản không đúng cách.\nHơi Hàn: Hơi hàn là tính chất nhiệt độ của mã tiên thảo.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThời Tiết Bảo Quản: Thời tiết bảo quản yêu cầu nhiệt độ không quá 30°C, tránh ánh sáng và ẩm.\nBa Đậu: Ba đậu là một loại cây gỗ nhỡ với chiều cao trung bình từ 3 đến 6 mét, cành nhẵn và thân tròn, không có lông. Hạt của cây này được sử dụng rộng rãi như một vị thuốc trong y học cổ truyền, đặc biệt là trong nền y học Đông y. Hạt ba đậu có vỏ cứng màu nâu xám, bên trong là nhân màu trắng giàu dầu. \n\nBa đậu được biết đến với nhiều tác dụng y tế, bao gồm cả khả năng nhuận tràng rất hiệu quả, mặc dù nó cũng có độc tính. Nó được sử dụng để điều trị các triệu chứng như bụng căng đầy, ngực đau, đại tiện không thông, hàn tích, ăn không tiêu, đại tiện bí, tích trệ, lở ngứa, lác đồng tiền, viêm niêm mạc dạ dày cấp tính, và đau bụng. Ngoài ra, ba đậu còn được sử dụng để điều trị các tình trạng khác như kích thích da và niêm mạc, và chống kết tập tiểu cầu.\n\nTrong y học cổ truyền, ba đậu đã được sử dụng từ lâu đời trong dân gian để điều trị nhiều loại bệnh khác nhau. Tuy nhiên, do tính độc của nó, việc sử dụng ba đậu cần phải hết sức thận trọng và dưới sự hướng dẫn của bác sĩ hoặc thầy thuốc chuyên môn.\nThuốc Cotrimoxazol: Cotrimoxazol là thuốc cần được bảo quản đúng cách, tránh ánh sáng trực tiếp và nhiệt độ không quá 30 độ Celsius.\nBảo Quản Dược Liệu: Bảo quản dược liệu sau khi sơ chế cần được bảo quản ở những nơi khô.&lt;SEP&gt;Bảo quản dược liệu trong bọc kín, hũ nhựa hay thủy tinh, cất trữ nơi thoáng mát, tránh tiếp xúc trực tiếp với ánh nắng mặt trời.&lt;SEP&gt;Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.&lt;SEP&gt;Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ, tránh nơi ẩm mốc và ánh nắng trực tiếp.&lt;SEP&gt;Bảo quản dược liệu cần để nơi khô ráo, thông thoáng.\nÁnh Đèn Sáng: Ánh đèn sáng là yếu tố môi trường có thể làm gián đoạn giấc ngủ.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nNhiệt Độ Nước: Nhiệt độ nước là yếu tố cần kiểm soát để tránh tác hại khi tắm.\nDebby: Debby là thuốc kê đơn được sản xuất bởi Công ty TNHH Thai Nakorn Patana, với thành phần chính là nifuroxazide. Thuốc được chỉ định trong điều trị tiêu chảy cấp và mạn, bệnh lỵ trực khuẩn và chứng viêm ruột kết.&lt;SEP&gt;Debby là thuốc được sử dụng theo đơn thuốc, chống chỉ định với người mẫn cảm với thành phần và trẻ sơ sinh dưới 1 tháng tuổi.&lt;SEP&gt;Debby là loại kháng sinh chỉ được sử dụng theo đơn thuốc, không tự ý sử dụng khi chưa có chỉ định hoặc kê toa của bác sĩ.&lt;SEP&gt;Debby là thuốc được chỉ định điều trị tiêu chảy cấp và mạn, bệnh ly trực khuẩn, và viêm ruột kết.\nThời Tiết Bảo Quản Thuốc: Thời tiết bảo quản thuốc là điều kiện nhiệt độ và độ ẩm thích hợp để bảo quản thuốc.\nDidicera: Didicera là thuốc thảo dược không kê toa, thuộc công ty Cổ phần Công nghệ cao Traphaco, điều chế dưới dạng viên hoàn và viên nang.&lt;SEP&gt;Viên nang Didicera chứa thành phần độc hoạt, tế tân, tang ký sinh, quế chi, tần giao, phòng phong, cam thảo, bạch linh và đảng sâm.&lt;SEP&gt;Didicera có công năng bổ khí huyết, trừ phong thấp, bổ can thận.&lt;SEP&gt;Didicera là thuốc được điều chế dưới dạng viên nang hoặc viên hoàn, dùng đường uống.&lt;SEP&gt;Didicera là thuốc được bán với giá trung bình khoảng 40.000 VNĐ/hộp 10 gói x viên hoàn 5g.&lt;SEP&gt;Didicera là thuốc cần tham khảo ý kiến dược sĩ hoặc bác sĩ về cách dùng và liều dùng trước khi sử dụng.\nHơi Ấm: Hơi ấm là tính chất của sòi.\nDiorophyl: Diorophyl là thuốc được sử dụng để điều trị các triệu chứng về thần kinh, chứa hoạt chất piracetam.&lt;SEP&gt;Diorophyl có thể điều trị triệu chứng chóng mặt ở người lớn và các triệu chứng như suy giảm trí nhớ, kém tập trung, rối loạn hành vi, thay đổi khí sắc, sa sút trí tuệ do nhồi máu não.&lt;SEP&gt;Diorophyl là thuốc được sử dụng để điều trị các triệu chứng liên quan đến nghiện rượu, nhưng có một số tác dụng không mong muốn và chống chỉ định.&lt;SEP&gt;Diorophyl là thuốc kê đơn được sử dụng theo chỉ định của bác sĩ, với các lưu ý về liều lượng, hạn sử dụng và cách bảo quản.\nThermo Regulation: Thermo regulation là quá trình duy trì nhiệt độ cơ thể phù hợp, cần tránh tiếp xúc trực tiếp với ánh nắng mặt trời.\nIsotretinoin: Isotretinoin là một loại thuốc được kê đơn để điều trị mụn trứng cá nặng, thường được sử dụng kéo dài trong các trường hợp không đáp ứng với các phương pháp điều trị khác như thuốc kháng sinh tại chỗ. Thuốc này là thành phần chính trong các sản phẩm như Acnotin, bao gồm Acnotin 10 và Acnotin 20.\n\nIsotretinoin có tác dụng bình thường hóa lượng bã nhờn, ngăn chặn lỗ chân lông bị tắc nghẽn, giảm số lượng vi khuẩn trên da và giảm mẩn đỏ và sưng tấy. Tuy nhiên, khi sử dụng isotretinoin, cần phải thận trọng do thuốc có thể gây ra các tương tác với một số thành phần khác như Agirenyl và vitamin A trong Appeton Lysine Syrup cũng như Avi-O5. Việc sử dụng isotretinoin cùng với vitamin A có thể dẫn đến tình trạng dùng vitamin A quá liều.\n\nĐặc biệt, việc sử dụng isotretinoin trong thời kỳ mang thai có thể làm tăng nguy cơ dị tật tim bẩm sinh ở trẻ sơ sinh. Vì vậy, cần phải tránh sử dụng isotretinoin với liều cao đối với phụ nữ có thai. Isotretinoin được chỉ định trong những trường hợp mụn trứng cá nặng và có nguy cơ gây dị tật thai nhi cao.&lt;SEP&gt;Isotretinoin là thuốc điều trị da, có thể gây suy yếu sự cân bằng nước của da.&lt;SEP&gt;Isotretinoin là thuốc gây khô da và bong tróc, được cải thiện bằng cách bổ sung tinh dầu hoa anh thảo.\nĐiều Kiện Bảo Quản Thuốc: Điều kiện bảo quản thuốc bao gồm bảo quản nơi khô ráo, thoáng mát, nhiệt độ từ 15°C – 30°C, tránh ánh sáng trực tiếp.\nThiết Bị Bảo Quản Thuốc: Thiết bị bảo quản thuốc là nơi lưu trữ thuốc, cần bảo quản ở nhiệt độ dưới 30°C, tránh ánh nắng mặt trời.\nDây Gắm: Dây gắm là thảo dược được sử dụng trong bài thuốc chữa thấp khớp.&lt;SEP&gt;Dây gắm là một loài cây thân leo trườn hóa gỗ, thuộc họ Dây gắm (Gnetaceae).&lt;SEP&gt;Dây Gắm mọc tự nhiên trong rừng thường xanh, ở độ cao 200 – 1200 m, phân bố ở các tỉnh: Sapa, Hà Giang, Vĩnh Phúc (Tam Đảo), Hà Nội (Ba Vì), Quảng Trị, Đà Nẵng, Lâm Đồng, Tây Ninh, Long An, Bến Tre, An Giang, Kiên Giang (Đảo Phú Quốc).&lt;SEP&gt;Dây Gắm được sử dụng để điều trị các chứng đau nhức xương khớp, chữa phong tê thấp, hỗ trợ trong điều trị bệnh gout.&lt;SEP&gt;Dây Gắm có vị đắng, tính mát, có tác dụng giải độc, tiêu viêm, thư giãn gân cốt, hoạt huyết, sát trùng.\nCiticoline: Thuốc bổ não Citicoline là thuốc được bảo quản ở nơi khô ráo thoáng mát, tránh tiếp xúc trực tiếp với ánh sáng hoặc nơi ẩm ướt.&lt;SEP&gt;Thuốc Citicoline được sử dụng để bổ não và có tương tác với các thuốc khác như Levodopa, Meclophenoxat, Centrophenoxine.&lt;SEP&gt;Citicoline là thuốc được dùng để điều trị bệnh Alzheimer, chứng mất trí, chấn thương đầu, bệnh mạch máu não như đột quỵ, mất trí nhớ liên quan đến tuổi, bệnh Parkinson, rối loạn tăng động giảm chú ý, và bệnh tăng nhãn áp.&lt;SEP&gt;Citicoline là thuốc được sử dụng trong điều trị bệnh rối loạn mạch máu não, rối loạn nhận thức, chấn thương đầu hoặc bệnh Parkinson.\nCotrimoxazol - Thuốc Cotrimoxazol: Thuốc Cotrimoxazol cần được bảo quản đúng cách, tránh ánh sáng trực tiếp và nhiệt độ không quá 30 độ Celsius.\nBảo Quản Thuốc - Thuốc: Bảo quản thuốc là quá trình lưu trữ thuốc.\nHơi Hàn - Mã Tiên Thảo: Mã tiên thảo có tính chất hơi hàn.\nBa Đậu - Bảo Quản Thuốc: Quá trình bảo quản thuốc giúp lưu giữ Ba đậu trong điều kiện thích hợp.\nGiấc Ngủ - Ánh Đèn Sáng: Ánh đèn sáng làm gián đoạn giấc ngủ.\nBảo Quản Dược Liệu - Dược Liệu: Bảo quản dược liệu cần được thực hiện ở nơi khô ráo, thoáng mát, sạch sẽ.\nAmlor 5 Pfizer - Thermo Regulation: Đảm bảo thermo regulation để giữ nhiệt độ bảo quản thuốc Amlor 5 Pfizer dưới 30 ºC.\nBảo Quản Thuốc - Debby: Thuốc Debby cần được bảo quản đúng cách để duy trì chất lượng và an toàn.\nHơi Ấm - Sòi: Sòi có tính hơi ấm.\nBảo Quản Thuốc - Didicera: Thuốc cần được bảo quản đúng cách để đảm bảo an toàn và hiệu quả.\nBổ Phế Nam Hà - Điều Kiện Bảo Quản Thuốc: Bổ phế Nam Hà cần được bảo quản tại nơi khô ráo, thoáng mát, nhiệt độ từ 15°C – 30°C, tránh ánh sáng trực tiếp.\nBảo Quản Thuốc - Diorophyl: Thuốc Diorophyl cần được bảo quản đúng cách để duy trì chất lượng.\nAllerphast 60 mg - Thời Tiết Bảo Quản: Hướng dẫn bảo quản Allerphast 60 mg yêu cầu nhiệt độ không quá 30°C, tránh ánh sáng và ẩm.\nIsotretinoin - Thiết Bị Bảo Quản Thuốc: Isotretinoin cần được bảo quản đúng cách để đảm bảo chất lượng.\nNhiệt Độ Nước - Tắm: Nhiệt độ nước cần được kiểm soát khi tắm.\nBảo Quản Dược Liệu - Dây Gắm: Bảo quản dược liệu nơi sạch sẽ, khô ráo, thoáng mát.\nBay Hơi - Nhiệt Độ Môi Trường: Nhiệt độ môi trường cao làm giảm khả năng tỏa nhiệt qua bay hơi.\nBảo Quản Thuốc - Citicoline: Citicoline cần được bảo quản đúng cách để đảm bảo chất lượng.\nNhiệt Độ Môi Trường - Đối Lưu: Nhiệt độ môi trường cao làm giảm hiệu quả của đối lưu trong việc tỏa nhiệt.\nBảo Quản Thuốc - Disulfiram: Bảo quản thuốc là cách bảo quản disulfiram tránh khỏi tầm tay của trẻ em và thú cưng, ở nơi khô ráo thoáng mát.']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Để bảo quản thuốc Comozol một cách hiệu quả, bạn cần lưu ý những điều kiện sau:
+- **Tránh ánh sáng**: Thuốc Comozol cần được bảo quản tránh khỏi ánh sáng trực tiếp.
+- **Nhiệt độ**: Thuốc nên được bảo quản ở nhiệt độ dưới 30°C.
+- **Địa điểm**: Bảo quản thuốc ở nơi khô ráo và thoáng mát.
+Đảm bảo tuân thủ các hướng dẫn bảo quản này sẽ giúp duy trì chất lượng và hiệu quả của thuốc Comozol.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bạn cần tránh ánh sáng, bảo quản nơi khô mát và giữ thuốc ở nhiệt độ dưới 30°C để bảo quản thuốc Comozol tốt nhất.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8017506478457568</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8004376619364392</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Phải làm gì khi xuất hiện triệu chứng bất thường khi sử dụng thuốc Amitriptylin?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>['Thay Đổi Hành Vi Bất Thường: Thay đổi hành vi bất thường có thể xảy ra khi sử dụng amitriptylin.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nAn Thần Quá Mức: An thần quá mức là tác dụng phụ thường gặp khi sử dụng Amilavil.&lt;SEP&gt;An thần quá mức là tác dụng phụ của Amitriptylin.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nQuá Liều Thuốc Ameflu DAYTIME: Quá liều thuốc Ameflu DAYTIME là tình trạng cần xử lý kịp thời.\nCách Sử Dụng: Cách sử dụng và công dụng của thuốc vẫn còn nhiều vấn đề tranh cãi.&lt;SEP&gt;Cách sử dụng là quy trình hướng dẫn cách sử dụng thuốc.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách thức và thời điểm sử dụng thuốc, nhằm đảm bảo hiệu quả tối ưu và giảm thiểu rủi ro.&lt;SEP&gt;Cách sử dụng là hướng dẫn về cách dùng thuốc Ciprobay.\nRối Loạn Điều Tế: Rối loạn điều tế là tác dụng phụ thường gặp khi sử dụng Amilavil.\nHướng Dẫn Sử Dụng: Hướng Dẫn Sử Dụng là một loại tài liệu cung cấp thông tin chi tiết về cách sử dụng nhiều sản phẩm khác nhau, bao gồm cả thuốc và các sản phẩm y tế khác. Tài liệu này không chỉ giới thiệu cách sử dụng sản phẩm mà còn cung cấp thông tin về việc sử dụng chúng một cách an toàn và hiệu quả. Người dùng được khuyến nghị đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào được đề cập. Thông tin trong Hướng Dẫn Sử Dụng giúp đảm bảo rằng người dùng hiểu rõ cách thức hoạt động của sản phẩm, cách sử dụng nó một cách chính xác, và những lưu ý cần thiết liên quan đến việc sử dụng sản phẩm đó.\n\nHướng Dẫn Sử Dụng cũng chứa thông tin về cách xử lý khi quên liều thuốc và cách bảo quản thuốc đúng cách. Điều này đảm bảo rằng sản phẩm luôn ở trạng thái tốt nhất và có thể được sử dụng một cách hiệu quả và an toàn. Tài liệu này cũng bao gồm các hướng dẫn về cách bảo quản sản phẩm, từ việc bảo quản thuốc đến việc bảo quản các sản phẩm khác như Ampelop. Hướng dẫn sử dụng không chỉ giới hạn ở việc sử dụng thuốc mà còn cung cấp thông tin về việc sử dụng và bảo quản các sản phẩm y tế khác.\n\nMột số sản phẩm cụ thể được đề cập trong Hướng Dẫn Sử Dụng bao gồm Aibezym, Algelstad, Alputine, Alzental, Ambroco, Arthrorein Pharmanel, Aspirin Vidipha, Augtipha, Babi B.O.N., Baby Septol, Bạch Long Thủy, Children’s Tylenol, Chlorocina-H, Cholapan, Ciacca, và Dentanalgi. Người dùng được yêu cầu tuân thủ liều lượng và thời gian sử dụng đúng theo chỉ định của nhân viên y tế. Việc đọc kỹ Hướng Dẫn Sử Dụng trước khi bắt đầu sử dụng bất kỳ sản phẩm nào là rất quan trọng để đảm bảo an toàn và hiệu quả trong quá trình sử dụng.&lt;SEP&gt;Hướng dẫn sử dụng cung cấp thông tin về cách bảo quản và sử dụng thuốc Bisacodyl.&lt;SEP&gt;Tờ hướng dẫn sử dụng cung cấp hướng dẫn về cách dùng dụng cụ hít Bricanyl.&lt;SEP&gt;Hướng dẫn sử dụng là thông tin cần đọc kỹ trước khi dùng Carbomango.&lt;SEP&gt;Đọc hướng dẫn sử dụng trước khi dùng Advil.\nTriệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nNgừng Sử Dụng Thuốc: Ngừng sử dụng thuốc là biện pháp xử trí khi gặp tác dụng phụ của thuốc Agi-Calci.&lt;SEP&gt;Ngừng sử dụng Cholapan khi nhận thấy dấu hiệu bất thường.&lt;SEP&gt;Ngừng sử dụng thuốc là phương pháp xử lý khi có kích ứng tại chỗ hoặc tác dụng phụ nghiêm trọng.\nTư Vấn Cụ Thể: Tư vấn cụ thể của bác sĩ/dược sĩ về việc sử dụng Amilavil.\nThuốc Quá Liều: Thuốc quá liều có thể gây triệu chứng bất thường.&lt;SEP&gt;Thuốc quá liều là việc sử dụng thuốc vượt quá liều lượng khuyến cáo.\nTổng hợp triệu chứng bất thường: Triệu chứng bất thường có thể xảy ra khi dùng quá liều Alzole TvPharm.\nTriệu Chứng Bất Thường: Triệu chứng bất thường là các dấu hiệu hoặc triệu chứng không bình thường có thể xuất hiện khi sử dụng nhiều loại thuốc khác nhau. Các triệu chứng này bao gồm hành vi lạ như vỗ tay, cắn tay, giảm khả năng giao tiếp bằng mắt, và cắn quần áo, đặc biệt là ở trẻ em bị bệnh tim bẩm sinh khi sử dụng một số loại thuốc cụ thể như Contractubex hoặc Clindamycin. Triệu chứng bất thường cũng có thể liên quan đến việc sử dụng nhiều loại thuốc khác nhau, bao gồm Acemol 325 mg, Agi-Calci, Agilosart, Agifuros, Alphachymotrypsin 4200 Mebiphar, AlphaDHG, Alputine, Alzole, Ambroxol, Amiparen 5 Otsuka, Amlodipin Domesco, Amoxicillin Mekophar, thuốc Ampelop, Atiliver, axit glutamic, Adrenoxyl 10 mg, Bluemint, Bofit F, Cadifast 120, Citicoline, Calcium Boston, Cenditan, Cefuroxim, Cerecaps, Bromelain, và Chlorocina-H. Ngoài ra, các triệu chứng bất thường cũng có thể xuất hiện khi sử dụng các thuốc như Cotrimstada Forte, Danospan, Adagrin, Betadine, Cetirizine, Biosubtyl, kem Biafine, Bixicam, Albis, BoniDiabet, và Berberin. Việc phát hiện sớm các triệu chứng bất thường rất quan trọng để được điều trị kịp thời và tránh các biến cố y tế nghiêm trọng, đặc biệt là ở trẻ em.\n\nTriệu chứng bất thường cũng có thể liên quan đến việc sử dụng axit nalidixic và Alaxan, cũng như thuốc B Complex C và Aluvia. Hội chứng rối loạn sinh tủy cũng có thể gây ra triệu chứng bất thường cần được bác sĩ thăm khám. Khi gặp phải triệu chứng bất thường, người bệnh nên thông báo ngay lập tức cho bác sĩ hoặc nhân viên y tế để có thể xử lý và hỗ trợ kịp thời. Báo cáo những triệu chứng này giúp đảm bảo sức khỏe của người dùng thuốc và ngăn chặn các biến cố y tế có thể xảy ra.\n\nNgoài ra, triệu chứng bất thường có thể xuất hiện khi sử dụng thuốc Broncho-Vaxom, Candesartan, captopril, Carbogast, và Ceftriaxone. Đặc biệt, việc dùng quá liều Acetazolamid, Carbogast, và Cimetidin cũng có thể gây ra triệu chứng bất thường. Trong mọi trường hợp, việc báo cáo kịp thời về các triệu chứng bất thường là rất quan trọng để được xử lý đúng cách và tránh các biến cố y tế nghiêm trọng.\n\nTriệu chứng bất thường cũng có thể xuất hiện khi sử dụng Benzalkonium Chloride, Thuốc Bar, và vượt liều điều trị. Triệu chứng bất thường cũng có thể liên quan đến các bệnh lý tử cung, cần được khám với bác sĩ để tìm nguyên nhân và điều trị kịp thời.&lt;SEP&gt;Triệu chứng bất thường liên quan đến túi tinh và tinh trùng cần được kiểm tra bởi bác sĩ chuyên khoa.\nThay Đổi Điện Tâm Đồ: Thay đổi điện tâm đồ là tác dụng phụ của Amitriptylin.\nAcritel: Thuốc Acritel là sản phẩm của Công ty Cổ phần Dược phẩm Đạt Vi Phú (Davipharm), chứa Levocetrizin dihydroclorid, dùng để điều trị triệu chứng liên quan đến dị ứng.&lt;SEP&gt;Thuốc Acritel có thành phần chính là Levocetrizin dihydroclorid, dùng điều trị triệu chứng các tình trạng dị ứng.&lt;SEP&gt;Acritel là thuốc có thể tương tác với một số thuốc khác và có các tác dụng phụ.&lt;SEP&gt;Acritel là thuốc có hướng dẫn sử dụng cụ thể, bao gồm việc không uống gấp đôi liều nếu bỏ lỡ một liều và cần tham khảo ý kiến bác sĩ hoặc dược sĩ nếu muốn ngừng thuốc sớm.&lt;SEP&gt;Thuốc Acritel được sử dụng trong điều trị các bệnh lý liên quan, cần điều chỉnh liều lượng dựa trên mức độ suy thận của bệnh nhân.&lt;SEP&gt;Thuốc Acritel chứa Levocetirizin, gây buồn ngủ và suy nhược.\nNgừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.&lt;SEP&gt;Ngừng dùng thuốc là việc dừng việc sử dụng thuốc khi gặp các dấu hiệu không mong muốn.&lt;SEP&gt;Ngừng dùng thuốc Amiodarone khi gặp các triệu chứng quá liều.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nYếu Mệt: Yếu mệt là triệu chứng của quá liều Amilavil.&lt;SEP&gt;Yếu mệt là triệu chứng của quá liều Amitriptylin.\nAmiodarone - Ngừng Dùng Thuốc: Khi gặp các triệu chứng quá liều, bạn nên ngừng dùng thuốc Amiodarone và lập tức đến cơ sở y tế gần nhất.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nAmitriptylin - An Thần Quá Mức: An thần quá mức là tác dụng phụ của Amitriptylin.\nCách Sử Dụng - Thuốc: Thuốc đi kèm hướng dẫn cách sử dụng.\nAmitriptylin - Yếu Mệt: Yếu mệt là triệu chứng của quá liều Amitriptylin.\nHướng Dẫn Sử Dụng - Ngừng Sử Dụng Thuốc: Hướng dẫn dừng sử dụng thuốc khi có tác dụng phụ nghiêm trọng.\nAmitriptylin - Thay Đổi Hành Vi Bất Thường: Thay đổi hành vi bất thường có thể là tác dụng phụ của amitriptylin.\nThuốc Quá Liều - Triệu Chứng Bất Thường: Triệu chứng bất thường có thể xảy ra khi sử dụng thuốc quá liều.\nAmitriptylin - Thay Đổi Điện Tâm Đồ: Thay đổi điện tâm đồ là tác dụng phụ của Amitriptylin.\nAcritel - Tác Dụng Phụ: Thuốc Acritel có hướng dẫn sử dụng cụ thể về cách xử lý tác dụng phụ.\nAmilavil - An Thần Quá Mức: An thần quá mức là tác dụng phụ thường gặp khi sử dụng Amilavil.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nAmilavil - Yếu Mệt: Yếu mệt là triệu chứng của quá liều Amilavil.\nThuốc Điều Trị - Tác Dụng Phụ: Thuốc điều trị có thể có tác dụng phụ nhưng thường không đáng kể với hầu hết bệnh nhân.\nAmilavil - Rối Loạn Điều Tế: Rối loạn điều tế là tác dụng phụ thường gặp khi sử dụng Amilavil.\nthuốc - tờ hướng dẫn sử dụng thuốc: Tờ hướng dẫn sử dụng thuốc cung cấp thông tin chi tiết về cách sử dụng thuốc một cách hiệu quả.\nAmilavil - Tư Vấn Cụ Thể: Sử dụng Amilavil cần tư vấn cụ thể của bác sĩ/dược sĩ.\nHướng Dẫn Sử Dụng - Tác Dụng Phụ Nghiêm Trọng: Hướng dẫn xử lý tác dụng phụ nghiêm trọng khi sử dụng Ciacca.\nPregabalin - Triệu Chứng Cai Thuốc: Triệu chứng cai thuốc là triệu chứng sau khi dừng điều trị Pregabalin.\nChuyên Gia Y Tế - Tác Dụng Phụ: Người dùng cần liên hệ với chuyên gia y tế để được tư vấn hướng xử trí khi gặp tác dụng phụ.\nAmpicillin Mekophar - Ngừng Dùng Thuốc: Ngừng dùng thuốc là biện pháp xử lý khi quá liều ampicillin.\nAmeflu DAYTIME - Quá Liều Thuốc Ameflu DAYTIME: Khi xảy ra quá liều thuốc Ameflu DAYTIME, cần xử lý kịp thời.\nLiệt Kê - Ngừng Dùng Thuốc: Khi gặp các dấu hiệu liệt kê, cần ngừng dùng thuốc.\nLên Cơ Sở Y Tế - Ngừng Dùng Thuốc: Sau khi ngừng dùng thuốc, cần lên cơ sở y tế để được xử lý kịp thời.']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Amitriptylin và xuất hiện các triệu chứng bất thường, bạn cần thực hiện các bước sau:
+1. **Dừng Sử Dụng Thuốc**: Nếu gặp tác dụng phụ nghiêm trọng, cần ngừng sử dụng thuốc ngay lập tức.
+2. **Lên Cơ Sở Y Tế**: Sau khi ngừng sử dụng thuốc, cần đến cơ sở y tế gần nhất để được xử lý kịp thời.
+3. **Thông Báo Cho Bác Sĩ**: Báo cáo tất cả các triệu chứng bất thường cho bác sĩ hoặc nhân viên y tế để họ có thể đánh giá tình trạng và đưa ra hướng xử lý phù hợp.
+Triệu chứng bất thường có thể bao gồm thay đổi hành vi bất thường, thay đổi điện tâm đồ, rối loạn điều tế, yếu mệt, và các triệu chứng khác như an thần quá mức.
+### Các Triệu Chứng Bất Thường Có Thể Xuất Hiện Khi Sử Dụng Amitriptylin
+- **Thay đổi hành vi bất thường**: Có thể xảy ra khi sử dụng amitriptylin.
+- **Thay đổi điện tâm đồ**: Là tác dụng phụ của amitriptylin.
+- **Rối loạn điều tế**: Là tác dụng phụ thường gặp khi sử dụng Amilavil.
+- **Yếu mệt**: Là triệu chứng của quá liều amitriptylin.
+### Xử Lý Khi Xảy Ra Triệu Chứng Bất Thường
+Khi gặp triệu chứng bất thường, cần tuân theo các hướng dẫn sau:
+- **Dừng sử dụng thuốc**: Ngừng sử dụng thuốc ngay lập tức.
+- **Đến cơ sở y tế**: Đến cơ sở y tế gần nhất để được xử lý kịp thời.
+- **Thông báo cho bác sĩ**: Báo cáo tình trạng cho bác sĩ hoặc nhân viên y tế.
+### Tham Khảo
+- **Thuốc Amitriptylin**: Thuốc Amitriptylin có thể gây ra nhiều tác dụng phụ, trong đó có triệu chứng bất thường.
+### Tham Khảo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cần gọi ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8514944654135403</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.9628736163283851</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nên lưu ý gì khi sử dụng thuốc Coversyl Plus với những người bị suy gan, suy thận?</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>['Bệnh Não Do Gan: Bệnh não do gan là tình trạng sức khỏe cần ngừng sử dụng Coversyl Plus.&lt;SEP&gt;Bệnh não do gan là bệnh cần ngưng dùng Coversyl Plus.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nTăng Nồng Độ Kali: Tăng nồng độ kali huyết thanh là tác dụng phụ khi dùng Coversyl Plus cùng với thuốc lợi tiểu giữ kali.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nNồng Độ Creatinin: Nồng độ creatinin cần được theo dõi khi sử dụng Beatil ở người cao tuổi và người bị suy giảm chức năng thận.&lt;SEP&gt;Nồng độ creatinin trong huyết thanh được kiểm tra để loại trừ suy thận.&lt;SEP&gt;Nồng độ creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nRối Loạn Muối Và Nước: Rối loạn muối và nước là triệu chứng của quá liều Coversyl Plus.&lt;SEP&gt;Rối loạn muối và nước là biểu hiện nặng hơn của quá liều Coversyl Plus.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nNgười Bị Suy Gan, Suy Thận: Người bị suy gan hay suy thận là đối tượng cần thận trọng khi sử dụng Combigan.\nSuy Giảm Hô Hấp: Suy giảm hô hấp là tình trạng cần thận trọng khi dùng thuốc.&lt;SEP&gt;Suy giảm hô hấp là một tình trạng mà cần thận trọng khi sử dụng thuốc Atussin.&lt;SEP&gt;Suy giảm hô hấp là một triệu chứng khi phản xạ tự động bị rối loạn.&lt;SEP&gt;Suy giảm hô hấp là tình trạng bệnh nhân cần thận trọng khi sử dụng thuốc.&lt;SEP&gt;Suy giảm hô hấp có thể xảy ra khi dùng Chlorpheniramine ở người bị bệnh phổi tắc nghẽn.\nĐể Xa Tầm Với: Coversyl Plus cần được bảo quản xa tầm với của trẻ em.\nCoversyl Plus - Tiêu Chảy: Coversyl Plus có thể gây tiêu chảy.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nBuồn Nôn - Coversyl Plus: Coversyl Plus có thể gây buồn nôn.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nChóng Mặt - Coversyl Plus: Coversyl Plus có thể gây chóng mặt.\nSuy Giảm Hô Hấp - Thận: Bệnh nhân có nguy cơ hoặc đang bị suy giảm hô hấp cần thận trọng khi sử dụng thuốc.\nCoversyl Plus - Táo Bón: Coversyl Plus có thể gây táo bón.\nAgimfast 60 - Suy Thận: Thận trọng và điều chỉnh liều thích hợp khi dùng thuốc cho người suy thận.\nCoversyl Plus - Đau Đầu: Coversyl Plus có thể gây đau đầu.\nBảo Vệ Gan - Thuốc: Khi sử dụng thuốc, cần hỏi ý kiến bác sĩ về tác dụng có hại đối với gan.\nCoversyl Plus - Tăng Huyết Áp: Coversyl Plus được chỉ định dùng để điều trị tăng huyết áp.\nClindamycin - Người Bệnh Suy Gan: Thận trọng đối với người bệnh suy gan khi dùng Clindamycin.\nCoversyl Plus - Suy Thận: Người suy thận cần thận trọng khi sử dụng Coversyl Plus.&lt;SEP&gt;Người suy thận cần thận trọng khi dùng Coversyl Plus.\nCombigan - Người Bị Suy Gan, Suy Thận: Combigan cần được sử dụng thận trọng ở người bị suy gan hay suy thận.\nCoversyl Plus - Mệt Mỏi: Mệt mỏi là triệu chứng của quá liều Coversyl Plus.&lt;SEP&gt;Coversyl Plus có thể gây mệt mỏi.\nBồ Công Anh - Thận Trọng Khi Sử Dụng: Thận trọng khi sử dụng Bồ công anh để tránh tác dụng phụ.\nCoversyl Plus - Nôn: Nôn là triệu chứng của quá liều Coversyl Plus.\nAzicine - Suy Chức Năng Gan: Azicine cần thận trọng khi sử dụng cho bệnh nhân suy chức năng gan.\nCoversyl Plus - Ho: Coversyl Plus có thể gây ho.\nNhôm Phosphat - Thận Trọng: Thận trọng khi dùng nhôm phosphat trong trường hợp suy thận mạn tính.\nCoversyl Plus - Khó Thở: Coversyl Plus có thể gây khó thở.\nCoversyl Plus - Suy Gan: Người suy gan cần thận trọng khi sử dụng Coversyl Plus.&lt;SEP&gt;Người suy gan cần thận trọng khi dùng Coversyl Plus.\nCoversyl Plus - Hạ Huyết Áp: Coversyl Plus được chỉ định để điều trị hạ huyết áp.&lt;SEP&gt;Coversyl Plus có thể gây hạ huyết áp.\nCoversyl Plus - Rối Loạn Tiêu Hóa: Coversyl Plus có thể gây rối loạn tiêu hóa.\nCoversyl Plus - Phụ Nữ Mang Thai: Phụ nữ mang thai không nên dùng Coversyl Plus.\nAmlodipin - Coversyl Plus: Coversyl Plus được so sánh với thuốc Amlodipin trong bài viết.\nQuá Liều - Rối Loạn Muối Và Nước: Quá liều Coversyl Plus có thể gây rối loạn muối và nước.\nBuồn Ngủ - Coversyl Plus: Buồn ngủ là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Trẻ Em: Trẻ em là đối tượng không nên sử dụng Coversyl Plus.\nCoversyl Plus - Khô Miệng: Coversyl Plus có thể gây khô miệng.\nCoversyl Plus - Perindopril: Perindopril là một trong hai hoạt chất chính của Coversyl Plus.\nCoversyl Plus - Đau Họng: Coversyl Plus có thể gây đau họng.\nAllopurinol - Coversyl Plus: Allopurinol có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Ù Tai: Coversyl Plus có thể gây ù tai.\nBaclofen - Coversyl Plus: Baclofen có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Giảm Bạch Cầu: Allopurinol, eytostatic hoặc các thuốc hỗ trợ miễn dịch, các corticosteroid tổng hợp hoặc procainamid có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Người Cao Tuổi: Người cao tuổi là đối tượng sử dụng Coversyl Plus.\nCoversyl Plus - Phản Ứng Dị Ứng: Coversyl Plus có thể gây phản ứng dị ứng.\nNồng Độ Creatinin - Thiếu Máu Não: Kiểm tra nồng độ creatinin trong huyết thanh có thể giúp loại trừ suy thận như nguyên nhân của thiếu máu não.\nCoversyl Plus - Rối Loạn Tâm Thần: Rối loạn tâm thần là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Hạ Kali Máu: Coversyl Plus có thể gây hạ kali máu.\nCoversyl Plus - Người Lớn: Người lớn là đối tượng sử dụng Coversyl Plus.\nCoversyl Plus - Ngất Xỉu: Ngất xỉu là triệu chứng của quá liều Coversyl Plus.\nChuột Rút - Coversyl Plus: Chuột rút là triệu chứng của quá liều Coversyl Plus.&lt;SEP&gt;Coversyl Plus có thể gây chuột rút.\nBệnh Nhân Suy Gan - Rosuvastatin: Bệnh nhân suy gan bị chống chỉ định khi sử dụng Rosuvastatin.\nCoversyl Plus - Rối Loạn Vị Giác: Coversyl Plus có thể gây rối loạn vị giác.\nCoversyl Plus - Thanh Thải Creatinin: Thanh thải creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Procainamid: Procainamid có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Nhịp Tim Bất Thường: Coversyl Plus có thể gây nhịp tim bất thường.\nCoversyl Plus - Lithi: Lithi có thể gây tương tác với Coversyl Plus, làm tăng nồng độ lithi và nguy cơ độc hại.\nCoversyl Plus - Thuốc Chống Viêm Không Steroid: Thuốc chống viêm không steroid có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Thuốc Gây Mê: Thuốc gây mê có thể tăng tác dụng hạ huyết áp của Coversyl Plus.\nBeatil - Nồng Độ Creatinin: Nồng độ creatinin cần được theo dõi khi sử dụng Beatil ở người cao tuổi và người bị suy giảm chức năng thận.\nCoversyl Plus - Hạ Huyết Áp Quá Mức: Thuốc hạ huyết áp khác có thể làm tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nCoversyl Plus - Nhạy Cảm Ánh Sáng: Coversyl Plus có thể gây nhạy cảm ánh sáng.&lt;SEP&gt;Nhạy cảm ánh sáng là triệu chứng cần ngưng dùng Coversyl Plus.\nBệnh Nhân Suy Gan - Coversyl Plus: Bệnh nhân suy gan là đối tượng cần điều chỉnh liều dùng Coversyl Plus.\nBệnh Nhân Suy Thận - Coversyl Plus: Bệnh nhân suy thận là đối tượng cần điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Nồng Độ Kali: Nồng độ kali là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nCoversyl Plus - Indapamide: Indapamide là một trong hai hoạt chất chính của Coversyl Plus.\nCoversyl Plus - Thuốc Lợi Tiểu Giữ Kali: Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.\nCoversyl Plus - Vàng: Vàng có thể gây phản ứng nitritoid khi dùng cùng Coversyl Plus.\nCoversyl Plus - Nồng Độ Creatinin: Nồng độ creatinin là xét nghiệm cần thực hiện để điều chỉnh liều dùng Coversyl Plus.\nAxit Acetylsalicylic - Coversyl Plus: Axit acetylsalicylic có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Rối Loạn Muối Và Nước: Rối loạn muối và nước là triệu chứng của quá liều Coversyl Plus.\nCoversyl Plus - Sưng Phù Mặt: Coversyl Plus có thể gây sưng phù mặt.\nCoversyl Plus - Thuốc Corticosteroid: Thuốc corticosteroid có thể làm giảm tác dụng hạ huyết áp của Coversyl Plus.\nCoversyl Plus - Thuốc Lợi Tiểu (Nhóm Thiazide Hoặc Lợi Tiểu Quai): Thuốc lợi tiểu (nhóm thiazide hoặc lợi tiểu quai) có thể làm giảm thể tích tuần hoàn và gây nguy cơ hạ huyết áp khi dùng cùng Coversyl Plus.\nCoversyl Plus - Tia UVA: Người dùng Coversyl Plus cần tránh tiếp xúc với tia UVA.\nBệnh Não Do Gan - Coversyl Plus: Coversyl Plus có thể gây bệnh não do gan.&lt;SEP&gt;Bệnh não do gan là bệnh cần ngưng dùng Coversyl Plus.\nCoversyl Plus - Tăng Nồng Độ Kali: Thuốc lợi tiểu giữ kali có thể làm tăng đáng kể nồng độ kali huyết thanh khi dùng cùng Coversyl Plus.\nCoversyl Plus - Để Xa Tầm Với: Coversyl Plus cần được bảo quản xa tầm với của trẻ em.\nCoversyl Plus - Phụ Nữ Có Kế Hoạch Mang Thai: Phụ nữ có kế hoạch mang thai không nên dùng Coversyl Plus.\nCoversyl Plus - Thuốc Chống Trầm Cảm Giống Imipramine: Thuốc chống trầm cảm giống imipramine có thể tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nCoversyl Plus - Thuốc Hạ Huyết Áp Khác: Thuốc hạ huyết áp khác có thể làm tăng nguy cơ hạ huyết áp quá mức khi dùng cùng Coversyl Plus.\nCoversyl Plus - Eytostatic: Eytostatic có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Thuốc Hỗ Trợ Miễn Dịch: Thuốc hỗ trợ miễn dịch có thể tăng nguy cơ giảm bạch cầu khi dùng cùng Coversyl Plus.\nCoversyl Plus - Giữ Nơi Khô Thoáng: Coversyl Plus cần được bảo quản ở nơi khô thoáng.\nCoversyl Plus - Dưới 30°C: Coversyl Plus cần được bảo quản ở nhiệt độ dưới 30°C.\nCoversyl Plus - Thạc Sĩ, Dược Sĩ Trương Văn Đạt: Thạc Sĩ, Dược Sĩ Trương Văn Đạt đã chia sẻ thông tin về Coversyl Plus.\nBetahistine - Bệnh Nhân Suy Gan: Betahistine cần thận trọng khi dùng cho bệnh nhân suy gan.\nCoversyl - Sưng Phù Mặt: Sưng phù mặt là tác dụng phụ hiếm gặp khi sử dụng Coversyl.\nAlsiful S.R - Bệnh Nhân Suy Gan: Bệnh nhân suy gan là đối tượng chống chỉ định dùng thuốc Alsiful S.R.\nCoAprovel - Tăng Ure Huyết, Creatinine và Creatin Kinase: Tăng ure huyết, creatinine và creatin kinase là một tác dụng phụ của CoAprovel.\nBệnh Nhân Suy Gan - Cilzec: Bệnh nhân suy gan cần theo dõi chặt chẽ khi sử dụng Cilzec.\nBilastine - Bệnh Nhân Suy Gan: Bilastine không cần điều chỉnh liều dùng trên bệnh nhân suy gan.']</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Khi sử dụng thuốc Coversyl Plus, người bệnh suy gan và suy thận cần đặc biệt lưu ý:
+- **Người suy gan**: Cần thận trọng khi sử dụng Coversyl Plus. Bệnh nhân suy gan nặng không nên dùng thuốc này. Với bệnh nhân suy gan vừa, không cần hiệu chỉnh liều nhưng cần theo dõi chặt chẽ.
+- **Người suy thận**: Cần điều chỉnh liều theo chỉ định của bác sĩ và theo dõi định kỳ nồng độ creatinin và kali huyết thanh. Coversyl Plus chống chỉ định dùng trên bệnh nhân suy thận nặng và vừa (độ thanh thải creatinin dưới 60ml/phút).</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thận trọng dùng thuốc Coversyl Plus ở người suy gan, suy thận.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.838255330585881</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8345638326214703</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong những trường hợp nào khác?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>['Rối Loạn Khó Tiêu: Rối loạn khó tiêu là tình trạng mà Argide hỗ trợ điều trị.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nBệnh Lý Về Gan: Bệnh lý về gan là các tình trạng bệnh liên quan đến gan được hỗ trợ điều trị bằng Argide.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nPhân Thủy: Phân thủy là tác dụng phụ khi dùng Argadin.\ndược sĩ: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTình Trạng Cương Dương: Tình trạng cương dương có thể xảy ra là tác dụng phụ khi dùng Argadin.\nthuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nTổng Hợp: Tổng hợp là cách xử lý khi quên một liều Argide.\nDược Sĩ: Dược Sĩ là chuyên gia tư vấn sử dụng thuốc an toàn và hiệu quả. Họ cung cấp hướng dẫn cụ thể cho bệnh nhân về cách sử dụng các loại thuốc khác nhau, bao gồm cả việc tư vấn về Actiso Ladophar, Baby Septol, Bagocit, Belara và Calcium Boston. Dược sĩ không chỉ giới thiệu thông tin chi tiết về từng sản phẩm mà còn hỗ trợ bệnh nhân trong việc hiểu rõ cách sử dụng chúng một cách an toàn và hiệu quả nhất. \n\nNgoài ra, Dược Sĩ cũng là người tư vấn cách xử lý thuốc không còn sử dụng. Họ có chuyên môn về thuốc và hướng dẫn sử dụng thuốc, đồng thời cung cấp tư vấn về thuốc. Khi bệnh nhân sử dụng Boganic, Dược Sĩ sẽ được thông báo về tình trạng của họ để có thể đưa ra những lời khuyên phù hợp. \n\nDược sĩ cũng là người chuyên môn trong việc tư vấn và quản lý thuốc. Họ có kiến thức sâu rộng về thuốc và có thể tư vấn về việc sử dụng thuốc một cách hiệu quả và an toàn. Ví dụ, Dược sĩ Nguyễn Hoàng Bảo Duy là một chuyên gia về dược phẩm và thuốc, với khả năng tư vấn và hỗ trợ bệnh nhân trong việc sử dụng thuốc đúng cách.\nTăng Ammoniac Huyết: Tăng ammoniac huyết là tác dụng phụ của thuốc Argide, đặc biệt ở người có nhiễm acid hữu cơ trong máu.&lt;SEP&gt;Tăng ammoniac huyết là tình trạng mà arginin được chỉ định để điều trị.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nArgide: Thuốc Argide được bào chế dưới dạng viên nang cứng hoặc mềm chứa 200 mg hoạt chất Arginine, được sử dụng để điều trị bệnh lý tăng Amoniac máu và hỗ trợ điều trị rối loạn tiêu hóa.&lt;SEP&gt;Thuốc Argide được sử dụng để điều trị bệnh lý tăng Amoniac máu và hỗ trợ các rối loạn khó tiêu.&lt;SEP&gt;Argide là thuốc có chống chỉ định cho những người có tiền sử dị ứng với thành phần của thuốc, tăng amoniac huyết, rối loạn chu trình ure và thiếu hụt enzym arginase. Argide có thể gây tác dụng liên quan đến thần kinh như chóng mặt và có thể gây đau bụng, tiêu chảy khi dùng quá liều.&lt;SEP&gt;Thuốc Argide có tác dụng phụ như buồn nôn, nôn ói, nhức đầu và có thể tương tác với các thuốc khác như Thiazid, Xylitol, Aminophyllin, Sulfonylurea, và Spironolacton.&lt;SEP&gt;Argide là thuốc được sản xuất dưới dạng viên nang, dùng hỗ trợ các bệnh lý về gan.\nbác sĩ: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArginine Hydrochloride: Arginine hydrochloride là hoạt chất chính trong Argide, giúp ổn định nồng độ Arginine trong máu và ngăn chặn sự tăng Amoniac huyết.\nNhân Viên Y Tế: Nhân viên y tế là người thực hiện nhiều nhiệm vụ khác nhau trong lĩnh vực y tế. Họ có trách nhiệm truyền dịch và theo dõi tình trạng của bệnh nhân. Nhân viên y tế cũng có chuyên môn để xử lý các trường hợp quá liều, đồng thời kiểm soát việc sử dụng Becozyme một cách hiệu quả. Bên cạnh đó, họ còn đóng vai trò hướng dẫn bệnh nhân về cách sử dụng thuốc đúng cách, hỗ trợ và tư vấn trong suốt quá trình sử dụng thuốc. Nhân viên y tế cũng là những chuyên gia trong ngành y tế, cung cấp tư vấn chi tiết về việc sử dụng thuốc, đảm bảo rằng bệnh nhân nhận được sự chăm sóc sức khỏe tốt nhất. Ngoài ra, họ còn tư vấn về việc sử dụng thuốc Atocib 90, góp phần quan trọng vào việc điều trị và chăm sóc sức khỏe cho bệnh nhân.&lt;SEP&gt;Nhân viên y tế là những người làm việc tại phòng cấp cứu.&lt;SEP&gt;Nhân viên y tế là người theo dõi và chăm sóc bệnh nhân mắc bệnh tay chân miệng.&lt;SEP&gt;Nhân viên y tế có nguy cơ bị nhiễm bệnh sốt Lassa khi chăm sóc bệnh nhân.\nThông Báo Bác Sĩ: Cần thông báo cho bác sĩ về tình trạng sức khỏe khi sử dụng thuốc Agi-Calci.\nBệnh: Bệnh là thuật ngữ chung chỉ tình trạng sức khỏe không tốt, cần được điều trị. Bệnh có thể là kết quả của nhiều yếu tố khác nhau và có thể gây ra lo lắng, đặc biệt là đối với những người chưa có con. Bệnh có thể được phát hiện và điều trị kịp thời nếu nhận thấy dấu hiệu bất thường. Một số bệnh có tiên lượng khá tốt, với khoảng 90% người bệnh được chữa khỏi chỉ bằng kháng sinh và không còn để lại di chứng. Tuy nhiên, cũng có một số bệnh chưa được mô tả cụ thể và có thể tái phát nếu ngừng thuốc sớm.\n\nBệnh có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng các loại thảo dược như cây Đại, Cần Tây, cây Bòng Bong, lá dứa, dền gai, hoa đậu biếc, và hồi đầu thảo. Thông tin về tác dụng của một số loại cây này chưa có nhiều nghiên cứu khoa học rõ ràng. Bệnh có thể xảy ra khi pH nước bọt chệch khỏi phạm vi lý tưởng trong một thời gian dài.\n\nBệnh cũng có thể được điều trị bằng Lô căn hoặc Tiền. Bệnh là tình trạng sức khỏe không bình thường và có thể được theo dõi và điều trị tại nhà nếu nhẹ. Bệnh có thể gây ra triệu chứng ngứa và nổi mề đay.\n\nTóm lại, bệnh là tình trạng sức khỏe không tốt cần được điều trị, có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng các loại thảo dược và dược liệu, cũng như các phương pháp điều trị khác như Lô căn và Tiền.&lt;SEP&gt;Bệnh là thuật ngữ chung để chỉ các trạng thái bệnh lý.&lt;SEP&gt;Bệnh cần được đánh giá tình trạng thông qua các xét nghiệm và kiểm tra y tế.&lt;SEP&gt;Bệnh là tình trạng sức khỏe bất thường cần được điều trị.&lt;SEP&gt;Bệnh là tình trạng mà việc rửa tay kỹ có thể giúp ngăn ngừa.\nThuốc Động Kinh: Thuốc động kinh là các loại thuốc được sử dụng để điều trị động kinh.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nSử Dụng: Sử dụng cúc tần cần thận trọng và tham khảo ý kiến bác sĩ.\nTùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc mà không tham khảo ý kiến chuyên gia.\nArgide - Tiêu Chảy: Argide có thể gây tiêu chảy khi dùng quá liều.&lt;SEP&gt;Khi sử dụng Argide, cần chú ý đến triệu chứng tiêu chảy.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nArgide - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp khi sử dụng Argide.&lt;SEP&gt;Buồn nôn là tác dụng phụ thường gặp của thuốc Argide.\ndược sĩ - thuốc: Dược sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArgide - Chóng Mặt: Argide có thể gây tác dụng liên quan đến thần kinh như chóng mặt.\nDược Sĩ - Thuốc: Dược sĩ tư vấn về việc sử dụng thuốc.\nArgide - Đau Bụng: Argide có thể gây đau bụng khi dùng quá liều.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nArgide - Dị Ứng: Argide chống chỉ định cho những người có tiền sử dị ứng với thành phần của thuốc.\nbác sĩ - thuốc: Bác sĩ hướng dẫn người dùng về cách sử dụng thuốc một cách hiệu quả.\nArgide - Ngứa: Ngứa là tác dụng phụ hiếm gặp của thuốc Argide.\nNhân Viên Y Tế - Thuốc: Nhân viên y tế hướng dẫn cách sử dụng thuốc.\nArgide - Gan: Argide hỗ trợ điều trị các bệnh lý về gan.\nBệnh - Vị Thuốc: Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được dùng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng trong điều trị bệnh.\nArgide - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng và cân nhắc giữa lợi ích và nguy cơ trước khi sử dụng Argide.\nBệnh - Thuốc: Thuốc được sử dụng để chữa bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.\nArgide - Hạ Huyết Áp: Hạ huyết áp là tác dụng phụ của thuốc Argide.\nDược Liệu - Hướng Dẫn: Hướng dẫn của bác sĩ về cách sử dụng dược liệu để phát huy tác dụng và đảm bảo an toàn cho sức khỏe.\nArgide - Nhức Đầu: Nhức đầu là tác dụng phụ thường gặp của thuốc Argide.\nSử Dụng - Tùy Tiện Sử Dụng: Không nên tùy tiện sử dụng thuốc.\nArgide - Phụ Nữ Cho Con Bú: Phụ nữ cho con bú cần thận trọng và cân nhắc giữa lợi ích và nguy cơ trước khi sử dụng Argide.\nArgide - Đầy Hơi: Khi sử dụng Argide, cần chú ý đến triệu chứng đầy hơi.\nArgide - Trướng Bụng: Khi sử dụng Argide, cần chú ý đến triệu chứng trướng bụng.\nArgide - Nôn Ói: Nôn ói là tác dụng phụ thường gặp của thuốc Argide.\nArgide - Mề Đay: Mề đay là tác dụng phụ hiếm gặp của thuốc Argide.\nArgide - Giảm Tiểu Cầu: Giảm tiểu cầu là tác dụng phụ của thuốc Argide.\nThuốc Động Kinh - Động Kinh: Thuốc động kinh được sử dụng để điều trị động kinh.\nArginin - Tăng Ammoniac Huyết: Arginin được chỉ định để điều trị tăng ammoniac huyết.\nArgide - Vận Hành Máy Móc: Người vận hành máy móc cần dừng vận hành máy nếu gặp tác dụng phụ liên quan đến thần kinh khi sử dụng Argide.\nArgide - Ánh Sáng Mặt Trời: Argide cần tránh tiếp xúc trực tiếp với ánh nắng mặt trời.\nArgide - Người Lái Xe: Người lái xe cần dừng lái xe nếu gặp tác dụng phụ liên quan đến thần kinh khi sử dụng Argide.\nArgide - Thiazid: Argide có thể tương tác với Thiazid, làm tăng nồng độ insulin trong huyết tương.\nArgide - Tăng Kali Huyết: Tăng kali huyết là tác dụng phụ của thuốc Argide, đặc biệt ở người có bệnh lý về gan, thận, tiểu đường.\nArgide - Sulfonylurea: Argide có thể tương tác với Sulfonylurea, ức chế đáp ứng của glucagon huyết tương với Arginin.\nArgide - Viên Nang: Argide được sản xuất dưới dạng viên nang.\nArgide - Spironolacton: Argide có thể tương tác với Spironolacton, gây tăng kali huyết.\nArgide - Phù Não: Argide có thể gây phù não khi dùng quá liều ở trẻ em.\nArgide - Nhiễm Acid Chuyển Hóa: Argide có thể gây nhiễm acid chuyển hóa khi dùng quá liều.\nAgi-Calci - Thông Báo Bác Sĩ: Cần thông báo cho bác sĩ về tình trạng sức khỏe khi sử dụng thuốc Agi-Calci.\nArgide - Co Cứng Cơ Bụng: Co cứng cơ bụng là tác dụng phụ của thuốc Argide.\nArgide - Chu Trình Ure: Argide hỗ trợ điều trị rối loạn chuyển hóa Amoniac trong chu trình Urê.\nArgide - Rối Loạn Chu Trình Ure: Argide chống chỉ định cho người đang rối loạn chu trình ure và thiếu hụt enzym arginase.&lt;SEP&gt;Rối loạn chu trình ure là chống chỉ định của thuốc Argide.\nArgide - Tăng Ammoniac Huyết: Tăng ammoniac huyết là chống chỉ định của thuốc Argide.\nArgide - Tăng Amoniac Huyết: Argide chống chỉ định cho người đang bị tăng amoniac huyết do nhiễm acid hữu cơ trong máu.\nArgide - Thở Quá Nhanh: Argide có thể gây thở quá nhanh khi dùng quá liều.\nArgide - Arginine Hydrochloride: Argide chứa hoạt chất Arginine hydrochloride.\nArgide - Tăng Ammoniac Máu: Argide được sử dụng để điều trị bệnh lý tăng Ammoniac máu.\nArgide - Arginosuccinic Niệu: Argide được sử dụng để điều trị Arginosuccinic niệu.\nArgide - Mẫn Đỏ: Mẫn đỏ là tác dụng phụ hiếm gặp của thuốc Argide.\nArgide - Xylitol: Argide có thể tương tác với Xylitol, làm tăng nồng độ insulin trong huyết tương.\nAminophyllin - Argide: Argide có thể tương tác với Aminophyllin, làm tăng nồng độ insulin trong huyết tương.\nArgide - Rối Loạn Khó Tiêu: Argide hỗ trợ điều trị rối loạn khó tiêu.\nArgide - Bệnh Lý Về Gan: Argide được sử dụng hỗ trợ điều trị các bệnh lý về gan.\nActis - Argide: Argide có thành phần tương tự với Actis.\nArgide - Tăng Amoniac Máu: Argide được sử dụng để điều trị bệnh lý tăng Amoniac máu.\nArgide - Thiếu Enzyme Chuyển Hóa: Argide điều trị cho bệnh nhân thiếu enzyme chuyển hóa trong chu trình Ure.\nArgide - Citrulin Máu: Argide được sử dụng để điều trị Citrulin máu.\nArgide - Ornithine Carbamyl Transferase: Argide được sử dụng để điều trị bệnh nhân thiếu Ornithine carbamyl transferase.\nArgide - Carbamylphosphate Synthetase: Argide được sử dụng để điều trị bệnh nhân thiếu Carbamylphosphate synthetase.\nArgide - N-Acetyl Glutamate Synthetase: Argide hỗ trợ điều trị người thiếu N-acetyl glutamate synthetase.\nArgide - Thời Tiết Khô RáO: Argide cần được bảo quản ở nơi khô ráo.\nArgide - Nhiệt Độ Dưới 30ºC: Argide cần được bảo quản ở nhiệt độ dưới 30ºC.\nArgadin - Phân Thủy: Phân thủy là tác dụng phụ khi dùng Argadin.\nArgadin - Tình Trạng Cương Dương: Tình trạng cương dương có thể xảy ra là tác dụng phụ khi dùng Argadin.\nThuốc Chống Động Kinh - Thuốc Động Kinh: Thuốc chống động kinh có thể tương tác với các loại thuốc động kinh khác.\nArginine Hydrochloride - Tăng Ammoniac Máu: Arginine hydrochloride giúp ổn định nồng độ Arginine trong máu, ngăn chặn sự tăng Ammoniac huyết.']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide được sử dụng trong nhiều trường hợp khác nhau ngoài việc điều trị bệnh lý tăng Amoniac máu và hỗ trợ điều trị rối loạn tiêu hóa. Theo hướng dẫn sử dụng, Argide có thể được dùng để:
+- Hỗ trợ điều trị các tình trạng bệnh lý về gan.
+- Điều trị các rối loạn chuyển hóa Amoniac trong chu trình Ure.
+- Hỗ trợ các rối loạn khó tiêu.
+- Bổ sung dinh dưỡng cho người bị rối loạn chu trình ure như tăng Amoniac máu tuýp I và II, tăng citrulin máu, arginosuccinic niệu và thiếu men N – acetyl glutamate synthetase.
+Đối với những người lớn bị rối loạn khó tiêu, liều dùng của Argide có thể dao động từ 3 đến 20 gram mỗi ngày, tùy thuộc vào tình trạng bệnh và thể trạng của bệnh nhân.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thuốc Argide hỗ trợ điều trị các chứng rối loạn khó tiêu và hỗ trợ các bệnh lý về gan.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7664422927892612</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8999439065056487</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ gì ở người cao tuổi?</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>['Chảy Máu Và Rối Loạn Tạo Máu Khác: Chảy máu và các rối loạn tạo máu khác là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nNgười Cao Tuổi: Người Cao Tuổi, từ 65 tuổi trở lên, là đối tượng cần được chăm sóc đặc biệt và điều chỉnh liều lượng của một số loại thuốc cụ thể. Họ thường gặp phải suy giảm chức năng thận, làm tăng nguy cơ nhiễm độc aspirin và yêu cầu điều chỉnh liều lượng của nhiều loại thuốc khác như Alchysin 8400, Allerphast, Allerphast 60 mg, Alpha-Chymotrypsin 4200 IU, và Amikacin Bidiphar. Trước khi sử dụng Alchysin 8400 trên người cao tuổi, cần thông báo cho bác sĩ biết về tình trạng sức khỏe hiện tại. Người cao tuổi cần đặc biệt chú ý khi sử dụng các loại thuốc như Acenocoumarol, Acritel, Aclasta, và Amiparen 5 Otsuka. Đối với Acritel, người cao tuổi cần thận trọng khi sử dụng nếu chức năng thận vẫn bình thường. Khi sử dụng Aclasta, người cao tuổi không cần điều chỉnh liều lượng, nhưng cần chú ý khi sử dụng cùng với thuốc lợi tiểu. Người cao tuổi cần bổ sung nước đầy đủ và điều chỉnh liều lượng phù hợp khi sử dụng Acyclovir để đảm bảo an toàn và hiệu quả của thuốc. Người cao tuổi thường có chỉ số BMI bình thường nhưng lượng mỡ cao do ít vận động. Họ cũng có nguy cơ tăng nhạy cảm với tác dụng chống tiết acetylcholin của thuốc Coldko khi lớn hơn 60 tuổi. Đặc biệt, người cao tuổi (trên 75 tuổi) không thích hợp để bắt đầu điều trị bằng Agilosart 100. Người cao tuổi cần cân nhắc lợi ích, nguy cơ khi sử dụng Cefurobiotic và Cefurich do suy giảm chức năng thận. Họ cũng cần cân nhắc khi sử dụng Cefpodoxim dựa trên hiệu quả và an toàn. Người cao tuổi thường được hỗ trợ cải thiện hệ miễn dịch bị suy giảm bởi Alputine 80mg và Bentarcin. Cuối cùng, người cao tuổi là đối tượng dễ nhạy cảm với các tác dụng không mong muốn của thuốc như Baby Septol, Batigan, và Coperil Plus. Họ cũng cần thận trọng khi dùng thuốc AlphaDHG và Amiparen 5 Otsuka do khả năng gây nhiễm độc aspirin. Người cao tuổi cũng dễ bị hạ huyết áp và cần đặc biệt lưu ý khi bị ngộ độc thực phẩm. Tuy nhiên, người cao tuổi không cần điều chỉnh liều dùng của Bilastine, nhưng cần điều chỉnh liều dùng khi sử dụng Bixicam. Người cao tuổi cũng là đối tượng có nguy cơ xuất huyết tiêu hóa cao khi sử dụng thuốc NSAID và có thể bị ảnh hưởng bởi quá liều Bisacodyl. Ngoài ra, người cao tuổi có nguy cơ mắc bệnh teo não và cần bồi bổ sức khỏe bằng 3B Medi. Người cao tuổi cần thận trọng khi dùng thuốc do có khả năng gặp tác dụng phụ và họ thường được điều trị bằng các thuốc chống ngứa.\n\nNgười cao tuổi cũng là đối tượng sử dụng Biviantac và có nguy cơ gặp tác dụng phụ khi dùng thuốc này kéo dài. Họ cũng là đối tượng mắc suy giảm trí nhớ và được điều trị bằng Bổ Huyết Ích Não. Người cao tuổi cần giảm liều Cordarone và theo dõi chặt chẽ. Ngoài ra, người cao tuổi là đối tượng sử dụng Coversyl Plus và thuốc Cozaar.&lt;SEP&gt;Người cao tuổi là đối tượng cần cân nhắc khi dùng thuốc moxifloxacin.&lt;SEP&gt;Người cao tuổi là đối tượng sử dụng Rosuvastatin không cần điều chỉnh liều.&lt;SEP&gt;Người cao tuổi là đối tượng không cần điều chỉnh liều Rosuvastatin.\nAxit Valproic (Depakene): Axit valproic (Depakene) là thuốc chống động kinh có liên quan đến nguy cơ gây dị tật bẩm sinh ở trẻ sơ sinh.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nGiảm Tiểu Паузы: Giảm tiểu cầu là tác dụng phụ có thể xảy ra khi dùng thuốc Aluvia.&lt;SEP&gt;Giảm tiểu cầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nCorticoid: Corticoid là một loại thuốc corticosteroid được sử dụng rộng rãi trong nhiều lĩnh vực y tế, từ điều trị các bệnh lý da liễu cho đến các tình trạng viêm nhiễm và dị ứng khác. Corticoid hoạt động bằng cách giảm hoặc ức chế các hóa chất và con đường viêm trong cơ thể, giúp kháng viêm và ngăn ngừa sự hình thành của các bóng nước mới, đặc biệt trong điều trị Pemphigus. Ngoài ra, corticoid còn được sử dụng trong việc điều chỉnh nồng độ canxi trong máu và là thành phần chính của thuốc Begenderm, có khả năng ức chế vỏ thượng thận ở trẻ sơ sinh. Khi sử dụng toàn thân, corticoid có thể bài tiết qua sữa mẹ với hàm lượng nhỏ và không gây ảnh hưởng đến trẻ sơ sinh.\n\nViệc sử dụng corticoid kéo dài hoặc quá liều có thể gây ra nhiều tác dụng phụ nghiêm trọng, bao gồm suy thượng thận cấp và hội chứng Cushing. Một số tác dụng phụ khác của corticoid bao gồm tăng nhu cầu sử dụng calci, gây ra mụn, và có thể làm giảm tác dụng của Beatisl do nó giữ muối và nước trong cơ thể. Corticoid cũng có thể gây ra các triệu chứng như teo da, khô da, và viêm da quanh miệng. Việc sử dụng corticoid tại chỗ có thể gây ra các phản ứng bất lợi khi ngừng sử dụng, đòi hỏi sự giám sát chặt chẽ của bác sĩ.\n\nCorticoid là một nhóm thuốc nhân tạo hoặc tổng hợp được sử dụng rộng rãi trong hầu hết các chuyên khoa y tế, giúp cải thiện nhiều vấn đề sức khỏe nhưng cũng tiềm ẩn nhiều rủi ro nếu không được sử dụng đúng cách. Corticoid có thể gây ra tương tác với nhiều loại thuốc khác và cần thận trọng khi kết hợp với thuốc kháng nấm. Loại thuốc này cũng được sử dụng để điều trị khối u nang bì trong hội chứng Gardner và có thể gây ảnh hưởng đến việc giảm sản xuất testosterone. Corticoid cũng được sử dụng để điều trị bệnh có thể gây ra triệu chứng loạn thần và thường được sử dụng ngắn ngày trong trường hợp nặng.\n\nNgoài ra, corticoid còn được biết đến như một loại thuốc kháng viêm mạnh thường được dùng đầu tay trong điều trị Sarcoidosis. Corticoid cũng là một thành phần trong thuốc Anginovag. Tuy nhiên, cần lưu ý rằng việc sử dụng corticoid có thể làm nặng thêm tình trạng suy tim.\n\nCuối cùng, corticoid là loại steroid tổng hợp có tác dụng như Betamethasone và thường được bệnh nhân điều trị cùng với Bepanthen.&lt;SEP&gt;Corticoid là thuốc có tương tác với Brexin.&lt;SEP&gt;Corticoid có tương tác với Brexin.&lt;SEP&gt;Corticoid là một loại thuốc có thể tương tác với Co-Diovan.\nThuốc Valproic Acid (Depakene): Thuốc valproic acid (Depakene) là thuốc có thể gây ra yếu tố nguy cơ nghi ngờ mắc bệnh tự kỷ nếu thai nhi tiếp xúc.\nNgười Già: Người già là đối tượng cần được chăm sóc đặc biệt và thận trọng trong nhiều khía cạnh sức khỏe. Họ cần được theo dõi chặt chẽ khi sử dụng một số loại thuốc và dược liệu, như Acenocoumarol 4 mg và dược liệu cóc. Người già cũng cần thận trọng khi sử dụng corticoid do dễ gặp phải tác dụng phụ. Bên cạnh đó, họ không bị ảnh hưởng bởi thuốc Air-X vì nó không hấp thụ vào máu qua đường tiêu hóa. Người già là đối tượng dễ bị ảnh hưởng nặng nề bởi bệnh cảm cúm và cần được theo dõi chặt chẽ trong quá trình điều trị bệnh này. Ngoài ra, người già có nguy cơ cao bị hóc xương.&lt;SEP&gt;Người già cần thận trọng khi sử dụng Cotrimoxazol.&lt;SEP&gt;Người già là đối tượng dễ mắc các bệnh đường hô hấp trên.&lt;SEP&gt;Người già là đối tượng cần thận trọng khi sử dụng Amitriptyline.&lt;SEP&gt;Người già cần lưu ý trước khi dùng thuốc Bolutin.&lt;SEP&gt;Người già là đối tượng cần đặc biệt chú ý khi sử dụng Deferasirox (Exjade).&lt;SEP&gt;Người già là đối tượng có nguy cơ cao xuất hiện biến chứng từ thủy đậu.\nAcid Valproic: Acid valproic là một loại thuốc được sử dụng trong điều trị các rối loạn thần kinh và tâm thần, bao gồm cả việc điều trị rối loạn lưỡng cực và rối loạn động kinh. Thuốc này hoạt động như một thuốc chống co giật hiệu quả và cũng có tác dụng an thần. Acid valproic có thể gây độc tính khi dùng chung với aspirin và vidipha, đồng thời có khả năng tương tác với erythromycin, một loại kháng sinh. Thuốc này cũng tương tác với các chất như cimetidin và amitriptyline, trong đó amitriptyline có thể làm giảm tác dụng của acid valproic. Ngoài ra, acid valproic không bị ảnh hưởng bởi gabapentin, cho thấy rằng nó có thể hoạt động độc lập hoặc ít bị ảnh hưởng bởi một số loại thuốc khác.&lt;SEP&gt;Acid valproic là hoạt chất chính trong Depakin.\nBiviantac: Biviantac là một loại thuốc được sử dụng trong việc điều trị các vấn đề về tiêu hóa như trướng bụng, đầy hơi, và tiêu chảy cấp. Thành phần chính của Biviantac là bismuth subsalicylate, một chất có khả năng bao phủ niêm mạc dạ dày, giúp giảm các triệu chứng khó chịu như nóng rát, đau vùng thượng vị, và tăng độ acid. \n\nNgoài ra, Biviantac cũng chứa các thành phần khác nhằm hỗ trợ điều trị các rối loạn thường gặp trong các bệnh lý như loét dạ dày tá tràng và thực quản. Thuốc này không chỉ giúp kiểm soát tình trạng tăng tiết acid mà còn có tác dụng chống đầy hơi thông qua sự kết hợp với simethicon.\n\nTuy nhiên, cần lưu ý rằng Biviantac có thể làm cản trở quá trình hấp thu của một số loại thuốc khác, đặc biệt là các thuốc kháng sinh như tetracyclin, ciprofloxacin, ketoconazol, chloroquin, cefpodoxim, và các vitamin. Điều này đòi hỏi người dùng phải tuân thủ hướng dẫn sử dụng thuốc và thông báo cho bác sĩ về tất cả các loại thuốc đang sử dụng để tránh bất kỳ tương tác có hại nào.\nValproic Acid: Valproic acid là thuốc chống co giật được sử dụng ở những bệnh nhân có tình trạng múa giật.&lt;SEP&gt;Valproic acid là thuốc điều trị giật.&lt;SEP&gt;Valproic acid là hoạt chất chính trong Depakin.&lt;SEP&gt;Valproic acid là hoạt chất chính của Depakin.\nAmitriptyline: Amitriptyline là một loại thuốc chống trầm cảm ba vòng (tricyclic antidepressant) được sử dụng để điều trị trầm cảm. Thuốc này không chỉ giúp giảm các triệu chứng của trầm cảm mà còn có khả năng giảm đau vùng chậu. Tuy nhiên, việc sử dụng Amitriptyline cần phải được thực hiện một cách thận trọng do tiềm ẩn nhiều tương tác thuốc khác nhau.\n\nAmitriptyline có thể tương tác với một số loại thuốc khác như Combigan và Depakin. Khi sử dụng Amitriptyline cùng với Depakin, cần phải điều chỉnh liều lượng để tránh các tác dụng phụ không mong muốn. Ngoài ra, Amitriptyline cũng có thể tương tác với disulfiram, dẫn đến tăng cường phản ứng giữa rượu và disulfiram khi cả hai được sử dụng cùng nhau.\n\nThuốc này cũng cần được sử dụng cẩn thận khi dùng cùng với các thuốc ức chế monoamin oxydase (MAOIs). Bệnh nhân rối loạn lưỡng cực cũng cần đặc biệt chú ý khi sử dụng Amitriptyline, đặc biệt là trong giai đoạn hồi phục sau nhồi máu cơ tim. \n\nMột điểm đáng lưu ý khác là Amitriptyline có thể gây ra tác dụng phụ ở thai nhi và có thể ảnh hưởng đến trẻ sơ sinh. Điều này nhấn mạnh tầm quan trọng của việc thông báo cho bác sĩ về tình trạng mang thai hoặc đang cho con bú trước khi bắt đầu sử dụng Amitriptyline.&lt;SEP&gt;Amitriptyline là một trong những thuốc chống trầm cảm ba vòng được liệt kê trong văn bản.&lt;SEP&gt;Amitriptyline là thuốc chống trầm cảm ba vòng có thể tương tác với moxifloxacin.\nHội Chứng Phát Ban Do Thuốc: Hội chứng phát ban do thuốc là một tác dụng phụ nghiêm trọng khi sử dụng Depakin.&lt;SEP&gt;Hội chứng phát ban do thuốc với tăng bạch cầu ái toan và nhiều triệu chứng toàn thân (DRESS) là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAtocib: Atocib là thuốc được sử dụng để điều trị các bệnh lý về khớp và các triệu chứng đau.&lt;SEP&gt;Thuốc Atocib 90 mg được chỉ định dùng trong các trường hợp như điều trị triệu chứng các bệnh lý viêm xương khớp, viêm cột sống dính khớp, Gout, giảm đau và đau bụng kinh nguyên phát.&lt;SEP&gt;Atocib là thuốc chống chỉ định nếu creatinin &lt; 30 ml/phút. Liều dùng cụ thể tùy thuộc vào tình trạng cụ thể của mỗi bệnh nhân.&lt;SEP&gt;Atocib là thuốc cần thận trọng khi sử dụng đối với bệnh nhân có nguy cơ phát triển biến chứng đường tiêu hóa với NSAID, người có tiền sử bệnh đường tiêu hóa như viêm loét và xuất huyết tiêu hóa, người bị nhồi máu cơ tim, suy tim sung huyết, đột quỵ, tăng huyết áp, tăng lipid máu, đái tháo đường, hút thuốc, người suy chức năng thận, xơ gan, người cao tuổi, và người lái xe hoặc vận hành máy móc.&lt;SEP&gt;Atocib là thuốc chứa thành phần tương tự với Arcoxia.\nTăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.&lt;SEP&gt;Tăng urê huyết là một tác dụng phụ khi sử dụng Depakin.\nBisacodyl: Bisacodyl là thuốc nhuần tràng, sạch ruột và trị táo bón.&lt;SEP&gt;Bisacodyl là thuốc làm tăng nhu động ruột, tương tác với Artreil.&lt;SEP&gt;Bisacodyl là thuốc được chỉ định điều trị táo bón và chuẩn bị cho chụp X-quang đại tràng.&lt;SEP&gt;Thuốc Bisacodyl được sử dụng đường uống hoặc đường trực tràng dưới dạng viên đạn hay thụt rửa, giúp giảm kích ứng ở dạ dày và buồn nôn.&lt;SEP&gt;Bisacodyl là thuốc nhuận tràng kích thích, thường gây tác dụng phụ trên tiêu hóa như đau bụng, nôn, buồn nôn, tiêu chảy.&lt;SEP&gt;Bisacodyl là thuốc điều trị táo bón, giúp thải sạch ruột cho phẫu thuật hoặc chuẩn bị X-quang đại tràng.&lt;SEP&gt;Bisacodyl là thuốc điều trị táo bón, có thể gây kích ứng dạ dày và tá tràng khi phối hợp với các thuốc kháng acid.\nKhối Tim: Khối tim có thể là triệu chứng khi dùng quá liều Depakin.\nDanapha Trihex: Danapha Trihex là thuốc được sử dụng để hỗ trợ hội chứng Parkinson và làm giảm hội chứng ngoại tháp do thuốc.&lt;SEP&gt;Danapha Trihex không được khuyến cáo sử dụng cho phụ nữ có thai trừ khi lợi ích lớn hơn nguy cơ. Thuốc này cũng không nên được sử dụng khi đang cho con bú.&lt;SEP&gt;Danapha Trihex là thuốc chứa hoạt chất trihexyphenidyl.\nDepakin: Depakin là thuốc điều trị động kinh chứa hoạt chất valproic acid.&lt;SEP&gt;Depakin là thuốc chứa valproic acid, được dùng trong điều trị động kinh.&lt;SEP&gt;Depakin là thuốc điều trị động kinh với hoạt chất là valproic acid.&lt;SEP&gt;Depakin, với hoạt chất là valproic acid, được sử dụng để điều trị động kinh.&lt;SEP&gt;Depakin (valproic acid) là thuốc điều trị, không được sử dụng trong một số trường hợp cụ thể.\nAlphaDHG: Thuốc AlphaDHG được sản xuất bởi Công ty Cổ phần Dược Hậu Giang, có thành phần chính là Chymotrypsin (hay Alpha-chymotrypsine) với 4200 đơn vị IU, được chỉ định dùng trong chống viêm, chống phù nề dạng men.&lt;SEP&gt;AlphaDHG là thuốc cần tuân thủ hướng dẫn sử dụng, đặc biệt chú ý đến việc báo cáo với bác sĩ hoặc dược sĩ về tình trạng sức khỏe trước khi dùng.&lt;SEP&gt;AlphaDHG là thuốc kháng viêm và điều trị phù nề dạng men, được sử dụng trong các trường hợp tổn thương mô mềm, chấn thương cấp, nhiễm trùng, phù nề mí mắt và chấn thương do vận động.&lt;SEP&gt;AlphaDHG là thuốc được sử dụng để điều trị các rối loạn tiêu hóa như đầy hơi, nặng bụng, tiêu chảy, táo bón hoặc buồn nôn. Thuốc có thể gây ra phản ứng dị ứng nhẹ như đỏ da khi sử dụng liều cao.&lt;SEP&gt;AlphaDHG là thuốc được sử dụng trong điều trị, với giá bán khoảng 80.000 VNĐ cho mỗi hộp.\nAceclofenac Stada: Aceclofenac Stada là thuốc kháng viêm không steroid (NSAID).\nCefurich: Cefurich là thuốc kháng sinh chứa hoạt chất chính là Cefuroxim, được chỉ định trong các trường hợp nhiễm khuẩn nhạy cảm với thuốc.&lt;SEP&gt;Cefurich là thuốc kháng sinh được sử dụng điều trị các nhiễm khuẩn khác nhau.&lt;SEP&gt;Cefurich là thuốc kháng sinh chứa hoạt chất cefuroxim axetil.&lt;SEP&gt;Cefurich là kháng sinh phổ rộng, có thể gây buồn nôn, nôn, tiêu chảy, tăng kích thích thần kinh cơ và cơn co giật, đặc biệt ở người suy thận.&lt;SEP&gt;Cefurich là thuốc kháng sinh cephalosporin, được sử dụng trong điều trị các bệnh nhiễm khuẩn.\nBuồn Nôn - Depakin: Buồn nôn là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nNgười Cao Tuổi - Tác Dụng Phụ: Người cao tuổi có nguy cơ gặp tác dụng phụ khi dùng thuốc.\nChóng Mặt - Depakin: Chóng mặt là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nCorticoid - Người Già: Người già là đối tượng dễ bị tác dụng phụ khi sử dụng corticoid.\nDepakin - Táo Bón: Táo bón là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nBiviantac - Người Cao Tuổi: Người cao tuổi là đối tượng sử dụng Biviantac.&lt;SEP&gt;Biviantac có thể gây tác dụng phụ ở người cao tuổi.\nDepakin - Đau Bụng: Đau bụng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAmitriptyline - Người Già: Amitriptyline cần thận trọng khi sử dụng ở người già.\nDepakin - Thiếu Máu: Thiếu máu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAtocib - Người Cao Tuổi: Người cao tuổi cần thận trọng khi sử dụng Atocib.\nAspirin - Depakin: Depakin có thể tương tác với Aspirin.\nBisacodyl - Người Cao Tuổi: Bisacodyl có thể gây ảnh hưởng đến người cao tuổi khi sử dụng.\nDepakin - Khó Thở: Khó thở là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDanapha Trihex - Người Cao Tuổi: Người cao tuổi dễ nhạy cảm với các dụng không mong muốn của thuốc.\nDepakin - Nhức Đầu: Nhức đầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAlphaDHG - Người Cao Tuổi: Người cao tuổi cần đặc biệt chú ý khi dùng thuốc AlphaDHG.\nAcid Valproic - Aspirin: Aspirin tăng nồng độ của Acid Valproic khi dùng chung, gây độc tính.&lt;SEP&gt;Acid Valproic khi dùng chung với Aspirin có thể gây độc tính.&lt;SEP&gt;Acid valproic có thể tương tác với Aspirin, làm tăng nồng độ Aspirin.&lt;SEP&gt;Aspirin có thể làm tăng nồng độ thuốc này trong huyết thanh và tăng độc tính khi dùng cùng Acid valproic.\nAceclofenac Stada - Người Cao Tuổi: Aceclofenac Stada có thể gây tác dụng phụ trên người cao tuổi.\nDepakin - Viêm Họng: Viêm họng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nCefurich - Người Cao Tuổi: Người cao tuổi cần cân nhắc an toàn và hiệu quả khi sử dụng Cefurich.\nDepakin - Khó Tiêu: Khó tiêu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nBuồn Ngủ - Depakin: Buồn ngủ là tác dụng phụ khi sử dụng Depakin.&lt;SEP&gt;Buồn ngủ có thể là tác dụng phụ khi dùng quá liều Depakin.&lt;SEP&gt;Buồn ngủ có thể xảy ra ở người cao tuổi khi sử dụng Depakin.\nChảy Máu - Depakin: Depakin được sử dụng để theo dõi số lượng tiểu cầu và xét nghiệm đông máu khi chảy máu.\nDepakin - Viêm Phế Quản: Viêm phế quản là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAcid Valproic - Amitriptylin: Amitriptylin giảm tác dụng của acid valproic.\nDepakin - Động Kinh: Depakin được chỉ định điều trị cho bệnh động kinh.&lt;SEP&gt;Depakin được sử dụng để điều trị động kinh.\nDepakin - Tác Dụng Phụ: Depakin có tác dụng phụ ảnh hưởng đến bệnh nhân.\nDepakin - Suy Nhược: Suy nhược là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Phenytoin: Depakin có thể tương tác với Phenytoin.\nAcid Valproic - Cimetidin: Cimetidin có tương tác với Acid valproic.&lt;SEP&gt;Acid valproic tương tác với Cimetidin.\nDepakin - Warfarin: Depakin có thể tương tác với Warfarin.\nDepakin - Sữa Mẹ: Valproate được bài tiết qua sữa mẹ.\nAluvia - Giảm Tiểu Паузы: Giảm tiểu cầu là tác dụng phụ có thể xảy ra khi dùng thuốc Aluvia.\nDepakin - Rụng Tóc: Rụng tóc là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.&lt;SEP&gt;Rụng tóc là một trong các tác dụng phụ thường gặp khi sử dụng Depaken.\nDepakin - Viêm Mũi: Viêm mũi là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Quá Mẫn: Bệnh nhân quá mẫn với các thành phần của thuốc tuyệt đối không được sử dụng Depakin.\nAcid Valproic - Amilavil: Amilavil giảm tác dụng của acid valproic.&lt;SEP&gt;Amilavil làm giảm tác dụng của acid valproic.\nBệnh Gan - Depakin: Bệnh nhân mắc bệnh gan hoặc rối loạn chức năng gan tuyệt đối không được sử dụng Depakin.\nBảo Quản - Depakin: Thuốc Depakin cần được bảo quản ở nơi khô ráo, nhiệt độ không quá 25°C.\nAcid Valproic - Erythromycin: Erythromycin làm tăng nồng độ acid valproic trong huyết tương.&lt;SEP&gt;Erythromycin làm tăng nồng độ Acid Valproic trong huyết tương.\nDepakin - Hồi Hộp: Hồi hộp là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAceclofenac - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ ít gặp khi sử dụng Aceclofenac.\nDepakin - Viêm Tụy: Viêm tụy là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nAmitriptyline - Depakin: Depakin có thể tương tác với Amitriptyline.\nRối Loạn Phổ Tự Kỷ - Thuốc Valproic Acid (Depakene): Thuốc valproic acid (Depakene) là yếu tố nguy cơ nghi ngờ mắc bệnh tự kỷ nếu thai nhi tiếp xúc.\nDepakin - Phenobarbital: Depakin có thể tương tác với Phenobarbital.\nCarbamazepine - Depakin: Depakin có thể tương tác với Carbamazepine.\nDepakin - Dị Tật Bẩm Sinh: Dị tật bẩm sinh là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nAxit Valproic (Depakene) - Động Kinh: Axit valproic (Depakene) là thuốc chống động kinh có liên quan đến nguy cơ gây dị tật bẩm sinh ở trẻ sơ sinh.\nDepakin - Rối Loạn Chức Năng Gan: Bệnh nhân rối loạn chức năng gan tuyệt đối không được sử dụng Depakin.\nDepakin - Động Kinh Vắng Ý Thức: Depakin được chỉ định điều trị cho bệnh động kinh vắng ý thức.\nChạy Thận Nhân Tạo - Depakin: Chạy thận nhân tạo có thể được sử dụng để xử lý quá liều Depakin.\nDepakin - Mờ Mắt: Mờ mắt là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nAcid Valproic - Depakin: Acid valproic là hoạt chất chính trong Depakin.\nAcid Valproic - Aspirin MKP 81: Khi dùng chung với Acid Valproic, Aspirin MKP 81 tăng nồng độ Acid Valproic trong huyết thanh.\nDepakin - Rifampin: Depakin có thể tương tác với Rifampin.\nDepakin - Rối Loạn Trí Nhớ: Rối loạn trí nhớ là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Hạ Thân Nhiệt: Hạ thân nhiệt là tác dụng phụ khi sử dụng Depakin.&lt;SEP&gt;Hạ thân nhiệt là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Nhiễm Độc Gan: Nhiễm độc gan là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nDepakin - Rung Giật Nhãn Cầu: Rung giật nhãn cầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Mất Thính Lực: Mất thính lực là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Tăng Natri Máu: Tăng natri máu có thể là tác dụng phụ khi dùng quá liều Depakin.\nDepakin - Tiểu Паузы: Số lượng tiểu cầu được theo dõi khi sử dụng Depakin.\nDepakin - Valproic Acid: Depakin chứa hoạt chất valproic acid.\nDepakin - Nortriptyline: Depakin có thể tương tác với Nortriptyline.\nDepakin - Topiramate: Depakin có thể tương tác với Topiramate.\nDepakin - Felbamate: Depakin có thể tương tác với Felbamate.\nDepakin - Phù Ngoại Biên: Phù ngoại biên là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Giảm Tiểu Паузы: Giảm tiểu cầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Tăng Urê Huyết: Tăng urê huyết là tác dụng phụ khi sử dụng Depakin.\nDepakin - Tăng Ure Huyết: Bệnh nhân mắc bệnh tăng ure huyết tuyệt đối không được sử dụng Depakin.\nDepakin - Tăng Sự Thèm Ăn: Tăng sự thèm ăn là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nDepakin - Động Kinh Cơn Lớn: Depakin được sử dụng trong điều trị động kinh cơn lớn.\nDepakin - Zidovudine: Depakin có thể tương tác với Zidovudine.\nDepakin - Hội Chứng Phát Ban Do Thuốc: Hội chứng phát ban do thuốc là tác dụng phụ nghiêm trọng khi sử dụng Depakin.&lt;SEP&gt;Hội chứng phát ban do thuốc với tăng bạch cầu ái toan và nhiều triệu chứng toàn thân (DRESS) là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.\nChảy Máu Và Rối Loạn Tạo Máu Khác - Depakin: Chảy máu và các rối loạn tạo máu khác là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nDepakin - Khối Tim: Khối tim có thể là tác dụng phụ khi dùng quá liều Depakin.\nAND Ty Thể - Depakin: AND ty thể (POLG) là yếu tố gây ra các bệnh như hội chứng Alpers-Huttenlocher.\nDepakin - Hội Chứng Alpers-Huttenlocher: Hội chứng Alpers-Huttenlocher là một trong các bệnh gây ra do sự đột biến ở AND ty thể (POLG).\nDepakin - Trẻ Em Dưới Hai Tuổi: Trẻ em dưới hai tuổi bị nghi mắc chứng rối loạn liên quan đến POLG tuyệt đối không được sử dụng Depakin.\nDepakin - Rối Loạn Chu Trình Chuyển Hóa Ure: Bệnh nhân rối loạn chu trình chuyển hóa Ure tuyệt đối không được sử dụng Depakin.\nDepakin - Hành Vi Hoặc Suy Nghĩ Tự Tử: Hành vi hoặc suy nghĩ tự tử là tác dụng phụ nghiêm trọng khi sử dụng Depakin.\nDepakin - Hôn Mê Sâu: Hôn mê sâu có thể là tác dụng phụ khi dùng quá liều Depakin.\nDepakin - Rufinamide: Rufinamide có thể được dùng thay thế Depakin khi bệnh nhân ổn định.\nDepakin - Valproate: Liều của Depakin có thể cần điều chỉnh nếu được sử dụng đồng thời với Valproate.\nDepakin - Thần Kinh Khuyết Tật Ống: Depakin có thể gây dị tật thần kinh khuyết tật ống.\nDepakin - Giảm IQ: Depakin có thể gây giảm IQ.\nDepakin - Primidone: Depakin có thể tương tác với Primidone.\nAntibiotic Carbapenem - Depakin: Depakin có thể tương tác với Antibiotic carbapenem.\nDepakin - Propofol: Depakin có thể tương tác với Propofol.\nAcid Valproic - Aspirin STELLA: Khi dùng Aspirin STELLA cùng Acid Valproic, sẽ tăng nồng độ Acid Valproic trong huyết thanh.\nAcid Valproic - Rối Loạn Lưỡng Cực: Acid valproic được sử dụng trong điều trị rối loạn lưỡng cực.\nAcid Valproic - Cimetidine MKP: Cimetidine MKP làm tăng nồng độ trong huyết tương của Acid valproic.\nAcid Valproic - Thuốc An Thần: Acid valproic (Depakene) là thuốc an thần được sử dụng trong điều trị rối loạn lưỡng cực.\nAcid Valproic - Độc Tính: Acid Valproic khi dùng chung với Aspirin có thể gây độc tính.\nAcid Valproic - Gabapentin: Gabapentin không làm thay đổi dược động học của acid valproic.\nAcid Valproic - Depakote: Depakote chứa hoạt chất acid valproic.\nAcid Valproic - Dalekine: Dalekine chứa hoạt chất acid valproic.\nAcid Valproic - Milepsy: Milepsy chứa hoạt chất acid valproic.\nGiật - Valproic Acid: Valproic acid được sử dụng để điều trị giật.\nMúa Giật - Valproic Acid: Valproic acid là thuốc chống co giật được sử dụng ở những bệnh nhân có tình trạng múa giật.\nValproic Acid - Động Kinh Cơn Lớn: Valproic acid được sử dụng trong điều trị động kinh cơn lớn.']</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra một số tác dụng phụ ở người cao tuổi, bao gồm:
+- **Táo bón**: Người cao tuổi có thể gặp phải tình trạng táo bón khi sử dụng Depakin.
+- **Buồn nôn**: Buồn nôn là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Chóng mặt**: Chóng mặt cũng là một tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Tăng sự thèm ăn**: Tăng sự thèm ăn là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Suy nhược**: Suy nhược là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Rụng tóc**: Rụng tóc cũng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Mờ mắt**: Mờ mắt là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Hạ thân nhiệt**: Hạ thân nhiệt là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Hồi hộp**: Hồi hộp là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Viêm phế quản**: Viêm phế quản là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Viêm mũi**: Viêm mũi cũng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Tăng urê huyết**: Tăng urê huyết là một tác dụng phụ khi sử dụng Depakin.
+- **Khó thở**: Khó thở là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Rối loạn trí nhớ**: Rối loạn trí nhớ là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Đau bụng**: Đau bụng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Viêm họng**: Viêm họng là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Khó tiêu**: Khó tiêu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Nhức đầu**: Nhức đầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Phù ngoại biên**: Phù ngoại biên là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Rung giật nhãn cầu**: Rung giật nhãn cầu là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+- **Mất thính lực**: Mất thính lực là một trong các tác dụng phụ thường gặp khi sử dụng Depakin.
+Ngoài ra, Depakin cũng có thể gây ra tình trạng **buồn ngủ**, đặc biệt ở người cao tuổi.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Thuốc Depakin (valproic acid) có thể gây ra tác dụng phụ buồn ngủ ở người cao tuổi.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.8420601076613057</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9496454616729351</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Virus nào có độ nhạy mạnh nhất với Acyclovir Stada 200 mg?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>['Acyclovir Stada 200 mg: Thuốc Acyclovir Stada 200 mg được sản xuất bởi Công ty TNHH Liên Doanh Stellapharm, dùng để điều trị và dự phòng nhiễm virus Herpes simplex, điều trị nhiễm virus Varicella Zoster.&lt;SEP&gt;Acyclovir Stada 200 mg là thuốc được chỉ định dùng trong các trường hợp nhiễm virus Herpes simplex và Varicella zoster.&lt;SEP&gt;Acyclovir Stada 200 mg được bán với giá tham khảo từ 40.000 – 50.000 VNĐ cho hộp 5 vỉ x 5 viên nén.&lt;SEP&gt;Thuốc Acyclovir Stada 200 mg được sử dụng để điều trị các bệnh như herpes simplex và herpes zoster.&lt;SEP&gt;Acyclovir Stada 200 mg là thuốc điều trị bệnh herpes simplex và zona, cần thận trọng khi sử dụng ở phụ nữ mang thai và cho con bú.&lt;SEP&gt;Acyclovir Stada 200 mg được sử dụng để điều trị các bệnh nhiễm trùng do virus.\nAcyclovir: Acyclovir là một hoạt chất chính được sử dụng trong nhiều loại thuốc điều trị các bệnh do virus herpes và varicella zoster gây ra. Nó là thành phần chính trong các loại thuốc như Acyclovir Boston 200, Acyclovir Boston 800, Acyclovir Stada 200 mg, Acyclovir Stella 400 mg, và Acyclovir Stella 800 mg. Acyclovir nổi tiếng với khả năng kháng virus mạnh mẽ nhất đối với virus Herpes simplex type 1, và tác dụng kém hơn đối với virus Herpes simplex type 2 và virus Varicella zoster. \n\nThuốc này được sử dụng để điều trị thủy đậu, bệnh zona, và các bệnh nhiễm herpes simplex và varicella zoster. Ngoài ra, nó cũng được sử dụng để dự phòng tái phát các bệnh này. Acyclovir có thể được sử dụng độc lập hoặc cùng với bữa ăn. Tuy nhiên, việc sử dụng thuốc có thể gây ra các tác dụng phụ như chóng mặt, vì vậy cần đánh giá kỹ lưỡng về phản ứng của bệnh nhân trước khi lái xe hoặc vận hành máy móc. \n\nAcyclovir còn là hoạt chất chính trong Acyclovir Stella Cream, được sử dụng để điều trị nhiễm trùng do virus, đặc biệt là nhiễm herpes simplex. Thuốc này được bài tiết qua sữa mẹ và đào thải qua thận. Do đó, cần chú ý đến việc sử dụng thuốc trong trường hợp bệnh nhân đang cho con bú. Thuốc này được ức chế đào thải bởi Probenecid và tăng hiệu lực khi dùng cùng Amphotericin B hoặc ketoconazole. Acyclovir là thuốc kháng virus có cấu trúc tương tự nucleosid, có tác dụng chọn lọc trên tế bào nhiễm virus Herpes, và có tác dụng ức chế tổng hợp ADN của virus Herpes.\n\nAcyclovir cũng được biết đến với khả năng bị kéo dài thời gian bài tiết bởi một số thuốc khác và có thể bị ảnh hưởng bởi Aspartam. Nó còn được sử dụng để điều trị triệu chứng của vảy phấn hồng dưới tên thương mại Zovirax. Acyclovir là thuốc điều trị và phòng ngừa nhiễm Herpes simplex, thủy đậu và bệnh zona. Nó có thể gây tác dụng phụ toàn thân nếu hấp thu quá mức qua da vào tuần hoàn.\n\nKem acyclovir được sử dụng trong điều trị và dự phòng nhiễm virus Herpes Simplex. Acyclovir là thuốc kháng vi-rút được sử dụng để điều trị giai đoạn bùng phát của Zona, giúp giảm mức độ nghiêm trọng và thời gian của cơn đau cấp tính. Nó cũng được sử dụng như một phương pháp hỗ trợ trong điều trị u nhú thanh quản.&lt;SEP&gt;Acyclovir là thuốc được Cơ quan Quản lý Thực phẩm và Dược phẩm Hoa Kỳ phân nhóm B, có thể sử dụng trong thai kỳ. Thuốc được khuyến nghị cho phụ nữ mang thai bị thủy đậu với các biến chứng nghiêm trọng.&lt;SEP&gt;Acyclovir là thuốc được khuyến nghị sử dụng để rút ngắn thời gian nhiễm trùng và giảm nguy cơ biến chứng thủy đậu.\nAciclovir 200mg: Acyclovir 200 mg Stada, đóng gói trong hộp 5 vỉ x 5 viên nén, giá tham khảo 32.000VNĐ/hộp.\nSự Nhân Lên Của Virus: Sự nhân lên của virus là quá trình được ức chế bởi Acyclovir.\nHerpes Simplex: Herpes simplex là bệnh nhiễm trùng do virus Herpes simplex gây ra. Bệnh này có thể ảnh hưởng đến da và niêm mạc, bao gồm cả bệnh Herpes sinh dục khởi phát và tái phát, thủy đậu, và bệnh zona. Điều trị cho bệnh herpes simplex thường được thực hiện bằng Acyclovir, một loại thuốc kháng virus phổ biến. Acyclovir có sẵn dưới nhiều dạng khác nhau như viên nén Acyclovir Boston 800, viên nén Acyclovir Stada 200 mg, viên nén Acyclovir Stella 400 mg, và kem Acyclovir Stella Cream. Thuốc này không chỉ giúp điều trị các triệu chứng của bệnh mà còn được sử dụng để phòng ngừa sự phát triển của bệnh herpes simplex. Ngoài ra, Acyclovir 5% Agimexpharm cũng được chỉ định để điều trị các trường hợp bệnh herpes simplex.\n\nBệnh herpes simplex được chống chỉ định sử dụng B – Sol. Bệnh này cũng được điều trị bằng *C. nutans* và được ức chế bởi kim vàng và Kim Ngân Hoa. Herpes simplex là vi rút gây bệnh da liễu và cũng được coi là bệnh nhiễm virus da.\nTế Bào Nhiễm Virus Herpes: Tế bào nhiễm virus herpes là mục tiêu điều trị của acyclovir.\nHerpes Zoster: Herpes zoster là bệnh được điều trị bằng Acyclovir Stada 200 mg.&lt;SEP&gt;Herpes zoster là bệnh nhiễm virus Herpes zoster.&lt;SEP&gt;Herpes zoster là bệnh nhiễm trùng do virus gây ra, được điều trị bằng Aciclovir 800 mg.&lt;SEP&gt;Herpes zoster là bệnh cần tránh khi dùng corticosteroid đường toàn thân.\nTriệu Chứng: Triệu chứng là các dấu hiệu hoặc biểu hiện cụ thể của bệnh lý hoặc tình trạng y tế mà bệnh nhân có thể cảm nhận được. Chúng bao gồm cả dấu hiệu bệnh lý mà bác sĩ có thể quan sát được và các biểu hiện mà bệnh nhân cảm nhận được. Triệu chứng có thể xuất hiện do nhiều nguyên nhân khác nhau, từ các bệnh lý cụ thể như Hội chứng Klinefelter, Bệnh Brucellosis, Bệnh cơ bẩm sinh, Bệnh tim phì đại, Bệnh Crohn, Bệnh gan nhiễm mỡ không do rượu, Bệnh Huntington, Bệnh viêm phổi kẽ, Bệnh phổi tắc nghẽn mạn tính, và Bệnh rối loạn chuyển hóa tinh bột, đến các tác dụng phụ của thuốc như ngộ độc hoặc quá liều Acetazolamid và Atorvasan. \n\nHội chứng Klinefelter có thể biểu hiện qua chiều cao vượt trội, giảm khả năng phối hợp, thiếu testosterone, tinh hoàn nhỏ, và vô sinh. Bệnh Brucellosis bao gồm sốt cao đột ngột, đau cơ, yếu cơ bất thường, và mệt mỏi. Bệnh cơ bẩm sinh bao gồm trướng bụng, đầy hơi và tiêu chảy cấp. Bệnh tim phì đại có thể bao gồm khó thở, ngất xỉu, đánh trống ngực, chóng mặt, mệt mỏi do gắng sức, và phù chân. Bệnh Crohn bao gồm đau bụng, tiêu chảy, và mất cân nặng. Bệnh gan nhiễm mỡ không do rượu thường không rõ ràng. Bệnh Huntington bao gồm rối loạn vận động và tâm thần. Bệnh viêm phổi kẽ bao gồm khó thở, đau ngực và ho. Bệnh phổi tắc nghẽn mạn tính bao gồm tắc nghẽn luồng khí từ phổi. Bệnh rối loạn chuyển hóa tinh bột có thể gây tử vong ở giai đoạn sớm sau sinh (&lt;1 tuổi).\n\nTriệu chứng của Bệnh tế bào mast hệ thống bao gồm đau da, đỏ mắt, ngứa mũi, khó thở, huyết áp thấp, quặn đau dạ dày, buồn nôn và đau đầu. Bệnh Lupus ban đỏ hệ thống bao gồm tổn thương da, khớp, thận và não. Bệnh Thận IgA có thể xuất hiện nếu không được chẩn đoán và điều trị kịp thời. Amyloidosis có thể giống với các triệu chứng của các bệnh khác.\n\nTriệu chứng không chỉ giới hạn ở các bệnh cụ thể mà còn bao gồm các dấu hiệu bệnh lý mà bác sĩ dựa vào để kê toa thuốc thích hợp. Triệu chứng có thể xuất hiện ở nhiều bệnh khác nhau, từ bệnh tim thiếu máu cục bộ đến bệnh trĩ ngoại. Triệu chứng có thể không rõ ràng, bệnh thường không có triệu chứng, chỉ được phát hiện qua xét nghiệm hoặc chẩn đoán hình ảnh. Triệu chứng giúp bác sĩ trong việc chẩn đoán và điều trị bệnh. Triệu chứng cũng có thể xuất hiện ở trẻ bị còn ống động mạch. Triệu chứng như trướng bụng, đầy hơi và tiêu chảy cần được thăm khám để xác định nguyên nhân và phương pháp điều trị.\n\nTriệu chứng của bệnh tay chân miệng bao gồm sốt, đau họng và vết loét hoặc bóng nước trên nền hồng ban ở niêm mạc miệng, bàn tay, bàn chân và đầu gối, cùi chỏ, mông. Phát ban và đau họng cũng là triệu chứng phổ biến của bệnh này.\n\nTriệu chứng cũng bao gồm dấu hiệu của các bệnh khác như viêm phế quản cấp, bệnh nổi mề đay, bệnh u nhú thanh quản, và bệnh phì đại tuyến tiền liệt. Các triệu chứng điển hình của viêm phế quản cấp bao gồm ho, tức ngực, khó thở, thở khò khè, đau nhức mình mẩy, sốt nhẹ, chảy nước mũi, và nghẹt mũi.\n\nNgoài ra, triệu chứng rối loạn giấc ngủ có thể trở nên rõ rệt hơn khi trải qua chuyến bay dài và bay về hướng đông. Triệu chứng rối loạn điện giải thường không đặc hiệu và khó nhận biết. Triệu chứng rối loạn lên đồng bao gồm sự thay đổi tạm thời về danh tính và ý thức về môi trường xung quanh, thay đổi hành vi hoặc hành động khác, mất nhận thức về môi trường xung quanh, đánh mất bản sắc cá nhân, khó phân biệt thực tế với tưởng tượng, thay đổi giọng nói, sự chú ý bị gián đoạn, khó tập trung, mất tri giác về thời gian, mất trí nhớ và niềm tin rằng cơ thể đã thay đổi về ngoại hình. Triệu chứng rối loạn nhận thức thần kinh nhẹ bao gồm các dấu hiệu cụ thể của rối loạn nhận thức. Tuy nhiên, rối loạn nhận thức thần kinh chưa có thuốc điều trị hiệu quả. Triệu chứng rối loạn phổ tự kỷ bao gồm khó chịu với sự thay đổi nhỏ, vấn đề về cảm giác và hành vi bất thường.\n\nTriệu chứng của run vô căn bao gồm khó khăn trong các hoạt động hàng ngày như giữ ly nước, ăn uống, trang điểm, nói chuyện, viết chữ. Triệu chứng của sa sút trí tuệ bao gồm mất trí nhớ, gặp vấn đề trong ngôn ngữ, khả năng tập trung, giải quyết vấn đề.\n\nTriệu chứng sẹo lồi bao gồm tăng sinh da quá mức, có thể gây khó chịu và ảnh hưởng thẩm mỹ. Triệu chứng của bệnh sỏi mật bao gồm đau quặn mật, vàng da, ngứa, tiểu vàng sậm, khó tiêu, ợ hơi, buồn nôn, nôn.\n\nTriệu chứng của sốt xuất huyết bao gồm sốt cao, nôn ói, và các triệu chứng khác.\n\nTriệu chứng suy gan bao gồm các triệu chứng nặng đe dọa tính mạng. Triệu chứng suy gan là những biểu hiện nghiêm trọng của tình trạng gan suy yếu. Triệu chứng gan xơ hóa bao gồm mệt mỏi, ăn uống kém, cổ trướng, vàng da, nôn ra máu.\n\nTriệu chứng cũng bao gồm việc tim không còn khả năng bơm hiệu quả để duy trì dòng máu cung cấp cho các cơ quan, đặc biệt trong suy tim.\n\nTriệu chứng của suy tuyến yên bao gồm các biểu hiện bất thường không đặc hiệu. Triệu chứng là dấu hiệu của bệnh suy tuyến yên.\n\nTriệu chứng teo não bao gồm sự phối hợp kém các động tác, chuyển động mắt, khả năng ngôn ngữ, tư duy, trí nhớ và giải quyết vấn đề.\n\nTriệu chứng tắc ruột bao gồm các dấu hiệu sớm giúp nhận biết bệnh.\n\nTriệu chứng của tăng áp phổi thường xuất hiện khi bệnh đã nặng, có thể dẫn đến tử vong nếu không được điều trị.\n\nTriệu chứng của tăng huyết áp vô căn thường không rõ ràng và khó nhận biết.\n\nTriệu chứng của tăng tiểu cầu bao gồm đau đầu, hoa mắt, chóng mặt, đau ngực, tê yếu cơ, dị cảm đầu chi.\n\nTriệu chứng của tăng nhãn áp có thể bao gồm suy giảm thị lực không hồi phục.\n\nTriệu chứng của bệnh thoái hóa điểm vàng thường biểu hiện rất ít ở giai đoạn sớm.\n\nTriệu chứng thoát vị đĩa đệm có thể do phần nhân nhầy tràn ra ngoài gây kích ứng các dây thần kinh lân cận. Triệu chứng thoát vị đĩa đệm cột sống thắt lưng bao gồm đau, tê, và yếu ở chân.\n\nTriệu chứng cũng bao gồm dấu hiệu cần xử lý khi dùng quá liều thuốc Cialis.\n\nTriệu chứng tiểu không tự chủ bao gồm việc mất kiểm soát việc tiểu tiện.\n\nTriệu chứng cũng có thể giảm sau khi sử dụng trầu không.\n\nTriệu chứng của tràn dịch màng phổi có thể rất khác nhau, từ không có triệu chứng đến khó thở.\n\nTriệu chứng và dấu hiệu của trào ngược dạ dày thực quản và trào ngược dịch mật khá tương đồng.\n\nTriệu chứng của trật khớp háng chưa được mô tả chi tiết trong đoạn văn đã cho.\n\nTriệu chứng mà phì đại tuyến tiền liệt mang lại ảnh hưởng đến cuộc sống là yếu tố quyết định trong việc lựa chọn phương pháp điều trị.\n\nTriệu chứng của ung thư TTL có thể tương tự như phì đại lành tính TTL hoặc không có biểu hiện gì.\nAgiclovir 200: Agiclovir 200 là viên nén chứa aciclovir, được sử dụng trong điều trị và dự phòng nhiễm virus.\nNhiễm HSV: Nhiễm HSV là tình trạng nhiễm virus Herpes simplex.\nAciclovir 800 mg: Thuốc Aciclovir 800 mg được sử dụng trong điều trị nhiễm Herpes simplex môi và sinh dục khởi phát và tái phát, cũng như nhiễm Herpes zoster.\nDa: Da là lớp mô bao phủ bên ngoài cơ thể, đóng vai trò quan trọng trong việc bảo vệ bề mặt ngoài và là nơi tiếp xúc của các thụ thể cảm giác, giúp nhận thông tin cảm giác. Da không chỉ bảo vệ cơ thể khỏi các yếu tố bên ngoài mà còn chịu tác động từ nhiều yếu tố khác nhau, bao gồm cả virus Herpes simplex và việc sử dụng nhiều loại thuốc như Acyclovir, Amikacin, Amoxicillin, Ampicillin, và Azaduo. Việc sử dụng lâu dài một số loại thuốc có thể dẫn đến biến đổi ở da do ngộ độc mạn tính. Da thường được chú ý trong các rối loạn phân ly, bao gồm cả tĩnh mạch. Da chân có thể bị khô, bong tróc, và đỏ do nấm nông ở chân. Ngoài ra, da cũng có thể sẫm màu trong bệnh Addison và có thể bị ảnh hưởng bởi bạch hầu. Da là cơ quan chịu ảnh hưởng của bệnh chàm và bệnh cước, tạo nên các vùng da bị đổi màu, sưng lên, phồng rộp và gây ngứa. Da cũng bị tổn thương do tiếp xúc với nhiệt độ lạnh, gây đỏ, ngứa, đau và loét.\n\nDa đóng vai trò quan trọng trong quá trình chuyển đổi androstenedione và DHEA thành testosterone. Nó cũng là vị trí ngoại vi quan trọng đòi hỏi sự chăm sóc đặc biệt và điều trị phù hợp để đảm bảo sức khỏe tổng thể. Da chịu ảnh hưởng kích thích từ dầu ba đậu và cần được làm sạch và lau khô trước khi thoa Bạch Hổ Hoạt Lạc Cao. Da cũng bị ảnh hưởng bởi bệnh phong thấp, làm các triệu chứng trở nên nghiêm trọng hơn. Trong bệnh tế bào mast hệ thống, da là nơi các tế bào mast dư thừa tích tụ. Da có thể gặp các triệu chứng như đau, đỏ, phát ban và đổ mồ hôi. Cuối cùng, da cũng là cơ quan có thể bị tổn thương bởi lupus ban đỏ hệ thống, amyloidosis, bệnh thoái hóa tinh bột, bệnh u hạt mạn tính, bệnh viêm mạch và đa u hạt dị ứng, viêm nang lông, và bệnh zona, biểu hiện qua mụn nước và cảm giác đau rát.\n\nDa chứa nhiều loại collagen, đặc biệt là loại I chiếm khoảng 90% lượng collagen trong cơ thể. Collagen giúp duy trì sự trẻ hóa cho da. Da có khả năng hấp thụ collagen để giảm các dấu hiệu lão hóa. Da là cơ quan được điều trị bằng kem và thuốc mỡ chứa corticosteroid. Da được bảo vệ và tăng độ đàn hồi nhờ các chất chống oxy hóa trong củ lùn. Da là bề mặt bị ảnh hưởng bởi viêm da tiếp xúc và hội chứng cai corticoid. Da là bề mặt ngoài cơ thể có thể bị ảnh hưởng bởi việc sử dụng corticoid, bao gồm teo da, khô da, và các triệu chứng khác. Da là bộ phận chịu ảnh hưởng bởi việc sử dụng corticosteroids. Da là bộ phận chịu ảnh hưởng bởi việc sử dụng corticoid thoa.\n\nDa cũng có thể nhợt nhạt, xanh xao hoặc đỏ bừng khi bị đau đầu cụm. Da cũng là bộ phận được thoa dầu bơ như một loại kem dưỡng ẩm và hưởng lợi ích từ việc sử dụng dầu bơ. Da là cơ quan được hỗ trợ làm đẹp bởi các dưỡng chất có trong dầu hạnh nhân. Da là lớp biểu mô trên cơ thể, nơi nốt ruồi mới mọc. Da là cơ quan mà dầu jojoba có tác dụng làm mềm, kiểm soát quá trình mất nước và tăng cường độ đàn hồi. Da là bộ phận cơ thể được làm mềm bởi dầu jojoba. Da là bề mặt ngoài của cơ thể, được chăm sóc bằng dầu jojoba. Da là khu vực mà dầu jojoba được sử dụng để chăm sóc. Da là cơ quan được bảo vệ và giữ gìn sự trẻ đẹp nhờ dầu tầm xuân. Da là bề mặt ngoài của cơ thể, được bảo vệ và chăm sóc bởi dầu tầm xuân. Da là bề mặt ngoài của cơ thể, nơi dầu tầm xuân được sử dụng để tái tạo và chữa lành.\n\nDa cũng bị kích ứng hoặc tổn thương, dẫn đến hình thành nang biểu bì. Ngoài những thông tin trên, da còn được mô tả như là lớp phủ bên ngoài của môi và má. Da cũng được chăm sóc và giảm đau, nhiễm trùng bằng lá Thường xuân. Da là cơ quan chịu ảnh hưởng trực tiếp từ lichen xơ hóa và chịu ảnh hưởng của corticosteroids khi điều trị lichen xơ hóa. Da là bề mặt được bảo vệ và cải thiện bởi gel Lô hội. Da được hỗ trợ bởi tinh dầu Manuka. Da được hỗ trợ săn chắc hơn nhờ vitamin và khoáng chất trong quả măng cụt.\n\nDa là cơ quan có khả năng bị xâm nhập bởi vi nấm sợi tơ. Da là cơ quan có khả năng bị ảnh hưởng bởi các yếu tố gây bệnh như vi khuẩn. Da là vùng cơ thể bị ảnh hưởng bởi mụn và các tác dụng phụ của thuốc kháng sinh. Da cũng là vùng bị ảnh hưởng bởi mụn trứng cá và được điều trị bằng các thuốc không kê đơn. Da cũng là vùng cơ thể bị ảnh hưởng bởi tác dụng của thuốc kháng sinh như tetracycline. Da là cơ quan mà muối biển giúp tẩy tế bào chết, thúc đẩy lưu thông máu, cân bằng độ ẩm. Da được hỗ trợ bảo vệ bởi nấm Chaga. Da là bề mặt ngoài của cơ thể, nơi xuất hiện nếp nhăn. Da là bộ phận bị ảnh hưởng bởi tia cực tím và thiếu dinh dưỡng, dẫn đến hình thành nếp nhăn. Da được làm đẹp và bảo vệ khỏi lão hóa bởi curcumin. Da được chăm sóc và cải thiện nhờ vào việc sử dụng tinh bột nghệ. Da vùng kín có thể bị kích ứng hoặc viêm, gây ngứa. Da là cơ quan có thể bị ảnh hưởng bởi bệnh Sarcoidosis. Ngoài ra, da có thể bị ảnh hưởng bởi hội chứng Sjogren. Da là vùng được Biafine trị bỏng. Da bị ảnh hưởng bởi viêm da tiết bã, trở nên đỏ và nhờn do lượng dầu dư thừa. Da cũng là bề mặt cơ thể nơi xuất hiện các sẩn hồng ban và tình trạng ngứa. Da chịu ảnh hưởng từ các chất trung gian hóa học, gây ra tình trạng ngứa. Da được làm đẹp nhờ hàm lượng vitamin A trong rau diếp. Da có thể trở nên khô và dày do suy giáp. Da được Thạch lựu bảo vệ khỏi tổn thương do tia UV.\n\nĐặc biệt, da có thể xuất hiện triệu chứng tăng sắc tố, dày sừng, hạt mụn cơm, rụng lông, tóc và thậm chí ung thư da do độc tính mạn tính. Da cũng là cơ quan nơi Asen vô cơ di chuyển đến sau khi hấp thụ qua đường tiêu hóa. Da là vị trí tác dụng chính của Acnotin. Da là cơ quan có thể bị ảnh hưởng bởi isotretinoin, gây ra các triệu chứng như ngoại ban, ngứa, viêm da, đổ mồ hôi u hạt mưng mủ, viêm quanh móng, teo móng, tăng tạo mô hạt, rụng tóc, xuất hiện nhiều trứng cá, rậm lông, tăng sắc tố, da tăng nhạy cảm ánh sáng.\n\nDa cũng bị ảnh hưởng bởi Betaserc, gây ra các phản ứng như sưng và phồng rộp. Da có thể bị rối loạn khi sử dụng Betaserc. Da là cơ quan có thể gặp các phản ứng dị ứng như ban da dạng sần, ngoại ban, nổi mày đay, ngứa khi sử dụng Cefadroxil. Da là vị trí điều trị của Cefpodoxim.\n\nNgoài ra, da có thể bị tác dụng phụ như phát ban, ngứa, nổi mề đay, phản ứng nhạy cảm với ánh sáng khi sử dụng Ciprobay. Da cũng có thể bị ảnh hưởng bởi tác dụng phụ của Combivent®. Da nhạy cảm với ánh nắng sau khi dùng Cordarone. Da là vị trí nhiễm khuẩn được điều trị bằng Cefoxitin.\n\nDa đóng vai trò quan trọng trong việc phát hiện thông tin cảm giác và đưa nó đến thùy đỉnh. Da cũng là vùng bị ảnh hưởng bởi thủy đậu và có thể dẫn đến sẹo lõm. Da là vùng cơ thể mà tinh dầu bạc hà có thể được thoa trực tiếp.\n\nDa chịu ảnh hưởng từ việc sử dụng tinh dầu Bergamot trong điều trị vảy nến. Da là vùng cơ thể được bảo vệ và kháng viêm bởi tinh dầu Bergamot.\n\nDa là bộ phận được chăm sóc và dưỡng ẩm bằng tinh dầu gừng. Da là cơ quan được bảo vệ và điều chỉnh bởi tinh dầu hoa anh thảo.\n\nDa có thể bị kích ứng nếu tinh dầu không được pha loãng trước khi sử dụng. Một vùng da nhỏ được sử dụng để kiểm tra phản ứng dị ứng với tinh dầu khuynh diệp. Da được chăm sóc và cải thiện bởi massage và tinh dầu, trở nên mịn màng, hồng hào, tươi trẻ và tràn đầy sức sống.\n\nDa là cơ quan có thể bị ảnh hưởng bởi coumarin trong tinh dầu quế. Làn da được cải thiện bởi tinh dầu nghệ. Tuy nhiên, da cũng có thể trở nên nhạy cảm hơn với tia UV khi sử dụng tinh dầu nghệ.\n\nDa là bộ phận dễ bị kích ứng bởi tinh dầu nếu không được pha loãng đúng cách. Da là bề mặt cơ thể có thể được dưỡng và bảo vệ khỏi các vết rạn da bằng các tinh dầu. Da bị co giãn nhanh, dẫn đến đứt gãy collagen và elastin, gây ra rạn da. Da là bộ phận mà tinh dầu trị rạn da được thoa lên để điều trị và phòng ngừa bệnh. Da là bề mặt được chăm sóc và điều trị bằng các tinh dầu và chiết xuất.\n\nDa cũng chịu ảnh hưởng của thiếu máu, thể hiện qua thay đổi màu sắc. Da là cơ quan được tăng độ đàn hồi bởi vitamin C trong trái tắc.\n\nDa vùng khớp có thể bị nề đỏ, đau hoặc có vạch đỏ chạy dọc các mạch máu khi có nhiễm trùng.\nClovir 200: Clovir 200 là viên nén chứa aciclovir, được sử dụng trong điều trị và dự phòng nhiễm virus.\nAcyclovir Stada 200 mg - Tiêu Chảy: Tiêu chảy là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Sự Nhân Lên Của Virus: Acyclovir ức chế sự nhân lên của virus.\nAcyclovir Stada 200 mg - Buồn Nôn: Buồn nôn là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Buồn nôn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Tế Bào Nhiễm Virus Herpes: Acyclovir có tác dụng chọn lọc trên tế bào nhiễm virus Herpes.\nAcyclovir Stada 200 mg - Chóng Mặt: Chóng mặt là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Triệu Chứng: Acyclovir được sử dụng để điều trị triệu chứng của bệnh.\nAcyclovir Stada 200 mg - Đau Đầu: Đau đầu là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Đau đầu là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Nhiễm HSV: Acyclovir được sử dụng để điều trị nhiễm HSV.\nAcyclovir Stada 200 mg - Sốt: Sốt là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Da: Acyclovir được chỉ định điều trị nhiễm virus Herpes simplex trên da.\nAcyclovir Stada 200 mg - Suy Thận: Liều và số lần uống Acyclovir Stada 200 mg phải được điều chỉnh tùy theo mức độ tổn thương thận.&lt;SEP&gt;Bệnh nhân suy thận cần điều chỉnh liều acyclovir.\nAcyclovir - Kem Acyclovir: Kem acyclovir là dạng thuốc tại chỗ của acyclovir.\nAcyclovir Stada 200 mg - Đau Bụng: Đau bụng là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Liều Dùng: Liều dùng là phương pháp điều chỉnh lượng thuốc Acyclovir dựa trên tình trạng sức khỏe của bệnh nhân.\nAcyclovir Stada 200 mg - Mệt Mỏi: Mệt mỏi là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir - Niêm Mạc: Acyclovir được chỉ định điều trị nhiễm virus Herpes simplex trên niêm mạc.\nAcyclovir Stada 200 mg - Nôn: Nôn là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.&lt;SEP&gt;Nôn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir - Viêm Nhiễm Do Virus Herpes Simplex: Acyclovir được sử dụng để điều trị viêm nhiễm do virus Herpes simplex.\nAcyclovir Stada 200 mg - Ngứa: Ngứa là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAciclovir - Virus Herpes: Aciclovir được chỉ định trong điều trị và dự phòng nhiễm virus Herpes.\nDa - Herpes Simplex: Nhiễm virus Herpes simplex có thể ảnh hưởng đến da.\nAcyclovir Stada 200 mg - Quá Liều: Quá liều acyclovir có thể gây ra các triệu chứng trên đường tiêu hóa và thần kinh.\nAcyclovir Stada 200 mg - Phụ Nữ Mang Thai: Acyclovir Stada 200 mg chưa có nghiên cứu đầy đủ và có kiểm soát trên phụ nữ mang thai.\nAcyclovir Stada 200 mg - Buồn Ngủ: Buồn ngủ là tác dụng phụ thường gặp khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Cimetidin: Cimetidin cạnh tranh bài tiết chủ động qua các ống thận và làm giảm độ thanh thải của acyclovir ở thận khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Phát Ban: Phát ban là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nHerpes Simplex - Tỏi: Chiết xuất tỏi có tác dụng kháng virus Herpes simplex.\nAcyclovir - Acyclovir Stada 200 mg: Acyclovir là hoạt chất chính của thuốc Acyclovir Stada 200 mg.&lt;SEP&gt;Acyclovir là hoạt chất chính của Acyclovir Stada 200 mg.&lt;SEP&gt;Acyclovir Stada 200 mg thuộc loại thuốc Acyclovir.\nAcyclovir Stada 200 mg - Thần Kinh: Tác dụng không mong muốn của acyclovir có thể ảnh hưởng đến hệ thần kinh.\nBetamethasone - Herpes Zoster: Dùng Betamethasone đường toàn thân làm tăng nguy cơ bị herpes zoster.\nAcyclovir - Herpes Simplex: Quan hệ giữa Acyclovir và Herpes Simplex được mô tả như sau: Acyclovir được sử dụng để điều trị và phòng ngừa nhiễm Herpes simplex. Nó có tác dụng mạnh nhất đối với virus Herpes simplex type 1 và cũng có tác dụng chọn lọc trên tế bào bị nhiễm virus này. Acyclovir nhắm trúng đích vào virus Herpes simplex, giúp kiểm soát và ngăn chặn sự phát triển của bệnh.&lt;SEP&gt;Acyclovir tác dụng chọn lọc trên tế bào nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir được chỉ định dùng trong điều trị nhiễm Herpes simplex.\nAcyclovir Stada 200 mg - Cho Con Bú: Phụ nữ cho con bú cần chú ý khi sử dụng acyclovir.\nBetadine - Herpes Simplex: Betadine được dùng để điều trị herpes simplex.\nAciclovir - Herpes Simplex: Aciclovir được chỉ định trong điều trị nhiễm virus Herpes simplex.\nAcyclovir Stada 200 mg - Mang Thai: Acyclovir Stada 200 mg chưa có nghiên cứu đầy đủ và có kiểm soát trên phụ nữ mang thai.&lt;SEP&gt;Phụ nữ mang thai cần chú ý khi sử dụng acyclovir do thiếu nghiên cứu đầy đủ và có kiểm soát.\nHerpes Simplex - Mắt: Nhiễm virus Herpes simplex có thể ảnh hưởng đến mắt.\nAciclovir 800 mg - Mất Nước: Bệnh nhân mất nước cần chú ý khi dùng Aciclovir 800 mg.\nAcyclovir Stada 200 mg - Mẫn Cảm: Acyclovir Stada 200 mg chống chỉ định đối với bệnh nhân mẫn cảm với acyclovir và valacyclovir hay bất cứ thành phần nào của thuốc.\nAcyclovir - Herpes Zoster: Acyclovir được chỉ định dùng trong điều trị nhiễm Herpes zoster.\nHerpes Simplex - Kim Ngân Hoa: Kim Ngân Hoa có tác dụng chống virus Herpes simplex.\nAcyclovir Stada 200 mg - Probenecid: Khi sử dụng đồng thời Probenecid và Acyclovir Stada 200 mg có thể gây ức chế cạnh.&lt;SEP&gt;Probenecid ức chế cạnh tranh đào thải acyclovir qua ống thận khi sử dụng cùng Acyclovir Stada 200 mg.\nAciclovir - Aciclovir 200mg: Aciclovir được chỉ định trong điều trị nhiễm virus Herpes simplex dưới dạng viên nén 200 mg.\nAciclovir - Agiclovir 200: Agiclovir 200 chứa aciclovir.\nAciclovir - Clovir 200: Clovir 200 chứa aciclovir.\nAciclovir - Ikovir-200: Ikovir-200 chứa aciclovir.\nAciclovir - Eurovir 200 mg: Eurovir 200 mg chứa aciclovir.\nAciclovir - Disvir 200: Disvir 200 chứa aciclovir.\nAcyclovir Stada 200 mg - Lú Lẫn: Lú lẫn là một trong những tác dụng phụ khi dùng quá liều acyclovir.\nAcyclovir Stada 200 mg - Cyclosporin: Cyclosporin có các dấu hiệu độc tính trên thận khi sử dụng cùng Acyclovir Stada 200 mg.\nGiác Mạc - Herpes Simplex: Nhiễm virus Herpes simplex có thể ảnh hưởng đến giác mạc.\nHerpes Simplex - Não: Nhiễm virus Herpes simplex có thể ảnh hưởng đến não.\nAcyclovir Stella 400 mg - Herpes Simplex: Thuốc Acyclovir Stella 400 mg được chỉ định điều trị nhiễm virus Herpes simplex da và niêm mạc.&lt;SEP&gt;Acyclovir Stella 400 mg được sử dụng để điều trị bệnh herpes simplex.\nHerpes Simplex - Niêm Mạc: Nhiễm virus Herpes simplex có thể ảnh hưởng đến niêm mạc.\nAcyclovir Stada 200 mg - Thẩm Phân Máu: Sau mỗi lần thẩm phân máu cần bổ sung ngay 1 liều Acyclovir Stada 200 mg.&lt;SEP&gt;Thẩm phân máu được sử dụng để kiểm soát độc tính khi dùng quá liều acyclovir.\nAcyclovir Stada 200 mg - Ketoconazol: Ketoconazol làm tăng hiệu lực chống virus của acyclovir khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Herpes Simplex: Thuốc Acyclovir Stada 200 mg được chỉ định điều trị và dự phòng nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir Stada 200 mg được sử dụng để điều trị herpes simplex.\nAcyclovir Stella 800 mg - Herpes Simplex: Acyclovir Stella 800 mg được chỉ định dùng trong điều trị nhiễm virus Herpes simplex.\nAcyclovir Boston 800 - Herpes Simplex: Thuốc Acyclovir Boston 800 được chỉ định dùng để điều trị và dự phòng nhiễm virus Herpes simplex.\nHerpes Simplex - Kim Vàng: Kim vàng kháng virus herpes simplex.\nAcyclovir Stada 200 mg - Amphotericin B: Amphotericin B làm tăng hiệu lực chống virus của acyclovir khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Thanh Thải Creatinin: Thanh thải creatinin giúp xác định liều dùng Acyclovir Stada 200 mg phù hợp với bệnh nhân suy thận.\nAcyclovir Stada 200 mg - Zidovudin: Khi sử dụng đồng thời Zidovudin và Acyclovir Stada 200 mg có thể gây trạng thái lơ mơ và ngủ lịm.&lt;SEP&gt;Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây trạng thái lơ mơ và ngủ lịm.\nAcyclovir Stada 200 mg - Viêm Giác Mạc: Acyclovir Stada 200 mg được chỉ định điều trị viêm giác mạc do nhiễm virus.\nAcyclovir Stada 200 mg - Theophyllin: Theophyllin tăng xấp xỉ 50% AUC của mình khi sử dụng cùng Acyclovir Stada 200 mg.\nB – Sol - Herpes Simplex: B – Sol chống chỉ định sử dụng đối với những người bị nhiễm herpes simplex.\nAcyclovir Stada 200 mg - Varicella Zoster: Thuốc Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Varicella zoster.&lt;SEP&gt;Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Varicella zoster.\nAcyclovir Stada 200 mg - Suy Chức Năng Thận: Bệnh nhân suy chức năng thận có thể gặp tác dụng phụ buồn ngủ và ngủ lơ mơ khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stella Cream - Herpes Simplex: Acyclovir Stella Cream được sử dụng để điều trị nhiễm virus Herpes simplex.&lt;SEP&gt;Acyclovir Stella Cream được sử dụng để điều trị nhiễm Herpes simplex.\nAcyclovir Stada 200 mg - Valacyclovir: Acyclovir Stada 200 mg chống chỉ định đối với bệnh nhân mẫn cảm với acyclovir và valacyclovir hay bất cứ thành phần nào của thuốc.\nAcyclovir Stada 200 mg - Herpes Simplex Type 1: Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Herpes simplex type 1.\nAcyclovir Stada 200 mg - Herpes Simplex Type 2: Acyclovir Stada 200 mg được chỉ định điều trị nhiễm virus Herpes simplex type 2.\nAcyclovir Stada 200 mg - Nhạy Cảm Với Ánh Sáng: Nhạy cảm với ánh sáng là tác dụng phụ thường gặp của Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Ngủ Lơ Mơ: Ngủ lơ mơ là tác dụng phụ thường gặp khi sử dụng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Bệnh Nhân Lớn Tuổi: Bệnh nhân lớn tuổi cần điều chỉnh liều acyclovir do thường có suy giảm chức năng thận.\nAcyclovir Stada 200 mg - Độc Tính Trên Thận: Sử dụng Acyclovir Stada 200 mg cùng Cyclosporin có thể gây độc tính trên thận.\nAcyclovir Stada 200 mg - Herpes Zoster: Acyclovir Stada 200 mg được sử dụng để điều trị herpes zoster.\nAcyclovir Stada 200 mg - Ngủ Lịm: Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây ngủ lịm.\nAciclovir 800 mg - Môi: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex ở môi.\nAcyclovir Stada 200 mg - Mycophenolat mofetil: Mycophenolat mofetil tăng AUC trong huyết tương của acyclovir và chất chuyển hóa không có hoạt tính của mình khi sử dụng cùng Acyclovir Stada 200 mg.\nAcyclovir Stada 200 mg - Trạng Thái Lơ Mơ: Sử dụng Acyclovir Stada 200 mg cùng Zidovudin có thể gây trạng thái lơ mơ.\nC. Nutans - Herpes Simplex: *C. nutans* được sử dụng để điều trị tổn thương do Herpes simplex.\nAciclovir 800 mg - Tổn Thương Thận: Bệnh nhân có tổn thương thận cần chú ý khi dùng Aciclovir 800 mg.\nAciclovir 800 mg - Creatinin: Bệnh nhân cần chú ý về creatinin khi dùng Aciclovir 800 mg.\nAgiclovir 5% Agimexpharm - Herpes Simplex: Agiclovir 5% Agimexpharm được sử dụng để điều trị nhiễm virus Herpes simplex.\nAciclovir 800 mg - Herpes Simplex: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex.\nAcyclovir 5% Agimexpharm - Herpes Simplex: Thuốc Acyclovir 5% Agimexpharm được chỉ định điều trị bệnh Herpes simplex.\nHerpes Simplex - Màng Não: Nhiễm virus Herpes simplex có thể ảnh hưởng đến màng não.\nHerpes Simplex - Ngăn Ngừa Tái Phát: Ngăn ngừa tái phát là phương pháp điều trị nhằm ngăn chặn sự tái phát của bệnh Herpes simplex.\nHerpes Simplex - Ngăn Ngừa Nhiễm: Ngăn ngừa nhiễm là phương pháp điều trị nhằm ngăn chặn sự nhiễm bệnh Herpes simplex.\nHerpes Simplex - Virus Kháng Thuốc: Virus kháng thuốc trở thành vấn đề lớn cho người bệnh suy giảm miễn dịch, đặc biệt là nhiễm virus Herpes simplex.\nAciclovir 800 mg - Nhiễm HIV: Bệnh nhân nhiễm HIV cần chú ý khi dùng Aciclovir 800 mg.\nAciclovir 800 mg - Tiêm Truyền Tĩnh Mạch: Aciclovir 800 mg được dùng qua tiêm truyền tĩnh mạch.\nAciclovir 800 mg - Thuốc Mỡ: Aciclovir 800 mg được dùng qua thuốc mỡ.\nAciclovir 800 mg - Herpes Zoster: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes zoster.\nAciclovir 800 mg - Sinh Dục: Aciclovir 800 mg được chỉ định để điều trị nhiễm Herpes simplex ở sinh dục.\nAciclovir 800 mg - Bôi: Aciclovir 800 mg được dùng qua bôi.\nAciclovir 800 mg - Độc Thận: Bệnh nhân cần chú ý về độc thận khi dùng Aciclovir 800 mg cùng với các thuốc khác.\nAciclovir 800 mg - Tra Mắt: Aciclovir 800 mg được dùng qua tra mắt.']</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thuốc **Acyclovir Stada 200 mg** có tác dụng mạnh nhất đối với virus **Herpes simplex** type 1. Độ nhạy với Acyclovir Stada 200 mg giảm dần đối với virus **Herpes simplex** type 2 và virus **Varicella zoster**.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Acyclovir Stada 200 mg có tác dụng mạnh nhất trên virus Herpes simplex type 1, kém hơn ở virus Herpes simplex 2 và virus Varicella zoster.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8443636521970252</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8777575796909229</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần làm gì?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>['Tăng Alanine: Tăng alanine là xét nghiệm đánh giá chức năng gan.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nKiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ, đặc biệt là chức năng gan, thận và hệ tạo máu nếu sử dụng Augmentin kéo dài.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ là việc khám sức khỏe theo lịch hẹn tái khám của bác sĩ hoặc khám ngay khi có dấu hiệu bất thường.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ để đánh giá chức năng gan và tầm soát viêm gan siêu vi B, C.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ giúp phát hiện tình trạng tăng huyết áp vô căn.&lt;SEP&gt;Kiểm tra sức khỏe định kỳ là việc kiểm tra sức khỏe nhằm phát hiện sớm các vấn đề về sức khỏe.\nThăm Khám: Thăm khám là quy trình kiểm tra sức khỏe được thực hiện bởi bác sĩ và chuyên gia y tế, nhằm xác định tình trạng sức khỏe của bệnh nhân. Quá trình thăm khám bao gồm việc kiểm tra sức khỏe tổng quát cũng như việc phát hiện các bệnh lý cụ thể. Thăm khám đóng vai trò quan trọng trong việc xác định tình trạng bệnh và nguyên nhân gây bệnh, giúp phát hiện sớm các vấn đề sức khỏe như áp-xe phổi, viêm phổi kẽ, và bệnh nấm da đùi. \n\nThăm khám không chỉ giúp bác sĩ nắm bắt thông tin về bệnh nhân mà còn là bước kiểm tra cần thiết để đánh giá tình trạng sức khỏe của bệnh nhân và xác định tình trạng bệnh lý. Qua quá trình thăm khám, mọi dấu hiệu và triệu chứng đều được đánh giá một cách kỹ lưỡng và toàn diện, từ đó hỗ trợ việc chẩn đoán bệnh lichen xơ hóa và loạn sản khớp háng ở trẻ em. \n\nNgoài ra, thăm khám còn giúp phát hiện tác dụng phụ do quá liều của một số thuốc như Carsantin. Thăm khám cũng đóng vai trò quan trọng trong việc xác định nguyên nhân và phương pháp điều trị thích hợp cho nhiều tình trạng khác nhau như phì đại tiền liệt tuyến, rụng tóc vành khăn ở trẻ, và sỏi mật.&lt;SEP&gt;Thăm khám tại các cơ sở y tế để được điều trị kịp thời khi có triệu chứng suy gan.&lt;SEP&gt;Thăm khám là quy trình kiểm tra sức khỏe nhằm phát hiện sớm và điều trị suy gan.&lt;SEP&gt;Thăm khám là quá trình bác sĩ kiểm tra sức khỏe người bệnh.&lt;SEP&gt;Thăm khám là quy trình kiểm tra sức khỏe do bác sĩ chuyên khoa nội tiết thực hiện.\nThông Tin Sử Dụng Thuốc: Thông tin sử dụng thuốc Acemol 325 mg bao gồm hướng dẫn bảo quản và cảnh báo về các tác dụng phụ nghiêm trọng.&lt;SEP&gt;Thông tin hướng dẫn sử dụng Dalacin T nhằm đảm bảo hiệu quả và an toàn khi sử dụng.\nNhững Lưu Ý Trước Khi Khám: Những lưu ý trước khi khám là những hướng dẫn cần tuân theo trước khi đi khám.\nXét Nghiệm Tìm Yếu Tố Dị Ứng: Xét nghiệm tìm yếu tố dị ứng trên da để có kế hoạch điều trị và phòng ngừa bệnh tái phát.\nThuốc Bổ Sung: Thuốc bổ sung là loại thuốc có thể được sử dụng để hỗ trợ điều trị gù cột sống.\nLẫy Da: Lẫy da là xét nghiệm dị ứng giúp chẩn đoán nguyên nhân gây mề đay.\nViệc Trao Đổi Với Bác Sĩ: Việc trao đổi với bác sĩ trước khi dùng bất kỳ loại thuốc nào để tránh các tác dụng phụ không đáng có.\nChẩn Đoán Dị Ứng Thời Tiết: Chẩn đoán dị ứng thời tiết bao gồm việc hỏi, khám và thực hiện xét nghiệm dị ứng.\nA.T.P: Thuốc A.T.P được chỉ định trong hỗ trợ điều trị chứng đau lưng.&lt;SEP&gt;A.T.P là thuốc giãn cơ, chứa hoạt chất dinatri adenosin triphosphat.&lt;SEP&gt;A.T.P là thuốc được đề cập trong bài viết.\nTest Da: Test da là phương pháp chẩn đoán dị ứng lúa mì thông qua tiêm dị nguyên vào da.\nThận: Thận là một cơ quan nội tạng quan trọng của cơ thể, thường có hình dạng giống hạt đậu và được tìm thấy ở hai bên cột sống, nằm dưới xương sườn và phía sau bụng, sau phúc mạc. Ở người trưởng thành, thận có chiều dài khoảng 12cm. Thận chịu trách nhiệm thực hiện nhiều chức năng thiết yếu, bao gồm lọc máu, tạo nước tiểu, duy trì cân bằng nước và điện giải, loại bỏ chất thải, tiết renin, erythropoietin, tham gia chuyển hóa vitamin D, và bài tiết bilirubin liên hợp. Bilirubin liên hợp được thận chuyển đổi thành dạng không liên hợp và thải ra ngoài.\n\nThận chịu tác động từ nhiều loại thuốc khác nhau, bao gồm ATP, ibuprofen syrup, paracetamol, Aclasta, corticoid, acetaminophen, Acnekyn, Actiso, Acetylcystein, Agi-Calci, thuốc thiazide, và Algelstad. Việc sử dụng các loại thuốc này có thể gây ra các tác dụng phụ nghiêm trọng như viêm thận kẽ, suy thận cấp và hội chứng thận hư. Trước khi bắt đầu điều trị bằng các loại thuốc có khả năng gây độc thận, cần kiểm tra chức năng thận và có thể cần giảm liều domperidone. Thận cũng chịu tác động từ việc sử dụng Amoxicillin Domesco, ampicillin, và metformin, đặc biệt khi sử dụng Amoxicillin. Thận chịu tác động từ việc sử dụng Amlodipin, đặc biệt khi mới bắt đầu điều trị. Thận chịu tác động từ nhiều yếu tố khác như nhịn tiểu và tăng huyết áp.\n\nTrong y học cổ truyền, thận được coi là một kinh, có vai trò quan trọng trong việc điều hòa và duy trì sự cân bằng trong cơ thể. Thận là tạng đóng vai trò "tiên thiên", quyết định trực tiếp đến sức sống toàn thân. Thận chịu ảnh hưởng từ việc sử dụng nhiều loại thuốc khác nhau, bao gồm Alputine, Aluminium Phosphat Gel, Amikacin Bidiphar, Amikain Bidiphar, Alzole TvPharm, và Augbidil, đặc biệt khi chức năng thận giảm (GFR &lt; 10 ml/phút).\n\nThận chịu tác động từ nhiều bệnh lý khác nhau như bệnh bạch hầu trong giai đoạn nặng, chứng aldosterone nguyên phát, bệnh cầu thận màng, viêm gan B hoặc C, bệnh thận đa nang, và amyloidosis. Chức năng thận cần được giám sát bằng xét nghiệm eGFR trước khi bắt đầu điều trị bằng amlodipin. Thận cũng có thể bị ảnh hưởng bởi bệnh bạch hầu trong giai đoạn nặng và chịu ảnh hưởng từ chứng aldosterone nguyên phát. Thận chịu ảnh hưởng trong bệnh cầu thận màng, dẫn đến các biến chứng như hội chứng thận hư, tổn thương thận cấp và bệnh thận mạn. Thận cũng chịu tổn thương do các bệnh như viêm gan B hoặc C. Thận cũng chịu ảnh hưởng bởi bệnh thận đa nang, có nhiều nang xuất hiện.\n\nThận cũng được sử dụng trong việc điều trị bổ thận tráng dương, điều trị bằng cát sâm, xử lý sỏi thận bằng La rừng, và liên quan đến tác dụng của rễ cây Sậy và cây Sậy trong quy kinh. Thận là một cơ quan mà Tỏa dương giúp bồi bổ, tăng cường sinh lý và lợi tiểu. Thận cũng được kiểm tra về tác dụng độc của chiết xuất lá xương khỉ. Thận cần được đánh giá chức năng khi dùng Cefuroxim axetil. Thận chịu ảnh hưởng khi dùng Chu Sa, đặc biệt đối với những người có chức năng thận kém. Thận cũng chịu ảnh hưởng của xơ vữa động mạch do rối loạn chuyển hóa mạn tính và tổn thương do tăng đường huyết mạn tính. Rượu chuối hột rừng có thể chữa bệnh thận và chuối hột hỗ trợ thận trong việc chữa bệnh thận, sỏi thận. Thận cũng được bảo vệ bởi dịch chiết cỏ mần trầu. Thận chịu ảnh hưởng từ chất nhựa mủ của cỏ sữa.\n\nThận là một cơ quan mỏng manh trong cơ thể được bảo vệ bởi collagen. Thận cũng dễ bị tổn thương bởi việc sử dụng Phòng kỷ và củ dòm. Thận cần được kiểm tra chức năng trước khi bắt đầu điều trị bằng Coveram. Thận được bổ sung bởi Cốt toái bổ. Thận chịu ảnh hưởng của Crinone khi người bệnh có vấn đề về thận. Thận là bộ phận được củ nén bổ sung. Thận là cơ quan nơi tái hấp thu natri và đảm bảo cân bằng điện giải trong máu. Thận cũng là một cơ quan cần được kiểm tra trong quá trình tầm soát biến chứng tiểu đường type 1. Thận chịu trách nhiệm cô đặc nước tiểu trong đái tháo nhạt. Thận chịu ảnh hưởng từ việc sử dụng thuốc clindamycin. Thận là một cơ quan cần được đánh giá chức năng trước khi sử dụng Pregabalin. Thận chịu ảnh hưởng khi sử dụng đậu mèo. Thận là cơ quan cần được bảo vệ khỏi biến cố tim mạch. Thận có thể gặp triệu chứng như rối loạn tiểu tiện. Thận là cơ quan thải trừ chủ yếu của thuốc và cần được theo dõi khi sử dụng Pregabalin, đặc biệt đối với bệnh nhân có bệnh nền đái tháo đường hoặc suy tim. Thận chịu trách nhiệm thải CO2 ra khỏi cơ thể mẹ khi mẹ thở ra và có thể bị dị tật bẩm sinh khi thai có dây rốn một động mạch. Thận cũng có thể bị ảnh hưởng bởi độc tính của rotenone.\n\nThận là cơ quan được Dây tơ hồng và Địa cốt bì điều trị. Thận cũng là cơ quan được điều trị bằng đỗ trọng. Thận là cơ quan quy kinh của Lưu huỳnh. Thận liên quan đến các bệnh như khó tiêu, lỵ, phù, bệnh lậu và đái tháo đường, được điều trị bằng Diệp hạ châu đắng. Trong y học cổ truyền, thận được coi là một kinh, có vai trò quan trọng trong việc điều hòa và duy trì sự cân bằng trong cơ thể. Thận cũng được Đông trùng hạ thảo bảo vệ. Thận là một cơ quan quan trọng chịu ảnh hưởng từ tình trạng tỳ thận thấp nhiệt gây ra khí hư màu vàng. Thận cũng được bổ trợ bởi đường phèn để tăng cường sức khỏe và điều hòa. Ngoài ra, thận là cơ quan chứa nồng độ fluor cao hơn trong huyết thanh. Thận nằm dưới xương sườn và có thể bị tổn thương nếu xương sườn bị gãy hoặc di chuyển. Thận chịu trách nhiệm thải axit uric khỏi cơ thể, nếu thận hoạt động kém hiệu quả thì nguy cơ mắc bệnh gout tăng cao. Thận chịu ảnh hưởng bởi huyết áp thấp. Khảo sát chức năng thận là một phần của việc chẩn đoán hạ huyết áp. Thận chịu ảnh hưởng khi máu không được bơm đầy đủ do hạ huyết áp. Thận chịu ảnh hưởng khi bị hạ huyết áp. Thận là cơ quan liên quan đến Hắc sâm. Thận là cơ quan đào thải kim loại nặng qua đường niệu nhờ tác dụng của Selenium có trong Hải sâm. Thận chịu tổn thương và được cải thiện chức năng bởi Hải sâm. Thận là bộ phận được hạt kê bổ sung theo y học cổ truyền. Ngoài ra, thận là một cơ quan giải phóng Dopamine từ dây thần kinh giao cảm. Thận chịu ảnh hưởng bởi hẹp động mạch thận. Thận cũng có thể xuất hiện khối u carcinoid. Trong y học cổ truyền, thận là cơ quan được điều trị bằng rễ cây hương bài ở Thái Lan. Thận được bảo vệ khỏi tổn thương chuyển hóa do nồng độ glucose cao gây ra. Thận cũng được bảo vệ bởi chiết xuất Hương thảo trong cồn chống lại tác dụng độc hại do chì. Thận là đối tượng thử nghiệm tác dụng tăng sự chuyển hóa phosphate của Kê huyết đằng. Thận là cơ quan cần xét nghiệm chức năng trước khi dùng cloramphenicol. Thận cần được theo dõi định kỳ khi sử dụng Clindamycin. Thận cũng liên quan đến tác dụng của Khiếm Thực trong y học cổ truyền và được bảo vệ bởi Khiếm thực. Thận cần được xét nghiệm chức năng trước khi dùng Cetirizine. Thận là cơ quan mà Lô căn tác động. Thận chịu ảnh hưởng độc tính của lược vàng khi sử dụng lâu dài hoặc ở liều cao. Thận là cơ quan liên quan đến việc điều trị sỏi thận bằng cây mã đề. Mía lau có thể gây hại cho thận nếu sử dụng quá nhiều, đặc biệt đối với người bị sỏi thận. Sử dụng nhiều muối có thể gây hại cho thận, đặc biệt là ở trẻ em. Ngoài ra, thận cũng được bảo vệ bởi mướp tây. Thận của chuột thí nghiệm không bị độc tính từ polysaccharides trong nấm Chaga. Thận là cơ quan không bị độc tính từ polysaccharides từ nấm. Thận cũng có thể bị suy do ngộ độc thực phẩm. Thận là bộ phận được bổ sung nhờ ngũ vị tử. Thận cũng là cơ quan được Nhũ hương hoạt huyết. Thận là cơ quan được Nhục thung dung bổ sung, giúp tăng cường khả năng miễn dịch và chức năng thực bào của đại thực bào. Thận cũng có thể bị ảnh hưởng bởi việc sử dụng thuốc điều trị khô mắt. Thận có thể bị ảnh hưởng bởi Sarcoidosis, gây sỏi thận và giảm chức năng thận. Thận cũng có thể bị ảnh hưởng bởi hội chứng Sjogren. Thận cũng chịu ảnh hưởng bởi biến chứng của đái tháo đường type 2. Thận cũng có thể gặp vấn đề khi hấp thụ quá nhiều protein. Ngoài ra, thận cũng có thể bị ảnh hưởng bởi bệnh cúm. Thận có vai trò thanh lọc và điều chỉnh dịch trong cơ thể, ảnh hưởng đến tình trạng phù phổi. Thận cũng được bổ sung bởi Quy Bản. Thận chịu tác động độc tính từ chiết xuất lá mùi tây ở liều cao. Đồng thời, thận cũng chịu trách nhiệm cân bằng lượng phosphate trong cơ thể. Thận chịu tác động từ polysaccharides trong rong biển. Rong biển giúp bảo vệ thận. Thận cũng chịu ảnh hưởng bởi vi rút Lassa trong bệnh sốt xuất huyết Lassa. Thận tạo ra nước tiểu bằng cách lọc chất thải và thêm nước từ máu. Thận cũng có thể bị tổn thương do tăng huyết áp ác tính. Thận chịu tác động trong tăng huyết áp cấp cứu. Thận cũng chịu tác động từ bệnh BPH. Ngoài ra, thận là cơ quan nơi Asen vô cơ di chuyển đến sau khi hấp thụ qua đường tiêu hóa. Thận cũng là kinh mạch mà thiên môn đông tác động vào. Thận là bộ phận được thỏ ty tử bổ sung theo y học cổ truyền. Thận cũng dễ bị kết tủa aciclovir nếu không đủ nước và chịu tác động của quá liều aciclovir, cần được thẩm phân máu. Thận cũng chịu tác động từ việc sử dụng Aciclovir khi tiêm tĩnh mạch liều quá cao. Thận là cơ quan cần được đánh giá giữa lợi ích và nguy cơ khi sử dụng Acnotin. Chức năng thận cần được chú ý đặc biệt khi điều trị bằng Chlopheniramin. Thận chịu trách nhiệm thải kali khỏi cơ thể, cần đánh giá tác dụng nhất thời đối với thận trước khi sử dụng Arginin. Thận là cơ quan cần được chú ý khi điều chỉnh liều dùng của thuốc Artreil cho bệnh nhân có suy thận. Thận cũng có thể bị suy giảm chức năng bởi Aspirin. Thận cũng dễ bị sỏi thận do quá liều vitamin C. Thận là cơ quan cần được thông báo tình trạng bệnh lý trước khi sử dụng Bactroban. Thận là cơ quan cần được kiểm tra chức năng khi dùng thuốc Bifril. Thận chịu tác động của Chophytol, tăng đào thải nước tiểu qua đường niệu. Thận là cơ quan nội tạng quan trọng chịu tác động từ nhiều yếu tố khác nhau, cần được bảo vệ và chăm sóc kỹ lưỡng để đảm bảo chức năng hoạt động tối ưu. Thận cũng cần được kiểm tra định kỳ trong suốt quá trình điều trị bằng Claminat. Thận chịu tác động từ hội chứng QT kéo dài do thuốc cisaprid. Thận là cơ quan bị ảnh hưởng bởi việc dùng thuốc deferasirox (Exjade). Thuốc deferasirox cũng có thể gây tác dụng phụ, ảnh hưởng đến thận. Thận là một cơ quan cần được bảo vệ và theo dõi chặt chẽ khi sử dụng deferasirox. Thận cũng là cơ quan đào thải thuốc. Thận chịu tác động từ việc sử dụng Moxifloxacin, bao gồm tăng albumin huyết thanh. Thận chịu tác động từ việc sử dụng Crestor liều cao. Thận có thể bị lắng đọng nếu sử dụng thuốc Avisure Safoli vào buổi tối. Thận có thể bị độc bởi neomycin, cần theo dõi chức năng thận. Ngoài ra, thận liên quan đến việc điều trị các triệu chứng như liệt dương, di tinh, tiểu đêm. Thận là cơ quan dễ bị ảnh hưởng bởi biến chứng mạn tính của bệnh Đái tháo đường và tiền đái tháo đường.\n\nThận cũng là một cơ quan nội tiết nằm cạnh tuyến thượng thận, cùng đóng vai trò quan trọng trong việc điều hòa hoạt động sống của cơ thể.\nMen Gan Transaminase: Men gan transaminase là xét nghiệm đánh giá chức năng gan.\nKiểm Tra Sức Khỏe Định Kỳ - Đau Bụng: Kiểm tra sức khỏe định kỳ giúp phát hiện và theo dõi dấu hiệu đau bụng.\nThuốc - Thăm Khám: Thăm khám nên được tiến hành trước khi sử dụng thuốc để ngăn chặn tác dụng phụ.\nKiểm Tra Sức Khỏe Định Kỳ - Suy Gan: Kiểm tra sức khỏe định kỳ để đánh giá chức năng gan và tầm soát bệnh.\nNhững Lưu Ý Trước Khi Khám - Thuốc Bổ Sung: Liệt kê các thuốc đang dùng, bao gồm cả vitamin và thuốc bổ sung, là một trong những lưu ý cần tuân theo trước khi khám.\nAugmentin - Kiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ, đặc biệt là chức năng gan, thận và hệ tạo máu nếu sử dụng Augmentin kéo dài.\nThuốc - Việc Trao Đổi Với Bác Sĩ: Việc trao đổi với bác sĩ trước khi dùng bất kỳ loại thuốc nào để tránh các tác dụng phụ không đáng có.\nChẩn Đoán Dị Ứng Thời Tiết - Viêm Mũi Dị Ứng: Chẩn đoán viêm mũi dị ứng là mục tiêu của chẩn đoán dị ứng thời tiết.\nA.T.P - Thận: Kiểm tra chức năng thận cần thiết trước khi sử dụng thuốc A.T.P.\nLẫy Da - Mề Đay: Lẫy da là xét nghiệm giúp chẩn đoán nguyên nhân gây mề đay.\nKiểm Tra Thuốc - Ma Túy: Kiểm tra thuốc trước khi sử dụng khi mang thai để đánh giá tác động của ma túy đến thai nhi.\nMen Gan Transaminase - Rosuvastatin: Rosuvastatin được kiểm tra men gan transaminase trước khi sử dụng.\nKiểm Tra Thuốc - Rượu: Kiểm tra thuốc trước khi sử dụng khi mang thai để đánh giá tác động của rượu đến thai nhi.\nBệnh Tim Mạch - Kiểm Tra Sức Khỏe Định Kỳ: Kiểm tra sức khỏe định kỳ giúp phát hiện sớm các vấn đề về sức khỏe, bao gồm cả bệnh tim mạch.\nTham Khảo Ý Kiến Bác Sĩ - Vị Thuốc: Bạn cần tham khảo ý kiến bác sĩ trước khi sử dụng các vị thuốc.\nDị Ứng Lúa Mì - Test Da: Test da là phương pháp chẩn đoán dị ứng lúa mì.\nKiểm Tra Thuốc - Thuốc Lá: Kiểm tra thuốc trước khi sử dụng khi mang thai để đánh giá tác động của hút thuốc lá đến thai nhi.\nAcemol 325 mg - Thông Tin Sử Dụng Thuốc: Thông tin sử dụng thuốc Acemol 325 mg cung cấp hướng dẫn bảo quản và cảnh báo về các tác dụng phụ nghiêm trọng.\nBricanyl - Xét Nghiệm Đường Huyết: Xét nghiệm đường huyết cần được thực hiện trước khi dùng thuốc Bricanyl.\nKiểm Tra Sức Khỏe Định Kỳ - Tăng Huyết Áp Vô Căn: Kiểm tra sức khỏe định kỳ giúp phát hiện tình trạng tăng huyết áp vô căn.\nHoa Sói - Thầy Thuốc: Người bệnh nên có sự thăm khám từ thầy thuốc trước khi sử dụng hoa sói để chữa bệnh.\nAllerphast 60 mg - Kiểm Tra Độ Nhạy Cảm: Kiểm tra độ nhạy cảm nhằm xác định phản ứng của người dùng với Allerphast 60 mg.\nKiểm Tra Sức Khỏe Định Kỳ - Nang Nước Cạnh Tai Vòi: Kiểm tra sức khỏe định kỳ giúp phát hiện sớm và theo dõi nang nước cạnh tai vòi.\nKiểm Tra Sức Khỏe Định Kỳ - Viêm Gan Siêu Vi B: Kiểm tra sức khỏe định kỳ để tầm soát viêm gan siêu vi B.\nKiểm Tra Sức Khỏe Định Kỳ - Viêm Gan Siêu Vi C: Kiểm tra sức khỏe định kỳ để tầm soát viêm gan siêu vi C.\nChẩn Đoán Dị Ứng Thời Tiết - Sốt Cỏ Khô: Chẩn đoán sốt cỏ khô là mục tiêu của chẩn đoán dị ứng thời tiết.\nBệnh Chàm - Xét Nghiệm Tìm Yếu Tố Dị Ứng: Xét nghiệm tìm yếu tố dị ứng trên da để có kế hoạch điều trị và phòng ngừa bệnh tái phát.\nDalacin T - Thông Tin Sử Dụng Thuốc: Thuốc Dalacin T được cung cấp thông tin hướng dẫn sử dụng.\nChẩn Đoán Dị Ứng Thời Tiết - Xét Nghiệm Da: Xét nghiệm da là phương pháp chẩn đoán dị ứng thời tiết.\nDiagnostic Test - Tăng Alanine: Tăng alanine là xét nghiệm đánh giá chức năng gan.\nChẩn Đoán Dị Ứng Thời Tiết - Triệu Chứng Hen Suyễn: Chẩn đoán dị ứng thời tiết dựa trên triệu chứng hen suyễn.\nChất Gây Dị Ứng Theo Mùa - Chẩn Đoán Dị Ứng Thời Tiết: Chẩn đoán dị ứng thời tiết bao gồm việc xét nghiệm chất gây dị ứng theo mùa.']</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Trước khi sử dụng thuốc Dalacin T, bệnh nhân cần:
+1. Tham khảo ý kiến bác sĩ để được hướng dẫn sử dụng thuốc một cách an toàn và hiệu quả.
+2. Cảnh báo bác sĩ về khả năng xảy ra tiêu chảy và viêm đại tràng liên quan đến việc sử dụng kháng sinh.
+3. Thông báo cho bác sĩ nếu xuất hiện các triệu chứng như tiêu chảy nặng hoặc kéo dài.
+4. Bảo quản thuốc nơi khô ráo và nhiệt độ dưới 30°C, tránh nơi có ánh sáng mạnh.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tham khảo ý kiến ​​bác sĩ hoặc chuyên gia y tế để đảm bảo liều dùng phù hợp.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7969121443187269</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6992280360546818</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa lượng Vitamin D2 là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>['Calci Milk - D: Calci Milk - D là thuốc chứa thành phần tương tự Calcigenol.\nCalcium Stada Vitamin D: Calcium Stada Vitamin D là hỗn dịch uống chứa calci và vitamin D, giúp điều chỉnh sự thiếu hụt đồng thời vitamin D và calci ở các đối tượng cao tuổi, điều trị loãng xương và cải thiện tình trạng thiếu calci cũng như vitamin D ở trẻ em.&lt;SEP&gt;Hỗn dịch Calcium Stada Vitamin D được dùng theo đường uống để bổ sung canxi và vitamin D.&lt;SEP&gt;Calcium Stada Vitamin D là hỗn dịch được bào chế ở dạng dung dịch dùng theo đường uống.&lt;SEP&gt;Calcium Stada Vitamin D là hỗn dịch chứa calci và vitamin D, cần được bảo quản tránh ánh nắng mặt trời và môi trường ẩm ướt.\nCá Ngừ: Cá ngừ là nguồn cung cấp vitamin D.\nVitamin D: Vitamin D là một chất dinh dưỡng cần thiết cho cơ thể, đóng vai trò quan trọng trong việc kiểm soát các hormon tuyến cận giáp và nồng độ của một số khoáng chất như calci và phospho. Vitamin D giúp xương khớp chắc khỏe, hỗ trợ quá trình tạo xương và phát triển của trẻ, và là chất dinh dưỡng cần thiết cho bệnh nhân loãng xương. Nó cũng là thành phần chính trong nhiều loại thuốc như Agi-Calci, Appeton Lysine Syrup, Calci - D Mekophar, Calci D Hasan, và Babi B.O.N. Vitamin D được chuyển hóa thành calcitriol (D3) bởi thận, giúp tạo đủ Vitamin D khi dùng Calcitriol, đặc biệt là đối với bệnh nhân bị bệnh thận. Vitamin D cũng được sử dụng để phòng ngừa gãy xương lâm sàng sau gãy xương đùi do chấn thương nhẹ thông qua việc điều trị cho bệnh nhân. Đặc biệt, nó là chất bổ sung cần thiết khi dùng acid zolendronic và Aclasta, đặc biệt là đối với bệnh nhân mắc bệnh Paget. Khi sử dụng Aclasta, việc bổ sung đầy đủ Vitamin D là rất quan trọng để ngăn chặn tình trạng loãng xương nếu chế độ ăn uống không đảm bảo đủ lượng Vitamin D cần thiết.\n\nVitamin D đóng vai trò quan trọng trong quá trình tăng cường sức khỏe của động mạch và các cơ quan nội tạng khác, giúp xương và răng trở nên chắc khỏe hơn nhờ vào khả năng tăng cường hấp thu canxi. Tuy nhiên, việc sử dụng Vitamin D ở liều lượng cao hoặc kéo dài có thể dẫn đến tình trạng cường vitamin D, gây ra các tác dụng phụ như mụn và tăng canxi huyết khi quá liều. Vitamin D là thành phần chính trong Calcigenol, có thể gây quá liều nếu sử dụng không đúng cách. Vitamin D cần được thận trọng khi dùng cho người suy thận, bệnh tim, hoặc xơ vữa động mạch vì có thể gây tăng canxi huyết nếu sử dụng quá liều. Vitamin D cũng có thể gây tăng canxi huyết khi sử dụng đồng thời với Calcium Boston và có thể gây rối loạn chuyển hoá calci nếu quá liều và khi dùng đồng thời với rifampicin, phenobarbital, phenytoin.\n\nVitamin D là chất dinh dưỡng cần được kiểm tra khi điều trị tăng canxi huyết. Vitamin D cũng là thành phần chính trong Calcium Stada Vitamin D, giúp điều chỉnh sự thiếu hụt vitamin D. Cuối cùng, bổ sung vitamin D có thể giúp bảo vệ xương khi điều trị bằng corticosteroid dài hạn. Vitamin D là thành phần cần thiết để ngăn ngừa loãng xương và là thành phần hỗ trợ Calci vào xương trong Davita Bone Sugar free. Vitamin D là thành phần hóa học trong dầu jojoba và trong dầu bơ giúp cấp ẩm và bảo vệ da khỏi tia UV. Vitamin D là sản phẩm của quá trình tổng hợp từ cholesterol và là một chất được gan lưu trữ. Vitamin D là dưỡng chất cần thiết cho mật độ xương và là chất dinh dưỡng quan trọng cho khả năng hấp thụ và sử dụng canxi của cơ thể. Vitamin D là chất bổ sung giúp tăng cường hấp thu canxi trong cơ thể và đóng vai trò quan trọng trong việc tăng khả năng hấp thu canxi vào máu.\n\nVitamin D là một vitamin cần thiết cho sự hấp thu calci. Nó cũng là thành phần trong kem bôi trơn được sử dụng trong hỗ trợ điều trị lichen sclerosus. Vitamin D là chất dinh dưỡng giúp hấp thu canxi và hỗ trợ sức khỏe xương. Vitamin D là chất dinh dưỡng cần thiết cho sự hấp thu canxi và duy trì sức khỏe xương. Thiếu vitamin D có thể gây ra bệnh loãng xương. Vitamin D cũng là một loại vitamin có trong mía lau. Vitamin D từ trứng, sữa và ánh sáng mặt trời có thể giúp giảm co thắt cơ mặt. Vitamin D là hợp chất hữu cơ cần thiết cho sự phát triển và duy trì sức khỏe của cơ thể. Vitamin D là chất cần thiết để tổng hợp qua việc tắm nắng buổi sớm. Vitamin D là chất dinh dưỡng cần thiết cho sự phát triển của xương và tóc. Vitamin D là thành phần trong dầu bơ có lợi cho da.\n\nNgoài ra, Vitamin D được bổ sung cho bệnh nhân suy thận mãn tính để hạn chế vấn đề yếu xương. Vitamin D cũng là thành phần trong Tang diệp và được khuyến nghị cho người lớn từ 400-800 IU mỗi ngày. Vitamin D là thành phần chính trong D-Cure, giúp bổ sung vitamin D cho cơ thể. Vitamin D là thành phần có trong các chế phẩm cần ngừng sử dụng khi điều trị tăng calci huyết.&lt;SEP&gt;Vitamin D là chất dinh dưỡng cần thiết cho cơ thể.&lt;SEP&gt;Vitamin D là chất dinh dưỡng cần thiết cho cơ thể, có thể tăng lượng canxi trong máu nếu uống quá nhiều.&lt;SEP&gt;Vitamin D là chất cần kiểm soát liều lượng để giảm nguy cơ tăng canxi máu.&lt;SEP&gt;Vitamin D là một trong những nhóm vitamin có trong trà đông trùng hạ thảo.&lt;SEP&gt;Vitamin D là một trong những vitamin có trong Đông trùng hạ thảo.\nCalcigenol: Calcigenol là sự kết hợp giữa canxi và vitamin D, được sử dụng để bổ sung canxi và phòng ngừa còi xương.&lt;SEP&gt;Calcigenol là thuốc bổ/khoáng chất và vitamin, giúp bổ sung canxi và vitamin D, phòng ngừa và hỗ trợ điều trị thiếu canxi.&lt;SEP&gt;Calcigenol là thuốc chứa vitamin D2, được sử dụng trong điều trị tình trạng thiếu vitamin D.&lt;SEP&gt;Calcigenol là thuốc phòng ngừa còi xương, có thể gây quá liều vitamin D nếu sử dụng liều cao và kéo dài.&lt;SEP&gt;Calcigenol là thuốc cần được bảo quản ở nơi khô ráo, không quá 30°C và tránh tầm tay trẻ em.&lt;SEP&gt;Calcigenol là thuốc chứa vitamin D, có thể gây tăng canxi huyết nếu sử dụng quá liều.\nCalci: Calci là một nguyên tố hóa học quan trọng, cần thiết cho sự phát triển và duy trì sức khỏe của xương. Nó đóng vai trò như một chất điện phân cần thiết, giúp xương trở nên chắc khỏe và phòng ngừa loãng xương. Calci là thành phần chính trong nhiều sản phẩm như Agi-Calci, Calcium Stada Vitamin D, và Davita Bone Sugar free, giúp duy trì sức khỏe xương và cải thiện khả năng hấp thụ của cơ thể nhờ vào Vitamin D3 trong Siro Appeton. Ngoài ra, Calci còn được tìm thấy trong thịt cóc và cây bèo Nhật Bản, chiếm khoảng 40,8mg%.\n\nCalci cũng được bổ sung cùng với vitamin D để phòng ngừa gãy xương lâm sàng ở những bệnh nhân đã từng bị gãy xương đùi do chấn thương nhẹ. Việc sử dụng Calci cần được cân nhắc kỹ lưỡng dựa trên tình trạng sức khỏe cụ thể của mỗi người vì nó có thể gây tăng độc tính đối với tim khi kết hợp với glycoside digitalis và có thể làm giảm nồng độ của các thuốc fluoroquinolon khi dùng cùng. Calci cũng có thể tương tác với các cation khác như magnesi, nhôm, sucralfat và các cation hóa trị 2 hoặc 3 như kẽm, sắt, có thể ảnh hưởng đến hấp thu acid nalidixic.\n\nCalci được xem là chất điện giải cần bổ sung khi dùng Betamethasone. Khi sử dụng betamethasone, Calci là khoáng chất cần bổ sung thêm vào cơ thể. Ngoài ra, Calci cũng là nguyên tố có thể gây nguy cơ kết tủa với Ceftriaxone tại thận và phổi ở trẻ sơ sinh. Calci là nguyên tố hóa học, thường được bổ sung trong điều trị.\n\nCalci cũng là thành phần trong thuốc D-Cure, tăng nồng độ trong máu và nước tiểu khi dùng quá liều. Calci có thể làm giảm khả năng hấp thu sắt trong cơ thể khi uống cùng với Avisure Safoli. Khi uống cùng với Avisure Safoli, Calci có thể tương tác với sắt, làm giảm khả năng hấp thu của cả hai dưỡng chất.&lt;SEP&gt;Calci là một trong những chất bị giảm hấp thu khi dùng neomycin.&lt;SEP&gt;Calci được bổ sung để phòng ngừa tiền sản giật.&lt;SEP&gt;Calci là nguyên tố hóa học có thể ảnh hưởng đến hấp thu của Ciprofloxacin.\nVitamin D2: Vitamin D2, còn gọi là ergocalciferol, có vai trò làm tăng hấp thu canxi ở đường tiêu hóa và điều chỉnh loạn dưỡng xương do thận.&lt;SEP&gt;Vitamin D2, còn gọi là ergocalciferol, là vitamin được sử dụng để hỗ trợ hấp thu canxi.\nMầm Đậu Nành: Mầm đậu nành là nguồn cung cấp nội tiết tố nữ dồi dào từ thiên nhiên, chứa isoflavon có cấu trúc tương tự với estrogen.&lt;SEP&gt;Mầm đậu nành chứa vitamin B, folate và isoflavon, có tác dụng bảo vệ chống ung thư vú trên động vật thí nghiệm.&lt;SEP&gt;Mầm đậu nành có thể ăn sống hoặc chế biến với các thực phẩm khác như xào với thịt, nấu canh, làm lẩu, hoặc làm thành bột mầm đậu nành pha nước uống hay tinh chất mầm đậu nành.&lt;SEP&gt;Mầm đậu nành gồm một rễ với ba bộ phận: lá, mầm rễ, thân mầm. Thân mầm dài ra, khoảng 3-7 cm và là bộ phận chủ yếu được sử dụng.&lt;SEP&gt;Mầm đậu nành có thể làm giảm khó tiêu, đầy hơi và tiêu chảy nếu dùng vừa phải.\nMẫn Cảm Với Vitamin D2: Mẫn cảm với vitamin D2 là triệu chứng chống chỉ định dùng Calcigenol.\nVitamin B2: Vitamin B2, còn được biết đến với tên gọi Riboflavin natri phosphate, là một thành phần quan trọng trong nhiều nguồn thực phẩm và sản phẩm y tế. Vitamin B2 đóng vai trò trong quá trình chuyển hóa protein, chất béo và carbohydrate để tạo ra năng lượng cho cơ thể. Nó cũng giúp duy trì sức khỏe của mắt, cơ bắp và da. Ngoài ra, Vitamin B2 còn góp phần ngăn chặn sự phát triển của bệnh đục thủy tinh thể. \n\nVitamin B2 có mặt trong nhiều loại thực phẩm và sản phẩm như Appeton Lysine Syrup, hạt bạch biển đậu, cây bèo Nhật Bản, bụp giấm, kỷ tử, quả ổi, cây Hoàng Liên Ô Rô, cây Me đất, cây Ráy, thịt Cóc, thốt nốt, củ niễng, đông trùng hạ thảo, hải sâm, kê, khổ qua rừng, kim thất tai, cây lược vàng, mầm đậu nành, mía lau, mít, hạt mùi tàu, quả tươi, và nhụy hoa nghệ tây. Trong Appeton Lysine Syrup, Vitamin B2 không chỉ hỗ trợ chuyển hóa năng lượng và tổng hợp protein mà còn có thể tương tác với một số loại thuốc khác. Vitamin B2 cũng là một hợp chất hóa học cần thiết cho nhiều chức năng sinh lý của cơ thể, thể hiện tầm quan trọng của nó trong việc duy trì hoạt động bình thường của hệ thống cơ thể. Vitamin B2 cần thiết để giữ cho da, mắt, dây thần kinh và hồng cầu khỏe mạnh.\n\nNgoài ra, Vitamin B2 còn được tìm thấy trong quả Tầm Xuân, Thiên lý, lá trầu không, và củ tỏi tươi. Vitamin B2 cũng là thành phần hoạt chất trong thuốc B Complex C và là một trong những vitamin chính trong tỏi. Vitamin B2 không chỉ hỗ trợ chuyển hóa năng lượng và tổng hợp protein mà còn góp phần ngăn ngừa ung thư và giảm cholesterol xấu.\nLiều Vitamin D: Liều vitamin D là lượng vitamin D cần thiết cho cơ thể.\nBạch Biển Đậu: Bạch biển đậu là một loại cây dây leo, sống từ 1-3 năm, với dây trưởng thành có thể dài tới 4-5 mét. Thân cây của nó có góc, hình trụ, màu xanh, nhỏ, bề mặt hơi có rãnh, và có lông thưa, dài và mềm. Cây này được trồng phổ biến tại nhiều tỉnh ở Việt Nam, đặc biệt là Tiền Giang, Bến Tre, Hậu Giang, An Giang, và Kiên Giang. Nó được sử dụng để lấy quả, hạt để ăn và hạt già dùng làm thuốc.\n\nBạch biển đậu được biết đến với nhiều tác dụng y tế. Nó được sử dụng để điều trị nhiều loại bệnh, bao gồm tiêu chảy, viêm dạ dày ruột cấp tính, ngộ độc rượu, độc thạch tín, độc cá nóc, và nhiều triệu chứng khác. Vị thuốc này có vị ngọt, tính hơi ấm, và được sử dụng trong nhiều bài thuốc khác nhau để điều trị các chứng bệnh như giải cảm nắng, khô khát họng, bổ tỳ vị hư yếu, ra huyết trắng ở phụ nữ, đau bụng, tiêu chảy, kiết lỵ, viêm dạ dày và ruột cấp tính, giải ngộ độc rượu, độc thạch tín, độc cá nóc, ngộ độc thức ăn mà sinh nôn mửa, hóc xương, yết hầu sưng đau, tiểu ra máu, và rắn cắn.\n\nNgoài ra, bạch biển đậu còn là một thành phần quan trọng trong bài thuốc Sâm linh bạch truật tán và một số bài thuốc khác. Nó đóng vai trò như một vị thuốc và món ăn quen thuộc, được sử dụng rộng rãi trong các bài thuốc hỗ trợ điều trị.\nCalci Alginat: Calci alginat là tá dược trong Adrenoxyl.\nHải Sâm: Hải sâm là loài động vật sống ở đáy biển, có khả năng tái sinh phần cơ thể bị mất.&lt;SEP&gt;Hải sâm là một món ăn từ biển ngon lành và bổ dưỡng, thuộc ngành động vật Da gai (Echinodermata). Nó là loại động vật biển thân mềm nhũn, dài trung bình khoảng 20cm.&lt;SEP&gt;Hải sâm là nguồn chứa các chất sinh học như lectin, saponin glucoside và các triterpene. Nó có khả năng chống ung thư, kháng khuẩn, cải thiện gan và tim mạch.&lt;SEP&gt;Hải sâm là loài động vật bậc thấp, được thu bắt trước mùa mưa để đảm bảo chất lượng. Hải sâm chứa nhiều thành phần dinh dưỡng như protein, các axit amin, yếu tố vi lượng, vitamin và các chất có hoạt tính sinh học.&lt;SEP&gt;Hải sâm là một vị thuốc rất bổ ích cho sức khỏe, nhưng không nên dùng cho những người đang bị tiêu chảy, lỵ, viêm đại tràng cấp tính, hoạt tinh, hoặc người có thể tạng đàm thấp (mập phì).&lt;SEP&gt;Hải sâm là vị thuốc tính ấm, vị mặn ngọt, không độc, giúp bổ thận tráng dương, bổ ích tinh tủy, giáng hỏa, điều hòa việc đi tiểu tiện, làm tiêu đờm dãi ứ đọng trong cơ thể, nhuận những chỗ khô ráo vón kết, chữa mọi chứng hư nhược cơ thể gầy còm ốm yếu, có tính sát trùng, chữa những chứng lở loét.\nRiboflavin (Vitamin B2): Riboflavin (vitamin B2) là thành phần hóa học trong cây lá gai.\nThiếu Canxi: Thiếu canxi là tình trạng thiếu hụt canxi trong cơ thể, có thể xảy ra do nhiều nguyên nhân như ăn kiêng, điều trị gãy xương, hoặc các bệnh tật khác như bệnh mắt, dị ứng, và bệnh đường ruột kéo dài. Thiếu canxi có thể gây ra các vấn đề nghiêm trọng như co giật do giảm canxi huyết. Tình trạng này được phòng ngừa và điều trị bằng nhiều loại thuốc bổ sung canxi khác nhau, bao gồm Agi-Calci, Briozcal, Calcium Boston, và Calcium Corbiere. Ngoài ra, canxi cũng có thể được sử dụng trong thời kỳ mang thai để ngăn chặn tình trạng thiếu canxi.&lt;SEP&gt;Thiếu canxi là tình trạng thiếu hụt canxi trong cơ thể, có thể được điều trị bằng hoa đu đủ đực.&lt;SEP&gt;Thiếu Canxi là bệnh được điều trị bằng các chất bổ sung Canxi.\nCalcium Corbière Extra: Calcium Corbière Extra là thuốc chứa canxi.\nCalcium Corbière: Calcium Corbière là thuốc chứa canxi và vitamin PP.\nQuả Ổi: Quả Ổi mọng có nhiều hình dáng tùy giống, chủ yếu là hình trứng, hình quả lê, hình cầu. Đầu quả có vết sẹo hình tròn do lá đài để lại. Thường có màu xanh đậm khi còn non và chuyển xanh nhạt pha trắng khi về già. Mỗi quả có chứa rất nhiều hạt, màu hơi hung, hình thân, không đều. Quả vị chua ngọt hay ngọt và có mùi thơm đặc trưng.&lt;SEP&gt;Quả ổi có nhiều hình dáng, chủ yếu là hình trứng, hình quả lê, hình cầu. Đầu quả có vết sẹo hình tròn do lá đài để lại. Quả thường có màu xanh đậm khi còn non và chuyển xanh nhạt pha trắng khi về già. Quả chứa rất nhiều hạt màu hơi hung, hình thân, không đều. Quả vị chua ngọt hay ngọt và có mùi thơm đặc trưng. Quả có thể ăn tươi, làm mứt hay làm nước giải khát.&lt;SEP&gt;Quả Ổi là bộ phận của Cây Ổi được sử dụng làm thuốc.&lt;SEP&gt;Quả ổi được dùng trong bài thuốc giải độc ba đậu.&lt;SEP&gt;Quả ổi chứa pectin, vitamin C, tinh dầu với hàm lượng cao hơn trong lá.\nTang Diệp: Tang Diệp là một loại thảo dược được sử dụng rộng rãi trong Đông y, đặc biệt là từ lá dâu tằm. Tang Diệp thường được thu hoạch vào mùa thu khi có sương, sau đó được sơ chế để có chất giòn, hơi có mùi, vị nhạt, hơi chát và đắng. Thảo dược này có nhiều công dụng quý đối với sức khỏe, bao gồm cả việc điều trị ho, viêm đường hô hấp, cảm mạo, sốt nóng, nhức đầu, mắt đỏ, đau mắt, chóng mặt, và các triệu chứng khác như trừ đàm và làm sáng mắt. Ngoài ra, Tang Diệp còn được sử dụng trong việc điều trị các bệnh lý mạch máu như huyết áp, mỡ máu, và đái tháo đường. Tang Diệp cũng là thành phần của nhiều bài thuốc khác nhau trong Đông y, ví dụ như bài thuốc Linh dương câu đằng ẩm và Sa sâm Mạch môn đông ẩm. Bài thuốc Linh dương câu đằng ẩm sử dụng Tang Diệp để hỗ trợ điều trị ho, sốt và cảm mạo, trong khi bài thuốc Sa sâm Mạch môn đông ẩm sử dụng Tang Diệp để điều trị lao phổi, viêm phế quản mạn tính và ho do phế táo. Tang Diệp nổi tiếng với khả năng giải nhiệt và thanh lọc cơ thể, đồng thời cũng giúp tăng cường sức khỏe tổng thể.\nKê: Kê là loại ngũ cốc chứa nhiều chất dinh dưỡng như protein, lipid, carbohydrate, vitamin A, B1, B2, acid folic, carotenoids.\nBé: Vitamin D được bổ sung cho bé.&lt;SEP&gt;Bé là đối tượng bị ảnh hưởng bởi tiểu đường thai kỳ.\nBuồn Nôn - Calcigenol: Calcigenol có thể gây buồn nôn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây buồn nôn do tăng canxi huyết.\nCalcium Stada Vitamin D - Vitamin D: Calcium Stada Vitamin D chứa vitamin D.\nCalcium Corbière - Đái Tháo Đường: Calcium Corbière cần quan tâm lượng đường trong thuốc.\nCalci - Calcium Stada Vitamin D: Calcium Stada Vitamin D chứa calci.\nCalcigenol - Chóng Mặt: Calcigenol có thể gây chóng mặt nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây chóng mặt do tăng canxi huyết.\nMầm Đậu Nành - Vitamin B2: Mầm đậu nành chứa vitamin B2.\nCalcigenol - Táo Bón: Calcigenol có thể gây táo bón nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây táo bón do tăng canxi huyết.\nBạch Biển Đậu - Vitamin B2: Hạt Bạch biển đậu chứa vitamin B2.\nCalcigenol - Đau Đầu: Calcigenol có thể gây đau đầu nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây đau đầu do tăng canxi huyết.\nHải Sâm - Vitamin B2: Hải sâm chứa vitamin B2.\nCalcigenol - Thận: Calcigenol có thể gây tổn thương thận nếu sử dụng không đúng cách.\nThiếu Canxi - Vitamin D2: Vitamin D2 hỗ trợ hấp thu canxi, giúp phòng ngừa thiếu canxi.\nCalcigenol - Suy Thận: Calcigenol cần thận trọng khi dùng cho người suy thận.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người suy thận do có thể tăng canxi huyết.\nQuả Ổi - Vitamin B2: Quả ổi chứa vitamin B2.\nCalcigenol - Đau Bụng: Calcigenol có thể gây đau bụng nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây đau bụng do tăng canxi huyết.\nTang Diệp - Vitamin D: Tang diệp chứa vitamin D.\nCalcigenol - Mệt Mỏi: Calcigenol có thể gây mệt mỏi nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây mệt mỏi do tăng canxi huyết.\nKê - Vitamin B2: Kê chứa nhiều vitamin B2.\nCalcigenol - Nôn: Calcigenol có thể gây nôn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây nôn do tăng canxi huyết.\nBé - Vitamin D: Vitamin D được bổ sung cho bé.\nCalcium Corbière - Suy Thận: Calcium Corbière cần thận trọng khi sử dụng cho người có suy thận.&lt;SEP&gt;Calcium Corbière không nên sử dụng cho người có suy thận.\nCalcigenol - Phụ Nữ Có Thai: Phụ nữ có thai cần thận trọng khi dùng Calcigenol.\nCalcium Corbière - Suy Tim: Calcium Corbière không nên sử dụng cho người có suy tim.\nCalcigenol - Canxi: Calcigenol chứa canxi làm tăng mức canxi trong máu.\nCalcigenol - Phụ Nữ Cho Con Bú: Phụ nữ cho con bú cần thận trọng khi dùng Calcigenol.\nCalcigenol - Loãng Xương: Calcigenol được dùng để ngăn ngừa và điều trị loãng xương.\nCalcigenol - Sỏi Thận: Calcigenol chống chỉ định dùng cho người bị sỏi thận.&lt;SEP&gt;Calcigenol có thể gây sỏi thận nếu sử dụng không đúng cách.\nCalcigenol - Khô Miệng: Calcigenol có thể gây khô miệng nếu sử dụng không đúng cách.\nCalcigenol - Phát Ban: Calcigenol có thể gây phát ban nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây phát ban do tăng canxi huyết.\nCalcigenol - Đau Cơ: Calcigenol có thể gây đau cơ do tăng canxi huyết.\nCalcium Corbière - Sỏi Thận: Calcium Corbière cần thận trọng khi sử dụng cho người có sỏi thận.\nCalcigenol - Xơ Vữa Động Mạch: Calcigenol cần thận trọng khi dùng cho người mắc xơ vữa động mạch.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người xơ vữa động mạch do có thể tăng canxi huyết.\nCalcigenol - Chán Ăn: Calcigenol có thể gây chán ăn nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây chán ăn do tăng canxi huyết.\nCalcigenol - Tăng Canxi Máu: Calcigenol chống chỉ định dùng cho người bị tăng canxi máu.&lt;SEP&gt;Calcigenol có thể gây tăng canxi máu nếu sử dụng quá liều.\nCalcigenol - Ù Tai: Calcigenol có thể gây ù tai nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây ù tai do tăng canxi huyết.\nAdrenalin - Calcium Corbière: Calcium Corbière không nên sử dụng cho người đang dùng adrenalin.\nCalcigenol - Yếu Cơ: Calcigenol có thể gây yếu cơ nếu sử dụng không đúng cách.\nCalcigenol - Vitamin D: Calcigenol chứa vitamin D làm tăng mức vitamin D trong cơ thể.&lt;SEP&gt;Calcigenol chứa vitamin D, cần thận trọng khi dùng cho người suy thận, bệnh tim, hoặc xơ vữa động mạch.&lt;SEP&gt;Calcigenol chứa vitamin D, có thể gây tăng canxi huyết nếu sử dụng quá liều.\nCalcigenol - Glucocorticoid: Calcigenol được sử dụng để điều trị loãng xương do glucocorticoid.\nCalcigenol - Người Cao Tuổi: Calcigenol được sử dụng để ngăn ngừa gãy xương do loãng xương ở người cao tuổi.\nCalcigenol - Tăng Canxi Huyết: Calcigenol cần thận trọng khi dùng cho người có tăng canxi huyết.&lt;SEP&gt;Calcigenol có thể gây tăng canxi huyết nếu sử dụng quá liều.\nBệnh Tim - Calcigenol: Calcigenol cần thận trọng khi dùng cho người mắc bệnh tim.&lt;SEP&gt;Calcigenol cần thận trọng khi dùng cho người bệnh tim do có thể tăng canxi huyết.\nCalcigenol - Loạn Nhịp Tim: Calcigenol cần thận trọng khi dùng cho người đang dùng glycosid trợ tim.&lt;SEP&gt;Calcigenol có thể gây loạn nhịp tim ở người đang dùng glycosid trợ tim.\nCalcigenol - Ngủ Gà: Calcigenol có thể gây ngủ gà nếu sử dụng không đúng cách.&lt;SEP&gt;Calcigenol có thể gây ngủ gà do tăng canxi huyết.\nCalcium Corbière - Tăng Canxi Máu: Calcium Corbière có thể gây tăng canxi máu trong một số trường hợp.\nCalcigenol - Suy Thận Mạn: Calcigenol được sử dụng để điều trị loạn dưỡng xương do suy thận mạn.\nCalcigenol - Người Lớn: Người lớn cần theo dõi khi trẻ em sử dụng Calcigenol.\nCalcigenol - Tổn Thương Thận: Calcigenol có thể gây tổn thương thận nếu sử dụng không đúng cách.\nCalcigenol - Phospho: Calcigenol chứa phospho làm tăng mức phospho trong máu.\nCalcigenol - Tá Dược: Calcigenol chứa tá dược để tạo ra dạng thuốc phù hợp.\nCalcigenol - Còi Xương: Calcigenol được sử dụng để điều trị và phòng ngừa còi xương.\nCalcigenol - Đau Xương: Calcigenol có thể gây đau xương do tăng canxi huyết.\nCalcigenol - Cơ: Calcigenol có thể gây yếu cơ nếu sử dụng không đúng cách.\nCalcigenol - Thiếu Canxi: Calcigenol được sử dụng để phòng ngừa và hỗ trợ điều trị thiếu canxi.\nCalcigenol - Thiếu Vitamin D: Calcigenol được sử dụng để điều trị và phòng ngừa thiếu vitamin D.\nCalcigenol - Giảm Trương Lực Cơ: Calcigenol có thể gây giảm trương lực cơ do tăng canxi huyết.\nCalcigenol - Thời Kỳ Mãn Kinh: Calcigenol được sử dụng để điều trị và phòng ngừa loãng xương ở phụ nữ thời kỳ mãn kinh.\nCá Ngừ - Vitamin D: Cá ngừ là nguồn cung cấp vitamin D.\nCalcigenol - Vị Kim Loại: Calcigenol có thể gây vị kim loại do tăng canxi huyết.\nCalcigenol - PTH: Calcigenol giúp giảm nồng độ PTH trong máu.\nCalcigenol - Tăng Canxi Niệu: Calcigenol chống chỉ định dùng cho người bị tăng canxi niệu.\nCalcigenol - Phụ Huynh: Phụ huynh cần theo dõi khi trẻ em sử dụng Calcigenol.\nCalcigenol - Chứng Co Giật: Calcigenol được sử dụng để điều trị chứng co giật do giảm canxi máu.\nCalcigenol - Phản Ứng Phụ: Khi sử dụng Calcigenol, nếu có bất kỳ phản ứng phụ nào thì nên liên hệ cơ sở y tế để được điều trị hợp lý.\nCalcigenol - Dương Thị Kim Ngân: Dược sĩ Dương Thị Kim Ngân hy vọng bài viết này đã cung cấp những thông tin cơ bản nhất về Calcigenol cho bạn đọc.\nCalcigenol - Glycosid Trợ Tim: Calcigenol có thể gây loạn nhịp tim ở người đang dùng glycosid trợ tim.\nCalcigenol - Vitamin D2: Calcigenol bao gồm vitamin D2 để tăng hấp thu canxi.&lt;SEP&gt;Calcigenol chứa Vitamin D2 làm thành phần chính.\nCalcigenol - Quá Liều Vitamin D: Calcigenol có thể gây quá liều vitamin D nếu sử dụng không đúng cách.\nCalcigenol - Tricanxi Photphat: Calcigenol chứa Tricanxi photphat làm thành phần chính.\nCalci Milk - D - Calcigenol: Calci Milk - D là thuốc chứa thành phần tương tự Calcigenol.\nCalcigenol - Khô Mồm: Calcigenol có thể gây khô mồm do tăng canxi huyết.\nCalcigenol - Mất Phối Hợp Động Tác: Calcigenol có thể gây mất phối hợp động tác do tăng canxi huyết.\nCalcigenol - Dược Sĩ Dương Thị Kim Ngân: Dược sĩ Dương Thị Kim Ngân đã viết bài viết này cung cấp thông tin cơ bản về Calcigenol.\nCalcigenol - Canxi Photphat: Calcigenol bao gồm canxi photphat để bổ sung canxi.\nCalcigenol - Giảm Canxi Máu: Calcigenol được sử dụng để điều trị chứng giảm canxi máu.\nCalcigenol - Người Nằm Viện: Calcigenol được sử dụng để ngăn ngừa gãy xương do loãng xương ở người nằm viện.\nCalcigenol - Người Suy Thận Mạn: Calcigenol được sử dụng để điều trị loạn dưỡng xương do thận ở người suy thận mạn.\nCalcigenol - Người Dùng Glucocorticoid: Calcigenol được sử dụng để điều trị loãng xương do glucocorticoid ở người dùng glucocorticoid.\nCalcigenol - Vôi Hóa Thận: Calcigenol có thể gây vôi hóa thận nếu sử dụng không đúng cách.\nCalcigenol - Có Vị Kim Loại: Calcigenol có thể gây có vị kim loại nếu sử dụng không đúng cách.\nCalcigenol - Co Giật Do Giảm Canxi Huyết: Calcigenol được sử dụng để hỗ trợ điều trị co giật do giảm canxi huyết.\nCalcigenol - Calciumgeral: Calciumgeral là thuốc chứa thành phần tương tự Calcigenol.\nCalcigenol - Mẫn Cảm Với Vitamin D2: Calcigenol chống chỉ định dùng cho người bị mẫn cảm với vitamin D2.\nBệnh Gút - Calcium Corbière: Calcium Corbière cần thận trọng khi sử dụng cho người có bệnh gút.\nCây Lá Gai - Riboflavin (Vitamin B2): Riboflavin (vitamin B2) là thành phần hóa học trong cây lá gai.\nBệnh Gút - Calcium Corbière Extra: Calcium Corbière Extra cần thận trọng khi sử dụng cho người có bệnh gút.\nCalcium Corbière - Vitamin PP: Calcium Corbière chứa vitamin PP.\nBệnh Gan Nặng - Calcium Corbière: Calcium Corbière không nên sử dụng cho người có bệnh gan nặng.\nCalcium Corbière - Hạ Huyết Áp Nặng: Calcium Corbière không nên sử dụng cho người có hạ huyết áp nặng.\nAdrenoxyl - Calci Alginat: Calci alginat là tá dược trong Adrenoxyl.\nCalcium Corbière - Tăng Canxi Niệu: Calcium Corbière có thể gây tăng canxi niệu trong một số trường hợp.\nCalcium Corbière - Loét Dạ Dày Tiến Triển: Calcium Corbière không nên sử dụng cho người có loét dạ dày tiến triển.\nCalcium Corbière - Viêm Khớp Do Gút: Calcium Corbière cần thận trọng khi sử dụng cho người có viêm khớp do gút.\nCalcium Corbière - Dư Galactose Trong Máu: Calcium Corbière không nên sử dụng cho người có dư galactose trong máu.\nCalcium Corbière - Sử Dụng Quá Liều Vitamin D: Calcium Corbière không nên sử dụng cho người sử dụng quá liều vitamin D.\nCalcium Corbière - Thuốc Digitalis: Calcium Corbière không nên sử dụng cho người đang dùng thuốc digitalis.\nCalcium Corbière - Xuất Huyết Động Mạch: Calcium Corbière không nên sử dụng cho người có xuất huyết động mạch.\nBệnh Túi Mật - Calcium Corbière: Calcium Corbière cần thận trọng khi sử dụng cho người có bệnh túi mật.\nCalcium Corbière - Liều Vitamin D: Calcium Corbière cần quan tâm liều vitamin D nếu có vitamin D trong các thuốc khác.\nCalcium Corbière - U Ác Tính Phá Huỷ Xương: Calcium Corbière không nên sử dụng cho người có u ác tính phá hủy xương.\nCalcium Corbière - Galactosemia: Calcium Corbière không nên sử dụng cho người có bệnh galactosemia.\nCalcium Corbière - Tăng Nhẹ Canxi Niệu: Calcium Corbière cần thận trọng khi sử dụng cho người có tăng nhẹ canxi niệu.\nCalcium Corbière - Tiền Sử Loét Dạ Dày: Calcium Corbière cần thận trọng khi sử dụng cho người có tiền sử loét dạ dày.\nCalcium Corbière - Tiền Sử Có Vàng Da Hoặc Bệnh Gan: Calcium Corbière cần thận trọng khi sử dụng cho người có tiền sử có vàng da hoặc bệnh gan.\nCalcium Corbière Extra - Viêm Khớp Do Gút: Calcium Corbière Extra cần thận trọng khi sử dụng cho người có viêm khớp do gút.']</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa:
+- Vitamin D2 với hàm lượng 72,000 IU (Internationale Unit).
+Vitamin D2 trong Calcigenol đóng vai trò quan trọng trong việc tăng hấp thu canxi ở đường tiêu hóa, giúp điều chỉnh loạn dưỡng xương do thận, và cải thiện tình trạng còi xương giảm canxi ở trẻ em.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trong một chai Calcigenol có chứa 72000UI Vitamin D2.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6706412494944983</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5426603123486246</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tôi có nên rửa tay trước khi sử dụng thuốc Combigan không?</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>['Rửa Tay: Rửa Tay là một biện pháp vệ sinh cá nhân quan trọng, được thực hiện trước khi ăn uống, sau khi đi vệ sinh, và trước khi sử dụng thuốc như Comozol. Rửa Tay bằng nước và xà phòng không chỉ giúp làm sạch bàn tay mà còn đóng vai trò quan trọng trong việc ngăn chặn sự lây lan của vi khuẩn và các bệnh truyền nhiễm khác. Việc rửa tay thường xuyên bằng xà phòng có thể giúp phòng ngừa các bệnh hô hấp và tiêu hóa, như quai bị và báng bụng. Đây là một biện pháp phòng ngừa hiệu quả giúp duy trì sức khỏe và vệ sinh cá nhân.\n\nRửa Tay cũng là phương pháp đơn giản và hiệu quả để ngăn ngừa bệnh truyền nhiễm. Nó giúp phòng ngừa đau họng bằng cách loại bỏ các tác nhân gây bệnh. Khi chế biến thức ăn, trước khi ăn và sau khi vệ sinh, rửa tay là phương pháp đơn giản nhưng rất có hiệu quả trong việc phòng ngừa nhiễm ký sinh trùng. Ngoài ra, rửa tay cũng là biện pháp phòng ngừa để giảm nguy cơ lây nhiễm các bệnh đường hô hấp trên.\n\nRửa Tay cũng đóng vai trò quan trọng trong việc ngăn ngừa nhiễm trùng đường tiêu hóa. Nó giúp ngăn chặn sự lây lan của vi khuẩn gây nhiễm trùng đường ruột và thậm chí là biện pháp giúp phòng ngừa và điều trị nhiễm trùng đường ruột.&lt;SEP&gt;Rửa tay thường xuyên và đúng cách, đặc biệt sau khi trẻ đi vệ sinh hoặc sau khi hắt hơi, ho.&lt;SEP&gt;Rửa tay thường xuyên với nước ấm và xà phòng, đặc biệt là trước khi ăn hoặc khi chế biến thức ăn.&lt;SEP&gt;Rửa tay là quá trình vệ sinh trước và sau khi sử dụng thuốc âm đạo.&lt;SEP&gt;Rửa tay kỹ là biện pháp giúp ngăn ngừa lây lan bệnh.&lt;SEP&gt;Rửa tay thường xuyên bằng xà phòng và nước ấm giúp giảm nguy cơ mắc hoặc lây lan các bệnh nhiễm trùng.&lt;SEP&gt;Rửa tay thường xuyên để tránh nhiễm trùng.\nKiểm Soát Dịch: Kiểm soát dịch bệnh tay chân miệng thông qua vệ sinh cá nhân và môi trường.\nThuốc Bôi Âm Đạo: Thuốc bôi âm đạo được sử dụng để điều trị tình trạng âm đạo.\nVệ Sinh Đúng Cách Các Đồ Vật Thông Thường: Vệ sinh đúng cách các đồ vật thông thường mà con người có thể lây nhiễm khi chạm vào.\nNgười Sử Dụng: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng Amepox cần tuân thủ hướng dẫn sử dụng và liều lượng khuyến cáo.\nVệ Sinh Bàn Tay: Vệ sinh bàn tay là việc làm quan trọng để ngăn ngừa vi khuẩn.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nVệ Sinh Cá Nhân: Vệ sinh cá nhân là quy trình chăm sóc bản thân nhằm phòng ngừa bệnh cúm.&lt;SEP&gt;Vệ sinh cá nhân là biện pháp phòng ngừa cảm cúm.&lt;SEP&gt;Vệ sinh cá nhân sạch sẽ là biện pháp phòng ngừa đau bụng dưới bên trái.&lt;SEP&gt;Vệ sinh cá nhân là quá trình giữ gìn vệ sinh cơ thể nhằm ngăn chặn sự lây lan của bệnh tiêu chảy.\nHướng Dẫn: Hướng dẫn sử dụng thuốc cần được xem kỹ trước khi uống.&lt;SEP&gt;Hướng dẫn của bác sĩ là những chỉ dẫn về cách sử dụng dược liệu.\nRửa Sạch Tay: Rửa sạch tay và vùng da mụn cần điều trị sau đó lau thật khô trước khi bôi thuốc.&lt;SEP&gt;Rửa sạch tay là biện pháp trước khi kích thích gây nôn.\nSức Khỏe: Sức khỏe là trạng thái tổng thể của cơ thể, bao gồm cả thể chất, tinh thần và xã hội. Trạng thái này được đánh giá qua các chỉ số như BMI và vòng eo, cũng như thông qua chế độ ăn uống và tập luyện. Sức khỏe cũng liên quan đến tình trạng huyết áp và có thể bị ảnh hưởng bởi tình trạng mất trí nhớ thoáng qua. \n\nĐể nâng cao sức khỏe, việc sử dụng các vị thuốc như Bồ đề, bạc hà, cây hoa cút lợn, cây Đước, Trường sinh thảo, và đông trùng hạ thảo ngâm mật ong được xem là phương pháp hiệu quả. Những vị thuốc này giúp tránh các tương tác có hại và cải thiện tình trạng tổng thể của cơ thể. Sức khỏe không chỉ là trạng thái tổng thể về thể chất mà còn bao gồm cả tinh thần và xã hội của con người. Nó được đề cập trong bài thuốc cổ truyền và cần được bảo vệ thông qua các thói quen sinh hoạt lành mạnh. Việc sử dụng lá Thường xuân cũng được biết đến với khả năng cải thiện sức khỏe. Ngoài ra, sức khỏe còn được coi là trạng thái tổng thể về thể chất và tinh thần, được ảnh hưởng bởi việc sử dụng Hoàng Nàn và bổ sung DHEA.\n\nSức khỏe cũng là yếu tố ảnh hưởng đến lượng protein cần thiết trong chế độ ăn uống, nhấn mạnh tầm quan trọng của việc duy trì một chế độ ăn uống cân bằng và hợp lý để nâng cao và duy trì sức khỏe tổng thể. Tình trạng sức khỏe cần được theo dõi cẩn thận khi sử dụng thuốc Aspegic, một yếu tố được điều trị bởi Aspegic. \n\nNgoài ra, cần lưu ý rằng có một tạp chí y tế tên là "Sức khỏe", nhưng đây không phải là định nghĩa chính cho thuật ngữ sức khỏe trong ngữ cảnh này.&lt;SEP&gt;Sức khỏe là trạng thái tổng thể của cơ thể và tâm trí, có thể được cải thiện thông qua việc sử dụng tinh dầu hoa cam.&lt;SEP&gt;Sức khỏe được cải thiện nhờ tác dụng của tinh dầu quế.&lt;SEP&gt;Sức khỏe được cải thiện nhờ việc ăn tỏi mỗi ngày.&lt;SEP&gt;Sức khỏe được cải thiện thông qua việc sử dụng vị thuốc đúng cách.&lt;SEP&gt;Sức khỏe được tăng cường nhờ bài thuốc ngâm trái quách.\nDung DỊch Vệ Sinh: Dung dịch vệ sinh là sản phẩm dùng để vệ sinh cá nhân.\nNhiễm Trùng: Nhiễm Trùng là tình trạng bệnh lý xảy ra khi vi khuẩn, virus, ký sinh trùng hoặc nấm xâm nhập vào cơ thể, gây ra nhiều triệu chứng và biến chứng khác nhau. Tình trạng này có thể biểu hiện qua các triệu chứng như tiểu máu, đổ mồ hôi lạnh, âm thổi bất thường ở tim do nhiễm trùng, và thậm chí là mất protein của hệ miễn dịch, gây ra bệnh cầu thận màng. Nhiễm Trùng có thể xảy ra ở nhiều bộ phận khác nhau của cơ thể, bao gồm nhiễm trùng răng miệng, da, hệ thống tuần hoàn, và thậm chí là móng chân quặp ngược. Vi khuẩn có thể gây ra xơ hóa lichen và vết loét họng, trong khi nhiễm trùng do nấm cũng có thể gây ra các triệu chứng tương tự.\n\nViệc điều trị Nhiễm Trùng thường đòi hỏi sự kết hợp của nhiều loại thuốc khác nhau như Alchysin 8400, Alpha-Kiisin, AlphaDHG, Amikacin Bidiphar, Begenderm, và Biseptol. Boston C 1000 cũng được sử dụng trong một số trường hợp để điều trị nhiễm trùng gây suy nhược. Anthocyanin và Cefurich bcm cũng được đề cập như là các lựa chọn điều trị, mặc dù việc sử dụng Cứt lợn để điều trị không còn được khuyến nghị trong y học hiện đại. Quản lý Nhiễm Trùng trong trường hợp CGD cần được thực hiện để tránh các vấn đề sức khỏe.\n\nNhiễm Trùng cũng là một rủi ro trong nhiều tình huống y tế phức tạp, bao gồm phẫu thuật cắt bỏ tuyến thượng thận, phương pháp tạo shunt trong điều trị giả u não, việc đặt ống dẫn lưu, và đặc biệt là trong quá trình điều trị bệnh bạch cầu cấp, không chỉ đối với trẻ em mà còn đối với người lớn. Nó cũng có thể là yếu tố gây ra bệnh Meniere, là triệu chứng của bệnh Pemphigus, và là triệu chứng thường gặp của bệnh phóng xạ cấp tính. Nhiễm Trùng cũng có thể kích hoạt đợt bệnh tế bào mast hệ thống và là triệu chứng của CGD, gây ảnh hưởng đến nhiều cơ quan của cơ thể.\n\nNgoài ra, Nhiễm Trùng cũng có thể xảy ra sau chọc dịch não tủy, và trong một số trường hợp, nó có thể là một biến chứng sau khi sử dụng corticoid ở người cao tuổi. Nhiễm Trùng cũng có thể xảy ra sau phẫu thuật tái tạo dây chằng chéo trước, từ gãy xương cành tươi, và sau phẫu thuật gãy xương cổ chân. Nhiễm Trùng cũng có thể xảy ra nếu chức năng của màng phim nước mắt bị xáo trộn. Nó có thể gây phì đại hạch bạch huyết và là nguyên nhân gây sưng hạch bạch huyết. Nhiễm trùng bao quy đầu hoặc đầu dương vật có thể gây hẹp bao quy đầu ở trẻ em trai hoặc nam giới. Nhiễm trùng là triệu chứng thường gặp sau phẫu thuật cắt bao quy đầu và là vấn đề thường gặp sau phẫu thuật bao quy đầu.\n\nNhiễm Trùng cũng có thể xảy ra khi bị hóc xương, là một biến chứng có thể xảy ra sau khi sử dụng Huyết kiệt trực tiếp lên vết thương hở hoặc thổi vào mũi. Nhiễm Trùng cũng là một trong những dấu hiệu được tìm kiếm trong khám sức khỏe. Nhiễm Trùng cũng là một triệu chứng của trẻ mắc hội chứng Down, thể hiện qua việc răng bị sâu hoặc nhiễm trùng. Nhiễm trùng hô hấp, viêm phổi, nhiễm trùng đường tiết niệu và viêm tai giữa cũng là những tình trạng cần được điều trị chuyên sâu. Nhiễm trùng cũng là tác dụng phụ của thuốc ức chế miễn dịch và là triệu chứng có thể xảy ra sau phẫu thuật hoặc thủ thuật y tế, được ngăn ngừa bằng thuốc kháng sinh phòng ngừa.\n\nNhiễm Trùng cũng có thể biểu hiện qua các dấu hiệu như viêm đỏ, sưng to và đau sau phẫu thuật loại bỏ kén bã đậu hoặc nhiễm trùng kén bã đậu. Ngoài ra, nhiễm trùng tại chỗ cũng có thể gây khô miệng. Nhiễm Trùng cũng có thể xảy ra nếu không có lá lách, và cũng có thể làm hỏng lá lách và gây lách to. Nhiễm Trùng là bệnh do vi khuẩn gây ra, có thể xảy ra ở mắt, và cũng có thể là nguyên nhân của xơ hóa lichen. Nhiễm trùng do nấm, vi khuẩn hay vi-rút có thể gây ra vết loét họng. Nhiễm Trùng là tình trạng nhiễm vi khuẩn hoặc nấm gây bệnh, và có thể được điều trị bằng mật ong Manuka và dầu Manuka để ngăn chặn và hạn chế sự lây lan.\n\nNhiễm Trùng lông mi là tình trạng lông mi bị nhiễm khuẩn, thể hiện qua các triệu chứng như viêm đỏ, sưng to và đau. Nhiễm Trùng cũng là biến chứng nghiêm trọng của lồng ruột, xảy ra nếu không được điều trị kịp thời. Nhiễm Trùng còn có thể tác động lên màng nhĩ. Nhiễm Trùng cũng là triệu chứng của nang khe mang và có thể xuất hiện ở các nang hoặc xoang khác trong cơ thể.\n\nNhiễm Trùng cũng thường là nguyên nhân gây nổi hạch dưới hàm, thể hiện qua các triệu chứng như viêm đỏ, sưng to và đau. Nhiễm Trùng cũng là nguyên nhân gây nổi hạch ở cổ. Nhiễm Trùng cũng có thể gây nổi hạch ở tay và chân. Nhiễm Trùng cũng có thể là nguyên nhân gây nổi mề đay.\n\nNhiễm Trùng răng khôn gây đau và sưng hàm.\n\nNhiễm Trùng cũng là nguyên nhân gây ra khoảng 60% trường hợp thai ngoài tử cung. Nhiễm Trùng cũng là triệu chứng của bệnh phình đại tràng bẩm sinh.\n\nNhiễm Trùng cũng là một trong những nguyên nhân gây polyp mũi.\n\nNhiễm Trùng cũng là triệu chứng gặp phải sau điều trị ung thư.\n\nNhiễm Trùng là tình trạng rối loạn về phụ khoa có thể làm tăng nguy cơ rối loạn chức năng tình dục.\n\nNhiễm Trùng cũng có thể gây ra sảng lú lẫn và sảng lú lẫn cấp.\n\nNhiễm Trùng là biến chứng sức khỏe mãn tính của trẻ sinh non và cũng là một trong những vấn đề sức khỏe mãn tính.\n\nNhiễm Trùng cũng là nguyên nhân gây sưng lưỡi gà. Nhiễm trùng do vi-rút hoặc vi khuẩn có thể làm sưng và đỏ lưỡi.\n\nNhiễm Trùng cũng là tình trạng dễ mắc các bệnh nhiễm khuẩn do gan không tổng hợp đủ kháng thể.\n\nNhiễm Trùng do khả năng chống nhiễm trùng thấp là một trong những nguy cơ của thai chậm tăng trưởng trong tử cung.\n\nNhiễm Trùng có thể được phát hiện thông qua xét nghiệm từ nước ối.\n\nNhiễm Trùng là một trong những yếu tố ảnh hưởng đến thai nhi.\n\nNhiễm Trùng là một yếu tố thúc đẩy suy tim cấp. Nhiễm Trùng là yếu tố thúc đẩy suy tim trái và một trong những yếu tố thường gặp ở bệnh nhân suy tim. Nhiễm Trùng cũng là một yếu tố làm tình trạng bệnh nặng thêm.\n\nNhiễm Trùng là yếu tố có thể gây ra suy thượng thận cấp và nguyên nhân gây suy thượng thận thứ phát.\n\nNhiễm trùng như lao, giang mai, nấm, HIV có thể gây suy tuyến yên.\n\nNhiễm trùng là nguyên nhân gây tăng tiểu cầu phản ứng.\n\nNhiễm Trùng là tình trạng bệnh lý được điều trị bằng thuốc kháng sinh hoặc thuốc chống nấm.\n\nNhiễm Trùng cũng có thể xảy ra khi sử dụng thuốc axit axetic.\n\nChymodk là một trong những thuốc được sử dụng để điều trị nhiễm trùng, đặc biệt trong một số trường hợp cụ thể.\n\nNhiễm Trùng cũng ảnh hưởng đến thùy trán.\n\nNhiễm Trùng là bệnh lý cấp tính nhập viện làm tăng nguy cơ thuyên tắc huyết khối tĩnh mạch.\n\nNhiễm Trùng cũng là một triệu chứng dễ xảy ra ở người mắc tiền đái tháo đường.\n\nNhiễm Trùng có thể gây giảm tiểu cầu hoặc tăng tiểu cầu thứ phát tùy thuộc vào nguyên nhân gây nhiễm trùng.\n\nNhiễm trùng do vi khuẩn là nguyên nhân gây tiêu chảy ở trẻ. Nhiễm Trùng cũng là nguyên nhân gây bệnh tiêu chảy.\n\nNhiễm Trùng vùng từ thắt lưng trở xuống là một trong những nguyên nhân gây đau thần kinh tọa.\n\nNhiễm Trùng cũng có thể xảy ra sau khi bị rệp cắn.\n\nNhiễm Trùng cũng là nguyên nhân có thể dẫn đến tình trạng tinh trùng loãng.\n\nNhiễm Trùng có thể làm hỏng hồng cầu.\n\nNhiễm Trùng cũng có thể là một nguyên nhân gây thiếu máu và cần được tránh bằng cách rửa tay thường xuyên.\n\nNhiễm trùng cũng là nguyên nhân có thể gây tràn dịch màng phổi.\n\nNhiễm trùng là biến chứng ít gặp sau phẫu thuật.\n\nNhiễm trùng có thể gây ra các bệnh lý tủy răng.\nVệ Sinh Tay: Vệ sinh tay là biện pháp kiểm soát nhiễm trùng trong cơ sở y tế.\nViệc Giữ Vệ Sinh: Việc giữ vệ sinh tốt bằng cách rửa tay thường xuyên hàng ngày, đặc biệt là trước bữa ăn và sau khi đi vệ sinh.&lt;SEP&gt;Việc giữ vệ sinh đúng cách rất quan trọng trong việc phòng ngừa và điều trị viêm nhiễm phụ khoa.\nTránh Dùng Chung Các Đồ Dùng Cá Nhân: Tránh dùng chung các đồ dùng cá nhân như khăn lau, quần áo là biện pháp phòng ngừa hắc lào.\nRửa Tay - Tiêu Chảy: Rửa tay thường xuyên bằng xà phòng và nước ấm giúp giảm nguy cơ mắc hoặc lây lan các bệnh tiêu chảy.\nRửa Tay - Thuốc Bôi Âm Đạo: Rửa tay trước và sau khi sử dụng thuốc bôi âm đạo.\nTiêu Chảy - Vệ Sinh Cá Nhân: Giữ gìn vệ sinh cá nhân là biện pháp phòng ngừa sự lây lan của bệnh tiêu chảy.\nNgười Sử Dụng - Thuốc: Khi sử dụng thuốc, người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.&lt;SEP&gt;Người sử dụng cần lưu ý và tuân thủ cách dùng thuốc đúng.\nRửa Tay - Thiếu Máu: Rửa tay thường xuyên giúp kiểm soát bệnh thiếu máu.\nHướng Dẫn - Sức Khỏe: Hướng dẫn của bác sĩ giúp đảm bảo an toàn cho sức khỏe khi sử dụng dược liệu.\nDung DỊch Vệ Sinh - Triệu Chứng: Dung dịch vệ sinh được từ từ sử dụng lại khi triệu chứng thuyên giảm.&lt;SEP&gt;Dung dịch vệ sinh được sử dụng để điều trị triệu chứng.\nNhiễm Trùng - Việc Giữ Vệ Sinh: Việc giữ vệ sinh tốt bằng cách rửa tay thường xuyên hàng ngày, đặc biệt là trước bữa ăn và sau khi đi vệ sinh.\nVi Khuẩn - Vệ Sinh Bàn Tay: Vệ sinh bàn tay ngăn ngừa sự phát triển của vi khuẩn.\nNiệu Quản - Thói Quen Tốt Trong Phòng Tắm: Thói quen tốt trong phòng tắm giúp vệ sinh cơ quan sinh dục và niệu quản.\nCảm Cúm - Vệ Sinh Cá Nhân: Vệ sinh cá nhân là biện pháp phòng ngừa cảm cúm.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nQuai Bị - Rửa Tay: Rửa tay bằng nước và xà phòng thường xuyên là biện pháp phòng ngừa lây nhiễm quai bị.\nBệnh Nhân - Thuốc: Bệnh nhân cần sử dụng thuốc đúng giờ và đúng liều.\nRửa Tay - Đau Họng: Rửa tay là phương pháp phòng ngừa đau họng.\nChế Độ Sinh Hoạt Lành Mạnh - Sức Khỏe: Chế độ sinh hoạt lành mạnh giúp bảo vệ sức khỏe.\nBệnh Cúm - Vệ Sinh Cá Nhân: Vệ sinh cá nhân là biện pháp phòng ngừa bệnh cúm.\nNhiễm Trùng Đường Hô Hấp Trên - Vệ Sinh Đúng Cách: Vệ sinh đúng cách các đồ vật thông thường giúp giảm nguy cơ lây nhiễm.\nBệnh Cúm - Chung Đồ Dùng Cá Nhân: Sử dụng chung đồ dùng cá nhân có thể làm tăng nguy cơ lây nhiễm bệnh cúm.\nBàn Tay - Vệ Sinh Sạch Sẽ: Vệ sinh sạch sẽ giúp bảo vệ bàn tay khỏi tác nhân gây hại.\nBệnh Tay Chân Miệng - Rửa Tay: Rửa tay thường xuyên và đúng cách giúp phòng ngừa bệnh tay chân miệng.\nBệnh - Rửa Tay: Rửa tay kỹ là biện pháp giúp ngăn ngừa lây lan bệnh.\nNhiễm Trùng Đường Ruột - Rửa Tay: Rửa tay giúp ngăn chặn sự lây lan của vi khuẩn gây nhiễm trùng đường ruột.&lt;SEP&gt;Rửa tay kỹ càng giúp phòng ngừa và điều trị nhiễm trùng đường ruột.\nHội Chứng Rối Loạn Sinh Tủy - Rửa Tay: Rửa tay thường xuyên giúp phòng ngừa và ngăn chặn sự lây lan của hội chứng rối loạn sinh tủy.\nPhế Quản - Rửa Tay: Thường xuyên rửa tay bằng xà phòng để bảo vệ phế quản.\nBáng Bụng - Rửa Tay: Rửa tay giúp phòng ngừa báng bụng.\nVệ Sinh Cá Nhân - Đau Bụng Dưới Bên Trái: Vệ sinh cá nhân sạch sẽ là biện pháp phòng ngừa đau bụng dưới bên trái.\nNhiễm Ký Sinh Trùng - Rửa Tay: Rửa tay khi chế biến, khi ăn, sau khi vệ sinh là phương pháp đơn giản nhưng rất có hiệu quả trong phòng ngừa nhiễm ký sinh trùng.\nNhiễm Trùng Đường Hô Hấp Trên - Rửa Tay: Rửa tay là biện pháp phòng ngừa để giảm nguy cơ lây nhiễm các bệnh đường hô hấp trên.\nNgộ Độc Thực Phẩm - Rửa Sạch Tay: Rửa sạch tay trước khi kích thích gây nôn.\nComozol - Rửa Tay: Rửa tay là bước tiền điều trị khi sử dụng Comozol.&lt;SEP&gt;Rửa tay trước khi sử dụng Comozol.\nBàn Tay - Rửa Tay: Rửa tay giúp bảo vệ bàn tay khỏi tác nhân gây hại.\nHắc Lào - Tránh Dùng Chung Các Đồ Dùng Cá Nhân: Tránh dùng chung các đồ dùng cá nhân như khăn lau, quần áo giúp phòng ngừa hắc lào.\nHệ Hô Hấp - Rửa Tay: Rửa tay bằng xà phòng là biện pháp vệ sinh cá nhân giúp ngăn chặn sự lây lan của vi khuẩn.\nDifferin - Rửa Sạch Tay: Rửa sạch tay và vùng da mụn cần điều trị sau đó lau thật khô trước khi bôi Differin.\nDịch Bệnh - Rửa Tay: Rửa tay là biện pháp phòng ngừa bệnh truyền nhiễm.\nSốt Lassa - Vệ Sinh Tay: Vệ sinh tay là biện pháp kiểm soát nhiễm trùng trong cơ sở y tế.\nNước Rửa Tay - Rửa Tay: Nước rửa tay chứa ít nhất 60 độ cồn giúp ngăn ngừa bệnh truyền nhiễm.\nVi Rút - Vệ Sinh Đúng Cách Các Đồ Vật Thông Thường: Vệ sinh đúng cách các đồ vật thông thường mà con người có thể lây nhiễm khi chạm vào.\nChất Tẩy Rửa - Dung DỊch Vệ Sinh: Dung dịch vệ sinh và chất tẩy rửa là các sản phẩm vệ sinh cá nhân.\nDung DỊch Vệ Sinh - Phản Ứng Phụ: Sử dụng dung dịch vệ sinh có thể gây ra phản ứng phụ.']</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bạn nên rửa tay trước khi sử dụng thuốc Combigan. Điều này giúp loại bỏ vi khuẩn và các tác nhân gây hại khác có thể làm ảnh hưởng đến hiệu quả của thuốc. Trước khi nhỏ mắt, hãy rửa sạch tay bằng xà phòng và nước ấm để đảm bảo vệ sinh cá nhân. Điều này cũng giúp ngăn chặn sự lây lan của vi khuẩn và các bệnh truyền nhiễm khác.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Có, bạn cần rửa sạch tay trước khi sử dụng thuốc Combigan để tránh nhiễm trùng mắt.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.7918738105111346</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.5104684526027836</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn có thể dùng cho các trường hợp đột quỵ hay tai biến mạch máu não nào không?</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>['Thiếu Oxy Não: Thiếu oxy não là triệu chứng của các bệnh như thiếu máu não, đột quỵ.\nBác Sĩ: Bác Sĩ là một người chuyên môn trong lĩnh vực y tế, chịu trách nhiệm tư vấn, điều trị và đưa ra chỉ định sử dụng nhiều loại thuốc khác nhau. Họ đóng vai trò quan trọng trong việc tư vấn và hướng dẫn việc sử dụng các sản phẩm như A.t Zinc, Acnequidt, Actiso Ladophar, Alzental, Ambroco, Baby Septol, Becozyme, Belara, và Bluemint. Bác sĩ quyết định liều lượng phù hợp cho từng bệnh nhân dựa trên tình trạng sức khỏe và nhu cầu dinh dưỡng của họ. Họ cần được thông báo về bất kỳ dị ứng hoặc tác dụng phụ nào mà bệnh nhân gặp phải khi sử dụng thuốc, ví dụ như Aspirin Vidipha. Ngoài việc kê đơn, bác sĩ còn điều chỉnh liều lượng thuốc để đảm bảo rằng phương pháp điều trị phù hợp nhất với từng bệnh nhân.\n\nBác sĩ cũng cung cấp tư vấn để kiểm soát rủi ro và tác dụng không mong muốn của thuốc và vị thuốc. Họ chăm sóc sức khỏe tổng thể cho bệnh nhân và có thể bao gồm cả bác sĩ chuyên khoa thần kinh và bác sĩ phục hồi chức năng. Bác sĩ là người chuyên môn giúp nhận biết chính xác nguyên nhân của vấn đề sức khỏe và có quyền quyết định về việc sử dụng men vi sinh Antibio cho bệnh nhân. Họ cũng tư vấn cách dùng và liều dùng nấm ngọc cẩu và nụ vối.\n\nTrong công việc của mình, Bác sĩ chịu trách nhiệm chẩn đoán và điều trị các vấn đề sức khỏe, bao gồm cả việc xử lý hóc xương cá. Đây là một nghề nghiệp chuyên môn trong y học, nơi bác sĩ có thể cung cấp lời khuyên về việc sử dụng thuốc và vị thuốc. Bác sĩ cũng là người được đào tạo chuyên môn về y tế, có thể tư vấn và áp dụng các biện pháp dự phòng chuyên sâu. Bác sĩ có thể tư vấn về tình trạng sức khỏe và giúp đỡ trong việc chẩn đoán và điều trị rối loạn tâm lý, bao gồm cả việc xử lý rối loạn nhân cách tránh né.\n\nBên cạnh đó, Bác sĩ là người được thông báo về tình trạng bệnh nhân khi sử dụng Boganic và Carbomango. Bạn nên liên hệ ngay với bác sĩ để được tư vấn nếu có bất kỳ thắc mắc nào trong quá trình sử dụng thuốc.\nThương Tổn Hệ Thần Kinh: Thương tổn hệ thần kinh bao gồm bệnh não tăng huyết áp, tai biến mạch máu não, chảy máu nội sọ.\nĐột Quỵ: Đột quỵ, còn được gọi là tai biến mạch máu não, là một tình trạng y học nghiêm trọng xảy ra khi não bị thiếu nguồn cung cấp máu đột ngột, thường do tắc nghẽn hoặc vỡ của mạch máu não. Đây là một tình trạng sức khỏe khẩn cấp và nghiêm trọng, có thể dẫn đến tử vong cao và di chứng nặng nề. Đột quỵ không chỉ là bệnh lý não mà còn liên quan đến các vấn đề về tim mạch và có thể là nguyên nhân gây ra bệnh động kinh thùy thái dương và thùy trán. Nguyên nhân của đột quỵ rất đa dạng, bao gồm tăng huyết áp, bệnh tim Ebstein, bệnh bụi phổi, bệnh cơ tim phì đại, chứng aldosterone nguyên phát, tình trạng béo phì, và nhiều yếu tố khác. Đột quỵ cũng có thể xảy ra do cục máu đông di chuyển đến động mạch não và gây tắc nghẽn. Tình trạng này diễn tiến rất nhanh và thường để lại nhiều di chứng trầm trọng.\n\nQuản lý và điều trị đột quỵ đòi hỏi sự chăm sóc y tế chuyên nghiệp và điều trị tích cực, bao gồm việc phục hồi chức năng sau khi xảy ra tình trạng này. Đột quỵ cũng được biết đến như một tình trạng bệnh tim mạch có thể được ngăn chặn bằng Telmisartan. Đột quỵ cũng có thể gây ra cơn động kinh toàn thể và là tình trạng cấp cứu liên quan đến não, bao gồm cả xuất huyết dưới nhện và rối loạn tuần hoàn não cấp tính. Đột quỵ có thể gây đau dây thần kinh sinh ba và là chống chỉ định cho Crinone, và nó có thể xảy ra do cục máu đông. Đột quỵ cũng là một trong những rối loạn tim mạch được cải thiện nhờ củ lùn, và cũng được ngăn chặn bởi Perindopril Erbumine trong Coperil Plus. Bệnh này cũng được hỗ trợ điều trị bằng củ nén và Đan sâm, và được xác định là bệnh liên quan đến yếu tố gây ra bởi cholesterol LDL.\n\nĐột quỵ cũng có thể được dự phòng và điều trị dự phòng bằng aspirin, cụ thể là Aspirin STELLA và Aspirin Vidipha. Tuy nhiên, Adagrin không nên được sử dụng trong điều trị đột quỵ. Đột quỵ cũng là bệnh tim mạch được ngăn ngừa bởi Bisoprolol và được điều trị bằng Furosemide trong trường hợp do huyết áp cao gây ra. Đột quỵ cũng được coi là biến chứng nguy hiểm của huyết áp không ổn định và cần thận trọng khi sử dụng Atocib. Đột quỵ cũng được đề cập trong phần về chất chống oxy hóa. Đột quỵ còn có thể gây nhiễu loạn cảm xúc và hậu quả của phì đại thất trái, cũng như gây bất lực. Đột quỵ là tình trạng thiếu máu não cấp tính, có thể được gây ra bởi rối loạn lipid máu, và cũng là tình trạng xảy ra khi huyết khối di chuyển đến động mạch não và gây tắc mạch. Đột quỵ cũng có thể gây ra run và là nguyên nhân có thể gây ra rung nhĩ. Đột quỵ là biến chứng nghiêm trọng của bệnh rung nhĩ và là bệnh cần được phòng ngừa bằng thuốc chống đông.\n\nĐột quỵ cũng có thể xảy ra do tình trạng tăng huyết áp ác tính, bệnh tăng huyết áp vô căn, và có thể gây ra táo bón. Đột quỵ là một tình trạng cấp cứu liên quan đến thiếu máu não và có thể là nguyên nhân gây tê lưỡi. Đột quỵ là nguyên nhân phổ biến gây thương tật cao, thậm chí là tử vong cho bệnh nhân, ảnh hưởng nhiều tới chất lượng cuộc sống người bệnh. Đột quỵ cũng được điều trị và dự phòng bằng Aspegic, Rosuvastatin, và Crestor.&lt;SEP&gt;Đột quỵ là một trong những nguyên nhân gây tổn thương thùy đỉnh.&lt;SEP&gt;Đột quỵ có thể gây tổn thương cho thùy trán.&lt;SEP&gt;Đột quỵ là nguyên nhân gây tổn thương cho thùy trán.&lt;SEP&gt;Đột quỵ là bệnh lý có thể gây bất động và là yếu tố nguy cơ thuyên tắc tĩnh mạch sâu.&lt;SEP&gt;Đột quỵ là biến chứng của tiền đái tháo đường nếu không được điều trị.&lt;SEP&gt;Turmerone hỗ trợ trong việc cải thiện các tình trạng sau đột quỵ.\nNgộ Độc Thần Kinh: Ngộ độc thần kinh là triệu chứng trong ngộ độc.\nCục Máu Đong: Cục máu đông là tình trạng cần được ngăn chặn để phòng tránh tai biến mạch máu não.\nTai Biến Mạch Não: Tai biến mạch não là tình trạng rối loạn tuần hoàn máu não.&lt;SEP&gt;Tai biến mạch não là một trong những bệnh lý mà thuốc An Cung Ngưu Hoàng Hoàn được sử dụng.&lt;SEP&gt;Tai biến mạch não là triệu chứng xuất hiện khi phình động mạch chủ ngực chèn ép vào mạch cảnh.\nNgăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não là việc giảm thiểu tỉ lệ mắc phải TBMMN thông qua việc dùng thuốc đúng chỉ định và liều lượng.\nTai Biến Xuất Huyết Não Diện Rộng: Tai biến xuất huyết não diện rộng là tình trạng chống chỉ định sử dụng An Cung Ngưu Hoàng Hoàn.\nRung Nhĩ: Rung nhĩ là tình trạng rối loạn nhịp tim, đặc trưng bởi nhịp tim không đều, mất sóng P và sự xuất hiện của sóng f. Tình trạng này xảy ra khi nút xoang không còn nắm quyền chỉ huy trong hệ thống dẫn truyền điện của tim, khiến tâm nhĩ không thể co bóp nhịp nhàng. Rung nhĩ có thể tồn tại ngắn hạn hoặc dài hạn, và được phân loại thành rung nhĩ dai dẳng, mạn tính, lâm sàng và dưới lâm sàng. Bệnh lý này gây ra nhiều biến chứng, bao gồm tăng nguy cơ hình thành cục máu đông và đột quỵ.\n\nRung nhĩ có thể dẫn đến các triệu chứng như giảm khả năng gắng sức, đau ngực, và ngất. Tuy nhiên, các triệu chứng thường không rõ ràng khi mới khởi phát. Tình trạng này cũng có thể là tác dụng ngoại ý ít gặp khi sử dụng các thuốc như Bambuterol và Bambec. Trong một số trường hợp, rung nhĩ được chỉ định để phòng ngừa biến cố huyết khối bằng Atidogrel, hoặc Clopidogrel được chỉ định sử dụng trong trường hợp này.\n\nRung nhĩ là tình trạng nhịp tim nhanh bất thường ở tim trên và có thể làm tăng nguy cơ thiếu máu não. Để quản lý rung nhĩ, mô hình ABC được áp dụng. Điều trị bao gồm nhiều phương pháp như sốc điện, thuốc chống loạn nhịp, cắt đốt, phẫu thuật và đặt máy tạo nhịp tim. Việc quản lý chặt chẽ là cần thiết do tiềm ẩn những nguy cơ biến chứng rất nguy hiểm, mặc dù bệnh có thể thầm lặng không gây ra triệu chứng rầm rộ. Một số thuốc được sử dụng để kiểm soát tình trạng này bao gồm Digoxin và Amiodarone.&lt;SEP&gt;Rung nhĩ là tình trạng loạn nhịp tim được điều trị sau phẫu thuật tim.&lt;SEP&gt;Rung nhĩ là triệu chứng của việc dùng quá liều ibuprofen.\nHoại Tử Tứ Chi: Hoại tử tứ chi là triệu chứng của độc tính mạn tính.\nThuốc Chống Đông Máu: Thuốc chống đông máu là một loại thuốc được sử dụng để ngăn ngừa tình trạng đông máu và phòng ngừa hình thành các cục máu đông. Thuốc này hoạt động bằng cách ức chế sự hình thành huyết khối và ngăn chặn cục máu đông hình thành quá dễ dàng. Thuốc chống đông máu thường được chỉ định để dự phòng khả năng tái diễn biến cố huyết khối, giúp duy trì lưu thông máu một cách an toàn và hiệu quả, đặc biệt là ở bệnh nhân rung nhĩ để phòng ngừa đột quỵ. Thuốc này cũng được sử dụng trong điều trị thuyên tắc động mạch phổi.\n\nThuốc chống đông máu cần được sử dụng thận trọng do khả năng tương tác với nhiều loại thuốc khác nhau, bao gồm A.t Ibuprofen Syrup, Acemol 325 mg, Agifuros 40 mg, Alchysin 8400, Aspirin MKP 81, Augbactam, Augbidil, và tenoxicam (một NSAID). Đặc biệt, thuốc chống đông máu có thể tương tác với Agimycob, làm tăng nồng độ của nó trong cơ thể. Thuốc này cũng có thể tương tác với cao khô Ginkgo biloba, tăng nguy cơ chảy máu khi dùng chung với warfarin. Ngoài ra, việc sử dụng thuốc chống đông máu cần tránh đồng thời với Hoa Bóng nước, hoa đậu biếc, và cam thảo, vì những thực phẩm và thảo dược này có thể ảnh hưởng đến hiệu quả của thuốc hoặc tăng nguy cơ chảy máu.\n\nThuốc chống đông máu tương tác với nhiều loại thuốc, thảo dược, và thực phẩm khác, bao gồm Chymodk, tinh dầu hoa anh thảo, và các sản phẩm chứa chiết xuất hương thảo. Thuốc chống đông máu cũng có thể tương tác với trà đông trùng hạ thảo, gây ảnh hưởng đến quá trình đông máu. Việc sử dụng thuốc chống đông máu cần được kiểm soát chặt chẽ bởi bác sĩ và theo dõi kỹ lưỡng các tương tác thuốc để đảm bảo an toàn cho người bệnh. Thuốc chống đông máu là yếu tố nguy cơ gây tai biến mạch máu não.\nBệnh Lý Thực Thể Thần Kinh: Bệnh lý thực thể thần kinh như di chứng sau nhồi máu não, bệnh Hirschsprung, bệnh Parkinson.\nChống Trầm Cảm: Chống Trầm Cảm là thuật ngữ chỉ các phương pháp hoặc thuốc được sử dụng để điều trị tình trạng trầm cảm. Thuốc chống trầm cảm thường được bác sĩ kê đơn cho người bệnh để điều trị trầm cảm và kiểm soát stress hoặc các vấn đề cảm xúc khác. \n\nNgoài ra, một số thảo dược cũng được biết đến với tác dụng chống trầm cảm, bao gồm Hoàng Bá, Ngọc Lan Tây, và nhụy hoa nghệ tây. Những thảo dược này giúp giảm trầm cảm và căng thẳng, mang lại cảm giác thoải mái và dễ chịu hơn cho người dùng. \n\nMột số nghiên cứu cũng chỉ ra rằng râu ngô có tác dụng chống trầm cảm. Ngoài ra, Amitriptylin là một loại thuốc chống trầm cảm đã được chứng minh là có thể giảm đau cổ, góp phần cải thiện sức khỏe tổng thể của người bệnh.\n\nTóm lại, Chống Trầm Cảm là một lĩnh vực rộng lớn bao gồm cả thuốc và thảo dược, mỗi loại đều có những ưu điểm riêng trong việc hỗ trợ điều trị trầm cảm và giảm stress.&lt;SEP&gt;Chống trầm cảm là mục tiêu điều trị của tinh dầu hoa nhài.&lt;SEP&gt;Hoạt động chống trầm cảm là một trong những hoạt động sinh học của Tử tô.\nRối Loạn Trên Mạch Máu: Rối loạn trên mạch máu liên quan đến viêm mạch, đột quỵ.\nNhóm Bác Sĩ Điều Trị: Nhóm bác sĩ điều trị bao gồm các chuyên gia y tế liên quan đến việc điều trị và phục hồi chức năng sau đột quỵ.\nHoại Tử Cơ Quan: Hoại tử cơ quan có thể xảy ra do tắc mạch máu, dẫn đến thiếu máu cục bộ.\nPhục Hồi Chức Năng Sau Đột Quỵ: Phục hồi chức năng sau đột quỵ là quá trình giúp bệnh nhân khôi phục lại khả năng sinh hoạt và chức năng cơ thể.&lt;SEP&gt;Phục hồi chức năng sau đột quỵ là một phần không thể thiếu trong phác đồ điều trị đột quỵ.\nThần Kinh Khứu: Thần kinh khứu bị tổn thương do nhiễm siêu vi, vi khuẩn hoặc hơi độc.\nClopidogrel: Clopidogrel là hoạt chất chính trong các sản phẩm như Atidogrel, Bilgrel, Caplor, Clopias, Bilomag, và Carbocistein. Nó được biết đến với khả năng ức chế thụ thể P2Y12 adenosine diphosphate của tiểu cầu, từ đó ngăn chặn sự kết tập tiểu cầu và ngăn chặn hình thành cục máu đông. Thuốc này thuộc loại thuốc chống kết tập tiểu cầu, thường được sử dụng kết hợp với aspirin sau sự cố cấp tính tim mạch (ACS).\n\nClopidogrel được sử dụng để điều trị hoặc dự phòng huyết khối, đặc biệt là trong việc kiểm soát các rối loạn do tắc nghẽn huyết khối như đột quỵ, nhồi máu cơ tim và bệnh động mạch ngoại biên. Ngoài ra, nó có thể gây tăng nguy cơ xuất huyết, đặc biệt là khi sử dụng trong vòng một tuần trước sinh. Clopidogrel cũng có thể gây tương tác với các thuốc khác như Bilomag, Carbocistein, Carflem, Bromelain, và Aspegic.\n\nThuốc này giúp giữ cho máu lưu thông trơn tru trong cơ thể, ngăn chặn hình thành các cục máu đông có hại. Clopidogrel là thuốc ức chế glycoprotein IIb/IIIa và cần thận trọng khi sử dụng với các thuốc khác như aspirin (ASA), heparin, NSAID, SSRI, thuốc chuyển hóa bởi cytochrom P450, chất ức chế CYP2C19 và rosuvastatin. Quá liều có thể dẫn đến thời gian chảy máu kéo dài và các biến chứng chảy máu.\n\nClopidogrel được sử dụng trong điều trị bệnh tim mạch, cần sử dụng cẩn thận cho bệnh nhân mắc bệnh gan.&lt;SEP&gt;Clopidogrel là thuốc làm chậm đông máu.&lt;SEP&gt;Clopidogrel là thuốc chống đông máu có tương tác với tinh dầu hương thảo.\nNhóm Thuốc Ngăn Ngừa Cục Máu Đong: Nhóm thuốc ngăn ngừa cục máu đông là thuốc giúp ngăn ngừa tai biến mạch máu não.\nTai Biến Mạch Máu Não: Tai biến mạch máu não là một tình trạng sức khỏe khẩn cấp liên quan đến hệ thống mạch máu não, thường xuất hiện do rối loạn tuần hoàn máu não hoặc sự hình thành cục máu đông đột ngột trong động mạch cung cấp máu cho não. Bệnh lý này có thể dẫn đến nhiều hậu quả nghiêm trọng như sa sút trí tuệ và tăng nguy cơ sa sút trí tuệ. Tai biến mạch máu não cũng được biết đến là một biến chứng nghiêm trọng của huyết áp không ổn định, tăng huyết áp trong thai kỳ, và là một trong các tình trạng nhiễm khuẩn ít gặp.\n\nTriệu chứng của tai biến mạch máu não bao gồm méo miệng, yếu hoặc tê ở tay, và khó khăn trong việc nói. Bệnh lý này có thể xảy ra khi dòng máu tới não bị chặn hoặc bị chảy máu, gây tổn thương tế bào não. Tai biến mạch máu não là nguyên nhân chính gây tử vong cho người bệnh sa sút trí tuệ và là một tình trạng y học gây tử vong và tàn tật.\n\nTai biến mạch máu não được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng thảo dược như Bạch cương tàm và quả Bạch tật lê sắc thành thuốc, cũng như sử dụng thuốc hiện đại như Cebrex và Cebraton. Ngoài ra, tai biến mạch máu não còn được hỗ trợ khắc phục di chứng bằng nấm lim xanh và nụ hoa tam thất giúp phòng ngừa biến chứng này. Thuốc bổ thần kinh H5000 cũng được sử dụng để giảm nhẹ và điều trị tai biến mạch máu não.\n\nNgoài ra, tai biến mạch máu não cũng là tác dụng phụ hiếm gặp khi sử dụng Celecoxib. Bệnh lý này có thể được phòng ngừa bằng Aspirin 81 ở những người có tiền sử thoáng mất não (TIA).\n\nTai biến mạch máu não là một tình trạng nghiêm trọng cần được phát hiện và điều trị kịp thời để giảm thiểu hậu quả và ngăn chặn tình trạng tái phát.&lt;SEP&gt;Tai biến mạch máu não là tình trạng nghiêm trọng cần tránh khi sử dụng Cialis.&lt;SEP&gt;Tai biến mạch máu não là triệu chứng trong vòng 6 tháng gần đây không được chỉ định dùng thuốc Cialis.\nThuốc Hạ Huyết Áp: Thuốc hạ huyết áp là nhóm thuốc được sử dụng để điều trị tình trạng huyết áp cao. Khi sử dụng, bệnh nhân cần được theo dõi huyết áp thường xuyên để đảm bảo hiệu quả và an toàn trong quá trình điều trị. Thuốc hạ huyết áp có thể tương tác với nhiều loại thuốc khác như A.t Ibuprofen Syrup, Agifuros 40 mg, Alsiful S.R, Bart, và Diurefar. Đặc biệt, cần phải phối hợp thận trọng khi sử dụng cùng với Alsiful S.R do có khả năng gây ra những tác dụng phụ không mong muốn. Ngoài ra, cần tránh sử dụng Thuốc hạ huyết áp cùng với Bisoprolol vì có thể xảy ra tương tác không tốt. Thuốc hạ huyết áp cũng cần được sử dụng thận trọng khi kết hợp với nhụy hoa nghệ tây. Thuốc này được uống hàng ngày để điều chỉnh huyết áp và giúp kiểm soát huyết áp, ngăn ngừa tai biến mạch máu não. Thuốc hạ huyết áp cũng được sử dụng trong điều trị tăng huyết áp cấp cứu.&lt;SEP&gt;Thuốc hạ huyết áp bị tăng tác dụng tụt huyết áp thế đứng bởi amitriptylin.\nNgộ Độc Thần Kinh - Tim Mạch: Ngộ độc glycoside tim gây ngộ độc thần kinh.\nBác Sĩ - Đột Quỵ: Bác sĩ chăm sóc sức khỏe chính cho bệnh nhân và tư vấn về điều trị đột quỵ.\nAmlodipin - Rối Loạn Trên Mạch Máu: Amlodipin gây ra rối loạn trên mạch máu như viêm mạch, đột quỵ.\nCục Máu Đong - Ngăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não thông qua việc ngăn chặn cục máu đông.\nPerindopril - Rối Loạn Trên Mạch Máu: Perindopril gây ra rối loạn trên mạch máu như viêm mạch, đột quỵ.\nRung Nhĩ - Thuốc Chống Đông Máu: Thuốc chống đông máu được sử dụng để phòng ngừa đột quỵ ở bệnh nhân rung nhĩ.\nHoại Tử Cơ Quan - Mạch Máu: Tắc mạch máu có thể dẫn đến hoại tử cơ quan do thiếu máu cục bộ.\nChống Trầm Cảm - Đột Quỵ: Thuốc chống trầm cảm được kê cho người bệnh bị đột quỵ.\nThiếu Máu Não - Thiếu Oxy Não: Thiếu oxy não là triệu chứng của thiếu máu não.\nNhóm Bác Sĩ Điều Trị - Phục Hồi Chức Năng Sau Đột Quỵ: Nhóm bác sĩ điều trị tham gia vào việc thực hiện và điều trị phục hồi chức năng sau đột quỵ.\nAn Cung Ngưu Hoàng Hoàn - Tai Biến Mạch Não: An Cung Ngưu Hoàng Hoàn được sử dụng để điều trị tai biến mạch não.&lt;SEP&gt;Thuốc An Cung Ngưu Hoàng Hoàn được sử dụng trong điều trị tai biến mạch não.\nClopidogrel - Đột Quỵ: Clopidogrel được chỉ định trong dự phòng đột quỵ.\nAn Cung Ngưu Hoàng Hoàn - Tai Biến Xuất Huyết Não Diện Rộng: An Cung Ngưu Hoàng Hoàn chống chỉ định ở bệnh nhân tai biến xuất huyết não diện rộng.\nNgăn Ngừa Tai Biến Mạch Máu Não - Nhóm Thuốc Ngăn Ngừa Cục Máu Đong: Ngăn ngừa tai biến mạch máu não thông qua việc dùng nhóm thuốc ngăn ngừa cục máu đông.\nThương Tổn Hệ Thần Kinh - Tăng Huyết Áp Cấp Cứu: Tăng huyết áp cấp cứu gây thương tổn hệ thần kinh.\nTai Biến Mạch Máu Não - Thuốc Hạ Huyết Áp: Thuốc hạ huyết áp giúp phòng ngừa tai biến mạch máu não.\nHoại Tử Tứ Chi - Thạch Tín: Thạch tín gây độc tính mạn tính, dẫn đến hoại tử tứ chi.\nCholesterol - Ngăn Ngừa Tai Biến Mạch Máu Não: Ngăn ngừa tai biến mạch máu não thông qua việc kiểm soát cholesterol.\nSiêu Vi - Thần Kinh Khứu: Siêu vi gây tổn thương lớp tế bào thần kinh trong hốc mũi.\nPhục Hồi Chức Năng Sau Đột Quỵ - Thuốc Bổ Não Cho Người Bị Tai Biến: Thuốc bổ não cho người bị tai biến là một chủ đề liên quan đến việc hỗ trợ phục hồi chức năng sau đột quỵ.\nPhình Động Mạch Chủ Ngực - Tai Biến Mạch Não: Tai biến mạch não là triệu chứng xuất hiện khi phình động mạch chủ ngực chèn ép vào mạch cảnh.\nAsen - Hoại Tử Tứ Chi: Asen gây độc tính mạn tính gây hoại tử tứ chi.\nBệnh Lý Thực Thể Thần Kinh - Liệt Ruột: Bệnh lý thực thể thần kinh gây liệt ruột.\nKhám Mắt - Thương Tổn Hệ Thần Kinh: Khám mắt giúp phát hiện thương tổn hệ thần kinh.\nHơi Độc - Thần Kinh Khứu: Hơi độc trong không khí làm tổn thương lớp biểu mô thần kinh khứu kéo dài.\nSiêu Vi Trùng - Thần Kinh Khứu: Siêu vi trùng gây tổn thương thần kinh khứu.']</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>An Cung Ngưu Hoàng Hoàn được sử dụng để điều trị tai biến mạch máu não, nhưng không phải tất cả các trường hợp đột quỵ đều phù hợp để sử dụng thuốc này. Thuốc này không phải là thần dược có thể chữa được mọi trường hợp đột quỵ. Việc sử dụng cần được chỉ định và theo dõi của chuyên gia y tế.
+Đặc biệt, An Cung Ngưu Hoàng Hoàn chống chỉ định ở những bệnh nhân bị tai biến xuất huyết não diện rộng hoặc chảy máu nhiều. Thuốc này cũng không nên được sử dụng cho những người có thể trạng hàn, dương hư, tỳ vị hư hàn, suy giảm chức năng gan thận.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Không thể dùng cho tất cả các trường hợp đột quỵ hay tai biến mạch máu não, việc dùng thuốc cần được chỉ định và theo dõi của chuyên gia y tế.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7011020226156063</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.5919421722955682</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Người bệnh có thể dùng thuốc Avelox không nếu đang gặp vấn đề với tim?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>['Phòng Ngừa Xơ Vữa Động Mạch: Atorvastatin phòng ngừa xơ vữa động mạch.\nSuy Tim Mạn: Suy tim mạn là bệnh lý tim mạch được điều trị bằng hạt đình lịch.&lt;SEP&gt;Suy tim mạn là bệnh tim mạch mãn tính được hỗ trợ điều trị bằng hạt đình lịch.&lt;SEP&gt;Suy tim mạn là tình trạng chức năng tim giảm dần do bệnh hở van tim kéo dài.&lt;SEP&gt;Suy tim mạn là tình trạng suy tim kéo dài, có thể tiến triển thành suy tim cấp.&lt;SEP&gt;Suy tim mạn là tình trạng bệnh lý tim mạch mạn tính.&lt;SEP&gt;Suy tim mạn là tình trạng bệnh tim mạch mạn tính được điều trị bằng Losartan.\nNguy Cơ Tim Mạch: Nguy cơ tim mạch là tình trạng có nguy cơ mắc các bệnh về tim mạch.&lt;SEP&gt;Nguy cơ tim mạch có thể tăng theo liều dùng và thời gian dùng thuốc Atocib.&lt;SEP&gt;Nguy cơ tim mạch là một tình trạng sức khỏe liên quan đến việc tiêu thụ tía tô.\nThuốc Lá: Thuốc lá là một chất kích thích gây hại nghiêm trọng cho sức khỏe, chứa hơn 200 chất độc hại, làm suy yếu cơ chế bảo vệ dạ dày và dẫn đến viêm loét. Việc sử dụng thuốc lá trước khi thực hiện xét nghiệm Albumin máu nên được tránh vì nó có thể ảnh hưởng đến kết quả xét nghiệm. Thuốc lá cũng là yếu tố làm tăng nguy cơ mắc nhiều bệnh khác nhau, bao gồm bệnh trào ngược dạ dày – thực quản, bệnh Crohn, và bệnh liệt dương. Nó làm chậm quá trình lành vết thương và tăng nguy cơ mắc bệnh cước, cùng với việc gia tăng nguy cơ mắc các bệnh về khớp. Thuốc lá được coi là một loại thực phẩm gây hại cho sức khỏe và cần phải được kiêng trong quá trình sử dụng bìm bịp. Bỏ thuốc lá là biện pháp cần thiết để phòng ngừa viêm loét dạ dày và giảm nguy cơ mắc bệnh động mạch vành. Hút thuốc lá lâu dài làm tăng nguy cơ mắc bệnh đau thắt ngực và là nguyên nhân chính gây ra nhiều bệnh như tăng huyết áp, rối loạn mỡ máu, và đái tháo đường. Ngoài ra, thuốc lá có thể ảnh hưởng đến cân bằng dịch trong tai, đặc biệt trong trường hợp mắc bệnh Meniere, và là nguyên nhân của viêm phổi kẽ.\n\nThuốc lá cũng là nhân tố gây sản sinh axit quá mức trong dạ dày và cần tránh để giữ độ pH cân bằng. Hút thuốc lá là thói quen cần từ bỏ để bảo vệ đường hô hấp trên, và hạn chế hút thuốc lá có thể giúp cải thiện tình trạng hạ huyết áp. Thuốc lá được xem là thức uống cần hạn chế trong chế độ ăn uống để tránh hạ huyết áp. Thuốc lá còn là yếu tố nguy cơ đẩy nhanh quá trình thoái hóa van và có thể ảnh hưởng xấu đến sức khỏe mắt. Thuốc lá cũng gây mất ngủ và ảnh hưởng xấu đến giấc ngủ. Nó là chất kích thích ảnh hưởng đến giấc ngủ và phơi nhiễm với thuốc lá là một yếu tố ảnh hưởng đến sức khỏe. Thuốc lá là nguyên nhân gây ra nhiều vấn đề về sức khỏe, đặc biệt là đối với lưỡi, và là chất gây hại cho sức khỏe tim mạch.\n\nThuốc lá là yếu tố nguy cơ cao mắc nấm miệng Candida và gây thương phổi. Hút thuốc lá là yếu tố nguy cơ hàng đầu gây ung thư họng. Thuốc lá cũng là một trong những hóa chất có thể gây ra hội chứng rối loạn sinh tủy. Thuốc lá là yếu tố nguy cơ gây nhiều vấn đề răng miệng và là một trong số những tác nhân gây sưng lưỡi gà. Thuốc lá cũng là một trong những yếu tố cần kiểm tra khi chẩn đoán rối loạn cương dương. Thuốc lá là chất gây hại, cần được bỏ hút để phòng tránh các bệnh lý đường hô hấp. Thuốc lá cũng là yếu tố nguy cơ đối với bệnh lý tim mạch và bệnh nhân suy tim. Hút thuốc lá là yếu tố nguy cơ gây ADHD và ảnh hưởng xấu đến thai nhi. Hút thuốc lá làm giảm khả năng hấp thụ vitamin C.\n\nThuốc lá là một chất kích thích gây hại nghiêm trọng cho sức khỏe, cần được từ bỏ để giảm thiểu nguy cơ mắc nhiều bệnh khác nhau, bao gồm cả các bệnh về hô hấp, tim mạch, và nhiều vấn đề sức khỏe khác.&lt;SEP&gt;Thuốc lá là chất cần hạn chế hoặc tránh hút.&lt;SEP&gt;Thuốc lá là nguồn gây nghiện và tăng khả năng gây dị tật thai nhi, sinh non, nhẹ cân.&lt;SEP&gt;Hút thuốc lá là yếu tố làm tăng sắc tố da.&lt;SEP&gt;Thuốc lá có tính kích thích không chỉ ảnh hưởng đến sức khỏe tổng thể của nam giới mà còn làm giảm nồng độ testosterone.&lt;SEP&gt;Thuốc lá là chất kích thích cần phải từ bỏ hoặc hạn chế sử dụng để ngăn ngừa tinh trùng yếu.\nBệnh Trên Tim Mạch: Bệnh trên tim mạch là một trong những chống chỉ định khi dùng A.t Ibuprofen Syrup.&lt;SEP&gt;Bệnh trên tim mạch là bệnh liên quan đến hệ tim mạch.\nThuốc Chẹn Beta: Thuốc chẹn beta là một loại thuốc được sử dụng trong việc điều trị bệnh tim mạch và tăng huyết áp. Thuốc này hoạt động bằng cách ức chế thụ thể beta-adrenergic, giúp kiểm soát phản ứng của cơ thể đối với căng thẳng và tăng huyết áp. Nó làm giảm nhịp tim và huyết áp, từ đó giúp kiểm soát các vấn đề liên quan đến tim mạch. Thuốc chẹn beta bao gồm nhiều loại thuốc khác nhau như Carvedilol, Metoprolol, Propranolol, Bisoprolol, và Acebutolol. Mỗi loại thuốc có thể có tác dụng phụ khác nhau, bao gồm khả năng gây ra liệt dương và ác mộng. Thuốc chẹn beta không chỉ giúp kiểm soát tăng huyết áp mà còn có thể giúp giảm run ở một số người. \n\nThuốc chẹn beta có thể tương tác với một số loại thuốc khác như Amaryl 1 mg và Carbimazol, đồng thời cũng tương tác với aspirin 81. Ngoài ra, nó cũng có thể làm giảm tác dụng hạ đường huyết của một số loại thuốc khác. Tuy nhiên, cần lưu ý rằng thuốc chẹn beta cũng có thể tăng nguy cơ mắc bệnh BPH (tăng kích thước tuyến tiền liệt lành tính).\n\nThuốc chẹn beta là một trong những loại thuốc hạ huyết áp phổ biến, thường được sử dụng để điều trị bệnh tim mạch và tăng huyết áp.&lt;SEP&gt;Thuốc chẹn beta là thuốc điều trị tăng huyết áp.&lt;SEP&gt;Sử dụng thuốc chẹn beta trong điều trị bệnh tim mạch có thể làm tăng nguy cơ mắc phì đại lành tính tuyến tiền liệt.\nBệnh Huyết Khối Tắc Mạch: Bệnh huyết khối tắc mạch là bệnh chống chỉ định sử dụng Avalo.\nTim Mạch: Tim mạch là hệ thống cơ quan gồm tim và mạch máu chịu trách nhiệm tuần hoàn máu khắp cơ thể. Đây không chỉ là một hệ thống cơ quan đơn thuần mà còn là một đối tượng cần được theo dõi chặt chẽ khi sử dụng nhiều loại thuốc khác nhau, bao gồm Atropine, Domperidone, Agietoxib gst, Fexofenadine, Amlor 5 của Pfizer, Atelec, Artrodar, Austriol Mebiphar, Atorhasan 20, Atorpa-E, và nhiều loại thuốc khác. Hệ thống tim mạch chịu ảnh hưởng từ việc hút thuốc lá, tình trạng béo phì, và sử dụng bạc hà. Bệnh nhân tim mạch cũng có thể gặp biến cố khi sử dụng Belara. Tim mạch còn có thể bị ảnh hưởng bởi chứng aldosterone nguyên phát và bệnh thận đa nang. Bệnh tim mạch có thể xảy ra do độ pH cơ thể bị quá axit và tăng axit dạ dày. Estrogen duy trì sự đàn hồi của mạch máu, giảm nguy cơ mắc các bệnh lý tim mạch do xơ vữa.\n\nHệ thống tim mạch liên quan đến bệnh tăng huyết áp, suy tim, bệnh mạch vành, và biến chứng đái tháo đường. Nó cũng chịu ảnh hưởng từ việc sử dụng các loại thuốc như Celecoxib, dầu bơ, dầu hạt cải, dầu hạnh nhân, và đậu mèo. Tim mạch cũng chịu ảnh hưởng từ việc sử dụng các loại thảo dược như Rau đắng đất, Biển súc, Ginkgo biloba, Biginol, Bisoplus, trà Bụp giấm, và dịch chiết từ dền cơm. Các thảo dược này có thể giúp cải thiện tình trạng tim mạch và bảo vệ hệ thống tim mạch khỏi biến cố tim mạch và bệnh tật.\n\nTim mạch cần được kiểm tra trước khi sử dụng Cadifast 120 và các loại thuốc khác. Hệ thống này cũng chịu ảnh hưởng từ việc kéo dài khoảng QT và bị ảnh hưởng bởi hút thuốc lá và cholesterol xấu. Tim mạch chịu ảnh hưởng tích cực từ Hắc sâm, giúp tăng lưu lượng máu và hạ huyết áp. Hệ thống tim mạch cũng chịu ảnh hưởng tích cực từ hạt Bo Bo, cải thiện tình trạng xơ vữa mạch máu và tăng độ đàn hồi mạch máu. Tim mạch cũng chịu ảnh hưởng từ các yếu tố nguy cơ chính như xơ vữa động mạch, tăng huyết áp mà Hoàng Liên có tác dụng bảo vệ. Tim mạch cũng có thể bị ảnh hưởng bởi hội chứng Carcinoid, gây ra lắng đọng mô xơ trên nội mạc buồng tim, van tim, buồng động mạch phổi và động mạch chủ. Tim mạch là hệ thống cơ quan gặp bất thường trong Hội chứng Edwards và Trisomy 18.\n\nNgười phụ nữ mắc hội chứng thiểu sản thất trái có nguy cơ gặp vấn đề về tim mạch khi mang thai. Hệ thống tim mạch cũng chịu ảnh hưởng bởi các hợp chất hóa học trong Huyền sâm. Tim mạch là đối tượng thử nghiệm tác dụng hạ huyết áp của nước sắc Kê huyết đằng. Tim mạch là hệ thống được bảo vệ bởi các hoạt chất trong Kha tử. Khế hỗ trợ tim mạch nhờ chứa vitamin A và kali. Tim mạch cũng chịu ảnh hưởng bởi khí phế thũng. Tim mạch là hệ thống mà Lô hội có tiềm năng bảo vệ. Hệ thống tim mạch cũng chịu ảnh hưởng bởi các biến chứng liên quan đến bệnh lây truyền qua đường tình dục. Bệnh tim mạch được ngăn ngừa nhờ Vitamin PP. Tim mạch là cơ quan được bảo vệ bởi các axit béo lành mạnh và các chất khác trong hạt gai dầu. Tim mạch là hệ thống mạch máu và tim, được nghiên cứu về tác dụng của phytoestrogen từ mầm đậu nành.\n\nTim mạch cũng được hỗ trợ bởi mít. Hệ thống tim mạch cần được bảo vệ khỏi tác hại của muối. Ngoài ra, Tim mạch được Ngân Hạnh bảo vệ. Nghệ trắng có tác dụng tốt đối với các bệnh lý tim mạch và cải thiện hệ thống tim mạch.\n\nBệnh tim mạch có thể là nguyên nhân của hình dùi trống trên móng. Tim mạch là hệ thống chịu ảnh hưởng bởi biến chứng của đái tháo đường type 2. Tim mạch cũng được bảo vệ khỏi biến chứng tiểu đường nhờ Kẽm. Bệnh tim mạch là vấn đề phổ biến trên toàn thế giới, liên quan đến rối loạn lipid máu.\n\nTim mạch cũng chịu tác động của độc tính từ Ô đầu và Phụ tử, làm tăng nguy cơ mắc các bệnh lý tim mạch và ảnh hưởng đến chức năng tổng thể của hệ thống tim mạch. Tim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi cả bệnh cúm mùa và bệnh cúm A/H1N1.\n\nHệ thống tim mạch chịu ảnh hưởng từ purin thông qua nhiều chức năng tim: lưu lượng máu và phân phối oxy. Hệ thống tim mạch chịu ảnh hưởng từ purin thông qua các thụ thể purinergic. Tim mạch là hệ thống mạch máu liên quan đến tim, nơi mùi tây có tác dụng tốt. Tim mạch là hệ thống được bảo vệ bởi hoạt tính ức chế kết tập tiểu cầu từ lá rau mùi tây. Tim mạch được điều trị bằng mùi tây.\n\nHệ thống tim mạch cũng dễ bị ảnh hưởng bởi gốc tự do và các bệnh liên quan. Bệnh tim mạch có thể là bệnh mạn tính có thể liên quan đến rối loạn tiền đình. Tim mạch cũng có thể được gây ra bởi stress. Rong biển giúp bảo vệ tim mạch.\n\nTim mạch cũng liên quan đến bệnh rung nhĩ. Tim mạch là hệ thống chịu ảnh hưởng từ bệnh lý tăng huyết áp. Tim mạch chịu tác động từ Đông trùng hạ thảo. Bộ phận này cần được tham khảo ý kiến bác sĩ trước khi sử dụng rượu Đông trùng hạ thảo.\n\nTim mạch là hệ thống cơ quan chịu sự kiểm soát của tuyến giáp. Suy giáp làm chậm nhịp tim và giảm chức năng co bóp của tim. Tim mạch là hệ thống cơ quan chịu chống chỉ định đối với xét nghiệm hạ đường huyết bằng insulin.\n\nTim mạch là hệ thống chịu ảnh hưởng tích cực từ dịch chiết rễ Tầm Xuân và tác dụng của Xuân. Tim mạch cũng là chuyên khoa y học tập trung vào việc điều trị các vấn đề về tim và mạch máu. Hệ thống tim mạch chịu ảnh hưởng trong tăng huyết áp cấp cứu.\n\nTim mạch là hệ thống gồm tim và mạch máu được Thạch lựu bảo vệ. Thiên ma cũng cải thiện chức năng của hệ thống tim mạch.\n\nHệ thống tim mạch chịu tác động độc hại từ Taxane. Tim mạch là hệ thống cơ quan liên quan đến việc truyền máu trong cơ thể, cần được thông báo cho bác sĩ khi dùng Ameflu DAYTIME.\n\nTim mạch cũng chịu ảnh hưởng của Amilavil. Tim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi việc sử dụng Arcoxia với liều cao, trong thời gian dài.\n\nTim mạch chịu ảnh hưởng của Brufen, đặc biệt đối với bệnh nhân lớn tuổi, có tiền sử bệnh tim mạch. Candesartan được sử dụng để điều trị các tình trạng liên quan đến tim mạch.\n\nTim mạch là hệ thống cơ quan liên quan đến việc điều trị rối loạn cương dương.\n\nTim mạch là hệ thống cơ quan có thể bị ảnh hưởng bởi tác dụng phụ của Combivent®, sử dụng Combivent® có thể dẫn đến bệnh tim mạch.\n\nBệnh tim mạch là bệnh mà Cozaar được dùng để điều trị.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng bởi bệnh tim mạch.\n\nRosuvastatin giảm nguy cơ bệnh tim mạch.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng từ tiền đái tháo đường.\n\nTim mạch là hệ thống gồm tim và các mạch máu.\n\nTim mạch là hệ thống cơ quan chịu ảnh hưởng từ việc bỏ hút thuốc lá.\n\nTim mạch cũng chịu ảnh hưởng từ tăng canxi máu, thể hiện qua tình trạng nhịp tim bất thường.\n\nTim mạch là hệ thống mạch máu, tim sen giúp làm tan huyết khối trong lòng mạch.\n\nTim mạch là hệ thống mạch máu chịu ảnh hưởng từ việc điều hòa lipid và đường huyết.\n\nTim mạch là hệ thống được bảo vệ khỏi bệnh tim mạch nhờ tinh dầu Bergamot.\n\nTim mạch là hệ thống tuần hoàn được bảo vệ khỏi nguy cơ bởi tinh dầu Bergamot.\n\nTim mạch là hệ thống cơ quan được hỗ trợ bởi tác dụng giảm huyết áp của tinh dầu xá xị.\n\nTim mạch chịu ảnh hưởng từ các hợp chất phenolic trong tinh dầu cỏ xạ hương.\n\nTỏi đen cũng có khả năng bảo vệ hệ thống tim mạch.\n\nTim mạch là hệ thống được bảo vệ bởi axit folic và các chất chống oxy hóa.\n\nSử dụng nước trà xanh thường xuyên có thể duy trì sức khỏe tim mạch và ngăn ngừa các bệnh lý về tim mạch. Tim mạch là hệ thống cơ quan được hỗ trợ bởi việc uống nước trà xanh thường xuyên.\n\nTuỷ sống tham gia và thực hiện các phản xạ vận động phức tạp liên quan đến tim mạch. Hệ thống tim mạch chịu ảnh hưởng từ hormon tuyến giáp.\nĐột Quỵ Tim Mạch: Đột quỵ tim mạch được giảm nguy cơ tử vong bởi loài cây này.\nBệnh Tim: Bệnh Tim là tình trạng rối loạn chức năng tim, gây ra bởi nhiều yếu tố như huyết áp cao, căng thẳng, hút thuốc, và mức cholesterol cao. Đây là một tình trạng bệnh lý nghiêm trọng liên quan đến hệ tim mạch, có thể làm tăng nguy cơ mắc các bệnh khác như phì đại tiền liệt tuyến (BPH), thiếu máu não, và rối loạn cương dương. Bệnh Tim cũng có thể gây ra tình trạng mất ngủ ở người già và liên quan đến chỉ số BMI cao. \n\nBệnh Tim được biết đến với các triệu chứng không liên quan trực tiếp đến nguyên nhân y tế khác, bao gồm cả ác mộng và hình thìa trên móng. Bệnh này cũng là biến chứng của tiền đái tháo đường nếu không được điều trị kịp thời. Bệnh Tim cũng là tình trạng chống chỉ định khi sử dụng một số loại thuốc cụ thể như A.T Calmax, Ba kích, Babi B.O.N, Aladka, và Calcigenol, do có thể gây ra các tác dụng phụ không mong muốn như miệng đắng, mắt mờ, mắt đau, cảm giác bứt rứt, và khát nước.\n\nNgười mắc Bệnh Tim cần thận trọng trong việc sử dụng nhiều loại thuốc và thực phẩm chức năng. Trong quá trình điều trị Bệnh Tim, cần thông báo cho bác sĩ trước khi sử dụng Dalfusin, Amilavil, và Alaxan. Bệnh Tim liên quan đến LDL cholesterol và có thể tăng nguy cơ do việc tiêu thụ sữa nguyên chất giàu cholesterol và chất béo bão hòa. Bệnh Tim cũng là yếu tố nguy cơ gây rối loạn cương dương và có thể được hỗ trợ bằng cách bổ sung vitamin B1.\n\nMột số tác dụng phụ thường gặp của thuốc như Brexin và Bricanyl có thể làm trầm trọng thêm tình trạng Bệnh Tim, bao gồm nhịp tim không đều hoặc đau thắt ngực.\nNguy Cơ Tim Mạch Cao: Nguy cơ tim mạch cao là tình trạng được Aspirin dự phòng biến chứng.\nHút Thuốc: Hút thuốc là hành vi có nhiều tác hại nghiêm trọng đến sức khỏe, bao gồm cả tác động đến hệ thống tim mạch, da, gan, và khả năng đáp ứng với các loại thuốc khác nhau. Đầu tiên, hút thuốc là yếu tố làm tăng nguy cơ mắc bệnh mạch máu ngoại biên, gây ra bệnh cước và tăng tốc độ xơ cứng động mạch. Nó cũng là yếu tố nguy cơ đối với ung thư thanh quản hầu (TNB) và có thể đóng vai trò gây ung thư TNB. Hút thuốc còn làm hỏng mạch máu, tăng nguy cơ mắc bệnh tim mạch và làm trầm trọng thêm hiệu ứng lạnh do lưu lượng máu giảm đến bàn tay và bàn chân. Ngoài ra, hút thuốc có thể làm tăng axit dạ dày và kích hoạt cơn co giật, gây thêm sự phức tạp trong việc quản lý các triệu chứng và bệnh lý liên quan đến hút thuốc.\n\nHút thuốc gây tổn hại cho da bằng cách làm hỏng collagen và elastin, thu hẹp các mạch máu, giảm cung cấp chất dinh dưỡng và oxy cho da. Điều này không chỉ làm xấu đi tình trạng của da mà còn góp phần vào việc làm suy yếu cấu trúc da. Hút thuốc lâu dài có thể làm phá hủy các động mạch, tạo ra các mảng xơ vữa do tích tụ cholesterol, dẫn đến tắc nghẽn động mạch vành, đây là một trong những nguyên nhân chính gây tử vong từ bệnh tim mạch.\n\nNgoài ra, hút thuốc còn gây tăng nguy cơ nhiễm trùng đường hô hấp trên, gây nấm thanh quản, góp phần tạo nên các nếp nhăn tĩnh và là yếu tố nguy cơ chính gây ra phình động mạch chủ. Hút thuốc cũng là yếu tố gây hại cho gan, được ngăn chặn bởi Cosele, và có thể ảnh hưởng đến sự tiến triển của bệnh u nhú thanh quản.\n\nHút thuốc là yếu tố nguy cơ chính gây ung thư phổi và ung thư thận. Nó cũng là nguyên nhân phổ biến của viêm phế quản mãn tính và khí phế thũng. Hút thuốc là một trong những yếu tố nguy cơ làm tăng khả năng mắc rối loạn nhận thức thần kinh và gây suy giảm nhận thức. Thói quen hút thuốc ở bà mẹ, bao gồm cả hút thuốc chủ động và thụ động, là hình thức lạm dụng chất kích thích và có thể gây ra tăng nguy cơ mắc hội chứng tăng trưởng intrauterine giảm (IUGR).&lt;SEP&gt;Hút thuốc có thể gây thiếu máu do thiếu vitamin C.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ liên quan đến xơ vữa động mạch.&lt;SEP&gt;Hút thuốc là yếu tố cần tránh khi sử dụng Aspilets EC.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ biến chứng tim mạch.&lt;SEP&gt;Hút thuốc là yếu tố nguy cơ làm tăng khả năng phát triển ung thư cổ tử cung.\nChậm Nhịp Xoang: Chậm nhịp xoang là một triệu chứng liên quan đến bệnh tim mạch.&lt;SEP&gt;Chậm nhịp xoang là triệu chứng.&lt;SEP&gt;Chậm nhịp xoang là triệu chứng không nên dùng Atenolol.\nSuy tim: Suy tim là bệnh tim mạch, liên quan đến chống chỉ định sử dụng thuốc.\nTiền Sử Nhồi Máu Cơ Tim: Tiền sử nhồi máu cơ tim là yếu tố nguy cơ cho bệnh nhân.&lt;SEP&gt;Tiền sử nhồi máu cơ tim là yếu tố nguy cơ tim mạch có thể dẫn đến suy tim trái.\nTim mạch: Tim mạch là hệ thống gồm tim và mạch máu, liên quan đến các chống chỉ định sử dụng thuốc.\nAvelox: Avelox là thương hiệu của thuốc kháng sinh moxifloxacin.&lt;SEP&gt;Avelox là thương hiệu của thuốc moxifloxacin.&lt;SEP&gt;Avelox là tên thương mại của thuốc moxifloxacin.\nFexofenadine: Fexofenadine là hoạt chất chính của một số thuốc như Agimfast 60 và Allerphast 60 mg, thuộc nhóm thuốc kháng histamine thế hệ thứ hai. Nó được sử dụng để điều trị các triệu chứng dị ứng. Fexofenadine là một thuốc đối kháng đặc hiệu và chọn lọc trên thụ thể Histamin H1 ngoại vi, không gây ngủ hay ảnh hưởng đến thần kinh trung ương. \n\nThuốc này có thể tương tác với các thuốc kháng acid chứa nhôm và magnesi. Sinh khả dụng của Fexofenadine có thể bị ảnh hưởng bởi Hesperidin trong Agiosmin 500mg.&lt;SEP&gt;Fexofenadine có thể bị ảnh hưởng bởi việc sử dụng cùng lúc với bưởi và táo.&lt;SEP&gt;Fexofenadine là hoạt chất chính trong Cadifast 120, thuốc kháng histamin có thể được sử dụng để điều trị các triệu chứng dị ứng.&lt;SEP&gt;Fexofenadine là hoạt chất chính trong Cadifast 120, có thể bị ảnh hưởng bởi các thuốc như Erythromycin, Ketoconazol, Verapamil, kháng acid chứa nhôm và magie, cồn, chất an thần, chất kháng cholinergic, và các loại nước hoa quả.&lt;SEP&gt;Fexofenadine là thuốc kháng histamin được sử dụng để giảm triệu chứng ngứa.\nRối Loạn Tim Mạch Nghiêm Trọng: Rối loạn tim mạch nghiêm trọng là bệnh lý cần thận trọng khi sử dụng Berodual.\nDanapha Trihex: Danapha Trihex là thuốc được sử dụng để hỗ trợ hội chứng Parkinson và làm giảm hội chứng ngoại tháp do thuốc.&lt;SEP&gt;Danapha Trihex không được khuyến cáo sử dụng cho phụ nữ có thai trừ khi lợi ích lớn hơn nguy cơ. Thuốc này cũng không nên được sử dụng khi đang cho con bú.&lt;SEP&gt;Danapha Trihex là thuốc chứa hoạt chất trihexyphenidyl.\nAspirin - Nguy Cơ Tim Mạch Cao: Aspirin được dùng dự phòng biến chứng tim mạch ở bệnh nhân có nguy cơ tim mạch cao.\nSuy Tim Mạn - Thuốc Lá: Thuốc lá là yếu tố nguy cơ đối với bệnh lý tim mạch.\nLiệt Dương - Nguy Cơ Tim Mạch: Nam giới có nguy cơ tim mạch cao hơn dễ bị liệt dương.\nThuốc Chẹn Beta - Tim Mạch: Tác dụng phụ của thuốc chẹn beta có thể bao gồm các vấn đề về tim mạch.\nSuy Tim Trái - Tiền Sử Nhồi Máu Cơ Tim: Tiền sử nhồi máu cơ tim là yếu tố nguy cơ tim mạch có thể dẫn đến suy tim trái.\nBệnh Tim - Hút Thuốc: Hút thuốc tăng nguy cơ mắc bệnh tim.\nAtenolol - Chậm Nhịp Xoang: Không nên dùng Atenolol trên đối tượng chậm nhịp xoang.\nSuy tim - Tim mạch: Suy tim nặng là một trong những chống chỉ định sử dụng thuốc.\nAvelox - Moxifloxacin: Avelox là thương hiệu của thuốc kháng sinh moxifloxacin.&lt;SEP&gt;Avelox là thương hiệu của thuốc moxifloxacin.\nFexofenadine - Tim Mạch: Bệnh nhân có nguy cơ tim mạch cần thận trọng khi dùng Fexofenadine.\nA.t Ibuprofen Syrup - Bệnh Trên Tim Mạch: Bệnh trên tim mạch là một trong những chống chỉ định khi dùng A.t Ibuprofen Syrup.\nDanapha Trihex - Loạn Nhịp Tim: Thuốc chống loạn nhịp không được khuyến cáo nếu có rối loạn nhịp tim.\nNguy Cơ Tim Mạch - Tía Tô: Tiêu thụ tía tô có thể liên quan đến việc giảm nguy cơ tim mạch nhờ khả năng chống oxy hóa cao.\nBrufen - Tim Mạch: Brufen có thể gây nguy cơ về tim mạch, đặc biệt đối với bệnh nhân lớn tuổi, có tiền sử bệnh tim mạch.\nAtidogrel - Tiền Sử Nhồi Máu Cơ Tim: Atidogrel được chỉ định để phòng ngừa biến cố huyết khối ở bệnh nhân có tiền sử nhồi máu cơ tim.\nDexamethason - Suy Tim Sung Huyết: Dexamethason có thể làm tăng nguy cơ mắc suy tim sung huyết.\nAtocib - Nguy Cơ Tim Mạch: Nguy cơ tim mạch có thể tăng theo liều dùng và thời gian dùng thuốc Atocib.\nRối Loạn Nhịp Tim - Thuốc Digoxin: Thuốc digoxin có thể gây rối loạn nhịp tim trong trường hợp hạ kali máu nhẹ.\nBerodual - Rối Loạn Tim Mạch Nghiêm Trọng: Berodual cần thận trọng trong rối loạn tim mạch nghiêm trọng.\nCandesartan - Phì Đại Cơ Tim: Cần thận trọng khi dùng Candesartan ở người bệnh có phì đại cơ tim.\nAvalo - Bệnh Huyết Khối Tắc Mạch: Bệnh huyết khối tắc mạch là bệnh chống chỉ định sử dụng Avalo.\nXyclotide - Đột Quỵ Tim Mạch: Xyclotide giảm nguy cơ đột quỵ tim mạch.']</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Người bệnh gặp vấn đề với tim cần cân nhắc kỹ trước khi sử dụng thuốc Avelox. Avelox là một loại thuốc kháng sinh thuộc nhóm fluoroquinolon, được sử dụng để điều trị các bệnh nhiễm khuẩn. Tuy nhiên, thuốc này có thể gây ra một số tác dụng phụ liên quan đến tim mạch, như làm tăng nguy cơ rối loạn nhịp tim, đặc biệt là ở những người có tiền sử bệnh tim.
+Do đó, nếu bạn đang gặp vấn đề với tim hoặc có tiền sử bệnh tim mạch, việc sử dụng Avelox cần được thảo luận kỹ với bác sĩ. Bác sĩ sẽ cân nhắc tình trạng sức khỏe của bạn và quyết định xem liệu Avelox có phù hợp để điều trị cho bạn hay không.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Không, nếu bệnh nhân đã từng được chẩn đoán rối loạn nhịp tim, suy tim hoặc nhịp tim chậm thì không được sử dụng thuốc này.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.9305958504582881</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.763898962589572</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Những đối tượng nào không được sử dụng thuốc trị viêm da axit salicylic có nồng độ trên 10%?</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>['Thuốc Trị Viêm Da: Thuốc trị viêm da chứa axit salicylic, được sử dụng để điều trị các tình trạng viêm da.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nThuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic được sử dụng để điều trị viêm da, có thể gây tác dụng phụ như kích ứng da.\nTác Dụng Không Mong Muốn: Tác Dụng Không Mong Muốn là các triệu chứng hoặc phản ứng phụ không mong đợi xảy ra khi sử dụng thuốc hoặc dược liệu. Những tác dụng này có thể bao gồm cả tác dụng phụ từ việc sử dụng thuốc đúng cách lẫn tác dụng phụ từ việc sử dụng quá liều hoặc sai cách. Tác dụng không mong muốn có thể xuất hiện khi sử dụng nhiều loại thuốc khác nhau, như Bisilkon, Bluemint, Belara, Biseptol, Brodicef, A.T.P., Ampicillin Brawn, Cefimbrano 100, và các vị thuốc cổ truyền như cỏ tháp bút, Cotrimstada, củ nén, dâm bụt, và địa cốt bì. Việc sử dụng quá liều của bất kỳ loại thuốc nào cũng có thể gây ra tác dụng không mong muốn nghiêm trọng. \n\nTác dụng không mong muốn cũng có thể xảy ra khi sử dụng dược liệu sai cách hoặc tự ý phối hợp thuốc mà không có sự tham vấn ý kiến bác sĩ. Những tác dụng này phụ thuộc vào từng cá nhân và có thể thay đổi dựa trên tình trạng sức khỏe và cách sử dụng thuốc của mỗi người. Ví dụ cụ thể về tác dụng không mong muốn có thể bao gồm việc sử dụng quá liều của thuốc A.T.P., làm tăng nguy cơ gặp tác dụng không mong muốn nghiêm trọng, đặc biệt đối với bệnh nhân suy thận. Khi sử dụng Ampicillin Brawn, bất kỳ phản ứng phụ nào cũng cần được báo cáo ngay lập tức cho bác sĩ.\n\nViệc tuân thủ chỉ định và hướng dẫn sử dụng thuốc từ bác sĩ là rất quan trọng để tránh gặp phải tác dụng không mong muốn. Tác dụng không mong muốn có thể xảy ra khi sử dụng thuốc Diurefar, Khiên ngưu, Hoàng Nàn, và nhiều vị thuốc khác. Sử dụng nhiều tỏi cũng có thể gây ra một số tác dụng không mong muốn. Tác dụng không mong muốn cũng có thể xảy ra trong quá trình sử dụng Cotrimoxazol, La hán quả, và nụ vối.\n\nNgoài ra, tác dụng không mong muốn cũng được ghi nhận khi sử dụng Mã Tiên Thảo, Tiền, Phan tả diệp, và râu mèo. Các tác dụng không mong muốn này có thể bao gồm cả tác dụng phụ từ việc sử dụng đúng cách lẫn tác dụng phụ từ việc sử dụng sai cách hoặc quá liều.\n\nTác dụng không mong muốn cũng có thể xảy ra khi sử dụng Amiodarone, Arginin, Brosafe, và Carbomango. Ngoài ra, tác dụng không mong muốn có thể xảy ra trong quá trình sử dụng thuốc tiêm bổ não Cerebrolysin và Chophytol.&lt;SEP&gt;Tác dụng không mong muốn có thể xảy ra khi sử dụng thuốc Curam.&lt;SEP&gt;Tác dụng không mong muốn có thể xảy ra trong quá trình sử dụng thuốc và cần được báo cáo cho bác sĩ.&lt;SEP&gt;Tác dụng không mong muốn có thể xảy ra khi sử dụng tinh dầu hoa cam mà không có sự hướng dẫn của bác sĩ hoặc chuyên gia.\nThuốc Dán: Thuốc dán chứa axit salicylic được sử dụng để điều trị mụn cơm và chai ở gan bàn chân.\nLiều Lượng Khuyến Nghị: Liều lượng khuyến nghị là mức sử dụng an toàn cho các thành phần từ thiên nhiên.\nAxit Salicylic: Axit salicylic là một hợp chất hóa học được tìm thấy trong rễ cây Hoàng tinh. Đây là thành phần chính của aspirin và cũng là hoạt chất trong nhiều loại thuốc trị viêm da, thuốc không kê đơn điều trị mụn trứng cá, và kem tiêu sừng tại chỗ. Axit salicylic có tác dụng làm tróc lớp sừng da và sát khuẩn nhẹ khi bôi lên da, giúp điều trị tại chỗ một số bệnh da tăng sừng hóa và bong da như viêm da tiết bã nhờn, trứng cá, gàu, bệnh vảy nến, hột cơm, và chai gan bàn chân. Nó cũng được sử dụng để đào thải mụn đầu đen và mụn đầu trắng, giảm viêm và sưng tấy. Axit salicylic giúp loại bỏ tế bào da chết và hỗ trợ điều trị bệnh nhân nhiễm trùng nấm da bàn chân. Tuy nhiên, cần lưu ý rằng axit salicylic có thể gây kích ứng và ngộ độc nếu sử dụng quá liều hoặc sai cách. Các sản phẩm chứa axit salicylic thường có nhiều nồng độ khác nhau tùy thuộc vào mục đích sử dụng cụ thể.\nTác Dụng Không Mông Muôn: Tác dụng không mong muốn có thể xảy ra khi sử dụng các thành phần từ thiên nhiên vượt quá liều lượng khuyến nghị.\nTác Dụng Phụ Khi Sử Dụng Thuốc Trị Viêm Da Axit Salicylic: Tác dụng phụ khi sử dụng thuốc trị viêm da axit salicylic bao gồm các triệu chứng như kích ứng da, nổi mề đay, khó thở, loét hoặc ăn mòn da.\nThực Phẩm: Thực Phẩm là danh từ chỉ các loại thức ăn, bao gồm cả những nguyên liệu dùng trong nấu ăn và các sản phẩm chế biến từ chúng. Thực phẩm đóng vai trò quan trọng trong cuộc sống hàng ngày và y tế. Trong y học, thực phẩm có thể gây ra tương tác với một số loại gel và thuốc như Aluminium Phosphat Gel Pharmedic và Atopiclair. Điều này nhấn mạnh tầm quan trọng của việc hiểu rõ về các thành phần và khả năng tương tác của chúng với các loại thuốc khác nhau.\n\nThực phẩm cũng đóng vai trò trong việc hỗ trợ sức khỏe tổng thể. Ví dụ, tinh dầu bạc hà thường được sử dụng trong lĩnh vực thực phẩm. Tuy nhiên, một số loại thực phẩm cụ thể như mắm, lòng heo, thịt trâu, thịt gà, thịt chó, và các sản phẩm như rượu bia, thuốc lá cần được tránh bởi những người bị hen suyễn. Việc tiêu thụ những thực phẩm này có thể làm tăng nguy cơ phát sinh triệu chứng hen suyễn. Thực phẩm cũng có thể chứa các chất hóa học gây ra triệu chứng cho người bệnh rối loạn chuyển hóa tinh bột. Điều này cho thấy tầm quan trọng của việc lựa chọn thực phẩm phù hợp để duy trì sức khỏe tốt nhất. Hơn nữa, thực phẩm còn đóng vai trò quan trọng trong việc cung cấp kali khi sử dụng Bisoplus.\n\nThực phẩm không chỉ giới hạn ở các nguyên liệu nấu ăn mà còn bao gồm cả cây trứng cá. Cây trứng cá có thể được sử dụng làm thực phẩm, mở rộng thêm phạm vi và đa dạng của thực phẩm trong đời sống hàng ngày. Thực phẩm chứa các chất dinh dưỡng hỗ trợ sự hình thành collagen. Thực phẩm là nguyên liệu được sử dụng để chế biến các món ăn, đồng thời là nguồn cung cấp dưỡng chất, được nghiên cứu về tác dụng của củ niễng. Dừa và các sản phẩm của nó (sữa và dầu) được sử dụng như thực phẩm trong cuộc sống hàng ngày. Thực phẩm giàu chất dinh dưỡng như Đông trùng hạ thảo mang lại giá trị dinh dưỡng cao và nhiều lợi ích cho sức khỏe nhưng cần tham khảo ý kiến của bác sĩ để kiểm soát rủi ro.\n\nHoa đậu biếc được sử dụng trong ẩm thực để tạo màu thực phẩm. Thực phẩm là đối tượng được bảo quản bởi hương thảo. Thực phẩm là nguyên liệu phổ biến trong các gia đình hiện nay. Thực phẩm là yếu tố có thể gây ra dị ứng. Thực phẩm là nguồn gây ra ngộ độc thực phẩm do Listeria. Ma tử nhân có thể được tiêu thụ như một loại thực phẩm sau khi nấu chín hoặc rang. Thực phẩm là các loại thức ăn cung cấp năng lượng và chất dinh dưỡng cho cơ thể.\n\nThực phẩm không vệ sinh hoặc khâu chế biến không đảm bảo có thể trở thành trung gian truyền ký sinh trùng. Thực phẩm có thể là nguyên nhân gây nhiễm trùng đường ruột nếu không được vệ sinh tốt hoặc chế biến kỹ lưỡng. Thực phẩm cũng có thể bị ô nhiễm bởi phẩy khuẩn tả nếu không được xử lý đúng cách. Thực phẩm là nguồn tiếp xúc với thạch tín, một vấn đề sức khỏe đáng lưu tâm.\n\nThực phẩm là nguồn cung cấp protein và axit amin thiết yếu cho cơ thể, đóng vai trò quan trọng trong quá trình phát triển và duy trì sức khỏe. Thực phẩm không chỉ đơn thuần là nguyên liệu nấu ăn mà còn bao gồm nhiều loại thực vật và động vật khác nhau, mỗi loại đều mang lại những giá trị dinh dưỡng riêng biệt.&lt;SEP&gt;Thực phẩm là vật liệu mà người dùng có thể đang sử dụng khi dùng Biviantac.&lt;SEP&gt;Thực phẩm có chứa fructose có thể gây tiêu chảy do không dung nạp fructose.&lt;SEP&gt;Thực phẩm là nguyên liệu được tiêu thụ có thể gây ra các triệu chứng như tiêu chảy.&lt;SEP&gt;Thực phẩm là nguồn cung cấp kẽm cho cơ thể.\nSuy Giảm Tuần Hoàn Ngoại Vi: Suy giảm tuần hoàn ngoại vi là bệnh cần thận trọng khi sử dụng axit salicylic.\nTác Dụng Phụ: Tác Dụng Phụ là các triệu chứng hoặc tình trạng sức khỏe không mong muốn có thể xảy ra khi sử dụng nhiều loại thuốc và phương pháp điều trị khác nhau. Đây là những phản ứng bất lợi xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Tác dụng phụ có thể bao gồm cả những triệu chứng không mong muốn và các tình trạng sức khỏe không thuận lợi phát sinh từ việc sử dụng thuốc.\n\nKhi sử dụng các sản phẩm như A.t Ascorbic Syrup, A.T Calmax, Domperidone, A.t Ibuprofen Syrup, Acepron 250 mg, Acnekyn, Acritel, Actiso Ladophar, Acyclovir Stella Cream, Agiosmin 500mg, Albutein, Alphalysosine, Alzental, Amoxicilin 500 mg, Appeton Lysine Syrup, Asakoya Mediplantex, Aspirin pH8, và Atenolol, có thể gặp phải tác dụng phụ. Ví dụ, khoảng 5-15% người bệnh gặp phải tác dụng phụ khi sử dụng A.t Ibuprofen Syrup, và việc sử dụng quá liều thuốc Aleucin 500 mg, Ambroxol Boston cũng có thể dẫn đến tác dụng phụ. Đặc biệt, việc sử dụng quá liều A.T Calmax có thể dẫn đến tình trạng quá liều canxi.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng Atorhasan và Atorpa-E, mặc dù chi tiết cụ thể về tác dụng phụ của Atorhasan chưa được nêu rõ trong văn bản. Tác dụng phụ cũng được xác định khi sử dụng Azanex và Azibiotic, bao gồm cả các phản ứng phụ không mong muốn. Thuốc Benda cũng có thể gây ra các tác dụng phụ như biểu hiện không mong muốn. Tác dụng phụ còn được ghi nhận khi sử dụng Bostanex và Calci D Hasan, bao gồm cả những phản ứng không mong muốn. Tác dụng phụ cũng thường gặp khi sử dụng Calci - D Mekophar. Tác dụng phụ là những dấu hiệu không mong muốn trong quá trình sử dụng thuốc, có thể xảy ra nếu sử dụng các sản phẩm như Cánh kiến đỏ tùy tiện. Tác dụng phụ cũng bao gồm các triệu chứng bất lợi do sử dụng cây xương khô.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng dược liệu từ cây Lưỡi hổ. Tác dụng phụ cũng có thể xảy ra nếu lạm dụng cây chanh trong điều trị sốt cao ở trẻ em. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng thuốc như Ciacca hay Cimetidine MKP, trong đó tác dụng phụ thường gặp của Cimetidine MKP bao gồm các vấn đề trên đường tiêu hóa. Cuối cùng, tác dụng phụ và biến chứng không thể phục hồi là hậu quả của việc sử dụng corticoid thoa trong thời gian dài.\n\nTác dụng phụ cũng được ghi nhận khi sử dụng dầu tràm trà, Diorophyl, cao dừa cạn, hoa đào, Bepanthen Balm, và Khiên ngưu tử. Việc sử dụng quá liều cao dừa cạn có thể gây ra sự phát triển bất thường của thai trong chuột. Tác dụng phụ của Diorophyl có thể nghiêm trọng đến mức người dùng cần phải đến cơ sở y tế nếu gặp tác dụng không mong muốn. Tác dụng phụ chưa được báo cáo rõ ràng khi sử dụng hoa đào.\n\nMã Tiên Thảo cũng có thể gây ra tác dụng phụ. Lá Ngũ trảo có thể gây dị ứng và mẩn ngứa khi được sử dụng. Sử dụng kháng sinh cũng có thể dẫn đến tình trạng kháng vi khuẩn và nhiễm trùng thứ phát. Tác dụng phụ có thể gây ảnh hưởng nghiêm trọng đến cơ thể khi sử dụng thuốc. Tác dụng phụ là những phản ứng không mong muốn khi sử dụng Clorocid. Tác dụng phụ cũng có thể là phản ứng phụ có thể xảy ra khi sử dụng các loại thuốc điều trị viêm da tiết bã, bao gồm cả tình trạng gây kích ứng da hoặc khó chịu.\n\nNgoài ra, tác dụng phụ có thể xảy ra khi sử dụng Atarax, thuốc Baclofen, Betmiga 50 mg, và Bioflora. Tác dụng phụ của Alpha Brain chưa được báo cáo. Tác dụng phụ cũng có thể xảy ra khi dùng thuốc Broncho-Vaxom kéo dài, cần cân nhắc có nên tiếp tục sử dụng. Các tác dụng phụ khác có thể bao gồm phản ứng phản vệ, bệnh huyết thanh, vàng da, ứ mật, hoại tử gan, tăng kali huyết, giảm đường huyết, suy thận, viêm thận kẽ, sỏi thận, ù tai, ảo giác, viêm màng não vô khuẩn.\n\nTóm lại, Tác Dụng Phụ là những phản ứng không mong muốn xảy ra khi sử dụng thuốc, dược liệu, hoặc các phương pháp điều trị khác. Chúng có thể bao gồm một loạt các triệu chứng và tình trạng sức khỏe không mong muốn, từ nhẹ đến nghiêm trọng, tùy thuộc vào loại thuốc hoặc phương pháp điều trị được sử dụng.&lt;SEP&gt;Tác dụng phụ có thể xảy ra khi sử dụng Advil.\nNhững Triệu Chứng Ngộ Độc Axit Salicylic: Những triệu chứng ngộ độc axit salicylic là các triệu chứng biểu hiện khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nCách Dùng Và Liều Dùng Thuốc: Cách dùng và liều dùng thuốc là hướng dẫn về cách sử dụng và liều lượng của thuốc.\nNgộ Độc Axit Salicylic: Ngộ độc axit salicylic là tình trạng sức khỏe xảy ra khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nThuốc Nước: Thuốc nước chứa axit salicylic được bôi lên vùng da cần điều trị.\nAxit Salicylic - Đái Tháo Đường: Người bệnh đái tháo đường không nên sử dụng axit salicylic.&lt;SEP&gt;Đái tháo đường là yếu tố nguy cơ khi sử dụng axit salicylic.\nDược Liệu - Tác Dụng Không Mong Muốn: Kiểm soát rủi ro và tác dụng không mong muốn khi sử dụng dược liệu.&lt;SEP&gt;Dùng dược liệu có thể gây ra tác dụng không mong muốn.&lt;SEP&gt;Dược liệu có thể gây ra tác dụng không mong muốn nếu không được sử dụng đúng cách.\nThuốc Trị Viêm Da - Đái Tháo Đường: Đái tháo đường là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nLiều Lượng Khuyến Nghị - Tác Dụng Không Mông Muôn: Sử dụng vượt quá liều lượng khuyến nghị có thể dẫn đến tác dụng không mong muốn.\nAxit Salicylic - Chóng Mặt: Chóng mặt là triệu chứng của ngộ độc axit salicylic.\nThực Phẩm - Tác Dụng Phụ: Cần cẩn trọng trong cách dùng, liều lượng và đối tượng người dùng để tránh tác dụng phụ không đáng có.\nAxit Salicylic - Đau Đầu: Đau đầu nặng hoặc liên tục là triệu chứng của ngộ độc axit salicylic.\nCách Dùng Và Liều Dùng Thuốc - Thuốc: Hướng dẫn cách dùng và liều dùng thuốc.\nChóng Mặt - Thuốc Trị Viêm Da: Chóng mặt là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nDược Sĩ - Thuốc: Dược sĩ tư vấn về việc sử dụng thuốc.\nChóng Mặt - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng chóng mặt.\nRủi Ro - Vị Thuốc: Việc sử dụng vị thuốc có thể dẫn đến rủi ro cần được kiểm soát.&lt;SEP&gt;Kiểm soát rủi ro khi sử dụng vị thuốc cần tham khảo ý kiến bác sĩ.&lt;SEP&gt;Việc sử dụng vị thuốc có thể mang lại rủi ro.&lt;SEP&gt;Y bác sĩ đề nghị kiểm soát rủi ro khi sử dụng vị thuốc.\nThuốc Trị Viêm Da - Đau Đầu: Đau đầu nặng hoặc liên tục là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nLạm Dụng Thuốc - Suy Nhược Thần Kinh: Lạm dụng thuốc là hành vi sử dụng thuốc không đúng cách.\nAxit Salicylic - Da: Axit salicylic có thể tác động lên da.\nThuốc - Việc Sử Dụng Sai Lầm: Sử dụng thuốc sai cách có thể dẫn đến việc sử dụng sai thuốc.\nBeprosalic - Ngứa: Beprosalic gây ngứa.\nQuá Liều - Thuốc A.T.P: Nguy cơ của việc dùng quá liều thuốc A.T.P.\nAspirin - Axit Salicylic: Axit salicylic là thành phần chính của aspirin.\nLiều Lượng - Thảo Dược: Việc sử dụng thảo dược cần chú ý đến liều lượng.\nDa - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên da.\nKhó Thở - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây khó thở.\nAxit Salicylic - Viêm Da: Axit salicylic có nhiều nồng độ khác nhau, cần bắt đầu với nồng độ thấp và tăng dần theo đáp ứng bệnh.&lt;SEP&gt;Axit salicylic được sử dụng để điều trị viêm da.\nAxit Salicylic - Mắt: Axit salicylic có thể tác động lên mắt.\nAxit Salicylic - Ngộ Độc: Axit salicylic có thể gây ngộ độc nếu sử dụng sai cách.\nAxit Salicylic - Cho Con Bú: Sử dụng axit salicylic cần thận trọng trong thời kỳ cho con bú.\nBeprosalic - Corticosteroid: Beprosalic có thể liên kết với corticosteroid trong việc điều trị nhiễm nấm da.\nAxit Salicylic - Hoàng Tinh: Hoàng tinh chứa axit salicylic như thành phần hóa học.\nAxit Salicylic - Mẫn Cảm: Người bị mẫn cảm với axit salicylic không nên sử dụng thuốc này.\nBeprosalic - Triệu Chứng Bất Thường: Khi xuất hiện triệu chứng bất thường, cần báo cáo ngay cho bác sĩ để được xử trí và hỗ trợ kịp thời.\nBeprosalic - Viêm Da Tiết Bã: Beprosalic được dùng để điều trị viêm da tiết bã.\nAxit Salicylic - Mụn Trứng Cá: Axit salicylic được dùng để điều trị mụn trứng cá.\nBeprosalic - Viêm Da: Beprosalic được sử dụng để điều trị viêm da.&lt;SEP&gt;Beprosalic có thể gây viêm da.\nAxit Salicylic - Mũi: Axit salicylic có thể tác động lên mũi.\nBeprosalic - Viêm Nang Lông: Beprosalic gây viêm nang lông.\nMắt - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên mắt.\nAxit Salicylic - Mụn Trứng Cà: Axit salicylic được sử dụng để điều trị mụn trứng cá ở dạng nhẹ.\nAxit Salicylic - Lú Lẫn: Lú lẫn là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Niêm Mạc: Không nên bôi axit salicylic lên niêm mạc.&lt;SEP&gt;Axit salicylic có thể tác động lên niêm mạc.\nNgộ Độc - Thuốc Trị Viêm Da: Thuốc trị viêm da chứa axit salicylic có thể gây ngộ độc nếu sử dụng sai cách.\nNgộ Độc Axit Salicylic - Ù Tai: Ngộ độc axit salicylic biểu hiện triệu chứng ù tai.\nAxit Salicylic - Da Đầu: Axit salicylic được sử dụng để điều trị các vấn đề da đầu như vảy da đầu.\nAxit Salicylic - Miệng: Axit salicylic có thể tác động lên miệng.\nThuốc Nước - Viêm Da: Thuốc nước chứa axit salicylic được sử dụng để điều trị viêm da.\nAxit Salicylic - Trứng Cá: Axit salicylic được sử dụng để điều trị trứng cá.&lt;SEP&gt;Axit salicylic được dùng để điều trị trứng cá.\nNổi Mề Đay - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây nổi mề đay.\nAxit Salicylic - Thuốc Kháng Nấm: Axit salicylic hỗ trợ phương pháp điều trị bằng thuốc kháng nấm.\nAxit Salicylic - Tay: Axit salicylic có thể tác động lên tay.\nAxit Salicylic - Thời Kỳ Mang Thai: Sử dụng axit salicylic cần thận trọng trong thời kỳ mang thai.\nBeprosalic - Quá Mẫn: Beprosalic có thể gây quá mẫn.\nAxit Salicylic - Liều Thuốc: Phải sử dụng axit salicylic theo đúng liều lượng và hướng dẫn của bác sĩ.\nMũi - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên mũi.\nAxit Salicylic - Thuốc Trị Viêm Da: Axit salicylic là thành phần chính của thuốc trị viêm da.\nAxit Salicylic - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic xảy ra khi sử dụng quá liều thuốc trị viêm da axit salicylic.\nAxit Salicylic - Thở Nhanh: Thở nhanh là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Mụn Dai Dẳng: Axit salicylic giúp loại bỏ tế bào da chết.\nAxit Salicylic - Bệnh Vảy Nến: Axit salicylic được dùng để điều trị bệnh vảy nến.\nAxit Salicylic - Gàu: Axit salicylic được dùng để điều trị gàu.\nAxit Salicylic - Thuốc Mỡ: Thuốc mỡ chứa axit salicylic.\nLú Lẫn - Thuốc Trị Viêm Da: Lú lẫn là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nLú Lẫn - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng lú lẫn.\nNiêm Mạc - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên niêm mạc.\nAxit Salicylic - Suy Tuần Hoàn: Người bệnh suy tuần hoàn không nên sử dụng axit salicylic.\nAxit Salicylic - Thuốc Trị Viêm Da Axit Salicylic: Axit salicylic là thành phần chính trong thuốc trị viêm da.\nAxit Salicylic - Thuốc Khác: Axit salicylic có thể xảy ra tương tác với các loại thuốc khác.\nAxit Salicylic - Viêm Da Tiết Bã Nhờn: Axit salicylic được dùng để điều trị viêm da tiết bã nhờn.\nBeprosalic - Kích Ứng: Beprosalic có thể gây kích ứng.&lt;SEP&gt;Beprosalic gây kích ứng.\nAxit Salicylic - Tăng Tiết Bã Nhờn: Axit salicylic được dùng để điều trị tăng tiết bã nhờn.\nAxit Salicylic - Mụn Cơm: Axit salicylic giúp loại bỏ mụn cơm.&lt;SEP&gt;Axit salicylic được sử dụng để điều trị mụn cơm.\nAxit Salicylic - Thuốc Dán: Thuốc dán chứa axit salicylic.\nAxit Salicylic - Dày Sừng Da Bàn Chân: Axit salicylic là hợp chất hóa học được sử dụng trong kem tiêu sừng để điều trị dày sừng da bàn chân.\nAxit Salicylic - Dầu Parafin: Dầu parafin được sử dụng để bảo vệ da khỏi kích ứng do axit salicylic.\nAxit Salicylic - Trí Tuệ: Axit salicylic có thể tác động lên trí tuệ.\nAxit Salicylic - Đầu Chi: Axit salicylic cần thận trọng khi bôi lên đầu chi của người bệnh suy giảm tuần hoàn ngoại vi hoặc đái tháo đường.\nAxit Salicylic - Tăng Sừng: Axit salicylic được sử dụng trong kem tiêu sừng tại chỗ để điều trị tăng sừng.\nAxit Salicylic - Tiêu Sừng Tại Chỗ: Axit salicylic là hoạt chất trong kem tiêu sừng tại chỗ.\nAxit Salicylic - Tiếng Rung Trong Tai: Tiếng rung hoặc tiếng vo vo trong tai liên tục là triệu chứng của ngộ độc axit salicylic.\nAxit Salicylic - Suy Giảm Tuần Hoàn Ngoại Vi: Suy giảm tuần hoàn ngoại vi là yếu tố nguy cơ khi sử dụng axit salicylic.\nAxit Salicylic - Đa Dây Thần Kinh Ngoại Vi: Đa dây thần kinh ngoại vi rõ là yếu tố nguy cơ khi sử dụng axit salicylic.\nAxit Salicylic - Thuốc Kem: Thuốc kem chứa axit salicylic.\nAxit Salicylic - Thuốc Nước: Thuốc nước chứa axit salicylic.\nAxit Salicylic - Thuốc Gel: Thuốc gel chứa axit salicylic.\nAxit Salicylic - Chai Ở Gan Bàn Chân: Axit salicylic được sử dụng để điều trị chai ở gan bàn chân.\nAxit Salicylic - Gan Bàn Chân: Axit salicylic điều trị chứng tăng sừng khu trú ở gan bàn chân.\nAxit Salicylic - Bệnh Da Tróc Vảy: Axit salicylic được dùng để điều trị bệnh da tróc vảy.\nAxit Salicylic - Hột Cơm: Axit salicylic được dùng để điều trị hột cơm.\nAxit Salicylic - Chai Gan Bàn Chân: Axit salicylic được dùng để điều trị chai gan bàn chân.\nAxit Salicylic - Niêm Mạc Tiêu Hóa: Axit salicylic đường toàn thân gây kích ứng mạnh niêm mạc tiêu hóa.\nAxit Salicylic - Tăng Sừng Khu Trú: Axit salicylic được dùng để điều trị tăng sừng khu trú.\nAxit Salicylic - Gan Bàn Tay: Axit salicylic điều trị chứng tăng sừng khu trú ở gan bàn tay.\nAxit Salicylic - Da Bị Nứt Nẻ: Không nên bôi axit salicylic trên da bị nứt nẻ.\nAxit Salicylic - Chứng Tăng Sừng Khu Trú: Axit salicylic được sử dụng để điều trị chứng tăng sừng khu trú.\nBeprosalic - Rạn Da: Beprosalic gây rạn da.\nMiệng - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên miệng.\nKích Ứng Da - Thuốc Trị Viêm Da Axit Salicylic: Thuốc trị viêm da axit salicylic có thể gây kích ứng da.\nBeprosalic - Khô Da: Beprosalic gây khô da.\nBeprosalic - Nóng Rát: Beprosalic gây nóng rát.\nBeprosalic - Teo Da: Beprosalic gây teo da.\nTay - Thuốc Trị Viêm Da: Thuốc trị viêm da có thể tác động lên tay.\nBeprosalic - Bệnh Vẩy Nến: Beprosalic được dùng để điều trị bệnh vẩy nến.\nNgộ Độc Axit Salicylic - Sưng Mặt: Ngộ độc axit salicylic biểu hiện triệu chứng sưng mặt.\nNgộ Độc Axit Salicylic - Ra Mồ Hôi: Ngộ độc axit salicylic biểu hiện triệu chứng ra mồ hôi.\nAcid Salicylic - Beprosalic: Beprosalic chứa hoạt chất acid salicylic.&lt;SEP&gt;Beprosalic chứa acid salicylic.\nGiãn Mạch - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic biểu hiện triệu chứng giãn mạch.\nThuốc Trị Viêm Da - Thở Nhanh: Thở nhanh là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nNgộ Độc Axit Salicylic - Thở Nhanh: Ngộ độc axit salicylic biểu hiện triệu chứng thở nhanh.\nBeprosalic - Betamethasone Dipropionate: Beprosalic chứa hoạt chất betamethasone dipropionate.\nNgộ Độc Axit Salicylic - Điếc: Ngộ độc axit salicylic biểu hiện triệu chứng điếc.\nBeprosalic - Viêm Da Thần Kinh: Beprosalic được dùng để điều trị viêm da thần kinh.\nBeprosalic - Thiểu Năng Tuyến Yên: Sử dụng Beprosalic quá lâu có thể gây ra thiểu năng tuyến yên.\nBan Hạt Kê - Beprosalic: Beprosalic gây ban hạt kê.\nBeprosalic - Giảm Sắc Tố Da: Beprosalic gây giảm sắc tố da.\nBeprosalic - Nguyễn Ngọc Cẩm Tiên: Dược sĩ Nguyễn Ngọc Cẩm Tiên đưa ra hướng dẫn sử dụng thuốc Beprosalic.\nBeprosalic - Nhiễm Khuẩn Thứ Phát: Beprosalic gây nhiễm khuẩn thứ phát.\nBeprosalic - Rậm Lông Tóc: Beprosalic gây rậm lông tóc.\nBan Dạng Mụn - Beprosalic: Beprosalic gây ban dạng mụn.\nBeprosalic - Bợt Da: Beprosalic gây bợt da.\nAminoleban - Beprosalic: Không có ghi nhận tương tác giữa Aminoleban và Beprosalic.\nBeprosalic - Carbimazole: Beprosalic chứa thành phần Carbimazole cần được bảo quản tránh tiếp xúc trực tiếp với ánh sáng.\nBeprosalic - Liều Quá Lâu: Sử dụng Beprosalic quá lâu có thể gây ra thiểu năng tuyến thượng thận thứ phát và ngộ độc Salicylate.\nBeprosalic - Viêm Da Dị Ứng Mạn Tính: Beprosalic được dùng để điều trị viêm da dị ứng mạn tính.\nBeprosalic - Lotusalic: Beprosalic có thành phần hoạt chất tương tự như Lotusalic.\nBeprosalic - Hasaderm: Beprosalic có thành phần hoạt chất tương tự như Hasaderm.\nNgộ Độc Axit Salicylic - Sưng Môi: Ngộ độc axit salicylic biểu hiện triệu chứng sưng môi.\nNgộ Độc Axit Salicylic - Sưng Cổ Họng: Ngộ độc axit salicylic biểu hiện triệu chứng sưng cổ họng.\nNgộ Độc Axit Salicylic - Sưng Lưỡi: Ngộ độc axit salicylic biểu hiện triệu chứng sưng lưỡi.\nDầu Parafin - Thuốc Trị Viêm Da: Dầu parafin được sử dụng để bảo vệ da khỏi kích ứng do thuốc trị viêm da.\nThuốc Trị Viêm Da - Trí Tuệ: Thuốc trị viêm da có thể tác động lên trí tuệ.\nThuốc Trị Viêm Da - Đầu Chi: Thuốc trị viêm da cần thận trọng khi bôi lên đầu chi của người bệnh suy giảm tuần hoàn ngoại vi hoặc đái tháo đường.\nThuốc Trị Viêm Da - Tiếng Rung Trong Tai: Tiếng rung hoặc tiếng vo vo trong tai liên tục là triệu chứng của ngộ độc axit salicylic từ thuốc trị viêm da.\nSuy Giảm Tuần Hoàn Ngoại Vi - Thuốc Trị Viêm Da: Suy giảm tuần hoàn ngoại vi là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nThuốc Trị Viêm Da - Đa Dây Thần Kinh Ngoại Vi: Đa dây thần kinh ngoại vi rõ là yếu tố nguy cơ khi sử dụng thuốc trị viêm da.\nNgộ Độc Axit Salicylic - Thở Sâu: Ngộ độc axit salicylic biểu hiện triệu chứng thở sâu.\nHấp Thu Thuốc - Ngộ Độc Axit Salicylic: Ngộ độc axit salicylic xảy ra do hấp thu quá nhiều axit salicylic.\nNgộ Độc Axit Salicylic - Tác Dụng Phụ Khi Sử Dụng Thuốc Trị Viêm Da Axit Salicylic: Ngộ độc axit salicylic là một trong những tác dụng phụ khi sử dụng thuốc trị viêm da axit salicylic.\nNgộ Độc Axit Salicylic - Tiếng Rung: Ngộ độc axit salicylic biểu hiện triệu chứng tiếng rung.\nNgộ Độc Axit Salicylic - Tiếng Vo Vo: Ng</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Thuốc trị viêm da axit salicylic có nồng độ trên 10% không được sử dụng cho:
+- Vùng da nhiễm khuẩn, bị viêm, hoặc kích ứng.
+- Mặt, bộ phận sinh dục, mũi, miệng, trên nốt ruồi, vết chàm, mụn cơm có lông mọc.
+- Người bệnh bị đái tháo đường hoặc suy tuần hoàn.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nồng độ trên 10% của thuốc trị viêm da axit salicylic không được sử dụng cho đối tượng bệnh nhân bị bẹnh tiểu đường hoặc suy tuần hoàn.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6146635792471733</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.7786658947867933</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>['Alphachymotrypsin: Alphachymotrypsin là thuốc được sử dụng trong một số trường hợp y tế.\nBệnh: Bệnh là thuật ngữ chung chỉ tình trạng sức khỏe không tốt, cần được điều trị. Bệnh có thể là kết quả của nhiều yếu tố khác nhau và có thể gây ra lo lắng, đặc biệt là đối với những người chưa có con. Bệnh có thể được phát hiện và điều trị kịp thời nếu nhận thấy dấu hiệu bất thường. Một số bệnh có tiên lượng khá tốt, với khoảng 90% người bệnh được chữa khỏi chỉ bằng kháng sinh và không còn để lại di chứng. Tuy nhiên, cũng có một số bệnh chưa được mô tả cụ thể và có thể tái phát nếu ngừng thuốc sớm.\n\nBệnh có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm việc sử dụng các loại thảo dược như cây Đại, Cần Tây, cây Bòng Bong, lá dứa, dền gai, hoa đậu biếc, và hồi đầu thảo. Thông tin về tác dụng của một số loại cây này chưa có nhiều nghiên cứu khoa học rõ ràng. Bệnh có thể xảy ra khi pH nước bọt chệch khỏi phạm vi lý tưởng trong một thời gian dài.\n\nBệnh cũng có thể được điều trị bằng Lô căn hoặc Tiền. Bệnh là tình trạng sức khỏe không bình thường và có thể được theo dõi và điều trị tại nhà nếu nhẹ. Bệnh có thể gây ra triệu chứng ngứa và nổi mề đay.\n\nTóm lại, bệnh là tình trạng sức khỏe không tốt cần được điều trị, có thể được điều trị bằng nhiều phương pháp khác nhau, bao gồm cả việc sử dụng các loại thảo dược và dược liệu, cũng như các phương pháp điều trị khác như Lô căn và Tiền.&lt;SEP&gt;Bệnh là thuật ngữ chung để chỉ các trạng thái bệnh lý.&lt;SEP&gt;Bệnh cần được đánh giá tình trạng thông qua các xét nghiệm và kiểm tra y tế.&lt;SEP&gt;Bệnh là tình trạng sức khỏe bất thường cần được điều trị.&lt;SEP&gt;Bệnh là tình trạng mà việc rửa tay kỹ có thể giúp ngăn ngừa.\nRối Loạn Trầm Trọng Chức Năng Gan: Rối loạn trầm trọng chức năng gan là một bệnh lý cần cân nhắc trước khi sử dụng Alphalysosine.\nThuốc: Thuốc là thuật ngữ chung chỉ các loại vật chất được sử dụng trong y học nhằm mục đích phòng ngừa, chẩn đoán, hoặc điều trị bệnh. Thuốc bao gồm nhiều loại khác nhau, từ các loại thuốc hiện đại như Ambroxol Boston và Asevictoria Mediplantex đến các bài thuốc truyền thống được chuẩn bị từ thảo mộc như Lá Chanh, Lá Chàm, Hương Nhu, Kinh Giới, và Tía Tô. Thuốc đóng vai trò quan trọng trong việc cải thiện sức khỏe và hỗ trợ điều trị nhiều loại bệnh khác nhau, bao gồm cả hội chứng Tourette khi triệu chứng tic trở nên quá nghiêm trọng, gây nguy hiểm cho người bệnh. Chúng cũng được sử dụng để điều trị các tình trạng khác như thuốc nhuận trường hoặc thuốc xổ để xử lý trường hợp quá liều Aluminium Phosphat Gel Pharmedic.\n\nThuốc cũng được vận chuyển bởi albumin trong Albiomin 20% và là phương án điều trị nội khoa cho bệnh Basedow, được sử dụng để điều trị bướu cổ dựa trên tình trạng và nguyên nhân bệnh. Đồng thời, thuốc cũng được sử dụng để điều trị động kinh thùy thái dương và động kinh nói chung. Cần lưu ý rằng việc sử dụng thuốc cần tuân thủ hướng dẫn của bác sĩ và dược sĩ, đồng thời kiểm tra hạn dùng và bảo quản thuốc đúng cách.\n\nThuốc cũng được sử dụng để điều trị chứng rối loạn khiếm khuyết cơ thể và các tình trạng khác. Tuy nhiên, việc sử dụng thuốc cần được thực hiện thận trọng, đặc biệt là đối với phụ nữ mang thai, người rối loạn chức năng gan nặng, hoặc người mắc hội chứng suy giảm hấp thu nặng như bệnh Crohn. Một số loại thuốc như an thần, hạ nhiệt, giảm đau có thể được hấp thụ tại ruột già. Thuốc cũng là thành phần của bài thuốc điều trị tiểu đường. Gần như toàn cây từ vỏ thân, vỏ rễ đến hoa, lá, nhựa, tất cả đều có thể dùng làm thuốc. Đặc biệt, quả, lá và rễ chanh được sử dụng làm thuốc. Thuốc từ cây Hoa mào gà được sử dụng để điều trị các bệnh khác nhau.\n\nThuốc có thể là yếu tố gây bệnh thận thứ phát, viêm mạch và đa u hạt dị ứng. Thuốc bao gồm cả thuốc kê đơn, không kê đơn, vitamin, thuốc dược liệu. Thuốc Bắc cảo bản và Liêu cảo bản cũng có tác dụng dược lý. Việc sử dụng thuốc cần tuân thủ chặt chẽ chỉ định của bác sĩ và dược sĩ, đảm bảo rằng thuốc được bảo quản đúng cách và không vượt quá hạn sử dụng.\n\nThuốc có thể gây ra các vấn đề như mất ngủ ở người già, gây chảy máu lâu cầm, làm mất hệ thống cân bằng ở tai trong và gây chóng mặt. Thuốc cũng được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng. Thuốc được sử dụng trong điều trị chứng ngủ nhiều nguyên phát để kiểm soát triệu chứng. Thuốc có thể ảnh hưởng đến sự phát triển não bộ của thai nhi. Thuốc là một phần của điều trị rối loạn phân ly. Thuốc là phương pháp điều trị chứng sợ khoảng rộng, giúp kiểm soát triệu chứng. Thuốc là chất có thể gây ra các triệu chứng tâm thần.\n\nThuốc cũng được sử dụng để giữ cho các cầu nối mở, giúp duy trì dòng máu chảy nuôi cơ thể cho đến khi phẫu thuật tim được thực hiện. Thuốc cũng được sử dụng để điều trị bệnh hoang tưởng và các rối loạn tâm thần khác. Thuốc cũng được sử dụng để điều trị các vấn đề liên quan đến hội chứng Down như nhiễm trùng hoặc bệnh tim. Thuốc có thể được sử dụng để giảm triệu chứng cho trẻ mắc hội chứng rượu bào thai. Thuốc còn được sử dụng để điều trị nhịp tim bất thường do WPW. Một số thuốc có tác dụng phụ làm khô miệng và khiến tế bào chết dễ tích tụ lại trên lưỡi.\n\nThuốc cũng được sử dụng để điều trị rối loạn mất ngủ và các rối loạn tâm thần liên quan. Thuốc được sử dụng để điều trị các triệu chứng như co giật, bế kinh, ho khạc ra đờm máu và bệnh lao phổi. Thuốc cũng được sử dụng để điều trị các triệu chứng liên quan đến nghiến răng. Thuốc được chỉ định dùng để kiểm soát đường huyết trong trường hợp tiểu đường thai kỳ không cải thiện bằng thay đổi lối sống. Thuốc không thể chữa khỏi nhiễm trùng đường hô hấp trên nhưng có thể giúp giảm các triệu chứng.\n\nThuốc, gồm các thuốc điều trị rối loạn nhịp tim, tăng huyết áp và loạn thần, có thể gây ra nhịp tim chậm. Thuốc cũng được sử dụng để điều trị bệnh Castleman, có thể bao gồm siltuximab, rituximab, corticosteroids và thuốc kháng virus. Thuốc được sử dụng để điều trị đau thắt ngực ổn định mạn tính, đau thắt ngực không ổn định hoặc nhồi máu cơ tim không có ST chênh, và nhồi máu cơ tim cấp. Thuốc cũng được sử dụng để điều trị co giật nửa mặt. Thuốc có thể là nguyên nhân gây mề đay cấp và cũng có thể là yếu tố gây khởi phát mề đay và phù mạch.\n\nThuốc là phương tiện điều trị bệnh tim mạch và cũng là phương pháp điều trị được sử dụng đầu tiên cho bệnh nhân phì đại tuyến tiền liệt. Ngoài ra, có một số thuốc được làm từ yếm rùa, dùng trong y học. Thuốc có thể gây ra rối loạn điện giải, đòi hỏi bác sĩ phải điều chỉnh liều lượng hoặc loại thuốc khác. Thuốc cũng có thể gây rối loạn khứu giác. Thuốc cũng có thể hữu ích trong điều trị rối loạn nhân cách hoang tưởng, đặc biệt nếu người bệnh có các tình trạng liên quan khác như trầm cảm hoặc rối loạn lo âu. Thuốc được sử dụng để điều trị các tình trạng bệnh đi kèm như trầm cảm, lo âu trong rối loạn nhân cách phân liệt. Thuốc được sử dụng trong điều trị nỗi đau phức tạp, nhưng các nghiên cứu về hiệu quả vẫn chưa nhiều.\n\nThuốc cũng được sử dụng để điều trị các bệnh như đái tháo đường, cường giáp, suy giáp và hội chứng Cushing. Việc sử dụng thuốc cần tuân thủ chính xác liều lượng theo chỉ định của bác sĩ. Thuốc cũng có thể gây tác dụng phụ như tiêu chảy nếu sử dụng lâu dài. Thuốc được sử dụng để giảm nguy cơ hấp thụ quá nhiều vitamin D và canxi. Thuốc cũng được sử dụng để điều trị viêm nhiễm gây ra tinh trùng yếu.\n\nThuốc được sử dụng để điều trị rối loạn trầm cảm ở mức độ trung bình trở lên. Thuốc có hai mặt lợi và hại như nhau, không ứ trệ không dùng. Thuốc cũng được sử dụng để làm giảm đau và dãn cơ trước khi đưa xương trở lại vị trí phù hợp. Thuốc cũng được sử dụng để kiểm soát cơn đau trong điều trị ung thư phổi giai đoạn cuối. Thuốc giúp cơ tim co bóp hoặc kiểm soát các bất thường về nhịp tim.\nRối Loạn Trầm Trọng Chức Năng Thận: Rối loạn trầm trọng chức năng thận là một bệnh lý cần cân nhắc trước khi sử dụng Alphalysosine.\nVị Thuốc: Vị Thuốc là thuật ngữ dùng để chỉ các loại thảo dược hoặc nguyên liệu tự nhiên được sử dụng trong y học cổ truyền để điều trị bệnh và cải thiện sức khỏe. Vị thuốc có thể phát huy công dụng đối với sức khỏe khi sử dụng đúng cách, tuy nhiên việc sử dụng chúng cũng tiềm ẩn rủi ro và tác dụng phụ. Do đó, người dùng cần tham khảo ý kiến của bác sĩ trước khi sử dụng bất kỳ vị thuốc nào để kiểm soát rủi ro và đảm bảo an toàn. Vị thuốc có nhiều tác dụng khác nhau, bao gồm cả việc chữa cảm sốt và các bệnh về tiêu hóa.\n\nCác vị thuốc khác nhau có thể được sử dụng để điều trị các bệnh cụ thể. Ví dụ, cà cuống được sử dụng để điều trị bệnh, trong khi cải cúc được sử dụng như một vị thuốc chữa ho và giải cảm. Vị thuốc cũng được sử dụng rộng rãi trong cuộc sống hàng ngày thông qua các bài thuốc chữa bệnh. Tuy nhiên, một số vị thuốc có thể gây dị ứng và cần được sử dụng một cách cẩn trọng. Vị thuốc này được sử dụng rộng rãi trong dân gian để điều trị bệnh.\n\nVị thuốc là nguyên liệu thảo dược được sử dụng trong điều trị bệnh. Thuật ngữ này cũng bao gồm các thành phần hoặc nguyên liệu dùng trong y học, như Đơn buốt. Vị thuốc có công dụng đối với sức khỏe nhưng cần kiểm soát rủi ro và tác dụng không mong muốn.&lt;SEP&gt;Vị thuốc là một loại thuốc hoặc thành phần thảo dược được sử dụng trong y học cổ truyền.&lt;SEP&gt;Vị thuốc Thạch hộc được đề cập đến như một vật phẩm quý giá, tương đương với số lượng gạo rất lớn.&lt;SEP&gt;Vị thuốc là các thành phần tự nhiên được sử dụng trong y học cổ truyền, có thể mang lại lợi ích nhưng cũng có thể gây hại tùy thuộc vào liều lượng và cách sử dụng.&lt;SEP&gt;Vị thuốc được dùng nhiều trong các bài thuốc chữa bệnh cũng như cuộc sống hằng ngày.&lt;SEP&gt;Vị thuốc là phương pháp điều trị được đề cập trong văn bản.\nViêm Nhiễm Sau Phẫu Thuật: Viêm nhiễm sau phẫu thuật là tình trạng mà Alphalysosine được sử dụng để điều trị.\nBệnh Về Tiêu Hóa: Hạt Gai cua được sử dụng uống trị các bệnh về tiêu hóa như nhuận tràng, gây nôn, long đờm.&lt;SEP&gt;Bệnh về tiêu hóa là bệnh được điều trị bằng vị thuốc.\nAlphathepham: Alphathepham là thuốc chứa thành phần tương tự như Alphalysosine.\nChữa Bệnh Di Tinh: Chữa bệnh di tinh có thể được thực hiện thông qua việc thay đổi lối sống hoặc dùng thuốc theo chỉ định của bác sĩ.\nViêm Nhiễm Sau Chấn Thương: Viêm nhiễm sau chấn thương là tình trạng mà Alphalysosine được sử dụng để điều trị.\nDược Liệu: Dược liệu là những thảo dược được sử dụng rộng rãi trong y học cổ truyền và cả trong việc điều chế thuốc hiện đại. Nhân dân có thể sử dụng dược liệu tươi trong nhiều trường hợp khác nhau. Dược liệu bao gồm các thành phần từ nhiều loại cây khác nhau, như cây cà na và cây bông ổi. Sau khi thu hái, dược liệu thường được rửa sạch và xử lý kỹ lưỡng để đảm bảo chất lượng. \n\nDược liệu không chỉ được sử dụng để điều trị các chứng bệnh cụ thể như ho do lạnh mà còn được sử dụng rộng rãi trong các bài thuốc chữa bệnh khác và trong cuộc sống hàng ngày để hỗ trợ sức khỏe tổng thể. Dược liệu cũng bao gồm toàn cây cỏ Bạc Đầu được sử dụng để làm thuốc. Hoa Quỳnh cũng được sử dụng làm dược liệu vì thành phần và tác dụng dược lý tốt của nó.\n\nDược liệu giúp duy trì mức bình thường của cortisol trong máu, chống oxy hóa, giảm viêm và sưng, giúp tiêu tiểu thông lợi, phòng viêm khớp và các tế bào ung thư. Ngoài ra, dược liệu còn được sử dụng để điều trị bệnh và là nguyên liệu dùng làm thuốc. Một số dược liệu đặc biệt được thu hái và chế biến từ Giảo cổ lam.\n\nTóm lại, dược liệu là một thuật ngữ chung để chỉ những thảo dược được sử dụng trong y học, với nhiều loại khác nhau được sử dụng cho mục đích điều trị và hỗ trợ sức khỏe.&lt;SEP&gt;Dược liệu là thành phần được sử dụng trong các bài thuốc chữa bệnh.&lt;SEP&gt;Dược liệu này có tác dụng tuyệt vời và được cung cấp thông tin về trong bài viết.&lt;SEP&gt;Dược liệu là thuật ngữ chung cho các loại thảo dược hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là các loại thảo mộc hoặc thực vật được sử dụng trong y học.&lt;SEP&gt;Dược liệu là nguyên liệu thảo dược, có hình dạng quả giống hình trứng, hơi dẹt, dài, cong, kích thước trung bình 5-7×2-3 mm, có bề mặt ngoài màu nâu xám, đốm đen, thường có khoảng 2 cạnh dọc, đỉnh quả hơi rộng, tù, có vòng tròn và vết vòi nhụy chính giữa, phần đáy hơi hẹp, vỏ quả cứng, bên trong chứa một hạt còn vỏ hạt thì mỏng mang 2 lá mầm trắng, có dầu.&lt;SEP&gt;Dược liệu là những nguyên liệu tự nhiên có tác dụng chữa bệnh khi sử dụng theo hướng dẫn của bác sĩ.\nAlphalysosine: Thuốc Alphalysosine được sử dụng để điều trị các bệnh lý và có thể gây ra một số tác dụng phụ như dị ứng.&lt;SEP&gt;Thuốc Alphalysosine chứa hoạt chất Serratiopeptidase, được sử dụng để điều trị các trường hợp viêm nhiễm sau phẫu thuật hay sau chấn thương.&lt;SEP&gt;Thuốc Alphalysosine có tác dụng phụ như hoa mắt, buồn ngủ, chóng mặt, rối loạn chức năng gan/thận, rối loạn tiêu hóa, dị ứng, và tương tác với thuốc chống đông.&lt;SEP&gt;Thuốc Alphalysosine được sử dụng bằng đường uống để điều trị các bệnh và triệu chứng như viêm nhiễm sau chấn thương hay phẫu thuật, bệnh trĩ, viêm xoang, viêm tai giữa, viêm họng, polyp mũi, viêm phế quản, hen phế quản, viêm phổi, lao, viêm nha chu, áp xe ổ răng, viêm túi lợi răng khôn, xuất huyết ở mắt, đục thủy tinh thể, căng tuyến vú, rách hoặc khâu tầng sinh môn ở sản phụ, và các bệnh đường tiết niệu.\nThiếu Máu Cơ Tim: Thiếu Máu Cơ Tim là một bệnh lý tim mạch nghiêm trọng được đề cập trong nhiều nguồn văn bản y học. Tình trạng này xảy ra khi cơ tim bị thiếu máu, gây ra bởi sự tắc nghẽn mạch máu và làm giảm lượng oxy đến cơ tim. Thiếu Máu Cơ Tim có thể dẫn đến tổn thương các cấu trúc của van tim và gây ra những hậu quả nghiêm trọng đối với sức khỏe tim mạch.\n\nCác triệu chứng của Thiếu Máu Cơ Tim bao gồm cảm giác khó chịu ở ngực, do tình trạng thiếu oxy và chất dinh dưỡng đến cơ tim. Bệnh này có thể được xem như là một dạng của bệnh mạch vành tim, trong đó mạch vành bị tắc nghẽn, dẫn đến giảm lượng máu đến tim.\n\nĐiều trị Thiếu Máu Cơ Tim thường bao gồm việc sử dụng các loại thuốc như nitrat, thuốc ức chế men chuyển Angiotensin, và Trimetazidin. Ngoài ra, thân rễ Dong riềng, cây trứng cá, và củ nén cũng được sử dụng như những phương pháp hỗ trợ tự nhiên nhằm mục đích ngăn chặn sự phát triển của bệnh và giảm thiểu tác động tiêu cực lên cơ tim. Các phương pháp điều trị này không chỉ giúp kiểm soát triệu chứng mà còn hỗ trợ trong việc ngăn chặn quá trình chết tự động của tế bào cơ tim.\n\nTóm lại, Thiếu Máu Cơ Tim là một bệnh lý tim mạch nghiêm trọng cần được điều trị kịp thời và hiệu quả để tránh những hậu quả nghiêm trọng đối với sức khỏe tim mạch.&lt;SEP&gt;Thiếu máu cơ tim là tình trạng bệnh tim cần lưu ý khi dùng Aluvia.&lt;SEP&gt;Thiếu máu cơ tim là tình trạng không nên dùng cisaprid.\nThiểu Năng Gan: Thiểu năng gan là bệnh lý mà Altamin được chỉ định điều trị.\nThuốc Trị Bệnh: Thuốc trị bệnh là các loại thuốc được sử dụng để điều trị các bệnh lý về tim mạch.\nCăng Tuyến Vú: Căng tuyến vú là triệu chứng được điều trị bằng Alphalysosine.\nRối Loạn Nhân Cách Phụ Thuộc: Người mắc rối loạn nhân cách phụ thuộc phụ thuộc rất nhiều vào người khác để đáp ứng nhu cầu về cảm xúc và thể chất, tránh ở một mình, cần sự yên tâm khi đưa ra quyết định và thường xuyên chịu đựng sự lạm dụng thể chất và lời nói từ người khác.&lt;SEP&gt;Rối loạn nhân cách phụ thuộc là một rối loạn sức khỏe tâm thần, thuộc nhóm C (Lo lắng) rối loạn nhân cách, trong đó người bệnh luôn đối mặt với cảm giác bất an và cần quá mức sự trấn an từ những người khác để hành động.&lt;SEP&gt;Rối loạn nhân cách phụ thuộc là tình trạng rối loạn nhân cách liên quan đến việc bị bỏ bê, ngược đãi và lạm dụng trong gia đình.&lt;SEP&gt;Rối loạn nhân cách phụ thuộc là bệnh rối loạn nhân cách, biểu hiện sự phụ thuộc vào người khác.&lt;SEP&gt;Rối loạn nhân cách phụ thuộc là tình trạng mà người mắc phải cần sự trấn an liên tục từ người khác và gặp khó khăn khi ở một mình.&lt;SEP&gt;Rối loạn nhân cách phụ thuộc là tình trạng心理健康系统已停止解析，但根据提供的文本内容，可以提取出以下实体和关系：&lt;SEP&gt;Rối loạn nhân cách phụ thuộc làm cho người bệnh sa sút về mặt tinh thần và gây ra sự mệt mỏi cho những người xung quanh.\nThời Gian Dùng: Thời gian dùng Albiomin tùy thuộc vào tình trạng bệnh và chỉ định điều trị.&lt;SEP&gt;Thời gian dùng là khoảng thời gian mà thuốc được sử dụng.\nThuốc Điều Trị: Thuốc Điều Trị là các loại thuốc được sử dụng để điều trị nhiều bệnh lý mạn tính, bao gồm cả những bệnh như lupus, bệnh teo đa hệ thống (MSA), và chảy dịch tai. Thuốc Điều Trị có thể cần dùng trong nhiều năm đối với những người mắc bệnh lupus ít bùng phát hoặc ít triệu chứng. Chúng giúp giảm triệu chứng trong bệnh MSA và làm cho cử động mềm hơn, ngăn ngừa tình trạng căng tức thành khi bị táo bón. \n\nTác dụng phụ phổ biến của Thuốc Điều Trị bao gồm mệt mỏi, đặc biệt khi sử dụng để điều trị động kinh. Thuốc Điều Trị có thể bị ảnh hưởng bởi Bibonlax khi sử dụng đồng thời, do đó cần lưu ý khi kê đơn và sử dụng cùng với các loại thuốc khác. Đối với trẻ sinh non có ống động mạch lớn, Thuốc Điều Trị có thể là một phần quan trọng trong quá trình điều trị.\n\nThuốc Điều Trị cũng được sử dụng để điều trị nấm da đầu, bao gồm cả thuốc uống và thuốc thoa. Tuy nhiên, Thuốc Điều Trị không được sử dụng để điều trị nang nước cạnh buồng trứng. Khi sử dụng Thuốc Điều Trị, cần thông báo cho bác sĩ về tình trạng bệnh lý phụ khoa. Ngoài ra, Thuốc Điều Trị cũng được sử dụng để điều trị rối loạn nhân cách phụ thuộc, cần được kê đơn bởi bác sĩ tâm lý.\n\nĐối với hội chứng Colic, không có thuốc điều trị cụ thể.&lt;SEP&gt;Thuốc điều trị rối loạn nhận thức thần kinh chưa được cấp phép.&lt;SEP&gt;Thuốc điều trị suy giáp bẩm sinh.&lt;SEP&gt;Thuốc được sử dụng nhằm mục đích ngăn chặn sự phát triển của các mạch máu mới và làm giảm sự rò rỉ dịch bên trong mắt gây nên bệnh thoái hóa điểm vàng thể ướt.\nRối Loạn Cương Dương: Rối loạn cương dương là một tình trạng y tế phức tạp liên quan đến khả năng cương cứng của dương vật ở nam giới. Đây là một vấn đề thường gặp, ảnh hưởng đến chất lượng cuộc sống của hàng nghìn nam giới. Rối loạn cương dương có thể xuất hiện ở những người bị ngưng thở khi ngủ và đặc biệt phổ biến khi tuổi tác tăng cao.\n\nNguyên nhân gây ra rối loạn cương dương rất đa dạng, bao gồm cả vấn đề về nội tiết tố và bệnh lý cụ thể. Một số nguyên nhân cụ thể bao gồm bệnh cường androgen, sự thiếu hụt androgen, suy sinh dục nam, bệnh tiểu đường, biến chứng dây thần kinh do đái tháo đường, bệnh động mạch ngoại biên, và dư thừa estrogen. Tình trạng này biểu hiện qua việc không thể đạt hoặc duy trì sự cương cứng cần thiết để thực hiện quan hệ tình dục.\n\nĐiều trị rối loạn cương dương thường bao gồm việc sử dụng các loại thuốc như sildenafil (Viagra). Trong một số trường hợp, rối loạn cương dương có thể là tác dụng phụ thường gặp khi sử dụng Biginol, trong khi Adagrin được sử dụng để điều trị tình trạng này. Ngoài ra, rối loạn cương dương cũng có thể là một triệu chứng gặp phải sau phẫu thuật. Rối loạn cương dương cũng là tình trạng mà Cialis được chỉ định và sử dụng để điều trị.\n\nTóm lại, rối loạn cương dương là một tình trạng phức tạp liên quan đến khả năng cương cứng của dương vật ở nam giới, với nhiều nguyên nhân khác nhau, từ vấn đề về nội tiết tố cho đến các bệnh lý cụ thể, và có thể được điều trị bằng nhiều phương pháp khác nhau.\nĐiều Trị Thuốc: Điều trị thuốc kết hợp vật lý trị liệu là phương pháp điều trị hàng đầu cho bệnh lý xương khớp.&lt;SEP&gt;Điều trị bằng thuốc cho nghiến răng ban đêm.&lt;SEP&gt;Điều trị thuốc là phương pháp điều trị rối loạn cương dương thông qua việc sử dụng thuốc.\nAlphalysosine - Tiêu Chảy: Tiêu chảy là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Tiêu chảy là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nBệnh - Thuốc: Thuốc được sử dụng để chữa bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Thuốc được sử dụng để điều trị bệnh.\nAlphalysosine - Buồn Nôn: Buồn nôn là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Buồn nôn là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nBệnh - Vị Thuốc: Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được dùng để điều trị bệnh.&lt;SEP&gt;Vị thuốc được sử dụng trong điều trị bệnh.\nAlphalysosine - Chóng Mặt: Chóng mặt là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Chóng mặt là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nBệnh Về Tiêu Hóa - Vị Thuốc: Vị thuốc được sử dụng để chữa bệnh về tiêu hóa.\nAlphalysosine - Đau Đầu: Đau đầu là tác dụng phụ của thuốc Alphalysosine.\nChữa Bệnh Di Tinh - Thuốc: Thuốc có thể được chỉ định dùng để chữa bệnh di tinh trong trường hợp nặng.\nAlphalysosine - Thận: Thận bị ảnh hưởng bởi rối loạn chức năng gan/thận do thuốc Alphalysosine.\nBệnh - Dược Liệu: Dược liệu được dùng để điều trị bệnh.&lt;SEP&gt;Dược liệu được sử dụng trong các bài thuốc chữa bệnh.\nAlphalysosine - Đau Bụng: Đau bụng là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Đau bụng là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nThiếu Máu Cơ Tim - Thuốc Trị Bệnh: Thuốc trị bệnh được sử dụng để điều trị tình trạng thiếu máu cơ tim.\nAlphalysosine - Dị Ứng: Dị ứng (phát ban, mẩn ngứa, nổi mề đay) là tác dụng phụ của thuốc Alphalysosine.\nRối Loạn Nhân Cách Phụ Thuộc - Thuốc Điều Trị: Thuốc điều trị là phương pháp sử dụng thuốc để điều trị rối loạn nhân cách phụ thuộc.\nAlphalysosine - Gan: Gan bị ảnh hưởng bởi rối loạn chức năng gan/thận do thuốc Alphalysosine.\nRối Loạn Cương Dương - Điều Trị Thuốc: Điều trị thuốc là phương pháp điều trị rối loạn cương dương thông qua việc sử dụng thuốc.\nAlphalysosine - Khó Thở: Khó thở là tác dụng phụ của thuốc Alphalysosine.\nTác Dụng Phụ - Điều Trị: Điều trị nhằm khắc phục và xử lý các tác dụng phụ của thuốc.\nAlphalysosine - Rối Loạn Tiêu Hóa: Rối loạn tiêu hóa, đau bụng, tiêu chảy, buồn nôn, nôn mửa là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Rối loạn tiêu hóa là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nThuốc - Động Kinh: Thuốc là phương pháp điều trị động kinh.\nAlphalysosine - Viêm Họng: Alphalysosine được sử dụng để điều trị viêm họng.\nAlphalysosine - Nôn Mửa: Nôn mửa là tác dụng phụ của thuốc Alphalysosine.\nAlphalysosine - Buồn Ngủ: Buồn ngủ là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Buồn ngủ là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nAlphalysosine - Phát Ban: Phát ban là tác dụng phụ của thuốc Alphalysosine.\nAlphalysosine - Viêm Phế Quản: Alphalysosine được sử dụng để điều trị viêm phế quản.\nAlphalysosine - Viêm Tai Giữa: Alphalysosine được sử dụng để điều trị viêm tai giữa.\nAlphalysosine - Viêm Phổi: Alphalysosine được sử dụng để điều trị viêm phổi.\nAlphalysosine - Viêm Xoang: Alphalysosine được sử dụng để điều trị viêm xoang.\nAlphachymotrypsin - Phụ Nữ Mang Thai: Không nên dùng Alphachymotrypsin trên phụ nữ mang thai.\nAlphalysosine - Hội Chứng Thận Hư: Hội chứng thận hư là bệnh chống chỉ định dùng Alphalysosine.\nAlphalysosine - Tác Dụng Phụ: Tác dụng phụ có thể xảy ra khi sử dụng Alphalysosine.\nAlphalysosine - Ngộ Độc: Ngộ độc là tác dụng phụ của thuốc Alphalysosine khi uống quá liều.\nAlphalysosine - Nổi Mề Đay: Nổi mề đay là tác dụng phụ của thuốc Alphalysosine.\nAlphalysosine - Bệnh Trĩ: Alphalysosine được sử dụng để điều trị bệnh trĩ.\nAlphalysosine - Mẩn Ngứa: Mẩn ngứa là tác dụng phụ của thuốc Alphalysosine.\nAlphalysosine - Hoa Mắt: Hoa mắt là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Hoa mắt là tác dụng phụ thường gặp khi sử dụng Alphalysosine.\nAlphalysosine - Polyp Mũi: Alphalysosine được sử dụng để điều trị polyp mũi.\nAlphalysosine - Hen Phế Quản: Alphalysosine được sử dụng để điều trị hen phế quản.\nAlphalysosine - Phù Nề: Alphalysosine được sử dụng để điều trị phù nề.\nAlphalysosine - Viêm Bàng Quang: Alphalysosine được sử dụng để điều trị viêm bàng quang.\nAlphalysosine - Khí Phế Thũng: Khí phế thũng là bệnh chống chỉ định dùng Alphalysosine.\nAlphalysosine - Thuốc Chống Đông: Thuốc Alphalysosine làm tăng tác dụng làm loãng máu của thuốc chống đông.\nAlphalysosine - Rối Loạn Đông Máu: Rối loạn đông máu là bệnh lý chống chỉ định khi sử dụng Alphalysosine.&lt;SEP&gt;Rối loạn đông máu là bệnh chống chỉ định dùng Alphalysosine.\nAlphalysosine - Loét Dạ Dày Tá Tràng: Loét dạ dày tá tràng là bệnh chống chỉ định dùng Alphalysosine.\nAlphalysosine - Viêm Nha Chu: Alphalysosine được sử dụng để điều trị viêm nha chu.\nAlphalysosine - Đục Thủy Tinh Thể: Alphalysosine được sử dụng để điều trị đục thủy tinh thể.\nThảo Dược - Thời Gian Dùng: Việc sử dụng thảo dược cần chú ý đến thời gian dùng.\nAlphalysosine - Lao: Alphalysosine được sử dụng để điều trị lao.\nAlphalysosine - Đau Tức Ngực: Đau tức ngực là tác dụng phụ của thuốc Alphalysosine.\nAlpha Chymotrypsine - Alphalysosine: Alphalysosine chứa hoạt chất Alpha chymotrypsine.\nAlphachymotrypsin - Sữa Mẹ: Không nên dùng Alphachymotrypsin trên phụ nữ đang cho con bú.\nAlphalysosine - Dược Sĩ Phan Tiểu Long: Dược sĩ Phan Tiểu Long cung cấp thông tin chi tiết về công dụng, cách dùng và tác dụng phụ của Alphalysosine.\nAlphalysosine - Thành Phần Thuốc: Alphalysosine chứa các thành phần hóa học.\nAlbiomin - Thời Gian Dùng: Liều và thời gian dùng Albiomin tùy thuộc vào tình trạng bệnh.\nAlphalysosine - Ánh Sáng Trực Tiếp: Ánh sáng trực tiếp có thể ảnh hưởng đến chất lượng của Alphalysosine.\nAlphalysosine - Viêm Mào Tinh: Alphalysosine được sử dụng để điều trị viêm mào tinh.\nAlphalysosine - Long Đàm: Alphalysosine được sử dụng để long đam trong các bệnh liên quan đến đường hô hấp.\nAlphalysosine - Serratiopeptidase: Alphalysosine chứa hoạt chất Serratiopeptidase.\nAlphalysosine - Áp Xe Ổ Răng: Alphalysosine được sử dụng để điều trị áp xe ổ răng.\nAlphalysosine - Phổi Tắc Nghẽn Mãn Tính: Phổi tắc nghẽn mãn tính là bệnh chống chỉ định dùng Alphalysosine.\nAlphalysosine - Tình Trạng Dị Ứng: Sử dụng Alphalysosine có thể gây ra tình trạng dị ứng.\nAlphalysosine - Rối Loạn Chức Năng Gan/Thận: Rối loạn chức năng gan/thận là tác dụng phụ của thuốc Alphalysosine.&lt;SEP&gt;Rối loạn chức năng gan/thận là tác dụng phụ nghiêm trọng của Alphalysosine.\nAlphalysosine - Rối Loạn Trầm Trọng Chức Năng Gan: Rối loạn trầm trọng chức năng gan là bệnh lý chống chỉ định khi sử dụng Alphalysosine.\nAlphalysosine - Rối Loạn Trầm Trọng Chức Năng Thận: Rối loạn trầm trọng chức năng thận là bệnh lý chống chỉ định khi sử dụng Alphalysosine.\nAlphalysosine - Viêm Nhiễm Sau Phẫu Thuật: Alphalysosine được sử dụng để điều trị viêm nhiễm sau phẫu thuật.\nAlphalysosine - Viêm Nhiễm Sau Chấn Thương: Alphalysosine được sử dụng để điều trị viêm nhiễm sau chấn thương.\nAlphalysosine - Viêm Nhiễm Sau Chấn Thương Hay Phẫu Thuật: Alphalysosine được sử dụng để điều trị viêm nhiễm sau chấn thương hay phẫu thuật.\nAlphalysosine - Viêm Túi Lợi Răng Khôn: Alphalysosine được sử dụng để điều trị viêm túi lợi răng khôn.\nAlphalysosine - Xuất Huyết Ở Mắt: Alphalysosine được sử dụng để điều trị xuất huyết ở mắt.\nAlphalysosine - Căng Tuyến Vú: Alphalysosine được sử dụng để điều trị căng tuyến vú.\nAlphalysosine - Rách Hoặc Khâu Tầng Sinh Môn: Alphalysosine được sử dụng để điều trị rách hoặc khâu tầng sinh môn ở sản phụ.\nAlphalysosine - NIC Pharma: NIC Pharma là công ty sản xuất thuốc Alphalysosine.\nAlphalysosine - Thời Tiết Phòng: Alphalysosine cần được bảo quản ở nhiệt độ phòng dưới 30°C.\nAlphalysosine - Bác Sỹ: Bác sĩ cung cấp tư vấn và hỗ trợ khi sử dụng Alphalysosine.\nAltamin - Thiểu Năng Gan: Altamin được chỉ định điều trị thiểu năng gan.\nChỉ Định - Thời Gian Dùng: Chỉ định liên quan đến thời gian dùng của thuốc.\nAlphachymotrypsin - Mebiphar: Mebiphar là công ty sản xuất Alphachymotrypsin.']</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị nhiều tình trạng và bệnh lý khác nhau, bao gồm:
+- Viêm nhiễm sau phẫu thuật hay chấn thương.
+- Bệnh trĩ (trĩ ngoại, trĩ nội), và sa hậu môn.
+- Viêm xoang, viêm tai giữa, viêm họng, polyp mũi.
+- Viêm nha chu, áp xe ổ răng, viêm túi lợi răng khôn.
+- Xuất huyết ở mắt, đục thủy tinh thể.
+- Căng tuyến vú, rách hoặc khâu tầng sinh môn ở sản phụ.
+- Bệnh đường tiết niệu như viêm bàng quang hay viêm mào tinh.
+### Tác dụng phụ và Lưu ý
+Khi sử dụng Alphalysosine, người bệnh có thể gặp phải một số tác dụng phụ như hoa mắt, buồn ngủ, chóng mặt, rối loạn chức năng gan/thận, rối loạn tiêu hóa, và dị ứng (phát ban, mẩn ngứa, nổi mề đay).
+### Đối tượng Chống Chỉ Định
+Thuốc Alphalysosine chống chỉ định với những bệnh nhân có tình trạng dị ứng với thuốc, khí phế thũng, phổi tắc nghẽn mãn tính, hội chứng thận hư, loét dạ dày tá tràng, và rối loạn đông máu.
+### Phụ nữ Có Thai và Mẹ Cho Con Bú
+Phụ nữ mang thai và mẹ cho con bú cần hỏi ý kiến bác sĩ trước khi sử dụng Alphalysosine do thiếu nghiên cứu đầy đủ về tác dụng của thuốc đối với phụ nữ trong thời kỳ mang thai hoặc cho con bú.
+### Liều Dùng
+Liều dùng của Alphalysosine sẽ phụ thuộc vào từng đối tượng bệnh nhân mà bác sĩ sẽ chỉ định liều phù hợp. Người lớn thường được chỉ định 1–2 viên trong 2–3 lần/ngày. Đối với trẻ em, liều dùng sẽ được chỉ định bởi bác sĩ nhi khoa.
+### Bảo Quản
+Thuốc Alphalysosine cần được bảo quản trong hộp kín, tránh ánh sáng trực tiếp, và giữ ở nhiệt độ phòng (dưới 30°C).
+### Giá Thuốc
+Giá tham khảo của thuốc Alphalysosine là 40.000 VNĐ cho hộp 20 vỉ x 10 viên.
+### Tổng Kết
+Thuốc Alphalysosine là một lựa chọn điều trị cho các tình trạng viêm nhiễm sau phẫu thuật hay chấn thương, và nhiều bệnh lý khác. Tuy nhiên, việc sử dụng cần tuân theo chỉ định của bác sĩ và chú ý đến các tác dụng phụ có thể xảy ra.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Thuốc Alphalysosine được sử dụng để điều trị các trường hợp viêm nhiễm sau phẫu thuật hay sau chấn thương.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.8315580892704135</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mix</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.912434976838058</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naive_Mean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Naive_Median</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Naive_Std</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Naive_Min</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Naive_Max</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid_Mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid_Median</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid_Std</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid_Min</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid_Max</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mix_Mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mix_Median</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mix_Std</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mix_Min</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Mix_Max</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spread_max_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Faithfulness</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Mix</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4021</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Answer Relevancy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9679</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8205</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4876</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Mix</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0896</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Context Recall</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6619</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Mix</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0786</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Context Precision</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Mix</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>RAGAS Score</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.375</v>
+        <v>0.3931</v>
       </c>
       <c r="C6" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>0.4359</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2035</v>
+      </c>
       <c r="E6" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.375</v>
+        <v>0.7159</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1667</v>
+        <v>0.6664</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.6818</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2154</v>
+      </c>
       <c r="J6" t="n">
-        <v>0.1667</v>
+        <v>0.2301</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Naive</t>
-        </is>
+        <v>0.992</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7439</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2083</v>
+        <v>0.7713</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Mix</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3507</v>
       </c>
     </row>
   </sheetData>
